--- a/data/50001557 - ATACAMA KOZAN OT4340.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4340.xlsx
@@ -1620,13 +1620,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46169.39133378472</v>
+        <v>46169.55800045139</v>
       </c>
       <c r="C4" s="5">
-        <v>46181.45679118056</v>
+        <v>46181.62345784722</v>
       </c>
       <c r="D4" s="5">
-        <v>46181.45680876158</v>
+        <v>46181.62347542824</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1673,13 +1673,13 @@
         <v>28</v>
       </c>
       <c r="B5" s="9">
-        <v>46169.39146962963</v>
+        <v>46169.5581362963</v>
       </c>
       <c r="C5" s="9">
-        <v>46181.45679953704</v>
+        <v>46181.6234662037</v>
       </c>
       <c r="D5" s="9">
-        <v>46181.456813819445</v>
+        <v>46181.623480486116</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>29</v>
@@ -1736,13 +1736,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46169.39147307871</v>
+        <v>46169.55813974537</v>
       </c>
       <c r="C6" s="5">
-        <v>46181.45680732639</v>
+        <v>46181.62347399305</v>
       </c>
       <c r="D6" s="5">
-        <v>46181.457589259255</v>
+        <v>46181.624255925926</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -1799,13 +1799,13 @@
         <v>36</v>
       </c>
       <c r="B7" s="9">
-        <v>46169.39147766204</v>
+        <v>46169.55814432871</v>
       </c>
       <c r="C7" s="9">
-        <v>46181.45681351852</v>
+        <v>46181.62348018518</v>
       </c>
       <c r="D7" s="9">
-        <v>46181.45683121528</v>
+        <v>46181.62349788194</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>37</v>
@@ -1862,13 +1862,13 @@
         <v>39</v>
       </c>
       <c r="B8" s="5">
-        <v>46169.39148107639</v>
+        <v>46169.55814774305</v>
       </c>
       <c r="C8" s="5">
-        <v>46181.45681916666</v>
+        <v>46181.623485833334</v>
       </c>
       <c r="D8" s="5">
-        <v>46181.45683517361</v>
+        <v>46181.62350184028</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>40</v>
@@ -1925,13 +1925,13 @@
         <v>43</v>
       </c>
       <c r="B9" s="9">
-        <v>46169.39148497685</v>
+        <v>46169.55815164352</v>
       </c>
       <c r="C9" s="9">
-        <v>46181.456824953704</v>
+        <v>46181.62349162037</v>
       </c>
       <c r="D9" s="9">
-        <v>46181.456841736115</v>
+        <v>46181.62350840278</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>44</v>
@@ -1988,11 +1988,11 @@
         <v>46</v>
       </c>
       <c r="B10" s="5">
-        <v>46169.391342731484</v>
+        <v>46169.55800939815</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46181.45772957176</v>
+        <v>46181.624396238425</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>47</v>
@@ -2035,13 +2035,13 @@
         <v>49</v>
       </c>
       <c r="B11" s="9">
-        <v>46169.391519004625</v>
+        <v>46169.558185671296</v>
       </c>
       <c r="C11" s="9">
-        <v>46181.4576984375</v>
+        <v>46181.624365104166</v>
       </c>
       <c r="D11" s="9">
-        <v>46181.45772152778</v>
+        <v>46181.62438819444</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>50</v>
@@ -2100,13 +2100,13 @@
         <v>55</v>
       </c>
       <c r="B12" s="5">
-        <v>46169.39152517361</v>
+        <v>46169.558191840275</v>
       </c>
       <c r="C12" s="5">
-        <v>46181.457710393515</v>
+        <v>46181.62437706019</v>
       </c>
       <c r="D12" s="5">
-        <v>46181.457725706015</v>
+        <v>46181.62439237269</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>56</v>
@@ -2165,13 +2165,13 @@
         <v>59</v>
       </c>
       <c r="B13" s="9">
-        <v>46169.39153075231</v>
+        <v>46169.558197418984</v>
       </c>
       <c r="C13" s="9">
-        <v>46181.45772287037</v>
+        <v>46181.624389537035</v>
       </c>
       <c r="D13" s="9">
-        <v>46181.457897546294</v>
+        <v>46181.624564212965</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>60</v>
@@ -2230,11 +2230,11 @@
         <v>62</v>
       </c>
       <c r="B14" s="5">
-        <v>46169.39153793981</v>
+        <v>46169.55820460648</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5">
-        <v>46181.457743113424</v>
+        <v>46181.624409780095</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>63</v>
@@ -2293,11 +2293,11 @@
         <v>66</v>
       </c>
       <c r="B15" s="9">
-        <v>46169.39134710648</v>
+        <v>46169.558013773145</v>
       </c>
       <c r="C15" s="10"/>
       <c r="D15" s="9">
-        <v>46183.73998796297</v>
+        <v>46183.90665462963</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>67</v>
@@ -2342,13 +2342,13 @@
         <v>69</v>
       </c>
       <c r="B16" s="5">
-        <v>46169.39154689814</v>
+        <v>46169.558213564815</v>
       </c>
       <c r="C16" s="5">
-        <v>46181.45778030093</v>
+        <v>46181.62444696759</v>
       </c>
       <c r="D16" s="5">
-        <v>46181.4577971875</v>
+        <v>46181.62446385417</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>70</v>
@@ -2407,13 +2407,13 @@
         <v>72</v>
       </c>
       <c r="B17" s="9">
-        <v>46169.3915578125</v>
+        <v>46169.558224479166</v>
       </c>
       <c r="C17" s="9">
-        <v>46181.457787060186</v>
+        <v>46181.62445372685</v>
       </c>
       <c r="D17" s="9">
-        <v>46181.45780335648</v>
+        <v>46181.62447002315</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>73</v>
@@ -2472,13 +2472,13 @@
         <v>75</v>
       </c>
       <c r="B18" s="5">
-        <v>46169.39156415509</v>
+        <v>46169.558230821756</v>
       </c>
       <c r="C18" s="5">
-        <v>46183.73984991898</v>
+        <v>46183.906516585645</v>
       </c>
       <c r="D18" s="5">
-        <v>46183.73985265046</v>
+        <v>46183.90651931713</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>76</v>
@@ -2537,13 +2537,13 @@
         <v>79</v>
       </c>
       <c r="B19" s="9">
-        <v>46169.391569803236</v>
+        <v>46169.55823646991</v>
       </c>
       <c r="C19" s="9">
-        <v>46183.73996832176</v>
+        <v>46183.90663498842</v>
       </c>
       <c r="D19" s="9">
-        <v>46183.73998440972</v>
+        <v>46183.90665107639</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>80</v>
@@ -2602,13 +2602,13 @@
         <v>85</v>
       </c>
       <c r="B20" s="5">
-        <v>46169.39157504629</v>
+        <v>46169.55824171296</v>
       </c>
       <c r="C20" s="5">
-        <v>46183.739979872684</v>
+        <v>46183.906646539355</v>
       </c>
       <c r="D20" s="5">
-        <v>46183.73999503472</v>
+        <v>46183.90666170139</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>86</v>
@@ -2667,11 +2667,11 @@
         <v>88</v>
       </c>
       <c r="B21" s="9">
-        <v>46169.39157907407</v>
+        <v>46169.55824574074</v>
       </c>
       <c r="C21" s="10"/>
       <c r="D21" s="9">
-        <v>46185.55507282408</v>
+        <v>46185.72173949074</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>89</v>
@@ -2730,13 +2730,13 @@
         <v>91</v>
       </c>
       <c r="B22" s="5">
-        <v>46169.39158340278</v>
+        <v>46169.55825006944</v>
       </c>
       <c r="C22" s="5">
-        <v>46183.74067290509</v>
+        <v>46183.90733957176</v>
       </c>
       <c r="D22" s="5">
-        <v>46183.74068726852</v>
+        <v>46183.90735393518</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>92</v>
@@ -2795,11 +2795,11 @@
         <v>94</v>
       </c>
       <c r="B23" s="9">
-        <v>46169.39135159722</v>
+        <v>46169.55801826389</v>
       </c>
       <c r="C23" s="10"/>
       <c r="D23" s="9">
-        <v>46184.56981677083</v>
+        <v>46184.736483437504</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>95</v>
@@ -2844,13 +2844,13 @@
         <v>97</v>
       </c>
       <c r="B24" s="5">
-        <v>46169.39163528935</v>
+        <v>46169.558301956014</v>
       </c>
       <c r="C24" s="5">
-        <v>46182.506723715276</v>
+        <v>46182.67339038194</v>
       </c>
       <c r="D24" s="5">
-        <v>46182.506736875</v>
+        <v>46182.67340354167</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>98</v>
@@ -2909,13 +2909,13 @@
         <v>102</v>
       </c>
       <c r="B25" s="9">
-        <v>46169.391639849535</v>
+        <v>46169.558306516206</v>
       </c>
       <c r="C25" s="9">
-        <v>46182.46699027778</v>
+        <v>46182.63365694444</v>
       </c>
       <c r="D25" s="9">
-        <v>46182.46699188657</v>
+        <v>46182.63365855324</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>103</v>
@@ -2970,13 +2970,13 @@
         <v>106</v>
       </c>
       <c r="B26" s="5">
-        <v>46169.391644710646</v>
+        <v>46169.55831137732</v>
       </c>
       <c r="C26" s="5">
-        <v>46182.50670748843</v>
+        <v>46182.67337415509</v>
       </c>
       <c r="D26" s="5">
-        <v>46182.50670925926</v>
+        <v>46182.67337592592</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>107</v>
@@ -3031,13 +3031,13 @@
         <v>109</v>
       </c>
       <c r="B27" s="9">
-        <v>46169.39164938657</v>
+        <v>46169.55831605324</v>
       </c>
       <c r="C27" s="9">
-        <v>46184.569797442135</v>
+        <v>46184.73646410879</v>
       </c>
       <c r="D27" s="9">
-        <v>46184.569945138894</v>
+        <v>46184.73661180555</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>110</v>
@@ -3096,13 +3096,13 @@
         <v>112</v>
       </c>
       <c r="B28" s="5">
-        <v>46169.391653969906</v>
+        <v>46169.55832063657</v>
       </c>
       <c r="C28" s="5">
-        <v>46184.56974114584</v>
+        <v>46184.736407812496</v>
       </c>
       <c r="D28" s="5">
-        <v>46184.56974306713</v>
+        <v>46184.7364097338</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>113</v>
@@ -3157,13 +3157,13 @@
         <v>115</v>
       </c>
       <c r="B29" s="9">
-        <v>46169.39165872685</v>
+        <v>46169.55832539352</v>
       </c>
       <c r="C29" s="9">
-        <v>46184.569781342594</v>
+        <v>46184.73644800926</v>
       </c>
       <c r="D29" s="9">
-        <v>46184.569782708335</v>
+        <v>46184.736449375</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>116</v>
@@ -3218,13 +3218,13 @@
         <v>118</v>
       </c>
       <c r="B30" s="5">
-        <v>46169.39166340278</v>
+        <v>46169.55833006944</v>
       </c>
       <c r="C30" s="5">
-        <v>46182.50683622685</v>
+        <v>46182.67350289352</v>
       </c>
       <c r="D30" s="5">
-        <v>46182.506847488425</v>
+        <v>46182.67351415509</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>119</v>
@@ -3283,13 +3283,13 @@
         <v>121</v>
       </c>
       <c r="B31" s="9">
-        <v>46169.39166819444</v>
+        <v>46169.55833486111</v>
       </c>
       <c r="C31" s="9">
-        <v>46182.466928622685</v>
+        <v>46182.63359528936</v>
       </c>
       <c r="D31" s="9">
-        <v>46182.466930752315</v>
+        <v>46182.633597418986</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>122</v>
@@ -3344,13 +3344,13 @@
         <v>124</v>
       </c>
       <c r="B32" s="5">
-        <v>46169.39167359954</v>
+        <v>46169.5583402662</v>
       </c>
       <c r="C32" s="5">
-        <v>46182.50676563657</v>
+        <v>46182.67343230324</v>
       </c>
       <c r="D32" s="5">
-        <v>46182.506766990744</v>
+        <v>46182.67343365741</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>125</v>
@@ -3405,13 +3405,13 @@
         <v>127</v>
       </c>
       <c r="B33" s="9">
-        <v>46169.391678368054</v>
+        <v>46169.55834503472</v>
       </c>
       <c r="C33" s="9">
-        <v>46182.50682142361</v>
+        <v>46182.67348809028</v>
       </c>
       <c r="D33" s="9">
-        <v>46182.506822766205</v>
+        <v>46182.67348943287</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>128</v>
@@ -3466,13 +3466,13 @@
         <v>130</v>
       </c>
       <c r="B34" s="5">
-        <v>46169.39169668981</v>
+        <v>46169.55836335648</v>
       </c>
       <c r="C34" s="5">
-        <v>46184.36596177083</v>
+        <v>46184.532628437504</v>
       </c>
       <c r="D34" s="5">
-        <v>46184.36597520833</v>
+        <v>46184.532641875005</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>131</v>
@@ -3531,13 +3531,13 @@
         <v>135</v>
       </c>
       <c r="B35" s="9">
-        <v>46169.391701319444</v>
+        <v>46169.558367986116</v>
       </c>
       <c r="C35" s="9">
-        <v>46184.36579065972</v>
+        <v>46184.53245732639</v>
       </c>
       <c r="D35" s="9">
-        <v>46184.365792083336</v>
+        <v>46184.53245875</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>136</v>
@@ -3592,13 +3592,13 @@
         <v>138</v>
       </c>
       <c r="B36" s="5">
-        <v>46169.39170626157</v>
+        <v>46169.55837292824</v>
       </c>
       <c r="C36" s="5">
-        <v>46184.36594700231</v>
+        <v>46184.532613668984</v>
       </c>
       <c r="D36" s="5">
-        <v>46184.365949189814</v>
+        <v>46184.532615856486</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>139</v>
@@ -3653,13 +3653,13 @@
         <v>141</v>
       </c>
       <c r="B37" s="9">
-        <v>46169.391711585646</v>
+        <v>46169.55837825232</v>
       </c>
       <c r="C37" s="9">
-        <v>46184.36590456018</v>
+        <v>46184.53257122685</v>
       </c>
       <c r="D37" s="9">
-        <v>46184.36591527778</v>
+        <v>46184.53258194444</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>142</v>
@@ -3718,13 +3718,13 @@
         <v>144</v>
       </c>
       <c r="B38" s="5">
-        <v>46169.3917153125</v>
+        <v>46169.558381979165</v>
       </c>
       <c r="C38" s="5">
-        <v>46184.365538680555</v>
+        <v>46184.53220534722</v>
       </c>
       <c r="D38" s="5">
-        <v>46184.365540520834</v>
+        <v>46184.5322071875</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>87</v>
@@ -3773,13 +3773,13 @@
         <v>146</v>
       </c>
       <c r="B39" s="9">
-        <v>46169.391719907406</v>
+        <v>46169.55838657408</v>
       </c>
       <c r="C39" s="9">
-        <v>46184.36588817129</v>
+        <v>46184.53255483796</v>
       </c>
       <c r="D39" s="9">
-        <v>46184.36588965278</v>
+        <v>46184.53255631945</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>147</v>
@@ -3828,11 +3828,11 @@
         <v>149</v>
       </c>
       <c r="B40" s="5">
-        <v>46169.391724409725</v>
+        <v>46169.55839107639</v>
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="5">
-        <v>46185.68889402778</v>
+        <v>46185.85556069444</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>150</v>
@@ -3891,11 +3891,11 @@
         <v>154</v>
       </c>
       <c r="B41" s="9">
-        <v>46169.39172811343</v>
+        <v>46169.55839478009</v>
       </c>
       <c r="C41" s="10"/>
       <c r="D41" s="9">
-        <v>46183.74067875</v>
+        <v>46183.907345416665</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>93</v>
@@ -3944,11 +3944,11 @@
         <v>156</v>
       </c>
       <c r="B42" s="5">
-        <v>46169.391732442135</v>
+        <v>46169.55839910879</v>
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="5">
-        <v>46169.65947974537</v>
+        <v>46169.82614641204</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>157</v>
@@ -3997,11 +3997,11 @@
         <v>159</v>
       </c>
       <c r="B43" s="9">
-        <v>46169.39173688657</v>
+        <v>46169.55840355324</v>
       </c>
       <c r="C43" s="10"/>
       <c r="D43" s="9">
-        <v>46169.659498877314</v>
+        <v>46169.826165543986</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>160</v>
@@ -4050,11 +4050,11 @@
         <v>163</v>
       </c>
       <c r="B44" s="5">
-        <v>46169.39174010417</v>
+        <v>46169.55840677083</v>
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="5">
-        <v>46169.65910377315</v>
+        <v>46169.82577043981</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>164</v>
@@ -4113,11 +4113,11 @@
         <v>166</v>
       </c>
       <c r="B45" s="9">
-        <v>46169.3917437037</v>
+        <v>46169.55841037037</v>
       </c>
       <c r="C45" s="10"/>
       <c r="D45" s="9">
-        <v>46169.65940934028</v>
+        <v>46169.826076006946</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>90</v>
@@ -4166,11 +4166,11 @@
         <v>168</v>
       </c>
       <c r="B46" s="5">
-        <v>46169.39179155092</v>
+        <v>46169.558458217594</v>
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46169.65942739583</v>
+        <v>46169.826094062504</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>169</v>
@@ -4219,11 +4219,11 @@
         <v>171</v>
       </c>
       <c r="B47" s="9">
-        <v>46169.391797662036</v>
+        <v>46169.5584643287</v>
       </c>
       <c r="C47" s="10"/>
       <c r="D47" s="9">
-        <v>46182.59295664352</v>
+        <v>46182.75962331019</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>172</v>
@@ -4268,13 +4268,13 @@
         <v>174</v>
       </c>
       <c r="B48" s="5">
-        <v>46169.39180146991</v>
+        <v>46169.55846813657</v>
       </c>
       <c r="C48" s="5">
-        <v>46181.559978171295</v>
+        <v>46181.72664483797</v>
       </c>
       <c r="D48" s="5">
-        <v>46185.03877824074</v>
+        <v>46185.205444907406</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>175</v>
@@ -4333,13 +4333,13 @@
         <v>180</v>
       </c>
       <c r="B49" s="9">
-        <v>46169.391806099535</v>
+        <v>46169.558472766206</v>
       </c>
       <c r="C49" s="9">
-        <v>46181.55996236111</v>
+        <v>46181.72662902778</v>
       </c>
       <c r="D49" s="9">
-        <v>46181.559963900465</v>
+        <v>46181.72663056713</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>178</v>
@@ -4388,13 +4388,13 @@
         <v>182</v>
       </c>
       <c r="B50" s="5">
-        <v>46169.391832719906</v>
+        <v>46169.55849938658</v>
       </c>
       <c r="C50" s="5">
-        <v>46182.59293549768</v>
+        <v>46182.759602164355</v>
       </c>
       <c r="D50" s="5">
-        <v>46182.59294935185</v>
+        <v>46182.75961601852</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>183</v>
@@ -4453,13 +4453,13 @@
         <v>184</v>
       </c>
       <c r="B51" s="9">
-        <v>46169.391837048606</v>
+        <v>46169.55850371528</v>
       </c>
       <c r="C51" s="9">
-        <v>46182.59291894676</v>
+        <v>46182.75958561343</v>
       </c>
       <c r="D51" s="9">
-        <v>46182.59292081019</v>
+        <v>46182.75958747685</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>178</v>
@@ -4508,13 +4508,13 @@
         <v>187</v>
       </c>
       <c r="B52" s="5">
-        <v>46169.39186561343</v>
+        <v>46169.55853228009</v>
       </c>
       <c r="C52" s="5">
-        <v>46182.59319480324</v>
+        <v>46182.75986146991</v>
       </c>
       <c r="D52" s="5">
-        <v>46182.59320440972</v>
+        <v>46182.759871076385</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>83</v>
@@ -4573,13 +4573,13 @@
         <v>189</v>
       </c>
       <c r="B53" s="9">
-        <v>46169.391879745366</v>
+        <v>46169.55854641204</v>
       </c>
       <c r="C53" s="9">
-        <v>46182.59318045139</v>
+        <v>46182.75984711805</v>
       </c>
       <c r="D53" s="9">
-        <v>46182.59318215278</v>
+        <v>46182.75984881945</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>178</v>
@@ -4628,11 +4628,11 @@
         <v>190</v>
       </c>
       <c r="B54" s="5">
-        <v>46169.3918991088</v>
+        <v>46169.558565775464</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46169.4521927662</v>
+        <v>46169.61885943287</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>191</v>
@@ -4691,11 +4691,11 @@
         <v>194</v>
       </c>
       <c r="B55" s="9">
-        <v>46169.391903055555</v>
+        <v>46169.55856972223</v>
       </c>
       <c r="C55" s="10"/>
       <c r="D55" s="9">
-        <v>46169.45215946759</v>
+        <v>46169.61882613426</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>178</v>
@@ -4744,11 +4744,11 @@
         <v>197</v>
       </c>
       <c r="B56" s="5">
-        <v>46169.3919196412</v>
+        <v>46169.558586307874</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46169.4259368287</v>
+        <v>46169.59260349537</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>198</v>
@@ -4791,11 +4791,11 @@
         <v>200</v>
       </c>
       <c r="B57" s="9">
-        <v>46169.39192278935</v>
+        <v>46169.55858945602</v>
       </c>
       <c r="C57" s="10"/>
       <c r="D57" s="9">
-        <v>46184.36596471065</v>
+        <v>46184.53263137731</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>201</v>
@@ -4854,11 +4854,11 @@
         <v>205</v>
       </c>
       <c r="B58" s="5">
-        <v>46169.39192821759</v>
+        <v>46169.55859488426</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46169.4536446875</v>
+        <v>46169.62031135417</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>206</v>
@@ -4917,11 +4917,11 @@
         <v>209</v>
       </c>
       <c r="B59" s="9">
-        <v>46169.391934513886</v>
+        <v>46169.55860118056</v>
       </c>
       <c r="C59" s="10"/>
       <c r="D59" s="9">
-        <v>46184.365908252315</v>
+        <v>46184.53257491898</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>210</v>
@@ -4980,11 +4980,11 @@
         <v>212</v>
       </c>
       <c r="B60" s="5">
-        <v>46169.391939699075</v>
+        <v>46169.55860636574</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46169.45364133102</v>
+        <v>46169.620307997684</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>213</v>
@@ -5043,11 +5043,11 @@
         <v>214</v>
       </c>
       <c r="B61" s="9">
-        <v>46169.39198346065</v>
+        <v>46169.558650127314</v>
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="9">
-        <v>46169.453549328704</v>
+        <v>46169.62021599537</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>215</v>
@@ -5106,11 +5106,11 @@
         <v>217</v>
       </c>
       <c r="B62" s="5">
-        <v>46169.391989421296</v>
+        <v>46169.55865608796</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46169.453636817125</v>
+        <v>46169.620303483796</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>216</v>
@@ -5169,11 +5169,11 @@
         <v>218</v>
       </c>
       <c r="B63" s="9">
-        <v>46169.39199438658</v>
+        <v>46169.55866105324</v>
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="9">
-        <v>46169.434008599535</v>
+        <v>46169.60067526621</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>219</v>
@@ -5216,11 +5216,11 @@
         <v>221</v>
       </c>
       <c r="B64" s="5">
-        <v>46169.391998032406</v>
+        <v>46169.55866469907</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46184.74444202546</v>
+        <v>46184.91110869213</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>222</v>
@@ -5279,11 +5279,11 @@
         <v>226</v>
       </c>
       <c r="B65" s="9">
-        <v>46169.39200432871</v>
+        <v>46169.55867099537</v>
       </c>
       <c r="C65" s="10"/>
       <c r="D65" s="9">
-        <v>46169.45392881944</v>
+        <v>46169.62059548611</v>
       </c>
       <c r="E65" s="10" t="s">
         <v>178</v>
@@ -5332,11 +5332,11 @@
         <v>229</v>
       </c>
       <c r="B66" s="5">
-        <v>46169.39203685185</v>
+        <v>46169.558703518516</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46184.75501782408</v>
+        <v>46184.92168449074</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>230</v>
@@ -5395,11 +5395,11 @@
         <v>231</v>
       </c>
       <c r="B67" s="9">
-        <v>46169.39204212963</v>
+        <v>46169.55870879629</v>
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="9">
-        <v>46182.59321112269</v>
+        <v>46182.75987778935</v>
       </c>
       <c r="E67" s="10" t="s">
         <v>178</v>
@@ -5448,11 +5448,11 @@
         <v>234</v>
       </c>
       <c r="B68" s="5">
-        <v>46169.392073958334</v>
+        <v>46169.558740625</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46169.45418033565</v>
+        <v>46169.62084700231</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>235</v>
@@ -5511,11 +5511,11 @@
         <v>236</v>
       </c>
       <c r="B69" s="9">
-        <v>46169.39207857639</v>
+        <v>46169.558745243055</v>
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="9">
-        <v>46182.59320952547</v>
+        <v>46182.759876192125</v>
       </c>
       <c r="E69" s="10" t="s">
         <v>178</v>
@@ -5564,11 +5564,11 @@
         <v>238</v>
       </c>
       <c r="B70" s="5">
-        <v>46169.392102812504</v>
+        <v>46169.55876947917</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46169.43569912037</v>
+        <v>46169.60236578704</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>198</v>
@@ -5611,11 +5611,11 @@
         <v>240</v>
       </c>
       <c r="B71" s="9">
-        <v>46169.39213966436</v>
+        <v>46169.55880633101</v>
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="9">
-        <v>46184.56980002315</v>
+        <v>46184.736466689814</v>
       </c>
       <c r="E71" s="10" t="s">
         <v>241</v>
@@ -5674,11 +5674,11 @@
         <v>243</v>
       </c>
       <c r="B72" s="5">
-        <v>46169.39215109954</v>
+        <v>46169.5588177662</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46182.50672740741</v>
+        <v>46182.673394074074</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>244</v>
@@ -5737,11 +5737,11 @@
         <v>246</v>
       </c>
       <c r="B73" s="9">
-        <v>46169.392156284724</v>
+        <v>46169.55882295139</v>
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="9">
-        <v>46182.50678083333</v>
+        <v>46182.6734475</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>247</v>
@@ -5800,11 +5800,11 @@
         <v>248</v>
       </c>
       <c r="B74" s="5">
-        <v>46169.39216121528</v>
+        <v>46169.55882788195</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46169.45425175926</v>
+        <v>46169.62091842592</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>249</v>
@@ -5863,11 +5863,11 @@
         <v>251</v>
       </c>
       <c r="B75" s="9">
-        <v>46169.392175879635</v>
+        <v>46169.55884254629</v>
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="9">
-        <v>46169.4385300463</v>
+        <v>46169.60519671296</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>252</v>
@@ -5910,11 +5910,11 @@
         <v>254</v>
       </c>
       <c r="B76" s="5">
-        <v>46169.39217881944</v>
+        <v>46169.55884548611</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46169.45435756944</v>
+        <v>46169.62102423611</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>255</v>
@@ -5973,11 +5973,11 @@
         <v>257</v>
       </c>
       <c r="B77" s="9">
-        <v>46169.39218326389</v>
+        <v>46169.55884993056</v>
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="9">
-        <v>46169.454309872686</v>
+        <v>46169.62097653935</v>
       </c>
       <c r="E77" s="10" t="s">
         <v>178</v>
@@ -6026,11 +6026,11 @@
         <v>259</v>
       </c>
       <c r="B78" s="5">
-        <v>46169.39226503472</v>
+        <v>46169.55893170139</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46169.45449284722</v>
+        <v>46169.62115951389</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>260</v>
@@ -6089,11 +6089,11 @@
         <v>261</v>
       </c>
       <c r="B79" s="9">
-        <v>46169.39226877315</v>
+        <v>46169.55893543981</v>
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="9">
-        <v>46182.59321179398</v>
+        <v>46182.75987846065</v>
       </c>
       <c r="E79" s="10" t="s">
         <v>178</v>
@@ -6142,11 +6142,11 @@
         <v>264</v>
       </c>
       <c r="B80" s="5">
-        <v>46169.39220289352</v>
+        <v>46169.558869560184</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46169.45459944445</v>
+        <v>46169.621266111106</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>265</v>
@@ -6205,11 +6205,11 @@
         <v>266</v>
       </c>
       <c r="B81" s="9">
-        <v>46169.392206296296</v>
+        <v>46169.55887296297</v>
       </c>
       <c r="C81" s="10"/>
       <c r="D81" s="9">
-        <v>46182.59321024305</v>
+        <v>46182.759876909724</v>
       </c>
       <c r="E81" s="10" t="s">
         <v>195</v>
@@ -6258,11 +6258,11 @@
         <v>269</v>
       </c>
       <c r="B82" s="5">
-        <v>46169.392235879626</v>
+        <v>46169.5589025463</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46169.454685150464</v>
+        <v>46169.62135181713</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>270</v>
@@ -6321,11 +6321,11 @@
         <v>271</v>
       </c>
       <c r="B83" s="9">
-        <v>46169.39223943287</v>
+        <v>46169.55890609954</v>
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="9">
-        <v>46182.59321077546</v>
+        <v>46182.759877442135</v>
       </c>
       <c r="E83" s="10" t="s">
         <v>178</v>
@@ -6374,11 +6374,11 @@
         <v>274</v>
       </c>
       <c r="B84" s="5">
-        <v>46169.3923377662</v>
+        <v>46169.55900443287</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46169.45477751158</v>
+        <v>46169.621444178236</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>275</v>
@@ -6437,11 +6437,11 @@
         <v>276</v>
       </c>
       <c r="B85" s="9">
-        <v>46169.39234335648</v>
+        <v>46169.55901002315</v>
       </c>
       <c r="C85" s="10"/>
       <c r="D85" s="9">
-        <v>46169.45474056713</v>
+        <v>46169.6214072338</v>
       </c>
       <c r="E85" s="10" t="s">
         <v>195</v>
@@ -6490,11 +6490,11 @@
         <v>278</v>
       </c>
       <c r="B86" s="5">
-        <v>46169.39237796296</v>
+        <v>46169.55904462963</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46169.454865057865</v>
+        <v>46169.62153172454</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>279</v>
@@ -6553,11 +6553,11 @@
         <v>281</v>
       </c>
       <c r="B87" s="9">
-        <v>46169.39238347222</v>
+        <v>46169.559050138894</v>
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="9">
-        <v>46169.454824872686</v>
+        <v>46169.62149153935</v>
       </c>
       <c r="E87" s="10" t="s">
         <v>195</v>
@@ -6606,11 +6606,11 @@
         <v>283</v>
       </c>
       <c r="B88" s="5">
-        <v>46169.39240818287</v>
+        <v>46169.55907484954</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46169.4395678588</v>
+        <v>46169.60623452546</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>284</v>
@@ -6653,11 +6653,11 @@
         <v>286</v>
       </c>
       <c r="B89" s="9">
-        <v>46169.392411967594</v>
+        <v>46169.55907863426</v>
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="9">
-        <v>46169.45497726851</v>
+        <v>46169.621643935185</v>
       </c>
       <c r="E89" s="10" t="s">
         <v>287</v>
@@ -6716,11 +6716,11 @@
         <v>290</v>
       </c>
       <c r="B90" s="5">
-        <v>46169.39242017361</v>
+        <v>46169.55908684028</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46169.4549275926</v>
+        <v>46169.62159425926</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>195</v>
@@ -6769,11 +6769,11 @@
         <v>292</v>
       </c>
       <c r="B91" s="9">
-        <v>46169.39252006944</v>
+        <v>46169.55918673611</v>
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="9">
-        <v>46169.45506896991</v>
+        <v>46169.621735636574</v>
       </c>
       <c r="E91" s="10" t="s">
         <v>293</v>
@@ -6832,11 +6832,11 @@
         <v>294</v>
       </c>
       <c r="B92" s="5">
-        <v>46169.39252446759</v>
+        <v>46169.55919113426</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46169.45502662037</v>
+        <v>46169.62169328704</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>195</v>
@@ -6885,11 +6885,11 @@
         <v>296</v>
       </c>
       <c r="B93" s="9">
-        <v>46169.392572893514</v>
+        <v>46169.559239560185</v>
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="9">
-        <v>46169.455176006944</v>
+        <v>46169.621842673616</v>
       </c>
       <c r="E93" s="10" t="s">
         <v>297</v>
@@ -6948,11 +6948,11 @@
         <v>298</v>
       </c>
       <c r="B94" s="5">
-        <v>46169.392577175924</v>
+        <v>46169.559243842596</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46169.45514178241</v>
+        <v>46169.621808449076</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>195</v>
@@ -7001,11 +7001,11 @@
         <v>300</v>
       </c>
       <c r="B95" s="9">
-        <v>46169.39263019676</v>
+        <v>46169.55929686343</v>
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="9">
-        <v>46169.45539672454</v>
+        <v>46169.6220633912</v>
       </c>
       <c r="E95" s="10" t="s">
         <v>301</v>
@@ -7064,11 +7064,11 @@
         <v>304</v>
       </c>
       <c r="B96" s="5">
-        <v>46169.39263513889</v>
+        <v>46169.55930180555</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46169.45522454861</v>
+        <v>46169.621891215276</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>302</v>
@@ -7117,11 +7117,11 @@
         <v>305</v>
       </c>
       <c r="B97" s="9">
-        <v>46169.39272054398</v>
+        <v>46169.55938721065</v>
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="9">
-        <v>46169.440061562505</v>
+        <v>46169.60672822916</v>
       </c>
       <c r="E97" s="10" t="s">
         <v>306</v>
@@ -7164,11 +7164,11 @@
         <v>308</v>
       </c>
       <c r="B98" s="5">
-        <v>46169.39272428241</v>
+        <v>46169.55939094907</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46169.45532454861</v>
+        <v>46169.621991215274</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>309</v>
@@ -7227,11 +7227,11 @@
         <v>312</v>
       </c>
       <c r="B99" s="9">
-        <v>46169.392729768515</v>
+        <v>46169.55939643519</v>
       </c>
       <c r="C99" s="10"/>
       <c r="D99" s="9">
-        <v>46169.4553590625</v>
+        <v>46169.62202572917</v>
       </c>
       <c r="E99" s="10" t="s">
         <v>313</v>

--- a/data/50001557 - ATACAMA KOZAN OT4340.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4340.xlsx
@@ -2295,9 +2295,11 @@
       <c r="B15" s="9">
         <v>46169.558013773145</v>
       </c>
-      <c r="C15" s="10"/>
+      <c r="C15" s="9">
+        <v>46190.64415828703</v>
+      </c>
       <c r="D15" s="9">
-        <v>46183.90665462963</v>
+        <v>46190.64417138889</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>67</v>
@@ -2332,9 +2334,11 @@
       <c r="Q15" s="10"/>
       <c r="R15" s="10"/>
       <c r="S15" s="10"/>
-      <c r="T15" s="10"/>
-      <c r="U15" s="11" t="s">
-        <v>65</v>
+      <c r="T15" s="10">
+        <v>1</v>
+      </c>
+      <c r="U15" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
@@ -2669,9 +2673,11 @@
       <c r="B21" s="9">
         <v>46169.55824574074</v>
       </c>
-      <c r="C21" s="10"/>
+      <c r="C21" s="9">
+        <v>46190.644140034725</v>
+      </c>
       <c r="D21" s="9">
-        <v>46185.72173949074</v>
+        <v>46190.64415820602</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>89</v>
@@ -2719,10 +2725,10 @@
         <v>33</v>
       </c>
       <c r="T21" s="10">
-        <v>0</v>
-      </c>
-      <c r="U21" s="11" t="s">
-        <v>65</v>
+        <v>1</v>
+      </c>
+      <c r="U21" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
@@ -3830,9 +3836,11 @@
       <c r="B40" s="5">
         <v>46169.55839107639</v>
       </c>
-      <c r="C40" s="6"/>
+      <c r="C40" s="5">
+        <v>46190.64487847222</v>
+      </c>
       <c r="D40" s="5">
-        <v>46185.85556069444</v>
+        <v>46190.64489506945</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>150</v>
@@ -3880,10 +3888,10 @@
         <v>33</v>
       </c>
       <c r="T40" s="6">
-        <v>0</v>
-      </c>
-      <c r="U40" s="12" t="s">
-        <v>105</v>
+        <v>1</v>
+      </c>
+      <c r="U40" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
@@ -4117,7 +4125,7 @@
       </c>
       <c r="C45" s="10"/>
       <c r="D45" s="9">
-        <v>46169.826076006946</v>
+        <v>46190.64414711806</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>90</v>
@@ -4748,7 +4756,7 @@
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46169.59260349537</v>
+        <v>46190.6449599537</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>198</v>
@@ -4793,9 +4801,11 @@
       <c r="B57" s="9">
         <v>46169.55858945602</v>
       </c>
-      <c r="C57" s="10"/>
+      <c r="C57" s="9">
+        <v>46190.64495354166</v>
+      </c>
       <c r="D57" s="9">
-        <v>46184.53263137731</v>
+        <v>46190.644969375004</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>201</v>
@@ -4843,10 +4853,10 @@
         <v>33</v>
       </c>
       <c r="T57" s="10">
-        <v>0</v>
-      </c>
-      <c r="U57" s="11" t="s">
-        <v>65</v>
+        <v>1</v>
+      </c>
+      <c r="U57" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
@@ -4858,7 +4868,7 @@
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46169.62031135417</v>
+        <v>46190.64496048611</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>206</v>
@@ -5173,7 +5183,7 @@
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="9">
-        <v>46169.60067526621</v>
+        <v>46190.645330810185</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>219</v>
@@ -5218,9 +5228,11 @@
       <c r="B64" s="5">
         <v>46169.55866469907</v>
       </c>
-      <c r="C64" s="6"/>
+      <c r="C64" s="5">
+        <v>46190.645243935185</v>
+      </c>
       <c r="D64" s="5">
-        <v>46184.91110869213</v>
+        <v>46190.645261516205</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>222</v>
@@ -5268,10 +5280,10 @@
         <v>33</v>
       </c>
       <c r="T64" s="6">
-        <v>0</v>
-      </c>
-      <c r="U64" s="12" t="s">
-        <v>105</v>
+        <v>1</v>
+      </c>
+      <c r="U64" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
@@ -5334,9 +5346,11 @@
       <c r="B66" s="5">
         <v>46169.558703518516</v>
       </c>
-      <c r="C66" s="6"/>
+      <c r="C66" s="5">
+        <v>46190.64532476851</v>
+      </c>
       <c r="D66" s="5">
-        <v>46184.92168449074</v>
+        <v>46190.64534048611</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>230</v>
@@ -5384,10 +5398,10 @@
         <v>33</v>
       </c>
       <c r="T66" s="6">
-        <v>0</v>
-      </c>
-      <c r="U66" s="12" t="s">
-        <v>105</v>
+        <v>1</v>
+      </c>
+      <c r="U66" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
@@ -5914,7 +5928,7 @@
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46169.62102423611</v>
+        <v>46190.645678113426</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>255</v>

--- a/data/50001557 - ATACAMA KOZAN OT4340.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4340.xlsx
@@ -4060,9 +4060,11 @@
       <c r="B44" s="5">
         <v>46169.55840677083</v>
       </c>
-      <c r="C44" s="6"/>
+      <c r="C44" s="5">
+        <v>46191.53700108796</v>
+      </c>
       <c r="D44" s="5">
-        <v>46169.82577043981</v>
+        <v>46191.53701371528</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>164</v>
@@ -4110,10 +4112,10 @@
         <v>33</v>
       </c>
       <c r="T44" s="6">
-        <v>0</v>
-      </c>
-      <c r="U44" s="12" t="s">
-        <v>105</v>
+        <v>1</v>
+      </c>
+      <c r="U44" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
@@ -4123,9 +4125,11 @@
       <c r="B45" s="9">
         <v>46169.55841037037</v>
       </c>
-      <c r="C45" s="10"/>
+      <c r="C45" s="9">
+        <v>46191.53678993056</v>
+      </c>
       <c r="D45" s="9">
-        <v>46190.64414711806</v>
+        <v>46191.53679194444</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>90</v>
@@ -4176,9 +4180,11 @@
       <c r="B46" s="5">
         <v>46169.558458217594</v>
       </c>
-      <c r="C46" s="6"/>
+      <c r="C46" s="5">
+        <v>46191.53698667824</v>
+      </c>
       <c r="D46" s="5">
-        <v>46169.826094062504</v>
+        <v>46191.53698841435</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>169</v>
@@ -5057,7 +5063,7 @@
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="9">
-        <v>46169.62021599537</v>
+        <v>46191.53700491898</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>215</v>
@@ -5107,8 +5113,8 @@
       <c r="T61" s="10">
         <v>0</v>
       </c>
-      <c r="U61" s="12" t="s">
-        <v>105</v>
+      <c r="U61" s="11" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001557 - ATACAMA KOZAN OT4340.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4340.xlsx
@@ -5934,7 +5934,7 @@
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46190.645678113426</v>
+        <v>46191.65585405093</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>255</v>

--- a/data/50001557 - ATACAMA KOZAN OT4340.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4340.xlsx
@@ -6793,7 +6793,7 @@
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="9">
-        <v>46169.621735636574</v>
+        <v>46195.5604462037</v>
       </c>
       <c r="E91" s="10" t="s">
         <v>293</v>
@@ -6909,7 +6909,7 @@
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="9">
-        <v>46169.621842673616</v>
+        <v>46195.56056820602</v>
       </c>
       <c r="E93" s="10" t="s">
         <v>297</v>
@@ -7025,7 +7025,7 @@
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="9">
-        <v>46169.6220633912</v>
+        <v>46195.56061262732</v>
       </c>
       <c r="E95" s="10" t="s">
         <v>301</v>

--- a/data/50001557 - ATACAMA KOZAN OT4340.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4340.xlsx
@@ -2856,7 +2856,7 @@
         <v>46182.67339038194</v>
       </c>
       <c r="D24" s="5">
-        <v>46182.67340354167</v>
+        <v>46195.69080631944</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>98</v>
@@ -2906,8 +2906,8 @@
       <c r="T24" s="6">
         <v>1</v>
       </c>
-      <c r="U24" s="7" t="s">
-        <v>27</v>
+      <c r="U24" s="11" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
@@ -2918,10 +2918,10 @@
         <v>46169.558306516206</v>
       </c>
       <c r="C25" s="9">
-        <v>46182.63365694444</v>
+        <v>46195.69079006945</v>
       </c>
       <c r="D25" s="9">
-        <v>46182.63365855324</v>
+        <v>46195.69079224537</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>103</v>
@@ -2982,7 +2982,7 @@
         <v>46182.67337415509</v>
       </c>
       <c r="D26" s="5">
-        <v>46182.67337592592</v>
+        <v>46195.690800474535</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>107</v>
@@ -3230,7 +3230,7 @@
         <v>46182.67350289352</v>
       </c>
       <c r="D30" s="5">
-        <v>46182.67351415509</v>
+        <v>46195.690666435185</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>119</v>
@@ -3280,8 +3280,8 @@
       <c r="T30" s="6">
         <v>1</v>
       </c>
-      <c r="U30" s="7" t="s">
-        <v>27</v>
+      <c r="U30" s="11" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
@@ -3292,10 +3292,10 @@
         <v>46169.55833486111</v>
       </c>
       <c r="C31" s="9">
-        <v>46182.63359528936</v>
+        <v>46195.69066097222</v>
       </c>
       <c r="D31" s="9">
-        <v>46182.633597418986</v>
+        <v>46195.69066259259</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>122</v>
@@ -3356,7 +3356,7 @@
         <v>46182.67343230324</v>
       </c>
       <c r="D32" s="5">
-        <v>46182.67343365741</v>
+        <v>46195.69066760417</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>125</v>
@@ -3414,10 +3414,10 @@
         <v>46169.55834503472</v>
       </c>
       <c r="C33" s="9">
-        <v>46182.67348809028</v>
+        <v>46195.6905771875</v>
       </c>
       <c r="D33" s="9">
-        <v>46182.67348943287</v>
+        <v>46195.6906680324</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>128</v>
@@ -3840,7 +3840,7 @@
         <v>46190.64487847222</v>
       </c>
       <c r="D40" s="5">
-        <v>46190.64489506945</v>
+        <v>46195.70377494213</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>150</v>
@@ -3890,8 +3890,8 @@
       <c r="T40" s="6">
         <v>1</v>
       </c>
-      <c r="U40" s="7" t="s">
-        <v>27</v>
+      <c r="U40" s="11" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
@@ -3901,9 +3901,11 @@
       <c r="B41" s="9">
         <v>46169.55839478009</v>
       </c>
-      <c r="C41" s="10"/>
+      <c r="C41" s="9">
+        <v>46195.70359988426</v>
+      </c>
       <c r="D41" s="9">
-        <v>46183.907345416665</v>
+        <v>46195.70360162037</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>93</v>
@@ -3954,9 +3956,11 @@
       <c r="B42" s="5">
         <v>46169.55839910879</v>
       </c>
-      <c r="C42" s="6"/>
+      <c r="C42" s="5">
+        <v>46195.703751678244</v>
+      </c>
       <c r="D42" s="5">
-        <v>46169.82614641204</v>
+        <v>46195.70375376157</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>157</v>
@@ -4009,7 +4013,7 @@
       </c>
       <c r="C43" s="10"/>
       <c r="D43" s="9">
-        <v>46169.826165543986</v>
+        <v>46195.703763495374</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>160</v>
@@ -4473,7 +4477,7 @@
         <v>46182.75958561343</v>
       </c>
       <c r="D51" s="9">
-        <v>46182.75958747685</v>
+        <v>46195.690583055555</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>178</v>
@@ -5824,7 +5828,7 @@
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46169.62091842592</v>
+        <v>46195.70377457176</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>249</v>
@@ -5874,8 +5878,8 @@
       <c r="T74" s="6">
         <v>0</v>
       </c>
-      <c r="U74" s="12" t="s">
-        <v>105</v>
+      <c r="U74" s="11" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001557 - ATACAMA KOZAN OT4340.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4340.xlsx
@@ -6797,7 +6797,7 @@
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="9">
-        <v>46195.5604462037</v>
+        <v>46196.561689236114</v>
       </c>
       <c r="E91" s="10" t="s">
         <v>293</v>

--- a/data/50001557 - ATACAMA KOZAN OT4340.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4340.xlsx
@@ -6913,7 +6913,7 @@
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="9">
-        <v>46195.56056820602</v>
+        <v>46196.565746747685</v>
       </c>
       <c r="E93" s="10" t="s">
         <v>297</v>
@@ -7029,7 +7029,7 @@
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="9">
-        <v>46195.56061262732</v>
+        <v>46196.573311342596</v>
       </c>
       <c r="E95" s="10" t="s">
         <v>301</v>

--- a/data/50001557 - ATACAMA KOZAN OT4340.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4340.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1194" uniqueCount="315">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1182" uniqueCount="308">
   <si>
     <t xml:space="preserve"> 50001557 - ATACAMA KOZAN</t>
   </si>
@@ -189,7 +189,7 @@
     <t>Ingenieria Jefe de proyecto:</t>
   </si>
   <si>
-    <t>Ingenieria Detalle,Analisis de costeo,Ingenieria Basica Motor,Ingenieria basica Rodete</t>
+    <t>Tarea en curso</t>
   </si>
   <si>
     <t>1215166329057002</t>
@@ -207,7 +207,7 @@
     <t>MOTOR DE STOCK WEG - 02 POLOS - IE3 FRAME 280</t>
   </si>
   <si>
-    <t>Analisis de costeo,propuesta motor OT 4340,Ingenieria Jefe de proyecto:</t>
+    <t>propuesta motor OT 4340,Ingenieria Jefe de proyecto:</t>
   </si>
   <si>
     <t>1215166329065515</t>
@@ -225,7 +225,7 @@
 </t>
   </si>
   <si>
-    <t>propuesta alabes OT 4340,Analisis de costeo,Ingenieria Jefe de proyecto:,propuesta nucleo rodete OT 4340</t>
+    <t>propuesta alabes OT 4340,Ingenieria Jefe de proyecto:,propuesta nucleo rodete OT 4340</t>
   </si>
   <si>
     <t>1215166329065538</t>
@@ -234,19 +234,7 @@
     <t>Ingenieria Detalle</t>
   </si>
   <si>
-    <t>Ingenieria Jefe de proyecto:,Analisis de costeo,OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR</t>
-  </si>
-  <si>
-    <t>1215165982699144</t>
-  </si>
-  <si>
-    <t>Analisis de costeo</t>
-  </si>
-  <si>
-    <t>Ingenieria Jefe de proyecto:,Costos</t>
-  </si>
-  <si>
-    <t>Tarea en curso</t>
+    <t>Ingenieria Jefe de proyecto:,OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR</t>
   </si>
   <si>
     <t>1215137857526528</t>
@@ -471,7 +459,7 @@
     <t>Fabricacion Corte Laser  OT 4340</t>
   </si>
   <si>
-    <t>Recepcion materiales corte laser,Materiales corte Laser OT 4340</t>
+    <t>Recepcionx materiales corte laser,Materiales corte Laser OT 4340</t>
   </si>
   <si>
     <t>1215166041659726</t>
@@ -648,13 +636,13 @@
     <t>Bodega:</t>
   </si>
   <si>
-    <t xml:space="preserve">Recepcion materiales corte laser,Control de calidad corte laser </t>
+    <t xml:space="preserve">Recepcionx materiales corte laser,Control de calidad corte laser </t>
   </si>
   <si>
     <t>1215165983005064</t>
   </si>
   <si>
-    <t>Recepcion materiales corte laser</t>
+    <t>Recepcionx materiales corte laser</t>
   </si>
   <si>
     <t>Victor Muñoz</t>
@@ -672,9 +660,6 @@
     <t xml:space="preserve">Control de calidad corte laser </t>
   </si>
   <si>
-    <t>Recepcion Materiales corte plasma,Recepcion materiales corte laser</t>
-  </si>
-  <si>
     <t>Bodega:,OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR</t>
   </si>
   <si>
@@ -684,15 +669,12 @@
     <t>Recepcion Materiales corte plasma</t>
   </si>
   <si>
-    <t>Control de calidad corte laser ,Control de calidad Corte plasma</t>
+    <t>Control de calidad Corte plasma</t>
   </si>
   <si>
     <t>1215166041891891</t>
   </si>
   <si>
-    <t>Control de calidad Corte plasma</t>
-  </si>
-  <si>
     <t>1215165982799201</t>
   </si>
   <si>
@@ -991,9 +973,6 @@
   </si>
   <si>
     <t>Costos</t>
-  </si>
-  <si>
-    <t>Despacho,Analisis de costeo</t>
   </si>
 </sst>
 </file>
@@ -1517,7 +1496,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:U99"/>
+  <dimension ref="A1:U98"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10.4" customWidth="1"/>
@@ -1992,7 +1971,7 @@
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46181.624396238425</v>
+        <v>46196.80568585648</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>47</v>
@@ -2019,7 +1998,7 @@
         <v>26</v>
       </c>
       <c r="O10" s="6" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="P10" s="6" t="s">
         <v>26</v>
@@ -2028,7 +2007,9 @@
       <c r="R10" s="6"/>
       <c r="S10" s="6"/>
       <c r="T10" s="6"/>
-      <c r="U10" s="6"/>
+      <c r="U10" s="11" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
@@ -2041,7 +2022,7 @@
         <v>46181.624365104166</v>
       </c>
       <c r="D11" s="9">
-        <v>46181.62438819444</v>
+        <v>46196.80567361111</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>50</v>
@@ -2106,7 +2087,7 @@
         <v>46181.62437706019</v>
       </c>
       <c r="D12" s="5">
-        <v>46181.62439237269</v>
+        <v>46196.80567332176</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>56</v>
@@ -2171,7 +2152,7 @@
         <v>46181.624389537035</v>
       </c>
       <c r="D13" s="9">
-        <v>46181.624564212965</v>
+        <v>46196.80567320602</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>60</v>
@@ -2230,30 +2211,26 @@
         <v>62</v>
       </c>
       <c r="B14" s="5">
-        <v>46169.55820460648</v>
-      </c>
-      <c r="C14" s="6"/>
+        <v>46169.558013773145</v>
+      </c>
+      <c r="C14" s="5">
+        <v>46190.64415828703</v>
+      </c>
       <c r="D14" s="5">
-        <v>46181.624409780095</v>
+        <v>46190.64417138889</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>63</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="H14" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="I14" s="5">
-        <v>46155</v>
-      </c>
-      <c r="J14" s="5">
-        <v>46164</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H14" s="6"/>
+      <c r="I14" s="6"/>
+      <c r="J14" s="6"/>
       <c r="K14" s="6" t="s">
         <v>26</v>
       </c>
@@ -2261,79 +2238,85 @@
         <v>26</v>
       </c>
       <c r="M14" s="6" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N14" s="6" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="O14" s="6" t="s">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="P14" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q14" s="5">
-        <v>46155</v>
-      </c>
-      <c r="R14" s="5">
-        <v>46164</v>
-      </c>
-      <c r="S14" s="7" t="s">
-        <v>33</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q14" s="6"/>
+      <c r="R14" s="6"/>
+      <c r="S14" s="6"/>
       <c r="T14" s="6">
-        <v>0</v>
-      </c>
-      <c r="U14" s="11" t="s">
-        <v>65</v>
+        <v>1</v>
+      </c>
+      <c r="U14" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="B15" s="9">
+        <v>46169.558213564815</v>
+      </c>
+      <c r="C15" s="9">
+        <v>46181.62444696759</v>
+      </c>
+      <c r="D15" s="9">
+        <v>46181.62446385417</v>
+      </c>
+      <c r="E15" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="B15" s="9">
-        <v>46169.558013773145</v>
-      </c>
-      <c r="C15" s="9">
-        <v>46190.64415828703</v>
-      </c>
-      <c r="D15" s="9">
-        <v>46190.64417138889</v>
-      </c>
-      <c r="E15" s="10" t="s">
+      <c r="F15" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G15" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="H15" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="I15" s="9">
+        <v>46157</v>
+      </c>
+      <c r="J15" s="9">
+        <v>46160</v>
+      </c>
+      <c r="K15" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L15" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M15" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N15" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="O15" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="P15" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="F15" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="G15" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H15" s="10"/>
-      <c r="I15" s="10"/>
-      <c r="J15" s="10"/>
-      <c r="K15" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L15" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M15" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="N15" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="O15" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="P15" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q15" s="10"/>
-      <c r="R15" s="10"/>
-      <c r="S15" s="10"/>
+      <c r="Q15" s="9">
+        <v>46157</v>
+      </c>
+      <c r="R15" s="9">
+        <v>46160</v>
+      </c>
+      <c r="S15" s="7" t="s">
+        <v>33</v>
+      </c>
       <c r="T15" s="10">
         <v>1</v>
       </c>
@@ -2343,19 +2326,19 @@
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B16" s="5">
+        <v>46169.558224479166</v>
+      </c>
+      <c r="C16" s="5">
+        <v>46181.62445372685</v>
+      </c>
+      <c r="D16" s="5">
+        <v>46181.62447002315</v>
+      </c>
+      <c r="E16" s="6" t="s">
         <v>69</v>
-      </c>
-      <c r="B16" s="5">
-        <v>46169.558213564815</v>
-      </c>
-      <c r="C16" s="5">
-        <v>46181.62444696759</v>
-      </c>
-      <c r="D16" s="5">
-        <v>46181.62446385417</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>70</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>26</v>
@@ -2367,10 +2350,10 @@
         <v>52</v>
       </c>
       <c r="I16" s="5">
-        <v>46157</v>
+        <v>46167</v>
       </c>
       <c r="J16" s="5">
-        <v>46160</v>
+        <v>46168</v>
       </c>
       <c r="K16" s="6" t="s">
         <v>26</v>
@@ -2382,19 +2365,19 @@
         <v>26</v>
       </c>
       <c r="N16" s="6" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O16" s="6" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="P16" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="Q16" s="5">
-        <v>46157</v>
+        <v>46167</v>
       </c>
       <c r="R16" s="5">
-        <v>46160</v>
+        <v>46168</v>
       </c>
       <c r="S16" s="7" t="s">
         <v>33</v>
@@ -2408,28 +2391,28 @@
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="B17" s="9">
+        <v>46169.558230821756</v>
+      </c>
+      <c r="C17" s="9">
+        <v>46183.906516585645</v>
+      </c>
+      <c r="D17" s="9">
+        <v>46183.90651931713</v>
+      </c>
+      <c r="E17" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="B17" s="9">
-        <v>46169.558224479166</v>
-      </c>
-      <c r="C17" s="9">
-        <v>46181.62445372685</v>
-      </c>
-      <c r="D17" s="9">
-        <v>46181.62447002315</v>
-      </c>
-      <c r="E17" s="10" t="s">
+      <c r="F17" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G17" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="F17" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G17" s="10" t="s">
-        <v>51</v>
-      </c>
       <c r="H17" s="10" t="s">
-        <v>52</v>
+        <v>73</v>
       </c>
       <c r="I17" s="9">
         <v>46167</v>
@@ -2447,7 +2430,7 @@
         <v>26</v>
       </c>
       <c r="N17" s="10" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O17" s="10" t="s">
         <v>56</v>
@@ -2476,13 +2459,13 @@
         <v>75</v>
       </c>
       <c r="B18" s="5">
-        <v>46169.558230821756</v>
+        <v>46169.55823646991</v>
       </c>
       <c r="C18" s="5">
-        <v>46183.906516585645</v>
+        <v>46183.90663498842</v>
       </c>
       <c r="D18" s="5">
-        <v>46183.90651931713</v>
+        <v>46183.90665107639</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>76</v>
@@ -2494,13 +2477,13 @@
         <v>77</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I18" s="5">
-        <v>46167</v>
+        <v>46239</v>
       </c>
       <c r="J18" s="5">
-        <v>46168</v>
+        <v>46240</v>
       </c>
       <c r="K18" s="6" t="s">
         <v>26</v>
@@ -2512,19 +2495,19 @@
         <v>26</v>
       </c>
       <c r="N18" s="6" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O18" s="6" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="Q18" s="5">
-        <v>46167</v>
+        <v>46239</v>
       </c>
       <c r="R18" s="5">
-        <v>46168</v>
+        <v>46240</v>
       </c>
       <c r="S18" s="7" t="s">
         <v>33</v>
@@ -2538,28 +2521,28 @@
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B19" s="9">
-        <v>46169.55823646991</v>
+        <v>46169.55824171296</v>
       </c>
       <c r="C19" s="9">
-        <v>46183.90663498842</v>
+        <v>46183.906646539355</v>
       </c>
       <c r="D19" s="9">
-        <v>46183.90665107639</v>
+        <v>46183.90666170139</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F19" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="I19" s="9">
         <v>46239</v>
@@ -2577,13 +2560,13 @@
         <v>26</v>
       </c>
       <c r="N19" s="10" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O19" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="P19" s="10" t="s">
         <v>83</v>
-      </c>
-      <c r="P19" s="10" t="s">
-        <v>84</v>
       </c>
       <c r="Q19" s="9">
         <v>46239</v>
@@ -2603,28 +2586,28 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="B20" s="5">
+        <v>46169.55824574074</v>
+      </c>
+      <c r="C20" s="5">
+        <v>46190.644140034725</v>
+      </c>
+      <c r="D20" s="5">
+        <v>46190.64415820602</v>
+      </c>
+      <c r="E20" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="B20" s="5">
-        <v>46169.55824171296</v>
-      </c>
-      <c r="C20" s="5">
-        <v>46183.906646539355</v>
-      </c>
-      <c r="D20" s="5">
-        <v>46183.90666170139</v>
-      </c>
-      <c r="E20" s="6" t="s">
-        <v>86</v>
-      </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="I20" s="5">
         <v>46239</v>
@@ -2642,13 +2625,13 @@
         <v>26</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="Q20" s="5">
         <v>46239</v>
@@ -2668,28 +2651,28 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="B21" s="9">
+        <v>46169.55825006944</v>
+      </c>
+      <c r="C21" s="9">
+        <v>46183.90733957176</v>
+      </c>
+      <c r="D21" s="9">
+        <v>46183.90735393518</v>
+      </c>
+      <c r="E21" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="B21" s="9">
-        <v>46169.55824574074</v>
-      </c>
-      <c r="C21" s="9">
-        <v>46190.644140034725</v>
-      </c>
-      <c r="D21" s="9">
-        <v>46190.64415820602</v>
-      </c>
-      <c r="E21" s="10" t="s">
-        <v>89</v>
-      </c>
       <c r="F21" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="I21" s="9">
         <v>46239</v>
@@ -2707,13 +2690,13 @@
         <v>26</v>
       </c>
       <c r="N21" s="10" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O21" s="10" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="P21" s="10" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="Q21" s="9">
         <v>46239</v>
@@ -2733,92 +2716,84 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="B22" s="5">
+        <v>46169.55801826389</v>
+      </c>
+      <c r="C22" s="6"/>
+      <c r="D22" s="5">
+        <v>46184.736483437504</v>
+      </c>
+      <c r="E22" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="B22" s="5">
-        <v>46169.55825006944</v>
-      </c>
-      <c r="C22" s="5">
-        <v>46183.90733957176</v>
-      </c>
-      <c r="D22" s="5">
-        <v>46183.90735393518</v>
-      </c>
-      <c r="E22" s="6" t="s">
+      <c r="F22" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="H22" s="6"/>
+      <c r="I22" s="6"/>
+      <c r="J22" s="6"/>
+      <c r="K22" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L22" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M22" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="N22" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="O22" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="F22" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G22" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="H22" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="I22" s="5">
-        <v>46239</v>
-      </c>
-      <c r="J22" s="5">
-        <v>46240</v>
-      </c>
-      <c r="K22" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L22" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M22" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N22" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="O22" s="6" t="s">
-        <v>83</v>
-      </c>
       <c r="P22" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="Q22" s="5">
-        <v>46239</v>
-      </c>
-      <c r="R22" s="5">
-        <v>46240</v>
-      </c>
-      <c r="S22" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T22" s="6">
-        <v>1</v>
-      </c>
-      <c r="U22" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
+      </c>
+      <c r="Q22" s="6"/>
+      <c r="R22" s="6"/>
+      <c r="S22" s="6"/>
+      <c r="T22" s="6"/>
+      <c r="U22" s="11" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="B23" s="9">
+        <v>46169.558301956014</v>
+      </c>
+      <c r="C23" s="9">
+        <v>46182.67339038194</v>
+      </c>
+      <c r="D23" s="9">
+        <v>46195.69080631944</v>
+      </c>
+      <c r="E23" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="B23" s="9">
-        <v>46169.55801826389</v>
-      </c>
-      <c r="C23" s="10"/>
-      <c r="D23" s="9">
-        <v>46184.736483437504</v>
-      </c>
-      <c r="E23" s="10" t="s">
+      <c r="F23" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G23" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="F23" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="G23" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H23" s="10"/>
-      <c r="I23" s="10"/>
-      <c r="J23" s="10"/>
+      <c r="H23" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="I23" s="9">
+        <v>46169</v>
+      </c>
+      <c r="J23" s="9">
+        <v>46324</v>
+      </c>
       <c r="K23" s="10" t="s">
         <v>26</v>
       </c>
@@ -2826,55 +2801,63 @@
         <v>26</v>
       </c>
       <c r="M23" s="10" t="s">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="N23" s="10" t="s">
-        <v>26</v>
+        <v>91</v>
       </c>
       <c r="O23" s="10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="P23" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q23" s="10"/>
-      <c r="R23" s="10"/>
-      <c r="S23" s="10"/>
-      <c r="T23" s="10"/>
+        <v>91</v>
+      </c>
+      <c r="Q23" s="9">
+        <v>46169</v>
+      </c>
+      <c r="R23" s="9">
+        <v>46324</v>
+      </c>
+      <c r="S23" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T23" s="10">
+        <v>1</v>
+      </c>
       <c r="U23" s="11" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B24" s="5">
-        <v>46169.558301956014</v>
+        <v>46169.558306516206</v>
       </c>
       <c r="C24" s="5">
-        <v>46182.67339038194</v>
+        <v>46195.69079006945</v>
       </c>
       <c r="D24" s="5">
-        <v>46195.69080631944</v>
+        <v>46195.69079224537</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="I24" s="5">
         <v>46169</v>
       </c>
       <c r="J24" s="5">
-        <v>46324</v>
+        <v>46170</v>
       </c>
       <c r="K24" s="6" t="s">
         <v>26</v>
@@ -2886,28 +2869,24 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>101</v>
+        <v>69</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="Q24" s="5">
-        <v>46169</v>
-      </c>
-      <c r="R24" s="5">
-        <v>46324</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="Q24" s="6"/>
+      <c r="R24" s="6"/>
       <c r="S24" s="7" t="s">
         <v>33</v>
       </c>
       <c r="T24" s="6">
-        <v>1</v>
-      </c>
-      <c r="U24" s="11" t="s">
-        <v>65</v>
+        <v>0</v>
+      </c>
+      <c r="U24" s="12" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
@@ -2915,13 +2894,13 @@
         <v>102</v>
       </c>
       <c r="B25" s="9">
-        <v>46169.558306516206</v>
+        <v>46169.55831137732</v>
       </c>
       <c r="C25" s="9">
-        <v>46195.69079006945</v>
+        <v>46182.67337415509</v>
       </c>
       <c r="D25" s="9">
-        <v>46195.69079224537</v>
+        <v>46195.690800474535</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>103</v>
@@ -2930,31 +2909,31 @@
         <v>26</v>
       </c>
       <c r="G25" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="H25" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="I25" s="9">
+        <v>46171</v>
+      </c>
+      <c r="J25" s="9">
+        <v>46324</v>
+      </c>
+      <c r="K25" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L25" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M25" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N25" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="O25" s="10" t="s">
         <v>99</v>
-      </c>
-      <c r="H25" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="I25" s="9">
-        <v>46169</v>
-      </c>
-      <c r="J25" s="9">
-        <v>46170</v>
-      </c>
-      <c r="K25" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L25" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M25" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N25" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="O25" s="10" t="s">
-        <v>73</v>
       </c>
       <c r="P25" s="10" t="s">
         <v>104</v>
@@ -2968,100 +2947,104 @@
         <v>0</v>
       </c>
       <c r="U25" s="12" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="B26" s="5">
+        <v>46169.55831605324</v>
+      </c>
+      <c r="C26" s="5">
+        <v>46184.73646410879</v>
+      </c>
+      <c r="D26" s="5">
+        <v>46184.73661180555</v>
+      </c>
+      <c r="E26" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="B26" s="5">
-        <v>46169.55831137732</v>
-      </c>
-      <c r="C26" s="5">
-        <v>46182.67337415509</v>
-      </c>
-      <c r="D26" s="5">
-        <v>46195.690800474535</v>
-      </c>
-      <c r="E26" s="6" t="s">
+      <c r="F26" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G26" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="H26" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="I26" s="5">
+        <v>46169</v>
+      </c>
+      <c r="J26" s="5">
+        <v>46219</v>
+      </c>
+      <c r="K26" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L26" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M26" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N26" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="O26" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="F26" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G26" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="H26" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="I26" s="5">
-        <v>46171</v>
-      </c>
-      <c r="J26" s="5">
-        <v>46324</v>
-      </c>
-      <c r="K26" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L26" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M26" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N26" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="O26" s="6" t="s">
-        <v>103</v>
-      </c>
       <c r="P26" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="Q26" s="6"/>
-      <c r="R26" s="6"/>
+        <v>91</v>
+      </c>
+      <c r="Q26" s="5">
+        <v>46169</v>
+      </c>
+      <c r="R26" s="5">
+        <v>46219</v>
+      </c>
       <c r="S26" s="7" t="s">
         <v>33</v>
       </c>
       <c r="T26" s="6">
-        <v>0</v>
-      </c>
-      <c r="U26" s="12" t="s">
-        <v>105</v>
+        <v>1</v>
+      </c>
+      <c r="U26" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="B27" s="9">
+        <v>46169.55832063657</v>
+      </c>
+      <c r="C27" s="9">
+        <v>46184.736407812496</v>
+      </c>
+      <c r="D27" s="9">
+        <v>46184.7364097338</v>
+      </c>
+      <c r="E27" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="B27" s="9">
-        <v>46169.55831605324</v>
-      </c>
-      <c r="C27" s="9">
-        <v>46184.73646410879</v>
-      </c>
-      <c r="D27" s="9">
-        <v>46184.73661180555</v>
-      </c>
-      <c r="E27" s="10" t="s">
-        <v>110</v>
-      </c>
       <c r="F27" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="I27" s="9">
         <v>46169</v>
       </c>
       <c r="J27" s="9">
-        <v>46219</v>
+        <v>46170</v>
       </c>
       <c r="K27" s="10" t="s">
         <v>26</v>
@@ -3073,78 +3056,74 @@
         <v>26</v>
       </c>
       <c r="N27" s="10" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="O27" s="10" t="s">
-        <v>111</v>
+        <v>72</v>
       </c>
       <c r="P27" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="Q27" s="9">
-        <v>46169</v>
-      </c>
-      <c r="R27" s="9">
-        <v>46219</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="Q27" s="10"/>
+      <c r="R27" s="10"/>
       <c r="S27" s="7" t="s">
         <v>33</v>
       </c>
       <c r="T27" s="10">
-        <v>1</v>
-      </c>
-      <c r="U27" s="7" t="s">
-        <v>27</v>
+        <v>0</v>
+      </c>
+      <c r="U27" s="12" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="B28" s="5">
+        <v>46169.55832539352</v>
+      </c>
+      <c r="C28" s="5">
+        <v>46184.73644800926</v>
+      </c>
+      <c r="D28" s="5">
+        <v>46184.736449375</v>
+      </c>
+      <c r="E28" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="B28" s="5">
-        <v>46169.55832063657</v>
-      </c>
-      <c r="C28" s="5">
-        <v>46184.736407812496</v>
-      </c>
-      <c r="D28" s="5">
-        <v>46184.7364097338</v>
-      </c>
-      <c r="E28" s="6" t="s">
+      <c r="F28" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G28" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="H28" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="I28" s="5">
+        <v>46171</v>
+      </c>
+      <c r="J28" s="5">
+        <v>46219</v>
+      </c>
+      <c r="K28" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L28" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M28" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N28" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="O28" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="P28" s="6" t="s">
         <v>113</v>
-      </c>
-      <c r="F28" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G28" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="H28" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="I28" s="5">
-        <v>46169</v>
-      </c>
-      <c r="J28" s="5">
-        <v>46170</v>
-      </c>
-      <c r="K28" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L28" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M28" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N28" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="O28" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="P28" s="6" t="s">
-        <v>114</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
@@ -3155,100 +3134,104 @@
         <v>0</v>
       </c>
       <c r="U28" s="12" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="B29" s="9">
+        <v>46169.55833006944</v>
+      </c>
+      <c r="C29" s="9">
+        <v>46182.67350289352</v>
+      </c>
+      <c r="D29" s="9">
+        <v>46195.690666435185</v>
+      </c>
+      <c r="E29" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="B29" s="9">
-        <v>46169.55832539352</v>
-      </c>
-      <c r="C29" s="9">
-        <v>46184.73644800926</v>
-      </c>
-      <c r="D29" s="9">
-        <v>46184.736449375</v>
-      </c>
-      <c r="E29" s="10" t="s">
+      <c r="F29" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G29" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="H29" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="I29" s="9">
+        <v>46161</v>
+      </c>
+      <c r="J29" s="9">
+        <v>46290</v>
+      </c>
+      <c r="K29" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L29" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M29" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N29" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="O29" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="F29" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G29" s="10" t="s">
-        <v>99</v>
-      </c>
-      <c r="H29" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="I29" s="9">
-        <v>46171</v>
-      </c>
-      <c r="J29" s="9">
-        <v>46219</v>
-      </c>
-      <c r="K29" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L29" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M29" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N29" s="10" t="s">
-        <v>110</v>
-      </c>
-      <c r="O29" s="10" t="s">
-        <v>113</v>
-      </c>
       <c r="P29" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q29" s="10"/>
-      <c r="R29" s="10"/>
+        <v>91</v>
+      </c>
+      <c r="Q29" s="9">
+        <v>46161</v>
+      </c>
+      <c r="R29" s="9">
+        <v>46290</v>
+      </c>
       <c r="S29" s="7" t="s">
         <v>33</v>
       </c>
       <c r="T29" s="10">
-        <v>0</v>
-      </c>
-      <c r="U29" s="12" t="s">
-        <v>105</v>
+        <v>1</v>
+      </c>
+      <c r="U29" s="11" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="B30" s="5">
+        <v>46169.55833486111</v>
+      </c>
+      <c r="C30" s="5">
+        <v>46195.69066097222</v>
+      </c>
+      <c r="D30" s="5">
+        <v>46195.69066259259</v>
+      </c>
+      <c r="E30" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="B30" s="5">
-        <v>46169.55833006944</v>
-      </c>
-      <c r="C30" s="5">
-        <v>46182.67350289352</v>
-      </c>
-      <c r="D30" s="5">
-        <v>46195.690666435185</v>
-      </c>
-      <c r="E30" s="6" t="s">
-        <v>119</v>
-      </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="I30" s="5">
         <v>46161</v>
       </c>
       <c r="J30" s="5">
-        <v>46290</v>
+        <v>46177</v>
       </c>
       <c r="K30" s="6" t="s">
         <v>26</v>
@@ -3260,78 +3243,74 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>95</v>
+        <v>115</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>120</v>
+        <v>66</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="Q30" s="5">
-        <v>46161</v>
-      </c>
-      <c r="R30" s="5">
-        <v>46290</v>
-      </c>
+        <v>119</v>
+      </c>
+      <c r="Q30" s="6"/>
+      <c r="R30" s="6"/>
       <c r="S30" s="7" t="s">
         <v>33</v>
       </c>
       <c r="T30" s="6">
-        <v>1</v>
-      </c>
-      <c r="U30" s="11" t="s">
-        <v>65</v>
+        <v>0</v>
+      </c>
+      <c r="U30" s="12" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="B31" s="9">
+        <v>46169.5583402662</v>
+      </c>
+      <c r="C31" s="9">
+        <v>46182.67343230324</v>
+      </c>
+      <c r="D31" s="9">
+        <v>46195.69066760417</v>
+      </c>
+      <c r="E31" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="B31" s="9">
-        <v>46169.55833486111</v>
-      </c>
-      <c r="C31" s="9">
-        <v>46195.69066097222</v>
-      </c>
-      <c r="D31" s="9">
-        <v>46195.69066259259</v>
-      </c>
-      <c r="E31" s="10" t="s">
+      <c r="F31" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G31" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="H31" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="I31" s="9">
+        <v>46178</v>
+      </c>
+      <c r="J31" s="9">
+        <v>46290</v>
+      </c>
+      <c r="K31" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L31" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M31" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N31" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="O31" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="P31" s="10" t="s">
         <v>122</v>
-      </c>
-      <c r="F31" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G31" s="10" t="s">
-        <v>99</v>
-      </c>
-      <c r="H31" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="I31" s="9">
-        <v>46161</v>
-      </c>
-      <c r="J31" s="9">
-        <v>46177</v>
-      </c>
-      <c r="K31" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L31" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M31" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N31" s="10" t="s">
-        <v>119</v>
-      </c>
-      <c r="O31" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="P31" s="10" t="s">
-        <v>123</v>
       </c>
       <c r="Q31" s="10"/>
       <c r="R31" s="10"/>
@@ -3342,39 +3321,39 @@
         <v>0</v>
       </c>
       <c r="U31" s="12" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="B32" s="5">
+        <v>46169.55834503472</v>
+      </c>
+      <c r="C32" s="5">
+        <v>46195.6905771875</v>
+      </c>
+      <c r="D32" s="5">
+        <v>46195.6906680324</v>
+      </c>
+      <c r="E32" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="B32" s="5">
-        <v>46169.5583402662</v>
-      </c>
-      <c r="C32" s="5">
-        <v>46182.67343230324</v>
-      </c>
-      <c r="D32" s="5">
-        <v>46195.69066760417</v>
-      </c>
-      <c r="E32" s="6" t="s">
-        <v>125</v>
-      </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="I32" s="5">
         <v>46178</v>
       </c>
       <c r="J32" s="5">
-        <v>46290</v>
+        <v>46217</v>
       </c>
       <c r="K32" s="6" t="s">
         <v>26</v>
@@ -3386,13 +3365,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
@@ -3403,39 +3382,39 @@
         <v>0</v>
       </c>
       <c r="U32" s="12" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="B33" s="9">
+        <v>46169.55836335648</v>
+      </c>
+      <c r="C33" s="9">
+        <v>46184.532628437504</v>
+      </c>
+      <c r="D33" s="9">
+        <v>46184.532641875005</v>
+      </c>
+      <c r="E33" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="B33" s="9">
-        <v>46169.55834503472</v>
-      </c>
-      <c r="C33" s="9">
-        <v>46195.6905771875</v>
-      </c>
-      <c r="D33" s="9">
-        <v>46195.6906680324</v>
-      </c>
-      <c r="E33" s="10" t="s">
+      <c r="F33" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G33" s="10" t="s">
         <v>128</v>
       </c>
-      <c r="F33" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G33" s="10" t="s">
-        <v>99</v>
-      </c>
       <c r="H33" s="10" t="s">
-        <v>100</v>
+        <v>129</v>
       </c>
       <c r="I33" s="9">
-        <v>46178</v>
+        <v>46241</v>
       </c>
       <c r="J33" s="9">
-        <v>46217</v>
+        <v>46253</v>
       </c>
       <c r="K33" s="10" t="s">
         <v>26</v>
@@ -3447,56 +3426,60 @@
         <v>26</v>
       </c>
       <c r="N33" s="10" t="s">
-        <v>119</v>
+        <v>91</v>
       </c>
       <c r="O33" s="10" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>129</v>
-      </c>
-      <c r="Q33" s="10"/>
-      <c r="R33" s="10"/>
+        <v>91</v>
+      </c>
+      <c r="Q33" s="9">
+        <v>46241</v>
+      </c>
+      <c r="R33" s="9">
+        <v>46253</v>
+      </c>
       <c r="S33" s="7" t="s">
         <v>33</v>
       </c>
       <c r="T33" s="10">
-        <v>0</v>
-      </c>
-      <c r="U33" s="12" t="s">
-        <v>105</v>
+        <v>1</v>
+      </c>
+      <c r="U33" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B34" s="5">
-        <v>46169.55836335648</v>
+        <v>46169.558367986116</v>
       </c>
       <c r="C34" s="5">
-        <v>46184.532628437504</v>
+        <v>46184.53245732639</v>
       </c>
       <c r="D34" s="5">
-        <v>46184.532641875005</v>
+        <v>46184.53245875</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="I34" s="5">
         <v>46241</v>
       </c>
       <c r="J34" s="5">
-        <v>46253</v>
+        <v>46244</v>
       </c>
       <c r="K34" s="6" t="s">
         <v>26</v>
@@ -3508,78 +3491,74 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>134</v>
+        <v>76</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="Q34" s="5">
-        <v>46241</v>
-      </c>
-      <c r="R34" s="5">
-        <v>46253</v>
-      </c>
+        <v>133</v>
+      </c>
+      <c r="Q34" s="6"/>
+      <c r="R34" s="6"/>
       <c r="S34" s="7" t="s">
         <v>33</v>
       </c>
       <c r="T34" s="6">
-        <v>1</v>
-      </c>
-      <c r="U34" s="7" t="s">
-        <v>27</v>
+        <v>0</v>
+      </c>
+      <c r="U34" s="12" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="B35" s="9">
+        <v>46169.55837292824</v>
+      </c>
+      <c r="C35" s="9">
+        <v>46184.532613668984</v>
+      </c>
+      <c r="D35" s="9">
+        <v>46184.532615856486</v>
+      </c>
+      <c r="E35" s="10" t="s">
         <v>135</v>
       </c>
-      <c r="B35" s="9">
-        <v>46169.558367986116</v>
-      </c>
-      <c r="C35" s="9">
-        <v>46184.53245732639</v>
-      </c>
-      <c r="D35" s="9">
-        <v>46184.53245875</v>
-      </c>
-      <c r="E35" s="10" t="s">
+      <c r="F35" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G35" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="H35" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="I35" s="9">
+        <v>46245</v>
+      </c>
+      <c r="J35" s="9">
+        <v>46253</v>
+      </c>
+      <c r="K35" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L35" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M35" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N35" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="O35" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="P35" s="10" t="s">
         <v>136</v>
-      </c>
-      <c r="F35" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G35" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="H35" s="10" t="s">
-        <v>133</v>
-      </c>
-      <c r="I35" s="9">
-        <v>46241</v>
-      </c>
-      <c r="J35" s="9">
-        <v>46244</v>
-      </c>
-      <c r="K35" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L35" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M35" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N35" s="10" t="s">
-        <v>131</v>
-      </c>
-      <c r="O35" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="P35" s="10" t="s">
-        <v>137</v>
       </c>
       <c r="Q35" s="10"/>
       <c r="R35" s="10"/>
@@ -3590,36 +3569,36 @@
         <v>0</v>
       </c>
       <c r="U35" s="12" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="B36" s="5">
+        <v>46169.55837825232</v>
+      </c>
+      <c r="C36" s="5">
+        <v>46184.53257122685</v>
+      </c>
+      <c r="D36" s="5">
+        <v>46184.53258194444</v>
+      </c>
+      <c r="E36" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="B36" s="5">
-        <v>46169.55837292824</v>
-      </c>
-      <c r="C36" s="5">
-        <v>46184.532613668984</v>
-      </c>
-      <c r="D36" s="5">
-        <v>46184.532615856486</v>
-      </c>
-      <c r="E36" s="6" t="s">
-        <v>139</v>
-      </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="I36" s="5">
-        <v>46245</v>
+        <v>46241</v>
       </c>
       <c r="J36" s="5">
         <v>46253</v>
@@ -3634,56 +3613,60 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>131</v>
+        <v>91</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="Q36" s="6"/>
-      <c r="R36" s="6"/>
+        <v>26</v>
+      </c>
+      <c r="Q36" s="5">
+        <v>46241</v>
+      </c>
+      <c r="R36" s="5">
+        <v>46253</v>
+      </c>
       <c r="S36" s="7" t="s">
         <v>33</v>
       </c>
       <c r="T36" s="6">
-        <v>0</v>
-      </c>
-      <c r="U36" s="12" t="s">
-        <v>105</v>
+        <v>1</v>
+      </c>
+      <c r="U36" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B37" s="9">
-        <v>46169.55837825232</v>
+        <v>46169.558381979165</v>
       </c>
       <c r="C37" s="9">
-        <v>46184.53257122685</v>
+        <v>46184.53220534722</v>
       </c>
       <c r="D37" s="9">
-        <v>46184.53258194444</v>
+        <v>46184.5322071875</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>142</v>
+        <v>83</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="I37" s="9">
         <v>46241</v>
       </c>
       <c r="J37" s="9">
-        <v>46253</v>
+        <v>46244</v>
       </c>
       <c r="K37" s="10" t="s">
         <v>26</v>
@@ -3695,78 +3678,68 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>95</v>
+        <v>138</v>
       </c>
       <c r="O37" s="10" t="s">
-        <v>143</v>
+        <v>82</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q37" s="9">
-        <v>46241</v>
-      </c>
-      <c r="R37" s="9">
-        <v>46253</v>
-      </c>
-      <c r="S37" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T37" s="10">
-        <v>1</v>
-      </c>
-      <c r="U37" s="7" t="s">
-        <v>27</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="Q37" s="10"/>
+      <c r="R37" s="10"/>
+      <c r="S37" s="10"/>
+      <c r="T37" s="10"/>
+      <c r="U37" s="10"/>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="B38" s="5">
+        <v>46169.55838657408</v>
+      </c>
+      <c r="C38" s="5">
+        <v>46184.53255483796</v>
+      </c>
+      <c r="D38" s="5">
+        <v>46184.53255631945</v>
+      </c>
+      <c r="E38" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="F38" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G38" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="H38" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="I38" s="5">
+        <v>46245</v>
+      </c>
+      <c r="J38" s="5">
+        <v>46253</v>
+      </c>
+      <c r="K38" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L38" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M38" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N38" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="O38" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="P38" s="6" t="s">
         <v>144</v>
-      </c>
-      <c r="B38" s="5">
-        <v>46169.558381979165</v>
-      </c>
-      <c r="C38" s="5">
-        <v>46184.53220534722</v>
-      </c>
-      <c r="D38" s="5">
-        <v>46184.5322071875</v>
-      </c>
-      <c r="E38" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="F38" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G38" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="H38" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="I38" s="5">
-        <v>46241</v>
-      </c>
-      <c r="J38" s="5">
-        <v>46244</v>
-      </c>
-      <c r="K38" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L38" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M38" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N38" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="O38" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="P38" s="6" t="s">
-        <v>145</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -3776,34 +3749,34 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="B39" s="9">
+        <v>46169.55839107639</v>
+      </c>
+      <c r="C39" s="9">
+        <v>46190.64487847222</v>
+      </c>
+      <c r="D39" s="9">
+        <v>46195.70377494213</v>
+      </c>
+      <c r="E39" s="10" t="s">
         <v>146</v>
       </c>
-      <c r="B39" s="9">
-        <v>46169.55838657408</v>
-      </c>
-      <c r="C39" s="9">
-        <v>46184.53255483796</v>
-      </c>
-      <c r="D39" s="9">
-        <v>46184.53255631945</v>
-      </c>
-      <c r="E39" s="10" t="s">
+      <c r="F39" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G39" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="F39" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G39" s="10" t="s">
-        <v>132</v>
-      </c>
       <c r="H39" s="10" t="s">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="I39" s="9">
-        <v>46245</v>
+        <v>46241</v>
       </c>
       <c r="J39" s="9">
-        <v>46253</v>
+        <v>46281</v>
       </c>
       <c r="K39" s="10" t="s">
         <v>26</v>
@@ -3815,50 +3788,60 @@
         <v>26</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>142</v>
+        <v>91</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>87</v>
+        <v>149</v>
       </c>
       <c r="P39" s="10" t="s">
-        <v>148</v>
-      </c>
-      <c r="Q39" s="10"/>
-      <c r="R39" s="10"/>
-      <c r="S39" s="10"/>
-      <c r="T39" s="10"/>
-      <c r="U39" s="10"/>
+        <v>26</v>
+      </c>
+      <c r="Q39" s="9">
+        <v>46241</v>
+      </c>
+      <c r="R39" s="9">
+        <v>46281</v>
+      </c>
+      <c r="S39" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T39" s="10">
+        <v>1</v>
+      </c>
+      <c r="U39" s="11" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B40" s="5">
-        <v>46169.55839107639</v>
+        <v>46169.55839478009</v>
       </c>
       <c r="C40" s="5">
-        <v>46190.64487847222</v>
+        <v>46195.70359988426</v>
       </c>
       <c r="D40" s="5">
-        <v>46195.70377494213</v>
+        <v>46195.70360162037</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>150</v>
+        <v>89</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="I40" s="5">
         <v>46241</v>
       </c>
       <c r="J40" s="5">
-        <v>46281</v>
+        <v>46251</v>
       </c>
       <c r="K40" s="6" t="s">
         <v>26</v>
@@ -3870,78 +3853,68 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>95</v>
+        <v>146</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>153</v>
+        <v>88</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q40" s="5">
-        <v>46241</v>
-      </c>
-      <c r="R40" s="5">
-        <v>46281</v>
-      </c>
-      <c r="S40" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T40" s="6">
-        <v>1</v>
-      </c>
-      <c r="U40" s="11" t="s">
-        <v>65</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="Q40" s="6"/>
+      <c r="R40" s="6"/>
+      <c r="S40" s="6"/>
+      <c r="T40" s="6"/>
+      <c r="U40" s="6"/>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="B41" s="9">
+        <v>46169.55839910879</v>
+      </c>
+      <c r="C41" s="9">
+        <v>46195.703751678244</v>
+      </c>
+      <c r="D41" s="9">
+        <v>46195.70375376157</v>
+      </c>
+      <c r="E41" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="F41" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G41" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="H41" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="I41" s="9">
+        <v>46252</v>
+      </c>
+      <c r="J41" s="9">
+        <v>46280</v>
+      </c>
+      <c r="K41" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L41" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M41" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N41" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="O41" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="P41" s="10" t="s">
         <v>154</v>
-      </c>
-      <c r="B41" s="9">
-        <v>46169.55839478009</v>
-      </c>
-      <c r="C41" s="9">
-        <v>46195.70359988426</v>
-      </c>
-      <c r="D41" s="9">
-        <v>46195.70360162037</v>
-      </c>
-      <c r="E41" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="F41" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G41" s="10" t="s">
-        <v>151</v>
-      </c>
-      <c r="H41" s="10" t="s">
-        <v>152</v>
-      </c>
-      <c r="I41" s="9">
-        <v>46241</v>
-      </c>
-      <c r="J41" s="9">
-        <v>46251</v>
-      </c>
-      <c r="K41" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L41" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M41" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N41" s="10" t="s">
-        <v>150</v>
-      </c>
-      <c r="O41" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="P41" s="10" t="s">
-        <v>155</v>
       </c>
       <c r="Q41" s="10"/>
       <c r="R41" s="10"/>
@@ -3951,34 +3924,32 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="B42" s="5">
+        <v>46169.55840355324</v>
+      </c>
+      <c r="C42" s="6"/>
+      <c r="D42" s="5">
+        <v>46195.703763495374</v>
+      </c>
+      <c r="E42" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="B42" s="5">
-        <v>46169.55839910879</v>
-      </c>
-      <c r="C42" s="5">
-        <v>46195.703751678244</v>
-      </c>
-      <c r="D42" s="5">
-        <v>46195.70375376157</v>
-      </c>
-      <c r="E42" s="6" t="s">
+      <c r="F42" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G42" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="F42" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G42" s="6" t="s">
-        <v>151</v>
-      </c>
       <c r="H42" s="6" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="I42" s="5">
-        <v>46252</v>
+        <v>46281</v>
       </c>
       <c r="J42" s="5">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="K42" s="6" t="s">
         <v>26</v>
@@ -3990,13 +3961,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>93</v>
+        <v>153</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>158</v>
+        <v>26</v>
       </c>
       <c r="Q42" s="6"/>
       <c r="R42" s="6"/>
@@ -4009,11 +3980,13 @@
         <v>159</v>
       </c>
       <c r="B43" s="9">
-        <v>46169.55840355324</v>
-      </c>
-      <c r="C43" s="10"/>
+        <v>46169.55840677083</v>
+      </c>
+      <c r="C43" s="9">
+        <v>46191.53700108796</v>
+      </c>
       <c r="D43" s="9">
-        <v>46195.703763495374</v>
+        <v>46191.53701371528</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>160</v>
@@ -4022,71 +3995,81 @@
         <v>26</v>
       </c>
       <c r="G43" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="H43" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="I43" s="9">
+        <v>46241</v>
+      </c>
+      <c r="J43" s="9">
+        <v>46253</v>
+      </c>
+      <c r="K43" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L43" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M43" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N43" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="O43" s="10" t="s">
         <v>161</v>
       </c>
-      <c r="H43" s="10" t="s">
-        <v>162</v>
-      </c>
-      <c r="I43" s="9">
-        <v>46281</v>
-      </c>
-      <c r="J43" s="9">
-        <v>46281</v>
-      </c>
-      <c r="K43" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L43" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M43" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N43" s="10" t="s">
-        <v>150</v>
-      </c>
-      <c r="O43" s="10" t="s">
-        <v>157</v>
-      </c>
       <c r="P43" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="Q43" s="10"/>
-      <c r="R43" s="10"/>
-      <c r="S43" s="10"/>
-      <c r="T43" s="10"/>
-      <c r="U43" s="10"/>
+      <c r="Q43" s="9">
+        <v>46241</v>
+      </c>
+      <c r="R43" s="9">
+        <v>46253</v>
+      </c>
+      <c r="S43" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T43" s="10">
+        <v>1</v>
+      </c>
+      <c r="U43" s="7" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B44" s="5">
-        <v>46169.55840677083</v>
+        <v>46169.55841037037</v>
       </c>
       <c r="C44" s="5">
-        <v>46191.53700108796</v>
+        <v>46191.53678993056</v>
       </c>
       <c r="D44" s="5">
-        <v>46191.53701371528</v>
+        <v>46191.53679194444</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>164</v>
+        <v>86</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="I44" s="5">
         <v>46241</v>
       </c>
       <c r="J44" s="5">
-        <v>46253</v>
+        <v>46244</v>
       </c>
       <c r="K44" s="6" t="s">
         <v>26</v>
@@ -4098,78 +4081,68 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>95</v>
+        <v>160</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>165</v>
+        <v>85</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q44" s="5">
-        <v>46241</v>
-      </c>
-      <c r="R44" s="5">
-        <v>46253</v>
-      </c>
-      <c r="S44" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T44" s="6">
-        <v>1</v>
-      </c>
-      <c r="U44" s="7" t="s">
-        <v>27</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="Q44" s="6"/>
+      <c r="R44" s="6"/>
+      <c r="S44" s="6"/>
+      <c r="T44" s="6"/>
+      <c r="U44" s="6"/>
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="B45" s="9">
+        <v>46169.558458217594</v>
+      </c>
+      <c r="C45" s="9">
+        <v>46191.53698667824</v>
+      </c>
+      <c r="D45" s="9">
+        <v>46191.53698841435</v>
+      </c>
+      <c r="E45" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="F45" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G45" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="H45" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="I45" s="9">
+        <v>46245</v>
+      </c>
+      <c r="J45" s="9">
+        <v>46253</v>
+      </c>
+      <c r="K45" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L45" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M45" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N45" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="O45" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="P45" s="10" t="s">
         <v>166</v>
-      </c>
-      <c r="B45" s="9">
-        <v>46169.55841037037</v>
-      </c>
-      <c r="C45" s="9">
-        <v>46191.53678993056</v>
-      </c>
-      <c r="D45" s="9">
-        <v>46191.53679194444</v>
-      </c>
-      <c r="E45" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="F45" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G45" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="H45" s="10" t="s">
-        <v>133</v>
-      </c>
-      <c r="I45" s="9">
-        <v>46241</v>
-      </c>
-      <c r="J45" s="9">
-        <v>46244</v>
-      </c>
-      <c r="K45" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L45" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M45" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N45" s="10" t="s">
-        <v>164</v>
-      </c>
-      <c r="O45" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="P45" s="10" t="s">
-        <v>167</v>
       </c>
       <c r="Q45" s="10"/>
       <c r="R45" s="10"/>
@@ -4179,82 +4152,84 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="B46" s="5">
+        <v>46169.5584643287</v>
+      </c>
+      <c r="C46" s="6"/>
+      <c r="D46" s="5">
+        <v>46182.75962331019</v>
+      </c>
+      <c r="E46" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="B46" s="5">
-        <v>46169.558458217594</v>
-      </c>
-      <c r="C46" s="5">
-        <v>46191.53698667824</v>
-      </c>
-      <c r="D46" s="5">
-        <v>46191.53698841435</v>
-      </c>
-      <c r="E46" s="6" t="s">
+      <c r="F46" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="G46" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="H46" s="6"/>
+      <c r="I46" s="6"/>
+      <c r="J46" s="6"/>
+      <c r="K46" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L46" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M46" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="N46" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="O46" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="F46" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G46" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="H46" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="I46" s="5">
-        <v>46245</v>
-      </c>
-      <c r="J46" s="5">
-        <v>46253</v>
-      </c>
-      <c r="K46" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L46" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M46" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N46" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="O46" s="6" t="s">
-        <v>90</v>
-      </c>
       <c r="P46" s="6" t="s">
-        <v>170</v>
+        <v>26</v>
       </c>
       <c r="Q46" s="6"/>
       <c r="R46" s="6"/>
       <c r="S46" s="6"/>
       <c r="T46" s="6"/>
-      <c r="U46" s="6"/>
+      <c r="U46" s="11" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="B47" s="9">
+        <v>46169.55846813657</v>
+      </c>
+      <c r="C47" s="9">
+        <v>46181.72664483797</v>
+      </c>
+      <c r="D47" s="9">
+        <v>46185.205444907406</v>
+      </c>
+      <c r="E47" s="10" t="s">
         <v>171</v>
       </c>
-      <c r="B47" s="9">
-        <v>46169.5584643287</v>
-      </c>
-      <c r="C47" s="10"/>
-      <c r="D47" s="9">
-        <v>46182.75962331019</v>
-      </c>
-      <c r="E47" s="10" t="s">
+      <c r="F47" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G47" s="10" t="s">
         <v>172</v>
       </c>
-      <c r="F47" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="G47" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H47" s="10"/>
-      <c r="I47" s="10"/>
-      <c r="J47" s="10"/>
+      <c r="H47" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="I47" s="9">
+        <v>46167</v>
+      </c>
+      <c r="J47" s="9">
+        <v>46184</v>
+      </c>
       <c r="K47" s="10" t="s">
         <v>26</v>
       </c>
@@ -4262,49 +4237,57 @@
         <v>26</v>
       </c>
       <c r="M47" s="10" t="s">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>26</v>
+        <v>168</v>
       </c>
       <c r="O47" s="10" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="P47" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q47" s="10"/>
-      <c r="R47" s="10"/>
-      <c r="S47" s="10"/>
-      <c r="T47" s="10"/>
-      <c r="U47" s="11" t="s">
-        <v>65</v>
+        <v>168</v>
+      </c>
+      <c r="Q47" s="9">
+        <v>46167</v>
+      </c>
+      <c r="R47" s="9">
+        <v>46184</v>
+      </c>
+      <c r="S47" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="T47" s="10">
+        <v>1</v>
+      </c>
+      <c r="U47" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="B48" s="5">
+        <v>46169.558472766206</v>
+      </c>
+      <c r="C48" s="5">
+        <v>46181.72662902778</v>
+      </c>
+      <c r="D48" s="5">
+        <v>46181.72663056713</v>
+      </c>
+      <c r="E48" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="B48" s="5">
-        <v>46169.55846813657</v>
-      </c>
-      <c r="C48" s="5">
-        <v>46181.72664483797</v>
-      </c>
-      <c r="D48" s="5">
-        <v>46185.205444907406</v>
-      </c>
-      <c r="E48" s="6" t="s">
-        <v>175</v>
-      </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="I48" s="5">
         <v>46167</v>
@@ -4322,60 +4305,50 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>178</v>
+        <v>60</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>172</v>
-      </c>
-      <c r="Q48" s="5">
-        <v>46167</v>
-      </c>
-      <c r="R48" s="5">
-        <v>46184</v>
-      </c>
-      <c r="S48" s="12" t="s">
-        <v>179</v>
-      </c>
-      <c r="T48" s="6">
-        <v>1</v>
-      </c>
-      <c r="U48" s="7" t="s">
-        <v>27</v>
-      </c>
+        <v>177</v>
+      </c>
+      <c r="Q48" s="6"/>
+      <c r="R48" s="6"/>
+      <c r="S48" s="6"/>
+      <c r="T48" s="6"/>
+      <c r="U48" s="6"/>
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B49" s="9">
-        <v>46169.558472766206</v>
+        <v>46169.55849938658</v>
       </c>
       <c r="C49" s="9">
-        <v>46181.72662902778</v>
+        <v>46182.759602164355</v>
       </c>
       <c r="D49" s="9">
-        <v>46181.72663056713</v>
+        <v>46182.75961601852</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="10" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="I49" s="9">
-        <v>46167</v>
+        <v>46218</v>
       </c>
       <c r="J49" s="9">
-        <v>46184</v>
+        <v>46237</v>
       </c>
       <c r="K49" s="10" t="s">
         <v>26</v>
@@ -4387,44 +4360,54 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>60</v>
+        <v>174</v>
       </c>
       <c r="P49" s="10" t="s">
-        <v>181</v>
-      </c>
-      <c r="Q49" s="10"/>
-      <c r="R49" s="10"/>
-      <c r="S49" s="10"/>
-      <c r="T49" s="10"/>
-      <c r="U49" s="10"/>
+        <v>168</v>
+      </c>
+      <c r="Q49" s="9">
+        <v>46218</v>
+      </c>
+      <c r="R49" s="9">
+        <v>46237</v>
+      </c>
+      <c r="S49" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T49" s="10">
+        <v>1</v>
+      </c>
+      <c r="U49" s="7" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B50" s="5">
-        <v>46169.55849938658</v>
+        <v>46169.55850371528</v>
       </c>
       <c r="C50" s="5">
-        <v>46182.759602164355</v>
+        <v>46182.75958561343</v>
       </c>
       <c r="D50" s="5">
-        <v>46182.75961601852</v>
+        <v>46195.690583055555</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="I50" s="5">
         <v>46218</v>
@@ -4442,109 +4425,109 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>172</v>
-      </c>
-      <c r="Q50" s="5">
-        <v>46218</v>
-      </c>
-      <c r="R50" s="5">
-        <v>46237</v>
-      </c>
-      <c r="S50" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T50" s="6">
-        <v>1</v>
-      </c>
-      <c r="U50" s="7" t="s">
-        <v>27</v>
-      </c>
+        <v>182</v>
+      </c>
+      <c r="Q50" s="6"/>
+      <c r="R50" s="6"/>
+      <c r="S50" s="6"/>
+      <c r="T50" s="6"/>
+      <c r="U50" s="6"/>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="B51" s="9">
+        <v>46169.55853228009</v>
+      </c>
+      <c r="C51" s="9">
+        <v>46182.75986146991</v>
+      </c>
+      <c r="D51" s="9">
+        <v>46182.759871076385</v>
+      </c>
+      <c r="E51" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="F51" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G51" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="H51" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="I51" s="9">
+        <v>46238</v>
+      </c>
+      <c r="J51" s="9">
+        <v>46238</v>
+      </c>
+      <c r="K51" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L51" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M51" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N51" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="O51" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="P51" s="10" t="s">
         <v>184</v>
       </c>
-      <c r="B51" s="9">
-        <v>46169.55850371528</v>
-      </c>
-      <c r="C51" s="9">
-        <v>46182.75958561343</v>
-      </c>
-      <c r="D51" s="9">
-        <v>46195.690583055555</v>
-      </c>
-      <c r="E51" s="10" t="s">
-        <v>178</v>
-      </c>
-      <c r="F51" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G51" s="10" t="s">
-        <v>176</v>
-      </c>
-      <c r="H51" s="10" t="s">
-        <v>177</v>
-      </c>
-      <c r="I51" s="9">
-        <v>46218</v>
-      </c>
-      <c r="J51" s="9">
-        <v>46237</v>
-      </c>
-      <c r="K51" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L51" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M51" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N51" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="O51" s="10" t="s">
-        <v>185</v>
-      </c>
-      <c r="P51" s="10" t="s">
-        <v>186</v>
-      </c>
-      <c r="Q51" s="10"/>
-      <c r="R51" s="10"/>
-      <c r="S51" s="10"/>
-      <c r="T51" s="10"/>
-      <c r="U51" s="10"/>
+      <c r="Q51" s="9">
+        <v>46238</v>
+      </c>
+      <c r="R51" s="9">
+        <v>46238</v>
+      </c>
+      <c r="S51" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T51" s="10">
+        <v>1</v>
+      </c>
+      <c r="U51" s="7" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B52" s="5">
-        <v>46169.55853228009</v>
+        <v>46169.55854641204</v>
       </c>
       <c r="C52" s="5">
-        <v>46182.75986146991</v>
+        <v>46182.75984711805</v>
       </c>
       <c r="D52" s="5">
-        <v>46182.759871076385</v>
+        <v>46182.75984881945</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>83</v>
+        <v>174</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="I52" s="5">
         <v>46238</v>
@@ -4562,60 +4545,48 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>172</v>
+        <v>79</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>188</v>
-      </c>
-      <c r="Q52" s="5">
-        <v>46238</v>
-      </c>
-      <c r="R52" s="5">
-        <v>46238</v>
-      </c>
-      <c r="S52" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T52" s="6">
-        <v>1</v>
-      </c>
-      <c r="U52" s="7" t="s">
-        <v>27</v>
-      </c>
+        <v>79</v>
+      </c>
+      <c r="Q52" s="6"/>
+      <c r="R52" s="6"/>
+      <c r="S52" s="6"/>
+      <c r="T52" s="6"/>
+      <c r="U52" s="6"/>
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="B53" s="9">
+        <v>46169.558565775464</v>
+      </c>
+      <c r="C53" s="10"/>
+      <c r="D53" s="9">
+        <v>46169.61885943287</v>
+      </c>
+      <c r="E53" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="F53" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G53" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="H53" s="10" t="s">
         <v>189</v>
       </c>
-      <c r="B53" s="9">
-        <v>46169.55854641204</v>
-      </c>
-      <c r="C53" s="9">
-        <v>46182.75984711805</v>
-      </c>
-      <c r="D53" s="9">
-        <v>46182.75984881945</v>
-      </c>
-      <c r="E53" s="10" t="s">
-        <v>178</v>
-      </c>
-      <c r="F53" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G53" s="10" t="s">
-        <v>176</v>
-      </c>
-      <c r="H53" s="10" t="s">
-        <v>177</v>
-      </c>
       <c r="I53" s="9">
-        <v>46238</v>
+        <v>46331</v>
       </c>
       <c r="J53" s="9">
-        <v>46238</v>
+        <v>46331</v>
       </c>
       <c r="K53" s="10" t="s">
         <v>26</v>
@@ -4627,42 +4598,52 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>83</v>
+        <v>168</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="Q53" s="10"/>
-      <c r="R53" s="10"/>
-      <c r="S53" s="10"/>
-      <c r="T53" s="10"/>
-      <c r="U53" s="10"/>
+        <v>26</v>
+      </c>
+      <c r="Q53" s="9">
+        <v>46331</v>
+      </c>
+      <c r="R53" s="9">
+        <v>46331</v>
+      </c>
+      <c r="S53" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T53" s="10">
+        <v>0</v>
+      </c>
+      <c r="U53" s="12" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
         <v>190</v>
       </c>
       <c r="B54" s="5">
-        <v>46169.558565775464</v>
+        <v>46169.55856972223</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46169.61885943287</v>
+        <v>46169.61882613426</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>191</v>
+        <v>174</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="I54" s="5">
         <v>46331</v>
@@ -4680,59 +4661,43 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>172</v>
+        <v>187</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q54" s="5">
-        <v>46331</v>
-      </c>
-      <c r="R54" s="5">
-        <v>46331</v>
-      </c>
-      <c r="S54" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T54" s="6">
-        <v>0</v>
-      </c>
-      <c r="U54" s="12" t="s">
-        <v>105</v>
-      </c>
+        <v>192</v>
+      </c>
+      <c r="Q54" s="6"/>
+      <c r="R54" s="6"/>
+      <c r="S54" s="6"/>
+      <c r="T54" s="6"/>
+      <c r="U54" s="6"/>
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B55" s="9">
-        <v>46169.55856972223</v>
+        <v>46169.558586307874</v>
       </c>
       <c r="C55" s="10"/>
       <c r="D55" s="9">
-        <v>46169.61882613426</v>
+        <v>46190.6449599537</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>178</v>
+        <v>194</v>
       </c>
       <c r="F55" s="10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G55" s="10" t="s">
-        <v>192</v>
-      </c>
-      <c r="H55" s="10" t="s">
-        <v>193</v>
-      </c>
-      <c r="I55" s="9">
-        <v>46331</v>
-      </c>
-      <c r="J55" s="9">
-        <v>46331</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H55" s="10"/>
+      <c r="I55" s="10"/>
+      <c r="J55" s="10"/>
       <c r="K55" s="10" t="s">
         <v>26</v>
       </c>
@@ -4740,16 +4705,16 @@
         <v>26</v>
       </c>
       <c r="M55" s="10" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>191</v>
+        <v>26</v>
       </c>
       <c r="O55" s="10" t="s">
         <v>195</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>196</v>
+        <v>26</v>
       </c>
       <c r="Q55" s="10"/>
       <c r="R55" s="10"/>
@@ -4759,27 +4724,35 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="B56" s="5">
+        <v>46169.55858945602</v>
+      </c>
+      <c r="C56" s="5">
+        <v>46190.64495354166</v>
+      </c>
+      <c r="D56" s="5">
+        <v>46196.80606199074</v>
+      </c>
+      <c r="E56" s="6" t="s">
         <v>197</v>
       </c>
-      <c r="B56" s="5">
-        <v>46169.558586307874</v>
-      </c>
-      <c r="C56" s="6"/>
-      <c r="D56" s="5">
-        <v>46190.6449599537</v>
-      </c>
-      <c r="E56" s="6" t="s">
+      <c r="F56" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G56" s="6" t="s">
         <v>198</v>
       </c>
-      <c r="F56" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G56" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H56" s="6"/>
-      <c r="I56" s="6"/>
-      <c r="J56" s="6"/>
+      <c r="H56" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="I56" s="5">
+        <v>46254</v>
+      </c>
+      <c r="J56" s="5">
+        <v>46255</v>
+      </c>
       <c r="K56" s="6" t="s">
         <v>26</v>
       </c>
@@ -4787,140 +4760,148 @@
         <v>26</v>
       </c>
       <c r="M56" s="6" t="s">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>26</v>
+        <v>194</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>199</v>
+        <v>135</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q56" s="6"/>
-      <c r="R56" s="6"/>
-      <c r="S56" s="6"/>
-      <c r="T56" s="6"/>
-      <c r="U56" s="6"/>
+        <v>200</v>
+      </c>
+      <c r="Q56" s="5">
+        <v>46254</v>
+      </c>
+      <c r="R56" s="5">
+        <v>46255</v>
+      </c>
+      <c r="S56" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T56" s="6">
+        <v>1</v>
+      </c>
+      <c r="U56" s="7" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B57" s="9">
-        <v>46169.55858945602</v>
-      </c>
-      <c r="C57" s="9">
-        <v>46190.64495354166</v>
-      </c>
+        <v>46169.55859488426</v>
+      </c>
+      <c r="C57" s="10"/>
       <c r="D57" s="9">
-        <v>46190.644969375004</v>
+        <v>46196.80590905093</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="10" t="s">
-        <v>202</v>
+        <v>157</v>
       </c>
       <c r="H57" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="I57" s="9">
+        <v>46258</v>
+      </c>
+      <c r="J57" s="9">
+        <v>46259</v>
+      </c>
+      <c r="K57" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L57" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M57" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N57" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="O57" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="P57" s="10" t="s">
         <v>203</v>
       </c>
-      <c r="I57" s="9">
-        <v>46254</v>
-      </c>
-      <c r="J57" s="9">
-        <v>46255</v>
-      </c>
-      <c r="K57" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L57" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M57" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N57" s="10" t="s">
-        <v>198</v>
-      </c>
-      <c r="O57" s="10" t="s">
-        <v>139</v>
-      </c>
-      <c r="P57" s="10" t="s">
-        <v>204</v>
-      </c>
       <c r="Q57" s="9">
-        <v>46254</v>
+        <v>46258</v>
       </c>
       <c r="R57" s="9">
-        <v>46255</v>
+        <v>46259</v>
       </c>
       <c r="S57" s="7" t="s">
         <v>33</v>
       </c>
       <c r="T57" s="10">
-        <v>1</v>
-      </c>
-      <c r="U57" s="7" t="s">
-        <v>27</v>
+        <v>0</v>
+      </c>
+      <c r="U57" s="11" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B58" s="5">
-        <v>46169.55859488426</v>
+        <v>46169.55860118056</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46190.64496048611</v>
+        <v>46196.80590315972</v>
       </c>
       <c r="E58" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="F58" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G58" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="H58" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="I58" s="5">
+        <v>46254</v>
+      </c>
+      <c r="J58" s="5">
+        <v>46255</v>
+      </c>
+      <c r="K58" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L58" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M58" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N58" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="O58" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="P58" s="6" t="s">
         <v>206</v>
       </c>
-      <c r="F58" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G58" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="H58" s="6" t="s">
-        <v>162</v>
-      </c>
-      <c r="I58" s="5">
-        <v>46258</v>
-      </c>
-      <c r="J58" s="5">
-        <v>46259</v>
-      </c>
-      <c r="K58" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L58" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M58" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N58" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="O58" s="6" t="s">
-        <v>207</v>
-      </c>
-      <c r="P58" s="6" t="s">
-        <v>208</v>
-      </c>
       <c r="Q58" s="5">
-        <v>46258</v>
+        <v>46254</v>
       </c>
       <c r="R58" s="5">
-        <v>46259</v>
+        <v>46255</v>
       </c>
       <c r="S58" s="7" t="s">
         <v>33</v>
@@ -4928,38 +4909,38 @@
       <c r="T58" s="6">
         <v>0</v>
       </c>
-      <c r="U58" s="12" t="s">
-        <v>105</v>
+      <c r="U58" s="11" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B59" s="9">
-        <v>46169.55860118056</v>
+        <v>46169.55860636574</v>
       </c>
       <c r="C59" s="10"/>
       <c r="D59" s="9">
-        <v>46184.53257491898</v>
+        <v>46169.620307997684</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>202</v>
+        <v>157</v>
       </c>
       <c r="H59" s="10" t="s">
-        <v>203</v>
+        <v>158</v>
       </c>
       <c r="I59" s="9">
-        <v>46254</v>
+        <v>46258</v>
       </c>
       <c r="J59" s="9">
-        <v>46255</v>
+        <v>46259</v>
       </c>
       <c r="K59" s="10" t="s">
         <v>26</v>
@@ -4971,19 +4952,19 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>147</v>
+        <v>205</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>211</v>
+        <v>174</v>
       </c>
       <c r="Q59" s="9">
-        <v>46254</v>
+        <v>46258</v>
       </c>
       <c r="R59" s="9">
-        <v>46255</v>
+        <v>46259</v>
       </c>
       <c r="S59" s="7" t="s">
         <v>33</v>
@@ -4991,38 +4972,38 @@
       <c r="T59" s="10">
         <v>0</v>
       </c>
-      <c r="U59" s="11" t="s">
-        <v>65</v>
+      <c r="U59" s="12" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="B60" s="5">
-        <v>46169.55860636574</v>
+        <v>46169.558650127314</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46169.620307997684</v>
+        <v>46191.53700491898</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>161</v>
+        <v>198</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>162</v>
+        <v>199</v>
       </c>
       <c r="I60" s="5">
-        <v>46258</v>
+        <v>46254</v>
       </c>
       <c r="J60" s="5">
-        <v>46259</v>
+        <v>46255</v>
       </c>
       <c r="K60" s="6" t="s">
         <v>26</v>
@@ -5034,19 +5015,19 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="O60" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="P60" s="6" t="s">
         <v>210</v>
       </c>
-      <c r="P60" s="6" t="s">
-        <v>178</v>
-      </c>
       <c r="Q60" s="5">
-        <v>46258</v>
+        <v>46254</v>
       </c>
       <c r="R60" s="5">
-        <v>46259</v>
+        <v>46255</v>
       </c>
       <c r="S60" s="7" t="s">
         <v>33</v>
@@ -5054,38 +5035,38 @@
       <c r="T60" s="6">
         <v>0</v>
       </c>
-      <c r="U60" s="12" t="s">
-        <v>105</v>
+      <c r="U60" s="11" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B61" s="9">
-        <v>46169.558650127314</v>
+        <v>46169.55865608796</v>
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="9">
-        <v>46191.53700491898</v>
+        <v>46169.620303483796</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="10" t="s">
-        <v>202</v>
+        <v>157</v>
       </c>
       <c r="H61" s="10" t="s">
-        <v>203</v>
+        <v>158</v>
       </c>
       <c r="I61" s="9">
-        <v>46254</v>
+        <v>46258</v>
       </c>
       <c r="J61" s="9">
-        <v>46255</v>
+        <v>46259</v>
       </c>
       <c r="K61" s="10" t="s">
         <v>26</v>
@@ -5097,19 +5078,19 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>169</v>
+        <v>209</v>
       </c>
       <c r="P61" s="10" t="s">
-        <v>216</v>
+        <v>174</v>
       </c>
       <c r="Q61" s="9">
-        <v>46254</v>
+        <v>46258</v>
       </c>
       <c r="R61" s="9">
-        <v>46255</v>
+        <v>46259</v>
       </c>
       <c r="S61" s="7" t="s">
         <v>33</v>
@@ -5117,39 +5098,33 @@
       <c r="T61" s="10">
         <v>0</v>
       </c>
-      <c r="U61" s="11" t="s">
-        <v>65</v>
+      <c r="U61" s="12" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="B62" s="5">
-        <v>46169.55865608796</v>
+        <v>46169.55866105324</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46169.620303483796</v>
+        <v>46190.645330810185</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="F62" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="H62" s="6" t="s">
-        <v>162</v>
-      </c>
-      <c r="I62" s="5">
-        <v>46258</v>
-      </c>
-      <c r="J62" s="5">
-        <v>46259</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H62" s="6"/>
+      <c r="I62" s="6"/>
+      <c r="J62" s="6"/>
       <c r="K62" s="6" t="s">
         <v>26</v>
       </c>
@@ -5157,104 +5132,110 @@
         <v>26</v>
       </c>
       <c r="M62" s="6" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>198</v>
+        <v>26</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="Q62" s="5">
-        <v>46258</v>
-      </c>
-      <c r="R62" s="5">
-        <v>46259</v>
-      </c>
-      <c r="S62" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T62" s="6">
-        <v>0</v>
-      </c>
-      <c r="U62" s="12" t="s">
-        <v>105</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q62" s="6"/>
+      <c r="R62" s="6"/>
+      <c r="S62" s="6"/>
+      <c r="T62" s="6"/>
+      <c r="U62" s="6"/>
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
+        <v>215</v>
+      </c>
+      <c r="B63" s="9">
+        <v>46169.55866469907</v>
+      </c>
+      <c r="C63" s="9">
+        <v>46190.645243935185</v>
+      </c>
+      <c r="D63" s="9">
+        <v>46190.645261516205</v>
+      </c>
+      <c r="E63" s="10" t="s">
+        <v>216</v>
+      </c>
+      <c r="F63" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G63" s="10" t="s">
+        <v>217</v>
+      </c>
+      <c r="H63" s="10" t="s">
         <v>218</v>
       </c>
-      <c r="B63" s="9">
-        <v>46169.55866105324</v>
-      </c>
-      <c r="C63" s="10"/>
-      <c r="D63" s="9">
-        <v>46190.645330810185</v>
-      </c>
-      <c r="E63" s="10" t="s">
+      <c r="I63" s="9">
+        <v>46260</v>
+      </c>
+      <c r="J63" s="9">
+        <v>46268</v>
+      </c>
+      <c r="K63" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L63" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M63" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N63" s="10" t="s">
+        <v>213</v>
+      </c>
+      <c r="O63" s="10" t="s">
         <v>219</v>
       </c>
-      <c r="F63" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="G63" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H63" s="10"/>
-      <c r="I63" s="10"/>
-      <c r="J63" s="10"/>
-      <c r="K63" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L63" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M63" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="N63" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="O63" s="10" t="s">
-        <v>220</v>
-      </c>
       <c r="P63" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q63" s="10"/>
-      <c r="R63" s="10"/>
-      <c r="S63" s="10"/>
-      <c r="T63" s="10"/>
-      <c r="U63" s="10"/>
+        <v>213</v>
+      </c>
+      <c r="Q63" s="9">
+        <v>46260</v>
+      </c>
+      <c r="R63" s="9">
+        <v>46268</v>
+      </c>
+      <c r="S63" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T63" s="10">
+        <v>1</v>
+      </c>
+      <c r="U63" s="7" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B64" s="5">
-        <v>46169.55866469907</v>
-      </c>
-      <c r="C64" s="5">
-        <v>46190.645243935185</v>
-      </c>
+        <v>46169.55867099537</v>
+      </c>
+      <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46190.645261516205</v>
+        <v>46169.62059548611</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>222</v>
+        <v>174</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="I64" s="5">
         <v>46260</v>
@@ -5272,58 +5253,50 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>219</v>
-      </c>
-      <c r="Q64" s="5">
-        <v>46260</v>
-      </c>
-      <c r="R64" s="5">
-        <v>46268</v>
-      </c>
-      <c r="S64" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T64" s="6">
-        <v>1</v>
-      </c>
-      <c r="U64" s="7" t="s">
-        <v>27</v>
-      </c>
+        <v>222</v>
+      </c>
+      <c r="Q64" s="6"/>
+      <c r="R64" s="6"/>
+      <c r="S64" s="6"/>
+      <c r="T64" s="6"/>
+      <c r="U64" s="6"/>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="B65" s="9">
-        <v>46169.55867099537</v>
-      </c>
-      <c r="C65" s="10"/>
+        <v>46169.558703518516</v>
+      </c>
+      <c r="C65" s="9">
+        <v>46190.64532476851</v>
+      </c>
       <c r="D65" s="9">
-        <v>46169.62059548611</v>
+        <v>46190.64534048611</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>178</v>
+        <v>224</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="H65" s="10" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="I65" s="9">
-        <v>46260</v>
+        <v>46269</v>
       </c>
       <c r="J65" s="9">
-        <v>46268</v>
+        <v>46273</v>
       </c>
       <c r="K65" s="10" t="s">
         <v>26</v>
@@ -5335,44 +5308,52 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>227</v>
+        <v>174</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>228</v>
-      </c>
-      <c r="Q65" s="10"/>
-      <c r="R65" s="10"/>
-      <c r="S65" s="10"/>
-      <c r="T65" s="10"/>
-      <c r="U65" s="10"/>
+        <v>213</v>
+      </c>
+      <c r="Q65" s="9">
+        <v>46269</v>
+      </c>
+      <c r="R65" s="9">
+        <v>46273</v>
+      </c>
+      <c r="S65" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T65" s="10">
+        <v>1</v>
+      </c>
+      <c r="U65" s="7" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="B66" s="5">
-        <v>46169.558703518516</v>
-      </c>
-      <c r="C66" s="5">
-        <v>46190.64532476851</v>
-      </c>
+        <v>46169.55870879629</v>
+      </c>
+      <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46190.64534048611</v>
+        <v>46182.75987778935</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>230</v>
+        <v>174</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="I66" s="5">
         <v>46269</v>
@@ -5390,58 +5371,48 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>178</v>
+        <v>226</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>219</v>
-      </c>
-      <c r="Q66" s="5">
-        <v>46269</v>
-      </c>
-      <c r="R66" s="5">
-        <v>46273</v>
-      </c>
-      <c r="S66" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T66" s="6">
-        <v>1</v>
-      </c>
-      <c r="U66" s="7" t="s">
-        <v>27</v>
-      </c>
+        <v>227</v>
+      </c>
+      <c r="Q66" s="6"/>
+      <c r="R66" s="6"/>
+      <c r="S66" s="6"/>
+      <c r="T66" s="6"/>
+      <c r="U66" s="6"/>
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="B67" s="9">
-        <v>46169.55870879629</v>
+        <v>46169.558740625</v>
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="9">
-        <v>46182.75987778935</v>
+        <v>46169.62084700231</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>178</v>
+        <v>229</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="I67" s="9">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="J67" s="9">
-        <v>46273</v>
+        <v>46275</v>
       </c>
       <c r="K67" s="10" t="s">
         <v>26</v>
@@ -5453,42 +5424,52 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>230</v>
+        <v>213</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>232</v>
+        <v>174</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>233</v>
-      </c>
-      <c r="Q67" s="10"/>
-      <c r="R67" s="10"/>
-      <c r="S67" s="10"/>
-      <c r="T67" s="10"/>
-      <c r="U67" s="10"/>
+        <v>213</v>
+      </c>
+      <c r="Q67" s="9">
+        <v>46274</v>
+      </c>
+      <c r="R67" s="9">
+        <v>46275</v>
+      </c>
+      <c r="S67" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T67" s="10">
+        <v>0</v>
+      </c>
+      <c r="U67" s="12" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="B68" s="5">
-        <v>46169.558740625</v>
+        <v>46169.558745243055</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46169.62084700231</v>
+        <v>46182.759876192125</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>235</v>
+        <v>174</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="I68" s="5">
         <v>46274</v>
@@ -5506,59 +5487,43 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>219</v>
+        <v>229</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>178</v>
+        <v>226</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>219</v>
-      </c>
-      <c r="Q68" s="5">
-        <v>46274</v>
-      </c>
-      <c r="R68" s="5">
-        <v>46275</v>
-      </c>
-      <c r="S68" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T68" s="6">
-        <v>0</v>
-      </c>
-      <c r="U68" s="12" t="s">
-        <v>105</v>
-      </c>
+        <v>231</v>
+      </c>
+      <c r="Q68" s="6"/>
+      <c r="R68" s="6"/>
+      <c r="S68" s="6"/>
+      <c r="T68" s="6"/>
+      <c r="U68" s="6"/>
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="B69" s="9">
-        <v>46169.558745243055</v>
+        <v>46169.55876947917</v>
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="9">
-        <v>46182.759876192125</v>
+        <v>46169.60236578704</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>178</v>
+        <v>194</v>
       </c>
       <c r="F69" s="10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G69" s="10" t="s">
-        <v>223</v>
-      </c>
-      <c r="H69" s="10" t="s">
-        <v>224</v>
-      </c>
-      <c r="I69" s="9">
-        <v>46274</v>
-      </c>
-      <c r="J69" s="9">
-        <v>46275</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H69" s="10"/>
+      <c r="I69" s="10"/>
+      <c r="J69" s="10"/>
       <c r="K69" s="10" t="s">
         <v>26</v>
       </c>
@@ -5566,16 +5531,16 @@
         <v>26</v>
       </c>
       <c r="M69" s="10" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>235</v>
+        <v>26</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>237</v>
+        <v>26</v>
       </c>
       <c r="Q69" s="10"/>
       <c r="R69" s="10"/>
@@ -5585,27 +5550,33 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="B70" s="5">
-        <v>46169.55876947917</v>
+        <v>46169.55880633101</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46169.60236578704</v>
+        <v>46184.736466689814</v>
       </c>
       <c r="E70" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="F70" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G70" s="6" t="s">
         <v>198</v>
       </c>
-      <c r="F70" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G70" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H70" s="6"/>
-      <c r="I70" s="6"/>
-      <c r="J70" s="6"/>
+      <c r="H70" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="I70" s="5">
+        <v>46220</v>
+      </c>
+      <c r="J70" s="5">
+        <v>46223</v>
+      </c>
       <c r="K70" s="6" t="s">
         <v>26</v>
       </c>
@@ -5613,51 +5584,61 @@
         <v>26</v>
       </c>
       <c r="M70" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N70" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="O70" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="P70" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="Q70" s="5">
+        <v>46220</v>
+      </c>
+      <c r="R70" s="5">
+        <v>46223</v>
+      </c>
+      <c r="S70" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T70" s="6">
         <v>0</v>
       </c>
-      <c r="N70" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="O70" s="6" t="s">
-        <v>239</v>
-      </c>
-      <c r="P70" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q70" s="6"/>
-      <c r="R70" s="6"/>
-      <c r="S70" s="6"/>
-      <c r="T70" s="6"/>
-      <c r="U70" s="6"/>
+      <c r="U70" s="11" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="B71" s="9">
-        <v>46169.55880633101</v>
+        <v>46169.5588177662</v>
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="9">
-        <v>46184.736466689814</v>
+        <v>46182.673394074074</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="10" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="H71" s="10" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="I71" s="9">
-        <v>46220</v>
+        <v>46325</v>
       </c>
       <c r="J71" s="9">
-        <v>46223</v>
+        <v>46325</v>
       </c>
       <c r="K71" s="10" t="s">
         <v>26</v>
@@ -5669,121 +5650,121 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="Q71" s="9">
-        <v>46220</v>
+        <v>46325</v>
       </c>
       <c r="R71" s="9">
-        <v>46223</v>
-      </c>
-      <c r="S71" s="7" t="s">
-        <v>33</v>
+        <v>46325</v>
+      </c>
+      <c r="S71" s="12" t="s">
+        <v>175</v>
       </c>
       <c r="T71" s="10">
         <v>0</v>
       </c>
       <c r="U71" s="11" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="B72" s="5">
-        <v>46169.5588177662</v>
+        <v>46169.55882295139</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46182.673394074074</v>
+        <v>46182.6734475</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="H72" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="I72" s="5">
+        <v>46293</v>
+      </c>
+      <c r="J72" s="5">
+        <v>46293</v>
+      </c>
+      <c r="K72" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L72" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M72" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N72" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="O72" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="P72" s="6" t="s">
         <v>203</v>
       </c>
-      <c r="I72" s="5">
-        <v>46325</v>
-      </c>
-      <c r="J72" s="5">
-        <v>46325</v>
-      </c>
-      <c r="K72" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L72" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M72" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N72" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="O72" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="P72" s="6" t="s">
-        <v>245</v>
-      </c>
       <c r="Q72" s="5">
-        <v>46325</v>
+        <v>46293</v>
       </c>
       <c r="R72" s="5">
-        <v>46325</v>
-      </c>
-      <c r="S72" s="12" t="s">
-        <v>179</v>
+        <v>46293</v>
+      </c>
+      <c r="S72" s="7" t="s">
+        <v>33</v>
       </c>
       <c r="T72" s="6">
         <v>0</v>
       </c>
       <c r="U72" s="11" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B73" s="9">
-        <v>46169.55882295139</v>
+        <v>46169.55882788195</v>
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="9">
-        <v>46182.6734475</v>
+        <v>46195.70377457176</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="10" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="H73" s="10" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="I73" s="9">
-        <v>46293</v>
+        <v>46282</v>
       </c>
       <c r="J73" s="9">
-        <v>46293</v>
+        <v>46282</v>
       </c>
       <c r="K73" s="10" t="s">
         <v>26</v>
@@ -5795,19 +5776,19 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>125</v>
+        <v>153</v>
       </c>
       <c r="P73" s="10" t="s">
-        <v>208</v>
+        <v>244</v>
       </c>
       <c r="Q73" s="9">
-        <v>46293</v>
+        <v>46282</v>
       </c>
       <c r="R73" s="9">
-        <v>46293</v>
+        <v>46282</v>
       </c>
       <c r="S73" s="7" t="s">
         <v>33</v>
@@ -5816,38 +5797,32 @@
         <v>0</v>
       </c>
       <c r="U73" s="11" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="B74" s="5">
-        <v>46169.55882788195</v>
+        <v>46169.55884254629</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46195.70377457176</v>
+        <v>46169.60519671296</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="F74" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>202</v>
-      </c>
-      <c r="H74" s="6" t="s">
-        <v>203</v>
-      </c>
-      <c r="I74" s="5">
-        <v>46282</v>
-      </c>
-      <c r="J74" s="5">
-        <v>46282</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H74" s="6"/>
+      <c r="I74" s="6"/>
+      <c r="J74" s="6"/>
       <c r="K74" s="6" t="s">
         <v>26</v>
       </c>
@@ -5855,56 +5830,52 @@
         <v>26</v>
       </c>
       <c r="M74" s="6" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>198</v>
+        <v>26</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>157</v>
+        <v>247</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>250</v>
-      </c>
-      <c r="Q74" s="5">
-        <v>46282</v>
-      </c>
-      <c r="R74" s="5">
-        <v>46282</v>
-      </c>
-      <c r="S74" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T74" s="6">
-        <v>0</v>
-      </c>
-      <c r="U74" s="11" t="s">
-        <v>65</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q74" s="6"/>
+      <c r="R74" s="6"/>
+      <c r="S74" s="6"/>
+      <c r="T74" s="6"/>
+      <c r="U74" s="6"/>
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="B75" s="9">
-        <v>46169.55884254629</v>
+        <v>46169.55884548611</v>
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="9">
-        <v>46169.60519671296</v>
+        <v>46191.65585405093</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="F75" s="10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G75" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H75" s="10"/>
-      <c r="I75" s="10"/>
-      <c r="J75" s="10"/>
+        <v>73</v>
+      </c>
+      <c r="H75" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="I75" s="9">
+        <v>46276</v>
+      </c>
+      <c r="J75" s="9">
+        <v>46295</v>
+      </c>
       <c r="K75" s="10" t="s">
         <v>26</v>
       </c>
@@ -5912,45 +5883,55 @@
         <v>26</v>
       </c>
       <c r="M75" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N75" s="10" t="s">
+        <v>246</v>
+      </c>
+      <c r="O75" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="P75" s="10" t="s">
+        <v>246</v>
+      </c>
+      <c r="Q75" s="9">
+        <v>46276</v>
+      </c>
+      <c r="R75" s="9">
+        <v>46295</v>
+      </c>
+      <c r="S75" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T75" s="10">
         <v>0</v>
       </c>
-      <c r="N75" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="O75" s="10" t="s">
-        <v>253</v>
-      </c>
-      <c r="P75" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q75" s="10"/>
-      <c r="R75" s="10"/>
-      <c r="S75" s="10"/>
-      <c r="T75" s="10"/>
-      <c r="U75" s="10"/>
+      <c r="U75" s="12" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="B76" s="5">
-        <v>46169.55884548611</v>
+        <v>46169.55884993056</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46191.65585405093</v>
+        <v>46169.62097653935</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>255</v>
+        <v>174</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="I76" s="5">
         <v>46276</v>
@@ -5968,58 +5949,48 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="O76" s="6" t="s">
         <v>252</v>
       </c>
-      <c r="O76" s="6" t="s">
-        <v>256</v>
-      </c>
       <c r="P76" s="6" t="s">
-        <v>252</v>
-      </c>
-      <c r="Q76" s="5">
-        <v>46276</v>
-      </c>
-      <c r="R76" s="5">
-        <v>46295</v>
-      </c>
-      <c r="S76" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T76" s="6">
-        <v>0</v>
-      </c>
-      <c r="U76" s="12" t="s">
-        <v>105</v>
-      </c>
+        <v>249</v>
+      </c>
+      <c r="Q76" s="6"/>
+      <c r="R76" s="6"/>
+      <c r="S76" s="6"/>
+      <c r="T76" s="6"/>
+      <c r="U76" s="6"/>
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="B77" s="9">
-        <v>46169.55884993056</v>
+        <v>46169.55893170139</v>
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="9">
-        <v>46169.62097653935</v>
+        <v>46169.62115951389</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>178</v>
+        <v>254</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="10" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H77" s="10" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="I77" s="9">
-        <v>46276</v>
+        <v>46296</v>
       </c>
       <c r="J77" s="9">
-        <v>46295</v>
+        <v>46297</v>
       </c>
       <c r="K77" s="10" t="s">
         <v>26</v>
@@ -6031,42 +6002,52 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>258</v>
+        <v>174</v>
       </c>
       <c r="P77" s="10" t="s">
-        <v>255</v>
-      </c>
-      <c r="Q77" s="10"/>
-      <c r="R77" s="10"/>
-      <c r="S77" s="10"/>
-      <c r="T77" s="10"/>
-      <c r="U77" s="10"/>
+        <v>246</v>
+      </c>
+      <c r="Q77" s="9">
+        <v>46296</v>
+      </c>
+      <c r="R77" s="9">
+        <v>46297</v>
+      </c>
+      <c r="S77" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T77" s="10">
+        <v>0</v>
+      </c>
+      <c r="U77" s="12" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="B78" s="5">
-        <v>46169.55893170139</v>
+        <v>46169.55893543981</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46169.62115951389</v>
+        <v>46182.75987846065</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>260</v>
+        <v>174</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="I78" s="5">
         <v>46296</v>
@@ -6084,58 +6065,48 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>178</v>
+        <v>256</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>252</v>
-      </c>
-      <c r="Q78" s="5">
-        <v>46296</v>
-      </c>
-      <c r="R78" s="5">
-        <v>46297</v>
-      </c>
-      <c r="S78" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T78" s="6">
-        <v>0</v>
-      </c>
-      <c r="U78" s="12" t="s">
-        <v>105</v>
-      </c>
+        <v>257</v>
+      </c>
+      <c r="Q78" s="6"/>
+      <c r="R78" s="6"/>
+      <c r="S78" s="6"/>
+      <c r="T78" s="6"/>
+      <c r="U78" s="6"/>
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="B79" s="9">
-        <v>46169.55893543981</v>
+        <v>46169.558869560184</v>
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="9">
-        <v>46182.75987846065</v>
+        <v>46169.621266111106</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>178</v>
+        <v>259</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="10" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H79" s="10" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="I79" s="9">
-        <v>46296</v>
+        <v>46328</v>
       </c>
       <c r="J79" s="9">
-        <v>46297</v>
+        <v>46328</v>
       </c>
       <c r="K79" s="10" t="s">
         <v>26</v>
@@ -6147,42 +6118,52 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>260</v>
+        <v>246</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>262</v>
+        <v>191</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>263</v>
-      </c>
-      <c r="Q79" s="10"/>
-      <c r="R79" s="10"/>
-      <c r="S79" s="10"/>
-      <c r="T79" s="10"/>
-      <c r="U79" s="10"/>
+        <v>246</v>
+      </c>
+      <c r="Q79" s="9">
+        <v>46328</v>
+      </c>
+      <c r="R79" s="9">
+        <v>46328</v>
+      </c>
+      <c r="S79" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T79" s="10">
+        <v>0</v>
+      </c>
+      <c r="U79" s="12" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="B80" s="5">
-        <v>46169.558869560184</v>
+        <v>46169.55887296297</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46169.621266111106</v>
+        <v>46182.759876909724</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>265</v>
+        <v>191</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="I80" s="5">
         <v>46328</v>
@@ -6200,58 +6181,48 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>195</v>
+        <v>261</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>252</v>
-      </c>
-      <c r="Q80" s="5">
-        <v>46328</v>
-      </c>
-      <c r="R80" s="5">
-        <v>46328</v>
-      </c>
-      <c r="S80" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T80" s="6">
-        <v>0</v>
-      </c>
-      <c r="U80" s="12" t="s">
-        <v>105</v>
-      </c>
+        <v>262</v>
+      </c>
+      <c r="Q80" s="6"/>
+      <c r="R80" s="6"/>
+      <c r="S80" s="6"/>
+      <c r="T80" s="6"/>
+      <c r="U80" s="6"/>
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="B81" s="9">
-        <v>46169.55887296297</v>
+        <v>46169.5589025463</v>
       </c>
       <c r="C81" s="10"/>
       <c r="D81" s="9">
-        <v>46182.759876909724</v>
+        <v>46169.62135181713</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>195</v>
+        <v>264</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="10" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H81" s="10" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="I81" s="9">
-        <v>46328</v>
+        <v>46329</v>
       </c>
       <c r="J81" s="9">
-        <v>46328</v>
+        <v>46329</v>
       </c>
       <c r="K81" s="10" t="s">
         <v>26</v>
@@ -6263,42 +6234,52 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>265</v>
+        <v>246</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>267</v>
+        <v>174</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>268</v>
-      </c>
-      <c r="Q81" s="10"/>
-      <c r="R81" s="10"/>
-      <c r="S81" s="10"/>
-      <c r="T81" s="10"/>
-      <c r="U81" s="10"/>
+        <v>246</v>
+      </c>
+      <c r="Q81" s="9">
+        <v>46329</v>
+      </c>
+      <c r="R81" s="9">
+        <v>46329</v>
+      </c>
+      <c r="S81" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T81" s="10">
+        <v>0</v>
+      </c>
+      <c r="U81" s="12" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="B82" s="5">
-        <v>46169.5589025463</v>
+        <v>46169.55890609954</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46169.62135181713</v>
+        <v>46182.759877442135</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>270</v>
+        <v>174</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="I82" s="5">
         <v>46329</v>
@@ -6316,58 +6297,48 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>178</v>
+        <v>266</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>252</v>
-      </c>
-      <c r="Q82" s="5">
-        <v>46329</v>
-      </c>
-      <c r="R82" s="5">
-        <v>46329</v>
-      </c>
-      <c r="S82" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T82" s="6">
-        <v>0</v>
-      </c>
-      <c r="U82" s="12" t="s">
-        <v>105</v>
-      </c>
+        <v>267</v>
+      </c>
+      <c r="Q82" s="6"/>
+      <c r="R82" s="6"/>
+      <c r="S82" s="6"/>
+      <c r="T82" s="6"/>
+      <c r="U82" s="6"/>
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="B83" s="9">
-        <v>46169.55890609954</v>
+        <v>46169.55900443287</v>
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="9">
-        <v>46182.759877442135</v>
+        <v>46169.621444178236</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>178</v>
+        <v>269</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="10" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H83" s="10" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="I83" s="9">
-        <v>46329</v>
+        <v>46330</v>
       </c>
       <c r="J83" s="9">
-        <v>46329</v>
+        <v>46330</v>
       </c>
       <c r="K83" s="10" t="s">
         <v>26</v>
@@ -6379,42 +6350,52 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>270</v>
+        <v>246</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>272</v>
+        <v>191</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>273</v>
-      </c>
-      <c r="Q83" s="10"/>
-      <c r="R83" s="10"/>
-      <c r="S83" s="10"/>
-      <c r="T83" s="10"/>
-      <c r="U83" s="10"/>
+        <v>246</v>
+      </c>
+      <c r="Q83" s="9">
+        <v>46330</v>
+      </c>
+      <c r="R83" s="9">
+        <v>46330</v>
+      </c>
+      <c r="S83" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T83" s="10">
+        <v>0</v>
+      </c>
+      <c r="U83" s="12" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="B84" s="5">
-        <v>46169.55900443287</v>
+        <v>46169.55901002315</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46169.621444178236</v>
+        <v>46169.6214072338</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>275</v>
+        <v>191</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="I84" s="5">
         <v>46330</v>
@@ -6432,58 +6413,48 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>252</v>
+        <v>269</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>195</v>
+        <v>174</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>252</v>
-      </c>
-      <c r="Q84" s="5">
-        <v>46330</v>
-      </c>
-      <c r="R84" s="5">
-        <v>46330</v>
-      </c>
-      <c r="S84" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T84" s="6">
-        <v>0</v>
-      </c>
-      <c r="U84" s="12" t="s">
-        <v>105</v>
-      </c>
+        <v>271</v>
+      </c>
+      <c r="Q84" s="6"/>
+      <c r="R84" s="6"/>
+      <c r="S84" s="6"/>
+      <c r="T84" s="6"/>
+      <c r="U84" s="6"/>
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="B85" s="9">
-        <v>46169.55901002315</v>
+        <v>46169.55904462963</v>
       </c>
       <c r="C85" s="10"/>
       <c r="D85" s="9">
-        <v>46169.6214072338</v>
+        <v>46169.62153172454</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>195</v>
+        <v>273</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="10" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H85" s="10" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="I85" s="9">
-        <v>46330</v>
+        <v>46332</v>
       </c>
       <c r="J85" s="9">
-        <v>46330</v>
+        <v>46332</v>
       </c>
       <c r="K85" s="10" t="s">
         <v>26</v>
@@ -6495,42 +6466,52 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>275</v>
+        <v>246</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="P85" s="10" t="s">
-        <v>277</v>
-      </c>
-      <c r="Q85" s="10"/>
-      <c r="R85" s="10"/>
-      <c r="S85" s="10"/>
-      <c r="T85" s="10"/>
-      <c r="U85" s="10"/>
+        <v>274</v>
+      </c>
+      <c r="Q85" s="9">
+        <v>46332</v>
+      </c>
+      <c r="R85" s="9">
+        <v>46332</v>
+      </c>
+      <c r="S85" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T85" s="10">
+        <v>0</v>
+      </c>
+      <c r="U85" s="12" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="B86" s="5">
-        <v>46169.55904462963</v>
+        <v>46169.559050138894</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46169.62153172454</v>
+        <v>46169.62149153935</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>279</v>
+        <v>191</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="I86" s="5">
         <v>46332</v>
@@ -6548,59 +6529,43 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>252</v>
+        <v>273</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>195</v>
+        <v>174</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>280</v>
-      </c>
-      <c r="Q86" s="5">
-        <v>46332</v>
-      </c>
-      <c r="R86" s="5">
-        <v>46332</v>
-      </c>
-      <c r="S86" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T86" s="6">
-        <v>0</v>
-      </c>
-      <c r="U86" s="12" t="s">
-        <v>105</v>
-      </c>
+        <v>276</v>
+      </c>
+      <c r="Q86" s="6"/>
+      <c r="R86" s="6"/>
+      <c r="S86" s="6"/>
+      <c r="T86" s="6"/>
+      <c r="U86" s="6"/>
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="B87" s="9">
-        <v>46169.559050138894</v>
+        <v>46169.55907484954</v>
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="9">
-        <v>46169.62149153935</v>
+        <v>46169.60623452546</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>195</v>
+        <v>278</v>
       </c>
       <c r="F87" s="10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G87" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="H87" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="I87" s="9">
-        <v>46332</v>
-      </c>
-      <c r="J87" s="9">
-        <v>46332</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H87" s="10"/>
+      <c r="I87" s="10"/>
+      <c r="J87" s="10"/>
       <c r="K87" s="10" t="s">
         <v>26</v>
       </c>
@@ -6608,16 +6573,16 @@
         <v>26</v>
       </c>
       <c r="M87" s="10" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N87" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="O87" s="10" t="s">
         <v>279</v>
       </c>
-      <c r="O87" s="10" t="s">
-        <v>178</v>
-      </c>
       <c r="P87" s="10" t="s">
-        <v>282</v>
+        <v>26</v>
       </c>
       <c r="Q87" s="10"/>
       <c r="R87" s="10"/>
@@ -6627,27 +6592,33 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="B88" s="5">
-        <v>46169.55907484954</v>
+        <v>46169.55907863426</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46169.60623452546</v>
+        <v>46169.621643935185</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="F88" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H88" s="6"/>
-      <c r="I88" s="6"/>
-      <c r="J88" s="6"/>
+        <v>282</v>
+      </c>
+      <c r="H88" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="I88" s="5">
+        <v>46335</v>
+      </c>
+      <c r="J88" s="5">
+        <v>46335</v>
+      </c>
       <c r="K88" s="6" t="s">
         <v>26</v>
       </c>
@@ -6655,45 +6626,55 @@
         <v>26</v>
       </c>
       <c r="M88" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N88" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="O88" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="P88" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="Q88" s="5">
+        <v>46335</v>
+      </c>
+      <c r="R88" s="5">
+        <v>46335</v>
+      </c>
+      <c r="S88" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T88" s="6">
         <v>0</v>
       </c>
-      <c r="N88" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="O88" s="6" t="s">
-        <v>285</v>
-      </c>
-      <c r="P88" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q88" s="6"/>
-      <c r="R88" s="6"/>
-      <c r="S88" s="6"/>
-      <c r="T88" s="6"/>
-      <c r="U88" s="6"/>
+      <c r="U88" s="12" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B89" s="9">
-        <v>46169.55907863426</v>
+        <v>46169.55908684028</v>
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="9">
-        <v>46169.621643935185</v>
+        <v>46169.62159425926</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>287</v>
+        <v>191</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="10" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="H89" s="10" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="I89" s="9">
         <v>46335</v>
@@ -6711,58 +6692,48 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>282</v>
+        <v>191</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>284</v>
-      </c>
-      <c r="Q89" s="9">
-        <v>46335</v>
-      </c>
-      <c r="R89" s="9">
-        <v>46335</v>
-      </c>
-      <c r="S89" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T89" s="10">
-        <v>0</v>
-      </c>
-      <c r="U89" s="12" t="s">
-        <v>105</v>
-      </c>
+        <v>285</v>
+      </c>
+      <c r="Q89" s="10"/>
+      <c r="R89" s="10"/>
+      <c r="S89" s="10"/>
+      <c r="T89" s="10"/>
+      <c r="U89" s="10"/>
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="B90" s="5">
-        <v>46169.55908684028</v>
+        <v>46169.55918673611</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46169.62159425926</v>
+        <v>46196.561689236114</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>195</v>
+        <v>287</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>288</v>
+        <v>73</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>289</v>
+        <v>73</v>
       </c>
       <c r="I90" s="5">
-        <v>46335</v>
+        <v>46336</v>
       </c>
       <c r="J90" s="5">
-        <v>46335</v>
+        <v>46336</v>
       </c>
       <c r="K90" s="6" t="s">
         <v>26</v>
@@ -6774,42 +6745,52 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>287</v>
+        <v>278</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>291</v>
-      </c>
-      <c r="Q90" s="6"/>
-      <c r="R90" s="6"/>
-      <c r="S90" s="6"/>
-      <c r="T90" s="6"/>
-      <c r="U90" s="6"/>
+        <v>278</v>
+      </c>
+      <c r="Q90" s="5">
+        <v>46336</v>
+      </c>
+      <c r="R90" s="5">
+        <v>46336</v>
+      </c>
+      <c r="S90" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T90" s="6">
+        <v>0</v>
+      </c>
+      <c r="U90" s="12" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="B91" s="9">
-        <v>46169.55918673611</v>
+        <v>46169.55919113426</v>
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="9">
-        <v>46196.561689236114</v>
+        <v>46169.62169328704</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>293</v>
+        <v>191</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="10" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H91" s="10" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="I91" s="9">
         <v>46336</v>
@@ -6827,58 +6808,48 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>284</v>
-      </c>
-      <c r="Q91" s="9">
-        <v>46336</v>
-      </c>
-      <c r="R91" s="9">
-        <v>46336</v>
-      </c>
-      <c r="S91" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T91" s="10">
-        <v>0</v>
-      </c>
-      <c r="U91" s="12" t="s">
-        <v>105</v>
-      </c>
+        <v>289</v>
+      </c>
+      <c r="Q91" s="10"/>
+      <c r="R91" s="10"/>
+      <c r="S91" s="10"/>
+      <c r="T91" s="10"/>
+      <c r="U91" s="10"/>
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="B92" s="5">
-        <v>46169.55919113426</v>
+        <v>46169.559239560185</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46169.62169328704</v>
+        <v>46196.565746747685</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>195</v>
+        <v>291</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>77</v>
+        <v>217</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>77</v>
+        <v>218</v>
       </c>
       <c r="I92" s="5">
-        <v>46336</v>
+        <v>46337</v>
       </c>
       <c r="J92" s="5">
-        <v>46336</v>
+        <v>46337</v>
       </c>
       <c r="K92" s="6" t="s">
         <v>26</v>
@@ -6890,42 +6861,52 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>293</v>
+        <v>278</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>295</v>
-      </c>
-      <c r="Q92" s="6"/>
-      <c r="R92" s="6"/>
-      <c r="S92" s="6"/>
-      <c r="T92" s="6"/>
-      <c r="U92" s="6"/>
+        <v>278</v>
+      </c>
+      <c r="Q92" s="5">
+        <v>46337</v>
+      </c>
+      <c r="R92" s="5">
+        <v>46337</v>
+      </c>
+      <c r="S92" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T92" s="6">
+        <v>0</v>
+      </c>
+      <c r="U92" s="12" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="B93" s="9">
-        <v>46169.559239560185</v>
+        <v>46169.559243842596</v>
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="9">
-        <v>46196.565746747685</v>
+        <v>46169.621808449076</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>297</v>
+        <v>191</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="10" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="H93" s="10" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="I93" s="9">
         <v>46337</v>
@@ -6943,58 +6924,48 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>284</v>
+        <v>291</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>284</v>
-      </c>
-      <c r="Q93" s="9">
-        <v>46337</v>
-      </c>
-      <c r="R93" s="9">
-        <v>46337</v>
-      </c>
-      <c r="S93" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T93" s="10">
-        <v>0</v>
-      </c>
-      <c r="U93" s="12" t="s">
-        <v>105</v>
-      </c>
+        <v>293</v>
+      </c>
+      <c r="Q93" s="10"/>
+      <c r="R93" s="10"/>
+      <c r="S93" s="10"/>
+      <c r="T93" s="10"/>
+      <c r="U93" s="10"/>
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="B94" s="5">
-        <v>46169.559243842596</v>
+        <v>46169.55929686343</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46169.621808449076</v>
+        <v>46196.573311342596</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>195</v>
+        <v>295</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="I94" s="5">
-        <v>46337</v>
+        <v>46338</v>
       </c>
       <c r="J94" s="5">
-        <v>46337</v>
+        <v>46338</v>
       </c>
       <c r="K94" s="6" t="s">
         <v>26</v>
@@ -7006,42 +6977,52 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="O94" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="P94" s="6" t="s">
         <v>297</v>
       </c>
-      <c r="O94" s="6" t="s">
-        <v>195</v>
-      </c>
-      <c r="P94" s="6" t="s">
-        <v>299</v>
-      </c>
-      <c r="Q94" s="6"/>
-      <c r="R94" s="6"/>
-      <c r="S94" s="6"/>
-      <c r="T94" s="6"/>
-      <c r="U94" s="6"/>
+      <c r="Q94" s="5">
+        <v>46338</v>
+      </c>
+      <c r="R94" s="5">
+        <v>46338</v>
+      </c>
+      <c r="S94" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T94" s="6">
+        <v>0</v>
+      </c>
+      <c r="U94" s="12" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B95" s="9">
-        <v>46169.55929686343</v>
+        <v>46169.55930180555</v>
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="9">
-        <v>46196.573311342596</v>
+        <v>46169.621891215276</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="10" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="H95" s="10" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="I95" s="9">
         <v>46338</v>
@@ -7059,59 +7040,43 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>284</v>
+        <v>295</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>302</v>
+        <v>191</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>303</v>
-      </c>
-      <c r="Q95" s="9">
-        <v>46338</v>
-      </c>
-      <c r="R95" s="9">
-        <v>46338</v>
-      </c>
-      <c r="S95" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T95" s="10">
-        <v>0</v>
-      </c>
-      <c r="U95" s="12" t="s">
-        <v>105</v>
-      </c>
+        <v>295</v>
+      </c>
+      <c r="Q95" s="10"/>
+      <c r="R95" s="10"/>
+      <c r="S95" s="10"/>
+      <c r="T95" s="10"/>
+      <c r="U95" s="10"/>
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="B96" s="5">
-        <v>46169.55930180555</v>
+        <v>46169.55938721065</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46169.621891215276</v>
+        <v>46169.60672822916</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="F96" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>223</v>
-      </c>
-      <c r="H96" s="6" t="s">
-        <v>224</v>
-      </c>
-      <c r="I96" s="5">
-        <v>46338</v>
-      </c>
-      <c r="J96" s="5">
-        <v>46338</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H96" s="6"/>
+      <c r="I96" s="6"/>
+      <c r="J96" s="6"/>
       <c r="K96" s="6" t="s">
         <v>26</v>
       </c>
@@ -7119,16 +7084,16 @@
         <v>26</v>
       </c>
       <c r="M96" s="6" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N96" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="O96" s="6" t="s">
         <v>301</v>
       </c>
-      <c r="O96" s="6" t="s">
-        <v>195</v>
-      </c>
       <c r="P96" s="6" t="s">
-        <v>301</v>
+        <v>26</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -7138,27 +7103,33 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="B97" s="9">
-        <v>46169.55938721065</v>
+        <v>46169.55939094907</v>
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="9">
-        <v>46169.60672822916</v>
+        <v>46169.621991215274</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="F97" s="10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G97" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H97" s="10"/>
-      <c r="I97" s="10"/>
-      <c r="J97" s="10"/>
+        <v>304</v>
+      </c>
+      <c r="H97" s="10" t="s">
+        <v>305</v>
+      </c>
+      <c r="I97" s="9">
+        <v>46339</v>
+      </c>
+      <c r="J97" s="9">
+        <v>46349</v>
+      </c>
       <c r="K97" s="10" t="s">
         <v>26</v>
       </c>
@@ -7166,45 +7137,55 @@
         <v>26</v>
       </c>
       <c r="M97" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N97" s="10" t="s">
+        <v>300</v>
+      </c>
+      <c r="O97" s="10" t="s">
+        <v>295</v>
+      </c>
+      <c r="P97" s="10" t="s">
+        <v>300</v>
+      </c>
+      <c r="Q97" s="9">
+        <v>46339</v>
+      </c>
+      <c r="R97" s="9">
+        <v>46349</v>
+      </c>
+      <c r="S97" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T97" s="10">
         <v>0</v>
       </c>
-      <c r="N97" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="O97" s="10" t="s">
-        <v>307</v>
-      </c>
-      <c r="P97" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q97" s="10"/>
-      <c r="R97" s="10"/>
-      <c r="S97" s="10"/>
-      <c r="T97" s="10"/>
-      <c r="U97" s="10"/>
+      <c r="U97" s="12" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B98" s="5">
-        <v>46169.55939094907</v>
+        <v>46169.55939643519</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46169.621991215274</v>
+        <v>46196.805673622686</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>310</v>
+        <v>51</v>
       </c>
       <c r="H98" s="6" t="s">
-        <v>311</v>
+        <v>52</v>
       </c>
       <c r="I98" s="5">
         <v>46339</v>
@@ -7222,13 +7203,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="Q98" s="5">
         <v>46339</v>
@@ -7243,70 +7224,7 @@
         <v>0</v>
       </c>
       <c r="U98" s="12" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="99" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A99" s="8" t="s">
-        <v>312</v>
-      </c>
-      <c r="B99" s="9">
-        <v>46169.55939643519</v>
-      </c>
-      <c r="C99" s="10"/>
-      <c r="D99" s="9">
-        <v>46169.62202572917</v>
-      </c>
-      <c r="E99" s="10" t="s">
-        <v>313</v>
-      </c>
-      <c r="F99" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G99" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="H99" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="I99" s="9">
-        <v>46339</v>
-      </c>
-      <c r="J99" s="9">
-        <v>46349</v>
-      </c>
-      <c r="K99" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L99" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M99" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N99" s="10" t="s">
-        <v>306</v>
-      </c>
-      <c r="O99" s="10" t="s">
-        <v>314</v>
-      </c>
-      <c r="P99" s="10" t="s">
-        <v>306</v>
-      </c>
-      <c r="Q99" s="9">
-        <v>46339</v>
-      </c>
-      <c r="R99" s="9">
-        <v>46349</v>
-      </c>
-      <c r="S99" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T99" s="10">
-        <v>0</v>
-      </c>
-      <c r="U99" s="12" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001557 - ATACAMA KOZAN OT4340.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4340.xlsx
@@ -708,7 +708,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t xml:space="preserve">OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR,OT2 4232 ZVN 1-9-86/2 </t>
+    <t xml:space="preserve">OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR,OT2 4307 ZVN 1-9-86/2 </t>
   </si>
   <si>
     <t>1215166433625244</t>

--- a/data/50001557 - ATACAMA KOZAN OT4340.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4340.xlsx
@@ -5809,7 +5809,7 @@
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46169.60519671296</v>
+        <v>46197.49537680556</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>246</v>
@@ -5854,9 +5854,11 @@
       <c r="B75" s="9">
         <v>46169.55884548611</v>
       </c>
-      <c r="C75" s="10"/>
+      <c r="C75" s="9">
+        <v>46197.49536869213</v>
+      </c>
       <c r="D75" s="9">
-        <v>46191.65585405093</v>
+        <v>46197.49537962963</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>249</v>
@@ -5904,10 +5906,10 @@
         <v>33</v>
       </c>
       <c r="T75" s="10">
-        <v>0</v>
-      </c>
-      <c r="U75" s="12" t="s">
-        <v>101</v>
+        <v>1</v>
+      </c>
+      <c r="U75" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
@@ -5917,9 +5919,11 @@
       <c r="B76" s="5">
         <v>46169.55884993056</v>
       </c>
-      <c r="C76" s="6"/>
+      <c r="C76" s="5">
+        <v>46197.49535652778</v>
+      </c>
       <c r="D76" s="5">
-        <v>46169.62097653935</v>
+        <v>46197.495357893524</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>174</v>
@@ -5970,9 +5974,11 @@
       <c r="B77" s="9">
         <v>46169.55893170139</v>
       </c>
-      <c r="C77" s="10"/>
+      <c r="C77" s="9">
+        <v>46197.49516923611</v>
+      </c>
       <c r="D77" s="9">
-        <v>46169.62115951389</v>
+        <v>46197.495185555556</v>
       </c>
       <c r="E77" s="10" t="s">
         <v>254</v>
@@ -6020,10 +6026,10 @@
         <v>33</v>
       </c>
       <c r="T77" s="10">
-        <v>0</v>
-      </c>
-      <c r="U77" s="12" t="s">
-        <v>101</v>
+        <v>1</v>
+      </c>
+      <c r="U77" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
@@ -6033,9 +6039,11 @@
       <c r="B78" s="5">
         <v>46169.55893543981</v>
       </c>
-      <c r="C78" s="6"/>
+      <c r="C78" s="5">
+        <v>46197.4951540162</v>
+      </c>
       <c r="D78" s="5">
-        <v>46182.75987846065</v>
+        <v>46197.49515607639</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>174</v>
@@ -6383,7 +6391,7 @@
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46169.6214072338</v>
+        <v>46197.495160011575</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>191</v>

--- a/data/50001557 - ATACAMA KOZAN OT4340.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4340.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1182" uniqueCount="308">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1182" uniqueCount="310">
   <si>
     <t xml:space="preserve"> 50001557 - ATACAMA KOZAN</t>
   </si>
@@ -567,19 +567,25 @@
     <t>Planos preliminar</t>
   </si>
   <si>
+    <t>Gonzalo Javier Dávila Bade</t>
+  </si>
+  <si>
+    <t>gonzalo.davila@zitron.com</t>
+  </si>
+  <si>
+    <t>OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR</t>
+  </si>
+  <si>
+    <t>Alta</t>
+  </si>
+  <si>
+    <t>1215166433496869</t>
+  </si>
+  <si>
     <t>Hernan Roberto Gutierrez Barrientos</t>
   </si>
   <si>
     <t>hgutierrez@zitron.com</t>
-  </si>
-  <si>
-    <t>OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR</t>
-  </si>
-  <si>
-    <t>Alta</t>
-  </si>
-  <si>
-    <t>1215166433496869</t>
   </si>
   <si>
     <t>OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR,Planos preliminar</t>
@@ -4210,7 +4216,7 @@
         <v>46181.72664483797</v>
       </c>
       <c r="D47" s="9">
-        <v>46185.205444907406</v>
+        <v>46197.715420312496</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>171</v>
@@ -4284,10 +4290,10 @@
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="I48" s="5">
         <v>46167</v>
@@ -4311,7 +4317,7 @@
         <v>60</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Q48" s="6"/>
       <c r="R48" s="6"/>
@@ -4321,7 +4327,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B49" s="9">
         <v>46169.55849938658</v>
@@ -4330,10 +4336,10 @@
         <v>46182.759602164355</v>
       </c>
       <c r="D49" s="9">
-        <v>46182.75961601852</v>
+        <v>46197.71545016204</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>26</v>
@@ -4386,7 +4392,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B50" s="5">
         <v>46169.55850371528</v>
@@ -4404,10 +4410,10 @@
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="I50" s="5">
         <v>46218</v>
@@ -4425,13 +4431,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Q50" s="6"/>
       <c r="R50" s="6"/>
@@ -4441,7 +4447,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B51" s="9">
         <v>46169.55853228009</v>
@@ -4459,10 +4465,10 @@
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="I51" s="9">
         <v>46238</v>
@@ -4486,7 +4492,7 @@
         <v>174</v>
       </c>
       <c r="P51" s="10" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Q51" s="9">
         <v>46238</v>
@@ -4506,7 +4512,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B52" s="5">
         <v>46169.55854641204</v>
@@ -4524,10 +4530,10 @@
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="I52" s="5">
         <v>46238</v>
@@ -4561,7 +4567,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B53" s="9">
         <v>46169.558565775464</v>
@@ -4571,16 +4577,16 @@
         <v>46169.61885943287</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="10" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="H53" s="10" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="I53" s="9">
         <v>46331</v>
@@ -4624,7 +4630,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B54" s="5">
         <v>46169.55856972223</v>
@@ -4640,10 +4646,10 @@
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="I54" s="5">
         <v>46331</v>
@@ -4661,13 +4667,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q54" s="6"/>
       <c r="R54" s="6"/>
@@ -4677,7 +4683,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B55" s="9">
         <v>46169.558586307874</v>
@@ -4687,7 +4693,7 @@
         <v>46190.6449599537</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>25</v>
@@ -4711,7 +4717,7 @@
         <v>26</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="P55" s="10" t="s">
         <v>26</v>
@@ -4724,7 +4730,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B56" s="5">
         <v>46169.55858945602</v>
@@ -4736,16 +4742,16 @@
         <v>46196.80606199074</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="I56" s="5">
         <v>46254</v>
@@ -4763,13 +4769,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="O56" s="6" t="s">
         <v>135</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q56" s="5">
         <v>46254</v>
@@ -4789,7 +4795,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B57" s="9">
         <v>46169.55859488426</v>
@@ -4799,7 +4805,7 @@
         <v>46196.80590905093</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>26</v>
@@ -4826,13 +4832,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="P57" s="10" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q57" s="9">
         <v>46258</v>
@@ -4852,7 +4858,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B58" s="5">
         <v>46169.55860118056</v>
@@ -4862,16 +4868,16 @@
         <v>46196.80590315972</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="I58" s="5">
         <v>46254</v>
@@ -4889,13 +4895,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="O58" s="6" t="s">
         <v>143</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q58" s="5">
         <v>46254</v>
@@ -4915,7 +4921,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B59" s="9">
         <v>46169.55860636574</v>
@@ -4925,7 +4931,7 @@
         <v>46169.620307997684</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
@@ -4952,10 +4958,10 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="P59" s="10" t="s">
         <v>174</v>
@@ -4978,7 +4984,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B60" s="5">
         <v>46169.558650127314</v>
@@ -4988,16 +4994,16 @@
         <v>46191.53700491898</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="I60" s="5">
         <v>46254</v>
@@ -5015,13 +5021,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="O60" s="6" t="s">
         <v>165</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q60" s="5">
         <v>46254</v>
@@ -5041,7 +5047,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B61" s="9">
         <v>46169.55865608796</v>
@@ -5051,7 +5057,7 @@
         <v>46169.620303483796</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>26</v>
@@ -5078,10 +5084,10 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="P61" s="10" t="s">
         <v>174</v>
@@ -5104,7 +5110,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B62" s="5">
         <v>46169.55866105324</v>
@@ -5114,7 +5120,7 @@
         <v>46190.645330810185</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>25</v>
@@ -5138,7 +5144,7 @@
         <v>26</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="P62" s="6" t="s">
         <v>26</v>
@@ -5151,7 +5157,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B63" s="9">
         <v>46169.55866469907</v>
@@ -5163,16 +5169,16 @@
         <v>46190.645261516205</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="I63" s="9">
         <v>46260</v>
@@ -5190,13 +5196,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="P63" s="10" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q63" s="9">
         <v>46260</v>
@@ -5216,7 +5222,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B64" s="5">
         <v>46169.55867099537</v>
@@ -5232,10 +5238,10 @@
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="I64" s="5">
         <v>46260</v>
@@ -5253,13 +5259,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5269,7 +5275,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B65" s="9">
         <v>46169.558703518516</v>
@@ -5281,16 +5287,16 @@
         <v>46190.64534048611</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="H65" s="10" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="I65" s="9">
         <v>46269</v>
@@ -5308,13 +5314,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="O65" s="10" t="s">
         <v>174</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q65" s="9">
         <v>46269</v>
@@ -5334,7 +5340,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B66" s="5">
         <v>46169.55870879629</v>
@@ -5350,10 +5356,10 @@
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="I66" s="5">
         <v>46269</v>
@@ -5371,13 +5377,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5387,7 +5393,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B67" s="9">
         <v>46169.558740625</v>
@@ -5397,16 +5403,16 @@
         <v>46169.62084700231</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="I67" s="9">
         <v>46274</v>
@@ -5424,13 +5430,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="O67" s="10" t="s">
         <v>174</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q67" s="9">
         <v>46274</v>
@@ -5450,7 +5456,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B68" s="5">
         <v>46169.558745243055</v>
@@ -5466,10 +5472,10 @@
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="I68" s="5">
         <v>46274</v>
@@ -5487,13 +5493,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q68" s="6"/>
       <c r="R68" s="6"/>
@@ -5503,7 +5509,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B69" s="9">
         <v>46169.55876947917</v>
@@ -5513,7 +5519,7 @@
         <v>46169.60236578704</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>25</v>
@@ -5537,7 +5543,7 @@
         <v>26</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="P69" s="10" t="s">
         <v>26</v>
@@ -5550,7 +5556,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B70" s="5">
         <v>46169.55880633101</v>
@@ -5560,16 +5566,16 @@
         <v>46184.736466689814</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="I70" s="5">
         <v>46220</v>
@@ -5587,13 +5593,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="O70" s="6" t="s">
         <v>112</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q70" s="5">
         <v>46220</v>
@@ -5613,7 +5619,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B71" s="9">
         <v>46169.5588177662</v>
@@ -5623,16 +5629,16 @@
         <v>46182.673394074074</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="10" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="H71" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="I71" s="9">
         <v>46325</v>
@@ -5650,13 +5656,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="O71" s="10" t="s">
         <v>103</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q71" s="9">
         <v>46325</v>
@@ -5676,7 +5682,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B72" s="5">
         <v>46169.55882295139</v>
@@ -5686,16 +5692,16 @@
         <v>46182.6734475</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="I72" s="5">
         <v>46293</v>
@@ -5713,13 +5719,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="O72" s="6" t="s">
         <v>121</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q72" s="5">
         <v>46293</v>
@@ -5739,7 +5745,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B73" s="9">
         <v>46169.55882788195</v>
@@ -5749,16 +5755,16 @@
         <v>46195.70377457176</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="10" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="H73" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="I73" s="9">
         <v>46282</v>
@@ -5776,13 +5782,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="O73" s="10" t="s">
         <v>153</v>
       </c>
       <c r="P73" s="10" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q73" s="9">
         <v>46282</v>
@@ -5802,7 +5808,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B74" s="5">
         <v>46169.55884254629</v>
@@ -5812,7 +5818,7 @@
         <v>46197.49537680556</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>25</v>
@@ -5836,7 +5842,7 @@
         <v>26</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="P74" s="6" t="s">
         <v>26</v>
@@ -5849,7 +5855,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B75" s="9">
         <v>46169.55884548611</v>
@@ -5861,7 +5867,7 @@
         <v>46197.49537962963</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
@@ -5888,13 +5894,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q75" s="9">
         <v>46276</v>
@@ -5914,7 +5920,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B76" s="5">
         <v>46169.55884993056</v>
@@ -5953,13 +5959,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -5969,7 +5975,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B77" s="9">
         <v>46169.55893170139</v>
@@ -5981,7 +5987,7 @@
         <v>46197.495185555556</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
@@ -6008,13 +6014,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="O77" s="10" t="s">
         <v>174</v>
       </c>
       <c r="P77" s="10" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q77" s="9">
         <v>46296</v>
@@ -6034,7 +6040,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B78" s="5">
         <v>46169.55893543981</v>
@@ -6073,13 +6079,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q78" s="6"/>
       <c r="R78" s="6"/>
@@ -6089,7 +6095,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B79" s="9">
         <v>46169.558869560184</v>
@@ -6099,7 +6105,7 @@
         <v>46169.621266111106</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
@@ -6126,13 +6132,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q79" s="9">
         <v>46328</v>
@@ -6152,7 +6158,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B80" s="5">
         <v>46169.55887296297</v>
@@ -6162,7 +6168,7 @@
         <v>46182.759876909724</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
@@ -6189,13 +6195,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -6205,7 +6211,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B81" s="9">
         <v>46169.5589025463</v>
@@ -6215,7 +6221,7 @@
         <v>46169.62135181713</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
@@ -6242,13 +6248,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="O81" s="10" t="s">
         <v>174</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q81" s="9">
         <v>46329</v>
@@ -6268,7 +6274,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B82" s="5">
         <v>46169.55890609954</v>
@@ -6305,13 +6311,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6321,7 +6327,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B83" s="9">
         <v>46169.55900443287</v>
@@ -6331,7 +6337,7 @@
         <v>46169.621444178236</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
@@ -6358,13 +6364,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q83" s="9">
         <v>46330</v>
@@ -6384,7 +6390,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B84" s="5">
         <v>46169.55901002315</v>
@@ -6394,7 +6400,7 @@
         <v>46197.495160011575</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
@@ -6421,13 +6427,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="O84" s="6" t="s">
         <v>174</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q84" s="6"/>
       <c r="R84" s="6"/>
@@ -6437,7 +6443,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B85" s="9">
         <v>46169.55904462963</v>
@@ -6447,7 +6453,7 @@
         <v>46169.62153172454</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
@@ -6474,13 +6480,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="P85" s="10" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q85" s="9">
         <v>46332</v>
@@ -6500,7 +6506,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B86" s="5">
         <v>46169.559050138894</v>
@@ -6510,7 +6516,7 @@
         <v>46169.62149153935</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6537,13 +6543,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="O86" s="6" t="s">
         <v>174</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6553,7 +6559,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B87" s="9">
         <v>46169.55907484954</v>
@@ -6563,7 +6569,7 @@
         <v>46169.60623452546</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>25</v>
@@ -6587,7 +6593,7 @@
         <v>26</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="P87" s="10" t="s">
         <v>26</v>
@@ -6600,7 +6606,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B88" s="5">
         <v>46169.55907863426</v>
@@ -6610,16 +6616,16 @@
         <v>46169.621643935185</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="I88" s="5">
         <v>46335</v>
@@ -6637,13 +6643,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="O88" s="6" t="s">
         <v>278</v>
       </c>
-      <c r="O88" s="6" t="s">
-        <v>276</v>
-      </c>
       <c r="P88" s="6" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q88" s="5">
         <v>46335</v>
@@ -6663,7 +6669,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B89" s="9">
         <v>46169.55908684028</v>
@@ -6673,16 +6679,16 @@
         <v>46169.62159425926</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="10" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="H89" s="10" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="I89" s="9">
         <v>46335</v>
@@ -6700,13 +6706,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q89" s="10"/>
       <c r="R89" s="10"/>
@@ -6716,7 +6722,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B90" s="5">
         <v>46169.55918673611</v>
@@ -6726,7 +6732,7 @@
         <v>46196.561689236114</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
@@ -6753,13 +6759,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q90" s="5">
         <v>46336</v>
@@ -6779,7 +6785,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B91" s="9">
         <v>46169.55919113426</v>
@@ -6789,7 +6795,7 @@
         <v>46169.62169328704</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
@@ -6816,13 +6822,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q91" s="10"/>
       <c r="R91" s="10"/>
@@ -6832,7 +6838,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B92" s="5">
         <v>46169.559239560185</v>
@@ -6842,16 +6848,16 @@
         <v>46196.565746747685</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="I92" s="5">
         <v>46337</v>
@@ -6869,13 +6875,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q92" s="5">
         <v>46337</v>
@@ -6895,7 +6901,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B93" s="9">
         <v>46169.559243842596</v>
@@ -6905,16 +6911,16 @@
         <v>46169.621808449076</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="10" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="H93" s="10" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="I93" s="9">
         <v>46337</v>
@@ -6932,13 +6938,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q93" s="10"/>
       <c r="R93" s="10"/>
@@ -6948,7 +6954,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B94" s="5">
         <v>46169.55929686343</v>
@@ -6958,16 +6964,16 @@
         <v>46196.573311342596</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="I94" s="5">
         <v>46338</v>
@@ -6985,13 +6991,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q94" s="5">
         <v>46338</v>
@@ -7011,7 +7017,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B95" s="9">
         <v>46169.55930180555</v>
@@ -7021,16 +7027,16 @@
         <v>46169.621891215276</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="10" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="H95" s="10" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="I95" s="9">
         <v>46338</v>
@@ -7048,13 +7054,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q95" s="10"/>
       <c r="R95" s="10"/>
@@ -7064,7 +7070,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B96" s="5">
         <v>46169.55938721065</v>
@@ -7074,7 +7080,7 @@
         <v>46169.60672822916</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>25</v>
@@ -7098,7 +7104,7 @@
         <v>26</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="P96" s="6" t="s">
         <v>26</v>
@@ -7111,7 +7117,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B97" s="9">
         <v>46169.55939094907</v>
@@ -7121,16 +7127,16 @@
         <v>46169.621991215274</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G97" s="10" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="H97" s="10" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="I97" s="9">
         <v>46339</v>
@@ -7148,13 +7154,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="P97" s="10" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q97" s="9">
         <v>46339</v>
@@ -7174,7 +7180,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B98" s="5">
         <v>46169.55939643519</v>
@@ -7184,7 +7190,7 @@
         <v>46196.805673622686</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -7211,13 +7217,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q98" s="5">
         <v>46339</v>

--- a/data/50001557 - ATACAMA KOZAN OT4340.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4340.xlsx
@@ -189,9 +189,6 @@
     <t>Ingenieria Jefe de proyecto:</t>
   </si>
   <si>
-    <t>Tarea en curso</t>
-  </si>
-  <si>
     <t>1215166329057002</t>
   </si>
   <si>
@@ -330,6 +327,9 @@
     <t>Alabe - OT 4340,rodete OT 4340,Motor OT 4340,Materiales corte Laser OT 4340</t>
   </si>
   <si>
+    <t>Tarea en curso</t>
+  </si>
+  <si>
     <t>1215166243111754</t>
   </si>
   <si>
@@ -459,7 +459,7 @@
     <t>Fabricacion Corte Laser  OT 4340</t>
   </si>
   <si>
-    <t>Recepcionx materiales corte laser,Materiales corte Laser OT 4340</t>
+    <t>Recepcion materiales corte laser,Materiales corte Laser OT 4340</t>
   </si>
   <si>
     <t>1215166041659726</t>
@@ -642,13 +642,13 @@
     <t>Bodega:</t>
   </si>
   <si>
-    <t xml:space="preserve">Recepcionx materiales corte laser,Control de calidad corte laser </t>
+    <t xml:space="preserve">Recepcion materiales corte laser,Control de calidad corte laser </t>
   </si>
   <si>
     <t>1215165983005064</t>
   </si>
   <si>
-    <t>Recepcionx materiales corte laser</t>
+    <t>Recepcion materiales corte laser</t>
   </si>
   <si>
     <t>Victor Muñoz</t>
@@ -1975,9 +1975,11 @@
       <c r="B10" s="5">
         <v>46169.55800939815</v>
       </c>
-      <c r="C10" s="6"/>
+      <c r="C10" s="5">
+        <v>46197.83890001157</v>
+      </c>
       <c r="D10" s="5">
-        <v>46196.80568585648</v>
+        <v>46197.83892112269</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>47</v>
@@ -2012,14 +2014,16 @@
       <c r="Q10" s="6"/>
       <c r="R10" s="6"/>
       <c r="S10" s="6"/>
-      <c r="T10" s="6"/>
-      <c r="U10" s="11" t="s">
-        <v>48</v>
+      <c r="T10" s="6">
+        <v>1</v>
+      </c>
+      <c r="U10" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B11" s="9">
         <v>46169.558185671296</v>
@@ -2031,16 +2035,16 @@
         <v>46196.80567361111</v>
       </c>
       <c r="E11" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="F11" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G11" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="F11" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G11" s="10" t="s">
+      <c r="H11" s="10" t="s">
         <v>51</v>
-      </c>
-      <c r="H11" s="10" t="s">
-        <v>52</v>
       </c>
       <c r="I11" s="9">
         <v>46155</v>
@@ -2052,7 +2056,7 @@
         <v>26</v>
       </c>
       <c r="L11" s="10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M11" s="10" t="s">
         <v>26</v>
@@ -2064,7 +2068,7 @@
         <v>40</v>
       </c>
       <c r="P11" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="Q11" s="9">
         <v>46155</v>
@@ -2084,7 +2088,7 @@
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B12" s="5">
         <v>46169.558191840275</v>
@@ -2096,16 +2100,16 @@
         <v>46196.80567332176</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G12" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="H12" s="6" t="s">
         <v>51</v>
-      </c>
-      <c r="H12" s="6" t="s">
-        <v>52</v>
       </c>
       <c r="I12" s="5">
         <v>46155</v>
@@ -2117,7 +2121,7 @@
         <v>26</v>
       </c>
       <c r="L12" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M12" s="6" t="s">
         <v>26</v>
@@ -2129,7 +2133,7 @@
         <v>40</v>
       </c>
       <c r="P12" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Q12" s="5">
         <v>46155</v>
@@ -2149,7 +2153,7 @@
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B13" s="9">
         <v>46169.558197418984</v>
@@ -2161,16 +2165,16 @@
         <v>46196.80567320602</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F13" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G13" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="H13" s="10" t="s">
         <v>51</v>
-      </c>
-      <c r="H13" s="10" t="s">
-        <v>52</v>
       </c>
       <c r="I13" s="9">
         <v>46155</v>
@@ -2194,7 +2198,7 @@
         <v>40</v>
       </c>
       <c r="P13" s="10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="Q13" s="9">
         <v>46155</v>
@@ -2214,7 +2218,7 @@
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B14" s="5">
         <v>46169.558013773145</v>
@@ -2226,7 +2230,7 @@
         <v>46190.64417138889</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>25</v>
@@ -2250,7 +2254,7 @@
         <v>26</v>
       </c>
       <c r="O14" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="P14" s="6" t="s">
         <v>26</v>
@@ -2267,7 +2271,7 @@
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B15" s="9">
         <v>46169.558213564815</v>
@@ -2279,16 +2283,16 @@
         <v>46181.62446385417</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F15" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G15" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="H15" s="10" t="s">
         <v>51</v>
-      </c>
-      <c r="H15" s="10" t="s">
-        <v>52</v>
       </c>
       <c r="I15" s="9">
         <v>46157</v>
@@ -2306,13 +2310,13 @@
         <v>26</v>
       </c>
       <c r="N15" s="10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="O15" s="10" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="P15" s="10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="Q15" s="9">
         <v>46157</v>
@@ -2332,7 +2336,7 @@
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B16" s="5">
         <v>46169.558224479166</v>
@@ -2344,16 +2348,16 @@
         <v>46181.62447002315</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G16" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="H16" s="6" t="s">
         <v>51</v>
-      </c>
-      <c r="H16" s="6" t="s">
-        <v>52</v>
       </c>
       <c r="I16" s="5">
         <v>46167</v>
@@ -2371,13 +2375,13 @@
         <v>26</v>
       </c>
       <c r="N16" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="O16" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="P16" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Q16" s="5">
         <v>46167</v>
@@ -2397,7 +2401,7 @@
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B17" s="9">
         <v>46169.558230821756</v>
@@ -2409,16 +2413,16 @@
         <v>46183.90651931713</v>
       </c>
       <c r="E17" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="F17" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G17" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="F17" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G17" s="10" t="s">
-        <v>73</v>
-      </c>
       <c r="H17" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I17" s="9">
         <v>46167</v>
@@ -2436,13 +2440,13 @@
         <v>26</v>
       </c>
       <c r="N17" s="10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="O17" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="P17" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="Q17" s="9">
         <v>46167</v>
@@ -2462,7 +2466,7 @@
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B18" s="5">
         <v>46169.55823646991</v>
@@ -2474,16 +2478,16 @@
         <v>46183.90665107639</v>
       </c>
       <c r="E18" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G18" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="F18" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G18" s="6" t="s">
+      <c r="H18" s="6" t="s">
         <v>77</v>
-      </c>
-      <c r="H18" s="6" t="s">
-        <v>78</v>
       </c>
       <c r="I18" s="5">
         <v>46239</v>
@@ -2501,13 +2505,13 @@
         <v>26</v>
       </c>
       <c r="N18" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="O18" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="P18" s="6" t="s">
         <v>79</v>
-      </c>
-      <c r="P18" s="6" t="s">
-        <v>80</v>
       </c>
       <c r="Q18" s="5">
         <v>46239</v>
@@ -2527,7 +2531,7 @@
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B19" s="9">
         <v>46169.55824171296</v>
@@ -2539,16 +2543,16 @@
         <v>46183.90666170139</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F19" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G19" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="H19" s="10" t="s">
         <v>77</v>
-      </c>
-      <c r="H19" s="10" t="s">
-        <v>78</v>
       </c>
       <c r="I19" s="9">
         <v>46239</v>
@@ -2566,13 +2570,13 @@
         <v>26</v>
       </c>
       <c r="N19" s="10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="O19" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="P19" s="10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q19" s="9">
         <v>46239</v>
@@ -2592,7 +2596,7 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B20" s="5">
         <v>46169.55824574074</v>
@@ -2604,16 +2608,16 @@
         <v>46190.64415820602</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G20" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="H20" s="6" t="s">
         <v>77</v>
-      </c>
-      <c r="H20" s="6" t="s">
-        <v>78</v>
       </c>
       <c r="I20" s="5">
         <v>46239</v>
@@ -2631,13 +2635,13 @@
         <v>26</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="Q20" s="5">
         <v>46239</v>
@@ -2657,7 +2661,7 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B21" s="9">
         <v>46169.55825006944</v>
@@ -2669,16 +2673,16 @@
         <v>46183.90735393518</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F21" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G21" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="H21" s="10" t="s">
         <v>77</v>
-      </c>
-      <c r="H21" s="10" t="s">
-        <v>78</v>
       </c>
       <c r="I21" s="9">
         <v>46239</v>
@@ -2696,13 +2700,13 @@
         <v>26</v>
       </c>
       <c r="N21" s="10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="O21" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="P21" s="10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="Q21" s="9">
         <v>46239</v>
@@ -2722,7 +2726,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B22" s="5">
         <v>46169.55801826389</v>
@@ -2732,7 +2736,7 @@
         <v>46184.736483437504</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>25</v>
@@ -2756,7 +2760,7 @@
         <v>26</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="P22" s="6" t="s">
         <v>26</v>
@@ -2766,7 +2770,7 @@
       <c r="S22" s="6"/>
       <c r="T22" s="6"/>
       <c r="U22" s="11" t="s">
-        <v>48</v>
+        <v>92</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
@@ -2810,13 +2814,13 @@
         <v>26</v>
       </c>
       <c r="N23" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="O23" s="10" t="s">
         <v>97</v>
       </c>
       <c r="P23" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="Q23" s="9">
         <v>46169</v>
@@ -2831,7 +2835,7 @@
         <v>1</v>
       </c>
       <c r="U23" s="11" t="s">
-        <v>48</v>
+        <v>92</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
@@ -2878,7 +2882,7 @@
         <v>94</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="P24" s="6" t="s">
         <v>100</v>
@@ -2997,13 +3001,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="O26" s="6" t="s">
         <v>107</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="Q26" s="5">
         <v>46169</v>
@@ -3065,7 +3069,7 @@
         <v>106</v>
       </c>
       <c r="O27" s="10" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="P27" s="10" t="s">
         <v>110</v>
@@ -3184,13 +3188,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="O29" s="10" t="s">
         <v>116</v>
       </c>
       <c r="P29" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="Q29" s="9">
         <v>46161</v>
@@ -3205,7 +3209,7 @@
         <v>1</v>
       </c>
       <c r="U29" s="11" t="s">
-        <v>48</v>
+        <v>92</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
@@ -3252,7 +3256,7 @@
         <v>115</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="P30" s="6" t="s">
         <v>119</v>
@@ -3432,13 +3436,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="O33" s="10" t="s">
         <v>130</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="Q33" s="9">
         <v>46241</v>
@@ -3500,7 +3504,7 @@
         <v>127</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="P34" s="6" t="s">
         <v>133</v>
@@ -3619,7 +3623,7 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="O36" s="6" t="s">
         <v>139</v>
@@ -3657,7 +3661,7 @@
         <v>46184.5322071875</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>26</v>
@@ -3687,7 +3691,7 @@
         <v>138</v>
       </c>
       <c r="O37" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="P37" s="10" t="s">
         <v>141</v>
@@ -3742,7 +3746,7 @@
         <v>138</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="P38" s="6" t="s">
         <v>144</v>
@@ -3794,7 +3798,7 @@
         <v>26</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="O39" s="10" t="s">
         <v>149</v>
@@ -3815,7 +3819,7 @@
         <v>1</v>
       </c>
       <c r="U39" s="11" t="s">
-        <v>48</v>
+        <v>92</v>
       </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
@@ -3832,7 +3836,7 @@
         <v>46195.70360162037</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
@@ -3862,7 +3866,7 @@
         <v>146</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="P40" s="6" t="s">
         <v>151</v>
@@ -3917,7 +3921,7 @@
         <v>146</v>
       </c>
       <c r="O41" s="10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="P41" s="10" t="s">
         <v>154</v>
@@ -4022,7 +4026,7 @@
         <v>26</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="O43" s="10" t="s">
         <v>161</v>
@@ -4060,7 +4064,7 @@
         <v>46191.53679194444</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
@@ -4090,7 +4094,7 @@
         <v>160</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="P44" s="6" t="s">
         <v>163</v>
@@ -4145,7 +4149,7 @@
         <v>160</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="P45" s="10" t="s">
         <v>166</v>
@@ -4202,7 +4206,7 @@
       <c r="S46" s="6"/>
       <c r="T46" s="6"/>
       <c r="U46" s="11" t="s">
-        <v>48</v>
+        <v>92</v>
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
@@ -4314,7 +4318,7 @@
         <v>171</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="P48" s="6" t="s">
         <v>179</v>
@@ -4459,7 +4463,7 @@
         <v>46182.759871076385</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
@@ -4551,13 +4555,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="O52" s="6" t="s">
         <v>174</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4739,7 +4743,7 @@
         <v>46190.64495354166</v>
       </c>
       <c r="D56" s="5">
-        <v>46196.80606199074</v>
+        <v>46197.83559606482</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>199</v>
@@ -4853,7 +4857,7 @@
         <v>0</v>
       </c>
       <c r="U57" s="11" t="s">
-        <v>48</v>
+        <v>92</v>
       </c>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
@@ -4916,7 +4920,7 @@
         <v>0</v>
       </c>
       <c r="U58" s="11" t="s">
-        <v>48</v>
+        <v>92</v>
       </c>
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
@@ -5042,7 +5046,7 @@
         <v>0</v>
       </c>
       <c r="U60" s="11" t="s">
-        <v>48</v>
+        <v>92</v>
       </c>
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
@@ -5400,7 +5404,7 @@
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="9">
-        <v>46169.62084700231</v>
+        <v>46197.83537991898</v>
       </c>
       <c r="E67" s="10" t="s">
         <v>231</v>
@@ -5409,10 +5413,10 @@
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>219</v>
+        <v>157</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>220</v>
+        <v>158</v>
       </c>
       <c r="I67" s="9">
         <v>46274</v>
@@ -5463,7 +5467,7 @@
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46182.759876192125</v>
+        <v>46197.83545261574</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>174</v>
@@ -5472,10 +5476,10 @@
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>219</v>
+        <v>157</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>220</v>
+        <v>158</v>
       </c>
       <c r="I68" s="5">
         <v>46274</v>
@@ -5614,7 +5618,7 @@
         <v>0</v>
       </c>
       <c r="U70" s="11" t="s">
-        <v>48</v>
+        <v>92</v>
       </c>
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
@@ -5677,7 +5681,7 @@
         <v>0</v>
       </c>
       <c r="U71" s="11" t="s">
-        <v>48</v>
+        <v>92</v>
       </c>
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
@@ -5740,7 +5744,7 @@
         <v>0</v>
       </c>
       <c r="U72" s="11" t="s">
-        <v>48</v>
+        <v>92</v>
       </c>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
@@ -5803,7 +5807,7 @@
         <v>0</v>
       </c>
       <c r="U73" s="11" t="s">
-        <v>48</v>
+        <v>92</v>
       </c>
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
@@ -5873,10 +5877,10 @@
         <v>26</v>
       </c>
       <c r="G75" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H75" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I75" s="9">
         <v>46276</v>
@@ -5938,10 +5942,10 @@
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I76" s="5">
         <v>46276</v>
@@ -5993,10 +5997,10 @@
         <v>26</v>
       </c>
       <c r="G77" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H77" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I77" s="9">
         <v>46296</v>
@@ -6058,10 +6062,10 @@
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I78" s="5">
         <v>46296</v>
@@ -6111,10 +6115,10 @@
         <v>26</v>
       </c>
       <c r="G79" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H79" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I79" s="9">
         <v>46328</v>
@@ -6174,10 +6178,10 @@
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I80" s="5">
         <v>46328</v>
@@ -6227,10 +6231,10 @@
         <v>26</v>
       </c>
       <c r="G81" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H81" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I81" s="9">
         <v>46329</v>
@@ -6290,10 +6294,10 @@
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I82" s="5">
         <v>46329</v>
@@ -6343,10 +6347,10 @@
         <v>26</v>
       </c>
       <c r="G83" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H83" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I83" s="9">
         <v>46330</v>
@@ -6406,10 +6410,10 @@
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I84" s="5">
         <v>46330</v>
@@ -6459,10 +6463,10 @@
         <v>26</v>
       </c>
       <c r="G85" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H85" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I85" s="9">
         <v>46332</v>
@@ -6522,10 +6526,10 @@
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I86" s="5">
         <v>46332</v>
@@ -6738,10 +6742,10 @@
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I90" s="5">
         <v>46336</v>
@@ -6801,10 +6805,10 @@
         <v>26</v>
       </c>
       <c r="G91" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H91" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I91" s="9">
         <v>46336</v>
@@ -7196,10 +7200,10 @@
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="H98" s="6" t="s">
         <v>51</v>
-      </c>
-      <c r="H98" s="6" t="s">
-        <v>52</v>
       </c>
       <c r="I98" s="5">
         <v>46339</v>

--- a/data/50001557 - ATACAMA KOZAN OT4340.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4340.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1182" uniqueCount="310">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1183" uniqueCount="310">
   <si>
     <t xml:space="preserve"> 50001557 - ATACAMA KOZAN</t>
   </si>
@@ -4694,7 +4694,7 @@
       </c>
       <c r="C55" s="10"/>
       <c r="D55" s="9">
-        <v>46190.6449599537</v>
+        <v>46197.85937315972</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>196</v>
@@ -4730,7 +4730,9 @@
       <c r="R55" s="10"/>
       <c r="S55" s="10"/>
       <c r="T55" s="10"/>
-      <c r="U55" s="10"/>
+      <c r="U55" s="11" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
@@ -4804,9 +4806,11 @@
       <c r="B57" s="9">
         <v>46169.55859488426</v>
       </c>
-      <c r="C57" s="10"/>
+      <c r="C57" s="9">
+        <v>46197.85935881945</v>
+      </c>
       <c r="D57" s="9">
-        <v>46196.80590905093</v>
+        <v>46197.85937331019</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>204</v>
@@ -4854,10 +4858,10 @@
         <v>33</v>
       </c>
       <c r="T57" s="10">
-        <v>0</v>
-      </c>
-      <c r="U57" s="11" t="s">
-        <v>92</v>
+        <v>1</v>
+      </c>
+      <c r="U57" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
@@ -4930,9 +4934,11 @@
       <c r="B59" s="9">
         <v>46169.55860636574</v>
       </c>
-      <c r="C59" s="10"/>
+      <c r="C59" s="9">
+        <v>46197.85931310186</v>
+      </c>
       <c r="D59" s="9">
-        <v>46169.620307997684</v>
+        <v>46197.859329756946</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>208</v>
@@ -4980,10 +4986,10 @@
         <v>33</v>
       </c>
       <c r="T59" s="10">
-        <v>0</v>
-      </c>
-      <c r="U59" s="12" t="s">
-        <v>101</v>
+        <v>1</v>
+      </c>
+      <c r="U59" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
@@ -5056,9 +5062,11 @@
       <c r="B61" s="9">
         <v>46169.55865608796</v>
       </c>
-      <c r="C61" s="10"/>
+      <c r="C61" s="9">
+        <v>46197.85923987269</v>
+      </c>
       <c r="D61" s="9">
-        <v>46169.620303483796</v>
+        <v>46197.859256180556</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>212</v>
@@ -5106,10 +5114,10 @@
         <v>33</v>
       </c>
       <c r="T61" s="10">
-        <v>0</v>
-      </c>
-      <c r="U61" s="12" t="s">
-        <v>101</v>
+        <v>1</v>
+      </c>
+      <c r="U61" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
@@ -5170,7 +5178,7 @@
         <v>46190.645243935185</v>
       </c>
       <c r="D63" s="9">
-        <v>46190.645261516205</v>
+        <v>46197.85915361111</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>218</v>
@@ -5231,9 +5239,11 @@
       <c r="B64" s="5">
         <v>46169.55867099537</v>
       </c>
-      <c r="C64" s="6"/>
+      <c r="C64" s="5">
+        <v>46197.85914688658</v>
+      </c>
       <c r="D64" s="5">
-        <v>46169.62059548611</v>
+        <v>46197.85936673611</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>174</v>
@@ -5288,7 +5298,7 @@
         <v>46190.64532476851</v>
       </c>
       <c r="D65" s="9">
-        <v>46190.64534048611</v>
+        <v>46197.85387390046</v>
       </c>
       <c r="E65" s="10" t="s">
         <v>226</v>
@@ -5338,8 +5348,8 @@
       <c r="T65" s="10">
         <v>1</v>
       </c>
-      <c r="U65" s="7" t="s">
-        <v>27</v>
+      <c r="U65" s="11" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
@@ -5349,9 +5359,11 @@
       <c r="B66" s="5">
         <v>46169.55870879629</v>
       </c>
-      <c r="C66" s="6"/>
+      <c r="C66" s="5">
+        <v>46197.853856608795</v>
+      </c>
       <c r="D66" s="5">
-        <v>46182.75987778935</v>
+        <v>46197.85915420139</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>174</v>
@@ -5467,7 +5479,7 @@
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46197.83545261574</v>
+        <v>46197.85386394676</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>174</v>
@@ -6570,7 +6582,7 @@
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="9">
-        <v>46169.60623452546</v>
+        <v>46197.85962290509</v>
       </c>
       <c r="E87" s="10" t="s">
         <v>280</v>
@@ -6847,9 +6859,11 @@
       <c r="B92" s="5">
         <v>46169.559239560185</v>
       </c>
-      <c r="C92" s="6"/>
+      <c r="C92" s="5">
+        <v>46197.859617372684</v>
+      </c>
       <c r="D92" s="5">
-        <v>46196.565746747685</v>
+        <v>46197.859819363424</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>293</v>
@@ -6897,10 +6911,10 @@
         <v>33</v>
       </c>
       <c r="T92" s="6">
-        <v>0</v>
-      </c>
-      <c r="U92" s="12" t="s">
-        <v>101</v>
+        <v>1</v>
+      </c>
+      <c r="U92" s="11" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
@@ -6910,9 +6924,11 @@
       <c r="B93" s="9">
         <v>46169.559243842596</v>
       </c>
-      <c r="C93" s="10"/>
+      <c r="C93" s="9">
+        <v>46197.859803263884</v>
+      </c>
       <c r="D93" s="9">
-        <v>46169.621808449076</v>
+        <v>46197.85980471065</v>
       </c>
       <c r="E93" s="10" t="s">
         <v>193</v>
@@ -7028,7 +7044,7 @@
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="9">
-        <v>46169.621891215276</v>
+        <v>46197.859809629634</v>
       </c>
       <c r="E95" s="10" t="s">
         <v>298</v>

--- a/data/50001557 - ATACAMA KOZAN OT4340.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4340.xlsx
@@ -4692,9 +4692,11 @@
       <c r="B55" s="9">
         <v>46169.558586307874</v>
       </c>
-      <c r="C55" s="10"/>
+      <c r="C55" s="9">
+        <v>46198.59773380787</v>
+      </c>
       <c r="D55" s="9">
-        <v>46197.85937315972</v>
+        <v>46198.597746307874</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>196</v>
@@ -4729,9 +4731,11 @@
       <c r="Q55" s="10"/>
       <c r="R55" s="10"/>
       <c r="S55" s="10"/>
-      <c r="T55" s="10"/>
-      <c r="U55" s="11" t="s">
-        <v>92</v>
+      <c r="T55" s="10">
+        <v>1</v>
+      </c>
+      <c r="U55" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
@@ -4871,9 +4875,11 @@
       <c r="B58" s="5">
         <v>46169.55860118056</v>
       </c>
-      <c r="C58" s="6"/>
+      <c r="C58" s="5">
+        <v>46198.597692881944</v>
+      </c>
       <c r="D58" s="5">
-        <v>46196.80590315972</v>
+        <v>46198.59771457176</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>207</v>
@@ -4921,10 +4927,10 @@
         <v>33</v>
       </c>
       <c r="T58" s="6">
-        <v>0</v>
-      </c>
-      <c r="U58" s="11" t="s">
-        <v>92</v>
+        <v>1</v>
+      </c>
+      <c r="U58" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
@@ -4938,7 +4944,7 @@
         <v>46197.85931310186</v>
       </c>
       <c r="D59" s="9">
-        <v>46197.859329756946</v>
+        <v>46198.597709444446</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>208</v>
@@ -4988,8 +4994,8 @@
       <c r="T59" s="10">
         <v>1</v>
       </c>
-      <c r="U59" s="7" t="s">
-        <v>27</v>
+      <c r="U59" s="11" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
@@ -4999,9 +5005,11 @@
       <c r="B60" s="5">
         <v>46169.558650127314</v>
       </c>
-      <c r="C60" s="6"/>
+      <c r="C60" s="5">
+        <v>46198.59771644676</v>
+      </c>
       <c r="D60" s="5">
-        <v>46191.53700491898</v>
+        <v>46198.59773310185</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>211</v>
@@ -5049,10 +5057,10 @@
         <v>33</v>
       </c>
       <c r="T60" s="6">
-        <v>0</v>
-      </c>
-      <c r="U60" s="11" t="s">
-        <v>92</v>
+        <v>1</v>
+      </c>
+      <c r="U60" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
@@ -5066,7 +5074,7 @@
         <v>46197.85923987269</v>
       </c>
       <c r="D61" s="9">
-        <v>46197.859256180556</v>
+        <v>46198.59773317129</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>212</v>
@@ -5116,8 +5124,8 @@
       <c r="T61" s="10">
         <v>1</v>
       </c>
-      <c r="U61" s="7" t="s">
-        <v>27</v>
+      <c r="U61" s="11" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001557 - ATACAMA KOZAN OT4340.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4340.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1183" uniqueCount="310">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1184" uniqueCount="310">
   <si>
     <t xml:space="preserve"> 50001557 - ATACAMA KOZAN</t>
   </si>
@@ -5135,9 +5135,11 @@
       <c r="B62" s="5">
         <v>46169.55866105324</v>
       </c>
-      <c r="C62" s="6"/>
+      <c r="C62" s="5">
+        <v>46198.682278935186</v>
+      </c>
       <c r="D62" s="5">
-        <v>46190.645330810185</v>
+        <v>46198.68229049769</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>215</v>
@@ -5172,8 +5174,12 @@
       <c r="Q62" s="6"/>
       <c r="R62" s="6"/>
       <c r="S62" s="6"/>
-      <c r="T62" s="6"/>
-      <c r="U62" s="6"/>
+      <c r="T62" s="6">
+        <v>1</v>
+      </c>
+      <c r="U62" s="7" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
@@ -5422,9 +5428,11 @@
       <c r="B67" s="9">
         <v>46169.558740625</v>
       </c>
-      <c r="C67" s="10"/>
+      <c r="C67" s="9">
+        <v>46198.68226086805</v>
+      </c>
       <c r="D67" s="9">
-        <v>46197.83537991898</v>
+        <v>46198.68228008102</v>
       </c>
       <c r="E67" s="10" t="s">
         <v>231</v>
@@ -5472,10 +5480,10 @@
         <v>33</v>
       </c>
       <c r="T67" s="10">
-        <v>0</v>
-      </c>
-      <c r="U67" s="12" t="s">
-        <v>101</v>
+        <v>1</v>
+      </c>
+      <c r="U67" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001557 - ATACAMA KOZAN OT4340.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4340.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1184" uniqueCount="310">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1183" uniqueCount="310">
   <si>
     <t xml:space="preserve"> 50001557 - ATACAMA KOZAN</t>
   </si>
@@ -94,25 +94,25 @@
     <t/>
   </si>
   <si>
+    <t>1215181626605571</t>
+  </si>
+  <si>
+    <t>Definición Jefe de proyecto</t>
+  </si>
+  <si>
+    <t>Sergio de la Fuente</t>
+  </si>
+  <si>
+    <t>sergio.delafuente@zitron.com</t>
+  </si>
+  <si>
+    <t>Francisca Ramos</t>
+  </si>
+  <si>
+    <t>Baja</t>
+  </si>
+  <si>
     <t>Tarea Terminada</t>
-  </si>
-  <si>
-    <t>1215181626605571</t>
-  </si>
-  <si>
-    <t>Definición Jefe de proyecto</t>
-  </si>
-  <si>
-    <t>Sergio de la Fuente</t>
-  </si>
-  <si>
-    <t>sergio.delafuente@zitron.com</t>
-  </si>
-  <si>
-    <t>Francisca Ramos</t>
-  </si>
-  <si>
-    <t>Baja</t>
   </si>
   <si>
     <t>1215166329020183</t>
@@ -327,238 +327,238 @@
     <t>Alabe - OT 4340,rodete OT 4340,Motor OT 4340,Materiales corte Laser OT 4340</t>
   </si>
   <si>
+    <t>1215166243111754</t>
+  </si>
+  <si>
+    <t>Alabe - OT 4340</t>
+  </si>
+  <si>
+    <t>Eliana</t>
+  </si>
+  <si>
+    <t>ecarico@zitron.com</t>
+  </si>
+  <si>
+    <t>Generación OC Alabe OT 4340,Fabricación Alabe OT 4340</t>
+  </si>
+  <si>
+    <t>1215166041639450</t>
+  </si>
+  <si>
+    <t>Generación OC Alabe OT 4340</t>
+  </si>
+  <si>
+    <t>Alabe - OT 4340,Fabricación Alabe OT 4340</t>
+  </si>
+  <si>
+    <t>Tarea sin iniciar</t>
+  </si>
+  <si>
+    <t>1215166041639470</t>
+  </si>
+  <si>
+    <t>Fabricación Alabe OT 4340</t>
+  </si>
+  <si>
+    <t>Alabe - OT 4340,Recepcion Alabe</t>
+  </si>
+  <si>
+    <t>1215166329218721</t>
+  </si>
+  <si>
+    <t>rodete OT 4340</t>
+  </si>
+  <si>
+    <t>Generación OC Rodete OT 4340 ,Fabricación Rodete OT 4340</t>
+  </si>
+  <si>
+    <t>1215166329218738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generación OC Rodete OT 4340 </t>
+  </si>
+  <si>
+    <t>rodete OT 4340,Fabricación Rodete OT 4340</t>
+  </si>
+  <si>
+    <t>1215166243290478</t>
+  </si>
+  <si>
+    <t>Fabricación Rodete OT 4340</t>
+  </si>
+  <si>
+    <t>rodete OT 4340,Recepcion Rodete</t>
+  </si>
+  <si>
+    <t>1215166433395167</t>
+  </si>
+  <si>
+    <t>Motor OT 4340</t>
+  </si>
+  <si>
+    <t>Generación OC motor OT 4340,Fabricación motor OT 4340,Planos motor proveedor OT 4340</t>
+  </si>
+  <si>
+    <t>1215166433395184</t>
+  </si>
+  <si>
+    <t>Generación OC motor OT 4340</t>
+  </si>
+  <si>
+    <t>Motor OT 4340,Fabricación motor OT 4340,Planos motor proveedor OT 4340</t>
+  </si>
+  <si>
+    <t>1215166329227522</t>
+  </si>
+  <si>
+    <t>Fabricación motor OT 4340</t>
+  </si>
+  <si>
+    <t>Motor OT 4340,Recepcion motor</t>
+  </si>
+  <si>
+    <t>1215166329227542</t>
+  </si>
+  <si>
+    <t>Planos motor proveedor OT 4340</t>
+  </si>
+  <si>
+    <t>OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR,Motor OT 4340</t>
+  </si>
+  <si>
+    <t>1215165982829078</t>
+  </si>
+  <si>
+    <t>Materiales corte Laser OT 4340</t>
+  </si>
+  <si>
+    <t>Yerlia Ayleen Castillo Diaz</t>
+  </si>
+  <si>
+    <t>yerlia.castillo@zitron.com</t>
+  </si>
+  <si>
+    <t>Fabricacion Corte Laser  OT 4340,Generación OC materiales corte Laser OT 4340</t>
+  </si>
+  <si>
+    <t>1215166433428453</t>
+  </si>
+  <si>
+    <t>Generación OC materiales corte Laser OT 4340</t>
+  </si>
+  <si>
+    <t>Fabricacion Corte Laser  OT 4340,Materiales corte Laser OT 4340</t>
+  </si>
+  <si>
+    <t>1215166041659706</t>
+  </si>
+  <si>
+    <t>Fabricacion Corte Laser  OT 4340</t>
+  </si>
+  <si>
+    <t>Recepcion materiales corte laser,Materiales corte Laser OT 4340</t>
+  </si>
+  <si>
+    <t>1215166041659726</t>
+  </si>
+  <si>
+    <t>Materiales Corte Plasma  OT 4340</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generación OC Corte Plasma  OT 4340,Fabricación Corte Plasma OT 4340 </t>
+  </si>
+  <si>
+    <t>1215166243334496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Materiales Corte Plasma  OT 4340,Fabricación Corte Plasma OT 4340 </t>
+  </si>
+  <si>
+    <t>1215166243334513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabricación Corte Plasma OT 4340 </t>
+  </si>
+  <si>
+    <t>Recepcion Materiales corte plasma,Materiales Corte Plasma  OT 4340</t>
+  </si>
+  <si>
+    <t>1215166243334594</t>
+  </si>
+  <si>
+    <t>Fabricación Externa  OT 4340</t>
+  </si>
+  <si>
+    <t>Rosemary Singh</t>
+  </si>
+  <si>
+    <t>rosemary.singh@zitron.com</t>
+  </si>
+  <si>
+    <t>Fabricación estructura proveedor externo OT 4340,Generacion OC Fabricación Externa OT 4340</t>
+  </si>
+  <si>
+    <t>1215166243334606</t>
+  </si>
+  <si>
+    <t>Fabricación estructura proveedor externo OT 4340,Fabricación Externa  OT 4340</t>
+  </si>
+  <si>
+    <t>1215165982859560</t>
+  </si>
+  <si>
+    <t>Fabricación estructura proveedor externo OT 4340</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabricación Externa  OT 4340,Control de calidad fabricación externa  OT 4340,Recepcion fabricación externa </t>
+  </si>
+  <si>
+    <t>1215165982859577</t>
+  </si>
+  <si>
+    <t>Control de calidad fabricación externa  OT 4340</t>
+  </si>
+  <si>
+    <t>Nicolás López</t>
+  </si>
+  <si>
+    <t>nicolas.lopez@zitron.com</t>
+  </si>
+  <si>
+    <t>1215165982859589</t>
+  </si>
+  <si>
+    <t>Mecanizado OT 4340</t>
+  </si>
+  <si>
+    <t>Fabricación Mecanizado OT 4340,Generación OC Mecanizado OT 4340</t>
+  </si>
+  <si>
+    <t>1215166433442059</t>
+  </si>
+  <si>
+    <t>Fabricación Mecanizado OT 4340,Mecanizado OT 4340</t>
+  </si>
+  <si>
+    <t>1215166243346004</t>
+  </si>
+  <si>
+    <t>Fabricación Mecanizado OT 4340</t>
+  </si>
+  <si>
+    <t>Recepcion mecanizado,Mecanizado OT 4340</t>
+  </si>
+  <si>
+    <t>1215166243396278</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseñoo:</t>
+  </si>
+  <si>
+    <t>Planos definitivos,Planos preliminar</t>
+  </si>
+  <si>
     <t>Tarea en curso</t>
-  </si>
-  <si>
-    <t>1215166243111754</t>
-  </si>
-  <si>
-    <t>Alabe - OT 4340</t>
-  </si>
-  <si>
-    <t>Eliana</t>
-  </si>
-  <si>
-    <t>ecarico@zitron.com</t>
-  </si>
-  <si>
-    <t>Generación OC Alabe OT 4340,Fabricación Alabe OT 4340</t>
-  </si>
-  <si>
-    <t>1215166041639450</t>
-  </si>
-  <si>
-    <t>Generación OC Alabe OT 4340</t>
-  </si>
-  <si>
-    <t>Alabe - OT 4340,Fabricación Alabe OT 4340</t>
-  </si>
-  <si>
-    <t>Tarea sin iniciar</t>
-  </si>
-  <si>
-    <t>1215166041639470</t>
-  </si>
-  <si>
-    <t>Fabricación Alabe OT 4340</t>
-  </si>
-  <si>
-    <t>Alabe - OT 4340,Recepcion Alabe</t>
-  </si>
-  <si>
-    <t>1215166329218721</t>
-  </si>
-  <si>
-    <t>rodete OT 4340</t>
-  </si>
-  <si>
-    <t>Generación OC Rodete OT 4340 ,Fabricación Rodete OT 4340</t>
-  </si>
-  <si>
-    <t>1215166329218738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generación OC Rodete OT 4340 </t>
-  </si>
-  <si>
-    <t>rodete OT 4340,Fabricación Rodete OT 4340</t>
-  </si>
-  <si>
-    <t>1215166243290478</t>
-  </si>
-  <si>
-    <t>Fabricación Rodete OT 4340</t>
-  </si>
-  <si>
-    <t>rodete OT 4340,Recepcion Rodete</t>
-  </si>
-  <si>
-    <t>1215166433395167</t>
-  </si>
-  <si>
-    <t>Motor OT 4340</t>
-  </si>
-  <si>
-    <t>Generación OC motor OT 4340,Fabricación motor OT 4340,Planos motor proveedor OT 4340</t>
-  </si>
-  <si>
-    <t>1215166433395184</t>
-  </si>
-  <si>
-    <t>Generación OC motor OT 4340</t>
-  </si>
-  <si>
-    <t>Motor OT 4340,Fabricación motor OT 4340,Planos motor proveedor OT 4340</t>
-  </si>
-  <si>
-    <t>1215166329227522</t>
-  </si>
-  <si>
-    <t>Fabricación motor OT 4340</t>
-  </si>
-  <si>
-    <t>Motor OT 4340,Recepcion motor</t>
-  </si>
-  <si>
-    <t>1215166329227542</t>
-  </si>
-  <si>
-    <t>Planos motor proveedor OT 4340</t>
-  </si>
-  <si>
-    <t>OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR,Motor OT 4340</t>
-  </si>
-  <si>
-    <t>1215165982829078</t>
-  </si>
-  <si>
-    <t>Materiales corte Laser OT 4340</t>
-  </si>
-  <si>
-    <t>Yerlia Ayleen Castillo Diaz</t>
-  </si>
-  <si>
-    <t>yerlia.castillo@zitron.com</t>
-  </si>
-  <si>
-    <t>Fabricacion Corte Laser  OT 4340,Generación OC materiales corte Laser OT 4340</t>
-  </si>
-  <si>
-    <t>1215166433428453</t>
-  </si>
-  <si>
-    <t>Generación OC materiales corte Laser OT 4340</t>
-  </si>
-  <si>
-    <t>Fabricacion Corte Laser  OT 4340,Materiales corte Laser OT 4340</t>
-  </si>
-  <si>
-    <t>1215166041659706</t>
-  </si>
-  <si>
-    <t>Fabricacion Corte Laser  OT 4340</t>
-  </si>
-  <si>
-    <t>Recepcion materiales corte laser,Materiales corte Laser OT 4340</t>
-  </si>
-  <si>
-    <t>1215166041659726</t>
-  </si>
-  <si>
-    <t>Materiales Corte Plasma  OT 4340</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generación OC Corte Plasma  OT 4340,Fabricación Corte Plasma OT 4340 </t>
-  </si>
-  <si>
-    <t>1215166243334496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Materiales Corte Plasma  OT 4340,Fabricación Corte Plasma OT 4340 </t>
-  </si>
-  <si>
-    <t>1215166243334513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabricación Corte Plasma OT 4340 </t>
-  </si>
-  <si>
-    <t>Recepcion Materiales corte plasma,Materiales Corte Plasma  OT 4340</t>
-  </si>
-  <si>
-    <t>1215166243334594</t>
-  </si>
-  <si>
-    <t>Fabricación Externa  OT 4340</t>
-  </si>
-  <si>
-    <t>Rosemary Singh</t>
-  </si>
-  <si>
-    <t>rosemary.singh@zitron.com</t>
-  </si>
-  <si>
-    <t>Fabricación estructura proveedor externo OT 4340,Generacion OC Fabricación Externa OT 4340</t>
-  </si>
-  <si>
-    <t>1215166243334606</t>
-  </si>
-  <si>
-    <t>Fabricación estructura proveedor externo OT 4340,Fabricación Externa  OT 4340</t>
-  </si>
-  <si>
-    <t>1215165982859560</t>
-  </si>
-  <si>
-    <t>Fabricación estructura proveedor externo OT 4340</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabricación Externa  OT 4340,Control de calidad fabricación externa  OT 4340,Recepcion fabricación externa </t>
-  </si>
-  <si>
-    <t>1215165982859577</t>
-  </si>
-  <si>
-    <t>Control de calidad fabricación externa  OT 4340</t>
-  </si>
-  <si>
-    <t>Nicolás López</t>
-  </si>
-  <si>
-    <t>nicolas.lopez@zitron.com</t>
-  </si>
-  <si>
-    <t>1215165982859589</t>
-  </si>
-  <si>
-    <t>Mecanizado OT 4340</t>
-  </si>
-  <si>
-    <t>Fabricación Mecanizado OT 4340,Generación OC Mecanizado OT 4340</t>
-  </si>
-  <si>
-    <t>1215166433442059</t>
-  </si>
-  <si>
-    <t>Fabricación Mecanizado OT 4340,Mecanizado OT 4340</t>
-  </si>
-  <si>
-    <t>1215166243346004</t>
-  </si>
-  <si>
-    <t>Fabricación Mecanizado OT 4340</t>
-  </si>
-  <si>
-    <t>Recepcion mecanizado,Mecanizado OT 4340</t>
-  </si>
-  <si>
-    <t>1215166243396278</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseñoo:</t>
-  </si>
-  <si>
-    <t>Planos definitivos,Planos preliminar</t>
   </si>
   <si>
     <t>1215166243396290</t>
@@ -1032,11 +1032,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF62d26f"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFBFBFBF"/>
       </patternFill>
     </fill>
@@ -1047,12 +1042,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFeec300"/>
+        <fgColor rgb="FF62d26f"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFe8384f"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFeec300"/>
       </patternFill>
     </fill>
   </fills>
@@ -1113,8 +1113,8 @@
     <xf numFmtId="14" fontId="0" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1611,7 +1611,7 @@
         <v>46181.62345784722</v>
       </c>
       <c r="D4" s="5">
-        <v>46181.62347542824</v>
+        <v>46200.818239016204</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1646,74 +1646,70 @@
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
       <c r="S4" s="6"/>
-      <c r="T4" s="6">
+      <c r="T4" s="6"/>
+      <c r="U4" s="6"/>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A5" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" s="8">
+        <v>46169.5581362963</v>
+      </c>
+      <c r="C5" s="8">
+        <v>46181.6234662037</v>
+      </c>
+      <c r="D5" s="8">
+        <v>46181.623480486116</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="I5" s="9"/>
+      <c r="J5" s="8">
+        <v>46154</v>
+      </c>
+      <c r="K5" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L5" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="M5" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N5" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="O5" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="P5" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q5" s="8">
+        <v>46154</v>
+      </c>
+      <c r="R5" s="8">
+        <v>46154</v>
+      </c>
+      <c r="S5" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="T5" s="9">
         <v>1</v>
       </c>
-      <c r="U4" s="7" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A5" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="B5" s="9">
-        <v>46169.5581362963</v>
-      </c>
-      <c r="C5" s="9">
-        <v>46181.6234662037</v>
-      </c>
-      <c r="D5" s="9">
-        <v>46181.623480486116</v>
-      </c>
-      <c r="E5" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="F5" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G5" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="H5" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="I5" s="10"/>
-      <c r="J5" s="9">
-        <v>46154</v>
-      </c>
-      <c r="K5" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L5" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="M5" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N5" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="O5" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="P5" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q5" s="9">
-        <v>46154</v>
-      </c>
-      <c r="R5" s="9">
-        <v>46154</v>
-      </c>
-      <c r="S5" s="7" t="s">
+      <c r="U5" s="10" t="s">
         <v>33</v>
-      </c>
-      <c r="T5" s="10">
-        <v>1</v>
-      </c>
-      <c r="U5" s="7" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.25">
@@ -1736,10 +1732,10 @@
         <v>26</v>
       </c>
       <c r="G6" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="H6" s="6" t="s">
         <v>30</v>
-      </c>
-      <c r="H6" s="6" t="s">
-        <v>31</v>
       </c>
       <c r="I6" s="6"/>
       <c r="J6" s="5">
@@ -1769,77 +1765,77 @@
       <c r="R6" s="5">
         <v>46154</v>
       </c>
-      <c r="S6" s="7" t="s">
-        <v>33</v>
+      <c r="S6" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T6" s="6">
         <v>1</v>
       </c>
-      <c r="U6" s="7" t="s">
-        <v>27</v>
+      <c r="U6" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="B7" s="9">
+      <c r="B7" s="8">
         <v>46169.55814432871</v>
       </c>
-      <c r="C7" s="9">
+      <c r="C7" s="8">
         <v>46181.62348018518</v>
       </c>
-      <c r="D7" s="9">
+      <c r="D7" s="8">
         <v>46181.62349788194</v>
       </c>
-      <c r="E7" s="10" t="s">
+      <c r="E7" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="F7" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G7" s="10" t="s">
+      <c r="F7" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="H7" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="H7" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="I7" s="10"/>
-      <c r="J7" s="9">
+      <c r="I7" s="9"/>
+      <c r="J7" s="8">
         <v>46154</v>
       </c>
-      <c r="K7" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L7" s="10" t="s">
+      <c r="K7" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L7" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="M7" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N7" s="10" t="s">
+      <c r="M7" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N7" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="O7" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="P7" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q7" s="9">
+      <c r="O7" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="P7" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q7" s="8">
         <v>46154</v>
       </c>
-      <c r="R7" s="9">
+      <c r="R7" s="8">
         <v>46154</v>
       </c>
-      <c r="S7" s="7" t="s">
+      <c r="S7" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="T7" s="9">
+        <v>1</v>
+      </c>
+      <c r="U7" s="10" t="s">
         <v>33</v>
-      </c>
-      <c r="T7" s="10">
-        <v>1</v>
-      </c>
-      <c r="U7" s="7" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.25">
@@ -1862,10 +1858,10 @@
         <v>26</v>
       </c>
       <c r="G8" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="H8" s="6" t="s">
         <v>30</v>
-      </c>
-      <c r="H8" s="6" t="s">
-        <v>31</v>
       </c>
       <c r="I8" s="6"/>
       <c r="J8" s="5">
@@ -1895,77 +1891,77 @@
       <c r="R8" s="5">
         <v>46154</v>
       </c>
-      <c r="S8" s="7" t="s">
-        <v>33</v>
+      <c r="S8" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T8" s="6">
         <v>1</v>
       </c>
-      <c r="U8" s="7" t="s">
-        <v>27</v>
+      <c r="U8" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B9" s="9">
+      <c r="B9" s="8">
         <v>46169.55815164352</v>
       </c>
-      <c r="C9" s="9">
+      <c r="C9" s="8">
         <v>46181.62349162037</v>
       </c>
-      <c r="D9" s="9">
+      <c r="D9" s="8">
         <v>46181.62350840278</v>
       </c>
-      <c r="E9" s="10" t="s">
+      <c r="E9" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="F9" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G9" s="10" t="s">
+      <c r="F9" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G9" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="H9" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="H9" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="I9" s="10"/>
-      <c r="J9" s="9">
+      <c r="I9" s="9"/>
+      <c r="J9" s="8">
         <v>46154</v>
       </c>
-      <c r="K9" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L9" s="10" t="s">
+      <c r="K9" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L9" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="M9" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N9" s="10" t="s">
+      <c r="M9" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N9" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="O9" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="P9" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q9" s="9">
+      <c r="O9" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="P9" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q9" s="8">
         <v>46154</v>
       </c>
-      <c r="R9" s="9">
+      <c r="R9" s="8">
         <v>46154</v>
       </c>
-      <c r="S9" s="7" t="s">
+      <c r="S9" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="T9" s="9">
+        <v>1</v>
+      </c>
+      <c r="U9" s="10" t="s">
         <v>33</v>
-      </c>
-      <c r="T9" s="10">
-        <v>1</v>
-      </c>
-      <c r="U9" s="7" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.25">
@@ -2017,73 +2013,73 @@
       <c r="T10" s="6">
         <v>1</v>
       </c>
-      <c r="U10" s="7" t="s">
-        <v>27</v>
+      <c r="U10" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="B11" s="9">
+      <c r="B11" s="8">
         <v>46169.558185671296</v>
       </c>
-      <c r="C11" s="9">
+      <c r="C11" s="8">
         <v>46181.624365104166</v>
       </c>
-      <c r="D11" s="9">
+      <c r="D11" s="8">
         <v>46196.80567361111</v>
       </c>
-      <c r="E11" s="10" t="s">
+      <c r="E11" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="F11" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G11" s="10" t="s">
+      <c r="F11" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G11" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="H11" s="10" t="s">
+      <c r="H11" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="I11" s="9">
+      <c r="I11" s="8">
         <v>46155</v>
       </c>
-      <c r="J11" s="9">
+      <c r="J11" s="8">
         <v>46156</v>
       </c>
-      <c r="K11" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L11" s="10" t="s">
+      <c r="K11" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L11" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="M11" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N11" s="10" t="s">
+      <c r="M11" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N11" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="O11" s="10" t="s">
+      <c r="O11" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="P11" s="10" t="s">
+      <c r="P11" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="Q11" s="9">
+      <c r="Q11" s="8">
         <v>46155</v>
       </c>
-      <c r="R11" s="9">
+      <c r="R11" s="8">
         <v>46156</v>
       </c>
-      <c r="S11" s="7" t="s">
+      <c r="S11" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="T11" s="9">
+        <v>1</v>
+      </c>
+      <c r="U11" s="10" t="s">
         <v>33</v>
-      </c>
-      <c r="T11" s="10">
-        <v>1</v>
-      </c>
-      <c r="U11" s="7" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
@@ -2141,79 +2137,79 @@
       <c r="R12" s="5">
         <v>46164</v>
       </c>
-      <c r="S12" s="7" t="s">
-        <v>33</v>
+      <c r="S12" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T12" s="6">
         <v>1</v>
       </c>
-      <c r="U12" s="7" t="s">
-        <v>27</v>
+      <c r="U12" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B13" s="9">
+      <c r="B13" s="8">
         <v>46169.558197418984</v>
       </c>
-      <c r="C13" s="9">
+      <c r="C13" s="8">
         <v>46181.624389537035</v>
       </c>
-      <c r="D13" s="9">
+      <c r="D13" s="8">
         <v>46196.80567320602</v>
       </c>
-      <c r="E13" s="10" t="s">
+      <c r="E13" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="F13" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G13" s="10" t="s">
+      <c r="F13" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G13" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="H13" s="10" t="s">
+      <c r="H13" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="I13" s="9">
+      <c r="I13" s="8">
         <v>46155</v>
       </c>
-      <c r="J13" s="9">
+      <c r="J13" s="8">
         <v>46164</v>
       </c>
-      <c r="K13" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L13" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M13" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N13" s="10" t="s">
+      <c r="K13" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L13" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M13" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N13" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="O13" s="10" t="s">
+      <c r="O13" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="P13" s="10" t="s">
+      <c r="P13" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="Q13" s="9">
+      <c r="Q13" s="8">
         <v>46155</v>
       </c>
-      <c r="R13" s="9">
+      <c r="R13" s="8">
         <v>46164</v>
       </c>
-      <c r="S13" s="7" t="s">
+      <c r="S13" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="T13" s="9">
+        <v>1</v>
+      </c>
+      <c r="U13" s="10" t="s">
         <v>33</v>
-      </c>
-      <c r="T13" s="10">
-        <v>1</v>
-      </c>
-      <c r="U13" s="7" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
@@ -2265,73 +2261,73 @@
       <c r="T14" s="6">
         <v>1</v>
       </c>
-      <c r="U14" s="7" t="s">
-        <v>27</v>
+      <c r="U14" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A15" s="8" t="s">
+      <c r="A15" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="B15" s="9">
+      <c r="B15" s="8">
         <v>46169.558213564815</v>
       </c>
-      <c r="C15" s="9">
+      <c r="C15" s="8">
         <v>46181.62444696759</v>
       </c>
-      <c r="D15" s="9">
+      <c r="D15" s="8">
         <v>46181.62446385417</v>
       </c>
-      <c r="E15" s="10" t="s">
+      <c r="E15" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="F15" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G15" s="10" t="s">
+      <c r="F15" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G15" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="H15" s="10" t="s">
+      <c r="H15" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="I15" s="9">
+      <c r="I15" s="8">
         <v>46157</v>
       </c>
-      <c r="J15" s="9">
+      <c r="J15" s="8">
         <v>46160</v>
       </c>
-      <c r="K15" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L15" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M15" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N15" s="10" t="s">
+      <c r="K15" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L15" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M15" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N15" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="O15" s="10" t="s">
+      <c r="O15" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="P15" s="10" t="s">
+      <c r="P15" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="Q15" s="9">
+      <c r="Q15" s="8">
         <v>46157</v>
       </c>
-      <c r="R15" s="9">
+      <c r="R15" s="8">
         <v>46160</v>
       </c>
-      <c r="S15" s="7" t="s">
+      <c r="S15" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="T15" s="9">
+        <v>1</v>
+      </c>
+      <c r="U15" s="10" t="s">
         <v>33</v>
-      </c>
-      <c r="T15" s="10">
-        <v>1</v>
-      </c>
-      <c r="U15" s="7" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
@@ -2389,79 +2385,79 @@
       <c r="R16" s="5">
         <v>46168</v>
       </c>
-      <c r="S16" s="7" t="s">
-        <v>33</v>
+      <c r="S16" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T16" s="6">
         <v>1</v>
       </c>
-      <c r="U16" s="7" t="s">
-        <v>27</v>
+      <c r="U16" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A17" s="8" t="s">
+      <c r="A17" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="B17" s="9">
+      <c r="B17" s="8">
         <v>46169.558230821756</v>
       </c>
-      <c r="C17" s="9">
+      <c r="C17" s="8">
         <v>46183.906516585645</v>
       </c>
-      <c r="D17" s="9">
+      <c r="D17" s="8">
         <v>46183.90651931713</v>
       </c>
-      <c r="E17" s="10" t="s">
+      <c r="E17" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="F17" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G17" s="10" t="s">
+      <c r="F17" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G17" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="H17" s="10" t="s">
+      <c r="H17" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="I17" s="9">
+      <c r="I17" s="8">
         <v>46167</v>
       </c>
-      <c r="J17" s="9">
+      <c r="J17" s="8">
         <v>46168</v>
       </c>
-      <c r="K17" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L17" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M17" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N17" s="10" t="s">
+      <c r="K17" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L17" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M17" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N17" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="O17" s="10" t="s">
+      <c r="O17" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="P17" s="10" t="s">
+      <c r="P17" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="Q17" s="9">
+      <c r="Q17" s="8">
         <v>46167</v>
       </c>
-      <c r="R17" s="9">
+      <c r="R17" s="8">
         <v>46168</v>
       </c>
-      <c r="S17" s="7" t="s">
+      <c r="S17" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="T17" s="9">
+        <v>1</v>
+      </c>
+      <c r="U17" s="10" t="s">
         <v>33</v>
-      </c>
-      <c r="T17" s="10">
-        <v>1</v>
-      </c>
-      <c r="U17" s="7" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
@@ -2519,79 +2515,79 @@
       <c r="R18" s="5">
         <v>46240</v>
       </c>
-      <c r="S18" s="7" t="s">
-        <v>33</v>
+      <c r="S18" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T18" s="6">
         <v>1</v>
       </c>
-      <c r="U18" s="7" t="s">
-        <v>27</v>
+      <c r="U18" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A19" s="8" t="s">
+      <c r="A19" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="B19" s="9">
+      <c r="B19" s="8">
         <v>46169.55824171296</v>
       </c>
-      <c r="C19" s="9">
+      <c r="C19" s="8">
         <v>46183.906646539355</v>
       </c>
-      <c r="D19" s="9">
+      <c r="D19" s="8">
         <v>46183.90666170139</v>
       </c>
-      <c r="E19" s="10" t="s">
+      <c r="E19" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="F19" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G19" s="10" t="s">
+      <c r="F19" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G19" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="H19" s="10" t="s">
+      <c r="H19" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="I19" s="9">
+      <c r="I19" s="8">
         <v>46239</v>
       </c>
-      <c r="J19" s="9">
+      <c r="J19" s="8">
         <v>46240</v>
       </c>
-      <c r="K19" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L19" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M19" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N19" s="10" t="s">
+      <c r="K19" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L19" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M19" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N19" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="O19" s="10" t="s">
+      <c r="O19" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="P19" s="10" t="s">
+      <c r="P19" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="Q19" s="9">
+      <c r="Q19" s="8">
         <v>46239</v>
       </c>
-      <c r="R19" s="9">
+      <c r="R19" s="8">
         <v>46240</v>
       </c>
-      <c r="S19" s="7" t="s">
+      <c r="S19" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="T19" s="9">
+        <v>1</v>
+      </c>
+      <c r="U19" s="10" t="s">
         <v>33</v>
-      </c>
-      <c r="T19" s="10">
-        <v>1</v>
-      </c>
-      <c r="U19" s="7" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
@@ -2649,79 +2645,79 @@
       <c r="R20" s="5">
         <v>46240</v>
       </c>
-      <c r="S20" s="7" t="s">
-        <v>33</v>
+      <c r="S20" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T20" s="6">
         <v>1</v>
       </c>
-      <c r="U20" s="7" t="s">
-        <v>27</v>
+      <c r="U20" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A21" s="8" t="s">
+      <c r="A21" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="B21" s="9">
+      <c r="B21" s="8">
         <v>46169.55825006944</v>
       </c>
-      <c r="C21" s="9">
+      <c r="C21" s="8">
         <v>46183.90733957176</v>
       </c>
-      <c r="D21" s="9">
+      <c r="D21" s="8">
         <v>46183.90735393518</v>
       </c>
-      <c r="E21" s="10" t="s">
+      <c r="E21" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="F21" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G21" s="10" t="s">
+      <c r="F21" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G21" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="H21" s="10" t="s">
+      <c r="H21" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="I21" s="9">
+      <c r="I21" s="8">
         <v>46239</v>
       </c>
-      <c r="J21" s="9">
+      <c r="J21" s="8">
         <v>46240</v>
       </c>
-      <c r="K21" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L21" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M21" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N21" s="10" t="s">
+      <c r="K21" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L21" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M21" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N21" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="O21" s="10" t="s">
+      <c r="O21" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="P21" s="10" t="s">
+      <c r="P21" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="Q21" s="9">
+      <c r="Q21" s="8">
         <v>46239</v>
       </c>
-      <c r="R21" s="9">
+      <c r="R21" s="8">
         <v>46240</v>
       </c>
-      <c r="S21" s="7" t="s">
+      <c r="S21" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="T21" s="9">
+        <v>1</v>
+      </c>
+      <c r="U21" s="10" t="s">
         <v>33</v>
-      </c>
-      <c r="T21" s="10">
-        <v>1</v>
-      </c>
-      <c r="U21" s="7" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
@@ -2731,9 +2727,11 @@
       <c r="B22" s="5">
         <v>46169.55801826389</v>
       </c>
-      <c r="C22" s="6"/>
+      <c r="C22" s="5">
+        <v>46200.818312083335</v>
+      </c>
       <c r="D22" s="5">
-        <v>46184.736483437504</v>
+        <v>46200.818425798614</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>90</v>
@@ -2769,78 +2767,76 @@
       <c r="R22" s="6"/>
       <c r="S22" s="6"/>
       <c r="T22" s="6"/>
-      <c r="U22" s="11" t="s">
+      <c r="U22" s="6"/>
+    </row>
+    <row r="23" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A23" s="7" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A23" s="8" t="s">
+      <c r="B23" s="8">
+        <v>46169.558301956014</v>
+      </c>
+      <c r="C23" s="8">
+        <v>46182.67339038194</v>
+      </c>
+      <c r="D23" s="8">
+        <v>46200.81833380787</v>
+      </c>
+      <c r="E23" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="B23" s="9">
-        <v>46169.558301956014</v>
-      </c>
-      <c r="C23" s="9">
-        <v>46182.67339038194</v>
-      </c>
-      <c r="D23" s="9">
-        <v>46195.69080631944</v>
-      </c>
-      <c r="E23" s="10" t="s">
+      <c r="F23" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G23" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="F23" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G23" s="10" t="s">
+      <c r="H23" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="H23" s="10" t="s">
+      <c r="I23" s="8">
+        <v>46169</v>
+      </c>
+      <c r="J23" s="8">
+        <v>46324</v>
+      </c>
+      <c r="K23" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L23" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M23" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N23" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="O23" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I23" s="9">
+      <c r="P23" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q23" s="8">
         <v>46169</v>
       </c>
-      <c r="J23" s="9">
+      <c r="R23" s="8">
         <v>46324</v>
       </c>
-      <c r="K23" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L23" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M23" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N23" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="O23" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="P23" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="Q23" s="9">
-        <v>46169</v>
-      </c>
-      <c r="R23" s="9">
-        <v>46324</v>
-      </c>
-      <c r="S23" s="7" t="s">
+      <c r="S23" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="T23" s="9">
+        <v>1</v>
+      </c>
+      <c r="U23" s="10" t="s">
         <v>33</v>
-      </c>
-      <c r="T23" s="10">
-        <v>1</v>
-      </c>
-      <c r="U23" s="11" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B24" s="5">
         <v>46169.558306516206</v>
@@ -2852,16 +2848,16 @@
         <v>46195.69079224537</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="H24" s="6" t="s">
         <v>95</v>
-      </c>
-      <c r="H24" s="6" t="s">
-        <v>96</v>
       </c>
       <c r="I24" s="5">
         <v>46169</v>
@@ -2879,90 +2875,90 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O24" s="6" t="s">
         <v>68</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="Q24" s="6"/>
       <c r="R24" s="6"/>
-      <c r="S24" s="7" t="s">
-        <v>33</v>
+      <c r="S24" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T24" s="6">
         <v>0</v>
       </c>
-      <c r="U24" s="12" t="s">
+      <c r="U24" s="11" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A25" s="7" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A25" s="8" t="s">
+      <c r="B25" s="8">
+        <v>46169.55831137732</v>
+      </c>
+      <c r="C25" s="8">
+        <v>46182.67337415509</v>
+      </c>
+      <c r="D25" s="8">
+        <v>46195.690800474535</v>
+      </c>
+      <c r="E25" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="B25" s="9">
-        <v>46169.55831137732</v>
-      </c>
-      <c r="C25" s="9">
-        <v>46182.67337415509</v>
-      </c>
-      <c r="D25" s="9">
-        <v>46195.690800474535</v>
-      </c>
-      <c r="E25" s="10" t="s">
+      <c r="F25" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G25" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="H25" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="I25" s="8">
+        <v>46171</v>
+      </c>
+      <c r="J25" s="8">
+        <v>46324</v>
+      </c>
+      <c r="K25" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L25" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M25" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N25" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="O25" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="P25" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="F25" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G25" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="H25" s="10" t="s">
-        <v>96</v>
-      </c>
-      <c r="I25" s="9">
-        <v>46171</v>
-      </c>
-      <c r="J25" s="9">
-        <v>46324</v>
-      </c>
-      <c r="K25" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L25" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M25" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N25" s="10" t="s">
-        <v>94</v>
-      </c>
-      <c r="O25" s="10" t="s">
-        <v>99</v>
-      </c>
-      <c r="P25" s="10" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q25" s="10"/>
-      <c r="R25" s="10"/>
-      <c r="S25" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T25" s="10">
+      <c r="Q25" s="9"/>
+      <c r="R25" s="9"/>
+      <c r="S25" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="T25" s="9">
         <v>0</v>
       </c>
-      <c r="U25" s="12" t="s">
-        <v>101</v>
+      <c r="U25" s="11" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B26" s="5">
         <v>46169.55831605324</v>
@@ -2974,16 +2970,16 @@
         <v>46184.73661180555</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="H26" s="6" t="s">
         <v>95</v>
-      </c>
-      <c r="H26" s="6" t="s">
-        <v>96</v>
       </c>
       <c r="I26" s="5">
         <v>46169</v>
@@ -3004,7 +3000,7 @@
         <v>90</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="P26" s="6" t="s">
         <v>90</v>
@@ -3015,80 +3011,80 @@
       <c r="R26" s="5">
         <v>46219</v>
       </c>
-      <c r="S26" s="7" t="s">
-        <v>33</v>
+      <c r="S26" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T26" s="6">
         <v>1</v>
       </c>
-      <c r="U26" s="7" t="s">
-        <v>27</v>
+      <c r="U26" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A27" s="8" t="s">
+      <c r="A27" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="B27" s="8">
+        <v>46169.55832063657</v>
+      </c>
+      <c r="C27" s="8">
+        <v>46184.736407812496</v>
+      </c>
+      <c r="D27" s="8">
+        <v>46184.7364097338</v>
+      </c>
+      <c r="E27" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="B27" s="9">
-        <v>46169.55832063657</v>
-      </c>
-      <c r="C27" s="9">
-        <v>46184.736407812496</v>
-      </c>
-      <c r="D27" s="9">
-        <v>46184.7364097338</v>
-      </c>
-      <c r="E27" s="10" t="s">
+      <c r="F27" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G27" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="H27" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="I27" s="8">
+        <v>46169</v>
+      </c>
+      <c r="J27" s="8">
+        <v>46170</v>
+      </c>
+      <c r="K27" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L27" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M27" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N27" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="O27" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="P27" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="F27" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G27" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="H27" s="10" t="s">
-        <v>96</v>
-      </c>
-      <c r="I27" s="9">
-        <v>46169</v>
-      </c>
-      <c r="J27" s="9">
-        <v>46170</v>
-      </c>
-      <c r="K27" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L27" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M27" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N27" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="O27" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="P27" s="10" t="s">
-        <v>110</v>
-      </c>
-      <c r="Q27" s="10"/>
-      <c r="R27" s="10"/>
-      <c r="S27" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T27" s="10">
+      <c r="Q27" s="9"/>
+      <c r="R27" s="9"/>
+      <c r="S27" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="T27" s="9">
         <v>0</v>
       </c>
-      <c r="U27" s="12" t="s">
-        <v>101</v>
+      <c r="U27" s="11" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B28" s="5">
         <v>46169.55832539352</v>
@@ -3100,16 +3096,16 @@
         <v>46184.736449375</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="H28" s="6" t="s">
         <v>95</v>
-      </c>
-      <c r="H28" s="6" t="s">
-        <v>96</v>
       </c>
       <c r="I28" s="5">
         <v>46171</v>
@@ -3127,94 +3123,94 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
-      <c r="S28" s="7" t="s">
-        <v>33</v>
+      <c r="S28" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T28" s="6">
         <v>0</v>
       </c>
-      <c r="U28" s="12" t="s">
-        <v>101</v>
+      <c r="U28" s="11" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A29" s="8" t="s">
+      <c r="A29" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="B29" s="8">
+        <v>46169.55833006944</v>
+      </c>
+      <c r="C29" s="8">
+        <v>46182.67350289352</v>
+      </c>
+      <c r="D29" s="8">
+        <v>46200.81836952546</v>
+      </c>
+      <c r="E29" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="B29" s="9">
-        <v>46169.55833006944</v>
-      </c>
-      <c r="C29" s="9">
-        <v>46182.67350289352</v>
-      </c>
-      <c r="D29" s="9">
-        <v>46195.690666435185</v>
-      </c>
-      <c r="E29" s="10" t="s">
+      <c r="F29" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G29" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="H29" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="I29" s="8">
+        <v>46161</v>
+      </c>
+      <c r="J29" s="8">
+        <v>46290</v>
+      </c>
+      <c r="K29" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L29" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M29" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N29" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="O29" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="F29" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G29" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="H29" s="10" t="s">
-        <v>96</v>
-      </c>
-      <c r="I29" s="9">
+      <c r="P29" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q29" s="8">
         <v>46161</v>
       </c>
-      <c r="J29" s="9">
+      <c r="R29" s="8">
         <v>46290</v>
       </c>
-      <c r="K29" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L29" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M29" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N29" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="O29" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="P29" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="Q29" s="9">
-        <v>46161</v>
-      </c>
-      <c r="R29" s="9">
-        <v>46290</v>
-      </c>
-      <c r="S29" s="7" t="s">
+      <c r="S29" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="T29" s="9">
+        <v>1</v>
+      </c>
+      <c r="U29" s="10" t="s">
         <v>33</v>
-      </c>
-      <c r="T29" s="10">
-        <v>1</v>
-      </c>
-      <c r="U29" s="11" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B30" s="5">
         <v>46169.55833486111</v>
@@ -3226,16 +3222,16 @@
         <v>46195.69066259259</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="H30" s="6" t="s">
         <v>95</v>
-      </c>
-      <c r="H30" s="6" t="s">
-        <v>96</v>
       </c>
       <c r="I30" s="5">
         <v>46161</v>
@@ -3253,90 +3249,90 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="O30" s="6" t="s">
         <v>65</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
-      <c r="S30" s="7" t="s">
-        <v>33</v>
+      <c r="S30" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T30" s="6">
         <v>0</v>
       </c>
-      <c r="U30" s="12" t="s">
-        <v>101</v>
+      <c r="U30" s="11" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A31" s="8" t="s">
+      <c r="A31" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="B31" s="8">
+        <v>46169.5583402662</v>
+      </c>
+      <c r="C31" s="8">
+        <v>46182.67343230324</v>
+      </c>
+      <c r="D31" s="8">
+        <v>46195.69066760417</v>
+      </c>
+      <c r="E31" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="B31" s="9">
-        <v>46169.5583402662</v>
-      </c>
-      <c r="C31" s="9">
-        <v>46182.67343230324</v>
-      </c>
-      <c r="D31" s="9">
-        <v>46195.69066760417</v>
-      </c>
-      <c r="E31" s="10" t="s">
+      <c r="F31" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G31" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="H31" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="I31" s="8">
+        <v>46178</v>
+      </c>
+      <c r="J31" s="8">
+        <v>46290</v>
+      </c>
+      <c r="K31" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L31" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M31" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N31" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="O31" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="P31" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="F31" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G31" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="H31" s="10" t="s">
-        <v>96</v>
-      </c>
-      <c r="I31" s="9">
-        <v>46178</v>
-      </c>
-      <c r="J31" s="9">
-        <v>46290</v>
-      </c>
-      <c r="K31" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L31" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M31" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N31" s="10" t="s">
-        <v>115</v>
-      </c>
-      <c r="O31" s="10" t="s">
-        <v>118</v>
-      </c>
-      <c r="P31" s="10" t="s">
-        <v>122</v>
-      </c>
-      <c r="Q31" s="10"/>
-      <c r="R31" s="10"/>
-      <c r="S31" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T31" s="10">
+      <c r="Q31" s="9"/>
+      <c r="R31" s="9"/>
+      <c r="S31" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="T31" s="9">
         <v>0</v>
       </c>
-      <c r="U31" s="12" t="s">
-        <v>101</v>
+      <c r="U31" s="11" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B32" s="5">
         <v>46169.55834503472</v>
@@ -3348,16 +3344,16 @@
         <v>46195.6906680324</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="H32" s="6" t="s">
         <v>95</v>
-      </c>
-      <c r="H32" s="6" t="s">
-        <v>96</v>
       </c>
       <c r="I32" s="5">
         <v>46178</v>
@@ -3375,94 +3371,94 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
-      <c r="S32" s="7" t="s">
-        <v>33</v>
+      <c r="S32" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T32" s="6">
         <v>0</v>
       </c>
-      <c r="U32" s="12" t="s">
-        <v>101</v>
+      <c r="U32" s="11" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A33" s="8" t="s">
+      <c r="A33" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="B33" s="8">
+        <v>46169.55836335648</v>
+      </c>
+      <c r="C33" s="8">
+        <v>46184.532628437504</v>
+      </c>
+      <c r="D33" s="8">
+        <v>46184.532641875005</v>
+      </c>
+      <c r="E33" s="9" t="s">
         <v>126</v>
       </c>
-      <c r="B33" s="9">
-        <v>46169.55836335648</v>
-      </c>
-      <c r="C33" s="9">
-        <v>46184.532628437504</v>
-      </c>
-      <c r="D33" s="9">
-        <v>46184.532641875005</v>
-      </c>
-      <c r="E33" s="10" t="s">
+      <c r="F33" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G33" s="9" t="s">
         <v>127</v>
       </c>
-      <c r="F33" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G33" s="10" t="s">
+      <c r="H33" s="9" t="s">
         <v>128</v>
       </c>
-      <c r="H33" s="10" t="s">
+      <c r="I33" s="8">
+        <v>46241</v>
+      </c>
+      <c r="J33" s="8">
+        <v>46253</v>
+      </c>
+      <c r="K33" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L33" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M33" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N33" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="O33" s="9" t="s">
         <v>129</v>
       </c>
-      <c r="I33" s="9">
+      <c r="P33" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q33" s="8">
         <v>46241</v>
       </c>
-      <c r="J33" s="9">
+      <c r="R33" s="8">
         <v>46253</v>
       </c>
-      <c r="K33" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L33" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M33" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N33" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="O33" s="10" t="s">
-        <v>130</v>
-      </c>
-      <c r="P33" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="Q33" s="9">
-        <v>46241</v>
-      </c>
-      <c r="R33" s="9">
-        <v>46253</v>
-      </c>
-      <c r="S33" s="7" t="s">
+      <c r="S33" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="T33" s="9">
+        <v>1</v>
+      </c>
+      <c r="U33" s="10" t="s">
         <v>33</v>
-      </c>
-      <c r="T33" s="10">
-        <v>1</v>
-      </c>
-      <c r="U33" s="7" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B34" s="5">
         <v>46169.558367986116</v>
@@ -3474,16 +3470,16 @@
         <v>46184.53245875</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="H34" s="6" t="s">
         <v>128</v>
-      </c>
-      <c r="H34" s="6" t="s">
-        <v>129</v>
       </c>
       <c r="I34" s="5">
         <v>46241</v>
@@ -3501,90 +3497,90 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="O34" s="6" t="s">
         <v>75</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
-      <c r="S34" s="7" t="s">
-        <v>33</v>
+      <c r="S34" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T34" s="6">
         <v>0</v>
       </c>
-      <c r="U34" s="12" t="s">
-        <v>101</v>
+      <c r="U34" s="11" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A35" s="8" t="s">
+      <c r="A35" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="B35" s="8">
+        <v>46169.55837292824</v>
+      </c>
+      <c r="C35" s="8">
+        <v>46184.532613668984</v>
+      </c>
+      <c r="D35" s="8">
+        <v>46184.532615856486</v>
+      </c>
+      <c r="E35" s="9" t="s">
         <v>134</v>
       </c>
-      <c r="B35" s="9">
-        <v>46169.55837292824</v>
-      </c>
-      <c r="C35" s="9">
-        <v>46184.532613668984</v>
-      </c>
-      <c r="D35" s="9">
-        <v>46184.532615856486</v>
-      </c>
-      <c r="E35" s="10" t="s">
+      <c r="F35" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G35" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="H35" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="I35" s="8">
+        <v>46245</v>
+      </c>
+      <c r="J35" s="8">
+        <v>46253</v>
+      </c>
+      <c r="K35" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L35" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M35" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N35" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="O35" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="P35" s="9" t="s">
         <v>135</v>
       </c>
-      <c r="F35" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G35" s="10" t="s">
-        <v>128</v>
-      </c>
-      <c r="H35" s="10" t="s">
-        <v>129</v>
-      </c>
-      <c r="I35" s="9">
-        <v>46245</v>
-      </c>
-      <c r="J35" s="9">
-        <v>46253</v>
-      </c>
-      <c r="K35" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L35" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M35" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N35" s="10" t="s">
-        <v>127</v>
-      </c>
-      <c r="O35" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="P35" s="10" t="s">
-        <v>136</v>
-      </c>
-      <c r="Q35" s="10"/>
-      <c r="R35" s="10"/>
-      <c r="S35" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T35" s="10">
+      <c r="Q35" s="9"/>
+      <c r="R35" s="9"/>
+      <c r="S35" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="T35" s="9">
         <v>0</v>
       </c>
-      <c r="U35" s="12" t="s">
-        <v>101</v>
+      <c r="U35" s="11" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B36" s="5">
         <v>46169.55837825232</v>
@@ -3596,16 +3592,16 @@
         <v>46184.53258194444</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="H36" s="6" t="s">
         <v>128</v>
-      </c>
-      <c r="H36" s="6" t="s">
-        <v>129</v>
       </c>
       <c r="I36" s="5">
         <v>46241</v>
@@ -3626,7 +3622,7 @@
         <v>90</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="P36" s="6" t="s">
         <v>26</v>
@@ -3637,74 +3633,74 @@
       <c r="R36" s="5">
         <v>46253</v>
       </c>
-      <c r="S36" s="7" t="s">
-        <v>33</v>
+      <c r="S36" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T36" s="6">
         <v>1</v>
       </c>
-      <c r="U36" s="7" t="s">
-        <v>27</v>
+      <c r="U36" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A37" s="8" t="s">
+      <c r="A37" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="B37" s="8">
+        <v>46169.558381979165</v>
+      </c>
+      <c r="C37" s="8">
+        <v>46184.53220534722</v>
+      </c>
+      <c r="D37" s="8">
+        <v>46184.5322071875</v>
+      </c>
+      <c r="E37" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="F37" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G37" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="H37" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="I37" s="8">
+        <v>46241</v>
+      </c>
+      <c r="J37" s="8">
+        <v>46244</v>
+      </c>
+      <c r="K37" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L37" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M37" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N37" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="O37" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="P37" s="9" t="s">
         <v>140</v>
       </c>
-      <c r="B37" s="9">
-        <v>46169.558381979165</v>
-      </c>
-      <c r="C37" s="9">
-        <v>46184.53220534722</v>
-      </c>
-      <c r="D37" s="9">
-        <v>46184.5322071875</v>
-      </c>
-      <c r="E37" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="F37" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G37" s="10" t="s">
-        <v>128</v>
-      </c>
-      <c r="H37" s="10" t="s">
-        <v>129</v>
-      </c>
-      <c r="I37" s="9">
-        <v>46241</v>
-      </c>
-      <c r="J37" s="9">
-        <v>46244</v>
-      </c>
-      <c r="K37" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L37" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M37" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N37" s="10" t="s">
-        <v>138</v>
-      </c>
-      <c r="O37" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="P37" s="10" t="s">
-        <v>141</v>
-      </c>
-      <c r="Q37" s="10"/>
-      <c r="R37" s="10"/>
-      <c r="S37" s="10"/>
-      <c r="T37" s="10"/>
-      <c r="U37" s="10"/>
+      <c r="Q37" s="9"/>
+      <c r="R37" s="9"/>
+      <c r="S37" s="9"/>
+      <c r="T37" s="9"/>
+      <c r="U37" s="9"/>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B38" s="5">
         <v>46169.55838657408</v>
@@ -3716,16 +3712,16 @@
         <v>46184.53255631945</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="H38" s="6" t="s">
         <v>128</v>
-      </c>
-      <c r="H38" s="6" t="s">
-        <v>129</v>
       </c>
       <c r="I38" s="5">
         <v>46245</v>
@@ -3743,13 +3739,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="O38" s="6" t="s">
         <v>82</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -3758,73 +3754,73 @@
       <c r="U38" s="6"/>
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A39" s="8" t="s">
+      <c r="A39" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="B39" s="8">
+        <v>46169.55839107639</v>
+      </c>
+      <c r="C39" s="8">
+        <v>46190.64487847222</v>
+      </c>
+      <c r="D39" s="8">
+        <v>46200.81849856481</v>
+      </c>
+      <c r="E39" s="9" t="s">
         <v>145</v>
       </c>
-      <c r="B39" s="9">
-        <v>46169.55839107639</v>
-      </c>
-      <c r="C39" s="9">
-        <v>46190.64487847222</v>
-      </c>
-      <c r="D39" s="9">
-        <v>46195.70377494213</v>
-      </c>
-      <c r="E39" s="10" t="s">
+      <c r="F39" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G39" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="F39" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G39" s="10" t="s">
+      <c r="H39" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="H39" s="10" t="s">
+      <c r="I39" s="8">
+        <v>46241</v>
+      </c>
+      <c r="J39" s="8">
+        <v>46281</v>
+      </c>
+      <c r="K39" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L39" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M39" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N39" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="O39" s="9" t="s">
         <v>148</v>
       </c>
-      <c r="I39" s="9">
+      <c r="P39" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q39" s="8">
         <v>46241</v>
       </c>
-      <c r="J39" s="9">
+      <c r="R39" s="8">
         <v>46281</v>
       </c>
-      <c r="K39" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L39" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M39" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N39" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="O39" s="10" t="s">
-        <v>149</v>
-      </c>
-      <c r="P39" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q39" s="9">
-        <v>46241</v>
-      </c>
-      <c r="R39" s="9">
-        <v>46281</v>
-      </c>
-      <c r="S39" s="7" t="s">
+      <c r="S39" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="T39" s="9">
+        <v>1</v>
+      </c>
+      <c r="U39" s="10" t="s">
         <v>33</v>
-      </c>
-      <c r="T39" s="10">
-        <v>1</v>
-      </c>
-      <c r="U39" s="11" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B40" s="5">
         <v>46169.55839478009</v>
@@ -3842,10 +3838,10 @@
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="H40" s="6" t="s">
         <v>147</v>
-      </c>
-      <c r="H40" s="6" t="s">
-        <v>148</v>
       </c>
       <c r="I40" s="5">
         <v>46241</v>
@@ -3863,13 +3859,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="O40" s="6" t="s">
         <v>87</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -3878,63 +3874,63 @@
       <c r="U40" s="6"/>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A41" s="8" t="s">
+      <c r="A41" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="B41" s="8">
+        <v>46169.55839910879</v>
+      </c>
+      <c r="C41" s="8">
+        <v>46195.703751678244</v>
+      </c>
+      <c r="D41" s="8">
+        <v>46195.70375376157</v>
+      </c>
+      <c r="E41" s="9" t="s">
         <v>152</v>
       </c>
-      <c r="B41" s="9">
-        <v>46169.55839910879</v>
-      </c>
-      <c r="C41" s="9">
-        <v>46195.703751678244</v>
-      </c>
-      <c r="D41" s="9">
-        <v>46195.70375376157</v>
-      </c>
-      <c r="E41" s="10" t="s">
+      <c r="F41" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G41" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="H41" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="I41" s="8">
+        <v>46252</v>
+      </c>
+      <c r="J41" s="8">
+        <v>46280</v>
+      </c>
+      <c r="K41" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L41" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M41" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N41" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="O41" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="P41" s="9" t="s">
         <v>153</v>
       </c>
-      <c r="F41" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G41" s="10" t="s">
-        <v>147</v>
-      </c>
-      <c r="H41" s="10" t="s">
-        <v>148</v>
-      </c>
-      <c r="I41" s="9">
-        <v>46252</v>
-      </c>
-      <c r="J41" s="9">
-        <v>46280</v>
-      </c>
-      <c r="K41" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L41" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M41" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N41" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="O41" s="10" t="s">
-        <v>88</v>
-      </c>
-      <c r="P41" s="10" t="s">
-        <v>154</v>
-      </c>
-      <c r="Q41" s="10"/>
-      <c r="R41" s="10"/>
-      <c r="S41" s="10"/>
-      <c r="T41" s="10"/>
-      <c r="U41" s="10"/>
+      <c r="Q41" s="9"/>
+      <c r="R41" s="9"/>
+      <c r="S41" s="9"/>
+      <c r="T41" s="9"/>
+      <c r="U41" s="9"/>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B42" s="5">
         <v>46169.55840355324</v>
@@ -3944,16 +3940,16 @@
         <v>46195.703763495374</v>
       </c>
       <c r="E42" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="F42" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G42" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="F42" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G42" s="6" t="s">
+      <c r="H42" s="6" t="s">
         <v>157</v>
-      </c>
-      <c r="H42" s="6" t="s">
-        <v>158</v>
       </c>
       <c r="I42" s="5">
         <v>46281</v>
@@ -3971,10 +3967,10 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>26</v>
@@ -3986,73 +3982,73 @@
       <c r="U42" s="6"/>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A43" s="8" t="s">
+      <c r="A43" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="B43" s="8">
+        <v>46169.55840677083</v>
+      </c>
+      <c r="C43" s="8">
+        <v>46191.53700108796</v>
+      </c>
+      <c r="D43" s="8">
+        <v>46191.53701371528</v>
+      </c>
+      <c r="E43" s="9" t="s">
         <v>159</v>
       </c>
-      <c r="B43" s="9">
-        <v>46169.55840677083</v>
-      </c>
-      <c r="C43" s="9">
-        <v>46191.53700108796</v>
-      </c>
-      <c r="D43" s="9">
-        <v>46191.53701371528</v>
-      </c>
-      <c r="E43" s="10" t="s">
+      <c r="F43" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G43" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="H43" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="I43" s="8">
+        <v>46241</v>
+      </c>
+      <c r="J43" s="8">
+        <v>46253</v>
+      </c>
+      <c r="K43" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L43" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M43" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N43" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="O43" s="9" t="s">
         <v>160</v>
       </c>
-      <c r="F43" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G43" s="10" t="s">
-        <v>128</v>
-      </c>
-      <c r="H43" s="10" t="s">
-        <v>129</v>
-      </c>
-      <c r="I43" s="9">
+      <c r="P43" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q43" s="8">
         <v>46241</v>
       </c>
-      <c r="J43" s="9">
+      <c r="R43" s="8">
         <v>46253</v>
       </c>
-      <c r="K43" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L43" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M43" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N43" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="O43" s="10" t="s">
-        <v>161</v>
-      </c>
-      <c r="P43" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q43" s="9">
-        <v>46241</v>
-      </c>
-      <c r="R43" s="9">
-        <v>46253</v>
-      </c>
-      <c r="S43" s="7" t="s">
+      <c r="S43" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="T43" s="9">
+        <v>1</v>
+      </c>
+      <c r="U43" s="10" t="s">
         <v>33</v>
-      </c>
-      <c r="T43" s="10">
-        <v>1</v>
-      </c>
-      <c r="U43" s="7" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B44" s="5">
         <v>46169.55841037037</v>
@@ -4070,10 +4066,10 @@
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="H44" s="6" t="s">
         <v>128</v>
-      </c>
-      <c r="H44" s="6" t="s">
-        <v>129</v>
       </c>
       <c r="I44" s="5">
         <v>46241</v>
@@ -4091,13 +4087,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="O44" s="6" t="s">
         <v>84</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4106,63 +4102,63 @@
       <c r="U44" s="6"/>
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A45" s="8" t="s">
+      <c r="A45" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="B45" s="8">
+        <v>46169.558458217594</v>
+      </c>
+      <c r="C45" s="8">
+        <v>46191.53698667824</v>
+      </c>
+      <c r="D45" s="8">
+        <v>46191.53698841435</v>
+      </c>
+      <c r="E45" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="B45" s="9">
-        <v>46169.558458217594</v>
-      </c>
-      <c r="C45" s="9">
-        <v>46191.53698667824</v>
-      </c>
-      <c r="D45" s="9">
-        <v>46191.53698841435</v>
-      </c>
-      <c r="E45" s="10" t="s">
+      <c r="F45" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G45" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="H45" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="I45" s="8">
+        <v>46245</v>
+      </c>
+      <c r="J45" s="8">
+        <v>46253</v>
+      </c>
+      <c r="K45" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L45" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M45" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N45" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="O45" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="P45" s="9" t="s">
         <v>165</v>
       </c>
-      <c r="F45" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G45" s="10" t="s">
-        <v>128</v>
-      </c>
-      <c r="H45" s="10" t="s">
-        <v>129</v>
-      </c>
-      <c r="I45" s="9">
-        <v>46245</v>
-      </c>
-      <c r="J45" s="9">
-        <v>46253</v>
-      </c>
-      <c r="K45" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L45" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M45" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N45" s="10" t="s">
-        <v>160</v>
-      </c>
-      <c r="O45" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="P45" s="10" t="s">
-        <v>166</v>
-      </c>
-      <c r="Q45" s="10"/>
-      <c r="R45" s="10"/>
-      <c r="S45" s="10"/>
-      <c r="T45" s="10"/>
-      <c r="U45" s="10"/>
+      <c r="Q45" s="9"/>
+      <c r="R45" s="9"/>
+      <c r="S45" s="9"/>
+      <c r="T45" s="9"/>
+      <c r="U45" s="9"/>
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B46" s="5">
         <v>46169.5584643287</v>
@@ -4172,7 +4168,7 @@
         <v>46182.75962331019</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>25</v>
@@ -4196,7 +4192,7 @@
         <v>26</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4205,73 +4201,73 @@
       <c r="R46" s="6"/>
       <c r="S46" s="6"/>
       <c r="T46" s="6"/>
-      <c r="U46" s="11" t="s">
-        <v>92</v>
+      <c r="U46" s="12" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A47" s="8" t="s">
+      <c r="A47" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="B47" s="9">
+      <c r="B47" s="8">
         <v>46169.55846813657</v>
       </c>
-      <c r="C47" s="9">
+      <c r="C47" s="8">
         <v>46181.72664483797</v>
       </c>
-      <c r="D47" s="9">
+      <c r="D47" s="8">
         <v>46197.715420312496</v>
       </c>
-      <c r="E47" s="10" t="s">
+      <c r="E47" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="F47" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G47" s="10" t="s">
+      <c r="F47" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G47" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="H47" s="10" t="s">
+      <c r="H47" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="I47" s="9">
+      <c r="I47" s="8">
         <v>46167</v>
       </c>
-      <c r="J47" s="9">
+      <c r="J47" s="8">
         <v>46184</v>
       </c>
-      <c r="K47" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L47" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M47" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N47" s="10" t="s">
-        <v>168</v>
-      </c>
-      <c r="O47" s="10" t="s">
+      <c r="K47" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L47" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M47" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N47" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="O47" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="P47" s="10" t="s">
-        <v>168</v>
-      </c>
-      <c r="Q47" s="9">
+      <c r="P47" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="Q47" s="8">
         <v>46167</v>
       </c>
-      <c r="R47" s="9">
+      <c r="R47" s="8">
         <v>46184</v>
       </c>
-      <c r="S47" s="12" t="s">
+      <c r="S47" s="11" t="s">
         <v>175</v>
       </c>
-      <c r="T47" s="10">
+      <c r="T47" s="9">
         <v>1</v>
       </c>
-      <c r="U47" s="7" t="s">
-        <v>27</v>
+      <c r="U47" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
@@ -4330,68 +4326,68 @@
       <c r="U48" s="6"/>
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A49" s="8" t="s">
+      <c r="A49" s="7" t="s">
         <v>180</v>
       </c>
-      <c r="B49" s="9">
+      <c r="B49" s="8">
         <v>46169.55849938658</v>
       </c>
-      <c r="C49" s="9">
+      <c r="C49" s="8">
         <v>46182.759602164355</v>
       </c>
-      <c r="D49" s="9">
+      <c r="D49" s="8">
         <v>46197.71545016204</v>
       </c>
-      <c r="E49" s="10" t="s">
+      <c r="E49" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="F49" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G49" s="10" t="s">
+      <c r="F49" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G49" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="H49" s="10" t="s">
+      <c r="H49" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="I49" s="9">
+      <c r="I49" s="8">
         <v>46218</v>
       </c>
-      <c r="J49" s="9">
+      <c r="J49" s="8">
         <v>46237</v>
       </c>
-      <c r="K49" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L49" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M49" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N49" s="10" t="s">
-        <v>168</v>
-      </c>
-      <c r="O49" s="10" t="s">
+      <c r="K49" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L49" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M49" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N49" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="O49" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="P49" s="10" t="s">
-        <v>168</v>
-      </c>
-      <c r="Q49" s="9">
+      <c r="P49" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="Q49" s="8">
         <v>46218</v>
       </c>
-      <c r="R49" s="9">
+      <c r="R49" s="8">
         <v>46237</v>
       </c>
-      <c r="S49" s="7" t="s">
+      <c r="S49" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="T49" s="9">
+        <v>1</v>
+      </c>
+      <c r="U49" s="10" t="s">
         <v>33</v>
-      </c>
-      <c r="T49" s="10">
-        <v>1</v>
-      </c>
-      <c r="U49" s="7" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
@@ -4450,68 +4446,68 @@
       <c r="U50" s="6"/>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A51" s="8" t="s">
+      <c r="A51" s="7" t="s">
         <v>185</v>
       </c>
-      <c r="B51" s="9">
+      <c r="B51" s="8">
         <v>46169.55853228009</v>
       </c>
-      <c r="C51" s="9">
+      <c r="C51" s="8">
         <v>46182.75986146991</v>
       </c>
-      <c r="D51" s="9">
+      <c r="D51" s="8">
         <v>46182.759871076385</v>
       </c>
-      <c r="E51" s="10" t="s">
+      <c r="E51" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="F51" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G51" s="10" t="s">
+      <c r="F51" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G51" s="9" t="s">
         <v>177</v>
       </c>
-      <c r="H51" s="10" t="s">
+      <c r="H51" s="9" t="s">
         <v>178</v>
       </c>
-      <c r="I51" s="9">
+      <c r="I51" s="8">
         <v>46238</v>
       </c>
-      <c r="J51" s="9">
+      <c r="J51" s="8">
         <v>46238</v>
       </c>
-      <c r="K51" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L51" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M51" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N51" s="10" t="s">
-        <v>168</v>
-      </c>
-      <c r="O51" s="10" t="s">
+      <c r="K51" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L51" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M51" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N51" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="O51" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="P51" s="10" t="s">
+      <c r="P51" s="9" t="s">
         <v>186</v>
       </c>
-      <c r="Q51" s="9">
+      <c r="Q51" s="8">
         <v>46238</v>
       </c>
-      <c r="R51" s="9">
+      <c r="R51" s="8">
         <v>46238</v>
       </c>
-      <c r="S51" s="7" t="s">
+      <c r="S51" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="T51" s="9">
+        <v>1</v>
+      </c>
+      <c r="U51" s="10" t="s">
         <v>33</v>
-      </c>
-      <c r="T51" s="10">
-        <v>1</v>
-      </c>
-      <c r="U51" s="7" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
@@ -4570,66 +4566,66 @@
       <c r="U52" s="6"/>
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A53" s="8" t="s">
+      <c r="A53" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="B53" s="9">
+      <c r="B53" s="8">
         <v>46169.558565775464</v>
       </c>
-      <c r="C53" s="10"/>
-      <c r="D53" s="9">
+      <c r="C53" s="9"/>
+      <c r="D53" s="8">
         <v>46169.61885943287</v>
       </c>
-      <c r="E53" s="10" t="s">
+      <c r="E53" s="9" t="s">
         <v>189</v>
       </c>
-      <c r="F53" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G53" s="10" t="s">
+      <c r="F53" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G53" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="H53" s="10" t="s">
+      <c r="H53" s="9" t="s">
         <v>191</v>
       </c>
-      <c r="I53" s="9">
+      <c r="I53" s="8">
         <v>46331</v>
       </c>
-      <c r="J53" s="9">
+      <c r="J53" s="8">
         <v>46331</v>
       </c>
-      <c r="K53" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L53" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M53" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N53" s="10" t="s">
-        <v>168</v>
-      </c>
-      <c r="O53" s="10" t="s">
+      <c r="K53" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L53" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M53" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N53" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="O53" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="P53" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q53" s="9">
+      <c r="P53" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q53" s="8">
         <v>46331</v>
       </c>
-      <c r="R53" s="9">
+      <c r="R53" s="8">
         <v>46331</v>
       </c>
-      <c r="S53" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T53" s="10">
+      <c r="S53" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="T53" s="9">
         <v>0</v>
       </c>
-      <c r="U53" s="12" t="s">
-        <v>101</v>
+      <c r="U53" s="11" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
@@ -4686,56 +4682,56 @@
       <c r="U54" s="6"/>
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A55" s="8" t="s">
+      <c r="A55" s="7" t="s">
         <v>195</v>
       </c>
-      <c r="B55" s="9">
+      <c r="B55" s="8">
         <v>46169.558586307874</v>
       </c>
-      <c r="C55" s="9">
+      <c r="C55" s="8">
         <v>46198.59773380787</v>
       </c>
-      <c r="D55" s="9">
+      <c r="D55" s="8">
         <v>46198.597746307874</v>
       </c>
-      <c r="E55" s="10" t="s">
+      <c r="E55" s="9" t="s">
         <v>196</v>
       </c>
-      <c r="F55" s="10" t="s">
+      <c r="F55" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="G55" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H55" s="10"/>
-      <c r="I55" s="10"/>
-      <c r="J55" s="10"/>
-      <c r="K55" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L55" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M55" s="10" t="s">
+      <c r="G55" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="H55" s="9"/>
+      <c r="I55" s="9"/>
+      <c r="J55" s="9"/>
+      <c r="K55" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L55" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M55" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="N55" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="O55" s="10" t="s">
+      <c r="N55" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="O55" s="9" t="s">
         <v>197</v>
       </c>
-      <c r="P55" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q55" s="10"/>
-      <c r="R55" s="10"/>
-      <c r="S55" s="10"/>
-      <c r="T55" s="10">
+      <c r="P55" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q55" s="9"/>
+      <c r="R55" s="9"/>
+      <c r="S55" s="9"/>
+      <c r="T55" s="9">
         <v>1</v>
       </c>
-      <c r="U55" s="7" t="s">
-        <v>27</v>
+      <c r="U55" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
@@ -4782,7 +4778,7 @@
         <v>196</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P56" s="6" t="s">
         <v>202</v>
@@ -4793,79 +4789,79 @@
       <c r="R56" s="5">
         <v>46255</v>
       </c>
-      <c r="S56" s="7" t="s">
-        <v>33</v>
+      <c r="S56" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T56" s="6">
         <v>1</v>
       </c>
-      <c r="U56" s="7" t="s">
-        <v>27</v>
+      <c r="U56" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A57" s="8" t="s">
+      <c r="A57" s="7" t="s">
         <v>203</v>
       </c>
-      <c r="B57" s="9">
+      <c r="B57" s="8">
         <v>46169.55859488426</v>
       </c>
-      <c r="C57" s="9">
+      <c r="C57" s="8">
         <v>46197.85935881945</v>
       </c>
-      <c r="D57" s="9">
+      <c r="D57" s="8">
         <v>46197.85937331019</v>
       </c>
-      <c r="E57" s="10" t="s">
+      <c r="E57" s="9" t="s">
         <v>204</v>
       </c>
-      <c r="F57" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G57" s="10" t="s">
+      <c r="F57" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G57" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="H57" s="9" t="s">
         <v>157</v>
       </c>
-      <c r="H57" s="10" t="s">
-        <v>158</v>
-      </c>
-      <c r="I57" s="9">
+      <c r="I57" s="8">
         <v>46258</v>
       </c>
-      <c r="J57" s="9">
+      <c r="J57" s="8">
         <v>46259</v>
       </c>
-      <c r="K57" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L57" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M57" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N57" s="10" t="s">
+      <c r="K57" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L57" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M57" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N57" s="9" t="s">
         <v>196</v>
       </c>
-      <c r="O57" s="10" t="s">
+      <c r="O57" s="9" t="s">
         <v>199</v>
       </c>
-      <c r="P57" s="10" t="s">
+      <c r="P57" s="9" t="s">
         <v>205</v>
       </c>
-      <c r="Q57" s="9">
+      <c r="Q57" s="8">
         <v>46258</v>
       </c>
-      <c r="R57" s="9">
+      <c r="R57" s="8">
         <v>46259</v>
       </c>
-      <c r="S57" s="7" t="s">
+      <c r="S57" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="T57" s="9">
+        <v>1</v>
+      </c>
+      <c r="U57" s="10" t="s">
         <v>33</v>
-      </c>
-      <c r="T57" s="10">
-        <v>1</v>
-      </c>
-      <c r="U57" s="7" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
@@ -4912,7 +4908,7 @@
         <v>196</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="P58" s="6" t="s">
         <v>208</v>
@@ -4923,79 +4919,79 @@
       <c r="R58" s="5">
         <v>46255</v>
       </c>
-      <c r="S58" s="7" t="s">
-        <v>33</v>
+      <c r="S58" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T58" s="6">
         <v>1</v>
       </c>
-      <c r="U58" s="7" t="s">
-        <v>27</v>
+      <c r="U58" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A59" s="8" t="s">
+      <c r="A59" s="7" t="s">
         <v>209</v>
       </c>
-      <c r="B59" s="9">
+      <c r="B59" s="8">
         <v>46169.55860636574</v>
       </c>
-      <c r="C59" s="9">
+      <c r="C59" s="8">
         <v>46197.85931310186</v>
       </c>
-      <c r="D59" s="9">
+      <c r="D59" s="8">
         <v>46198.597709444446</v>
       </c>
-      <c r="E59" s="10" t="s">
+      <c r="E59" s="9" t="s">
         <v>208</v>
       </c>
-      <c r="F59" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G59" s="10" t="s">
+      <c r="F59" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G59" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="H59" s="9" t="s">
         <v>157</v>
       </c>
-      <c r="H59" s="10" t="s">
-        <v>158</v>
-      </c>
-      <c r="I59" s="9">
+      <c r="I59" s="8">
         <v>46258</v>
       </c>
-      <c r="J59" s="9">
+      <c r="J59" s="8">
         <v>46259</v>
       </c>
-      <c r="K59" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L59" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M59" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N59" s="10" t="s">
+      <c r="K59" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L59" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M59" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N59" s="9" t="s">
         <v>196</v>
       </c>
-      <c r="O59" s="10" t="s">
+      <c r="O59" s="9" t="s">
         <v>207</v>
       </c>
-      <c r="P59" s="10" t="s">
+      <c r="P59" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="Q59" s="9">
+      <c r="Q59" s="8">
         <v>46258</v>
       </c>
-      <c r="R59" s="9">
+      <c r="R59" s="8">
         <v>46259</v>
       </c>
-      <c r="S59" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T59" s="10">
+      <c r="S59" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="T59" s="9">
         <v>1</v>
       </c>
-      <c r="U59" s="11" t="s">
-        <v>92</v>
+      <c r="U59" s="12" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
@@ -5042,7 +5038,7 @@
         <v>196</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="P60" s="6" t="s">
         <v>212</v>
@@ -5053,79 +5049,79 @@
       <c r="R60" s="5">
         <v>46255</v>
       </c>
-      <c r="S60" s="7" t="s">
-        <v>33</v>
+      <c r="S60" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T60" s="6">
         <v>1</v>
       </c>
-      <c r="U60" s="7" t="s">
-        <v>27</v>
+      <c r="U60" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A61" s="8" t="s">
+      <c r="A61" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="B61" s="9">
+      <c r="B61" s="8">
         <v>46169.55865608796</v>
       </c>
-      <c r="C61" s="9">
+      <c r="C61" s="8">
         <v>46197.85923987269</v>
       </c>
-      <c r="D61" s="9">
+      <c r="D61" s="8">
         <v>46198.59773317129</v>
       </c>
-      <c r="E61" s="10" t="s">
+      <c r="E61" s="9" t="s">
         <v>212</v>
       </c>
-      <c r="F61" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G61" s="10" t="s">
+      <c r="F61" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G61" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="H61" s="9" t="s">
         <v>157</v>
       </c>
-      <c r="H61" s="10" t="s">
-        <v>158</v>
-      </c>
-      <c r="I61" s="9">
+      <c r="I61" s="8">
         <v>46258</v>
       </c>
-      <c r="J61" s="9">
+      <c r="J61" s="8">
         <v>46259</v>
       </c>
-      <c r="K61" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L61" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M61" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N61" s="10" t="s">
+      <c r="K61" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L61" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M61" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N61" s="9" t="s">
         <v>196</v>
       </c>
-      <c r="O61" s="10" t="s">
+      <c r="O61" s="9" t="s">
         <v>211</v>
       </c>
-      <c r="P61" s="10" t="s">
+      <c r="P61" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="Q61" s="9">
+      <c r="Q61" s="8">
         <v>46258</v>
       </c>
-      <c r="R61" s="9">
+      <c r="R61" s="8">
         <v>46259</v>
       </c>
-      <c r="S61" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T61" s="10">
+      <c r="S61" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="T61" s="9">
         <v>1</v>
       </c>
-      <c r="U61" s="11" t="s">
-        <v>92</v>
+      <c r="U61" s="12" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
@@ -5177,73 +5173,73 @@
       <c r="T62" s="6">
         <v>1</v>
       </c>
-      <c r="U62" s="7" t="s">
-        <v>27</v>
+      <c r="U62" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A63" s="8" t="s">
+      <c r="A63" s="7" t="s">
         <v>217</v>
       </c>
-      <c r="B63" s="9">
+      <c r="B63" s="8">
         <v>46169.55866469907</v>
       </c>
-      <c r="C63" s="9">
+      <c r="C63" s="8">
         <v>46190.645243935185</v>
       </c>
-      <c r="D63" s="9">
+      <c r="D63" s="8">
         <v>46197.85915361111</v>
       </c>
-      <c r="E63" s="10" t="s">
+      <c r="E63" s="9" t="s">
         <v>218</v>
       </c>
-      <c r="F63" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G63" s="10" t="s">
+      <c r="F63" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G63" s="9" t="s">
         <v>219</v>
       </c>
-      <c r="H63" s="10" t="s">
+      <c r="H63" s="9" t="s">
         <v>220</v>
       </c>
-      <c r="I63" s="9">
+      <c r="I63" s="8">
         <v>46260</v>
       </c>
-      <c r="J63" s="9">
+      <c r="J63" s="8">
         <v>46268</v>
       </c>
-      <c r="K63" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L63" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M63" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N63" s="10" t="s">
+      <c r="K63" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L63" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M63" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N63" s="9" t="s">
         <v>215</v>
       </c>
-      <c r="O63" s="10" t="s">
+      <c r="O63" s="9" t="s">
         <v>221</v>
       </c>
-      <c r="P63" s="10" t="s">
+      <c r="P63" s="9" t="s">
         <v>215</v>
       </c>
-      <c r="Q63" s="9">
+      <c r="Q63" s="8">
         <v>46260</v>
       </c>
-      <c r="R63" s="9">
+      <c r="R63" s="8">
         <v>46268</v>
       </c>
-      <c r="S63" s="7" t="s">
+      <c r="S63" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="T63" s="9">
+        <v>1</v>
+      </c>
+      <c r="U63" s="10" t="s">
         <v>33</v>
-      </c>
-      <c r="T63" s="10">
-        <v>1</v>
-      </c>
-      <c r="U63" s="7" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
@@ -5302,68 +5298,68 @@
       <c r="U64" s="6"/>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A65" s="8" t="s">
+      <c r="A65" s="7" t="s">
         <v>225</v>
       </c>
-      <c r="B65" s="9">
+      <c r="B65" s="8">
         <v>46169.558703518516</v>
       </c>
-      <c r="C65" s="9">
+      <c r="C65" s="8">
         <v>46190.64532476851</v>
       </c>
-      <c r="D65" s="9">
+      <c r="D65" s="8">
         <v>46197.85387390046</v>
       </c>
-      <c r="E65" s="10" t="s">
+      <c r="E65" s="9" t="s">
         <v>226</v>
       </c>
-      <c r="F65" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G65" s="10" t="s">
+      <c r="F65" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G65" s="9" t="s">
         <v>219</v>
       </c>
-      <c r="H65" s="10" t="s">
+      <c r="H65" s="9" t="s">
         <v>220</v>
       </c>
-      <c r="I65" s="9">
+      <c r="I65" s="8">
         <v>46269</v>
       </c>
-      <c r="J65" s="9">
+      <c r="J65" s="8">
         <v>46273</v>
       </c>
-      <c r="K65" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L65" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M65" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N65" s="10" t="s">
+      <c r="K65" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L65" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M65" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N65" s="9" t="s">
         <v>215</v>
       </c>
-      <c r="O65" s="10" t="s">
+      <c r="O65" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="P65" s="10" t="s">
+      <c r="P65" s="9" t="s">
         <v>215</v>
       </c>
-      <c r="Q65" s="9">
+      <c r="Q65" s="8">
         <v>46269</v>
       </c>
-      <c r="R65" s="9">
+      <c r="R65" s="8">
         <v>46273</v>
       </c>
-      <c r="S65" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T65" s="10">
+      <c r="S65" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="T65" s="9">
         <v>1</v>
       </c>
-      <c r="U65" s="11" t="s">
-        <v>92</v>
+      <c r="U65" s="12" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
@@ -5422,68 +5418,68 @@
       <c r="U66" s="6"/>
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A67" s="8" t="s">
+      <c r="A67" s="7" t="s">
         <v>230</v>
       </c>
-      <c r="B67" s="9">
+      <c r="B67" s="8">
         <v>46169.558740625</v>
       </c>
-      <c r="C67" s="9">
+      <c r="C67" s="8">
         <v>46198.68226086805</v>
       </c>
-      <c r="D67" s="9">
+      <c r="D67" s="8">
         <v>46198.68228008102</v>
       </c>
-      <c r="E67" s="10" t="s">
+      <c r="E67" s="9" t="s">
         <v>231</v>
       </c>
-      <c r="F67" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G67" s="10" t="s">
+      <c r="F67" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G67" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="H67" s="9" t="s">
         <v>157</v>
       </c>
-      <c r="H67" s="10" t="s">
-        <v>158</v>
-      </c>
-      <c r="I67" s="9">
+      <c r="I67" s="8">
         <v>46274</v>
       </c>
-      <c r="J67" s="9">
+      <c r="J67" s="8">
         <v>46275</v>
       </c>
-      <c r="K67" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L67" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M67" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N67" s="10" t="s">
+      <c r="K67" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L67" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M67" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N67" s="9" t="s">
         <v>215</v>
       </c>
-      <c r="O67" s="10" t="s">
+      <c r="O67" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="P67" s="10" t="s">
+      <c r="P67" s="9" t="s">
         <v>215</v>
       </c>
-      <c r="Q67" s="9">
+      <c r="Q67" s="8">
         <v>46274</v>
       </c>
-      <c r="R67" s="9">
+      <c r="R67" s="8">
         <v>46275</v>
       </c>
-      <c r="S67" s="7" t="s">
+      <c r="S67" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="T67" s="9">
+        <v>1</v>
+      </c>
+      <c r="U67" s="10" t="s">
         <v>33</v>
-      </c>
-      <c r="T67" s="10">
-        <v>1</v>
-      </c>
-      <c r="U67" s="7" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
@@ -5504,10 +5500,10 @@
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="H68" s="6" t="s">
         <v>157</v>
-      </c>
-      <c r="H68" s="6" t="s">
-        <v>158</v>
       </c>
       <c r="I68" s="5">
         <v>46274</v>
@@ -5540,51 +5536,53 @@
       <c r="U68" s="6"/>
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A69" s="8" t="s">
+      <c r="A69" s="7" t="s">
         <v>234</v>
       </c>
-      <c r="B69" s="9">
+      <c r="B69" s="8">
         <v>46169.55876947917</v>
       </c>
-      <c r="C69" s="10"/>
-      <c r="D69" s="9">
-        <v>46169.60236578704</v>
-      </c>
-      <c r="E69" s="10" t="s">
+      <c r="C69" s="9"/>
+      <c r="D69" s="8">
+        <v>46200.819705856484</v>
+      </c>
+      <c r="E69" s="9" t="s">
         <v>196</v>
       </c>
-      <c r="F69" s="10" t="s">
+      <c r="F69" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="G69" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H69" s="10"/>
-      <c r="I69" s="10"/>
-      <c r="J69" s="10"/>
-      <c r="K69" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L69" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M69" s="10" t="s">
+      <c r="G69" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="H69" s="9"/>
+      <c r="I69" s="9"/>
+      <c r="J69" s="9"/>
+      <c r="K69" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L69" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M69" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="N69" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="O69" s="10" t="s">
+      <c r="N69" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="O69" s="9" t="s">
         <v>235</v>
       </c>
-      <c r="P69" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q69" s="10"/>
-      <c r="R69" s="10"/>
-      <c r="S69" s="10"/>
-      <c r="T69" s="10"/>
-      <c r="U69" s="10"/>
+      <c r="P69" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q69" s="9"/>
+      <c r="R69" s="9"/>
+      <c r="S69" s="9"/>
+      <c r="T69" s="9"/>
+      <c r="U69" s="12" t="s">
+        <v>169</v>
+      </c>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
@@ -5593,9 +5591,11 @@
       <c r="B70" s="5">
         <v>46169.55880633101</v>
       </c>
-      <c r="C70" s="6"/>
+      <c r="C70" s="5">
+        <v>46200.81968587963</v>
+      </c>
       <c r="D70" s="5">
-        <v>46184.736466689814</v>
+        <v>46200.8197621875</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>237</v>
@@ -5628,7 +5628,7 @@
         <v>196</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>238</v>
@@ -5639,77 +5639,79 @@
       <c r="R70" s="5">
         <v>46223</v>
       </c>
-      <c r="S70" s="7" t="s">
+      <c r="S70" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="T70" s="6">
+        <v>1</v>
+      </c>
+      <c r="U70" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="T70" s="6">
-        <v>0</v>
-      </c>
-      <c r="U70" s="11" t="s">
-        <v>92</v>
-      </c>
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A71" s="8" t="s">
+      <c r="A71" s="7" t="s">
         <v>239</v>
       </c>
-      <c r="B71" s="9">
+      <c r="B71" s="8">
         <v>46169.5588177662</v>
       </c>
-      <c r="C71" s="10"/>
-      <c r="D71" s="9">
-        <v>46182.673394074074</v>
-      </c>
-      <c r="E71" s="10" t="s">
+      <c r="C71" s="8">
+        <v>46200.81967096065</v>
+      </c>
+      <c r="D71" s="8">
+        <v>46200.819831597226</v>
+      </c>
+      <c r="E71" s="9" t="s">
         <v>240</v>
       </c>
-      <c r="F71" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G71" s="10" t="s">
+      <c r="F71" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G71" s="9" t="s">
         <v>200</v>
       </c>
-      <c r="H71" s="10" t="s">
+      <c r="H71" s="9" t="s">
         <v>201</v>
       </c>
-      <c r="I71" s="9">
+      <c r="I71" s="8">
         <v>46325</v>
       </c>
-      <c r="J71" s="9">
+      <c r="J71" s="8">
         <v>46325</v>
       </c>
-      <c r="K71" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L71" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M71" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N71" s="10" t="s">
+      <c r="K71" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L71" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M71" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N71" s="9" t="s">
         <v>196</v>
       </c>
-      <c r="O71" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="P71" s="10" t="s">
+      <c r="O71" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="P71" s="9" t="s">
         <v>241</v>
       </c>
-      <c r="Q71" s="9">
+      <c r="Q71" s="8">
         <v>46325</v>
       </c>
-      <c r="R71" s="9">
+      <c r="R71" s="8">
         <v>46325</v>
       </c>
-      <c r="S71" s="12" t="s">
+      <c r="S71" s="11" t="s">
         <v>175</v>
       </c>
-      <c r="T71" s="10">
-        <v>0</v>
-      </c>
-      <c r="U71" s="11" t="s">
-        <v>92</v>
+      <c r="T71" s="9">
+        <v>1</v>
+      </c>
+      <c r="U71" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
@@ -5719,9 +5721,11 @@
       <c r="B72" s="5">
         <v>46169.55882295139</v>
       </c>
-      <c r="C72" s="6"/>
+      <c r="C72" s="5">
+        <v>46200.819208981484</v>
+      </c>
       <c r="D72" s="5">
-        <v>46182.6734475</v>
+        <v>46200.81928909722</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>243</v>
@@ -5754,7 +5758,7 @@
         <v>196</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="P72" s="6" t="s">
         <v>205</v>
@@ -5765,77 +5769,77 @@
       <c r="R72" s="5">
         <v>46293</v>
       </c>
-      <c r="S72" s="7" t="s">
+      <c r="S72" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="T72" s="6">
+        <v>1</v>
+      </c>
+      <c r="U72" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="T72" s="6">
+    </row>
+    <row r="73" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A73" s="7" t="s">
+        <v>244</v>
+      </c>
+      <c r="B73" s="8">
+        <v>46169.55882788195</v>
+      </c>
+      <c r="C73" s="9"/>
+      <c r="D73" s="8">
+        <v>46195.70377457176</v>
+      </c>
+      <c r="E73" s="9" t="s">
+        <v>245</v>
+      </c>
+      <c r="F73" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G73" s="9" t="s">
+        <v>200</v>
+      </c>
+      <c r="H73" s="9" t="s">
+        <v>201</v>
+      </c>
+      <c r="I73" s="8">
+        <v>46282</v>
+      </c>
+      <c r="J73" s="8">
+        <v>46282</v>
+      </c>
+      <c r="K73" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L73" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M73" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N73" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="O73" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="P73" s="9" t="s">
+        <v>246</v>
+      </c>
+      <c r="Q73" s="8">
+        <v>46282</v>
+      </c>
+      <c r="R73" s="8">
+        <v>46282</v>
+      </c>
+      <c r="S73" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="T73" s="9">
         <v>0</v>
       </c>
-      <c r="U72" s="11" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="73" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A73" s="8" t="s">
-        <v>244</v>
-      </c>
-      <c r="B73" s="9">
-        <v>46169.55882788195</v>
-      </c>
-      <c r="C73" s="10"/>
-      <c r="D73" s="9">
-        <v>46195.70377457176</v>
-      </c>
-      <c r="E73" s="10" t="s">
-        <v>245</v>
-      </c>
-      <c r="F73" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G73" s="10" t="s">
-        <v>200</v>
-      </c>
-      <c r="H73" s="10" t="s">
-        <v>201</v>
-      </c>
-      <c r="I73" s="9">
-        <v>46282</v>
-      </c>
-      <c r="J73" s="9">
-        <v>46282</v>
-      </c>
-      <c r="K73" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L73" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M73" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N73" s="10" t="s">
-        <v>196</v>
-      </c>
-      <c r="O73" s="10" t="s">
-        <v>153</v>
-      </c>
-      <c r="P73" s="10" t="s">
-        <v>246</v>
-      </c>
-      <c r="Q73" s="9">
-        <v>46282</v>
-      </c>
-      <c r="R73" s="9">
-        <v>46282</v>
-      </c>
-      <c r="S73" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T73" s="10">
-        <v>0</v>
-      </c>
-      <c r="U73" s="11" t="s">
-        <v>92</v>
+      <c r="U73" s="12" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
@@ -5886,68 +5890,68 @@
       <c r="U74" s="6"/>
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A75" s="8" t="s">
+      <c r="A75" s="7" t="s">
         <v>250</v>
       </c>
-      <c r="B75" s="9">
+      <c r="B75" s="8">
         <v>46169.55884548611</v>
       </c>
-      <c r="C75" s="9">
+      <c r="C75" s="8">
         <v>46197.49536869213</v>
       </c>
-      <c r="D75" s="9">
+      <c r="D75" s="8">
         <v>46197.49537962963</v>
       </c>
-      <c r="E75" s="10" t="s">
+      <c r="E75" s="9" t="s">
         <v>251</v>
       </c>
-      <c r="F75" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G75" s="10" t="s">
+      <c r="F75" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G75" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="H75" s="10" t="s">
+      <c r="H75" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="I75" s="9">
+      <c r="I75" s="8">
         <v>46276</v>
       </c>
-      <c r="J75" s="9">
+      <c r="J75" s="8">
         <v>46295</v>
       </c>
-      <c r="K75" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L75" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M75" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N75" s="10" t="s">
+      <c r="K75" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L75" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M75" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N75" s="9" t="s">
         <v>248</v>
       </c>
-      <c r="O75" s="10" t="s">
+      <c r="O75" s="9" t="s">
         <v>252</v>
       </c>
-      <c r="P75" s="10" t="s">
+      <c r="P75" s="9" t="s">
         <v>248</v>
       </c>
-      <c r="Q75" s="9">
+      <c r="Q75" s="8">
         <v>46276</v>
       </c>
-      <c r="R75" s="9">
+      <c r="R75" s="8">
         <v>46295</v>
       </c>
-      <c r="S75" s="7" t="s">
+      <c r="S75" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="T75" s="9">
+        <v>1</v>
+      </c>
+      <c r="U75" s="10" t="s">
         <v>33</v>
-      </c>
-      <c r="T75" s="10">
-        <v>1</v>
-      </c>
-      <c r="U75" s="7" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
@@ -6006,68 +6010,68 @@
       <c r="U76" s="6"/>
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A77" s="8" t="s">
+      <c r="A77" s="7" t="s">
         <v>255</v>
       </c>
-      <c r="B77" s="9">
+      <c r="B77" s="8">
         <v>46169.55893170139</v>
       </c>
-      <c r="C77" s="9">
+      <c r="C77" s="8">
         <v>46197.49516923611</v>
       </c>
-      <c r="D77" s="9">
+      <c r="D77" s="8">
         <v>46197.495185555556</v>
       </c>
-      <c r="E77" s="10" t="s">
+      <c r="E77" s="9" t="s">
         <v>256</v>
       </c>
-      <c r="F77" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G77" s="10" t="s">
+      <c r="F77" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G77" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="H77" s="10" t="s">
+      <c r="H77" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="I77" s="9">
+      <c r="I77" s="8">
         <v>46296</v>
       </c>
-      <c r="J77" s="9">
+      <c r="J77" s="8">
         <v>46297</v>
       </c>
-      <c r="K77" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L77" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M77" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N77" s="10" t="s">
+      <c r="K77" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L77" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M77" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N77" s="9" t="s">
         <v>248</v>
       </c>
-      <c r="O77" s="10" t="s">
+      <c r="O77" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="P77" s="10" t="s">
+      <c r="P77" s="9" t="s">
         <v>248</v>
       </c>
-      <c r="Q77" s="9">
+      <c r="Q77" s="8">
         <v>46296</v>
       </c>
-      <c r="R77" s="9">
+      <c r="R77" s="8">
         <v>46297</v>
       </c>
-      <c r="S77" s="7" t="s">
+      <c r="S77" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="T77" s="9">
+        <v>1</v>
+      </c>
+      <c r="U77" s="10" t="s">
         <v>33</v>
-      </c>
-      <c r="T77" s="10">
-        <v>1</v>
-      </c>
-      <c r="U77" s="7" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
@@ -6081,7 +6085,7 @@
         <v>46197.4951540162</v>
       </c>
       <c r="D78" s="5">
-        <v>46197.49515607639</v>
+        <v>46200.819215173615</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>174</v>
@@ -6126,66 +6130,66 @@
       <c r="U78" s="6"/>
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A79" s="8" t="s">
+      <c r="A79" s="7" t="s">
         <v>260</v>
       </c>
-      <c r="B79" s="9">
+      <c r="B79" s="8">
         <v>46169.558869560184</v>
       </c>
-      <c r="C79" s="10"/>
-      <c r="D79" s="9">
+      <c r="C79" s="9"/>
+      <c r="D79" s="8">
         <v>46169.621266111106</v>
       </c>
-      <c r="E79" s="10" t="s">
+      <c r="E79" s="9" t="s">
         <v>261</v>
       </c>
-      <c r="F79" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G79" s="10" t="s">
+      <c r="F79" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G79" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="H79" s="10" t="s">
+      <c r="H79" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="I79" s="9">
+      <c r="I79" s="8">
         <v>46328</v>
       </c>
-      <c r="J79" s="9">
+      <c r="J79" s="8">
         <v>46328</v>
       </c>
-      <c r="K79" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L79" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M79" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N79" s="10" t="s">
+      <c r="K79" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L79" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M79" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N79" s="9" t="s">
         <v>248</v>
       </c>
-      <c r="O79" s="10" t="s">
+      <c r="O79" s="9" t="s">
         <v>193</v>
       </c>
-      <c r="P79" s="10" t="s">
+      <c r="P79" s="9" t="s">
         <v>248</v>
       </c>
-      <c r="Q79" s="9">
+      <c r="Q79" s="8">
         <v>46328</v>
       </c>
-      <c r="R79" s="9">
+      <c r="R79" s="8">
         <v>46328</v>
       </c>
-      <c r="S79" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T79" s="10">
+      <c r="S79" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="T79" s="9">
         <v>0</v>
       </c>
-      <c r="U79" s="12" t="s">
-        <v>101</v>
+      <c r="U79" s="11" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
@@ -6197,7 +6201,7 @@
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46182.759876909724</v>
+        <v>46200.81967626157</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>193</v>
@@ -6242,66 +6246,66 @@
       <c r="U80" s="6"/>
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A81" s="8" t="s">
+      <c r="A81" s="7" t="s">
         <v>265</v>
       </c>
-      <c r="B81" s="9">
+      <c r="B81" s="8">
         <v>46169.5589025463</v>
       </c>
-      <c r="C81" s="10"/>
-      <c r="D81" s="9">
+      <c r="C81" s="9"/>
+      <c r="D81" s="8">
         <v>46169.62135181713</v>
       </c>
-      <c r="E81" s="10" t="s">
+      <c r="E81" s="9" t="s">
         <v>266</v>
       </c>
-      <c r="F81" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G81" s="10" t="s">
+      <c r="F81" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G81" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="H81" s="10" t="s">
+      <c r="H81" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="I81" s="9">
+      <c r="I81" s="8">
         <v>46329</v>
       </c>
-      <c r="J81" s="9">
+      <c r="J81" s="8">
         <v>46329</v>
       </c>
-      <c r="K81" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L81" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M81" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N81" s="10" t="s">
+      <c r="K81" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L81" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M81" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N81" s="9" t="s">
         <v>248</v>
       </c>
-      <c r="O81" s="10" t="s">
+      <c r="O81" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="P81" s="10" t="s">
+      <c r="P81" s="9" t="s">
         <v>248</v>
       </c>
-      <c r="Q81" s="9">
+      <c r="Q81" s="8">
         <v>46329</v>
       </c>
-      <c r="R81" s="9">
+      <c r="R81" s="8">
         <v>46329</v>
       </c>
-      <c r="S81" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T81" s="10">
+      <c r="S81" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="T81" s="9">
         <v>0</v>
       </c>
-      <c r="U81" s="12" t="s">
-        <v>101</v>
+      <c r="U81" s="11" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
@@ -6313,7 +6317,7 @@
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46182.759877442135</v>
+        <v>46200.81969234954</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>174</v>
@@ -6358,66 +6362,66 @@
       <c r="U82" s="6"/>
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A83" s="8" t="s">
+      <c r="A83" s="7" t="s">
         <v>270</v>
       </c>
-      <c r="B83" s="9">
+      <c r="B83" s="8">
         <v>46169.55900443287</v>
       </c>
-      <c r="C83" s="10"/>
-      <c r="D83" s="9">
+      <c r="C83" s="9"/>
+      <c r="D83" s="8">
         <v>46169.621444178236</v>
       </c>
-      <c r="E83" s="10" t="s">
+      <c r="E83" s="9" t="s">
         <v>271</v>
       </c>
-      <c r="F83" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G83" s="10" t="s">
+      <c r="F83" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G83" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="H83" s="10" t="s">
+      <c r="H83" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="I83" s="9">
+      <c r="I83" s="8">
         <v>46330</v>
       </c>
-      <c r="J83" s="9">
+      <c r="J83" s="8">
         <v>46330</v>
       </c>
-      <c r="K83" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L83" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M83" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N83" s="10" t="s">
+      <c r="K83" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L83" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M83" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N83" s="9" t="s">
         <v>248</v>
       </c>
-      <c r="O83" s="10" t="s">
+      <c r="O83" s="9" t="s">
         <v>193</v>
       </c>
-      <c r="P83" s="10" t="s">
+      <c r="P83" s="9" t="s">
         <v>248</v>
       </c>
-      <c r="Q83" s="9">
+      <c r="Q83" s="8">
         <v>46330</v>
       </c>
-      <c r="R83" s="9">
+      <c r="R83" s="8">
         <v>46330</v>
       </c>
-      <c r="S83" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T83" s="10">
+      <c r="S83" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="T83" s="9">
         <v>0</v>
       </c>
-      <c r="U83" s="12" t="s">
-        <v>101</v>
+      <c r="U83" s="11" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
@@ -6474,66 +6478,66 @@
       <c r="U84" s="6"/>
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A85" s="8" t="s">
+      <c r="A85" s="7" t="s">
         <v>274</v>
       </c>
-      <c r="B85" s="9">
+      <c r="B85" s="8">
         <v>46169.55904462963</v>
       </c>
-      <c r="C85" s="10"/>
-      <c r="D85" s="9">
+      <c r="C85" s="9"/>
+      <c r="D85" s="8">
         <v>46169.62153172454</v>
       </c>
-      <c r="E85" s="10" t="s">
+      <c r="E85" s="9" t="s">
         <v>275</v>
       </c>
-      <c r="F85" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G85" s="10" t="s">
+      <c r="F85" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G85" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="H85" s="10" t="s">
+      <c r="H85" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="I85" s="9">
+      <c r="I85" s="8">
         <v>46332</v>
       </c>
-      <c r="J85" s="9">
+      <c r="J85" s="8">
         <v>46332</v>
       </c>
-      <c r="K85" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L85" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M85" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N85" s="10" t="s">
+      <c r="K85" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L85" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M85" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N85" s="9" t="s">
         <v>248</v>
       </c>
-      <c r="O85" s="10" t="s">
+      <c r="O85" s="9" t="s">
         <v>193</v>
       </c>
-      <c r="P85" s="10" t="s">
+      <c r="P85" s="9" t="s">
         <v>276</v>
       </c>
-      <c r="Q85" s="9">
+      <c r="Q85" s="8">
         <v>46332</v>
       </c>
-      <c r="R85" s="9">
+      <c r="R85" s="8">
         <v>46332</v>
       </c>
-      <c r="S85" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T85" s="10">
+      <c r="S85" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="T85" s="9">
         <v>0</v>
       </c>
-      <c r="U85" s="12" t="s">
-        <v>101</v>
+      <c r="U85" s="11" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
@@ -6590,51 +6594,51 @@
       <c r="U86" s="6"/>
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A87" s="8" t="s">
+      <c r="A87" s="7" t="s">
         <v>279</v>
       </c>
-      <c r="B87" s="9">
+      <c r="B87" s="8">
         <v>46169.55907484954</v>
       </c>
-      <c r="C87" s="10"/>
-      <c r="D87" s="9">
+      <c r="C87" s="9"/>
+      <c r="D87" s="8">
         <v>46197.85962290509</v>
       </c>
-      <c r="E87" s="10" t="s">
+      <c r="E87" s="9" t="s">
         <v>280</v>
       </c>
-      <c r="F87" s="10" t="s">
+      <c r="F87" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="G87" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H87" s="10"/>
-      <c r="I87" s="10"/>
-      <c r="J87" s="10"/>
-      <c r="K87" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L87" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M87" s="10" t="s">
+      <c r="G87" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="H87" s="9"/>
+      <c r="I87" s="9"/>
+      <c r="J87" s="9"/>
+      <c r="K87" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L87" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M87" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="N87" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="O87" s="10" t="s">
+      <c r="N87" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="O87" s="9" t="s">
         <v>281</v>
       </c>
-      <c r="P87" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q87" s="10"/>
-      <c r="R87" s="10"/>
-      <c r="S87" s="10"/>
-      <c r="T87" s="10"/>
-      <c r="U87" s="10"/>
+      <c r="P87" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q87" s="9"/>
+      <c r="R87" s="9"/>
+      <c r="S87" s="9"/>
+      <c r="T87" s="9"/>
+      <c r="U87" s="9"/>
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
@@ -6689,68 +6693,68 @@
       <c r="R88" s="5">
         <v>46335</v>
       </c>
-      <c r="S88" s="7" t="s">
-        <v>33</v>
+      <c r="S88" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T88" s="6">
         <v>0</v>
       </c>
-      <c r="U88" s="12" t="s">
-        <v>101</v>
+      <c r="U88" s="11" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A89" s="8" t="s">
+      <c r="A89" s="7" t="s">
         <v>286</v>
       </c>
-      <c r="B89" s="9">
+      <c r="B89" s="8">
         <v>46169.55908684028</v>
       </c>
-      <c r="C89" s="10"/>
-      <c r="D89" s="9">
+      <c r="C89" s="9"/>
+      <c r="D89" s="8">
         <v>46169.62159425926</v>
       </c>
-      <c r="E89" s="10" t="s">
+      <c r="E89" s="9" t="s">
         <v>193</v>
       </c>
-      <c r="F89" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G89" s="10" t="s">
+      <c r="F89" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G89" s="9" t="s">
         <v>284</v>
       </c>
-      <c r="H89" s="10" t="s">
+      <c r="H89" s="9" t="s">
         <v>285</v>
       </c>
-      <c r="I89" s="9">
+      <c r="I89" s="8">
         <v>46335</v>
       </c>
-      <c r="J89" s="9">
+      <c r="J89" s="8">
         <v>46335</v>
       </c>
-      <c r="K89" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L89" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M89" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N89" s="10" t="s">
+      <c r="K89" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L89" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M89" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N89" s="9" t="s">
         <v>283</v>
       </c>
-      <c r="O89" s="10" t="s">
+      <c r="O89" s="9" t="s">
         <v>193</v>
       </c>
-      <c r="P89" s="10" t="s">
+      <c r="P89" s="9" t="s">
         <v>287</v>
       </c>
-      <c r="Q89" s="10"/>
-      <c r="R89" s="10"/>
-      <c r="S89" s="10"/>
-      <c r="T89" s="10"/>
-      <c r="U89" s="10"/>
+      <c r="Q89" s="9"/>
+      <c r="R89" s="9"/>
+      <c r="S89" s="9"/>
+      <c r="T89" s="9"/>
+      <c r="U89" s="9"/>
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
@@ -6805,68 +6809,68 @@
       <c r="R90" s="5">
         <v>46336</v>
       </c>
-      <c r="S90" s="7" t="s">
-        <v>33</v>
+      <c r="S90" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T90" s="6">
         <v>0</v>
       </c>
-      <c r="U90" s="12" t="s">
-        <v>101</v>
+      <c r="U90" s="11" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A91" s="8" t="s">
+      <c r="A91" s="7" t="s">
         <v>290</v>
       </c>
-      <c r="B91" s="9">
+      <c r="B91" s="8">
         <v>46169.55919113426</v>
       </c>
-      <c r="C91" s="10"/>
-      <c r="D91" s="9">
+      <c r="C91" s="9"/>
+      <c r="D91" s="8">
         <v>46169.62169328704</v>
       </c>
-      <c r="E91" s="10" t="s">
+      <c r="E91" s="9" t="s">
         <v>193</v>
       </c>
-      <c r="F91" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G91" s="10" t="s">
+      <c r="F91" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G91" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="H91" s="10" t="s">
+      <c r="H91" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="I91" s="9">
+      <c r="I91" s="8">
         <v>46336</v>
       </c>
-      <c r="J91" s="9">
+      <c r="J91" s="8">
         <v>46336</v>
       </c>
-      <c r="K91" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L91" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M91" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N91" s="10" t="s">
+      <c r="K91" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L91" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M91" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N91" s="9" t="s">
         <v>289</v>
       </c>
-      <c r="O91" s="10" t="s">
+      <c r="O91" s="9" t="s">
         <v>193</v>
       </c>
-      <c r="P91" s="10" t="s">
+      <c r="P91" s="9" t="s">
         <v>291</v>
       </c>
-      <c r="Q91" s="10"/>
-      <c r="R91" s="10"/>
-      <c r="S91" s="10"/>
-      <c r="T91" s="10"/>
-      <c r="U91" s="10"/>
+      <c r="Q91" s="9"/>
+      <c r="R91" s="9"/>
+      <c r="S91" s="9"/>
+      <c r="T91" s="9"/>
+      <c r="U91" s="9"/>
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
@@ -6923,70 +6927,70 @@
       <c r="R92" s="5">
         <v>46337</v>
       </c>
-      <c r="S92" s="7" t="s">
-        <v>33</v>
+      <c r="S92" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T92" s="6">
         <v>1</v>
       </c>
-      <c r="U92" s="11" t="s">
-        <v>92</v>
+      <c r="U92" s="12" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A93" s="8" t="s">
+      <c r="A93" s="7" t="s">
         <v>294</v>
       </c>
-      <c r="B93" s="9">
+      <c r="B93" s="8">
         <v>46169.559243842596</v>
       </c>
-      <c r="C93" s="9">
+      <c r="C93" s="8">
         <v>46197.859803263884</v>
       </c>
-      <c r="D93" s="9">
+      <c r="D93" s="8">
         <v>46197.85980471065</v>
       </c>
-      <c r="E93" s="10" t="s">
+      <c r="E93" s="9" t="s">
         <v>193</v>
       </c>
-      <c r="F93" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G93" s="10" t="s">
+      <c r="F93" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G93" s="9" t="s">
         <v>219</v>
       </c>
-      <c r="H93" s="10" t="s">
+      <c r="H93" s="9" t="s">
         <v>220</v>
       </c>
-      <c r="I93" s="9">
+      <c r="I93" s="8">
         <v>46337</v>
       </c>
-      <c r="J93" s="9">
+      <c r="J93" s="8">
         <v>46337</v>
       </c>
-      <c r="K93" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L93" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M93" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N93" s="10" t="s">
+      <c r="K93" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L93" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M93" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N93" s="9" t="s">
         <v>293</v>
       </c>
-      <c r="O93" s="10" t="s">
+      <c r="O93" s="9" t="s">
         <v>193</v>
       </c>
-      <c r="P93" s="10" t="s">
+      <c r="P93" s="9" t="s">
         <v>295</v>
       </c>
-      <c r="Q93" s="10"/>
-      <c r="R93" s="10"/>
-      <c r="S93" s="10"/>
-      <c r="T93" s="10"/>
-      <c r="U93" s="10"/>
+      <c r="Q93" s="9"/>
+      <c r="R93" s="9"/>
+      <c r="S93" s="9"/>
+      <c r="T93" s="9"/>
+      <c r="U93" s="9"/>
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
@@ -7041,68 +7045,68 @@
       <c r="R94" s="5">
         <v>46338</v>
       </c>
-      <c r="S94" s="7" t="s">
-        <v>33</v>
+      <c r="S94" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T94" s="6">
         <v>0</v>
       </c>
-      <c r="U94" s="12" t="s">
-        <v>101</v>
+      <c r="U94" s="11" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A95" s="8" t="s">
+      <c r="A95" s="7" t="s">
         <v>300</v>
       </c>
-      <c r="B95" s="9">
+      <c r="B95" s="8">
         <v>46169.55930180555</v>
       </c>
-      <c r="C95" s="10"/>
-      <c r="D95" s="9">
+      <c r="C95" s="9"/>
+      <c r="D95" s="8">
         <v>46197.859809629634</v>
       </c>
-      <c r="E95" s="10" t="s">
+      <c r="E95" s="9" t="s">
         <v>298</v>
       </c>
-      <c r="F95" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G95" s="10" t="s">
+      <c r="F95" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G95" s="9" t="s">
         <v>219</v>
       </c>
-      <c r="H95" s="10" t="s">
+      <c r="H95" s="9" t="s">
         <v>220</v>
       </c>
-      <c r="I95" s="9">
+      <c r="I95" s="8">
         <v>46338</v>
       </c>
-      <c r="J95" s="9">
+      <c r="J95" s="8">
         <v>46338</v>
       </c>
-      <c r="K95" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L95" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M95" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N95" s="10" t="s">
+      <c r="K95" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L95" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M95" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N95" s="9" t="s">
         <v>297</v>
       </c>
-      <c r="O95" s="10" t="s">
+      <c r="O95" s="9" t="s">
         <v>193</v>
       </c>
-      <c r="P95" s="10" t="s">
+      <c r="P95" s="9" t="s">
         <v>297</v>
       </c>
-      <c r="Q95" s="10"/>
-      <c r="R95" s="10"/>
-      <c r="S95" s="10"/>
-      <c r="T95" s="10"/>
-      <c r="U95" s="10"/>
+      <c r="Q95" s="9"/>
+      <c r="R95" s="9"/>
+      <c r="S95" s="9"/>
+      <c r="T95" s="9"/>
+      <c r="U95" s="9"/>
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
@@ -7152,66 +7156,66 @@
       <c r="U96" s="6"/>
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A97" s="8" t="s">
+      <c r="A97" s="7" t="s">
         <v>304</v>
       </c>
-      <c r="B97" s="9">
+      <c r="B97" s="8">
         <v>46169.55939094907</v>
       </c>
-      <c r="C97" s="10"/>
-      <c r="D97" s="9">
+      <c r="C97" s="9"/>
+      <c r="D97" s="8">
         <v>46169.621991215274</v>
       </c>
-      <c r="E97" s="10" t="s">
+      <c r="E97" s="9" t="s">
         <v>305</v>
       </c>
-      <c r="F97" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G97" s="10" t="s">
+      <c r="F97" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G97" s="9" t="s">
         <v>306</v>
       </c>
-      <c r="H97" s="10" t="s">
+      <c r="H97" s="9" t="s">
         <v>307</v>
       </c>
-      <c r="I97" s="9">
+      <c r="I97" s="8">
         <v>46339</v>
       </c>
-      <c r="J97" s="9">
+      <c r="J97" s="8">
         <v>46349</v>
       </c>
-      <c r="K97" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L97" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M97" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N97" s="10" t="s">
+      <c r="K97" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L97" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M97" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N97" s="9" t="s">
         <v>302</v>
       </c>
-      <c r="O97" s="10" t="s">
+      <c r="O97" s="9" t="s">
         <v>297</v>
       </c>
-      <c r="P97" s="10" t="s">
+      <c r="P97" s="9" t="s">
         <v>302</v>
       </c>
-      <c r="Q97" s="9">
+      <c r="Q97" s="8">
         <v>46339</v>
       </c>
-      <c r="R97" s="9">
+      <c r="R97" s="8">
         <v>46349</v>
       </c>
-      <c r="S97" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T97" s="10">
+      <c r="S97" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="T97" s="9">
         <v>0</v>
       </c>
-      <c r="U97" s="12" t="s">
-        <v>101</v>
+      <c r="U97" s="11" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
@@ -7267,14 +7271,14 @@
       <c r="R98" s="5">
         <v>46349</v>
       </c>
-      <c r="S98" s="7" t="s">
-        <v>33</v>
+      <c r="S98" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T98" s="6">
         <v>0</v>
       </c>
-      <c r="U98" s="12" t="s">
-        <v>101</v>
+      <c r="U98" s="11" t="s">
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001557 - ATACAMA KOZAN OT4340.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4340.xlsx
@@ -5851,7 +5851,7 @@
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46197.49537680556</v>
+        <v>46204.879935543984</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>248</v>
@@ -6085,7 +6085,7 @@
         <v>46197.4951540162</v>
       </c>
       <c r="D78" s="5">
-        <v>46200.819215173615</v>
+        <v>46204.879924837966</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>174</v>
@@ -6136,9 +6136,11 @@
       <c r="B79" s="8">
         <v>46169.558869560184</v>
       </c>
-      <c r="C79" s="9"/>
+      <c r="C79" s="8">
+        <v>46204.87979715278</v>
+      </c>
       <c r="D79" s="8">
-        <v>46169.621266111106</v>
+        <v>46204.87981377315</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>261</v>
@@ -6186,10 +6188,10 @@
         <v>32</v>
       </c>
       <c r="T79" s="9">
-        <v>0</v>
-      </c>
-      <c r="U79" s="11" t="s">
-        <v>100</v>
+        <v>1</v>
+      </c>
+      <c r="U79" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
@@ -6199,9 +6201,11 @@
       <c r="B80" s="5">
         <v>46169.55887296297</v>
       </c>
-      <c r="C80" s="6"/>
+      <c r="C80" s="5">
+        <v>46204.87978053241</v>
+      </c>
       <c r="D80" s="5">
-        <v>46200.81967626157</v>
+        <v>46204.87978310185</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>193</v>
@@ -6252,9 +6256,11 @@
       <c r="B81" s="8">
         <v>46169.5589025463</v>
       </c>
-      <c r="C81" s="9"/>
+      <c r="C81" s="8">
+        <v>46204.87992821759</v>
+      </c>
       <c r="D81" s="8">
-        <v>46169.62135181713</v>
+        <v>46204.880057013885</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>266</v>
@@ -6302,10 +6308,10 @@
         <v>32</v>
       </c>
       <c r="T81" s="9">
-        <v>0</v>
-      </c>
-      <c r="U81" s="11" t="s">
-        <v>100</v>
+        <v>1</v>
+      </c>
+      <c r="U81" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
@@ -6315,9 +6321,11 @@
       <c r="B82" s="5">
         <v>46169.55890609954</v>
       </c>
-      <c r="C82" s="6"/>
+      <c r="C82" s="5">
+        <v>46204.87991554398</v>
+      </c>
       <c r="D82" s="5">
-        <v>46200.81969234954</v>
+        <v>46204.87991711806</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>174</v>
@@ -6370,7 +6378,7 @@
       </c>
       <c r="C83" s="9"/>
       <c r="D83" s="8">
-        <v>46169.621444178236</v>
+        <v>46204.88038796296</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>271</v>

--- a/data/50001557 - ATACAMA KOZAN OT4340.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4340.xlsx
@@ -1605,13 +1605,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46169.55800045139</v>
+        <v>46169.39133378472</v>
       </c>
       <c r="C4" s="5">
-        <v>46181.62345784722</v>
+        <v>46181.45679118056</v>
       </c>
       <c r="D4" s="5">
-        <v>46200.818239016204</v>
+        <v>46200.65157234954</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1654,13 +1654,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46169.5581362963</v>
+        <v>46169.39146962963</v>
       </c>
       <c r="C5" s="8">
-        <v>46181.6234662037</v>
+        <v>46181.45679953704</v>
       </c>
       <c r="D5" s="8">
-        <v>46181.623480486116</v>
+        <v>46181.456813819445</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1717,13 +1717,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46169.55813974537</v>
+        <v>46169.39147307871</v>
       </c>
       <c r="C6" s="5">
-        <v>46181.62347399305</v>
+        <v>46181.45680732639</v>
       </c>
       <c r="D6" s="5">
-        <v>46181.624255925926</v>
+        <v>46181.457589259255</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -1780,13 +1780,13 @@
         <v>36</v>
       </c>
       <c r="B7" s="8">
-        <v>46169.55814432871</v>
+        <v>46169.39147766204</v>
       </c>
       <c r="C7" s="8">
-        <v>46181.62348018518</v>
+        <v>46181.45681351852</v>
       </c>
       <c r="D7" s="8">
-        <v>46181.62349788194</v>
+        <v>46181.45683121528</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>37</v>
@@ -1843,13 +1843,13 @@
         <v>39</v>
       </c>
       <c r="B8" s="5">
-        <v>46169.55814774305</v>
+        <v>46169.39148107639</v>
       </c>
       <c r="C8" s="5">
-        <v>46181.623485833334</v>
+        <v>46181.45681916666</v>
       </c>
       <c r="D8" s="5">
-        <v>46181.62350184028</v>
+        <v>46181.45683517361</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>40</v>
@@ -1906,13 +1906,13 @@
         <v>43</v>
       </c>
       <c r="B9" s="8">
-        <v>46169.55815164352</v>
+        <v>46169.39148497685</v>
       </c>
       <c r="C9" s="8">
-        <v>46181.62349162037</v>
+        <v>46181.456824953704</v>
       </c>
       <c r="D9" s="8">
-        <v>46181.62350840278</v>
+        <v>46181.456841736115</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>44</v>
@@ -1969,13 +1969,13 @@
         <v>46</v>
       </c>
       <c r="B10" s="5">
-        <v>46169.55800939815</v>
+        <v>46169.391342731484</v>
       </c>
       <c r="C10" s="5">
-        <v>46197.83890001157</v>
+        <v>46197.67223334491</v>
       </c>
       <c r="D10" s="5">
-        <v>46197.83892112269</v>
+        <v>46197.67225445602</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>47</v>
@@ -2022,13 +2022,13 @@
         <v>48</v>
       </c>
       <c r="B11" s="8">
-        <v>46169.558185671296</v>
+        <v>46169.391519004625</v>
       </c>
       <c r="C11" s="8">
-        <v>46181.624365104166</v>
+        <v>46181.4576984375</v>
       </c>
       <c r="D11" s="8">
-        <v>46196.80567361111</v>
+        <v>46196.639006944446</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>49</v>
@@ -2087,13 +2087,13 @@
         <v>54</v>
       </c>
       <c r="B12" s="5">
-        <v>46169.558191840275</v>
+        <v>46169.39152517361</v>
       </c>
       <c r="C12" s="5">
-        <v>46181.62437706019</v>
+        <v>46181.457710393515</v>
       </c>
       <c r="D12" s="5">
-        <v>46196.80567332176</v>
+        <v>46196.639006655096</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>55</v>
@@ -2152,13 +2152,13 @@
         <v>58</v>
       </c>
       <c r="B13" s="8">
-        <v>46169.558197418984</v>
+        <v>46169.39153075231</v>
       </c>
       <c r="C13" s="8">
-        <v>46181.624389537035</v>
+        <v>46181.45772287037</v>
       </c>
       <c r="D13" s="8">
-        <v>46196.80567320602</v>
+        <v>46196.63900653935</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>59</v>
@@ -2217,13 +2217,13 @@
         <v>61</v>
       </c>
       <c r="B14" s="5">
-        <v>46169.558013773145</v>
+        <v>46169.39134710648</v>
       </c>
       <c r="C14" s="5">
-        <v>46190.64415828703</v>
+        <v>46190.477491620375</v>
       </c>
       <c r="D14" s="5">
-        <v>46190.64417138889</v>
+        <v>46190.47750472222</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>62</v>
@@ -2270,13 +2270,13 @@
         <v>64</v>
       </c>
       <c r="B15" s="8">
-        <v>46169.558213564815</v>
+        <v>46169.39154689814</v>
       </c>
       <c r="C15" s="8">
-        <v>46181.62444696759</v>
+        <v>46181.45778030093</v>
       </c>
       <c r="D15" s="8">
-        <v>46181.62446385417</v>
+        <v>46181.4577971875</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>65</v>
@@ -2335,13 +2335,13 @@
         <v>67</v>
       </c>
       <c r="B16" s="5">
-        <v>46169.558224479166</v>
+        <v>46169.3915578125</v>
       </c>
       <c r="C16" s="5">
-        <v>46181.62445372685</v>
+        <v>46181.457787060186</v>
       </c>
       <c r="D16" s="5">
-        <v>46181.62447002315</v>
+        <v>46181.45780335648</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>68</v>
@@ -2400,13 +2400,13 @@
         <v>70</v>
       </c>
       <c r="B17" s="8">
-        <v>46169.558230821756</v>
+        <v>46169.39156415509</v>
       </c>
       <c r="C17" s="8">
-        <v>46183.906516585645</v>
+        <v>46183.73984991898</v>
       </c>
       <c r="D17" s="8">
-        <v>46183.90651931713</v>
+        <v>46183.73985265046</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>71</v>
@@ -2465,13 +2465,13 @@
         <v>74</v>
       </c>
       <c r="B18" s="5">
-        <v>46169.55823646991</v>
+        <v>46169.391569803236</v>
       </c>
       <c r="C18" s="5">
-        <v>46183.90663498842</v>
+        <v>46183.73996832176</v>
       </c>
       <c r="D18" s="5">
-        <v>46183.90665107639</v>
+        <v>46183.73998440972</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>75</v>
@@ -2530,13 +2530,13 @@
         <v>80</v>
       </c>
       <c r="B19" s="8">
-        <v>46169.55824171296</v>
+        <v>46169.39157504629</v>
       </c>
       <c r="C19" s="8">
-        <v>46183.906646539355</v>
+        <v>46183.739979872684</v>
       </c>
       <c r="D19" s="8">
-        <v>46183.90666170139</v>
+        <v>46183.73999503472</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>81</v>
@@ -2595,13 +2595,13 @@
         <v>83</v>
       </c>
       <c r="B20" s="5">
-        <v>46169.55824574074</v>
+        <v>46169.39157907407</v>
       </c>
       <c r="C20" s="5">
-        <v>46190.644140034725</v>
+        <v>46190.47747336805</v>
       </c>
       <c r="D20" s="5">
-        <v>46190.64415820602</v>
+        <v>46190.47749153935</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>84</v>
@@ -2660,13 +2660,13 @@
         <v>86</v>
       </c>
       <c r="B21" s="8">
-        <v>46169.55825006944</v>
+        <v>46169.39158340278</v>
       </c>
       <c r="C21" s="8">
-        <v>46183.90733957176</v>
+        <v>46183.74067290509</v>
       </c>
       <c r="D21" s="8">
-        <v>46183.90735393518</v>
+        <v>46183.74068726852</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>87</v>
@@ -2725,13 +2725,13 @@
         <v>89</v>
       </c>
       <c r="B22" s="5">
-        <v>46169.55801826389</v>
+        <v>46169.39135159722</v>
       </c>
       <c r="C22" s="5">
-        <v>46200.818312083335</v>
+        <v>46200.65164541667</v>
       </c>
       <c r="D22" s="5">
-        <v>46200.818425798614</v>
+        <v>46200.65175913194</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>90</v>
@@ -2774,13 +2774,13 @@
         <v>92</v>
       </c>
       <c r="B23" s="8">
-        <v>46169.558301956014</v>
+        <v>46169.39163528935</v>
       </c>
       <c r="C23" s="8">
-        <v>46182.67339038194</v>
+        <v>46182.506723715276</v>
       </c>
       <c r="D23" s="8">
-        <v>46200.81833380787</v>
+        <v>46200.6516671412</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>93</v>
@@ -2839,13 +2839,13 @@
         <v>97</v>
       </c>
       <c r="B24" s="5">
-        <v>46169.558306516206</v>
+        <v>46169.391639849535</v>
       </c>
       <c r="C24" s="5">
-        <v>46195.69079006945</v>
+        <v>46195.52412340278</v>
       </c>
       <c r="D24" s="5">
-        <v>46195.69079224537</v>
+        <v>46195.524125578704</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>98</v>
@@ -2900,13 +2900,13 @@
         <v>101</v>
       </c>
       <c r="B25" s="8">
-        <v>46169.55831137732</v>
+        <v>46169.391644710646</v>
       </c>
       <c r="C25" s="8">
-        <v>46182.67337415509</v>
+        <v>46182.50670748843</v>
       </c>
       <c r="D25" s="8">
-        <v>46195.690800474535</v>
+        <v>46195.52413380787</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>102</v>
@@ -2961,13 +2961,13 @@
         <v>104</v>
       </c>
       <c r="B26" s="5">
-        <v>46169.55831605324</v>
+        <v>46169.39164938657</v>
       </c>
       <c r="C26" s="5">
-        <v>46184.73646410879</v>
+        <v>46184.569797442135</v>
       </c>
       <c r="D26" s="5">
-        <v>46184.73661180555</v>
+        <v>46184.569945138894</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>105</v>
@@ -3026,13 +3026,13 @@
         <v>107</v>
       </c>
       <c r="B27" s="8">
-        <v>46169.55832063657</v>
+        <v>46169.391653969906</v>
       </c>
       <c r="C27" s="8">
-        <v>46184.736407812496</v>
+        <v>46184.56974114584</v>
       </c>
       <c r="D27" s="8">
-        <v>46184.7364097338</v>
+        <v>46184.56974306713</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>108</v>
@@ -3087,13 +3087,13 @@
         <v>110</v>
       </c>
       <c r="B28" s="5">
-        <v>46169.55832539352</v>
+        <v>46169.39165872685</v>
       </c>
       <c r="C28" s="5">
-        <v>46184.73644800926</v>
+        <v>46184.569781342594</v>
       </c>
       <c r="D28" s="5">
-        <v>46184.736449375</v>
+        <v>46184.569782708335</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>111</v>
@@ -3148,13 +3148,13 @@
         <v>113</v>
       </c>
       <c r="B29" s="8">
-        <v>46169.55833006944</v>
+        <v>46169.39166340278</v>
       </c>
       <c r="C29" s="8">
-        <v>46182.67350289352</v>
+        <v>46182.50683622685</v>
       </c>
       <c r="D29" s="8">
-        <v>46200.81836952546</v>
+        <v>46200.6517028588</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>114</v>
@@ -3213,13 +3213,13 @@
         <v>116</v>
       </c>
       <c r="B30" s="5">
-        <v>46169.55833486111</v>
+        <v>46169.39166819444</v>
       </c>
       <c r="C30" s="5">
-        <v>46195.69066097222</v>
+        <v>46195.52399430556</v>
       </c>
       <c r="D30" s="5">
-        <v>46195.69066259259</v>
+        <v>46195.52399592593</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>117</v>
@@ -3274,13 +3274,13 @@
         <v>119</v>
       </c>
       <c r="B31" s="8">
-        <v>46169.5583402662</v>
+        <v>46169.39167359954</v>
       </c>
       <c r="C31" s="8">
-        <v>46182.67343230324</v>
+        <v>46182.50676563657</v>
       </c>
       <c r="D31" s="8">
-        <v>46195.69066760417</v>
+        <v>46195.5240009375</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>120</v>
@@ -3335,13 +3335,13 @@
         <v>122</v>
       </c>
       <c r="B32" s="5">
-        <v>46169.55834503472</v>
+        <v>46169.391678368054</v>
       </c>
       <c r="C32" s="5">
-        <v>46195.6905771875</v>
+        <v>46195.52391052083</v>
       </c>
       <c r="D32" s="5">
-        <v>46195.6906680324</v>
+        <v>46195.524001365746</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>123</v>
@@ -3396,13 +3396,13 @@
         <v>125</v>
       </c>
       <c r="B33" s="8">
-        <v>46169.55836335648</v>
+        <v>46169.39169668981</v>
       </c>
       <c r="C33" s="8">
-        <v>46184.532628437504</v>
+        <v>46184.36596177083</v>
       </c>
       <c r="D33" s="8">
-        <v>46184.532641875005</v>
+        <v>46184.36597520833</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>126</v>
@@ -3461,13 +3461,13 @@
         <v>130</v>
       </c>
       <c r="B34" s="5">
-        <v>46169.558367986116</v>
+        <v>46169.391701319444</v>
       </c>
       <c r="C34" s="5">
-        <v>46184.53245732639</v>
+        <v>46184.36579065972</v>
       </c>
       <c r="D34" s="5">
-        <v>46184.53245875</v>
+        <v>46184.365792083336</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>131</v>
@@ -3522,13 +3522,13 @@
         <v>133</v>
       </c>
       <c r="B35" s="8">
-        <v>46169.55837292824</v>
+        <v>46169.39170626157</v>
       </c>
       <c r="C35" s="8">
-        <v>46184.532613668984</v>
+        <v>46184.36594700231</v>
       </c>
       <c r="D35" s="8">
-        <v>46184.532615856486</v>
+        <v>46184.365949189814</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>134</v>
@@ -3583,13 +3583,13 @@
         <v>136</v>
       </c>
       <c r="B36" s="5">
-        <v>46169.55837825232</v>
+        <v>46169.391711585646</v>
       </c>
       <c r="C36" s="5">
-        <v>46184.53257122685</v>
+        <v>46184.36590456018</v>
       </c>
       <c r="D36" s="5">
-        <v>46184.53258194444</v>
+        <v>46184.36591527778</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>137</v>
@@ -3648,13 +3648,13 @@
         <v>139</v>
       </c>
       <c r="B37" s="8">
-        <v>46169.558381979165</v>
+        <v>46169.3917153125</v>
       </c>
       <c r="C37" s="8">
-        <v>46184.53220534722</v>
+        <v>46184.365538680555</v>
       </c>
       <c r="D37" s="8">
-        <v>46184.5322071875</v>
+        <v>46184.365540520834</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>82</v>
@@ -3703,13 +3703,13 @@
         <v>141</v>
       </c>
       <c r="B38" s="5">
-        <v>46169.55838657408</v>
+        <v>46169.391719907406</v>
       </c>
       <c r="C38" s="5">
-        <v>46184.53255483796</v>
+        <v>46184.36588817129</v>
       </c>
       <c r="D38" s="5">
-        <v>46184.53255631945</v>
+        <v>46184.36588965278</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>142</v>
@@ -3758,13 +3758,13 @@
         <v>144</v>
       </c>
       <c r="B39" s="8">
-        <v>46169.55839107639</v>
+        <v>46169.391724409725</v>
       </c>
       <c r="C39" s="8">
-        <v>46190.64487847222</v>
+        <v>46190.47821180556</v>
       </c>
       <c r="D39" s="8">
-        <v>46200.81849856481</v>
+        <v>46200.65183189815</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>145</v>
@@ -3823,13 +3823,13 @@
         <v>149</v>
       </c>
       <c r="B40" s="5">
-        <v>46169.55839478009</v>
+        <v>46169.39172811343</v>
       </c>
       <c r="C40" s="5">
-        <v>46195.70359988426</v>
+        <v>46195.53693321759</v>
       </c>
       <c r="D40" s="5">
-        <v>46195.70360162037</v>
+        <v>46195.53693495371</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>88</v>
@@ -3878,13 +3878,13 @@
         <v>151</v>
       </c>
       <c r="B41" s="8">
-        <v>46169.55839910879</v>
+        <v>46169.391732442135</v>
       </c>
       <c r="C41" s="8">
-        <v>46195.703751678244</v>
+        <v>46195.53708501157</v>
       </c>
       <c r="D41" s="8">
-        <v>46195.70375376157</v>
+        <v>46195.53708709491</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>152</v>
@@ -3933,11 +3933,11 @@
         <v>154</v>
       </c>
       <c r="B42" s="5">
-        <v>46169.55840355324</v>
+        <v>46169.39173688657</v>
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="5">
-        <v>46195.703763495374</v>
+        <v>46195.5370968287</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>155</v>
@@ -3986,13 +3986,13 @@
         <v>158</v>
       </c>
       <c r="B43" s="8">
-        <v>46169.55840677083</v>
+        <v>46169.39174010417</v>
       </c>
       <c r="C43" s="8">
-        <v>46191.53700108796</v>
+        <v>46191.3703344213</v>
       </c>
       <c r="D43" s="8">
-        <v>46191.53701371528</v>
+        <v>46191.37034704861</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>159</v>
@@ -4051,13 +4051,13 @@
         <v>161</v>
       </c>
       <c r="B44" s="5">
-        <v>46169.55841037037</v>
+        <v>46169.3917437037</v>
       </c>
       <c r="C44" s="5">
-        <v>46191.53678993056</v>
+        <v>46191.370123263885</v>
       </c>
       <c r="D44" s="5">
-        <v>46191.53679194444</v>
+        <v>46191.37012527778</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>85</v>
@@ -4106,13 +4106,13 @@
         <v>163</v>
       </c>
       <c r="B45" s="8">
-        <v>46169.558458217594</v>
+        <v>46169.39179155092</v>
       </c>
       <c r="C45" s="8">
-        <v>46191.53698667824</v>
+        <v>46191.37032001157</v>
       </c>
       <c r="D45" s="8">
-        <v>46191.53698841435</v>
+        <v>46191.37032174769</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>164</v>
@@ -4161,11 +4161,11 @@
         <v>166</v>
       </c>
       <c r="B46" s="5">
-        <v>46169.5584643287</v>
+        <v>46169.391797662036</v>
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46182.75962331019</v>
+        <v>46182.59295664352</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>167</v>
@@ -4210,13 +4210,13 @@
         <v>170</v>
       </c>
       <c r="B47" s="8">
-        <v>46169.55846813657</v>
+        <v>46169.39180146991</v>
       </c>
       <c r="C47" s="8">
-        <v>46181.72664483797</v>
+        <v>46181.559978171295</v>
       </c>
       <c r="D47" s="8">
-        <v>46197.715420312496</v>
+        <v>46197.54875364584</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>171</v>
@@ -4275,13 +4275,13 @@
         <v>176</v>
       </c>
       <c r="B48" s="5">
-        <v>46169.558472766206</v>
+        <v>46169.391806099535</v>
       </c>
       <c r="C48" s="5">
-        <v>46181.72662902778</v>
+        <v>46181.55996236111</v>
       </c>
       <c r="D48" s="5">
-        <v>46181.72663056713</v>
+        <v>46181.559963900465</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>174</v>
@@ -4330,13 +4330,13 @@
         <v>180</v>
       </c>
       <c r="B49" s="8">
-        <v>46169.55849938658</v>
+        <v>46169.391832719906</v>
       </c>
       <c r="C49" s="8">
-        <v>46182.759602164355</v>
+        <v>46182.59293549768</v>
       </c>
       <c r="D49" s="8">
-        <v>46197.71545016204</v>
+        <v>46197.54878349537</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>181</v>
@@ -4395,13 +4395,13 @@
         <v>182</v>
       </c>
       <c r="B50" s="5">
-        <v>46169.55850371528</v>
+        <v>46169.391837048606</v>
       </c>
       <c r="C50" s="5">
-        <v>46182.75958561343</v>
+        <v>46182.59291894676</v>
       </c>
       <c r="D50" s="5">
-        <v>46195.690583055555</v>
+        <v>46195.52391638889</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>174</v>
@@ -4450,13 +4450,13 @@
         <v>185</v>
       </c>
       <c r="B51" s="8">
-        <v>46169.55853228009</v>
+        <v>46169.39186561343</v>
       </c>
       <c r="C51" s="8">
-        <v>46182.75986146991</v>
+        <v>46182.59319480324</v>
       </c>
       <c r="D51" s="8">
-        <v>46182.759871076385</v>
+        <v>46182.59320440972</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>78</v>
@@ -4515,13 +4515,13 @@
         <v>187</v>
       </c>
       <c r="B52" s="5">
-        <v>46169.55854641204</v>
+        <v>46169.391879745366</v>
       </c>
       <c r="C52" s="5">
-        <v>46182.75984711805</v>
+        <v>46182.59318045139</v>
       </c>
       <c r="D52" s="5">
-        <v>46182.75984881945</v>
+        <v>46182.59318215278</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>174</v>
@@ -4570,11 +4570,11 @@
         <v>188</v>
       </c>
       <c r="B53" s="8">
-        <v>46169.558565775464</v>
+        <v>46169.3918991088</v>
       </c>
       <c r="C53" s="9"/>
       <c r="D53" s="8">
-        <v>46169.61885943287</v>
+        <v>46169.4521927662</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>189</v>
@@ -4633,11 +4633,11 @@
         <v>192</v>
       </c>
       <c r="B54" s="5">
-        <v>46169.55856972223</v>
+        <v>46169.391903055555</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46169.61882613426</v>
+        <v>46169.45215946759</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>174</v>
@@ -4686,13 +4686,13 @@
         <v>195</v>
       </c>
       <c r="B55" s="8">
-        <v>46169.558586307874</v>
+        <v>46169.3919196412</v>
       </c>
       <c r="C55" s="8">
-        <v>46198.59773380787</v>
+        <v>46198.4310671412</v>
       </c>
       <c r="D55" s="8">
-        <v>46198.597746307874</v>
+        <v>46198.4310796412</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>196</v>
@@ -4739,13 +4739,13 @@
         <v>198</v>
       </c>
       <c r="B56" s="5">
-        <v>46169.55858945602</v>
+        <v>46169.39192278935</v>
       </c>
       <c r="C56" s="5">
-        <v>46190.64495354166</v>
+        <v>46190.478286875004</v>
       </c>
       <c r="D56" s="5">
-        <v>46197.83559606482</v>
+        <v>46197.66892939815</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>199</v>
@@ -4804,13 +4804,13 @@
         <v>203</v>
       </c>
       <c r="B57" s="8">
-        <v>46169.55859488426</v>
+        <v>46169.39192821759</v>
       </c>
       <c r="C57" s="8">
-        <v>46197.85935881945</v>
+        <v>46197.69269215278</v>
       </c>
       <c r="D57" s="8">
-        <v>46197.85937331019</v>
+        <v>46197.69270664352</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>204</v>
@@ -4869,13 +4869,13 @@
         <v>206</v>
       </c>
       <c r="B58" s="5">
-        <v>46169.55860118056</v>
+        <v>46169.391934513886</v>
       </c>
       <c r="C58" s="5">
-        <v>46198.597692881944</v>
+        <v>46198.43102621528</v>
       </c>
       <c r="D58" s="5">
-        <v>46198.59771457176</v>
+        <v>46198.43104790509</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>207</v>
@@ -4934,13 +4934,13 @@
         <v>209</v>
       </c>
       <c r="B59" s="8">
-        <v>46169.55860636574</v>
+        <v>46169.391939699075</v>
       </c>
       <c r="C59" s="8">
-        <v>46197.85931310186</v>
+        <v>46197.692646435185</v>
       </c>
       <c r="D59" s="8">
-        <v>46198.597709444446</v>
+        <v>46198.43104277778</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>208</v>
@@ -4999,13 +4999,13 @@
         <v>210</v>
       </c>
       <c r="B60" s="5">
-        <v>46169.558650127314</v>
+        <v>46169.39198346065</v>
       </c>
       <c r="C60" s="5">
-        <v>46198.59771644676</v>
+        <v>46198.43104978009</v>
       </c>
       <c r="D60" s="5">
-        <v>46198.59773310185</v>
+        <v>46198.43106643519</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>211</v>
@@ -5064,13 +5064,13 @@
         <v>213</v>
       </c>
       <c r="B61" s="8">
-        <v>46169.55865608796</v>
+        <v>46169.391989421296</v>
       </c>
       <c r="C61" s="8">
-        <v>46197.85923987269</v>
+        <v>46197.69257320602</v>
       </c>
       <c r="D61" s="8">
-        <v>46198.59773317129</v>
+        <v>46198.43106650463</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>212</v>
@@ -5129,13 +5129,13 @@
         <v>214</v>
       </c>
       <c r="B62" s="5">
-        <v>46169.55866105324</v>
+        <v>46169.39199438658</v>
       </c>
       <c r="C62" s="5">
-        <v>46198.682278935186</v>
+        <v>46198.515612268515</v>
       </c>
       <c r="D62" s="5">
-        <v>46198.68229049769</v>
+        <v>46198.515623831016</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>215</v>
@@ -5182,13 +5182,13 @@
         <v>217</v>
       </c>
       <c r="B63" s="8">
-        <v>46169.55866469907</v>
+        <v>46169.391998032406</v>
       </c>
       <c r="C63" s="8">
-        <v>46190.645243935185</v>
+        <v>46190.47857726851</v>
       </c>
       <c r="D63" s="8">
-        <v>46197.85915361111</v>
+        <v>46197.69248694445</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>218</v>
@@ -5247,13 +5247,13 @@
         <v>222</v>
       </c>
       <c r="B64" s="5">
-        <v>46169.55867099537</v>
+        <v>46169.39200432871</v>
       </c>
       <c r="C64" s="5">
-        <v>46197.85914688658</v>
+        <v>46197.69248021991</v>
       </c>
       <c r="D64" s="5">
-        <v>46197.85936673611</v>
+        <v>46197.69270006944</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>174</v>
@@ -5302,13 +5302,13 @@
         <v>225</v>
       </c>
       <c r="B65" s="8">
-        <v>46169.558703518516</v>
+        <v>46169.39203685185</v>
       </c>
       <c r="C65" s="8">
-        <v>46190.64532476851</v>
+        <v>46190.478658101856</v>
       </c>
       <c r="D65" s="8">
-        <v>46197.85387390046</v>
+        <v>46197.6872072338</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>226</v>
@@ -5367,13 +5367,13 @@
         <v>227</v>
       </c>
       <c r="B66" s="5">
-        <v>46169.55870879629</v>
+        <v>46169.39204212963</v>
       </c>
       <c r="C66" s="5">
-        <v>46197.853856608795</v>
+        <v>46197.68718994213</v>
       </c>
       <c r="D66" s="5">
-        <v>46197.85915420139</v>
+        <v>46197.69248753472</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>174</v>
@@ -5422,13 +5422,13 @@
         <v>230</v>
       </c>
       <c r="B67" s="8">
-        <v>46169.558740625</v>
+        <v>46169.392073958334</v>
       </c>
       <c r="C67" s="8">
-        <v>46198.68226086805</v>
+        <v>46198.51559420139</v>
       </c>
       <c r="D67" s="8">
-        <v>46198.68228008102</v>
+        <v>46198.51561341435</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>231</v>
@@ -5487,11 +5487,11 @@
         <v>232</v>
       </c>
       <c r="B68" s="5">
-        <v>46169.558745243055</v>
+        <v>46169.39207857639</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46197.85386394676</v>
+        <v>46197.68719728009</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>174</v>
@@ -5540,11 +5540,11 @@
         <v>234</v>
       </c>
       <c r="B69" s="8">
-        <v>46169.55876947917</v>
+        <v>46169.392102812504</v>
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46200.819705856484</v>
+        <v>46200.65303918981</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>196</v>
@@ -5589,13 +5589,13 @@
         <v>236</v>
       </c>
       <c r="B70" s="5">
-        <v>46169.55880633101</v>
+        <v>46169.39213966436</v>
       </c>
       <c r="C70" s="5">
-        <v>46200.81968587963</v>
+        <v>46200.65301921296</v>
       </c>
       <c r="D70" s="5">
-        <v>46200.8197621875</v>
+        <v>46200.65309552083</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>237</v>
@@ -5654,13 +5654,13 @@
         <v>239</v>
       </c>
       <c r="B71" s="8">
-        <v>46169.5588177662</v>
+        <v>46169.39215109954</v>
       </c>
       <c r="C71" s="8">
-        <v>46200.81967096065</v>
+        <v>46200.653004293985</v>
       </c>
       <c r="D71" s="8">
-        <v>46200.819831597226</v>
+        <v>46200.653164930554</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>240</v>
@@ -5719,13 +5719,13 @@
         <v>242</v>
       </c>
       <c r="B72" s="5">
-        <v>46169.55882295139</v>
+        <v>46169.392156284724</v>
       </c>
       <c r="C72" s="5">
-        <v>46200.819208981484</v>
+        <v>46200.65254231481</v>
       </c>
       <c r="D72" s="5">
-        <v>46200.81928909722</v>
+        <v>46200.652622430556</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>243</v>
@@ -5784,11 +5784,11 @@
         <v>244</v>
       </c>
       <c r="B73" s="8">
-        <v>46169.55882788195</v>
+        <v>46169.39216121528</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46195.70377457176</v>
+        <v>46195.5371079051</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>245</v>
@@ -5847,11 +5847,11 @@
         <v>247</v>
       </c>
       <c r="B74" s="5">
-        <v>46169.55884254629</v>
+        <v>46169.392175879635</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46204.879935543984</v>
+        <v>46204.71326887731</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>248</v>
@@ -5894,13 +5894,13 @@
         <v>250</v>
       </c>
       <c r="B75" s="8">
-        <v>46169.55884548611</v>
+        <v>46169.39217881944</v>
       </c>
       <c r="C75" s="8">
-        <v>46197.49536869213</v>
+        <v>46197.328702025465</v>
       </c>
       <c r="D75" s="8">
-        <v>46197.49537962963</v>
+        <v>46197.32871296296</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>251</v>
@@ -5959,13 +5959,13 @@
         <v>253</v>
       </c>
       <c r="B76" s="5">
-        <v>46169.55884993056</v>
+        <v>46169.39218326389</v>
       </c>
       <c r="C76" s="5">
-        <v>46197.49535652778</v>
+        <v>46197.32868986111</v>
       </c>
       <c r="D76" s="5">
-        <v>46197.495357893524</v>
+        <v>46197.32869122685</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>174</v>
@@ -6014,13 +6014,13 @@
         <v>255</v>
       </c>
       <c r="B77" s="8">
-        <v>46169.55893170139</v>
+        <v>46169.39226503472</v>
       </c>
       <c r="C77" s="8">
-        <v>46197.49516923611</v>
+        <v>46197.32850256945</v>
       </c>
       <c r="D77" s="8">
-        <v>46197.495185555556</v>
+        <v>46197.328518888884</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>256</v>
@@ -6079,13 +6079,13 @@
         <v>257</v>
       </c>
       <c r="B78" s="5">
-        <v>46169.55893543981</v>
+        <v>46169.39226877315</v>
       </c>
       <c r="C78" s="5">
-        <v>46197.4951540162</v>
+        <v>46197.328487349536</v>
       </c>
       <c r="D78" s="5">
-        <v>46204.879924837966</v>
+        <v>46204.713258171294</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>174</v>
@@ -6134,13 +6134,13 @@
         <v>260</v>
       </c>
       <c r="B79" s="8">
-        <v>46169.558869560184</v>
+        <v>46169.39220289352</v>
       </c>
       <c r="C79" s="8">
-        <v>46204.87979715278</v>
+        <v>46204.71313048611</v>
       </c>
       <c r="D79" s="8">
-        <v>46204.87981377315</v>
+        <v>46204.71314710648</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>261</v>
@@ -6199,13 +6199,13 @@
         <v>262</v>
       </c>
       <c r="B80" s="5">
-        <v>46169.55887296297</v>
+        <v>46169.392206296296</v>
       </c>
       <c r="C80" s="5">
-        <v>46204.87978053241</v>
+        <v>46204.71311386574</v>
       </c>
       <c r="D80" s="5">
-        <v>46204.87978310185</v>
+        <v>46204.71311643519</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>193</v>
@@ -6254,13 +6254,13 @@
         <v>265</v>
       </c>
       <c r="B81" s="8">
-        <v>46169.5589025463</v>
+        <v>46169.392235879626</v>
       </c>
       <c r="C81" s="8">
-        <v>46204.87992821759</v>
+        <v>46204.713261550925</v>
       </c>
       <c r="D81" s="8">
-        <v>46204.880057013885</v>
+        <v>46204.71339034722</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>266</v>
@@ -6319,13 +6319,13 @@
         <v>267</v>
       </c>
       <c r="B82" s="5">
-        <v>46169.55890609954</v>
+        <v>46169.39223943287</v>
       </c>
       <c r="C82" s="5">
-        <v>46204.87991554398</v>
+        <v>46204.71324887731</v>
       </c>
       <c r="D82" s="5">
-        <v>46204.87991711806</v>
+        <v>46204.71325045139</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>174</v>
@@ -6374,11 +6374,11 @@
         <v>270</v>
       </c>
       <c r="B83" s="8">
-        <v>46169.55900443287</v>
+        <v>46169.3923377662</v>
       </c>
       <c r="C83" s="9"/>
       <c r="D83" s="8">
-        <v>46204.88038796296</v>
+        <v>46204.7137212963</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>271</v>
@@ -6437,11 +6437,11 @@
         <v>272</v>
       </c>
       <c r="B84" s="5">
-        <v>46169.55901002315</v>
+        <v>46169.39234335648</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46197.495160011575</v>
+        <v>46197.3284933449</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>193</v>
@@ -6490,11 +6490,11 @@
         <v>274</v>
       </c>
       <c r="B85" s="8">
-        <v>46169.55904462963</v>
+        <v>46169.39237796296</v>
       </c>
       <c r="C85" s="9"/>
       <c r="D85" s="8">
-        <v>46169.62153172454</v>
+        <v>46169.454865057865</v>
       </c>
       <c r="E85" s="9" t="s">
         <v>275</v>
@@ -6553,11 +6553,11 @@
         <v>277</v>
       </c>
       <c r="B86" s="5">
-        <v>46169.559050138894</v>
+        <v>46169.39238347222</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46169.62149153935</v>
+        <v>46169.454824872686</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>193</v>
@@ -6606,11 +6606,11 @@
         <v>279</v>
       </c>
       <c r="B87" s="8">
-        <v>46169.55907484954</v>
+        <v>46169.39240818287</v>
       </c>
       <c r="C87" s="9"/>
       <c r="D87" s="8">
-        <v>46197.85962290509</v>
+        <v>46197.692956238425</v>
       </c>
       <c r="E87" s="9" t="s">
         <v>280</v>
@@ -6653,11 +6653,11 @@
         <v>282</v>
       </c>
       <c r="B88" s="5">
-        <v>46169.55907863426</v>
+        <v>46169.392411967594</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46169.621643935185</v>
+        <v>46169.45497726851</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>283</v>
@@ -6716,11 +6716,11 @@
         <v>286</v>
       </c>
       <c r="B89" s="8">
-        <v>46169.55908684028</v>
+        <v>46169.39242017361</v>
       </c>
       <c r="C89" s="9"/>
       <c r="D89" s="8">
-        <v>46169.62159425926</v>
+        <v>46169.4549275926</v>
       </c>
       <c r="E89" s="9" t="s">
         <v>193</v>
@@ -6769,11 +6769,11 @@
         <v>288</v>
       </c>
       <c r="B90" s="5">
-        <v>46169.55918673611</v>
+        <v>46169.39252006944</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46196.561689236114</v>
+        <v>46196.39502256944</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>289</v>
@@ -6832,11 +6832,11 @@
         <v>290</v>
       </c>
       <c r="B91" s="8">
-        <v>46169.55919113426</v>
+        <v>46169.39252446759</v>
       </c>
       <c r="C91" s="9"/>
       <c r="D91" s="8">
-        <v>46169.62169328704</v>
+        <v>46169.45502662037</v>
       </c>
       <c r="E91" s="9" t="s">
         <v>193</v>
@@ -6885,13 +6885,13 @@
         <v>292</v>
       </c>
       <c r="B92" s="5">
-        <v>46169.559239560185</v>
+        <v>46169.392572893514</v>
       </c>
       <c r="C92" s="5">
-        <v>46197.859617372684</v>
+        <v>46197.69295070602</v>
       </c>
       <c r="D92" s="5">
-        <v>46197.859819363424</v>
+        <v>46197.69315269676</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>293</v>
@@ -6950,13 +6950,13 @@
         <v>294</v>
       </c>
       <c r="B93" s="8">
-        <v>46169.559243842596</v>
+        <v>46169.392577175924</v>
       </c>
       <c r="C93" s="8">
-        <v>46197.859803263884</v>
+        <v>46197.69313659723</v>
       </c>
       <c r="D93" s="8">
-        <v>46197.85980471065</v>
+        <v>46197.69313804398</v>
       </c>
       <c r="E93" s="9" t="s">
         <v>193</v>
@@ -7005,11 +7005,11 @@
         <v>296</v>
       </c>
       <c r="B94" s="5">
-        <v>46169.55929686343</v>
+        <v>46169.39263019676</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46196.573311342596</v>
+        <v>46196.406644675924</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>297</v>
@@ -7068,11 +7068,11 @@
         <v>300</v>
       </c>
       <c r="B95" s="8">
-        <v>46169.55930180555</v>
+        <v>46169.39263513889</v>
       </c>
       <c r="C95" s="9"/>
       <c r="D95" s="8">
-        <v>46197.859809629634</v>
+        <v>46197.69314296296</v>
       </c>
       <c r="E95" s="9" t="s">
         <v>298</v>
@@ -7121,11 +7121,11 @@
         <v>301</v>
       </c>
       <c r="B96" s="5">
-        <v>46169.55938721065</v>
+        <v>46169.39272054398</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46169.60672822916</v>
+        <v>46169.440061562505</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>302</v>
@@ -7168,11 +7168,11 @@
         <v>304</v>
       </c>
       <c r="B97" s="8">
-        <v>46169.55939094907</v>
+        <v>46169.39272428241</v>
       </c>
       <c r="C97" s="9"/>
       <c r="D97" s="8">
-        <v>46169.621991215274</v>
+        <v>46169.45532454861</v>
       </c>
       <c r="E97" s="9" t="s">
         <v>305</v>
@@ -7231,11 +7231,11 @@
         <v>308</v>
       </c>
       <c r="B98" s="5">
-        <v>46169.55939643519</v>
+        <v>46169.392729768515</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46196.805673622686</v>
+        <v>46196.639006956015</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>309</v>

--- a/data/50001557 - ATACAMA KOZAN OT4340.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4340.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1183" uniqueCount="310">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1183" uniqueCount="309">
   <si>
     <t xml:space="preserve"> 50001557 - ATACAMA KOZAN</t>
   </si>
@@ -630,213 +630,213 @@
     <t>1215165982983056</t>
   </si>
   <si>
+    <t>check pruebas FAT,OT 4335 - ZVN 1-7-37/2 + TOB + REJ</t>
+  </si>
+  <si>
+    <t>1215165983005052</t>
+  </si>
+  <si>
+    <t>Bodega:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recepcion materiales corte laser,Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>1215165983005064</t>
+  </si>
+  <si>
+    <t>Recepcion materiales corte laser</t>
+  </si>
+  <si>
+    <t>Victor Muñoz</t>
+  </si>
+  <si>
+    <t>victor.munoz@zitron.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bodega:,Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>1215166329404944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>Bodega:,OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR</t>
+  </si>
+  <si>
+    <t>1215166041891869</t>
+  </si>
+  <si>
+    <t>Recepcion Materiales corte plasma</t>
+  </si>
+  <si>
+    <t>Control de calidad Corte plasma</t>
+  </si>
+  <si>
+    <t>1215166041891891</t>
+  </si>
+  <si>
+    <t>1215165982799201</t>
+  </si>
+  <si>
+    <t>Recepcion mecanizado</t>
+  </si>
+  <si>
+    <t>Control de calidad Mecanizado</t>
+  </si>
+  <si>
+    <t>1215166243533900</t>
+  </si>
+  <si>
+    <t>1215166243533917</t>
+  </si>
+  <si>
+    <t>Caldereria:</t>
+  </si>
+  <si>
+    <t>Control de calidad Armado,Armado,Preparación Materiales</t>
+  </si>
+  <si>
+    <t>1215166433625222</t>
+  </si>
+  <si>
+    <t>Preparación Materiales</t>
+  </si>
+  <si>
+    <t>Nicolás Mol</t>
+  </si>
+  <si>
+    <t>nicolas.mol@zitron.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR,OT2 4307 ZVN 1-9-86/2 </t>
+  </si>
+  <si>
+    <t>1215166433625244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad Mecanizado,Control de calidad Corte plasma,Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>Preparación Materiales,OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR</t>
+  </si>
+  <si>
+    <t>1215166243563189</t>
+  </si>
+  <si>
+    <t>Armado</t>
+  </si>
+  <si>
+    <t>1215166329517772</t>
+  </si>
+  <si>
+    <t>OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR,check planos</t>
+  </si>
+  <si>
+    <t>OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR,Armado</t>
+  </si>
+  <si>
+    <t>1215166041950163</t>
+  </si>
+  <si>
+    <t>Control de calidad Armado</t>
+  </si>
+  <si>
+    <t>1215166041950180</t>
+  </si>
+  <si>
+    <t>Control de calidad Armado,OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR</t>
+  </si>
+  <si>
+    <t>1215165983080450</t>
+  </si>
+  <si>
+    <t>Recepcion Rodete,Recepcion Alabe,Recepcion motor</t>
+  </si>
+  <si>
+    <t>1215166329573409</t>
+  </si>
+  <si>
+    <t>Recepcion Rodete</t>
+  </si>
+  <si>
+    <t>OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR,Bodega:</t>
+  </si>
+  <si>
+    <t>1215166329573431</t>
+  </si>
+  <si>
+    <t>Recepcion Alabe</t>
+  </si>
+  <si>
+    <t>OT 4335 - ZVN 1-7-37/2 + TOB + REJ,Bodega:</t>
+  </si>
+  <si>
+    <t>1215166433753017</t>
+  </si>
+  <si>
+    <t>Recepcion motor</t>
+  </si>
+  <si>
+    <t>1215166329638303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recepcion fabricación externa </t>
+  </si>
+  <si>
+    <t>Revestimiento,OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR</t>
+  </si>
+  <si>
+    <t>1215166243719413</t>
+  </si>
+  <si>
+    <t>Montaje:</t>
+  </si>
+  <si>
+    <t>Montaje motor,Revestimiento,Montaje Alabe,Montaje Rodete,Pruebas FAT,RE-PINTADO</t>
+  </si>
+  <si>
+    <t>1215166243719425</t>
+  </si>
+  <si>
+    <t>Revestimiento</t>
+  </si>
+  <si>
+    <t>Recepcion fabricación externa ,OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR</t>
+  </si>
+  <si>
+    <t>1215166243721553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR,Recepcion fabricación externa </t>
+  </si>
+  <si>
+    <t>1215166042063677</t>
+  </si>
+  <si>
+    <t>Montaje motor</t>
+  </si>
+  <si>
+    <t>1215166433822992</t>
+  </si>
+  <si>
+    <t>OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR,Recepcion motor,check planos</t>
+  </si>
+  <si>
+    <t>OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR,Montaje motor</t>
+  </si>
+  <si>
+    <t>1215166243741268</t>
+  </si>
+  <si>
+    <t>Montaje Alabe</t>
+  </si>
+  <si>
     <t>OT 4335 - ZVN 1-7-37/2 + TOB + REJ</t>
   </si>
   <si>
-    <t>check pruebas FAT,OT 4335 - ZVN 1-7-37/2 + TOB + REJ</t>
-  </si>
-  <si>
-    <t>1215165983005052</t>
-  </si>
-  <si>
-    <t>Bodega:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recepcion materiales corte laser,Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>1215165983005064</t>
-  </si>
-  <si>
-    <t>Recepcion materiales corte laser</t>
-  </si>
-  <si>
-    <t>Victor Muñoz</t>
-  </si>
-  <si>
-    <t>victor.munoz@zitron.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bodega:,Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>1215166329404944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>Bodega:,OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR</t>
-  </si>
-  <si>
-    <t>1215166041891869</t>
-  </si>
-  <si>
-    <t>Recepcion Materiales corte plasma</t>
-  </si>
-  <si>
-    <t>Control de calidad Corte plasma</t>
-  </si>
-  <si>
-    <t>1215166041891891</t>
-  </si>
-  <si>
-    <t>1215165982799201</t>
-  </si>
-  <si>
-    <t>Recepcion mecanizado</t>
-  </si>
-  <si>
-    <t>Control de calidad Mecanizado</t>
-  </si>
-  <si>
-    <t>1215166243533900</t>
-  </si>
-  <si>
-    <t>1215166243533917</t>
-  </si>
-  <si>
-    <t>Caldereria:</t>
-  </si>
-  <si>
-    <t>Control de calidad Armado,Armado,Preparación Materiales</t>
-  </si>
-  <si>
-    <t>1215166433625222</t>
-  </si>
-  <si>
-    <t>Preparación Materiales</t>
-  </si>
-  <si>
-    <t>Nicolás Mol</t>
-  </si>
-  <si>
-    <t>nicolas.mol@zitron.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR,OT2 4307 ZVN 1-9-86/2 </t>
-  </si>
-  <si>
-    <t>1215166433625244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad Mecanizado,Control de calidad Corte plasma,Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>Preparación Materiales,OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR</t>
-  </si>
-  <si>
-    <t>1215166243563189</t>
-  </si>
-  <si>
-    <t>Armado</t>
-  </si>
-  <si>
-    <t>1215166329517772</t>
-  </si>
-  <si>
-    <t>OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR,check planos</t>
-  </si>
-  <si>
-    <t>OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR,Armado</t>
-  </si>
-  <si>
-    <t>1215166041950163</t>
-  </si>
-  <si>
-    <t>Control de calidad Armado</t>
-  </si>
-  <si>
-    <t>1215166041950180</t>
-  </si>
-  <si>
-    <t>Control de calidad Armado,OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR</t>
-  </si>
-  <si>
-    <t>1215165983080450</t>
-  </si>
-  <si>
-    <t>Recepcion Rodete,Recepcion Alabe,Recepcion motor</t>
-  </si>
-  <si>
-    <t>1215166329573409</t>
-  </si>
-  <si>
-    <t>Recepcion Rodete</t>
-  </si>
-  <si>
-    <t>OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR,Bodega:</t>
-  </si>
-  <si>
-    <t>1215166329573431</t>
-  </si>
-  <si>
-    <t>Recepcion Alabe</t>
-  </si>
-  <si>
-    <t>OT 4335 - ZVN 1-7-37/2 + TOB + REJ,Bodega:</t>
-  </si>
-  <si>
-    <t>1215166433753017</t>
-  </si>
-  <si>
-    <t>Recepcion motor</t>
-  </si>
-  <si>
-    <t>1215166329638303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recepcion fabricación externa </t>
-  </si>
-  <si>
-    <t>Revestimiento,OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR</t>
-  </si>
-  <si>
-    <t>1215166243719413</t>
-  </si>
-  <si>
-    <t>Montaje:</t>
-  </si>
-  <si>
-    <t>Montaje motor,Revestimiento,Montaje Alabe,Montaje Rodete,Pruebas FAT,RE-PINTADO</t>
-  </si>
-  <si>
-    <t>1215166243719425</t>
-  </si>
-  <si>
-    <t>Revestimiento</t>
-  </si>
-  <si>
-    <t>Recepcion fabricación externa ,OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR</t>
-  </si>
-  <si>
-    <t>1215166243721553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR,Recepcion fabricación externa </t>
-  </si>
-  <si>
-    <t>1215166042063677</t>
-  </si>
-  <si>
-    <t>Montaje motor</t>
-  </si>
-  <si>
-    <t>1215166433822992</t>
-  </si>
-  <si>
-    <t>OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR,Recepcion motor,check planos</t>
-  </si>
-  <si>
-    <t>OT 4335 - ZVN 1-7-37/2 + TOB + REJ,Montaje motor</t>
-  </si>
-  <si>
-    <t>1215166243741268</t>
-  </si>
-  <si>
-    <t>Montaje Alabe</t>
-  </si>
-  <si>
     <t>1215166243741285</t>
   </si>
   <si>
@@ -885,7 +885,7 @@
     <t>1215166433909056</t>
   </si>
   <si>
-    <t>OT 4335 - ZVN 1-7-37/2 + TOB + REJ,RE-PINTADO</t>
+    <t>OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR,RE-PINTADO</t>
   </si>
   <si>
     <t>1215166243860810</t>
@@ -912,7 +912,7 @@
     <t>1215166042182264</t>
   </si>
   <si>
-    <t>Coordinacion Entrega con Cliente,OT 4335 - ZVN 1-7-37/2 + TOB + REJ</t>
+    <t>Coordinacion Entrega con Cliente,OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR</t>
   </si>
   <si>
     <t>1215166042241854</t>
@@ -924,7 +924,7 @@
     <t>1215166042241871</t>
   </si>
   <si>
-    <t>Embalaje,OT 4335 - ZVN 1-7-37/2 + TOB + REJ</t>
+    <t>Embalaje,OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR</t>
   </si>
   <si>
     <t>1215166244019141</t>
@@ -936,16 +936,13 @@
     <t>1215166329951799</t>
   </si>
   <si>
-    <t>OT1 4335 - ZVN 1-7-37/2 + TOB + REJ,Planos Preliminar,PACKING LIST</t>
+    <t>OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR,Planos Preliminar,PACKING LIST</t>
   </si>
   <si>
     <t>1215166324086107</t>
   </si>
   <si>
     <t>Despacho</t>
-  </si>
-  <si>
-    <t>OT1 4335 - ZVN 1-7-37/2 + TOB + REJ</t>
   </si>
   <si>
     <t>Gestion,Logistica:,Costos</t>
@@ -1605,13 +1602,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46169.39133378472</v>
+        <v>46169.55800045139</v>
       </c>
       <c r="C4" s="5">
-        <v>46181.45679118056</v>
+        <v>46181.62345784722</v>
       </c>
       <c r="D4" s="5">
-        <v>46200.65157234954</v>
+        <v>46200.818239016204</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1654,13 +1651,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46169.39146962963</v>
+        <v>46169.5581362963</v>
       </c>
       <c r="C5" s="8">
-        <v>46181.45679953704</v>
+        <v>46181.6234662037</v>
       </c>
       <c r="D5" s="8">
-        <v>46181.456813819445</v>
+        <v>46181.623480486116</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1717,13 +1714,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46169.39147307871</v>
+        <v>46169.55813974537</v>
       </c>
       <c r="C6" s="5">
-        <v>46181.45680732639</v>
+        <v>46181.62347399305</v>
       </c>
       <c r="D6" s="5">
-        <v>46181.457589259255</v>
+        <v>46181.624255925926</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -1780,13 +1777,13 @@
         <v>36</v>
       </c>
       <c r="B7" s="8">
-        <v>46169.39147766204</v>
+        <v>46169.55814432871</v>
       </c>
       <c r="C7" s="8">
-        <v>46181.45681351852</v>
+        <v>46181.62348018518</v>
       </c>
       <c r="D7" s="8">
-        <v>46181.45683121528</v>
+        <v>46181.62349788194</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>37</v>
@@ -1843,13 +1840,13 @@
         <v>39</v>
       </c>
       <c r="B8" s="5">
-        <v>46169.39148107639</v>
+        <v>46169.55814774305</v>
       </c>
       <c r="C8" s="5">
-        <v>46181.45681916666</v>
+        <v>46181.623485833334</v>
       </c>
       <c r="D8" s="5">
-        <v>46181.45683517361</v>
+        <v>46181.62350184028</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>40</v>
@@ -1906,13 +1903,13 @@
         <v>43</v>
       </c>
       <c r="B9" s="8">
-        <v>46169.39148497685</v>
+        <v>46169.55815164352</v>
       </c>
       <c r="C9" s="8">
-        <v>46181.456824953704</v>
+        <v>46181.62349162037</v>
       </c>
       <c r="D9" s="8">
-        <v>46181.456841736115</v>
+        <v>46181.62350840278</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>44</v>
@@ -1969,13 +1966,13 @@
         <v>46</v>
       </c>
       <c r="B10" s="5">
-        <v>46169.391342731484</v>
+        <v>46169.55800939815</v>
       </c>
       <c r="C10" s="5">
-        <v>46197.67223334491</v>
+        <v>46197.83890001157</v>
       </c>
       <c r="D10" s="5">
-        <v>46197.67225445602</v>
+        <v>46197.83892112269</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>47</v>
@@ -2022,13 +2019,13 @@
         <v>48</v>
       </c>
       <c r="B11" s="8">
-        <v>46169.391519004625</v>
+        <v>46169.558185671296</v>
       </c>
       <c r="C11" s="8">
-        <v>46181.4576984375</v>
+        <v>46181.624365104166</v>
       </c>
       <c r="D11" s="8">
-        <v>46196.639006944446</v>
+        <v>46196.80567361111</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>49</v>
@@ -2087,13 +2084,13 @@
         <v>54</v>
       </c>
       <c r="B12" s="5">
-        <v>46169.39152517361</v>
+        <v>46169.558191840275</v>
       </c>
       <c r="C12" s="5">
-        <v>46181.457710393515</v>
+        <v>46181.62437706019</v>
       </c>
       <c r="D12" s="5">
-        <v>46196.639006655096</v>
+        <v>46196.80567332176</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>55</v>
@@ -2152,13 +2149,13 @@
         <v>58</v>
       </c>
       <c r="B13" s="8">
-        <v>46169.39153075231</v>
+        <v>46169.558197418984</v>
       </c>
       <c r="C13" s="8">
-        <v>46181.45772287037</v>
+        <v>46181.624389537035</v>
       </c>
       <c r="D13" s="8">
-        <v>46196.63900653935</v>
+        <v>46196.80567320602</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>59</v>
@@ -2217,13 +2214,13 @@
         <v>61</v>
       </c>
       <c r="B14" s="5">
-        <v>46169.39134710648</v>
+        <v>46169.558013773145</v>
       </c>
       <c r="C14" s="5">
-        <v>46190.477491620375</v>
+        <v>46190.64415828703</v>
       </c>
       <c r="D14" s="5">
-        <v>46190.47750472222</v>
+        <v>46190.64417138889</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>62</v>
@@ -2270,13 +2267,13 @@
         <v>64</v>
       </c>
       <c r="B15" s="8">
-        <v>46169.39154689814</v>
+        <v>46169.558213564815</v>
       </c>
       <c r="C15" s="8">
-        <v>46181.45778030093</v>
+        <v>46181.62444696759</v>
       </c>
       <c r="D15" s="8">
-        <v>46181.4577971875</v>
+        <v>46181.62446385417</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>65</v>
@@ -2335,13 +2332,13 @@
         <v>67</v>
       </c>
       <c r="B16" s="5">
-        <v>46169.3915578125</v>
+        <v>46169.558224479166</v>
       </c>
       <c r="C16" s="5">
-        <v>46181.457787060186</v>
+        <v>46181.62445372685</v>
       </c>
       <c r="D16" s="5">
-        <v>46181.45780335648</v>
+        <v>46181.62447002315</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>68</v>
@@ -2400,13 +2397,13 @@
         <v>70</v>
       </c>
       <c r="B17" s="8">
-        <v>46169.39156415509</v>
+        <v>46169.558230821756</v>
       </c>
       <c r="C17" s="8">
-        <v>46183.73984991898</v>
+        <v>46183.906516585645</v>
       </c>
       <c r="D17" s="8">
-        <v>46183.73985265046</v>
+        <v>46183.90651931713</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>71</v>
@@ -2465,13 +2462,13 @@
         <v>74</v>
       </c>
       <c r="B18" s="5">
-        <v>46169.391569803236</v>
+        <v>46169.55823646991</v>
       </c>
       <c r="C18" s="5">
-        <v>46183.73996832176</v>
+        <v>46183.90663498842</v>
       </c>
       <c r="D18" s="5">
-        <v>46183.73998440972</v>
+        <v>46183.90665107639</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>75</v>
@@ -2530,13 +2527,13 @@
         <v>80</v>
       </c>
       <c r="B19" s="8">
-        <v>46169.39157504629</v>
+        <v>46169.55824171296</v>
       </c>
       <c r="C19" s="8">
-        <v>46183.739979872684</v>
+        <v>46183.906646539355</v>
       </c>
       <c r="D19" s="8">
-        <v>46183.73999503472</v>
+        <v>46183.90666170139</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>81</v>
@@ -2595,13 +2592,13 @@
         <v>83</v>
       </c>
       <c r="B20" s="5">
-        <v>46169.39157907407</v>
+        <v>46169.55824574074</v>
       </c>
       <c r="C20" s="5">
-        <v>46190.47747336805</v>
+        <v>46190.644140034725</v>
       </c>
       <c r="D20" s="5">
-        <v>46190.47749153935</v>
+        <v>46190.64415820602</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>84</v>
@@ -2660,13 +2657,13 @@
         <v>86</v>
       </c>
       <c r="B21" s="8">
-        <v>46169.39158340278</v>
+        <v>46169.55825006944</v>
       </c>
       <c r="C21" s="8">
-        <v>46183.74067290509</v>
+        <v>46183.90733957176</v>
       </c>
       <c r="D21" s="8">
-        <v>46183.74068726852</v>
+        <v>46183.90735393518</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>87</v>
@@ -2725,13 +2722,13 @@
         <v>89</v>
       </c>
       <c r="B22" s="5">
-        <v>46169.39135159722</v>
+        <v>46169.55801826389</v>
       </c>
       <c r="C22" s="5">
-        <v>46200.65164541667</v>
+        <v>46200.818312083335</v>
       </c>
       <c r="D22" s="5">
-        <v>46200.65175913194</v>
+        <v>46200.818425798614</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>90</v>
@@ -2774,13 +2771,13 @@
         <v>92</v>
       </c>
       <c r="B23" s="8">
-        <v>46169.39163528935</v>
+        <v>46169.558301956014</v>
       </c>
       <c r="C23" s="8">
-        <v>46182.506723715276</v>
+        <v>46182.67339038194</v>
       </c>
       <c r="D23" s="8">
-        <v>46200.6516671412</v>
+        <v>46200.81833380787</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>93</v>
@@ -2839,13 +2836,13 @@
         <v>97</v>
       </c>
       <c r="B24" s="5">
-        <v>46169.391639849535</v>
+        <v>46169.558306516206</v>
       </c>
       <c r="C24" s="5">
-        <v>46195.52412340278</v>
+        <v>46195.69079006945</v>
       </c>
       <c r="D24" s="5">
-        <v>46195.524125578704</v>
+        <v>46195.69079224537</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>98</v>
@@ -2900,13 +2897,13 @@
         <v>101</v>
       </c>
       <c r="B25" s="8">
-        <v>46169.391644710646</v>
+        <v>46169.55831137732</v>
       </c>
       <c r="C25" s="8">
-        <v>46182.50670748843</v>
+        <v>46182.67337415509</v>
       </c>
       <c r="D25" s="8">
-        <v>46195.52413380787</v>
+        <v>46195.690800474535</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>102</v>
@@ -2961,13 +2958,13 @@
         <v>104</v>
       </c>
       <c r="B26" s="5">
-        <v>46169.39164938657</v>
+        <v>46169.55831605324</v>
       </c>
       <c r="C26" s="5">
-        <v>46184.569797442135</v>
+        <v>46184.73646410879</v>
       </c>
       <c r="D26" s="5">
-        <v>46184.569945138894</v>
+        <v>46184.73661180555</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>105</v>
@@ -3026,13 +3023,13 @@
         <v>107</v>
       </c>
       <c r="B27" s="8">
-        <v>46169.391653969906</v>
+        <v>46169.55832063657</v>
       </c>
       <c r="C27" s="8">
-        <v>46184.56974114584</v>
+        <v>46184.736407812496</v>
       </c>
       <c r="D27" s="8">
-        <v>46184.56974306713</v>
+        <v>46184.7364097338</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>108</v>
@@ -3087,13 +3084,13 @@
         <v>110</v>
       </c>
       <c r="B28" s="5">
-        <v>46169.39165872685</v>
+        <v>46169.55832539352</v>
       </c>
       <c r="C28" s="5">
-        <v>46184.569781342594</v>
+        <v>46184.73644800926</v>
       </c>
       <c r="D28" s="5">
-        <v>46184.569782708335</v>
+        <v>46184.736449375</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>111</v>
@@ -3148,13 +3145,13 @@
         <v>113</v>
       </c>
       <c r="B29" s="8">
-        <v>46169.39166340278</v>
+        <v>46169.55833006944</v>
       </c>
       <c r="C29" s="8">
-        <v>46182.50683622685</v>
+        <v>46182.67350289352</v>
       </c>
       <c r="D29" s="8">
-        <v>46200.6517028588</v>
+        <v>46200.81836952546</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>114</v>
@@ -3213,13 +3210,13 @@
         <v>116</v>
       </c>
       <c r="B30" s="5">
-        <v>46169.39166819444</v>
+        <v>46169.55833486111</v>
       </c>
       <c r="C30" s="5">
-        <v>46195.52399430556</v>
+        <v>46195.69066097222</v>
       </c>
       <c r="D30" s="5">
-        <v>46195.52399592593</v>
+        <v>46195.69066259259</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>117</v>
@@ -3274,13 +3271,13 @@
         <v>119</v>
       </c>
       <c r="B31" s="8">
-        <v>46169.39167359954</v>
+        <v>46169.5583402662</v>
       </c>
       <c r="C31" s="8">
-        <v>46182.50676563657</v>
+        <v>46182.67343230324</v>
       </c>
       <c r="D31" s="8">
-        <v>46195.5240009375</v>
+        <v>46195.69066760417</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>120</v>
@@ -3335,13 +3332,13 @@
         <v>122</v>
       </c>
       <c r="B32" s="5">
-        <v>46169.391678368054</v>
+        <v>46169.55834503472</v>
       </c>
       <c r="C32" s="5">
-        <v>46195.52391052083</v>
+        <v>46195.6905771875</v>
       </c>
       <c r="D32" s="5">
-        <v>46195.524001365746</v>
+        <v>46195.6906680324</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>123</v>
@@ -3396,13 +3393,13 @@
         <v>125</v>
       </c>
       <c r="B33" s="8">
-        <v>46169.39169668981</v>
+        <v>46169.55836335648</v>
       </c>
       <c r="C33" s="8">
-        <v>46184.36596177083</v>
+        <v>46184.532628437504</v>
       </c>
       <c r="D33" s="8">
-        <v>46184.36597520833</v>
+        <v>46184.532641875005</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>126</v>
@@ -3461,13 +3458,13 @@
         <v>130</v>
       </c>
       <c r="B34" s="5">
-        <v>46169.391701319444</v>
+        <v>46169.558367986116</v>
       </c>
       <c r="C34" s="5">
-        <v>46184.36579065972</v>
+        <v>46184.53245732639</v>
       </c>
       <c r="D34" s="5">
-        <v>46184.365792083336</v>
+        <v>46184.53245875</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>131</v>
@@ -3522,13 +3519,13 @@
         <v>133</v>
       </c>
       <c r="B35" s="8">
-        <v>46169.39170626157</v>
+        <v>46169.55837292824</v>
       </c>
       <c r="C35" s="8">
-        <v>46184.36594700231</v>
+        <v>46184.532613668984</v>
       </c>
       <c r="D35" s="8">
-        <v>46184.365949189814</v>
+        <v>46184.532615856486</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>134</v>
@@ -3583,13 +3580,13 @@
         <v>136</v>
       </c>
       <c r="B36" s="5">
-        <v>46169.391711585646</v>
+        <v>46169.55837825232</v>
       </c>
       <c r="C36" s="5">
-        <v>46184.36590456018</v>
+        <v>46184.53257122685</v>
       </c>
       <c r="D36" s="5">
-        <v>46184.36591527778</v>
+        <v>46184.53258194444</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>137</v>
@@ -3648,13 +3645,13 @@
         <v>139</v>
       </c>
       <c r="B37" s="8">
-        <v>46169.3917153125</v>
+        <v>46169.558381979165</v>
       </c>
       <c r="C37" s="8">
-        <v>46184.365538680555</v>
+        <v>46184.53220534722</v>
       </c>
       <c r="D37" s="8">
-        <v>46184.365540520834</v>
+        <v>46184.5322071875</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>82</v>
@@ -3703,13 +3700,13 @@
         <v>141</v>
       </c>
       <c r="B38" s="5">
-        <v>46169.391719907406</v>
+        <v>46169.55838657408</v>
       </c>
       <c r="C38" s="5">
-        <v>46184.36588817129</v>
+        <v>46184.53255483796</v>
       </c>
       <c r="D38" s="5">
-        <v>46184.36588965278</v>
+        <v>46184.53255631945</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>142</v>
@@ -3758,13 +3755,13 @@
         <v>144</v>
       </c>
       <c r="B39" s="8">
-        <v>46169.391724409725</v>
+        <v>46169.55839107639</v>
       </c>
       <c r="C39" s="8">
-        <v>46190.47821180556</v>
+        <v>46190.64487847222</v>
       </c>
       <c r="D39" s="8">
-        <v>46200.65183189815</v>
+        <v>46205.600326053245</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>145</v>
@@ -3823,13 +3820,13 @@
         <v>149</v>
       </c>
       <c r="B40" s="5">
-        <v>46169.39172811343</v>
+        <v>46169.55839478009</v>
       </c>
       <c r="C40" s="5">
-        <v>46195.53693321759</v>
+        <v>46195.70359988426</v>
       </c>
       <c r="D40" s="5">
-        <v>46195.53693495371</v>
+        <v>46195.70360162037</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>88</v>
@@ -3878,13 +3875,13 @@
         <v>151</v>
       </c>
       <c r="B41" s="8">
-        <v>46169.391732442135</v>
+        <v>46169.55839910879</v>
       </c>
       <c r="C41" s="8">
-        <v>46195.53708501157</v>
+        <v>46195.703751678244</v>
       </c>
       <c r="D41" s="8">
-        <v>46195.53708709491</v>
+        <v>46195.70375376157</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>152</v>
@@ -3933,11 +3930,13 @@
         <v>154</v>
       </c>
       <c r="B42" s="5">
-        <v>46169.39173688657</v>
-      </c>
-      <c r="C42" s="6"/>
+        <v>46169.55840355324</v>
+      </c>
+      <c r="C42" s="5">
+        <v>46205.599944490736</v>
+      </c>
       <c r="D42" s="5">
-        <v>46195.5370968287</v>
+        <v>46205.59994755787</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>155</v>
@@ -3986,13 +3985,13 @@
         <v>158</v>
       </c>
       <c r="B43" s="8">
-        <v>46169.39174010417</v>
+        <v>46169.55840677083</v>
       </c>
       <c r="C43" s="8">
-        <v>46191.3703344213</v>
+        <v>46191.53700108796</v>
       </c>
       <c r="D43" s="8">
-        <v>46191.37034704861</v>
+        <v>46191.53701371528</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>159</v>
@@ -4051,13 +4050,13 @@
         <v>161</v>
       </c>
       <c r="B44" s="5">
-        <v>46169.3917437037</v>
+        <v>46169.55841037037</v>
       </c>
       <c r="C44" s="5">
-        <v>46191.370123263885</v>
+        <v>46191.53678993056</v>
       </c>
       <c r="D44" s="5">
-        <v>46191.37012527778</v>
+        <v>46191.53679194444</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>85</v>
@@ -4106,13 +4105,13 @@
         <v>163</v>
       </c>
       <c r="B45" s="8">
-        <v>46169.39179155092</v>
+        <v>46169.558458217594</v>
       </c>
       <c r="C45" s="8">
-        <v>46191.37032001157</v>
+        <v>46191.53698667824</v>
       </c>
       <c r="D45" s="8">
-        <v>46191.37032174769</v>
+        <v>46191.53698841435</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>164</v>
@@ -4161,11 +4160,11 @@
         <v>166</v>
       </c>
       <c r="B46" s="5">
-        <v>46169.391797662036</v>
+        <v>46169.5584643287</v>
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46182.59295664352</v>
+        <v>46182.75962331019</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>167</v>
@@ -4210,13 +4209,13 @@
         <v>170</v>
       </c>
       <c r="B47" s="8">
-        <v>46169.39180146991</v>
+        <v>46169.55846813657</v>
       </c>
       <c r="C47" s="8">
-        <v>46181.559978171295</v>
+        <v>46181.72664483797</v>
       </c>
       <c r="D47" s="8">
-        <v>46197.54875364584</v>
+        <v>46197.715420312496</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>171</v>
@@ -4275,13 +4274,13 @@
         <v>176</v>
       </c>
       <c r="B48" s="5">
-        <v>46169.391806099535</v>
+        <v>46169.558472766206</v>
       </c>
       <c r="C48" s="5">
-        <v>46181.55996236111</v>
+        <v>46181.72662902778</v>
       </c>
       <c r="D48" s="5">
-        <v>46181.559963900465</v>
+        <v>46181.72663056713</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>174</v>
@@ -4330,13 +4329,13 @@
         <v>180</v>
       </c>
       <c r="B49" s="8">
-        <v>46169.391832719906</v>
+        <v>46169.55849938658</v>
       </c>
       <c r="C49" s="8">
-        <v>46182.59293549768</v>
+        <v>46182.759602164355</v>
       </c>
       <c r="D49" s="8">
-        <v>46197.54878349537</v>
+        <v>46197.71545016204</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>181</v>
@@ -4395,13 +4394,13 @@
         <v>182</v>
       </c>
       <c r="B50" s="5">
-        <v>46169.391837048606</v>
+        <v>46169.55850371528</v>
       </c>
       <c r="C50" s="5">
-        <v>46182.59291894676</v>
+        <v>46182.75958561343</v>
       </c>
       <c r="D50" s="5">
-        <v>46195.52391638889</v>
+        <v>46195.690583055555</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>174</v>
@@ -4450,13 +4449,13 @@
         <v>185</v>
       </c>
       <c r="B51" s="8">
-        <v>46169.39186561343</v>
+        <v>46169.55853228009</v>
       </c>
       <c r="C51" s="8">
-        <v>46182.59319480324</v>
+        <v>46182.75986146991</v>
       </c>
       <c r="D51" s="8">
-        <v>46182.59320440972</v>
+        <v>46182.759871076385</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>78</v>
@@ -4515,13 +4514,13 @@
         <v>187</v>
       </c>
       <c r="B52" s="5">
-        <v>46169.391879745366</v>
+        <v>46169.55854641204</v>
       </c>
       <c r="C52" s="5">
-        <v>46182.59318045139</v>
+        <v>46182.75984711805</v>
       </c>
       <c r="D52" s="5">
-        <v>46182.59318215278</v>
+        <v>46182.75984881945</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>174</v>
@@ -4570,11 +4569,11 @@
         <v>188</v>
       </c>
       <c r="B53" s="8">
-        <v>46169.3918991088</v>
+        <v>46169.558565775464</v>
       </c>
       <c r="C53" s="9"/>
       <c r="D53" s="8">
-        <v>46169.4521927662</v>
+        <v>46169.61885943287</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>189</v>
@@ -4633,11 +4632,11 @@
         <v>192</v>
       </c>
       <c r="B54" s="5">
-        <v>46169.391903055555</v>
+        <v>46169.55856972223</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46169.45215946759</v>
+        <v>46169.61882613426</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>174</v>
@@ -4670,10 +4669,10 @@
         <v>189</v>
       </c>
       <c r="O54" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="P54" s="6" t="s">
         <v>193</v>
-      </c>
-      <c r="P54" s="6" t="s">
-        <v>194</v>
       </c>
       <c r="Q54" s="6"/>
       <c r="R54" s="6"/>
@@ -4683,19 +4682,19 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="B55" s="8">
+        <v>46169.558586307874</v>
+      </c>
+      <c r="C55" s="8">
+        <v>46198.59773380787</v>
+      </c>
+      <c r="D55" s="8">
+        <v>46198.597746307874</v>
+      </c>
+      <c r="E55" s="9" t="s">
         <v>195</v>
-      </c>
-      <c r="B55" s="8">
-        <v>46169.3919196412</v>
-      </c>
-      <c r="C55" s="8">
-        <v>46198.4310671412</v>
-      </c>
-      <c r="D55" s="8">
-        <v>46198.4310796412</v>
-      </c>
-      <c r="E55" s="9" t="s">
-        <v>196</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>25</v>
@@ -4719,7 +4718,7 @@
         <v>26</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P55" s="9" t="s">
         <v>26</v>
@@ -4736,28 +4735,28 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="B56" s="5">
+        <v>46169.55858945602</v>
+      </c>
+      <c r="C56" s="5">
+        <v>46190.64495354166</v>
+      </c>
+      <c r="D56" s="5">
+        <v>46197.83559606482</v>
+      </c>
+      <c r="E56" s="6" t="s">
         <v>198</v>
       </c>
-      <c r="B56" s="5">
-        <v>46169.39192278935</v>
-      </c>
-      <c r="C56" s="5">
-        <v>46190.478286875004</v>
-      </c>
-      <c r="D56" s="5">
-        <v>46197.66892939815</v>
-      </c>
-      <c r="E56" s="6" t="s">
+      <c r="F56" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G56" s="6" t="s">
         <v>199</v>
       </c>
-      <c r="F56" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G56" s="6" t="s">
+      <c r="H56" s="6" t="s">
         <v>200</v>
-      </c>
-      <c r="H56" s="6" t="s">
-        <v>201</v>
       </c>
       <c r="I56" s="5">
         <v>46254</v>
@@ -4775,13 +4774,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="O56" s="6" t="s">
         <v>134</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="Q56" s="5">
         <v>46254</v>
@@ -4801,19 +4800,19 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="B57" s="8">
+        <v>46169.55859488426</v>
+      </c>
+      <c r="C57" s="8">
+        <v>46197.85935881945</v>
+      </c>
+      <c r="D57" s="8">
+        <v>46197.85937331019</v>
+      </c>
+      <c r="E57" s="9" t="s">
         <v>203</v>
-      </c>
-      <c r="B57" s="8">
-        <v>46169.39192821759</v>
-      </c>
-      <c r="C57" s="8">
-        <v>46197.69269215278</v>
-      </c>
-      <c r="D57" s="8">
-        <v>46197.69270664352</v>
-      </c>
-      <c r="E57" s="9" t="s">
-        <v>204</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
@@ -4840,13 +4839,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="Q57" s="8">
         <v>46258</v>
@@ -4866,28 +4865,28 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="B58" s="5">
+        <v>46169.55860118056</v>
+      </c>
+      <c r="C58" s="5">
+        <v>46198.597692881944</v>
+      </c>
+      <c r="D58" s="5">
+        <v>46198.59771457176</v>
+      </c>
+      <c r="E58" s="6" t="s">
         <v>206</v>
       </c>
-      <c r="B58" s="5">
-        <v>46169.391934513886</v>
-      </c>
-      <c r="C58" s="5">
-        <v>46198.43102621528</v>
-      </c>
-      <c r="D58" s="5">
-        <v>46198.43104790509</v>
-      </c>
-      <c r="E58" s="6" t="s">
-        <v>207</v>
-      </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="H58" s="6" t="s">
         <v>200</v>
-      </c>
-      <c r="H58" s="6" t="s">
-        <v>201</v>
       </c>
       <c r="I58" s="5">
         <v>46254</v>
@@ -4905,13 +4904,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="O58" s="6" t="s">
         <v>142</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="Q58" s="5">
         <v>46254</v>
@@ -4931,19 +4930,19 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B59" s="8">
-        <v>46169.391939699075</v>
+        <v>46169.55860636574</v>
       </c>
       <c r="C59" s="8">
-        <v>46197.692646435185</v>
+        <v>46197.85931310186</v>
       </c>
       <c r="D59" s="8">
-        <v>46198.43104277778</v>
+        <v>46198.597709444446</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
@@ -4970,10 +4969,10 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P59" s="9" t="s">
         <v>174</v>
@@ -4996,28 +4995,28 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="B60" s="5">
+        <v>46169.558650127314</v>
+      </c>
+      <c r="C60" s="5">
+        <v>46198.59771644676</v>
+      </c>
+      <c r="D60" s="5">
+        <v>46198.59773310185</v>
+      </c>
+      <c r="E60" s="6" t="s">
         <v>210</v>
       </c>
-      <c r="B60" s="5">
-        <v>46169.39198346065</v>
-      </c>
-      <c r="C60" s="5">
-        <v>46198.43104978009</v>
-      </c>
-      <c r="D60" s="5">
-        <v>46198.43106643519</v>
-      </c>
-      <c r="E60" s="6" t="s">
-        <v>211</v>
-      </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="H60" s="6" t="s">
         <v>200</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>201</v>
       </c>
       <c r="I60" s="5">
         <v>46254</v>
@@ -5035,13 +5034,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="O60" s="6" t="s">
         <v>164</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="Q60" s="5">
         <v>46254</v>
@@ -5061,19 +5060,19 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B61" s="8">
-        <v>46169.391989421296</v>
+        <v>46169.55865608796</v>
       </c>
       <c r="C61" s="8">
-        <v>46197.69257320602</v>
+        <v>46197.85923987269</v>
       </c>
       <c r="D61" s="8">
-        <v>46198.43106650463</v>
+        <v>46198.59773317129</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
@@ -5100,10 +5099,10 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P61" s="9" t="s">
         <v>174</v>
@@ -5126,19 +5125,19 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="B62" s="5">
+        <v>46169.55866105324</v>
+      </c>
+      <c r="C62" s="5">
+        <v>46198.682278935186</v>
+      </c>
+      <c r="D62" s="5">
+        <v>46198.68229049769</v>
+      </c>
+      <c r="E62" s="6" t="s">
         <v>214</v>
-      </c>
-      <c r="B62" s="5">
-        <v>46169.39199438658</v>
-      </c>
-      <c r="C62" s="5">
-        <v>46198.515612268515</v>
-      </c>
-      <c r="D62" s="5">
-        <v>46198.515623831016</v>
-      </c>
-      <c r="E62" s="6" t="s">
-        <v>215</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>25</v>
@@ -5162,7 +5161,7 @@
         <v>26</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P62" s="6" t="s">
         <v>26</v>
@@ -5179,28 +5178,28 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="B63" s="8">
+        <v>46169.55866469907</v>
+      </c>
+      <c r="C63" s="8">
+        <v>46190.645243935185</v>
+      </c>
+      <c r="D63" s="8">
+        <v>46197.85915361111</v>
+      </c>
+      <c r="E63" s="9" t="s">
         <v>217</v>
       </c>
-      <c r="B63" s="8">
-        <v>46169.391998032406</v>
-      </c>
-      <c r="C63" s="8">
-        <v>46190.47857726851</v>
-      </c>
-      <c r="D63" s="8">
-        <v>46197.69248694445</v>
-      </c>
-      <c r="E63" s="9" t="s">
+      <c r="F63" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G63" s="9" t="s">
         <v>218</v>
       </c>
-      <c r="F63" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G63" s="9" t="s">
+      <c r="H63" s="9" t="s">
         <v>219</v>
-      </c>
-      <c r="H63" s="9" t="s">
-        <v>220</v>
       </c>
       <c r="I63" s="8">
         <v>46260</v>
@@ -5218,13 +5217,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="P63" s="9" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="Q63" s="8">
         <v>46260</v>
@@ -5244,16 +5243,16 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B64" s="5">
-        <v>46169.39200432871</v>
+        <v>46169.55867099537</v>
       </c>
       <c r="C64" s="5">
-        <v>46197.69248021991</v>
+        <v>46197.85914688658</v>
       </c>
       <c r="D64" s="5">
-        <v>46197.69270006944</v>
+        <v>46197.85936673611</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>174</v>
@@ -5262,10 +5261,10 @@
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="H64" s="6" t="s">
         <v>219</v>
-      </c>
-      <c r="H64" s="6" t="s">
-        <v>220</v>
       </c>
       <c r="I64" s="5">
         <v>46260</v>
@@ -5283,13 +5282,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="O64" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="P64" s="6" t="s">
         <v>223</v>
-      </c>
-      <c r="P64" s="6" t="s">
-        <v>224</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5299,28 +5298,28 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
+        <v>224</v>
+      </c>
+      <c r="B65" s="8">
+        <v>46169.558703518516</v>
+      </c>
+      <c r="C65" s="8">
+        <v>46190.64532476851</v>
+      </c>
+      <c r="D65" s="8">
+        <v>46197.85387390046</v>
+      </c>
+      <c r="E65" s="9" t="s">
         <v>225</v>
       </c>
-      <c r="B65" s="8">
-        <v>46169.39203685185</v>
-      </c>
-      <c r="C65" s="8">
-        <v>46190.478658101856</v>
-      </c>
-      <c r="D65" s="8">
-        <v>46197.6872072338</v>
-      </c>
-      <c r="E65" s="9" t="s">
-        <v>226</v>
-      </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="H65" s="9" t="s">
         <v>219</v>
-      </c>
-      <c r="H65" s="9" t="s">
-        <v>220</v>
       </c>
       <c r="I65" s="8">
         <v>46269</v>
@@ -5338,13 +5337,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="O65" s="9" t="s">
         <v>174</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="Q65" s="8">
         <v>46269</v>
@@ -5364,16 +5363,16 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B66" s="5">
-        <v>46169.39204212963</v>
+        <v>46169.55870879629</v>
       </c>
       <c r="C66" s="5">
-        <v>46197.68718994213</v>
+        <v>46197.853856608795</v>
       </c>
       <c r="D66" s="5">
-        <v>46197.69248753472</v>
+        <v>46197.85915420139</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>174</v>
@@ -5382,10 +5381,10 @@
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="H66" s="6" t="s">
         <v>219</v>
-      </c>
-      <c r="H66" s="6" t="s">
-        <v>220</v>
       </c>
       <c r="I66" s="5">
         <v>46269</v>
@@ -5403,13 +5402,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="O66" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="P66" s="6" t="s">
         <v>228</v>
-      </c>
-      <c r="P66" s="6" t="s">
-        <v>229</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5419,19 +5418,19 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="B67" s="8">
+        <v>46169.558740625</v>
+      </c>
+      <c r="C67" s="8">
+        <v>46198.68226086805</v>
+      </c>
+      <c r="D67" s="8">
+        <v>46198.68228008102</v>
+      </c>
+      <c r="E67" s="9" t="s">
         <v>230</v>
-      </c>
-      <c r="B67" s="8">
-        <v>46169.392073958334</v>
-      </c>
-      <c r="C67" s="8">
-        <v>46198.51559420139</v>
-      </c>
-      <c r="D67" s="8">
-        <v>46198.51561341435</v>
-      </c>
-      <c r="E67" s="9" t="s">
-        <v>231</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
@@ -5458,13 +5457,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="O67" s="9" t="s">
         <v>174</v>
       </c>
       <c r="P67" s="9" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="Q67" s="8">
         <v>46274</v>
@@ -5484,14 +5483,14 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B68" s="5">
-        <v>46169.39207857639</v>
+        <v>46169.558745243055</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46197.68719728009</v>
+        <v>46197.85386394676</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>174</v>
@@ -5521,13 +5520,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q68" s="6"/>
       <c r="R68" s="6"/>
@@ -5537,17 +5536,19 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B69" s="8">
-        <v>46169.392102812504</v>
-      </c>
-      <c r="C69" s="9"/>
+        <v>46169.55876947917</v>
+      </c>
+      <c r="C69" s="8">
+        <v>46205.60074232639</v>
+      </c>
       <c r="D69" s="8">
-        <v>46200.65303918981</v>
+        <v>46205.60075471065</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>25</v>
@@ -5571,7 +5572,7 @@
         <v>26</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="P69" s="9" t="s">
         <v>26</v>
@@ -5579,35 +5580,37 @@
       <c r="Q69" s="9"/>
       <c r="R69" s="9"/>
       <c r="S69" s="9"/>
-      <c r="T69" s="9"/>
-      <c r="U69" s="12" t="s">
-        <v>169</v>
+      <c r="T69" s="9">
+        <v>1</v>
+      </c>
+      <c r="U69" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="B70" s="5">
+        <v>46169.55880633101</v>
+      </c>
+      <c r="C70" s="5">
+        <v>46200.81968587963</v>
+      </c>
+      <c r="D70" s="5">
+        <v>46200.8197621875</v>
+      </c>
+      <c r="E70" s="6" t="s">
         <v>236</v>
       </c>
-      <c r="B70" s="5">
-        <v>46169.39213966436</v>
-      </c>
-      <c r="C70" s="5">
-        <v>46200.65301921296</v>
-      </c>
-      <c r="D70" s="5">
-        <v>46200.65309552083</v>
-      </c>
-      <c r="E70" s="6" t="s">
-        <v>237</v>
-      </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="H70" s="6" t="s">
         <v>200</v>
-      </c>
-      <c r="H70" s="6" t="s">
-        <v>201</v>
       </c>
       <c r="I70" s="5">
         <v>46220</v>
@@ -5625,13 +5628,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="O70" s="6" t="s">
         <v>111</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="Q70" s="5">
         <v>46220</v>
@@ -5651,28 +5654,28 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="B71" s="8">
+        <v>46169.5588177662</v>
+      </c>
+      <c r="C71" s="8">
+        <v>46200.81967096065</v>
+      </c>
+      <c r="D71" s="8">
+        <v>46200.819831597226</v>
+      </c>
+      <c r="E71" s="9" t="s">
         <v>239</v>
       </c>
-      <c r="B71" s="8">
-        <v>46169.39215109954</v>
-      </c>
-      <c r="C71" s="8">
-        <v>46200.653004293985</v>
-      </c>
-      <c r="D71" s="8">
-        <v>46200.653164930554</v>
-      </c>
-      <c r="E71" s="9" t="s">
-        <v>240</v>
-      </c>
       <c r="F71" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="H71" s="9" t="s">
         <v>200</v>
-      </c>
-      <c r="H71" s="9" t="s">
-        <v>201</v>
       </c>
       <c r="I71" s="8">
         <v>46325</v>
@@ -5690,13 +5693,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="O71" s="9" t="s">
         <v>102</v>
       </c>
       <c r="P71" s="9" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="Q71" s="8">
         <v>46325</v>
@@ -5716,28 +5719,28 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="B72" s="5">
+        <v>46169.55882295139</v>
+      </c>
+      <c r="C72" s="5">
+        <v>46200.819208981484</v>
+      </c>
+      <c r="D72" s="5">
+        <v>46200.81928909722</v>
+      </c>
+      <c r="E72" s="6" t="s">
         <v>242</v>
       </c>
-      <c r="B72" s="5">
-        <v>46169.392156284724</v>
-      </c>
-      <c r="C72" s="5">
-        <v>46200.65254231481</v>
-      </c>
-      <c r="D72" s="5">
-        <v>46200.652622430556</v>
-      </c>
-      <c r="E72" s="6" t="s">
-        <v>243</v>
-      </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="H72" s="6" t="s">
         <v>200</v>
-      </c>
-      <c r="H72" s="6" t="s">
-        <v>201</v>
       </c>
       <c r="I72" s="5">
         <v>46293</v>
@@ -5755,13 +5758,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="O72" s="6" t="s">
         <v>120</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="Q72" s="5">
         <v>46293</v>
@@ -5781,26 +5784,28 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
+        <v>243</v>
+      </c>
+      <c r="B73" s="8">
+        <v>46169.55882788195</v>
+      </c>
+      <c r="C73" s="8">
+        <v>46205.60072428241</v>
+      </c>
+      <c r="D73" s="8">
+        <v>46205.60074188658</v>
+      </c>
+      <c r="E73" s="9" t="s">
         <v>244</v>
       </c>
-      <c r="B73" s="8">
-        <v>46169.39216121528</v>
-      </c>
-      <c r="C73" s="9"/>
-      <c r="D73" s="8">
-        <v>46195.5371079051</v>
-      </c>
-      <c r="E73" s="9" t="s">
-        <v>245</v>
-      </c>
       <c r="F73" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="H73" s="9" t="s">
         <v>200</v>
-      </c>
-      <c r="H73" s="9" t="s">
-        <v>201</v>
       </c>
       <c r="I73" s="8">
         <v>46282</v>
@@ -5818,13 +5823,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="9" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="O73" s="9" t="s">
         <v>152</v>
       </c>
       <c r="P73" s="9" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="Q73" s="8">
         <v>46282</v>
@@ -5836,25 +5841,25 @@
         <v>32</v>
       </c>
       <c r="T73" s="9">
-        <v>0</v>
-      </c>
-      <c r="U73" s="12" t="s">
-        <v>169</v>
+        <v>1</v>
+      </c>
+      <c r="U73" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B74" s="5">
-        <v>46169.392175879635</v>
+        <v>46169.55884254629</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46204.71326887731</v>
+        <v>46204.879935543984</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>25</v>
@@ -5878,7 +5883,7 @@
         <v>26</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="P74" s="6" t="s">
         <v>26</v>
@@ -5891,19 +5896,19 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="B75" s="8">
+        <v>46169.55884548611</v>
+      </c>
+      <c r="C75" s="8">
+        <v>46197.49536869213</v>
+      </c>
+      <c r="D75" s="8">
+        <v>46205.6007421875</v>
+      </c>
+      <c r="E75" s="9" t="s">
         <v>250</v>
-      </c>
-      <c r="B75" s="8">
-        <v>46169.39217881944</v>
-      </c>
-      <c r="C75" s="8">
-        <v>46197.328702025465</v>
-      </c>
-      <c r="D75" s="8">
-        <v>46197.32871296296</v>
-      </c>
-      <c r="E75" s="9" t="s">
-        <v>251</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
@@ -5930,13 +5935,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="Q75" s="8">
         <v>46276</v>
@@ -5950,22 +5955,22 @@
       <c r="T75" s="9">
         <v>1</v>
       </c>
-      <c r="U75" s="10" t="s">
-        <v>33</v>
+      <c r="U75" s="12" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B76" s="5">
-        <v>46169.39218326389</v>
+        <v>46169.55884993056</v>
       </c>
       <c r="C76" s="5">
-        <v>46197.32868986111</v>
+        <v>46197.49535652778</v>
       </c>
       <c r="D76" s="5">
-        <v>46197.32869122685</v>
+        <v>46205.600734074076</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>174</v>
@@ -5995,13 +6000,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -6011,19 +6016,19 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="B77" s="8">
+        <v>46169.55893170139</v>
+      </c>
+      <c r="C77" s="8">
+        <v>46197.49516923611</v>
+      </c>
+      <c r="D77" s="8">
+        <v>46197.495185555556</v>
+      </c>
+      <c r="E77" s="9" t="s">
         <v>255</v>
-      </c>
-      <c r="B77" s="8">
-        <v>46169.39226503472</v>
-      </c>
-      <c r="C77" s="8">
-        <v>46197.32850256945</v>
-      </c>
-      <c r="D77" s="8">
-        <v>46197.328518888884</v>
-      </c>
-      <c r="E77" s="9" t="s">
-        <v>256</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>26</v>
@@ -6050,13 +6055,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="O77" s="9" t="s">
         <v>174</v>
       </c>
       <c r="P77" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="Q77" s="8">
         <v>46296</v>
@@ -6076,16 +6081,16 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B78" s="5">
-        <v>46169.39226877315</v>
+        <v>46169.55893543981</v>
       </c>
       <c r="C78" s="5">
-        <v>46197.328487349536</v>
+        <v>46197.4951540162</v>
       </c>
       <c r="D78" s="5">
-        <v>46204.713258171294</v>
+        <v>46204.879924837966</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>174</v>
@@ -6115,13 +6120,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="O78" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="P78" s="6" t="s">
         <v>258</v>
-      </c>
-      <c r="P78" s="6" t="s">
-        <v>259</v>
       </c>
       <c r="Q78" s="6"/>
       <c r="R78" s="6"/>
@@ -6131,19 +6136,19 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
+        <v>259</v>
+      </c>
+      <c r="B79" s="8">
+        <v>46169.558869560184</v>
+      </c>
+      <c r="C79" s="8">
+        <v>46204.87979715278</v>
+      </c>
+      <c r="D79" s="8">
+        <v>46204.87981377315</v>
+      </c>
+      <c r="E79" s="9" t="s">
         <v>260</v>
-      </c>
-      <c r="B79" s="8">
-        <v>46169.39220289352</v>
-      </c>
-      <c r="C79" s="8">
-        <v>46204.71313048611</v>
-      </c>
-      <c r="D79" s="8">
-        <v>46204.71314710648</v>
-      </c>
-      <c r="E79" s="9" t="s">
-        <v>261</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>26</v>
@@ -6170,13 +6175,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>193</v>
+        <v>261</v>
       </c>
       <c r="P79" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="Q79" s="8">
         <v>46328</v>
@@ -6199,16 +6204,16 @@
         <v>262</v>
       </c>
       <c r="B80" s="5">
-        <v>46169.392206296296</v>
+        <v>46169.55887296297</v>
       </c>
       <c r="C80" s="5">
-        <v>46204.71311386574</v>
+        <v>46204.87978053241</v>
       </c>
       <c r="D80" s="5">
-        <v>46204.71311643519</v>
+        <v>46204.87978310185</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>193</v>
+        <v>261</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
@@ -6235,7 +6240,7 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="O80" s="6" t="s">
         <v>263</v>
@@ -6254,13 +6259,13 @@
         <v>265</v>
       </c>
       <c r="B81" s="8">
-        <v>46169.392235879626</v>
+        <v>46169.5589025463</v>
       </c>
       <c r="C81" s="8">
-        <v>46204.713261550925</v>
+        <v>46204.87992821759</v>
       </c>
       <c r="D81" s="8">
-        <v>46204.71339034722</v>
+        <v>46204.880057013885</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>266</v>
@@ -6290,13 +6295,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="O81" s="9" t="s">
         <v>174</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="Q81" s="8">
         <v>46329</v>
@@ -6319,13 +6324,13 @@
         <v>267</v>
       </c>
       <c r="B82" s="5">
-        <v>46169.39223943287</v>
+        <v>46169.55890609954</v>
       </c>
       <c r="C82" s="5">
-        <v>46204.71324887731</v>
+        <v>46204.87991554398</v>
       </c>
       <c r="D82" s="5">
-        <v>46204.71325045139</v>
+        <v>46204.87991711806</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>174</v>
@@ -6374,11 +6379,11 @@
         <v>270</v>
       </c>
       <c r="B83" s="8">
-        <v>46169.3923377662</v>
+        <v>46169.55900443287</v>
       </c>
       <c r="C83" s="9"/>
       <c r="D83" s="8">
-        <v>46204.7137212963</v>
+        <v>46205.60103440972</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>271</v>
@@ -6408,13 +6413,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="O83" s="9" t="s">
-        <v>193</v>
+        <v>174</v>
       </c>
       <c r="P83" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="Q83" s="8">
         <v>46330</v>
@@ -6437,14 +6442,14 @@
         <v>272</v>
       </c>
       <c r="B84" s="5">
-        <v>46169.39234335648</v>
+        <v>46169.55901002315</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46197.3284933449</v>
+        <v>46205.59815806713</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>193</v>
+        <v>174</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
@@ -6490,11 +6495,11 @@
         <v>274</v>
       </c>
       <c r="B85" s="8">
-        <v>46169.39237796296</v>
+        <v>46169.55904462963</v>
       </c>
       <c r="C85" s="9"/>
       <c r="D85" s="8">
-        <v>46169.454865057865</v>
+        <v>46169.62153172454</v>
       </c>
       <c r="E85" s="9" t="s">
         <v>275</v>
@@ -6524,10 +6529,10 @@
         <v>26</v>
       </c>
       <c r="N85" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="O85" s="9" t="s">
-        <v>193</v>
+        <v>261</v>
       </c>
       <c r="P85" s="9" t="s">
         <v>276</v>
@@ -6553,14 +6558,14 @@
         <v>277</v>
       </c>
       <c r="B86" s="5">
-        <v>46169.39238347222</v>
+        <v>46169.559050138894</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46169.454824872686</v>
+        <v>46169.62149153935</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>193</v>
+        <v>261</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6606,11 +6611,11 @@
         <v>279</v>
       </c>
       <c r="B87" s="8">
-        <v>46169.39240818287</v>
+        <v>46169.55907484954</v>
       </c>
       <c r="C87" s="9"/>
       <c r="D87" s="8">
-        <v>46197.692956238425</v>
+        <v>46197.85962290509</v>
       </c>
       <c r="E87" s="9" t="s">
         <v>280</v>
@@ -6653,11 +6658,11 @@
         <v>282</v>
       </c>
       <c r="B88" s="5">
-        <v>46169.392411967594</v>
+        <v>46169.55907863426</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46169.45497726851</v>
+        <v>46169.621643935185</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>283</v>
@@ -6716,14 +6721,14 @@
         <v>286</v>
       </c>
       <c r="B89" s="8">
-        <v>46169.39242017361</v>
+        <v>46169.55908684028</v>
       </c>
       <c r="C89" s="9"/>
       <c r="D89" s="8">
-        <v>46169.4549275926</v>
+        <v>46205.59791611111</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>193</v>
+        <v>174</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>26</v>
@@ -6753,7 +6758,7 @@
         <v>283</v>
       </c>
       <c r="O89" s="9" t="s">
-        <v>193</v>
+        <v>261</v>
       </c>
       <c r="P89" s="9" t="s">
         <v>287</v>
@@ -6769,11 +6774,11 @@
         <v>288</v>
       </c>
       <c r="B90" s="5">
-        <v>46169.39252006944</v>
+        <v>46169.55918673611</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46196.39502256944</v>
+        <v>46196.561689236114</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>289</v>
@@ -6806,7 +6811,7 @@
         <v>280</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>193</v>
+        <v>174</v>
       </c>
       <c r="P90" s="6" t="s">
         <v>280</v>
@@ -6832,14 +6837,14 @@
         <v>290</v>
       </c>
       <c r="B91" s="8">
-        <v>46169.39252446759</v>
+        <v>46169.55919113426</v>
       </c>
       <c r="C91" s="9"/>
       <c r="D91" s="8">
-        <v>46169.45502662037</v>
+        <v>46205.597946215275</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>193</v>
+        <v>174</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>26</v>
@@ -6869,7 +6874,7 @@
         <v>289</v>
       </c>
       <c r="O91" s="9" t="s">
-        <v>193</v>
+        <v>174</v>
       </c>
       <c r="P91" s="9" t="s">
         <v>291</v>
@@ -6885,13 +6890,13 @@
         <v>292</v>
       </c>
       <c r="B92" s="5">
-        <v>46169.392572893514</v>
+        <v>46169.559239560185</v>
       </c>
       <c r="C92" s="5">
-        <v>46197.69295070602</v>
+        <v>46197.859617372684</v>
       </c>
       <c r="D92" s="5">
-        <v>46197.69315269676</v>
+        <v>46197.859819363424</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>293</v>
@@ -6900,10 +6905,10 @@
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="H92" s="6" t="s">
         <v>219</v>
-      </c>
-      <c r="H92" s="6" t="s">
-        <v>220</v>
       </c>
       <c r="I92" s="5">
         <v>46337</v>
@@ -6924,7 +6929,7 @@
         <v>280</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>193</v>
+        <v>174</v>
       </c>
       <c r="P92" s="6" t="s">
         <v>280</v>
@@ -6950,25 +6955,25 @@
         <v>294</v>
       </c>
       <c r="B93" s="8">
-        <v>46169.392577175924</v>
+        <v>46169.559243842596</v>
       </c>
       <c r="C93" s="8">
-        <v>46197.69313659723</v>
+        <v>46197.859803263884</v>
       </c>
       <c r="D93" s="8">
-        <v>46197.69313804398</v>
+        <v>46205.597989988426</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>193</v>
+        <v>174</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="H93" s="9" t="s">
         <v>219</v>
-      </c>
-      <c r="H93" s="9" t="s">
-        <v>220</v>
       </c>
       <c r="I93" s="8">
         <v>46337</v>
@@ -6989,7 +6994,7 @@
         <v>293</v>
       </c>
       <c r="O93" s="9" t="s">
-        <v>193</v>
+        <v>174</v>
       </c>
       <c r="P93" s="9" t="s">
         <v>295</v>
@@ -7005,11 +7010,11 @@
         <v>296</v>
       </c>
       <c r="B94" s="5">
-        <v>46169.39263019676</v>
+        <v>46169.55929686343</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46196.406644675924</v>
+        <v>46196.573311342596</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>297</v>
@@ -7018,10 +7023,10 @@
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="H94" s="6" t="s">
         <v>219</v>
-      </c>
-      <c r="H94" s="6" t="s">
-        <v>220</v>
       </c>
       <c r="I94" s="5">
         <v>46338</v>
@@ -7042,10 +7047,10 @@
         <v>280</v>
       </c>
       <c r="O94" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="P94" s="6" t="s">
         <v>298</v>
-      </c>
-      <c r="P94" s="6" t="s">
-        <v>299</v>
       </c>
       <c r="Q94" s="5">
         <v>46338</v>
@@ -7065,26 +7070,26 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B95" s="8">
-        <v>46169.39263513889</v>
+        <v>46169.55930180555</v>
       </c>
       <c r="C95" s="9"/>
       <c r="D95" s="8">
-        <v>46197.69314296296</v>
+        <v>46205.598038449076</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>298</v>
+        <v>174</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="H95" s="9" t="s">
         <v>219</v>
-      </c>
-      <c r="H95" s="9" t="s">
-        <v>220</v>
       </c>
       <c r="I95" s="8">
         <v>46338</v>
@@ -7105,7 +7110,7 @@
         <v>297</v>
       </c>
       <c r="O95" s="9" t="s">
-        <v>193</v>
+        <v>174</v>
       </c>
       <c r="P95" s="9" t="s">
         <v>297</v>
@@ -7118,17 +7123,17 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B96" s="5">
-        <v>46169.39272054398</v>
+        <v>46169.55938721065</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46169.440061562505</v>
+        <v>46169.60672822916</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>25</v>
@@ -7152,7 +7157,7 @@
         <v>26</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P96" s="6" t="s">
         <v>26</v>
@@ -7165,26 +7170,26 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B97" s="8">
-        <v>46169.39272428241</v>
+        <v>46169.55939094907</v>
       </c>
       <c r="C97" s="9"/>
       <c r="D97" s="8">
-        <v>46169.45532454861</v>
+        <v>46169.621991215274</v>
       </c>
       <c r="E97" s="9" t="s">
+        <v>304</v>
+      </c>
+      <c r="F97" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G97" s="9" t="s">
         <v>305</v>
       </c>
-      <c r="F97" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G97" s="9" t="s">
+      <c r="H97" s="9" t="s">
         <v>306</v>
-      </c>
-      <c r="H97" s="9" t="s">
-        <v>307</v>
       </c>
       <c r="I97" s="8">
         <v>46339</v>
@@ -7202,13 +7207,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="9" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="O97" s="9" t="s">
         <v>297</v>
       </c>
       <c r="P97" s="9" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="Q97" s="8">
         <v>46339</v>
@@ -7228,17 +7233,17 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B98" s="5">
-        <v>46169.392729768515</v>
+        <v>46169.55939643519</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46196.639006956015</v>
+        <v>46196.805673622686</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -7265,13 +7270,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="O98" s="6" t="s">
         <v>297</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="Q98" s="5">
         <v>46339</v>

--- a/data/50001557 - ATACAMA KOZAN OT4340.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4340.xlsx
@@ -5427,7 +5427,7 @@
         <v>46198.68226086805</v>
       </c>
       <c r="D67" s="8">
-        <v>46198.68228008102</v>
+        <v>46205.65959174768</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>230</v>
@@ -5477,8 +5477,8 @@
       <c r="T67" s="9">
         <v>1</v>
       </c>
-      <c r="U67" s="10" t="s">
-        <v>33</v>
+      <c r="U67" s="12" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
@@ -5488,9 +5488,11 @@
       <c r="B68" s="5">
         <v>46169.558745243055</v>
       </c>
-      <c r="C68" s="6"/>
+      <c r="C68" s="5">
+        <v>46205.659586458336</v>
+      </c>
       <c r="D68" s="5">
-        <v>46197.85386394676</v>
+        <v>46205.659588587965</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>174</v>
@@ -5789,11 +5791,9 @@
       <c r="B73" s="8">
         <v>46169.55882788195</v>
       </c>
-      <c r="C73" s="8">
-        <v>46205.60072428241</v>
-      </c>
+      <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46205.60074188658</v>
+        <v>46205.64471479166</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>244</v>
@@ -5841,7 +5841,7 @@
         <v>32</v>
       </c>
       <c r="T73" s="9">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="U73" s="10" t="s">
         <v>33</v>
@@ -5905,7 +5905,7 @@
         <v>46197.49536869213</v>
       </c>
       <c r="D75" s="8">
-        <v>46205.6007421875</v>
+        <v>46205.644681192134</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>250</v>
@@ -5970,7 +5970,7 @@
         <v>46197.49535652778</v>
       </c>
       <c r="D76" s="5">
-        <v>46205.600734074076</v>
+        <v>46205.659593136574</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>174</v>

--- a/data/50001557 - ATACAMA KOZAN OT4340.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4340.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1183" uniqueCount="309">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1184" uniqueCount="309">
   <si>
     <t xml:space="preserve"> 50001557 - ATACAMA KOZAN</t>
   </si>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46169.61882613426</v>
+        <v>46206.486704027775</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>174</v>
@@ -5856,7 +5856,7 @@
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46204.879935543984</v>
+        <v>46206.48683333333</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>247</v>
@@ -5892,7 +5892,9 @@
       <c r="R74" s="6"/>
       <c r="S74" s="6"/>
       <c r="T74" s="6"/>
-      <c r="U74" s="6"/>
+      <c r="U74" s="12" t="s">
+        <v>169</v>
+      </c>
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
@@ -6381,9 +6383,11 @@
       <c r="B83" s="8">
         <v>46169.55900443287</v>
       </c>
-      <c r="C83" s="9"/>
+      <c r="C83" s="8">
+        <v>46206.4867090162</v>
+      </c>
       <c r="D83" s="8">
-        <v>46205.60103440972</v>
+        <v>46206.48671975694</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>271</v>
@@ -6431,10 +6435,10 @@
         <v>32</v>
       </c>
       <c r="T83" s="9">
-        <v>0</v>
-      </c>
-      <c r="U83" s="11" t="s">
-        <v>100</v>
+        <v>1</v>
+      </c>
+      <c r="U83" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
@@ -6444,9 +6448,11 @@
       <c r="B84" s="5">
         <v>46169.55901002315</v>
       </c>
-      <c r="C84" s="6"/>
+      <c r="C84" s="5">
+        <v>46206.48669384259</v>
+      </c>
       <c r="D84" s="5">
-        <v>46205.59815806713</v>
+        <v>46206.48669563657</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>174</v>
@@ -6497,9 +6503,11 @@
       <c r="B85" s="8">
         <v>46169.55904462963</v>
       </c>
-      <c r="C85" s="9"/>
+      <c r="C85" s="8">
+        <v>46206.48680728009</v>
+      </c>
       <c r="D85" s="8">
-        <v>46169.62153172454</v>
+        <v>46206.48682021991</v>
       </c>
       <c r="E85" s="9" t="s">
         <v>275</v>
@@ -6547,10 +6555,10 @@
         <v>32</v>
       </c>
       <c r="T85" s="9">
-        <v>0</v>
-      </c>
-      <c r="U85" s="11" t="s">
-        <v>100</v>
+        <v>1</v>
+      </c>
+      <c r="U85" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
@@ -6560,9 +6568,11 @@
       <c r="B86" s="5">
         <v>46169.559050138894</v>
       </c>
-      <c r="C86" s="6"/>
+      <c r="C86" s="5">
+        <v>46206.486792916665</v>
+      </c>
       <c r="D86" s="5">
-        <v>46169.62149153935</v>
+        <v>46206.48679516204</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>261</v>
@@ -6662,7 +6672,7 @@
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46169.621643935185</v>
+        <v>46206.486817604164</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>283</v>
@@ -6725,7 +6735,7 @@
       </c>
       <c r="C89" s="9"/>
       <c r="D89" s="8">
-        <v>46205.59791611111</v>
+        <v>46206.48680179398</v>
       </c>
       <c r="E89" s="9" t="s">
         <v>174</v>

--- a/data/50001557 - ATACAMA KOZAN OT4340.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4340.xlsx
@@ -6735,7 +6735,7 @@
       </c>
       <c r="C89" s="9"/>
       <c r="D89" s="8">
-        <v>46206.48680179398</v>
+        <v>46210.698995046296</v>
       </c>
       <c r="E89" s="9" t="s">
         <v>174</v>

--- a/data/50001557 - ATACAMA KOZAN OT4340.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4340.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1184" uniqueCount="309">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1183" uniqueCount="309">
   <si>
     <t xml:space="preserve"> 50001557 - ATACAMA KOZAN</t>
   </si>
@@ -5547,7 +5547,7 @@
         <v>46205.60074232639</v>
       </c>
       <c r="D69" s="8">
-        <v>46205.60075471065</v>
+        <v>46211.70953918982</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>195</v>
@@ -5582,12 +5582,8 @@
       <c r="Q69" s="9"/>
       <c r="R69" s="9"/>
       <c r="S69" s="9"/>
-      <c r="T69" s="9">
-        <v>1</v>
-      </c>
-      <c r="U69" s="10" t="s">
-        <v>33</v>
-      </c>
+      <c r="T69" s="9"/>
+      <c r="U69" s="9"/>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
@@ -5791,9 +5787,11 @@
       <c r="B73" s="8">
         <v>46169.55882788195</v>
       </c>
-      <c r="C73" s="9"/>
+      <c r="C73" s="8">
+        <v>46211.70928436343</v>
+      </c>
       <c r="D73" s="8">
-        <v>46205.64471479166</v>
+        <v>46211.7093043287</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>244</v>
@@ -5841,7 +5839,7 @@
         <v>32</v>
       </c>
       <c r="T73" s="9">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="U73" s="10" t="s">
         <v>33</v>
@@ -5907,7 +5905,7 @@
         <v>46197.49536869213</v>
       </c>
       <c r="D75" s="8">
-        <v>46205.644681192134</v>
+        <v>46211.70929236111</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>250</v>
@@ -5972,7 +5970,7 @@
         <v>46197.49535652778</v>
       </c>
       <c r="D76" s="5">
-        <v>46205.659593136574</v>
+        <v>46211.70929407407</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>174</v>
@@ -6625,7 +6623,7 @@
       </c>
       <c r="C87" s="9"/>
       <c r="D87" s="8">
-        <v>46197.85962290509</v>
+        <v>46211.70008122685</v>
       </c>
       <c r="E87" s="9" t="s">
         <v>280</v>
@@ -6670,9 +6668,11 @@
       <c r="B88" s="5">
         <v>46169.55907863426</v>
       </c>
-      <c r="C88" s="6"/>
+      <c r="C88" s="5">
+        <v>46211.700068715276</v>
+      </c>
       <c r="D88" s="5">
-        <v>46206.486817604164</v>
+        <v>46211.70008446759</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>283</v>
@@ -6720,10 +6720,10 @@
         <v>32</v>
       </c>
       <c r="T88" s="6">
-        <v>0</v>
-      </c>
-      <c r="U88" s="11" t="s">
-        <v>100</v>
+        <v>1</v>
+      </c>
+      <c r="U88" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
@@ -6733,9 +6733,11 @@
       <c r="B89" s="8">
         <v>46169.55908684028</v>
       </c>
-      <c r="C89" s="9"/>
+      <c r="C89" s="8">
+        <v>46211.70005122686</v>
+      </c>
       <c r="D89" s="8">
-        <v>46210.698995046296</v>
+        <v>46211.700054201385</v>
       </c>
       <c r="E89" s="9" t="s">
         <v>174</v>
@@ -6851,7 +6853,7 @@
       </c>
       <c r="C91" s="9"/>
       <c r="D91" s="8">
-        <v>46205.597946215275</v>
+        <v>46211.70006402778</v>
       </c>
       <c r="E91" s="9" t="s">
         <v>174</v>

--- a/data/50001557 - ATACAMA KOZAN OT4340.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4340.xlsx
@@ -6623,7 +6623,7 @@
       </c>
       <c r="C87" s="9"/>
       <c r="D87" s="8">
-        <v>46211.70008122685</v>
+        <v>46211.83096003473</v>
       </c>
       <c r="E87" s="9" t="s">
         <v>280</v>
@@ -6788,9 +6788,11 @@
       <c r="B90" s="5">
         <v>46169.55918673611</v>
       </c>
-      <c r="C90" s="6"/>
+      <c r="C90" s="5">
+        <v>46211.830949814816</v>
+      </c>
       <c r="D90" s="5">
-        <v>46196.561689236114</v>
+        <v>46211.83096391204</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>289</v>
@@ -6838,10 +6840,10 @@
         <v>32</v>
       </c>
       <c r="T90" s="6">
-        <v>0</v>
-      </c>
-      <c r="U90" s="11" t="s">
-        <v>100</v>
+        <v>1</v>
+      </c>
+      <c r="U90" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
@@ -6851,9 +6853,11 @@
       <c r="B91" s="8">
         <v>46169.55919113426</v>
       </c>
-      <c r="C91" s="9"/>
+      <c r="C91" s="8">
+        <v>46211.83093260416</v>
+      </c>
       <c r="D91" s="8">
-        <v>46211.70006402778</v>
+        <v>46211.83093474537</v>
       </c>
       <c r="E91" s="9" t="s">
         <v>174</v>
@@ -6973,7 +6977,7 @@
         <v>46197.859803263884</v>
       </c>
       <c r="D93" s="8">
-        <v>46205.597989988426</v>
+        <v>46211.830942650464</v>
       </c>
       <c r="E93" s="9" t="s">
         <v>174</v>

--- a/data/50001557 - ATACAMA KOZAN OT4340.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4340.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1183" uniqueCount="309">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1184" uniqueCount="309">
   <si>
     <t xml:space="preserve"> 50001557 - ATACAMA KOZAN</t>
   </si>
@@ -4571,9 +4571,11 @@
       <c r="B53" s="8">
         <v>46169.558565775464</v>
       </c>
-      <c r="C53" s="9"/>
+      <c r="C53" s="8">
+        <v>46211.86420568287</v>
+      </c>
       <c r="D53" s="8">
-        <v>46169.61885943287</v>
+        <v>46211.86422231482</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>189</v>
@@ -4621,10 +4623,10 @@
         <v>32</v>
       </c>
       <c r="T53" s="9">
-        <v>0</v>
-      </c>
-      <c r="U53" s="11" t="s">
-        <v>100</v>
+        <v>1</v>
+      </c>
+      <c r="U53" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
@@ -4634,9 +4636,11 @@
       <c r="B54" s="5">
         <v>46169.55856972223</v>
       </c>
-      <c r="C54" s="6"/>
+      <c r="C54" s="5">
+        <v>46211.864191967594</v>
+      </c>
       <c r="D54" s="5">
-        <v>46206.486704027775</v>
+        <v>46211.86419394676</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>174</v>
@@ -5852,9 +5856,11 @@
       <c r="B74" s="5">
         <v>46169.55884254629</v>
       </c>
-      <c r="C74" s="6"/>
+      <c r="C74" s="5">
+        <v>46211.86404540509</v>
+      </c>
       <c r="D74" s="5">
-        <v>46206.48683333333</v>
+        <v>46211.86406403936</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>247</v>
@@ -5889,9 +5895,11 @@
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
       <c r="S74" s="6"/>
-      <c r="T74" s="6"/>
-      <c r="U74" s="12" t="s">
-        <v>169</v>
+      <c r="T74" s="6">
+        <v>1</v>
+      </c>
+      <c r="U74" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
@@ -6570,7 +6578,7 @@
         <v>46206.486792916665</v>
       </c>
       <c r="D86" s="5">
-        <v>46206.48679516204</v>
+        <v>46211.86420142361</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>261</v>
@@ -6623,7 +6631,7 @@
       </c>
       <c r="C87" s="9"/>
       <c r="D87" s="8">
-        <v>46211.83096003473</v>
+        <v>46211.8640300463</v>
       </c>
       <c r="E87" s="9" t="s">
         <v>280</v>
@@ -6659,7 +6667,9 @@
       <c r="R87" s="9"/>
       <c r="S87" s="9"/>
       <c r="T87" s="9"/>
-      <c r="U87" s="9"/>
+      <c r="U87" s="12" t="s">
+        <v>169</v>
+      </c>
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
@@ -7028,9 +7038,11 @@
       <c r="B94" s="5">
         <v>46169.55929686343</v>
       </c>
-      <c r="C94" s="6"/>
+      <c r="C94" s="5">
+        <v>46211.86400608796</v>
+      </c>
       <c r="D94" s="5">
-        <v>46196.573311342596</v>
+        <v>46211.86402001158</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>297</v>
@@ -7078,10 +7090,10 @@
         <v>32</v>
       </c>
       <c r="T94" s="6">
-        <v>0</v>
-      </c>
-      <c r="U94" s="11" t="s">
-        <v>100</v>
+        <v>1</v>
+      </c>
+      <c r="U94" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
@@ -7091,9 +7103,11 @@
       <c r="B95" s="8">
         <v>46169.55930180555</v>
       </c>
-      <c r="C95" s="9"/>
+      <c r="C95" s="8">
+        <v>46211.863989895835</v>
+      </c>
       <c r="D95" s="8">
-        <v>46205.598038449076</v>
+        <v>46211.863992280094</v>
       </c>
       <c r="E95" s="9" t="s">
         <v>174</v>
@@ -7193,7 +7207,7 @@
       </c>
       <c r="C97" s="9"/>
       <c r="D97" s="8">
-        <v>46169.621991215274</v>
+        <v>46211.86403020834</v>
       </c>
       <c r="E97" s="9" t="s">
         <v>304</v>
@@ -7243,8 +7257,8 @@
       <c r="T97" s="9">
         <v>0</v>
       </c>
-      <c r="U97" s="11" t="s">
-        <v>100</v>
+      <c r="U97" s="12" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
@@ -7256,7 +7270,7 @@
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46196.805673622686</v>
+        <v>46211.86403085648</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>308</v>
@@ -7306,8 +7320,8 @@
       <c r="T98" s="6">
         <v>0</v>
       </c>
-      <c r="U98" s="11" t="s">
-        <v>100</v>
+      <c r="U98" s="12" t="s">
+        <v>169</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001557 - ATACAMA KOZAN OT4340.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4340.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1184" uniqueCount="309">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1184" uniqueCount="310">
   <si>
     <t xml:space="preserve"> 50001557 - ATACAMA KOZAN</t>
   </si>
@@ -370,6 +370,9 @@
   </si>
   <si>
     <t>Generación OC Rodete OT 4340 ,Fabricación Rodete OT 4340</t>
+  </si>
+  <si>
+    <t>Media</t>
   </si>
   <si>
     <t>1215166329218738</t>
@@ -2964,7 +2967,7 @@
         <v>46184.73646410879</v>
       </c>
       <c r="D26" s="5">
-        <v>46184.73661180555</v>
+        <v>46212.20714363426</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>105</v>
@@ -3008,8 +3011,8 @@
       <c r="R26" s="5">
         <v>46219</v>
       </c>
-      <c r="S26" s="10" t="s">
-        <v>32</v>
+      <c r="S26" s="12" t="s">
+        <v>107</v>
       </c>
       <c r="T26" s="6">
         <v>1</v>
@@ -3020,7 +3023,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B27" s="8">
         <v>46169.55832063657</v>
@@ -3032,7 +3035,7 @@
         <v>46184.7364097338</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>26</v>
@@ -3065,7 +3068,7 @@
         <v>71</v>
       </c>
       <c r="P27" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Q27" s="9"/>
       <c r="R27" s="9"/>
@@ -3081,7 +3084,7 @@
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B28" s="5">
         <v>46169.55832539352</v>
@@ -3093,7 +3096,7 @@
         <v>46184.736449375</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
@@ -3123,10 +3126,10 @@
         <v>105</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
@@ -3142,7 +3145,7 @@
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B29" s="8">
         <v>46169.55833006944</v>
@@ -3154,7 +3157,7 @@
         <v>46200.81836952546</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
@@ -3184,7 +3187,7 @@
         <v>90</v>
       </c>
       <c r="O29" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="P29" s="9" t="s">
         <v>90</v>
@@ -3207,7 +3210,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B30" s="5">
         <v>46169.55833486111</v>
@@ -3219,7 +3222,7 @@
         <v>46195.69066259259</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
@@ -3246,13 +3249,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O30" s="6" t="s">
         <v>65</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -3268,7 +3271,7 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B31" s="8">
         <v>46169.5583402662</v>
@@ -3280,7 +3283,7 @@
         <v>46195.69066760417</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>26</v>
@@ -3307,13 +3310,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O31" s="9" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="P31" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="Q31" s="9"/>
       <c r="R31" s="9"/>
@@ -3329,7 +3332,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B32" s="5">
         <v>46169.55834503472</v>
@@ -3341,7 +3344,7 @@
         <v>46195.6906680324</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
@@ -3368,13 +3371,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
@@ -3390,7 +3393,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B33" s="8">
         <v>46169.55836335648</v>
@@ -3402,16 +3405,16 @@
         <v>46184.532641875005</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I33" s="8">
         <v>46241</v>
@@ -3432,7 +3435,7 @@
         <v>90</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="P33" s="9" t="s">
         <v>90</v>
@@ -3455,7 +3458,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B34" s="5">
         <v>46169.558367986116</v>
@@ -3467,16 +3470,16 @@
         <v>46184.53245875</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I34" s="5">
         <v>46241</v>
@@ -3494,13 +3497,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O34" s="6" t="s">
         <v>75</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3516,7 +3519,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B35" s="8">
         <v>46169.55837292824</v>
@@ -3528,16 +3531,16 @@
         <v>46184.532615856486</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I35" s="8">
         <v>46245</v>
@@ -3555,13 +3558,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="P35" s="9" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="Q35" s="9"/>
       <c r="R35" s="9"/>
@@ -3577,7 +3580,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B36" s="5">
         <v>46169.55837825232</v>
@@ -3589,16 +3592,16 @@
         <v>46184.53258194444</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I36" s="5">
         <v>46241</v>
@@ -3619,7 +3622,7 @@
         <v>90</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="P36" s="6" t="s">
         <v>26</v>
@@ -3642,7 +3645,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B37" s="8">
         <v>46169.558381979165</v>
@@ -3660,10 +3663,10 @@
         <v>26</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I37" s="8">
         <v>46241</v>
@@ -3681,13 +3684,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="O37" s="9" t="s">
         <v>81</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="Q37" s="9"/>
       <c r="R37" s="9"/>
@@ -3697,7 +3700,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B38" s="5">
         <v>46169.55838657408</v>
@@ -3709,16 +3712,16 @@
         <v>46184.53255631945</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I38" s="5">
         <v>46245</v>
@@ -3736,13 +3739,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="O38" s="6" t="s">
         <v>82</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -3752,7 +3755,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B39" s="8">
         <v>46169.55839107639</v>
@@ -3764,16 +3767,16 @@
         <v>46205.600326053245</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I39" s="8">
         <v>46241</v>
@@ -3794,7 +3797,7 @@
         <v>90</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P39" s="9" t="s">
         <v>26</v>
@@ -3817,7 +3820,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B40" s="5">
         <v>46169.55839478009</v>
@@ -3835,10 +3838,10 @@
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I40" s="5">
         <v>46241</v>
@@ -3856,13 +3859,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="O40" s="6" t="s">
         <v>87</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -3872,7 +3875,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B41" s="8">
         <v>46169.55839910879</v>
@@ -3884,16 +3887,16 @@
         <v>46195.70375376157</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I41" s="8">
         <v>46252</v>
@@ -3911,13 +3914,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="O41" s="9" t="s">
         <v>88</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Q41" s="9"/>
       <c r="R41" s="9"/>
@@ -3927,7 +3930,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B42" s="5">
         <v>46169.55840355324</v>
@@ -3939,16 +3942,16 @@
         <v>46205.59994755787</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I42" s="5">
         <v>46281</v>
@@ -3966,10 +3969,10 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>26</v>
@@ -3982,7 +3985,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B43" s="8">
         <v>46169.55840677083</v>
@@ -3994,16 +3997,16 @@
         <v>46191.53701371528</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I43" s="8">
         <v>46241</v>
@@ -4024,7 +4027,7 @@
         <v>90</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="P43" s="9" t="s">
         <v>26</v>
@@ -4047,7 +4050,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B44" s="5">
         <v>46169.55841037037</v>
@@ -4065,10 +4068,10 @@
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I44" s="5">
         <v>46241</v>
@@ -4086,13 +4089,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O44" s="6" t="s">
         <v>84</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4102,7 +4105,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B45" s="8">
         <v>46169.558458217594</v>
@@ -4114,16 +4117,16 @@
         <v>46191.53698841435</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I45" s="8">
         <v>46245</v>
@@ -4141,13 +4144,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O45" s="9" t="s">
         <v>85</v>
       </c>
       <c r="P45" s="9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q45" s="9"/>
       <c r="R45" s="9"/>
@@ -4157,7 +4160,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B46" s="5">
         <v>46169.5584643287</v>
@@ -4167,7 +4170,7 @@
         <v>46182.75962331019</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>25</v>
@@ -4191,7 +4194,7 @@
         <v>26</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4201,12 +4204,12 @@
       <c r="S46" s="6"/>
       <c r="T46" s="6"/>
       <c r="U46" s="12" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B47" s="8">
         <v>46169.55846813657</v>
@@ -4218,16 +4221,16 @@
         <v>46197.715420312496</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I47" s="8">
         <v>46167</v>
@@ -4245,13 +4248,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q47" s="8">
         <v>46167</v>
@@ -4260,7 +4263,7 @@
         <v>46184</v>
       </c>
       <c r="S47" s="11" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="T47" s="9">
         <v>1</v>
@@ -4271,7 +4274,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B48" s="5">
         <v>46169.558472766206</v>
@@ -4283,16 +4286,16 @@
         <v>46181.72663056713</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I48" s="5">
         <v>46167</v>
@@ -4310,13 +4313,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="O48" s="6" t="s">
         <v>59</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q48" s="6"/>
       <c r="R48" s="6"/>
@@ -4326,7 +4329,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B49" s="8">
         <v>46169.55849938658</v>
@@ -4338,16 +4341,16 @@
         <v>46197.71545016204</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I49" s="8">
         <v>46218</v>
@@ -4365,13 +4368,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q49" s="8">
         <v>46218</v>
@@ -4391,7 +4394,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B50" s="5">
         <v>46169.55850371528</v>
@@ -4403,16 +4406,16 @@
         <v>46195.690583055555</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I50" s="5">
         <v>46218</v>
@@ -4430,13 +4433,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q50" s="6"/>
       <c r="R50" s="6"/>
@@ -4446,7 +4449,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B51" s="8">
         <v>46169.55853228009</v>
@@ -4464,10 +4467,10 @@
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I51" s="8">
         <v>46238</v>
@@ -4485,13 +4488,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q51" s="8">
         <v>46238</v>
@@ -4511,7 +4514,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B52" s="5">
         <v>46169.55854641204</v>
@@ -4523,16 +4526,16 @@
         <v>46182.75984881945</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I52" s="5">
         <v>46238</v>
@@ -4553,7 +4556,7 @@
         <v>78</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P52" s="6" t="s">
         <v>78</v>
@@ -4566,7 +4569,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B53" s="8">
         <v>46169.558565775464</v>
@@ -4578,16 +4581,16 @@
         <v>46211.86422231482</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I53" s="8">
         <v>46331</v>
@@ -4605,10 +4608,10 @@
         <v>26</v>
       </c>
       <c r="N53" s="9" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P53" s="9" t="s">
         <v>26</v>
@@ -4631,7 +4634,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B54" s="5">
         <v>46169.55856972223</v>
@@ -4643,16 +4646,16 @@
         <v>46211.86419394676</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I54" s="5">
         <v>46331</v>
@@ -4670,13 +4673,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q54" s="6"/>
       <c r="R54" s="6"/>
@@ -4686,7 +4689,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B55" s="8">
         <v>46169.558586307874</v>
@@ -4698,7 +4701,7 @@
         <v>46198.597746307874</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>25</v>
@@ -4722,7 +4725,7 @@
         <v>26</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="P55" s="9" t="s">
         <v>26</v>
@@ -4739,7 +4742,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B56" s="5">
         <v>46169.55858945602</v>
@@ -4751,16 +4754,16 @@
         <v>46197.83559606482</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="I56" s="5">
         <v>46254</v>
@@ -4778,13 +4781,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q56" s="5">
         <v>46254</v>
@@ -4804,7 +4807,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B57" s="8">
         <v>46169.55859488426</v>
@@ -4816,16 +4819,16 @@
         <v>46197.85937331019</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I57" s="8">
         <v>46258</v>
@@ -4843,13 +4846,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q57" s="8">
         <v>46258</v>
@@ -4869,7 +4872,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B58" s="5">
         <v>46169.55860118056</v>
@@ -4881,16 +4884,16 @@
         <v>46198.59771457176</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="I58" s="5">
         <v>46254</v>
@@ -4908,13 +4911,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q58" s="5">
         <v>46254</v>
@@ -4934,7 +4937,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B59" s="8">
         <v>46169.55860636574</v>
@@ -4946,16 +4949,16 @@
         <v>46198.597709444446</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I59" s="8">
         <v>46258</v>
@@ -4973,13 +4976,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q59" s="8">
         <v>46258</v>
@@ -4994,12 +4997,12 @@
         <v>1</v>
       </c>
       <c r="U59" s="12" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B60" s="5">
         <v>46169.558650127314</v>
@@ -5011,16 +5014,16 @@
         <v>46198.59773310185</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="I60" s="5">
         <v>46254</v>
@@ -5038,13 +5041,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q60" s="5">
         <v>46254</v>
@@ -5064,7 +5067,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B61" s="8">
         <v>46169.55865608796</v>
@@ -5076,16 +5079,16 @@
         <v>46198.59773317129</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I61" s="8">
         <v>46258</v>
@@ -5103,13 +5106,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q61" s="8">
         <v>46258</v>
@@ -5124,12 +5127,12 @@
         <v>1</v>
       </c>
       <c r="U61" s="12" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B62" s="5">
         <v>46169.55866105324</v>
@@ -5141,7 +5144,7 @@
         <v>46198.68229049769</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>25</v>
@@ -5165,7 +5168,7 @@
         <v>26</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="P62" s="6" t="s">
         <v>26</v>
@@ -5182,7 +5185,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B63" s="8">
         <v>46169.55866469907</v>
@@ -5194,16 +5197,16 @@
         <v>46197.85915361111</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="9" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H63" s="9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I63" s="8">
         <v>46260</v>
@@ -5221,13 +5224,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P63" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q63" s="8">
         <v>46260</v>
@@ -5247,7 +5250,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B64" s="5">
         <v>46169.55867099537</v>
@@ -5259,16 +5262,16 @@
         <v>46197.85936673611</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I64" s="5">
         <v>46260</v>
@@ -5286,13 +5289,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5302,7 +5305,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B65" s="8">
         <v>46169.558703518516</v>
@@ -5314,16 +5317,16 @@
         <v>46197.85387390046</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H65" s="9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I65" s="8">
         <v>46269</v>
@@ -5341,13 +5344,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q65" s="8">
         <v>46269</v>
@@ -5362,12 +5365,12 @@
         <v>1</v>
       </c>
       <c r="U65" s="12" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B66" s="5">
         <v>46169.55870879629</v>
@@ -5379,16 +5382,16 @@
         <v>46197.85915420139</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I66" s="5">
         <v>46269</v>
@@ -5406,13 +5409,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5422,7 +5425,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B67" s="8">
         <v>46169.558740625</v>
@@ -5434,16 +5437,16 @@
         <v>46205.65959174768</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H67" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I67" s="8">
         <v>46274</v>
@@ -5461,13 +5464,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P67" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q67" s="8">
         <v>46274</v>
@@ -5482,12 +5485,12 @@
         <v>1</v>
       </c>
       <c r="U67" s="12" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B68" s="5">
         <v>46169.558745243055</v>
@@ -5499,16 +5502,16 @@
         <v>46205.659588587965</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I68" s="5">
         <v>46274</v>
@@ -5526,13 +5529,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q68" s="6"/>
       <c r="R68" s="6"/>
@@ -5542,7 +5545,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B69" s="8">
         <v>46169.55876947917</v>
@@ -5554,7 +5557,7 @@
         <v>46211.70953918982</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>25</v>
@@ -5578,7 +5581,7 @@
         <v>26</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="P69" s="9" t="s">
         <v>26</v>
@@ -5591,7 +5594,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B70" s="5">
         <v>46169.55880633101</v>
@@ -5603,16 +5606,16 @@
         <v>46200.8197621875</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="I70" s="5">
         <v>46220</v>
@@ -5630,13 +5633,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q70" s="5">
         <v>46220</v>
@@ -5656,7 +5659,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B71" s="8">
         <v>46169.5588177662</v>
@@ -5668,16 +5671,16 @@
         <v>46200.819831597226</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H71" s="9" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="I71" s="8">
         <v>46325</v>
@@ -5695,13 +5698,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="O71" s="9" t="s">
         <v>102</v>
       </c>
       <c r="P71" s="9" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q71" s="8">
         <v>46325</v>
@@ -5710,7 +5713,7 @@
         <v>46325</v>
       </c>
       <c r="S71" s="11" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="T71" s="9">
         <v>1</v>
@@ -5721,7 +5724,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B72" s="5">
         <v>46169.55882295139</v>
@@ -5733,16 +5736,16 @@
         <v>46200.81928909722</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="I72" s="5">
         <v>46293</v>
@@ -5760,13 +5763,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q72" s="5">
         <v>46293</v>
@@ -5786,7 +5789,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B73" s="8">
         <v>46169.55882788195</v>
@@ -5798,16 +5801,16 @@
         <v>46211.7093043287</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H73" s="9" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="I73" s="8">
         <v>46282</v>
@@ -5825,13 +5828,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="P73" s="9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q73" s="8">
         <v>46282</v>
@@ -5851,7 +5854,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B74" s="5">
         <v>46169.55884254629</v>
@@ -5863,7 +5866,7 @@
         <v>46211.86406403936</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>25</v>
@@ -5887,7 +5890,7 @@
         <v>26</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="P74" s="6" t="s">
         <v>26</v>
@@ -5904,7 +5907,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B75" s="8">
         <v>46169.55884548611</v>
@@ -5916,7 +5919,7 @@
         <v>46211.70929236111</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
@@ -5943,13 +5946,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q75" s="8">
         <v>46276</v>
@@ -5964,12 +5967,12 @@
         <v>1</v>
       </c>
       <c r="U75" s="12" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B76" s="5">
         <v>46169.55884993056</v>
@@ -5981,7 +5984,7 @@
         <v>46211.70929407407</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
@@ -6008,13 +6011,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -6024,7 +6027,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B77" s="8">
         <v>46169.55893170139</v>
@@ -6036,7 +6039,7 @@
         <v>46197.495185555556</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>26</v>
@@ -6063,13 +6066,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P77" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q77" s="8">
         <v>46296</v>
@@ -6089,7 +6092,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B78" s="5">
         <v>46169.55893543981</v>
@@ -6101,7 +6104,7 @@
         <v>46204.879924837966</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
@@ -6128,13 +6131,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q78" s="6"/>
       <c r="R78" s="6"/>
@@ -6144,7 +6147,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B79" s="8">
         <v>46169.558869560184</v>
@@ -6156,7 +6159,7 @@
         <v>46204.87981377315</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>26</v>
@@ -6183,13 +6186,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="P79" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q79" s="8">
         <v>46328</v>
@@ -6209,7 +6212,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B80" s="5">
         <v>46169.55887296297</v>
@@ -6221,7 +6224,7 @@
         <v>46204.87978310185</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
@@ -6248,13 +6251,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -6264,7 +6267,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B81" s="8">
         <v>46169.5589025463</v>
@@ -6276,7 +6279,7 @@
         <v>46204.880057013885</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
@@ -6303,13 +6306,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q81" s="8">
         <v>46329</v>
@@ -6329,7 +6332,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B82" s="5">
         <v>46169.55890609954</v>
@@ -6341,7 +6344,7 @@
         <v>46204.87991711806</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
@@ -6368,13 +6371,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6384,7 +6387,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B83" s="8">
         <v>46169.55900443287</v>
@@ -6396,7 +6399,7 @@
         <v>46206.48671975694</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>26</v>
@@ -6423,13 +6426,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O83" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P83" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q83" s="8">
         <v>46330</v>
@@ -6449,7 +6452,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B84" s="5">
         <v>46169.55901002315</v>
@@ -6461,7 +6464,7 @@
         <v>46206.48669563657</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
@@ -6488,13 +6491,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q84" s="6"/>
       <c r="R84" s="6"/>
@@ -6504,7 +6507,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B85" s="8">
         <v>46169.55904462963</v>
@@ -6516,7 +6519,7 @@
         <v>46206.48682021991</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>26</v>
@@ -6543,13 +6546,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O85" s="9" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="P85" s="9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q85" s="8">
         <v>46332</v>
@@ -6569,7 +6572,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B86" s="5">
         <v>46169.559050138894</v>
@@ -6581,7 +6584,7 @@
         <v>46211.86420142361</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6608,13 +6611,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6624,7 +6627,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B87" s="8">
         <v>46169.55907484954</v>
@@ -6634,7 +6637,7 @@
         <v>46211.8640300463</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>25</v>
@@ -6658,7 +6661,7 @@
         <v>26</v>
       </c>
       <c r="O87" s="9" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="P87" s="9" t="s">
         <v>26</v>
@@ -6668,12 +6671,12 @@
       <c r="S87" s="9"/>
       <c r="T87" s="9"/>
       <c r="U87" s="12" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B88" s="5">
         <v>46169.55907863426</v>
@@ -6685,16 +6688,16 @@
         <v>46211.70008446759</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="I88" s="5">
         <v>46335</v>
@@ -6712,13 +6715,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q88" s="5">
         <v>46335</v>
@@ -6738,7 +6741,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B89" s="8">
         <v>46169.55908684028</v>
@@ -6750,16 +6753,16 @@
         <v>46211.700054201385</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H89" s="9" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="I89" s="8">
         <v>46335</v>
@@ -6777,13 +6780,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O89" s="9" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="P89" s="9" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q89" s="9"/>
       <c r="R89" s="9"/>
@@ -6793,7 +6796,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B90" s="5">
         <v>46169.55918673611</v>
@@ -6805,7 +6808,7 @@
         <v>46211.83096391204</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
@@ -6832,13 +6835,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q90" s="5">
         <v>46336</v>
@@ -6858,7 +6861,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B91" s="8">
         <v>46169.55919113426</v>
@@ -6870,7 +6873,7 @@
         <v>46211.83093474537</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>26</v>
@@ -6897,13 +6900,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="9" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="O91" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P91" s="9" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q91" s="9"/>
       <c r="R91" s="9"/>
@@ -6913,7 +6916,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B92" s="5">
         <v>46169.559239560185</v>
@@ -6925,16 +6928,16 @@
         <v>46197.859819363424</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I92" s="5">
         <v>46337</v>
@@ -6952,13 +6955,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q92" s="5">
         <v>46337</v>
@@ -6973,12 +6976,12 @@
         <v>1</v>
       </c>
       <c r="U92" s="12" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B93" s="8">
         <v>46169.559243842596</v>
@@ -6990,16 +6993,16 @@
         <v>46211.830942650464</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="9" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H93" s="9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I93" s="8">
         <v>46337</v>
@@ -7017,13 +7020,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="9" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="O93" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P93" s="9" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q93" s="9"/>
       <c r="R93" s="9"/>
@@ -7033,7 +7036,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B94" s="5">
         <v>46169.55929686343</v>
@@ -7045,16 +7048,16 @@
         <v>46211.86402001158</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I94" s="5">
         <v>46338</v>
@@ -7072,13 +7075,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q94" s="5">
         <v>46338</v>
@@ -7098,7 +7101,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B95" s="8">
         <v>46169.55930180555</v>
@@ -7110,16 +7113,16 @@
         <v>46211.863992280094</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="9" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H95" s="9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I95" s="8">
         <v>46338</v>
@@ -7137,13 +7140,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="9" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="O95" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P95" s="9" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q95" s="9"/>
       <c r="R95" s="9"/>
@@ -7153,7 +7156,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B96" s="5">
         <v>46169.55938721065</v>
@@ -7163,7 +7166,7 @@
         <v>46169.60672822916</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>25</v>
@@ -7187,7 +7190,7 @@
         <v>26</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="P96" s="6" t="s">
         <v>26</v>
@@ -7200,7 +7203,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B97" s="8">
         <v>46169.55939094907</v>
@@ -7210,16 +7213,16 @@
         <v>46211.86403020834</v>
       </c>
       <c r="E97" s="9" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G97" s="9" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H97" s="9" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="I97" s="8">
         <v>46339</v>
@@ -7237,13 +7240,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="9" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="O97" s="9" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="P97" s="9" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q97" s="8">
         <v>46339</v>
@@ -7258,12 +7261,12 @@
         <v>0</v>
       </c>
       <c r="U97" s="12" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B98" s="5">
         <v>46169.55939643519</v>
@@ -7273,7 +7276,7 @@
         <v>46211.86403085648</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -7300,13 +7303,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q98" s="5">
         <v>46339</v>
@@ -7321,7 +7324,7 @@
         <v>0</v>
       </c>
       <c r="U98" s="12" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001557 - ATACAMA KOZAN OT4340.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4340.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1184" uniqueCount="310">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1184" uniqueCount="311">
   <si>
     <t xml:space="preserve"> 50001557 - ATACAMA KOZAN</t>
   </si>
@@ -119,6 +119,72 @@
   </si>
   <si>
     <t>Apertura pedido</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buen día,
+Para el pedido 1557 se tienen 2 equipos ZVN 1-7-37/2, 2 equipos ZVN 1-7-30/2, 1 equipo ZVN 1-9-37/2 y 1 equipo JZR 6-18.5/2 para Atacama Kozan:
+    *    Planos para fabricación Ventilador ZVN 1-7-37/2 con motor OMEC
+        *    Incluye: Tobera + Rejilla
+        *    hgutierrez@zitron.com, tu apoyo con los planos.
+    *    Rodete:
+        *    Rodete monobloque GEL 7-37  
+        *    Código: 300065
+        *    Plano Mecanizado 3534.07.04.37.D55
+    *    Datos eléctricos para el motor:
+        *    Motor 37 KW, 2 Polos, Frame 200L.
+        *    380 VAC, 50 Hz, IEC, IP55, FS 1.0.-
+        *    Código: 350004
+--
+    *    Planos para fabricación Ventilador ZVN 1-7-30/2 con motor OMEC
+        *    Incluye: Tobera + Rejilla
+        *    hgutierrez@zitron.com, tu apoyo con los planos.
+    *    Rodete:
+        *    Rodete monobloque GEL 7-30
+        *    Código: 300062
+        *    Plano Mecanizado 3534.07.04.30.D55
+    *    Datos eléctricos para el motor:
+        *    Motor 30 KW, 2 Polos, Frame 200L.
+        *    380 VAC, 50 Hz, IEC, IP55, FS 1.0.-
+        *    Código: 350004
+        *    benjamin.bustos@zitron.com, se debe solicitar duplicado de placas.
+--
+    *    Planos para fabricación Ventilador ZVN 1-9-37/2 con motor OMEC
+        *    Incluye: Tobera + Rejilla
+        *    hgutierrez@zitron.com, tu apoyo con los planos.
+    *    Rodete:
+        *    Rodete de placas s/plano 4999.00
+        *    Alabe s/ plano 4999.01
+        *    Z8 N590
+        *    Código 300000
+        *    hgutierrez@zitron.com, tu apoyo con la definición de calaje
+    *    Datos eléctricos para el motor:
+        *    Motor 37 KW, 2 Polos, Frame 200L.
+        *    380 VAC, 50 Hz, IEC, IP55, FS 1.0.-
+        *    Código: 350004
+--
+    *    Fabricación Ventilador JZR 6-18.5/2 con motor WEG
+        *    Incluye: Tobera + Rejilla + 2FAR90/100 + Bastidor
+        *    Plano CH1463
+    *    Rodete:
+        *    Rodete monobloque GEL 6-15  
+        *    Código 300056
+        *    Plano Mecanizado 3534.06.04.15.D42
+    *    Datos eléctricos para el motor:
+        *    Motor 18.5 KW, 2 Polos, Frame 160L.
+        *    380 VAC, 50 Hz, IEC, IP55, FS 1.0.-
+--
+    *    Datos eléctricos para tableros:
+        *    Tablero YD  18.5kW, 380 VAC, 50 Hz, IP66.
+        *    Tablero YD  30kW, 380 VAC, 50 Hz, IP66.
+        *    Tablero YD  37kW, 380 VAC, 50 Hz, IP66.
+        *    Incluye luces piloto, botones y protección de entrada
+        *    Propuestas en sistema.
+    *    Tratamiento superficial estándar Zitron para todas las unidades:
+        *    Preparación de superficie: Arenado SSPC-SP10
+        *    1ª capa imprimación 60 micras Hempadur 15570 Color 12430
+        *    2ª capa intermedia 40 micras Hempathane HS 55610 Color 20450 RAL 9001
+    *    Fecha de entrega: 16-06-2026
+</t>
   </si>
   <si>
     <t>1215166329020201</t>
@@ -1723,7 +1789,7 @@
         <v>46181.62347399305</v>
       </c>
       <c r="D6" s="5">
-        <v>46181.624255925926</v>
+        <v>46213.7119689699</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -1745,7 +1811,7 @@
         <v>26</v>
       </c>
       <c r="L6" s="6" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="M6" s="6" t="s">
         <v>26</v>
@@ -1777,7 +1843,7 @@
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B7" s="8">
         <v>46169.55814432871</v>
@@ -1789,7 +1855,7 @@
         <v>46181.62349788194</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F7" s="9" t="s">
         <v>26</v>
@@ -1808,7 +1874,7 @@
         <v>26</v>
       </c>
       <c r="L7" s="9" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M7" s="9" t="s">
         <v>26</v>
@@ -1840,7 +1906,7 @@
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B8" s="5">
         <v>46169.55814774305</v>
@@ -1852,7 +1918,7 @@
         <v>46181.62350184028</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>26</v>
@@ -1871,7 +1937,7 @@
         <v>26</v>
       </c>
       <c r="L8" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M8" s="6" t="s">
         <v>26</v>
@@ -1883,7 +1949,7 @@
         <v>26</v>
       </c>
       <c r="P8" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q8" s="5">
         <v>46154</v>
@@ -1903,7 +1969,7 @@
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B9" s="8">
         <v>46169.55815164352</v>
@@ -1915,7 +1981,7 @@
         <v>46181.62350840278</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F9" s="9" t="s">
         <v>26</v>
@@ -1934,7 +2000,7 @@
         <v>26</v>
       </c>
       <c r="L9" s="9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M9" s="9" t="s">
         <v>26</v>
@@ -1966,7 +2032,7 @@
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B10" s="5">
         <v>46169.55800939815</v>
@@ -1978,7 +2044,7 @@
         <v>46197.83892112269</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>25</v>
@@ -2002,7 +2068,7 @@
         <v>26</v>
       </c>
       <c r="O10" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P10" s="6" t="s">
         <v>26</v>
@@ -2019,7 +2085,7 @@
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B11" s="8">
         <v>46169.558185671296</v>
@@ -2031,16 +2097,16 @@
         <v>46196.80567361111</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F11" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H11" s="9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I11" s="8">
         <v>46155</v>
@@ -2052,19 +2118,19 @@
         <v>26</v>
       </c>
       <c r="L11" s="9" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="M11" s="9" t="s">
         <v>26</v>
       </c>
       <c r="N11" s="9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="O11" s="9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="P11" s="9" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="Q11" s="8">
         <v>46155</v>
@@ -2084,7 +2150,7 @@
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B12" s="5">
         <v>46169.558191840275</v>
@@ -2096,16 +2162,16 @@
         <v>46196.80567332176</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I12" s="5">
         <v>46155</v>
@@ -2117,19 +2183,19 @@
         <v>26</v>
       </c>
       <c r="L12" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="M12" s="6" t="s">
         <v>26</v>
       </c>
       <c r="N12" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="O12" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="P12" s="6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q12" s="5">
         <v>46155</v>
@@ -2149,7 +2215,7 @@
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B13" s="8">
         <v>46169.558197418984</v>
@@ -2161,16 +2227,16 @@
         <v>46196.80567320602</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F13" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I13" s="8">
         <v>46155</v>
@@ -2188,13 +2254,13 @@
         <v>26</v>
       </c>
       <c r="N13" s="9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="O13" s="9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="P13" s="9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="Q13" s="8">
         <v>46155</v>
@@ -2214,7 +2280,7 @@
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B14" s="5">
         <v>46169.558013773145</v>
@@ -2226,7 +2292,7 @@
         <v>46190.64417138889</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>25</v>
@@ -2250,7 +2316,7 @@
         <v>26</v>
       </c>
       <c r="O14" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="P14" s="6" t="s">
         <v>26</v>
@@ -2267,7 +2333,7 @@
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B15" s="8">
         <v>46169.558213564815</v>
@@ -2279,16 +2345,16 @@
         <v>46181.62446385417</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F15" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H15" s="9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I15" s="8">
         <v>46157</v>
@@ -2306,13 +2372,13 @@
         <v>26</v>
       </c>
       <c r="N15" s="9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="O15" s="9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="P15" s="9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="Q15" s="8">
         <v>46157</v>
@@ -2332,7 +2398,7 @@
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B16" s="5">
         <v>46169.558224479166</v>
@@ -2344,16 +2410,16 @@
         <v>46181.62447002315</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I16" s="5">
         <v>46167</v>
@@ -2371,13 +2437,13 @@
         <v>26</v>
       </c>
       <c r="N16" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="O16" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="P16" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="Q16" s="5">
         <v>46167</v>
@@ -2397,7 +2463,7 @@
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B17" s="8">
         <v>46169.558230821756</v>
@@ -2409,16 +2475,16 @@
         <v>46183.90651931713</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F17" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I17" s="8">
         <v>46167</v>
@@ -2436,13 +2502,13 @@
         <v>26</v>
       </c>
       <c r="N17" s="9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="O17" s="9" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="P17" s="9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Q17" s="8">
         <v>46167</v>
@@ -2462,7 +2528,7 @@
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B18" s="5">
         <v>46169.55823646991</v>
@@ -2474,16 +2540,16 @@
         <v>46183.90665107639</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I18" s="5">
         <v>46239</v>
@@ -2501,13 +2567,13 @@
         <v>26</v>
       </c>
       <c r="N18" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="O18" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q18" s="5">
         <v>46239</v>
@@ -2527,7 +2593,7 @@
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B19" s="8">
         <v>46169.55824171296</v>
@@ -2539,16 +2605,16 @@
         <v>46183.90666170139</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F19" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G19" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I19" s="8">
         <v>46239</v>
@@ -2566,13 +2632,13 @@
         <v>26</v>
       </c>
       <c r="N19" s="9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="O19" s="9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="P19" s="9" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q19" s="8">
         <v>46239</v>
@@ -2592,7 +2658,7 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B20" s="5">
         <v>46169.55824574074</v>
@@ -2604,16 +2670,16 @@
         <v>46190.64415820602</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I20" s="5">
         <v>46239</v>
@@ -2631,13 +2697,13 @@
         <v>26</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="Q20" s="5">
         <v>46239</v>
@@ -2657,7 +2723,7 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B21" s="8">
         <v>46169.55825006944</v>
@@ -2669,16 +2735,16 @@
         <v>46183.90735393518</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F21" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G21" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I21" s="8">
         <v>46239</v>
@@ -2696,13 +2762,13 @@
         <v>26</v>
       </c>
       <c r="N21" s="9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="O21" s="9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="P21" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="Q21" s="8">
         <v>46239</v>
@@ -2722,7 +2788,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B22" s="5">
         <v>46169.55801826389</v>
@@ -2734,7 +2800,7 @@
         <v>46200.818425798614</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>25</v>
@@ -2758,7 +2824,7 @@
         <v>26</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="P22" s="6" t="s">
         <v>26</v>
@@ -2771,7 +2837,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B23" s="8">
         <v>46169.558301956014</v>
@@ -2783,16 +2849,16 @@
         <v>46200.81833380787</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I23" s="8">
         <v>46169</v>
@@ -2810,13 +2876,13 @@
         <v>26</v>
       </c>
       <c r="N23" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O23" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="P23" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="Q23" s="8">
         <v>46169</v>
@@ -2836,7 +2902,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B24" s="5">
         <v>46169.558306516206</v>
@@ -2848,16 +2914,16 @@
         <v>46195.69079224537</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I24" s="5">
         <v>46169</v>
@@ -2875,13 +2941,13 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="Q24" s="6"/>
       <c r="R24" s="6"/>
@@ -2892,12 +2958,12 @@
         <v>0</v>
       </c>
       <c r="U24" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B25" s="8">
         <v>46169.55831137732</v>
@@ -2909,16 +2975,16 @@
         <v>46195.690800474535</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I25" s="8">
         <v>46171</v>
@@ -2936,13 +3002,13 @@
         <v>26</v>
       </c>
       <c r="N25" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="O25" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="P25" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Q25" s="9"/>
       <c r="R25" s="9"/>
@@ -2953,12 +3019,12 @@
         <v>0</v>
       </c>
       <c r="U25" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B26" s="5">
         <v>46169.55831605324</v>
@@ -2970,16 +3036,16 @@
         <v>46212.20714363426</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I26" s="5">
         <v>46169</v>
@@ -2997,13 +3063,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="Q26" s="5">
         <v>46169</v>
@@ -3012,7 +3078,7 @@
         <v>46219</v>
       </c>
       <c r="S26" s="12" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="T26" s="6">
         <v>1</v>
@@ -3023,7 +3089,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B27" s="8">
         <v>46169.55832063657</v>
@@ -3035,16 +3101,16 @@
         <v>46184.7364097338</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I27" s="8">
         <v>46169</v>
@@ -3062,13 +3128,13 @@
         <v>26</v>
       </c>
       <c r="N27" s="9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O27" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="P27" s="9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Q27" s="9"/>
       <c r="R27" s="9"/>
@@ -3079,12 +3145,12 @@
         <v>0</v>
       </c>
       <c r="U27" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B28" s="5">
         <v>46169.55832539352</v>
@@ -3096,16 +3162,16 @@
         <v>46184.736449375</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I28" s="5">
         <v>46171</v>
@@ -3123,13 +3189,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
@@ -3140,12 +3206,12 @@
         <v>0</v>
       </c>
       <c r="U28" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B29" s="8">
         <v>46169.55833006944</v>
@@ -3157,16 +3223,16 @@
         <v>46200.81836952546</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I29" s="8">
         <v>46161</v>
@@ -3184,13 +3250,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O29" s="9" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="P29" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="Q29" s="8">
         <v>46161</v>
@@ -3210,7 +3276,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B30" s="5">
         <v>46169.55833486111</v>
@@ -3222,16 +3288,16 @@
         <v>46195.69066259259</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I30" s="5">
         <v>46161</v>
@@ -3249,13 +3315,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -3266,12 +3332,12 @@
         <v>0</v>
       </c>
       <c r="U30" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B31" s="8">
         <v>46169.5583402662</v>
@@ -3283,16 +3349,16 @@
         <v>46195.69066760417</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I31" s="8">
         <v>46178</v>
@@ -3310,13 +3376,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="O31" s="9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="P31" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="Q31" s="9"/>
       <c r="R31" s="9"/>
@@ -3327,12 +3393,12 @@
         <v>0</v>
       </c>
       <c r="U31" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B32" s="5">
         <v>46169.55834503472</v>
@@ -3344,16 +3410,16 @@
         <v>46195.6906680324</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I32" s="5">
         <v>46178</v>
@@ -3371,13 +3437,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
@@ -3388,12 +3454,12 @@
         <v>0</v>
       </c>
       <c r="U32" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B33" s="8">
         <v>46169.55836335648</v>
@@ -3405,16 +3471,16 @@
         <v>46184.532641875005</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I33" s="8">
         <v>46241</v>
@@ -3432,13 +3498,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="Q33" s="8">
         <v>46241</v>
@@ -3458,7 +3524,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B34" s="5">
         <v>46169.558367986116</v>
@@ -3470,16 +3536,16 @@
         <v>46184.53245875</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I34" s="5">
         <v>46241</v>
@@ -3497,13 +3563,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3514,12 +3580,12 @@
         <v>0</v>
       </c>
       <c r="U34" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B35" s="8">
         <v>46169.55837292824</v>
@@ -3531,16 +3597,16 @@
         <v>46184.532615856486</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I35" s="8">
         <v>46245</v>
@@ -3558,13 +3624,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="P35" s="9" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="Q35" s="9"/>
       <c r="R35" s="9"/>
@@ -3575,12 +3641,12 @@
         <v>0</v>
       </c>
       <c r="U35" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B36" s="5">
         <v>46169.55837825232</v>
@@ -3592,16 +3658,16 @@
         <v>46184.53258194444</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I36" s="5">
         <v>46241</v>
@@ -3619,10 +3685,10 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P36" s="6" t="s">
         <v>26</v>
@@ -3645,7 +3711,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B37" s="8">
         <v>46169.558381979165</v>
@@ -3657,16 +3723,16 @@
         <v>46184.5322071875</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I37" s="8">
         <v>46241</v>
@@ -3684,13 +3750,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="Q37" s="9"/>
       <c r="R37" s="9"/>
@@ -3700,7 +3766,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B38" s="5">
         <v>46169.55838657408</v>
@@ -3712,16 +3778,16 @@
         <v>46184.53255631945</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I38" s="5">
         <v>46245</v>
@@ -3739,13 +3805,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -3755,7 +3821,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B39" s="8">
         <v>46169.55839107639</v>
@@ -3767,16 +3833,16 @@
         <v>46205.600326053245</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I39" s="8">
         <v>46241</v>
@@ -3794,10 +3860,10 @@
         <v>26</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P39" s="9" t="s">
         <v>26</v>
@@ -3820,7 +3886,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B40" s="5">
         <v>46169.55839478009</v>
@@ -3832,16 +3898,16 @@
         <v>46195.70360162037</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I40" s="5">
         <v>46241</v>
@@ -3859,13 +3925,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -3875,7 +3941,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B41" s="8">
         <v>46169.55839910879</v>
@@ -3887,16 +3953,16 @@
         <v>46195.70375376157</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I41" s="8">
         <v>46252</v>
@@ -3914,13 +3980,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q41" s="9"/>
       <c r="R41" s="9"/>
@@ -3930,7 +3996,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B42" s="5">
         <v>46169.55840355324</v>
@@ -3942,16 +4008,16 @@
         <v>46205.59994755787</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I42" s="5">
         <v>46281</v>
@@ -3969,10 +4035,10 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>26</v>
@@ -3985,7 +4051,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B43" s="8">
         <v>46169.55840677083</v>
@@ -3997,16 +4063,16 @@
         <v>46191.53701371528</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I43" s="8">
         <v>46241</v>
@@ -4024,10 +4090,10 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="P43" s="9" t="s">
         <v>26</v>
@@ -4050,7 +4116,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B44" s="5">
         <v>46169.55841037037</v>
@@ -4062,16 +4128,16 @@
         <v>46191.53679194444</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I44" s="5">
         <v>46241</v>
@@ -4089,13 +4155,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4105,7 +4171,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B45" s="8">
         <v>46169.558458217594</v>
@@ -4117,16 +4183,16 @@
         <v>46191.53698841435</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I45" s="8">
         <v>46245</v>
@@ -4144,13 +4210,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="P45" s="9" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q45" s="9"/>
       <c r="R45" s="9"/>
@@ -4160,7 +4226,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B46" s="5">
         <v>46169.5584643287</v>
@@ -4170,7 +4236,7 @@
         <v>46182.75962331019</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>25</v>
@@ -4194,7 +4260,7 @@
         <v>26</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4204,12 +4270,12 @@
       <c r="S46" s="6"/>
       <c r="T46" s="6"/>
       <c r="U46" s="12" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B47" s="8">
         <v>46169.55846813657</v>
@@ -4221,16 +4287,16 @@
         <v>46197.715420312496</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I47" s="8">
         <v>46167</v>
@@ -4248,13 +4314,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q47" s="8">
         <v>46167</v>
@@ -4263,7 +4329,7 @@
         <v>46184</v>
       </c>
       <c r="S47" s="11" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="T47" s="9">
         <v>1</v>
@@ -4274,7 +4340,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B48" s="5">
         <v>46169.558472766206</v>
@@ -4286,16 +4352,16 @@
         <v>46181.72663056713</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="I48" s="5">
         <v>46167</v>
@@ -4313,13 +4379,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q48" s="6"/>
       <c r="R48" s="6"/>
@@ -4329,7 +4395,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B49" s="8">
         <v>46169.55849938658</v>
@@ -4341,16 +4407,16 @@
         <v>46197.71545016204</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I49" s="8">
         <v>46218</v>
@@ -4368,13 +4434,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q49" s="8">
         <v>46218</v>
@@ -4394,7 +4460,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B50" s="5">
         <v>46169.55850371528</v>
@@ -4406,16 +4472,16 @@
         <v>46195.690583055555</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="I50" s="5">
         <v>46218</v>
@@ -4433,13 +4499,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q50" s="6"/>
       <c r="R50" s="6"/>
@@ -4449,7 +4515,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B51" s="8">
         <v>46169.55853228009</v>
@@ -4461,16 +4527,16 @@
         <v>46182.759871076385</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="I51" s="8">
         <v>46238</v>
@@ -4488,13 +4554,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q51" s="8">
         <v>46238</v>
@@ -4514,7 +4580,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B52" s="5">
         <v>46169.55854641204</v>
@@ -4526,16 +4592,16 @@
         <v>46182.75984881945</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="I52" s="5">
         <v>46238</v>
@@ -4553,13 +4619,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4569,7 +4635,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B53" s="8">
         <v>46169.558565775464</v>
@@ -4581,16 +4647,16 @@
         <v>46211.86422231482</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I53" s="8">
         <v>46331</v>
@@ -4608,10 +4674,10 @@
         <v>26</v>
       </c>
       <c r="N53" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P53" s="9" t="s">
         <v>26</v>
@@ -4634,7 +4700,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B54" s="5">
         <v>46169.55856972223</v>
@@ -4646,16 +4712,16 @@
         <v>46211.86419394676</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I54" s="5">
         <v>46331</v>
@@ -4673,13 +4739,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q54" s="6"/>
       <c r="R54" s="6"/>
@@ -4689,7 +4755,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B55" s="8">
         <v>46169.558586307874</v>
@@ -4701,7 +4767,7 @@
         <v>46198.597746307874</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>25</v>
@@ -4725,7 +4791,7 @@
         <v>26</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P55" s="9" t="s">
         <v>26</v>
@@ -4742,7 +4808,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B56" s="5">
         <v>46169.55858945602</v>
@@ -4754,16 +4820,16 @@
         <v>46197.83559606482</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I56" s="5">
         <v>46254</v>
@@ -4781,13 +4847,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q56" s="5">
         <v>46254</v>
@@ -4807,7 +4873,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B57" s="8">
         <v>46169.55859488426</v>
@@ -4819,16 +4885,16 @@
         <v>46197.85937331019</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I57" s="8">
         <v>46258</v>
@@ -4846,13 +4912,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q57" s="8">
         <v>46258</v>
@@ -4872,7 +4938,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B58" s="5">
         <v>46169.55860118056</v>
@@ -4884,16 +4950,16 @@
         <v>46198.59771457176</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I58" s="5">
         <v>46254</v>
@@ -4911,13 +4977,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q58" s="5">
         <v>46254</v>
@@ -4937,7 +5003,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B59" s="8">
         <v>46169.55860636574</v>
@@ -4949,16 +5015,16 @@
         <v>46198.597709444446</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I59" s="8">
         <v>46258</v>
@@ -4976,13 +5042,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q59" s="8">
         <v>46258</v>
@@ -4997,12 +5063,12 @@
         <v>1</v>
       </c>
       <c r="U59" s="12" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B60" s="5">
         <v>46169.558650127314</v>
@@ -5014,16 +5080,16 @@
         <v>46198.59773310185</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I60" s="5">
         <v>46254</v>
@@ -5041,13 +5107,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q60" s="5">
         <v>46254</v>
@@ -5067,7 +5133,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B61" s="8">
         <v>46169.55865608796</v>
@@ -5079,16 +5145,16 @@
         <v>46198.59773317129</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I61" s="8">
         <v>46258</v>
@@ -5106,13 +5172,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q61" s="8">
         <v>46258</v>
@@ -5127,12 +5193,12 @@
         <v>1</v>
       </c>
       <c r="U61" s="12" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B62" s="5">
         <v>46169.55866105324</v>
@@ -5144,7 +5210,7 @@
         <v>46198.68229049769</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>25</v>
@@ -5168,7 +5234,7 @@
         <v>26</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P62" s="6" t="s">
         <v>26</v>
@@ -5185,7 +5251,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B63" s="8">
         <v>46169.55866469907</v>
@@ -5197,16 +5263,16 @@
         <v>46197.85915361111</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H63" s="9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="I63" s="8">
         <v>46260</v>
@@ -5224,13 +5290,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P63" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q63" s="8">
         <v>46260</v>
@@ -5250,7 +5316,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B64" s="5">
         <v>46169.55867099537</v>
@@ -5262,16 +5328,16 @@
         <v>46197.85936673611</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="I64" s="5">
         <v>46260</v>
@@ -5289,13 +5355,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5305,7 +5371,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B65" s="8">
         <v>46169.558703518516</v>
@@ -5317,16 +5383,16 @@
         <v>46197.85387390046</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H65" s="9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="I65" s="8">
         <v>46269</v>
@@ -5344,13 +5410,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q65" s="8">
         <v>46269</v>
@@ -5365,12 +5431,12 @@
         <v>1</v>
       </c>
       <c r="U65" s="12" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B66" s="5">
         <v>46169.55870879629</v>
@@ -5382,16 +5448,16 @@
         <v>46197.85915420139</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="I66" s="5">
         <v>46269</v>
@@ -5409,13 +5475,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5425,7 +5491,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B67" s="8">
         <v>46169.558740625</v>
@@ -5437,16 +5503,16 @@
         <v>46205.65959174768</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H67" s="9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I67" s="8">
         <v>46274</v>
@@ -5464,13 +5530,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P67" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q67" s="8">
         <v>46274</v>
@@ -5485,12 +5551,12 @@
         <v>1</v>
       </c>
       <c r="U67" s="12" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B68" s="5">
         <v>46169.558745243055</v>
@@ -5502,16 +5568,16 @@
         <v>46205.659588587965</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I68" s="5">
         <v>46274</v>
@@ -5529,13 +5595,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q68" s="6"/>
       <c r="R68" s="6"/>
@@ -5545,7 +5611,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B69" s="8">
         <v>46169.55876947917</v>
@@ -5557,7 +5623,7 @@
         <v>46211.70953918982</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>25</v>
@@ -5581,7 +5647,7 @@
         <v>26</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="P69" s="9" t="s">
         <v>26</v>
@@ -5594,7 +5660,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B70" s="5">
         <v>46169.55880633101</v>
@@ -5606,16 +5672,16 @@
         <v>46200.8197621875</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I70" s="5">
         <v>46220</v>
@@ -5633,13 +5699,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q70" s="5">
         <v>46220</v>
@@ -5659,7 +5725,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B71" s="8">
         <v>46169.5588177662</v>
@@ -5671,16 +5737,16 @@
         <v>46200.819831597226</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H71" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I71" s="8">
         <v>46325</v>
@@ -5698,13 +5764,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="P71" s="9" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q71" s="8">
         <v>46325</v>
@@ -5713,7 +5779,7 @@
         <v>46325</v>
       </c>
       <c r="S71" s="11" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="T71" s="9">
         <v>1</v>
@@ -5724,7 +5790,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B72" s="5">
         <v>46169.55882295139</v>
@@ -5736,16 +5802,16 @@
         <v>46200.81928909722</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I72" s="5">
         <v>46293</v>
@@ -5763,13 +5829,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q72" s="5">
         <v>46293</v>
@@ -5789,7 +5855,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B73" s="8">
         <v>46169.55882788195</v>
@@ -5801,16 +5867,16 @@
         <v>46211.7093043287</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="9" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H73" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I73" s="8">
         <v>46282</v>
@@ -5828,13 +5894,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="9" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="P73" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q73" s="8">
         <v>46282</v>
@@ -5854,7 +5920,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B74" s="5">
         <v>46169.55884254629</v>
@@ -5866,7 +5932,7 @@
         <v>46211.86406403936</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>25</v>
@@ -5890,7 +5956,7 @@
         <v>26</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="P74" s="6" t="s">
         <v>26</v>
@@ -5907,7 +5973,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B75" s="8">
         <v>46169.55884548611</v>
@@ -5919,16 +5985,16 @@
         <v>46211.70929236111</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H75" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I75" s="8">
         <v>46276</v>
@@ -5946,13 +6012,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q75" s="8">
         <v>46276</v>
@@ -5967,12 +6033,12 @@
         <v>1</v>
       </c>
       <c r="U75" s="12" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B76" s="5">
         <v>46169.55884993056</v>
@@ -5984,16 +6050,16 @@
         <v>46211.70929407407</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I76" s="5">
         <v>46276</v>
@@ -6011,13 +6077,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -6027,7 +6093,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B77" s="8">
         <v>46169.55893170139</v>
@@ -6039,16 +6105,16 @@
         <v>46197.495185555556</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H77" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I77" s="8">
         <v>46296</v>
@@ -6066,13 +6132,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="9" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P77" s="9" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q77" s="8">
         <v>46296</v>
@@ -6092,7 +6158,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B78" s="5">
         <v>46169.55893543981</v>
@@ -6104,16 +6170,16 @@
         <v>46204.879924837966</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I78" s="5">
         <v>46296</v>
@@ -6131,13 +6197,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q78" s="6"/>
       <c r="R78" s="6"/>
@@ -6147,7 +6213,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B79" s="8">
         <v>46169.558869560184</v>
@@ -6159,16 +6225,16 @@
         <v>46204.87981377315</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H79" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I79" s="8">
         <v>46328</v>
@@ -6186,13 +6252,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="9" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="P79" s="9" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q79" s="8">
         <v>46328</v>
@@ -6212,7 +6278,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B80" s="5">
         <v>46169.55887296297</v>
@@ -6224,16 +6290,16 @@
         <v>46204.87978310185</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I80" s="5">
         <v>46328</v>
@@ -6251,13 +6317,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -6267,7 +6333,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B81" s="8">
         <v>46169.5589025463</v>
@@ -6279,16 +6345,16 @@
         <v>46204.880057013885</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H81" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I81" s="8">
         <v>46329</v>
@@ -6306,13 +6372,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q81" s="8">
         <v>46329</v>
@@ -6332,7 +6398,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B82" s="5">
         <v>46169.55890609954</v>
@@ -6344,16 +6410,16 @@
         <v>46204.87991711806</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I82" s="5">
         <v>46329</v>
@@ -6371,13 +6437,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6387,7 +6453,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B83" s="8">
         <v>46169.55900443287</v>
@@ -6399,16 +6465,16 @@
         <v>46206.48671975694</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H83" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I83" s="8">
         <v>46330</v>
@@ -6426,13 +6492,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="9" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="O83" s="9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P83" s="9" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q83" s="8">
         <v>46330</v>
@@ -6452,7 +6518,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B84" s="5">
         <v>46169.55901002315</v>
@@ -6464,16 +6530,16 @@
         <v>46206.48669563657</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I84" s="5">
         <v>46330</v>
@@ -6491,13 +6557,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q84" s="6"/>
       <c r="R84" s="6"/>
@@ -6507,7 +6573,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B85" s="8">
         <v>46169.55904462963</v>
@@ -6519,16 +6585,16 @@
         <v>46206.48682021991</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H85" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I85" s="8">
         <v>46332</v>
@@ -6546,13 +6612,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="9" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="O85" s="9" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="P85" s="9" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q85" s="8">
         <v>46332</v>
@@ -6572,7 +6638,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B86" s="5">
         <v>46169.559050138894</v>
@@ -6584,16 +6650,16 @@
         <v>46211.86420142361</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I86" s="5">
         <v>46332</v>
@@ -6611,13 +6677,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6627,7 +6693,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B87" s="8">
         <v>46169.55907484954</v>
@@ -6637,7 +6703,7 @@
         <v>46211.8640300463</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>25</v>
@@ -6661,7 +6727,7 @@
         <v>26</v>
       </c>
       <c r="O87" s="9" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="P87" s="9" t="s">
         <v>26</v>
@@ -6671,12 +6737,12 @@
       <c r="S87" s="9"/>
       <c r="T87" s="9"/>
       <c r="U87" s="12" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B88" s="5">
         <v>46169.55907863426</v>
@@ -6688,16 +6754,16 @@
         <v>46211.70008446759</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="I88" s="5">
         <v>46335</v>
@@ -6715,13 +6781,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q88" s="5">
         <v>46335</v>
@@ -6741,7 +6807,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B89" s="8">
         <v>46169.55908684028</v>
@@ -6753,16 +6819,16 @@
         <v>46211.700054201385</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="9" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H89" s="9" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="I89" s="8">
         <v>46335</v>
@@ -6780,13 +6846,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="O89" s="9" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="P89" s="9" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q89" s="9"/>
       <c r="R89" s="9"/>
@@ -6796,7 +6862,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B90" s="5">
         <v>46169.55918673611</v>
@@ -6808,16 +6874,16 @@
         <v>46211.83096391204</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I90" s="5">
         <v>46336</v>
@@ -6835,13 +6901,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q90" s="5">
         <v>46336</v>
@@ -6861,7 +6927,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B91" s="8">
         <v>46169.55919113426</v>
@@ -6873,16 +6939,16 @@
         <v>46211.83093474537</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H91" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I91" s="8">
         <v>46336</v>
@@ -6900,13 +6966,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="9" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="O91" s="9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P91" s="9" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q91" s="9"/>
       <c r="R91" s="9"/>
@@ -6916,7 +6982,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B92" s="5">
         <v>46169.559239560185</v>
@@ -6928,16 +6994,16 @@
         <v>46197.859819363424</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="I92" s="5">
         <v>46337</v>
@@ -6955,13 +7021,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q92" s="5">
         <v>46337</v>
@@ -6976,12 +7042,12 @@
         <v>1</v>
       </c>
       <c r="U92" s="12" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B93" s="8">
         <v>46169.559243842596</v>
@@ -6993,16 +7059,16 @@
         <v>46211.830942650464</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H93" s="9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="I93" s="8">
         <v>46337</v>
@@ -7020,13 +7086,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="9" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="O93" s="9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P93" s="9" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q93" s="9"/>
       <c r="R93" s="9"/>
@@ -7036,7 +7102,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B94" s="5">
         <v>46169.55929686343</v>
@@ -7048,16 +7114,16 @@
         <v>46211.86402001158</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="I94" s="5">
         <v>46338</v>
@@ -7075,13 +7141,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q94" s="5">
         <v>46338</v>
@@ -7101,7 +7167,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B95" s="8">
         <v>46169.55930180555</v>
@@ -7113,16 +7179,16 @@
         <v>46211.863992280094</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H95" s="9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="I95" s="8">
         <v>46338</v>
@@ -7140,13 +7206,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="9" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="O95" s="9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P95" s="9" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q95" s="9"/>
       <c r="R95" s="9"/>
@@ -7156,7 +7222,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B96" s="5">
         <v>46169.55938721065</v>
@@ -7166,7 +7232,7 @@
         <v>46169.60672822916</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>25</v>
@@ -7190,7 +7256,7 @@
         <v>26</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="P96" s="6" t="s">
         <v>26</v>
@@ -7203,7 +7269,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B97" s="8">
         <v>46169.55939094907</v>
@@ -7213,16 +7279,16 @@
         <v>46211.86403020834</v>
       </c>
       <c r="E97" s="9" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G97" s="9" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H97" s="9" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="I97" s="8">
         <v>46339</v>
@@ -7240,13 +7306,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="9" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="O97" s="9" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="P97" s="9" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q97" s="8">
         <v>46339</v>
@@ -7261,12 +7327,12 @@
         <v>0</v>
       </c>
       <c r="U97" s="12" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B98" s="5">
         <v>46169.55939643519</v>
@@ -7276,16 +7342,16 @@
         <v>46211.86403085648</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H98" s="6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I98" s="5">
         <v>46339</v>
@@ -7303,13 +7369,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q98" s="5">
         <v>46339</v>
@@ -7324,7 +7390,7 @@
         <v>0</v>
       </c>
       <c r="U98" s="12" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001557 - ATACAMA KOZAN OT4340.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4340.xlsx
@@ -5669,7 +5669,7 @@
         <v>46200.81968587963</v>
       </c>
       <c r="D70" s="5">
-        <v>46200.8197621875</v>
+        <v>46216.206479560184</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>238</v>
@@ -5713,8 +5713,8 @@
       <c r="R70" s="5">
         <v>46223</v>
       </c>
-      <c r="S70" s="10" t="s">
-        <v>32</v>
+      <c r="S70" s="12" t="s">
+        <v>108</v>
       </c>
       <c r="T70" s="6">
         <v>1</v>

--- a/data/50001557 - ATACAMA KOZAN OT4340.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4340.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1184" uniqueCount="311">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1165" uniqueCount="308">
   <si>
     <t xml:space="preserve"> 50001557 - ATACAMA KOZAN</t>
   </si>
@@ -333,9 +333,6 @@
     <t>propuesta nucleo rodete OT 4340</t>
   </si>
   <si>
-    <t>benjamin.bustos@zitron.com</t>
-  </si>
-  <si>
     <t>Generación OC Rodete OT 4340 ,Propuesta compras:</t>
   </si>
   <si>
@@ -343,12 +340,6 @@
   </si>
   <si>
     <t>propuesta Corte Laser OT 4340</t>
-  </si>
-  <si>
-    <t>hugo isla martinez</t>
-  </si>
-  <si>
-    <t>hugo.isla@zitron.com</t>
   </si>
   <si>
     <t>check planos</t>
@@ -2481,11 +2472,9 @@
         <v>26</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="H17" s="9" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H17" s="9"/>
       <c r="I17" s="8">
         <v>46167</v>
       </c>
@@ -2508,7 +2497,7 @@
         <v>56</v>
       </c>
       <c r="P17" s="9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="Q17" s="8">
         <v>46167</v>
@@ -2528,7 +2517,7 @@
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B18" s="5">
         <v>46169.55823646991</v>
@@ -2540,17 +2529,15 @@
         <v>46183.90665107639</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="H18" s="6" t="s">
-        <v>78</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H18" s="6"/>
       <c r="I18" s="5">
         <v>46239</v>
       </c>
@@ -2570,10 +2557,10 @@
         <v>63</v>
       </c>
       <c r="O18" s="6" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="Q18" s="5">
         <v>46239</v>
@@ -2593,7 +2580,7 @@
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B19" s="8">
         <v>46169.55824171296</v>
@@ -2605,17 +2592,15 @@
         <v>46183.90666170139</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="F19" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G19" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="H19" s="9" t="s">
-        <v>78</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H19" s="9"/>
       <c r="I19" s="8">
         <v>46239</v>
       </c>
@@ -2635,10 +2620,10 @@
         <v>63</v>
       </c>
       <c r="O19" s="9" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="P19" s="9" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="Q19" s="8">
         <v>46239</v>
@@ -2658,7 +2643,7 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B20" s="5">
         <v>46169.55824574074</v>
@@ -2670,17 +2655,15 @@
         <v>46190.64415820602</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="H20" s="6" t="s">
-        <v>78</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H20" s="6"/>
       <c r="I20" s="5">
         <v>46239</v>
       </c>
@@ -2700,10 +2683,10 @@
         <v>63</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="Q20" s="5">
         <v>46239</v>
@@ -2723,7 +2706,7 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B21" s="8">
         <v>46169.55825006944</v>
@@ -2735,17 +2718,15 @@
         <v>46183.90735393518</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="F21" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G21" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="H21" s="9" t="s">
-        <v>78</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H21" s="9"/>
       <c r="I21" s="8">
         <v>46239</v>
       </c>
@@ -2765,10 +2746,10 @@
         <v>63</v>
       </c>
       <c r="O21" s="9" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="P21" s="9" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="Q21" s="8">
         <v>46239</v>
@@ -2788,7 +2769,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B22" s="5">
         <v>46169.55801826389</v>
@@ -2800,7 +2781,7 @@
         <v>46200.818425798614</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>25</v>
@@ -2824,7 +2805,7 @@
         <v>26</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="P22" s="6" t="s">
         <v>26</v>
@@ -2837,7 +2818,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B23" s="8">
         <v>46169.558301956014</v>
@@ -2849,16 +2830,16 @@
         <v>46200.81833380787</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="I23" s="8">
         <v>46169</v>
@@ -2876,13 +2857,13 @@
         <v>26</v>
       </c>
       <c r="N23" s="9" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="O23" s="9" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="P23" s="9" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="Q23" s="8">
         <v>46169</v>
@@ -2902,7 +2883,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B24" s="5">
         <v>46169.558306516206</v>
@@ -2914,16 +2895,16 @@
         <v>46195.69079224537</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="I24" s="5">
         <v>46169</v>
@@ -2941,13 +2922,13 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="O24" s="6" t="s">
         <v>69</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="Q24" s="6"/>
       <c r="R24" s="6"/>
@@ -2958,12 +2939,12 @@
         <v>0</v>
       </c>
       <c r="U24" s="11" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B25" s="8">
         <v>46169.55831137732</v>
@@ -2975,16 +2956,16 @@
         <v>46195.690800474535</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="I25" s="8">
         <v>46171</v>
@@ -3002,13 +2983,13 @@
         <v>26</v>
       </c>
       <c r="N25" s="9" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="O25" s="9" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="P25" s="9" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="Q25" s="9"/>
       <c r="R25" s="9"/>
@@ -3019,12 +3000,12 @@
         <v>0</v>
       </c>
       <c r="U25" s="11" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B26" s="5">
         <v>46169.55831605324</v>
@@ -3036,16 +3017,16 @@
         <v>46212.20714363426</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="I26" s="5">
         <v>46169</v>
@@ -3063,13 +3044,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="Q26" s="5">
         <v>46169</v>
@@ -3078,7 +3059,7 @@
         <v>46219</v>
       </c>
       <c r="S26" s="12" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="T26" s="6">
         <v>1</v>
@@ -3089,7 +3070,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B27" s="8">
         <v>46169.55832063657</v>
@@ -3101,16 +3082,16 @@
         <v>46184.7364097338</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="I27" s="8">
         <v>46169</v>
@@ -3128,13 +3109,13 @@
         <v>26</v>
       </c>
       <c r="N27" s="9" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="O27" s="9" t="s">
         <v>72</v>
       </c>
       <c r="P27" s="9" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="Q27" s="9"/>
       <c r="R27" s="9"/>
@@ -3145,12 +3126,12 @@
         <v>0</v>
       </c>
       <c r="U27" s="11" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B28" s="5">
         <v>46169.55832539352</v>
@@ -3162,16 +3143,16 @@
         <v>46184.736449375</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="I28" s="5">
         <v>46171</v>
@@ -3189,13 +3170,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
@@ -3206,12 +3187,12 @@
         <v>0</v>
       </c>
       <c r="U28" s="11" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B29" s="8">
         <v>46169.55833006944</v>
@@ -3223,16 +3204,16 @@
         <v>46200.81836952546</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="I29" s="8">
         <v>46161</v>
@@ -3250,13 +3231,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="9" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="O29" s="9" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="P29" s="9" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="Q29" s="8">
         <v>46161</v>
@@ -3276,7 +3257,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B30" s="5">
         <v>46169.55833486111</v>
@@ -3288,16 +3269,16 @@
         <v>46195.69066259259</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="I30" s="5">
         <v>46161</v>
@@ -3315,13 +3296,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="O30" s="6" t="s">
         <v>66</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -3332,12 +3313,12 @@
         <v>0</v>
       </c>
       <c r="U30" s="11" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="B31" s="8">
         <v>46169.5583402662</v>
@@ -3349,16 +3330,16 @@
         <v>46195.69066760417</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="I31" s="8">
         <v>46178</v>
@@ -3376,13 +3357,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="O31" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="O31" s="9" t="s">
-        <v>119</v>
-      </c>
       <c r="P31" s="9" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="Q31" s="9"/>
       <c r="R31" s="9"/>
@@ -3393,12 +3374,12 @@
         <v>0</v>
       </c>
       <c r="U31" s="11" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B32" s="5">
         <v>46169.55834503472</v>
@@ -3410,16 +3391,16 @@
         <v>46195.6906680324</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="I32" s="5">
         <v>46178</v>
@@ -3437,13 +3418,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="O32" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="O32" s="6" t="s">
-        <v>119</v>
-      </c>
       <c r="P32" s="6" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
@@ -3454,12 +3435,12 @@
         <v>0</v>
       </c>
       <c r="U32" s="11" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B33" s="8">
         <v>46169.55836335648</v>
@@ -3471,16 +3452,16 @@
         <v>46184.532641875005</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="I33" s="8">
         <v>46241</v>
@@ -3498,13 +3479,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="Q33" s="8">
         <v>46241</v>
@@ -3524,7 +3505,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B34" s="5">
         <v>46169.558367986116</v>
@@ -3536,16 +3517,16 @@
         <v>46184.53245875</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="I34" s="5">
         <v>46241</v>
@@ -3563,13 +3544,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3580,12 +3561,12 @@
         <v>0</v>
       </c>
       <c r="U34" s="11" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B35" s="8">
         <v>46169.55837292824</v>
@@ -3597,16 +3578,16 @@
         <v>46184.532615856486</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="I35" s="8">
         <v>46245</v>
@@ -3624,13 +3605,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="P35" s="9" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="Q35" s="9"/>
       <c r="R35" s="9"/>
@@ -3641,12 +3622,12 @@
         <v>0</v>
       </c>
       <c r="U35" s="11" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="B36" s="5">
         <v>46169.55837825232</v>
@@ -3658,16 +3639,16 @@
         <v>46184.53258194444</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="I36" s="5">
         <v>46241</v>
@@ -3685,10 +3666,10 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="P36" s="6" t="s">
         <v>26</v>
@@ -3711,7 +3692,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B37" s="8">
         <v>46169.558381979165</v>
@@ -3723,16 +3704,16 @@
         <v>46184.5322071875</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="I37" s="8">
         <v>46241</v>
@@ -3750,13 +3731,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="O37" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="P37" s="9" t="s">
         <v>139</v>
-      </c>
-      <c r="O37" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="P37" s="9" t="s">
-        <v>142</v>
       </c>
       <c r="Q37" s="9"/>
       <c r="R37" s="9"/>
@@ -3766,7 +3747,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="B38" s="5">
         <v>46169.55838657408</v>
@@ -3778,16 +3759,16 @@
         <v>46184.53255631945</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="I38" s="5">
         <v>46245</v>
@@ -3805,13 +3786,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -3821,7 +3802,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="B39" s="8">
         <v>46169.55839107639</v>
@@ -3833,16 +3814,16 @@
         <v>46205.600326053245</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="I39" s="8">
         <v>46241</v>
@@ -3860,10 +3841,10 @@
         <v>26</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="P39" s="9" t="s">
         <v>26</v>
@@ -3886,7 +3867,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="B40" s="5">
         <v>46169.55839478009</v>
@@ -3898,16 +3879,16 @@
         <v>46195.70360162037</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="I40" s="5">
         <v>46241</v>
@@ -3925,13 +3906,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -3941,7 +3922,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="B41" s="8">
         <v>46169.55839910879</v>
@@ -3953,16 +3934,16 @@
         <v>46195.70375376157</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="I41" s="8">
         <v>46252</v>
@@ -3980,13 +3961,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="Q41" s="9"/>
       <c r="R41" s="9"/>
@@ -3996,7 +3977,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B42" s="5">
         <v>46169.55840355324</v>
@@ -4008,16 +3989,16 @@
         <v>46205.59994755787</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="I42" s="5">
         <v>46281</v>
@@ -4035,10 +4016,10 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>26</v>
@@ -4051,7 +4032,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="B43" s="8">
         <v>46169.55840677083</v>
@@ -4063,16 +4044,16 @@
         <v>46191.53701371528</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="I43" s="8">
         <v>46241</v>
@@ -4090,10 +4071,10 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="P43" s="9" t="s">
         <v>26</v>
@@ -4116,7 +4097,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="B44" s="5">
         <v>46169.55841037037</v>
@@ -4128,16 +4109,16 @@
         <v>46191.53679194444</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="I44" s="5">
         <v>46241</v>
@@ -4155,13 +4136,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="O44" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="P44" s="6" t="s">
         <v>161</v>
-      </c>
-      <c r="O44" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="P44" s="6" t="s">
-        <v>164</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4171,7 +4152,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="B45" s="8">
         <v>46169.558458217594</v>
@@ -4183,16 +4164,16 @@
         <v>46191.53698841435</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="I45" s="8">
         <v>46245</v>
@@ -4210,13 +4191,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="P45" s="9" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="Q45" s="9"/>
       <c r="R45" s="9"/>
@@ -4226,7 +4207,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="B46" s="5">
         <v>46169.5584643287</v>
@@ -4236,7 +4217,7 @@
         <v>46182.75962331019</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>25</v>
@@ -4260,7 +4241,7 @@
         <v>26</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4270,12 +4251,12 @@
       <c r="S46" s="6"/>
       <c r="T46" s="6"/>
       <c r="U46" s="12" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="B47" s="8">
         <v>46169.55846813657</v>
@@ -4287,16 +4268,16 @@
         <v>46197.715420312496</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I47" s="8">
         <v>46167</v>
@@ -4314,13 +4295,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="Q47" s="8">
         <v>46167</v>
@@ -4329,7 +4310,7 @@
         <v>46184</v>
       </c>
       <c r="S47" s="11" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="T47" s="9">
         <v>1</v>
@@ -4340,7 +4321,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="B48" s="5">
         <v>46169.558472766206</v>
@@ -4352,16 +4333,16 @@
         <v>46181.72663056713</v>
       </c>
       <c r="E48" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="F48" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G48" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="F48" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G48" s="6" t="s">
-        <v>179</v>
-      </c>
       <c r="H48" s="6" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="I48" s="5">
         <v>46167</v>
@@ -4379,13 +4360,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="O48" s="6" t="s">
         <v>60</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="Q48" s="6"/>
       <c r="R48" s="6"/>
@@ -4395,7 +4376,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="B49" s="8">
         <v>46169.55849938658</v>
@@ -4407,16 +4388,16 @@
         <v>46197.71545016204</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I49" s="8">
         <v>46218</v>
@@ -4434,13 +4415,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="Q49" s="8">
         <v>46218</v>
@@ -4460,7 +4441,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B50" s="5">
         <v>46169.55850371528</v>
@@ -4472,16 +4453,16 @@
         <v>46195.690583055555</v>
       </c>
       <c r="E50" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="F50" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G50" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="F50" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G50" s="6" t="s">
-        <v>179</v>
-      </c>
       <c r="H50" s="6" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="I50" s="5">
         <v>46218</v>
@@ -4499,13 +4480,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="O50" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="P50" s="6" t="s">
         <v>183</v>
-      </c>
-      <c r="O50" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="P50" s="6" t="s">
-        <v>186</v>
       </c>
       <c r="Q50" s="6"/>
       <c r="R50" s="6"/>
@@ -4515,7 +4496,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="B51" s="8">
         <v>46169.55853228009</v>
@@ -4527,16 +4508,16 @@
         <v>46182.759871076385</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="I51" s="8">
         <v>46238</v>
@@ -4554,13 +4535,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="Q51" s="8">
         <v>46238</v>
@@ -4580,7 +4561,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="B52" s="5">
         <v>46169.55854641204</v>
@@ -4592,16 +4573,16 @@
         <v>46182.75984881945</v>
       </c>
       <c r="E52" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="F52" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G52" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="F52" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G52" s="6" t="s">
-        <v>179</v>
-      </c>
       <c r="H52" s="6" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="I52" s="5">
         <v>46238</v>
@@ -4619,13 +4600,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4635,7 +4616,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="B53" s="8">
         <v>46169.558565775464</v>
@@ -4647,16 +4628,16 @@
         <v>46211.86422231482</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="I53" s="8">
         <v>46331</v>
@@ -4674,10 +4655,10 @@
         <v>26</v>
       </c>
       <c r="N53" s="9" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="P53" s="9" t="s">
         <v>26</v>
@@ -4700,7 +4681,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="B54" s="5">
         <v>46169.55856972223</v>
@@ -4712,16 +4693,16 @@
         <v>46211.86419394676</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="I54" s="5">
         <v>46331</v>
@@ -4739,13 +4720,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="Q54" s="6"/>
       <c r="R54" s="6"/>
@@ -4755,7 +4736,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="B55" s="8">
         <v>46169.558586307874</v>
@@ -4767,7 +4748,7 @@
         <v>46198.597746307874</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>25</v>
@@ -4791,7 +4772,7 @@
         <v>26</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="P55" s="9" t="s">
         <v>26</v>
@@ -4808,7 +4789,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="B56" s="5">
         <v>46169.55858945602</v>
@@ -4820,16 +4801,16 @@
         <v>46197.83559606482</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="I56" s="5">
         <v>46254</v>
@@ -4847,13 +4828,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="Q56" s="5">
         <v>46254</v>
@@ -4873,7 +4854,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="B57" s="8">
         <v>46169.55859488426</v>
@@ -4885,16 +4866,16 @@
         <v>46197.85937331019</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="I57" s="8">
         <v>46258</v>
@@ -4912,13 +4893,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="O57" s="9" t="s">
         <v>197</v>
       </c>
-      <c r="O57" s="9" t="s">
-        <v>200</v>
-      </c>
       <c r="P57" s="9" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="Q57" s="8">
         <v>46258</v>
@@ -4938,7 +4919,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B58" s="5">
         <v>46169.55860118056</v>
@@ -4950,16 +4931,16 @@
         <v>46198.59771457176</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="I58" s="5">
         <v>46254</v>
@@ -4977,13 +4958,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="Q58" s="5">
         <v>46254</v>
@@ -5003,7 +4984,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="B59" s="8">
         <v>46169.55860636574</v>
@@ -5015,16 +4996,16 @@
         <v>46198.597709444446</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="I59" s="8">
         <v>46258</v>
@@ -5042,13 +5023,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="Q59" s="8">
         <v>46258</v>
@@ -5063,12 +5044,12 @@
         <v>1</v>
       </c>
       <c r="U59" s="12" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="B60" s="5">
         <v>46169.558650127314</v>
@@ -5080,16 +5061,16 @@
         <v>46198.59773310185</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="I60" s="5">
         <v>46254</v>
@@ -5107,13 +5088,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="Q60" s="5">
         <v>46254</v>
@@ -5133,7 +5114,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B61" s="8">
         <v>46169.55865608796</v>
@@ -5145,16 +5126,16 @@
         <v>46198.59773317129</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="I61" s="8">
         <v>46258</v>
@@ -5172,13 +5153,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="Q61" s="8">
         <v>46258</v>
@@ -5193,12 +5174,12 @@
         <v>1</v>
       </c>
       <c r="U61" s="12" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="B62" s="5">
         <v>46169.55866105324</v>
@@ -5210,7 +5191,7 @@
         <v>46198.68229049769</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>25</v>
@@ -5234,7 +5215,7 @@
         <v>26</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="P62" s="6" t="s">
         <v>26</v>
@@ -5251,7 +5232,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="B63" s="8">
         <v>46169.55866469907</v>
@@ -5263,16 +5244,16 @@
         <v>46197.85915361111</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="9" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="H63" s="9" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="I63" s="8">
         <v>46260</v>
@@ -5290,13 +5271,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="P63" s="9" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="Q63" s="8">
         <v>46260</v>
@@ -5316,7 +5297,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="B64" s="5">
         <v>46169.55867099537</v>
@@ -5328,16 +5309,16 @@
         <v>46197.85936673611</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="I64" s="5">
         <v>46260</v>
@@ -5355,13 +5336,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5371,7 +5352,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="B65" s="8">
         <v>46169.558703518516</v>
@@ -5383,16 +5364,16 @@
         <v>46197.85387390046</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="H65" s="9" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="I65" s="8">
         <v>46269</v>
@@ -5410,13 +5391,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="Q65" s="8">
         <v>46269</v>
@@ -5431,12 +5412,12 @@
         <v>1</v>
       </c>
       <c r="U65" s="12" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="B66" s="5">
         <v>46169.55870879629</v>
@@ -5448,16 +5429,16 @@
         <v>46197.85915420139</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="I66" s="5">
         <v>46269</v>
@@ -5475,13 +5456,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="O66" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="P66" s="6" t="s">
         <v>227</v>
-      </c>
-      <c r="O66" s="6" t="s">
-        <v>229</v>
-      </c>
-      <c r="P66" s="6" t="s">
-        <v>230</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5491,7 +5472,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="B67" s="8">
         <v>46169.558740625</v>
@@ -5503,16 +5484,16 @@
         <v>46205.65959174768</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="H67" s="9" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="I67" s="8">
         <v>46274</v>
@@ -5530,13 +5511,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="P67" s="9" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="Q67" s="8">
         <v>46274</v>
@@ -5551,12 +5532,12 @@
         <v>1</v>
       </c>
       <c r="U67" s="12" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="B68" s="5">
         <v>46169.558745243055</v>
@@ -5568,16 +5549,16 @@
         <v>46205.659588587965</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="I68" s="5">
         <v>46274</v>
@@ -5595,13 +5576,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="Q68" s="6"/>
       <c r="R68" s="6"/>
@@ -5611,7 +5592,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="B69" s="8">
         <v>46169.55876947917</v>
@@ -5623,7 +5604,7 @@
         <v>46211.70953918982</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>25</v>
@@ -5647,7 +5628,7 @@
         <v>26</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="P69" s="9" t="s">
         <v>26</v>
@@ -5660,7 +5641,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="B70" s="5">
         <v>46169.55880633101</v>
@@ -5672,16 +5653,16 @@
         <v>46216.206479560184</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="I70" s="5">
         <v>46220</v>
@@ -5699,13 +5680,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="Q70" s="5">
         <v>46220</v>
@@ -5714,7 +5695,7 @@
         <v>46223</v>
       </c>
       <c r="S70" s="12" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="T70" s="6">
         <v>1</v>
@@ -5725,7 +5706,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="B71" s="8">
         <v>46169.5588177662</v>
@@ -5737,16 +5718,16 @@
         <v>46200.819831597226</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="H71" s="9" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="I71" s="8">
         <v>46325</v>
@@ -5764,13 +5745,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="P71" s="9" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="Q71" s="8">
         <v>46325</v>
@@ -5779,7 +5760,7 @@
         <v>46325</v>
       </c>
       <c r="S71" s="11" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="T71" s="9">
         <v>1</v>
@@ -5790,7 +5771,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="B72" s="5">
         <v>46169.55882295139</v>
@@ -5802,16 +5783,16 @@
         <v>46200.81928909722</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="I72" s="5">
         <v>46293</v>
@@ -5829,13 +5810,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="Q72" s="5">
         <v>46293</v>
@@ -5855,7 +5836,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="B73" s="8">
         <v>46169.55882788195</v>
@@ -5867,16 +5848,16 @@
         <v>46211.7093043287</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="9" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="H73" s="9" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="I73" s="8">
         <v>46282</v>
@@ -5894,13 +5875,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="9" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="P73" s="9" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="Q73" s="8">
         <v>46282</v>
@@ -5920,7 +5901,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="B74" s="5">
         <v>46169.55884254629</v>
@@ -5932,7 +5913,7 @@
         <v>46211.86406403936</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>25</v>
@@ -5956,7 +5937,7 @@
         <v>26</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="P74" s="6" t="s">
         <v>26</v>
@@ -5973,7 +5954,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="B75" s="8">
         <v>46169.55884548611</v>
@@ -5985,17 +5966,15 @@
         <v>46211.70929236111</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="H75" s="9" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H75" s="9"/>
       <c r="I75" s="8">
         <v>46276</v>
       </c>
@@ -6012,13 +5991,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="Q75" s="8">
         <v>46276</v>
@@ -6033,12 +6012,12 @@
         <v>1</v>
       </c>
       <c r="U75" s="12" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="B76" s="5">
         <v>46169.55884993056</v>
@@ -6050,17 +6029,15 @@
         <v>46211.70929407407</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="H76" s="6" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H76" s="6"/>
       <c r="I76" s="5">
         <v>46276</v>
       </c>
@@ -6077,13 +6054,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="O76" s="6" t="s">
         <v>252</v>
       </c>
-      <c r="O76" s="6" t="s">
-        <v>255</v>
-      </c>
       <c r="P76" s="6" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -6093,7 +6070,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="B77" s="8">
         <v>46169.55893170139</v>
@@ -6105,17 +6082,15 @@
         <v>46197.495185555556</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="H77" s="9" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H77" s="9"/>
       <c r="I77" s="8">
         <v>46296</v>
       </c>
@@ -6132,13 +6107,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="9" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="P77" s="9" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="Q77" s="8">
         <v>46296</v>
@@ -6158,7 +6133,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="B78" s="5">
         <v>46169.55893543981</v>
@@ -6170,17 +6145,15 @@
         <v>46204.879924837966</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="H78" s="6" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H78" s="6"/>
       <c r="I78" s="5">
         <v>46296</v>
       </c>
@@ -6197,13 +6170,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="O78" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="P78" s="6" t="s">
         <v>257</v>
-      </c>
-      <c r="O78" s="6" t="s">
-        <v>259</v>
-      </c>
-      <c r="P78" s="6" t="s">
-        <v>260</v>
       </c>
       <c r="Q78" s="6"/>
       <c r="R78" s="6"/>
@@ -6213,7 +6186,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="B79" s="8">
         <v>46169.558869560184</v>
@@ -6225,17 +6198,15 @@
         <v>46204.87981377315</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="H79" s="9" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H79" s="9"/>
       <c r="I79" s="8">
         <v>46328</v>
       </c>
@@ -6252,13 +6223,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="9" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="P79" s="9" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="Q79" s="8">
         <v>46328</v>
@@ -6278,7 +6249,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="B80" s="5">
         <v>46169.55887296297</v>
@@ -6290,17 +6261,15 @@
         <v>46204.87978310185</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="H80" s="6" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H80" s="6"/>
       <c r="I80" s="5">
         <v>46328</v>
       </c>
@@ -6317,13 +6286,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="O80" s="6" t="s">
         <v>262</v>
       </c>
-      <c r="O80" s="6" t="s">
-        <v>265</v>
-      </c>
       <c r="P80" s="6" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -6333,7 +6302,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="B81" s="8">
         <v>46169.5589025463</v>
@@ -6345,17 +6314,15 @@
         <v>46204.880057013885</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="H81" s="9" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H81" s="9"/>
       <c r="I81" s="8">
         <v>46329</v>
       </c>
@@ -6372,13 +6339,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="Q81" s="8">
         <v>46329</v>
@@ -6398,7 +6365,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="B82" s="5">
         <v>46169.55890609954</v>
@@ -6410,17 +6377,15 @@
         <v>46204.87991711806</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="H82" s="6" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H82" s="6"/>
       <c r="I82" s="5">
         <v>46329</v>
       </c>
@@ -6437,13 +6402,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="O82" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="P82" s="6" t="s">
         <v>268</v>
-      </c>
-      <c r="O82" s="6" t="s">
-        <v>270</v>
-      </c>
-      <c r="P82" s="6" t="s">
-        <v>271</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6453,7 +6418,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="B83" s="8">
         <v>46169.55900443287</v>
@@ -6465,17 +6430,15 @@
         <v>46206.48671975694</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="H83" s="9" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H83" s="9"/>
       <c r="I83" s="8">
         <v>46330</v>
       </c>
@@ -6492,13 +6455,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="9" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="O83" s="9" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="P83" s="9" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="Q83" s="8">
         <v>46330</v>
@@ -6518,7 +6481,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="B84" s="5">
         <v>46169.55901002315</v>
@@ -6530,17 +6493,15 @@
         <v>46206.48669563657</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="H84" s="6" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H84" s="6"/>
       <c r="I84" s="5">
         <v>46330</v>
       </c>
@@ -6557,13 +6518,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="Q84" s="6"/>
       <c r="R84" s="6"/>
@@ -6573,7 +6534,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="B85" s="8">
         <v>46169.55904462963</v>
@@ -6585,17 +6546,15 @@
         <v>46206.48682021991</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="H85" s="9" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H85" s="9"/>
       <c r="I85" s="8">
         <v>46332</v>
       </c>
@@ -6612,13 +6571,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="9" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="O85" s="9" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="P85" s="9" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="Q85" s="8">
         <v>46332</v>
@@ -6638,7 +6597,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="B86" s="5">
         <v>46169.559050138894</v>
@@ -6650,17 +6609,15 @@
         <v>46211.86420142361</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="H86" s="6" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H86" s="6"/>
       <c r="I86" s="5">
         <v>46332</v>
       </c>
@@ -6677,13 +6634,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
+        <v>274</v>
+      </c>
+      <c r="O86" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="P86" s="6" t="s">
         <v>277</v>
-      </c>
-      <c r="O86" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="P86" s="6" t="s">
-        <v>280</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6693,7 +6650,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="B87" s="8">
         <v>46169.55907484954</v>
@@ -6703,7 +6660,7 @@
         <v>46211.8640300463</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>25</v>
@@ -6727,7 +6684,7 @@
         <v>26</v>
       </c>
       <c r="O87" s="9" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="P87" s="9" t="s">
         <v>26</v>
@@ -6737,12 +6694,12 @@
       <c r="S87" s="9"/>
       <c r="T87" s="9"/>
       <c r="U87" s="12" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="B88" s="5">
         <v>46169.55907863426</v>
@@ -6754,16 +6711,16 @@
         <v>46211.70008446759</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="I88" s="5">
         <v>46335</v>
@@ -6781,13 +6738,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="Q88" s="5">
         <v>46335</v>
@@ -6807,7 +6764,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="B89" s="8">
         <v>46169.55908684028</v>
@@ -6819,16 +6776,16 @@
         <v>46211.700054201385</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="9" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="H89" s="9" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="I89" s="8">
         <v>46335</v>
@@ -6846,13 +6803,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="9" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="O89" s="9" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="P89" s="9" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="Q89" s="9"/>
       <c r="R89" s="9"/>
@@ -6862,7 +6819,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="B90" s="5">
         <v>46169.55918673611</v>
@@ -6874,17 +6831,15 @@
         <v>46211.83096391204</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="H90" s="6" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H90" s="6"/>
       <c r="I90" s="5">
         <v>46336</v>
       </c>
@@ -6901,13 +6856,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="Q90" s="5">
         <v>46336</v>
@@ -6927,7 +6882,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="B91" s="8">
         <v>46169.55919113426</v>
@@ -6939,17 +6894,15 @@
         <v>46211.83093474537</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="H91" s="9" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H91" s="9"/>
       <c r="I91" s="8">
         <v>46336</v>
       </c>
@@ -6966,13 +6919,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="9" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="O91" s="9" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="P91" s="9" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="Q91" s="9"/>
       <c r="R91" s="9"/>
@@ -6982,7 +6935,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="B92" s="5">
         <v>46169.559239560185</v>
@@ -6994,16 +6947,16 @@
         <v>46197.859819363424</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="I92" s="5">
         <v>46337</v>
@@ -7021,13 +6974,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="Q92" s="5">
         <v>46337</v>
@@ -7042,12 +6995,12 @@
         <v>1</v>
       </c>
       <c r="U92" s="12" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="B93" s="8">
         <v>46169.559243842596</v>
@@ -7059,16 +7012,16 @@
         <v>46211.830942650464</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="9" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="H93" s="9" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="I93" s="8">
         <v>46337</v>
@@ -7086,13 +7039,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="9" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="O93" s="9" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="P93" s="9" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="Q93" s="9"/>
       <c r="R93" s="9"/>
@@ -7102,7 +7055,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="B94" s="5">
         <v>46169.55929686343</v>
@@ -7114,16 +7067,16 @@
         <v>46211.86402001158</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="I94" s="5">
         <v>46338</v>
@@ -7141,13 +7094,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="Q94" s="5">
         <v>46338</v>
@@ -7167,7 +7120,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="B95" s="8">
         <v>46169.55930180555</v>
@@ -7179,16 +7132,16 @@
         <v>46211.863992280094</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="9" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="H95" s="9" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="I95" s="8">
         <v>46338</v>
@@ -7206,13 +7159,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="9" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="O95" s="9" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="P95" s="9" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="Q95" s="9"/>
       <c r="R95" s="9"/>
@@ -7222,7 +7175,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="B96" s="5">
         <v>46169.55938721065</v>
@@ -7232,7 +7185,7 @@
         <v>46169.60672822916</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>25</v>
@@ -7256,7 +7209,7 @@
         <v>26</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="P96" s="6" t="s">
         <v>26</v>
@@ -7269,7 +7222,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="B97" s="8">
         <v>46169.55939094907</v>
@@ -7279,16 +7232,16 @@
         <v>46211.86403020834</v>
       </c>
       <c r="E97" s="9" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G97" s="9" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="H97" s="9" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="I97" s="8">
         <v>46339</v>
@@ -7306,13 +7259,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="9" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="O97" s="9" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="P97" s="9" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="Q97" s="8">
         <v>46339</v>
@@ -7327,12 +7280,12 @@
         <v>0</v>
       </c>
       <c r="U97" s="12" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="B98" s="5">
         <v>46169.55939643519</v>
@@ -7342,7 +7295,7 @@
         <v>46211.86403085648</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -7369,13 +7322,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="Q98" s="5">
         <v>46339</v>
@@ -7390,7 +7343,7 @@
         <v>0</v>
       </c>
       <c r="U98" s="12" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001557 - ATACAMA KOZAN OT4340.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4340.xlsx
@@ -429,400 +429,400 @@
     <t>Generación OC Rodete OT 4340 ,Fabricación Rodete OT 4340</t>
   </si>
   <si>
+    <t>Alta</t>
+  </si>
+  <si>
+    <t>1215166329218738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generación OC Rodete OT 4340 </t>
+  </si>
+  <si>
+    <t>rodete OT 4340,Fabricación Rodete OT 4340</t>
+  </si>
+  <si>
+    <t>1215166243290478</t>
+  </si>
+  <si>
+    <t>Fabricación Rodete OT 4340</t>
+  </si>
+  <si>
+    <t>rodete OT 4340,Recepcion Rodete</t>
+  </si>
+  <si>
+    <t>1215166433395167</t>
+  </si>
+  <si>
+    <t>Motor OT 4340</t>
+  </si>
+  <si>
+    <t>Generación OC motor OT 4340,Fabricación motor OT 4340,Planos motor proveedor OT 4340</t>
+  </si>
+  <si>
+    <t>1215166433395184</t>
+  </si>
+  <si>
+    <t>Generación OC motor OT 4340</t>
+  </si>
+  <si>
+    <t>Motor OT 4340,Fabricación motor OT 4340,Planos motor proveedor OT 4340</t>
+  </si>
+  <si>
+    <t>1215166329227522</t>
+  </si>
+  <si>
+    <t>Fabricación motor OT 4340</t>
+  </si>
+  <si>
+    <t>Motor OT 4340,Recepcion motor</t>
+  </si>
+  <si>
+    <t>1215166329227542</t>
+  </si>
+  <si>
+    <t>Planos motor proveedor OT 4340</t>
+  </si>
+  <si>
+    <t>OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR,Motor OT 4340</t>
+  </si>
+  <si>
+    <t>1215165982829078</t>
+  </si>
+  <si>
+    <t>Materiales corte Laser OT 4340</t>
+  </si>
+  <si>
+    <t>Yerlia Ayleen Castillo Diaz</t>
+  </si>
+  <si>
+    <t>yerlia.castillo@zitron.com</t>
+  </si>
+  <si>
+    <t>Fabricacion Corte Laser  OT 4340,Generación OC materiales corte Laser OT 4340</t>
+  </si>
+  <si>
+    <t>1215166433428453</t>
+  </si>
+  <si>
+    <t>Generación OC materiales corte Laser OT 4340</t>
+  </si>
+  <si>
+    <t>Fabricacion Corte Laser  OT 4340,Materiales corte Laser OT 4340</t>
+  </si>
+  <si>
+    <t>1215166041659706</t>
+  </si>
+  <si>
+    <t>Fabricacion Corte Laser  OT 4340</t>
+  </si>
+  <si>
+    <t>Recepcion materiales corte laser,Materiales corte Laser OT 4340</t>
+  </si>
+  <si>
+    <t>1215166041659726</t>
+  </si>
+  <si>
+    <t>Materiales Corte Plasma  OT 4340</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generación OC Corte Plasma  OT 4340,Fabricación Corte Plasma OT 4340 </t>
+  </si>
+  <si>
+    <t>1215166243334496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Materiales Corte Plasma  OT 4340,Fabricación Corte Plasma OT 4340 </t>
+  </si>
+  <si>
+    <t>1215166243334513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabricación Corte Plasma OT 4340 </t>
+  </si>
+  <si>
+    <t>Recepcion Materiales corte plasma,Materiales Corte Plasma  OT 4340</t>
+  </si>
+  <si>
+    <t>1215166243334594</t>
+  </si>
+  <si>
+    <t>Fabricación Externa  OT 4340</t>
+  </si>
+  <si>
+    <t>Rosemary Singh</t>
+  </si>
+  <si>
+    <t>rosemary.singh@zitron.com</t>
+  </si>
+  <si>
+    <t>Fabricación estructura proveedor externo OT 4340,Generacion OC Fabricación Externa OT 4340</t>
+  </si>
+  <si>
+    <t>1215166243334606</t>
+  </si>
+  <si>
+    <t>Fabricación estructura proveedor externo OT 4340,Fabricación Externa  OT 4340</t>
+  </si>
+  <si>
+    <t>1215165982859560</t>
+  </si>
+  <si>
+    <t>Fabricación estructura proveedor externo OT 4340</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabricación Externa  OT 4340,Control de calidad fabricación externa  OT 4340,Recepcion fabricación externa </t>
+  </si>
+  <si>
+    <t>1215165982859577</t>
+  </si>
+  <si>
+    <t>Control de calidad fabricación externa  OT 4340</t>
+  </si>
+  <si>
+    <t>Nicolás López</t>
+  </si>
+  <si>
+    <t>nicolas.lopez@zitron.com</t>
+  </si>
+  <si>
+    <t>1215165982859589</t>
+  </si>
+  <si>
+    <t>Mecanizado OT 4340</t>
+  </si>
+  <si>
+    <t>Fabricación Mecanizado OT 4340,Generación OC Mecanizado OT 4340</t>
+  </si>
+  <si>
+    <t>1215166433442059</t>
+  </si>
+  <si>
+    <t>Fabricación Mecanizado OT 4340,Mecanizado OT 4340</t>
+  </si>
+  <si>
+    <t>1215166243346004</t>
+  </si>
+  <si>
+    <t>Fabricación Mecanizado OT 4340</t>
+  </si>
+  <si>
+    <t>Recepcion mecanizado,Mecanizado OT 4340</t>
+  </si>
+  <si>
+    <t>1215166243396278</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseñoo:</t>
+  </si>
+  <si>
+    <t>Planos definitivos,Planos preliminar</t>
+  </si>
+  <si>
+    <t>Tarea en curso</t>
+  </si>
+  <si>
+    <t>1215166243396290</t>
+  </si>
+  <si>
+    <t>Planos preliminar</t>
+  </si>
+  <si>
+    <t>Gonzalo Javier Dávila Bade</t>
+  </si>
+  <si>
+    <t>gonzalo.davila@zitron.com</t>
+  </si>
+  <si>
+    <t>OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR</t>
+  </si>
+  <si>
+    <t>1215166433496869</t>
+  </si>
+  <si>
+    <t>Hernan Roberto Gutierrez Barrientos</t>
+  </si>
+  <si>
+    <t>hgutierrez@zitron.com</t>
+  </si>
+  <si>
+    <t>OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR,Planos preliminar</t>
+  </si>
+  <si>
+    <t>1215166041791429</t>
+  </si>
+  <si>
+    <t>Planos definitivos</t>
+  </si>
+  <si>
+    <t>1215166041791446</t>
+  </si>
+  <si>
+    <t>OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR,Planos motor proveedor OT 4340</t>
+  </si>
+  <si>
+    <t>Planos definitivos,OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR</t>
+  </si>
+  <si>
+    <t>1215165982964919</t>
+  </si>
+  <si>
+    <t>Propuesta Mecanizado OT 4340,Propuesta Fabricación externa  OT 4340,propuesta Corte Laser OT 4340,Propuesta Corte plasma  OT 4340,OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR,OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR,OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR</t>
+  </si>
+  <si>
+    <t>1215166243476961</t>
+  </si>
+  <si>
+    <t>1215165982983044</t>
+  </si>
+  <si>
+    <t>check pruebas FAT</t>
+  </si>
+  <si>
+    <t>Francisca González Cornejo</t>
+  </si>
+  <si>
+    <t>francisca.gonzalez@zitron.com</t>
+  </si>
+  <si>
+    <t>1215165982983056</t>
+  </si>
+  <si>
+    <t>check pruebas FAT,OT 4335 - ZVN 1-7-37/2 + TOB + REJ</t>
+  </si>
+  <si>
+    <t>1215165983005052</t>
+  </si>
+  <si>
+    <t>Bodega:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recepcion materiales corte laser,Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>1215165983005064</t>
+  </si>
+  <si>
+    <t>Recepcion materiales corte laser</t>
+  </si>
+  <si>
+    <t>Victor Muñoz</t>
+  </si>
+  <si>
+    <t>victor.munoz@zitron.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bodega:,Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>1215166329404944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>Bodega:,OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR</t>
+  </si>
+  <si>
+    <t>1215166041891869</t>
+  </si>
+  <si>
+    <t>Recepcion Materiales corte plasma</t>
+  </si>
+  <si>
+    <t>Control de calidad Corte plasma</t>
+  </si>
+  <si>
+    <t>1215166041891891</t>
+  </si>
+  <si>
+    <t>1215165982799201</t>
+  </si>
+  <si>
+    <t>Recepcion mecanizado</t>
+  </si>
+  <si>
+    <t>Control de calidad Mecanizado</t>
+  </si>
+  <si>
+    <t>1215166243533900</t>
+  </si>
+  <si>
+    <t>1215166243533917</t>
+  </si>
+  <si>
+    <t>Caldereria:</t>
+  </si>
+  <si>
+    <t>Control de calidad Armado,Armado,Preparación Materiales</t>
+  </si>
+  <si>
+    <t>1215166433625222</t>
+  </si>
+  <si>
+    <t>Preparación Materiales</t>
+  </si>
+  <si>
+    <t>Nicolás Mol</t>
+  </si>
+  <si>
+    <t>nicolas.mol@zitron.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR,OT2 4307 ZVN 1-9-86/2 </t>
+  </si>
+  <si>
+    <t>1215166433625244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad Mecanizado,Control de calidad Corte plasma,Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>Preparación Materiales,OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR</t>
+  </si>
+  <si>
+    <t>1215166243563189</t>
+  </si>
+  <si>
+    <t>Armado</t>
+  </si>
+  <si>
+    <t>1215166329517772</t>
+  </si>
+  <si>
+    <t>OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR,check planos</t>
+  </si>
+  <si>
+    <t>OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR,Armado</t>
+  </si>
+  <si>
+    <t>1215166041950163</t>
+  </si>
+  <si>
+    <t>Control de calidad Armado</t>
+  </si>
+  <si>
+    <t>1215166041950180</t>
+  </si>
+  <si>
+    <t>Control de calidad Armado,OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR</t>
+  </si>
+  <si>
+    <t>1215165983080450</t>
+  </si>
+  <si>
+    <t>Recepcion Rodete,Recepcion Alabe,Recepcion motor</t>
+  </si>
+  <si>
+    <t>1215166329573409</t>
+  </si>
+  <si>
+    <t>Recepcion Rodete</t>
+  </si>
+  <si>
+    <t>OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR,Bodega:</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1215166329218738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generación OC Rodete OT 4340 </t>
-  </si>
-  <si>
-    <t>rodete OT 4340,Fabricación Rodete OT 4340</t>
-  </si>
-  <si>
-    <t>1215166243290478</t>
-  </si>
-  <si>
-    <t>Fabricación Rodete OT 4340</t>
-  </si>
-  <si>
-    <t>rodete OT 4340,Recepcion Rodete</t>
-  </si>
-  <si>
-    <t>1215166433395167</t>
-  </si>
-  <si>
-    <t>Motor OT 4340</t>
-  </si>
-  <si>
-    <t>Generación OC motor OT 4340,Fabricación motor OT 4340,Planos motor proveedor OT 4340</t>
-  </si>
-  <si>
-    <t>1215166433395184</t>
-  </si>
-  <si>
-    <t>Generación OC motor OT 4340</t>
-  </si>
-  <si>
-    <t>Motor OT 4340,Fabricación motor OT 4340,Planos motor proveedor OT 4340</t>
-  </si>
-  <si>
-    <t>1215166329227522</t>
-  </si>
-  <si>
-    <t>Fabricación motor OT 4340</t>
-  </si>
-  <si>
-    <t>Motor OT 4340,Recepcion motor</t>
-  </si>
-  <si>
-    <t>1215166329227542</t>
-  </si>
-  <si>
-    <t>Planos motor proveedor OT 4340</t>
-  </si>
-  <si>
-    <t>OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR,Motor OT 4340</t>
-  </si>
-  <si>
-    <t>1215165982829078</t>
-  </si>
-  <si>
-    <t>Materiales corte Laser OT 4340</t>
-  </si>
-  <si>
-    <t>Yerlia Ayleen Castillo Diaz</t>
-  </si>
-  <si>
-    <t>yerlia.castillo@zitron.com</t>
-  </si>
-  <si>
-    <t>Fabricacion Corte Laser  OT 4340,Generación OC materiales corte Laser OT 4340</t>
-  </si>
-  <si>
-    <t>1215166433428453</t>
-  </si>
-  <si>
-    <t>Generación OC materiales corte Laser OT 4340</t>
-  </si>
-  <si>
-    <t>Fabricacion Corte Laser  OT 4340,Materiales corte Laser OT 4340</t>
-  </si>
-  <si>
-    <t>1215166041659706</t>
-  </si>
-  <si>
-    <t>Fabricacion Corte Laser  OT 4340</t>
-  </si>
-  <si>
-    <t>Recepcion materiales corte laser,Materiales corte Laser OT 4340</t>
-  </si>
-  <si>
-    <t>1215166041659726</t>
-  </si>
-  <si>
-    <t>Materiales Corte Plasma  OT 4340</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generación OC Corte Plasma  OT 4340,Fabricación Corte Plasma OT 4340 </t>
-  </si>
-  <si>
-    <t>1215166243334496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Materiales Corte Plasma  OT 4340,Fabricación Corte Plasma OT 4340 </t>
-  </si>
-  <si>
-    <t>1215166243334513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabricación Corte Plasma OT 4340 </t>
-  </si>
-  <si>
-    <t>Recepcion Materiales corte plasma,Materiales Corte Plasma  OT 4340</t>
-  </si>
-  <si>
-    <t>1215166243334594</t>
-  </si>
-  <si>
-    <t>Fabricación Externa  OT 4340</t>
-  </si>
-  <si>
-    <t>Rosemary Singh</t>
-  </si>
-  <si>
-    <t>rosemary.singh@zitron.com</t>
-  </si>
-  <si>
-    <t>Fabricación estructura proveedor externo OT 4340,Generacion OC Fabricación Externa OT 4340</t>
-  </si>
-  <si>
-    <t>1215166243334606</t>
-  </si>
-  <si>
-    <t>Fabricación estructura proveedor externo OT 4340,Fabricación Externa  OT 4340</t>
-  </si>
-  <si>
-    <t>1215165982859560</t>
-  </si>
-  <si>
-    <t>Fabricación estructura proveedor externo OT 4340</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabricación Externa  OT 4340,Control de calidad fabricación externa  OT 4340,Recepcion fabricación externa </t>
-  </si>
-  <si>
-    <t>1215165982859577</t>
-  </si>
-  <si>
-    <t>Control de calidad fabricación externa  OT 4340</t>
-  </si>
-  <si>
-    <t>Nicolás López</t>
-  </si>
-  <si>
-    <t>nicolas.lopez@zitron.com</t>
-  </si>
-  <si>
-    <t>1215165982859589</t>
-  </si>
-  <si>
-    <t>Mecanizado OT 4340</t>
-  </si>
-  <si>
-    <t>Fabricación Mecanizado OT 4340,Generación OC Mecanizado OT 4340</t>
-  </si>
-  <si>
-    <t>1215166433442059</t>
-  </si>
-  <si>
-    <t>Fabricación Mecanizado OT 4340,Mecanizado OT 4340</t>
-  </si>
-  <si>
-    <t>1215166243346004</t>
-  </si>
-  <si>
-    <t>Fabricación Mecanizado OT 4340</t>
-  </si>
-  <si>
-    <t>Recepcion mecanizado,Mecanizado OT 4340</t>
-  </si>
-  <si>
-    <t>1215166243396278</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseñoo:</t>
-  </si>
-  <si>
-    <t>Planos definitivos,Planos preliminar</t>
-  </si>
-  <si>
-    <t>Tarea en curso</t>
-  </si>
-  <si>
-    <t>1215166243396290</t>
-  </si>
-  <si>
-    <t>Planos preliminar</t>
-  </si>
-  <si>
-    <t>Gonzalo Javier Dávila Bade</t>
-  </si>
-  <si>
-    <t>gonzalo.davila@zitron.com</t>
-  </si>
-  <si>
-    <t>OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR</t>
-  </si>
-  <si>
-    <t>Alta</t>
-  </si>
-  <si>
-    <t>1215166433496869</t>
-  </si>
-  <si>
-    <t>Hernan Roberto Gutierrez Barrientos</t>
-  </si>
-  <si>
-    <t>hgutierrez@zitron.com</t>
-  </si>
-  <si>
-    <t>OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR,Planos preliminar</t>
-  </si>
-  <si>
-    <t>1215166041791429</t>
-  </si>
-  <si>
-    <t>Planos definitivos</t>
-  </si>
-  <si>
-    <t>1215166041791446</t>
-  </si>
-  <si>
-    <t>OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR,Planos motor proveedor OT 4340</t>
-  </si>
-  <si>
-    <t>Planos definitivos,OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR</t>
-  </si>
-  <si>
-    <t>1215165982964919</t>
-  </si>
-  <si>
-    <t>Propuesta Mecanizado OT 4340,Propuesta Fabricación externa  OT 4340,propuesta Corte Laser OT 4340,Propuesta Corte plasma  OT 4340,OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR,OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR,OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR</t>
-  </si>
-  <si>
-    <t>1215166243476961</t>
-  </si>
-  <si>
-    <t>1215165982983044</t>
-  </si>
-  <si>
-    <t>check pruebas FAT</t>
-  </si>
-  <si>
-    <t>Francisca González Cornejo</t>
-  </si>
-  <si>
-    <t>francisca.gonzalez@zitron.com</t>
-  </si>
-  <si>
-    <t>1215165982983056</t>
-  </si>
-  <si>
-    <t>check pruebas FAT,OT 4335 - ZVN 1-7-37/2 + TOB + REJ</t>
-  </si>
-  <si>
-    <t>1215165983005052</t>
-  </si>
-  <si>
-    <t>Bodega:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recepcion materiales corte laser,Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>1215165983005064</t>
-  </si>
-  <si>
-    <t>Recepcion materiales corte laser</t>
-  </si>
-  <si>
-    <t>Victor Muñoz</t>
-  </si>
-  <si>
-    <t>victor.munoz@zitron.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bodega:,Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>1215166329404944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>Bodega:,OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR</t>
-  </si>
-  <si>
-    <t>1215166041891869</t>
-  </si>
-  <si>
-    <t>Recepcion Materiales corte plasma</t>
-  </si>
-  <si>
-    <t>Control de calidad Corte plasma</t>
-  </si>
-  <si>
-    <t>1215166041891891</t>
-  </si>
-  <si>
-    <t>1215165982799201</t>
-  </si>
-  <si>
-    <t>Recepcion mecanizado</t>
-  </si>
-  <si>
-    <t>Control de calidad Mecanizado</t>
-  </si>
-  <si>
-    <t>1215166243533900</t>
-  </si>
-  <si>
-    <t>1215166243533917</t>
-  </si>
-  <si>
-    <t>Caldereria:</t>
-  </si>
-  <si>
-    <t>Control de calidad Armado,Armado,Preparación Materiales</t>
-  </si>
-  <si>
-    <t>1215166433625222</t>
-  </si>
-  <si>
-    <t>Preparación Materiales</t>
-  </si>
-  <si>
-    <t>Nicolás Mol</t>
-  </si>
-  <si>
-    <t>nicolas.mol@zitron.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR,OT2 4307 ZVN 1-9-86/2 </t>
-  </si>
-  <si>
-    <t>1215166433625244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad Mecanizado,Control de calidad Corte plasma,Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>Preparación Materiales,OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR</t>
-  </si>
-  <si>
-    <t>1215166243563189</t>
-  </si>
-  <si>
-    <t>Armado</t>
-  </si>
-  <si>
-    <t>1215166329517772</t>
-  </si>
-  <si>
-    <t>OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR,check planos</t>
-  </si>
-  <si>
-    <t>OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR,Armado</t>
-  </si>
-  <si>
-    <t>1215166041950163</t>
-  </si>
-  <si>
-    <t>Control de calidad Armado</t>
-  </si>
-  <si>
-    <t>1215166041950180</t>
-  </si>
-  <si>
-    <t>Control de calidad Armado,OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR</t>
-  </si>
-  <si>
-    <t>1215165983080450</t>
-  </si>
-  <si>
-    <t>Recepcion Rodete,Recepcion Alabe,Recepcion motor</t>
-  </si>
-  <si>
-    <t>1215166329573409</t>
-  </si>
-  <si>
-    <t>Recepcion Rodete</t>
-  </si>
-  <si>
-    <t>OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR,Bodega:</t>
   </si>
   <si>
     <t>1215166329573431</t>
@@ -3014,7 +3014,7 @@
         <v>46184.73646410879</v>
       </c>
       <c r="D26" s="5">
-        <v>46212.20714363426</v>
+        <v>46220.171629351855</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>103</v>
@@ -3058,7 +3058,7 @@
       <c r="R26" s="5">
         <v>46219</v>
       </c>
-      <c r="S26" s="12" t="s">
+      <c r="S26" s="11" t="s">
         <v>105</v>
       </c>
       <c r="T26" s="6">
@@ -4310,7 +4310,7 @@
         <v>46184</v>
       </c>
       <c r="S47" s="11" t="s">
-        <v>174</v>
+        <v>105</v>
       </c>
       <c r="T47" s="9">
         <v>1</v>
@@ -4321,7 +4321,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B48" s="5">
         <v>46169.558472766206</v>
@@ -4339,10 +4339,10 @@
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="H48" s="6" t="s">
         <v>176</v>
-      </c>
-      <c r="H48" s="6" t="s">
-        <v>177</v>
       </c>
       <c r="I48" s="5">
         <v>46167</v>
@@ -4366,7 +4366,7 @@
         <v>60</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q48" s="6"/>
       <c r="R48" s="6"/>
@@ -4376,7 +4376,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B49" s="8">
         <v>46169.55849938658</v>
@@ -4388,7 +4388,7 @@
         <v>46197.71545016204</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
@@ -4441,7 +4441,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B50" s="5">
         <v>46169.55850371528</v>
@@ -4459,10 +4459,10 @@
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="H50" s="6" t="s">
         <v>176</v>
-      </c>
-      <c r="H50" s="6" t="s">
-        <v>177</v>
       </c>
       <c r="I50" s="5">
         <v>46218</v>
@@ -4480,13 +4480,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="O50" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="P50" s="6" t="s">
         <v>182</v>
-      </c>
-      <c r="P50" s="6" t="s">
-        <v>183</v>
       </c>
       <c r="Q50" s="6"/>
       <c r="R50" s="6"/>
@@ -4496,7 +4496,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B51" s="8">
         <v>46169.55853228009</v>
@@ -4514,10 +4514,10 @@
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="H51" s="9" t="s">
         <v>176</v>
-      </c>
-      <c r="H51" s="9" t="s">
-        <v>177</v>
       </c>
       <c r="I51" s="8">
         <v>46238</v>
@@ -4541,7 +4541,7 @@
         <v>173</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q51" s="8">
         <v>46238</v>
@@ -4561,7 +4561,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B52" s="5">
         <v>46169.55854641204</v>
@@ -4579,10 +4579,10 @@
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="H52" s="6" t="s">
         <v>176</v>
-      </c>
-      <c r="H52" s="6" t="s">
-        <v>177</v>
       </c>
       <c r="I52" s="5">
         <v>46238</v>
@@ -4616,7 +4616,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B53" s="8">
         <v>46169.558565775464</v>
@@ -4628,16 +4628,16 @@
         <v>46211.86422231482</v>
       </c>
       <c r="E53" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="F53" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G53" s="9" t="s">
         <v>188</v>
       </c>
-      <c r="F53" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G53" s="9" t="s">
+      <c r="H53" s="9" t="s">
         <v>189</v>
-      </c>
-      <c r="H53" s="9" t="s">
-        <v>190</v>
       </c>
       <c r="I53" s="8">
         <v>46331</v>
@@ -4681,7 +4681,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B54" s="5">
         <v>46169.55856972223</v>
@@ -4699,10 +4699,10 @@
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="H54" s="6" t="s">
         <v>189</v>
-      </c>
-      <c r="H54" s="6" t="s">
-        <v>190</v>
       </c>
       <c r="I54" s="5">
         <v>46331</v>
@@ -4720,13 +4720,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="O54" s="6" t="s">
         <v>173</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="Q54" s="6"/>
       <c r="R54" s="6"/>
@@ -4736,7 +4736,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B55" s="8">
         <v>46169.558586307874</v>
@@ -4748,7 +4748,7 @@
         <v>46198.597746307874</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>25</v>
@@ -4772,7 +4772,7 @@
         <v>26</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="P55" s="9" t="s">
         <v>26</v>
@@ -4789,7 +4789,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B56" s="5">
         <v>46169.55858945602</v>
@@ -4801,16 +4801,16 @@
         <v>46197.83559606482</v>
       </c>
       <c r="E56" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="F56" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G56" s="6" t="s">
         <v>197</v>
       </c>
-      <c r="F56" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G56" s="6" t="s">
+      <c r="H56" s="6" t="s">
         <v>198</v>
-      </c>
-      <c r="H56" s="6" t="s">
-        <v>199</v>
       </c>
       <c r="I56" s="5">
         <v>46254</v>
@@ -4828,13 +4828,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="O56" s="6" t="s">
         <v>133</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="Q56" s="5">
         <v>46254</v>
@@ -4854,7 +4854,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B57" s="8">
         <v>46169.55859488426</v>
@@ -4866,7 +4866,7 @@
         <v>46197.85937331019</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
@@ -4893,13 +4893,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="Q57" s="8">
         <v>46258</v>
@@ -4919,7 +4919,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B58" s="5">
         <v>46169.55860118056</v>
@@ -4931,16 +4931,16 @@
         <v>46198.59771457176</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="H58" s="6" t="s">
         <v>198</v>
-      </c>
-      <c r="H58" s="6" t="s">
-        <v>199</v>
       </c>
       <c r="I58" s="5">
         <v>46254</v>
@@ -4958,13 +4958,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="O58" s="6" t="s">
         <v>141</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="Q58" s="5">
         <v>46254</v>
@@ -4984,7 +4984,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B59" s="8">
         <v>46169.55860636574</v>
@@ -4996,7 +4996,7 @@
         <v>46198.597709444446</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
@@ -5023,10 +5023,10 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="P59" s="9" t="s">
         <v>173</v>
@@ -5049,7 +5049,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B60" s="5">
         <v>46169.558650127314</v>
@@ -5061,16 +5061,16 @@
         <v>46198.59773310185</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="H60" s="6" t="s">
         <v>198</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>199</v>
       </c>
       <c r="I60" s="5">
         <v>46254</v>
@@ -5088,13 +5088,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="O60" s="6" t="s">
         <v>163</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="Q60" s="5">
         <v>46254</v>
@@ -5114,7 +5114,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B61" s="8">
         <v>46169.55865608796</v>
@@ -5126,7 +5126,7 @@
         <v>46198.59773317129</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
@@ -5153,10 +5153,10 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="P61" s="9" t="s">
         <v>173</v>
@@ -5179,7 +5179,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B62" s="5">
         <v>46169.55866105324</v>
@@ -5191,7 +5191,7 @@
         <v>46198.68229049769</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>25</v>
@@ -5215,7 +5215,7 @@
         <v>26</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="P62" s="6" t="s">
         <v>26</v>
@@ -5232,7 +5232,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B63" s="8">
         <v>46169.55866469907</v>
@@ -5244,16 +5244,16 @@
         <v>46197.85915361111</v>
       </c>
       <c r="E63" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="F63" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G63" s="9" t="s">
         <v>216</v>
       </c>
-      <c r="F63" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G63" s="9" t="s">
+      <c r="H63" s="9" t="s">
         <v>217</v>
-      </c>
-      <c r="H63" s="9" t="s">
-        <v>218</v>
       </c>
       <c r="I63" s="8">
         <v>46260</v>
@@ -5271,13 +5271,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="P63" s="9" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Q63" s="8">
         <v>46260</v>
@@ -5297,7 +5297,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B64" s="5">
         <v>46169.55867099537</v>
@@ -5315,10 +5315,10 @@
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="H64" s="6" t="s">
         <v>217</v>
-      </c>
-      <c r="H64" s="6" t="s">
-        <v>218</v>
       </c>
       <c r="I64" s="5">
         <v>46260</v>
@@ -5336,13 +5336,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="O64" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="P64" s="6" t="s">
         <v>221</v>
-      </c>
-      <c r="P64" s="6" t="s">
-        <v>222</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5352,7 +5352,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B65" s="8">
         <v>46169.558703518516</v>
@@ -5364,16 +5364,16 @@
         <v>46197.85387390046</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="H65" s="9" t="s">
         <v>217</v>
-      </c>
-      <c r="H65" s="9" t="s">
-        <v>218</v>
       </c>
       <c r="I65" s="8">
         <v>46269</v>
@@ -5391,13 +5391,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="O65" s="9" t="s">
         <v>173</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Q65" s="8">
         <v>46269</v>
@@ -5417,7 +5417,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B66" s="5">
         <v>46169.55870879629</v>
@@ -5435,10 +5435,10 @@
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="H66" s="6" t="s">
         <v>217</v>
-      </c>
-      <c r="H66" s="6" t="s">
-        <v>218</v>
       </c>
       <c r="I66" s="5">
         <v>46269</v>
@@ -5456,13 +5456,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="O66" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="P66" s="6" t="s">
         <v>226</v>
-      </c>
-      <c r="P66" s="6" t="s">
-        <v>227</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5472,7 +5472,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B67" s="8">
         <v>46169.558740625</v>
@@ -5484,7 +5484,7 @@
         <v>46205.65959174768</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
@@ -5511,13 +5511,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="O67" s="9" t="s">
         <v>173</v>
       </c>
       <c r="P67" s="9" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Q67" s="8">
         <v>46274</v>
@@ -5537,7 +5537,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B68" s="5">
         <v>46169.558745243055</v>
@@ -5576,13 +5576,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="Q68" s="6"/>
       <c r="R68" s="6"/>
@@ -5592,7 +5592,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B69" s="8">
         <v>46169.55876947917</v>
@@ -5604,7 +5604,7 @@
         <v>46211.70953918982</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>25</v>
@@ -5628,7 +5628,7 @@
         <v>26</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="P69" s="9" t="s">
         <v>26</v>
@@ -5641,7 +5641,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B70" s="5">
         <v>46169.55880633101</v>
@@ -5653,16 +5653,16 @@
         <v>46216.206479560184</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="H70" s="6" t="s">
         <v>198</v>
-      </c>
-      <c r="H70" s="6" t="s">
-        <v>199</v>
       </c>
       <c r="I70" s="5">
         <v>46220</v>
@@ -5680,13 +5680,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="O70" s="6" t="s">
         <v>110</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="Q70" s="5">
         <v>46220</v>
@@ -5695,7 +5695,7 @@
         <v>46223</v>
       </c>
       <c r="S70" s="12" t="s">
-        <v>105</v>
+        <v>236</v>
       </c>
       <c r="T70" s="6">
         <v>1</v>
@@ -5724,10 +5724,10 @@
         <v>26</v>
       </c>
       <c r="G71" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="H71" s="9" t="s">
         <v>198</v>
-      </c>
-      <c r="H71" s="9" t="s">
-        <v>199</v>
       </c>
       <c r="I71" s="8">
         <v>46325</v>
@@ -5745,7 +5745,7 @@
         <v>26</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="O71" s="9" t="s">
         <v>100</v>
@@ -5760,7 +5760,7 @@
         <v>46325</v>
       </c>
       <c r="S71" s="11" t="s">
-        <v>174</v>
+        <v>105</v>
       </c>
       <c r="T71" s="9">
         <v>1</v>
@@ -5789,10 +5789,10 @@
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="H72" s="6" t="s">
         <v>198</v>
-      </c>
-      <c r="H72" s="6" t="s">
-        <v>199</v>
       </c>
       <c r="I72" s="5">
         <v>46293</v>
@@ -5810,13 +5810,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="O72" s="6" t="s">
         <v>119</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="Q72" s="5">
         <v>46293</v>
@@ -5854,10 +5854,10 @@
         <v>26</v>
       </c>
       <c r="G73" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="H73" s="9" t="s">
         <v>198</v>
-      </c>
-      <c r="H73" s="9" t="s">
-        <v>199</v>
       </c>
       <c r="I73" s="8">
         <v>46282</v>
@@ -5875,7 +5875,7 @@
         <v>26</v>
       </c>
       <c r="N73" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="O73" s="9" t="s">
         <v>151</v>
@@ -6953,10 +6953,10 @@
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="H92" s="6" t="s">
         <v>217</v>
-      </c>
-      <c r="H92" s="6" t="s">
-        <v>218</v>
       </c>
       <c r="I92" s="5">
         <v>46337</v>
@@ -7018,10 +7018,10 @@
         <v>26</v>
       </c>
       <c r="G93" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="H93" s="9" t="s">
         <v>217</v>
-      </c>
-      <c r="H93" s="9" t="s">
-        <v>218</v>
       </c>
       <c r="I93" s="8">
         <v>46337</v>
@@ -7073,10 +7073,10 @@
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="H94" s="6" t="s">
         <v>217</v>
-      </c>
-      <c r="H94" s="6" t="s">
-        <v>218</v>
       </c>
       <c r="I94" s="5">
         <v>46338</v>
@@ -7138,10 +7138,10 @@
         <v>26</v>
       </c>
       <c r="G95" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="H95" s="9" t="s">
         <v>217</v>
-      </c>
-      <c r="H95" s="9" t="s">
-        <v>218</v>
       </c>
       <c r="I95" s="8">
         <v>46338</v>

--- a/data/50001557 - ATACAMA KOZAN OT4340.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4340.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1165" uniqueCount="308">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1183" uniqueCount="309">
   <si>
     <t xml:space="preserve"> 50001557 - ATACAMA KOZAN</t>
   </si>
@@ -331,6 +331,9 @@
   </si>
   <si>
     <t>propuesta nucleo rodete OT 4340</t>
+  </si>
+  <si>
+    <t>nespinoza@zitron.com</t>
   </si>
   <si>
     <t>Generación OC Rodete OT 4340 ,Propuesta compras:</t>
@@ -2463,7 +2466,7 @@
         <v>46183.906516585645</v>
       </c>
       <c r="D17" s="8">
-        <v>46183.90651931713</v>
+        <v>46223.570564340276</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>72</v>
@@ -2472,9 +2475,11 @@
         <v>26</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H17" s="9"/>
+        <v>73</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>73</v>
+      </c>
       <c r="I17" s="8">
         <v>46167</v>
       </c>
@@ -2497,7 +2502,7 @@
         <v>56</v>
       </c>
       <c r="P17" s="9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Q17" s="8">
         <v>46167</v>
@@ -2517,7 +2522,7 @@
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B18" s="5">
         <v>46169.55823646991</v>
@@ -2526,18 +2531,20 @@
         <v>46183.90663498842</v>
       </c>
       <c r="D18" s="5">
-        <v>46183.90665107639</v>
+        <v>46223.570560636574</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H18" s="6"/>
+        <v>73</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>73</v>
+      </c>
       <c r="I18" s="5">
         <v>46239</v>
       </c>
@@ -2557,10 +2564,10 @@
         <v>63</v>
       </c>
       <c r="O18" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Q18" s="5">
         <v>46239</v>
@@ -2580,7 +2587,7 @@
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B19" s="8">
         <v>46169.55824171296</v>
@@ -2589,18 +2596,20 @@
         <v>46183.906646539355</v>
       </c>
       <c r="D19" s="8">
-        <v>46183.90666170139</v>
+        <v>46223.57055704861</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F19" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G19" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H19" s="9"/>
+        <v>73</v>
+      </c>
+      <c r="H19" s="9" t="s">
+        <v>73</v>
+      </c>
       <c r="I19" s="8">
         <v>46239</v>
       </c>
@@ -2620,10 +2629,10 @@
         <v>63</v>
       </c>
       <c r="O19" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="P19" s="9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="Q19" s="8">
         <v>46239</v>
@@ -2643,7 +2652,7 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B20" s="5">
         <v>46169.55824574074</v>
@@ -2652,18 +2661,20 @@
         <v>46190.644140034725</v>
       </c>
       <c r="D20" s="5">
-        <v>46190.64415820602</v>
+        <v>46223.57055334491</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H20" s="6"/>
+        <v>73</v>
+      </c>
+      <c r="H20" s="6" t="s">
+        <v>73</v>
+      </c>
       <c r="I20" s="5">
         <v>46239</v>
       </c>
@@ -2683,10 +2694,10 @@
         <v>63</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Q20" s="5">
         <v>46239</v>
@@ -2706,7 +2717,7 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B21" s="8">
         <v>46169.55825006944</v>
@@ -2715,18 +2726,20 @@
         <v>46183.90733957176</v>
       </c>
       <c r="D21" s="8">
-        <v>46183.90735393518</v>
+        <v>46223.570547662035</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F21" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G21" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H21" s="9"/>
+        <v>73</v>
+      </c>
+      <c r="H21" s="9" t="s">
+        <v>73</v>
+      </c>
       <c r="I21" s="8">
         <v>46239</v>
       </c>
@@ -2746,10 +2759,10 @@
         <v>63</v>
       </c>
       <c r="O21" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="P21" s="9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="Q21" s="8">
         <v>46239</v>
@@ -2769,7 +2782,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B22" s="5">
         <v>46169.55801826389</v>
@@ -2781,7 +2794,7 @@
         <v>46200.818425798614</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>25</v>
@@ -2805,7 +2818,7 @@
         <v>26</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="P22" s="6" t="s">
         <v>26</v>
@@ -2818,7 +2831,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B23" s="8">
         <v>46169.558301956014</v>
@@ -2830,16 +2843,16 @@
         <v>46200.81833380787</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I23" s="8">
         <v>46169</v>
@@ -2857,13 +2870,13 @@
         <v>26</v>
       </c>
       <c r="N23" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="O23" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="P23" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="Q23" s="8">
         <v>46169</v>
@@ -2883,7 +2896,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B24" s="5">
         <v>46169.558306516206</v>
@@ -2895,16 +2908,16 @@
         <v>46195.69079224537</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I24" s="5">
         <v>46169</v>
@@ -2922,13 +2935,13 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="O24" s="6" t="s">
         <v>69</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="Q24" s="6"/>
       <c r="R24" s="6"/>
@@ -2939,12 +2952,12 @@
         <v>0</v>
       </c>
       <c r="U24" s="11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B25" s="8">
         <v>46169.55831137732</v>
@@ -2956,16 +2969,16 @@
         <v>46195.690800474535</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I25" s="8">
         <v>46171</v>
@@ -2983,13 +2996,13 @@
         <v>26</v>
       </c>
       <c r="N25" s="9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="O25" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="P25" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="Q25" s="9"/>
       <c r="R25" s="9"/>
@@ -3000,12 +3013,12 @@
         <v>0</v>
       </c>
       <c r="U25" s="11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B26" s="5">
         <v>46169.55831605324</v>
@@ -3017,16 +3030,16 @@
         <v>46220.171629351855</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I26" s="5">
         <v>46169</v>
@@ -3044,13 +3057,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="Q26" s="5">
         <v>46169</v>
@@ -3059,7 +3072,7 @@
         <v>46219</v>
       </c>
       <c r="S26" s="11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="T26" s="6">
         <v>1</v>
@@ -3070,7 +3083,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B27" s="8">
         <v>46169.55832063657</v>
@@ -3082,16 +3095,16 @@
         <v>46184.7364097338</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I27" s="8">
         <v>46169</v>
@@ -3109,13 +3122,13 @@
         <v>26</v>
       </c>
       <c r="N27" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O27" s="9" t="s">
         <v>72</v>
       </c>
       <c r="P27" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Q27" s="9"/>
       <c r="R27" s="9"/>
@@ -3126,12 +3139,12 @@
         <v>0</v>
       </c>
       <c r="U27" s="11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B28" s="5">
         <v>46169.55832539352</v>
@@ -3143,16 +3156,16 @@
         <v>46184.736449375</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I28" s="5">
         <v>46171</v>
@@ -3170,13 +3183,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
@@ -3187,12 +3200,12 @@
         <v>0</v>
       </c>
       <c r="U28" s="11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B29" s="8">
         <v>46169.55833006944</v>
@@ -3204,16 +3217,16 @@
         <v>46200.81836952546</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I29" s="8">
         <v>46161</v>
@@ -3231,13 +3244,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="O29" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="P29" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="Q29" s="8">
         <v>46161</v>
@@ -3257,7 +3270,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B30" s="5">
         <v>46169.55833486111</v>
@@ -3269,16 +3282,16 @@
         <v>46195.69066259259</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I30" s="5">
         <v>46161</v>
@@ -3296,13 +3309,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O30" s="6" t="s">
         <v>66</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -3313,12 +3326,12 @@
         <v>0</v>
       </c>
       <c r="U30" s="11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B31" s="8">
         <v>46169.5583402662</v>
@@ -3330,16 +3343,16 @@
         <v>46195.69066760417</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I31" s="8">
         <v>46178</v>
@@ -3357,13 +3370,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O31" s="9" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="P31" s="9" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="Q31" s="9"/>
       <c r="R31" s="9"/>
@@ -3374,12 +3387,12 @@
         <v>0</v>
       </c>
       <c r="U31" s="11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B32" s="5">
         <v>46169.55834503472</v>
@@ -3391,16 +3404,16 @@
         <v>46195.6906680324</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I32" s="5">
         <v>46178</v>
@@ -3418,13 +3431,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
@@ -3435,12 +3448,12 @@
         <v>0</v>
       </c>
       <c r="U32" s="11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B33" s="8">
         <v>46169.55836335648</v>
@@ -3452,16 +3465,16 @@
         <v>46184.532641875005</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I33" s="8">
         <v>46241</v>
@@ -3479,13 +3492,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="Q33" s="8">
         <v>46241</v>
@@ -3505,7 +3518,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B34" s="5">
         <v>46169.558367986116</v>
@@ -3517,16 +3530,16 @@
         <v>46184.53245875</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I34" s="5">
         <v>46241</v>
@@ -3544,13 +3557,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3561,12 +3574,12 @@
         <v>0</v>
       </c>
       <c r="U34" s="11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B35" s="8">
         <v>46169.55837292824</v>
@@ -3578,16 +3591,16 @@
         <v>46184.532615856486</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I35" s="8">
         <v>46245</v>
@@ -3605,13 +3618,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="P35" s="9" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Q35" s="9"/>
       <c r="R35" s="9"/>
@@ -3622,12 +3635,12 @@
         <v>0</v>
       </c>
       <c r="U35" s="11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B36" s="5">
         <v>46169.55837825232</v>
@@ -3639,16 +3652,16 @@
         <v>46184.53258194444</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I36" s="5">
         <v>46241</v>
@@ -3666,10 +3679,10 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="P36" s="6" t="s">
         <v>26</v>
@@ -3692,7 +3705,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B37" s="8">
         <v>46169.558381979165</v>
@@ -3704,16 +3717,16 @@
         <v>46184.5322071875</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I37" s="8">
         <v>46241</v>
@@ -3731,13 +3744,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="Q37" s="9"/>
       <c r="R37" s="9"/>
@@ -3747,7 +3760,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B38" s="5">
         <v>46169.55838657408</v>
@@ -3759,16 +3772,16 @@
         <v>46184.53255631945</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I38" s="5">
         <v>46245</v>
@@ -3786,13 +3799,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -3802,7 +3815,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B39" s="8">
         <v>46169.55839107639</v>
@@ -3814,16 +3827,16 @@
         <v>46205.600326053245</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I39" s="8">
         <v>46241</v>
@@ -3841,10 +3854,10 @@
         <v>26</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="P39" s="9" t="s">
         <v>26</v>
@@ -3867,7 +3880,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B40" s="5">
         <v>46169.55839478009</v>
@@ -3879,16 +3892,16 @@
         <v>46195.70360162037</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I40" s="5">
         <v>46241</v>
@@ -3906,13 +3919,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -3922,7 +3935,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B41" s="8">
         <v>46169.55839910879</v>
@@ -3934,16 +3947,16 @@
         <v>46195.70375376157</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I41" s="8">
         <v>46252</v>
@@ -3961,13 +3974,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q41" s="9"/>
       <c r="R41" s="9"/>
@@ -3977,7 +3990,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B42" s="5">
         <v>46169.55840355324</v>
@@ -3989,16 +4002,16 @@
         <v>46205.59994755787</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I42" s="5">
         <v>46281</v>
@@ -4016,10 +4029,10 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>26</v>
@@ -4032,7 +4045,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B43" s="8">
         <v>46169.55840677083</v>
@@ -4044,16 +4057,16 @@
         <v>46191.53701371528</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I43" s="8">
         <v>46241</v>
@@ -4071,10 +4084,10 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="P43" s="9" t="s">
         <v>26</v>
@@ -4097,7 +4110,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B44" s="5">
         <v>46169.55841037037</v>
@@ -4109,16 +4122,16 @@
         <v>46191.53679194444</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I44" s="5">
         <v>46241</v>
@@ -4136,13 +4149,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4152,7 +4165,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B45" s="8">
         <v>46169.558458217594</v>
@@ -4164,16 +4177,16 @@
         <v>46191.53698841435</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I45" s="8">
         <v>46245</v>
@@ -4191,13 +4204,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P45" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q45" s="9"/>
       <c r="R45" s="9"/>
@@ -4207,7 +4220,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B46" s="5">
         <v>46169.5584643287</v>
@@ -4217,7 +4230,7 @@
         <v>46182.75962331019</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>25</v>
@@ -4241,7 +4254,7 @@
         <v>26</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4251,12 +4264,12 @@
       <c r="S46" s="6"/>
       <c r="T46" s="6"/>
       <c r="U46" s="12" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B47" s="8">
         <v>46169.55846813657</v>
@@ -4268,16 +4281,16 @@
         <v>46197.715420312496</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I47" s="8">
         <v>46167</v>
@@ -4295,13 +4308,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q47" s="8">
         <v>46167</v>
@@ -4310,7 +4323,7 @@
         <v>46184</v>
       </c>
       <c r="S47" s="11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="T47" s="9">
         <v>1</v>
@@ -4321,7 +4334,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B48" s="5">
         <v>46169.558472766206</v>
@@ -4333,16 +4346,16 @@
         <v>46181.72663056713</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I48" s="5">
         <v>46167</v>
@@ -4360,13 +4373,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O48" s="6" t="s">
         <v>60</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q48" s="6"/>
       <c r="R48" s="6"/>
@@ -4376,7 +4389,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B49" s="8">
         <v>46169.55849938658</v>
@@ -4388,16 +4401,16 @@
         <v>46197.71545016204</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I49" s="8">
         <v>46218</v>
@@ -4415,13 +4428,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q49" s="8">
         <v>46218</v>
@@ -4441,7 +4454,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B50" s="5">
         <v>46169.55850371528</v>
@@ -4453,16 +4466,16 @@
         <v>46195.690583055555</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I50" s="5">
         <v>46218</v>
@@ -4480,13 +4493,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q50" s="6"/>
       <c r="R50" s="6"/>
@@ -4496,7 +4509,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B51" s="8">
         <v>46169.55853228009</v>
@@ -4508,16 +4521,16 @@
         <v>46182.759871076385</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I51" s="8">
         <v>46238</v>
@@ -4535,13 +4548,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q51" s="8">
         <v>46238</v>
@@ -4561,7 +4574,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B52" s="5">
         <v>46169.55854641204</v>
@@ -4573,16 +4586,16 @@
         <v>46182.75984881945</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I52" s="5">
         <v>46238</v>
@@ -4600,13 +4613,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4616,7 +4629,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B53" s="8">
         <v>46169.558565775464</v>
@@ -4628,16 +4641,16 @@
         <v>46211.86422231482</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="I53" s="8">
         <v>46331</v>
@@ -4655,10 +4668,10 @@
         <v>26</v>
       </c>
       <c r="N53" s="9" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="P53" s="9" t="s">
         <v>26</v>
@@ -4681,7 +4694,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B54" s="5">
         <v>46169.55856972223</v>
@@ -4693,16 +4706,16 @@
         <v>46211.86419394676</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="I54" s="5">
         <v>46331</v>
@@ -4720,13 +4733,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q54" s="6"/>
       <c r="R54" s="6"/>
@@ -4736,7 +4749,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B55" s="8">
         <v>46169.558586307874</v>
@@ -4748,7 +4761,7 @@
         <v>46198.597746307874</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>25</v>
@@ -4772,7 +4785,7 @@
         <v>26</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P55" s="9" t="s">
         <v>26</v>
@@ -4789,7 +4802,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B56" s="5">
         <v>46169.55858945602</v>
@@ -4801,16 +4814,16 @@
         <v>46197.83559606482</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I56" s="5">
         <v>46254</v>
@@ -4828,13 +4841,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q56" s="5">
         <v>46254</v>
@@ -4854,7 +4867,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B57" s="8">
         <v>46169.55859488426</v>
@@ -4866,16 +4879,16 @@
         <v>46197.85937331019</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I57" s="8">
         <v>46258</v>
@@ -4893,13 +4906,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q57" s="8">
         <v>46258</v>
@@ -4919,7 +4932,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B58" s="5">
         <v>46169.55860118056</v>
@@ -4931,16 +4944,16 @@
         <v>46198.59771457176</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I58" s="5">
         <v>46254</v>
@@ -4958,13 +4971,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q58" s="5">
         <v>46254</v>
@@ -4984,7 +4997,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B59" s="8">
         <v>46169.55860636574</v>
@@ -4996,16 +5009,16 @@
         <v>46198.597709444446</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I59" s="8">
         <v>46258</v>
@@ -5023,13 +5036,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q59" s="8">
         <v>46258</v>
@@ -5044,12 +5057,12 @@
         <v>1</v>
       </c>
       <c r="U59" s="12" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B60" s="5">
         <v>46169.558650127314</v>
@@ -5061,16 +5074,16 @@
         <v>46198.59773310185</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I60" s="5">
         <v>46254</v>
@@ -5088,13 +5101,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q60" s="5">
         <v>46254</v>
@@ -5114,7 +5127,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B61" s="8">
         <v>46169.55865608796</v>
@@ -5126,16 +5139,16 @@
         <v>46198.59773317129</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I61" s="8">
         <v>46258</v>
@@ -5153,13 +5166,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q61" s="8">
         <v>46258</v>
@@ -5174,12 +5187,12 @@
         <v>1</v>
       </c>
       <c r="U61" s="12" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B62" s="5">
         <v>46169.55866105324</v>
@@ -5191,7 +5204,7 @@
         <v>46198.68229049769</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>25</v>
@@ -5215,7 +5228,7 @@
         <v>26</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="P62" s="6" t="s">
         <v>26</v>
@@ -5232,7 +5245,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B63" s="8">
         <v>46169.55866469907</v>
@@ -5244,16 +5257,16 @@
         <v>46197.85915361111</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H63" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I63" s="8">
         <v>46260</v>
@@ -5271,13 +5284,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="P63" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q63" s="8">
         <v>46260</v>
@@ -5297,7 +5310,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B64" s="5">
         <v>46169.55867099537</v>
@@ -5309,16 +5322,16 @@
         <v>46197.85936673611</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I64" s="5">
         <v>46260</v>
@@ -5336,13 +5349,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5352,7 +5365,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B65" s="8">
         <v>46169.558703518516</v>
@@ -5364,16 +5377,16 @@
         <v>46197.85387390046</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H65" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I65" s="8">
         <v>46269</v>
@@ -5391,13 +5404,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q65" s="8">
         <v>46269</v>
@@ -5412,12 +5425,12 @@
         <v>1</v>
       </c>
       <c r="U65" s="12" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B66" s="5">
         <v>46169.55870879629</v>
@@ -5429,16 +5442,16 @@
         <v>46197.85915420139</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I66" s="5">
         <v>46269</v>
@@ -5456,13 +5469,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5472,7 +5485,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B67" s="8">
         <v>46169.558740625</v>
@@ -5484,16 +5497,16 @@
         <v>46205.65959174768</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H67" s="9" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I67" s="8">
         <v>46274</v>
@@ -5511,13 +5524,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="P67" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q67" s="8">
         <v>46274</v>
@@ -5532,12 +5545,12 @@
         <v>1</v>
       </c>
       <c r="U67" s="12" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B68" s="5">
         <v>46169.558745243055</v>
@@ -5549,16 +5562,16 @@
         <v>46205.659588587965</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I68" s="5">
         <v>46274</v>
@@ -5576,13 +5589,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q68" s="6"/>
       <c r="R68" s="6"/>
@@ -5592,7 +5605,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B69" s="8">
         <v>46169.55876947917</v>
@@ -5604,7 +5617,7 @@
         <v>46211.70953918982</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>25</v>
@@ -5628,7 +5641,7 @@
         <v>26</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="P69" s="9" t="s">
         <v>26</v>
@@ -5641,7 +5654,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B70" s="5">
         <v>46169.55880633101</v>
@@ -5653,16 +5666,16 @@
         <v>46216.206479560184</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I70" s="5">
         <v>46220</v>
@@ -5680,13 +5693,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q70" s="5">
         <v>46220</v>
@@ -5695,7 +5708,7 @@
         <v>46223</v>
       </c>
       <c r="S70" s="12" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="T70" s="6">
         <v>1</v>
@@ -5706,7 +5719,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B71" s="8">
         <v>46169.5588177662</v>
@@ -5718,16 +5731,16 @@
         <v>46200.819831597226</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H71" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I71" s="8">
         <v>46325</v>
@@ -5745,13 +5758,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="P71" s="9" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q71" s="8">
         <v>46325</v>
@@ -5760,7 +5773,7 @@
         <v>46325</v>
       </c>
       <c r="S71" s="11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="T71" s="9">
         <v>1</v>
@@ -5771,7 +5784,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B72" s="5">
         <v>46169.55882295139</v>
@@ -5783,16 +5796,16 @@
         <v>46200.81928909722</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I72" s="5">
         <v>46293</v>
@@ -5810,13 +5823,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q72" s="5">
         <v>46293</v>
@@ -5836,7 +5849,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B73" s="8">
         <v>46169.55882788195</v>
@@ -5848,16 +5861,16 @@
         <v>46211.7093043287</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H73" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I73" s="8">
         <v>46282</v>
@@ -5875,13 +5888,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="P73" s="9" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q73" s="8">
         <v>46282</v>
@@ -5901,7 +5914,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B74" s="5">
         <v>46169.55884254629</v>
@@ -5913,7 +5926,7 @@
         <v>46211.86406403936</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>25</v>
@@ -5937,7 +5950,7 @@
         <v>26</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P74" s="6" t="s">
         <v>26</v>
@@ -5954,7 +5967,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B75" s="8">
         <v>46169.55884548611</v>
@@ -5963,18 +5976,20 @@
         <v>46197.49536869213</v>
       </c>
       <c r="D75" s="8">
-        <v>46211.70929236111</v>
+        <v>46223.571425636575</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H75" s="9"/>
+        <v>73</v>
+      </c>
+      <c r="H75" s="9" t="s">
+        <v>73</v>
+      </c>
       <c r="I75" s="8">
         <v>46276</v>
       </c>
@@ -5991,13 +6006,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q75" s="8">
         <v>46276</v>
@@ -6012,12 +6027,12 @@
         <v>1</v>
       </c>
       <c r="U75" s="12" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B76" s="5">
         <v>46169.55884993056</v>
@@ -6026,18 +6041,20 @@
         <v>46197.49535652778</v>
       </c>
       <c r="D76" s="5">
-        <v>46211.70929407407</v>
+        <v>46223.57064498843</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H76" s="6"/>
+        <v>73</v>
+      </c>
+      <c r="H76" s="6" t="s">
+        <v>73</v>
+      </c>
       <c r="I76" s="5">
         <v>46276</v>
       </c>
@@ -6054,13 +6071,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -6070,7 +6087,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B77" s="8">
         <v>46169.55893170139</v>
@@ -6079,18 +6096,20 @@
         <v>46197.49516923611</v>
       </c>
       <c r="D77" s="8">
-        <v>46197.495185555556</v>
+        <v>46223.57142202546</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H77" s="9"/>
+        <v>73</v>
+      </c>
+      <c r="H77" s="9" t="s">
+        <v>73</v>
+      </c>
       <c r="I77" s="8">
         <v>46296</v>
       </c>
@@ -6107,13 +6126,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="P77" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q77" s="8">
         <v>46296</v>
@@ -6133,7 +6152,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B78" s="5">
         <v>46169.55893543981</v>
@@ -6142,18 +6161,20 @@
         <v>46197.4951540162</v>
       </c>
       <c r="D78" s="5">
-        <v>46204.879924837966</v>
+        <v>46223.57074214121</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H78" s="6"/>
+        <v>73</v>
+      </c>
+      <c r="H78" s="6" t="s">
+        <v>73</v>
+      </c>
       <c r="I78" s="5">
         <v>46296</v>
       </c>
@@ -6170,13 +6191,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q78" s="6"/>
       <c r="R78" s="6"/>
@@ -6186,7 +6207,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B79" s="8">
         <v>46169.558869560184</v>
@@ -6195,18 +6216,20 @@
         <v>46204.87979715278</v>
       </c>
       <c r="D79" s="8">
-        <v>46204.87981377315</v>
+        <v>46223.57141798611</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H79" s="9"/>
+        <v>73</v>
+      </c>
+      <c r="H79" s="9" t="s">
+        <v>73</v>
+      </c>
       <c r="I79" s="8">
         <v>46328</v>
       </c>
@@ -6223,13 +6246,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="P79" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q79" s="8">
         <v>46328</v>
@@ -6249,7 +6272,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B80" s="5">
         <v>46169.55887296297</v>
@@ -6258,18 +6281,20 @@
         <v>46204.87978053241</v>
       </c>
       <c r="D80" s="5">
-        <v>46204.87978310185</v>
+        <v>46223.57080435185</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H80" s="6"/>
+        <v>73</v>
+      </c>
+      <c r="H80" s="6" t="s">
+        <v>73</v>
+      </c>
       <c r="I80" s="5">
         <v>46328</v>
       </c>
@@ -6286,13 +6311,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -6302,7 +6327,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B81" s="8">
         <v>46169.5589025463</v>
@@ -6311,18 +6336,20 @@
         <v>46204.87992821759</v>
       </c>
       <c r="D81" s="8">
-        <v>46204.880057013885</v>
+        <v>46223.57141431713</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H81" s="9"/>
+        <v>73</v>
+      </c>
+      <c r="H81" s="9" t="s">
+        <v>73</v>
+      </c>
       <c r="I81" s="8">
         <v>46329</v>
       </c>
@@ -6339,13 +6366,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q81" s="8">
         <v>46329</v>
@@ -6365,7 +6392,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B82" s="5">
         <v>46169.55890609954</v>
@@ -6377,7 +6404,7 @@
         <v>46204.87991711806</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
@@ -6402,13 +6429,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6418,7 +6445,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B83" s="8">
         <v>46169.55900443287</v>
@@ -6427,18 +6454,20 @@
         <v>46206.4867090162</v>
       </c>
       <c r="D83" s="8">
-        <v>46206.48671975694</v>
+        <v>46223.57141039352</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H83" s="9"/>
+        <v>73</v>
+      </c>
+      <c r="H83" s="9" t="s">
+        <v>73</v>
+      </c>
       <c r="I83" s="8">
         <v>46330</v>
       </c>
@@ -6455,13 +6484,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O83" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="P83" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q83" s="8">
         <v>46330</v>
@@ -6481,7 +6510,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B84" s="5">
         <v>46169.55901002315</v>
@@ -6490,18 +6519,20 @@
         <v>46206.48669384259</v>
       </c>
       <c r="D84" s="5">
-        <v>46206.48669563657</v>
+        <v>46223.57092783565</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H84" s="6"/>
+        <v>73</v>
+      </c>
+      <c r="H84" s="6" t="s">
+        <v>73</v>
+      </c>
       <c r="I84" s="5">
         <v>46330</v>
       </c>
@@ -6518,13 +6549,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q84" s="6"/>
       <c r="R84" s="6"/>
@@ -6534,7 +6565,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B85" s="8">
         <v>46169.55904462963</v>
@@ -6543,18 +6574,20 @@
         <v>46206.48680728009</v>
       </c>
       <c r="D85" s="8">
-        <v>46206.48682021991</v>
+        <v>46223.5714043287</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H85" s="9"/>
+        <v>73</v>
+      </c>
+      <c r="H85" s="9" t="s">
+        <v>73</v>
+      </c>
       <c r="I85" s="8">
         <v>46332</v>
       </c>
@@ -6571,13 +6604,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O85" s="9" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="P85" s="9" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q85" s="8">
         <v>46332</v>
@@ -6597,7 +6630,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B86" s="5">
         <v>46169.559050138894</v>
@@ -6606,18 +6639,20 @@
         <v>46206.486792916665</v>
       </c>
       <c r="D86" s="5">
-        <v>46211.86420142361</v>
+        <v>46223.57102379629</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H86" s="6"/>
+        <v>73</v>
+      </c>
+      <c r="H86" s="6" t="s">
+        <v>73</v>
+      </c>
       <c r="I86" s="5">
         <v>46332</v>
       </c>
@@ -6634,13 +6669,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6650,7 +6685,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B87" s="8">
         <v>46169.55907484954</v>
@@ -6660,7 +6695,7 @@
         <v>46211.8640300463</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>25</v>
@@ -6684,7 +6719,7 @@
         <v>26</v>
       </c>
       <c r="O87" s="9" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="P87" s="9" t="s">
         <v>26</v>
@@ -6694,12 +6729,12 @@
       <c r="S87" s="9"/>
       <c r="T87" s="9"/>
       <c r="U87" s="12" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B88" s="5">
         <v>46169.55907863426</v>
@@ -6711,16 +6746,16 @@
         <v>46211.70008446759</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="I88" s="5">
         <v>46335</v>
@@ -6738,13 +6773,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q88" s="5">
         <v>46335</v>
@@ -6764,7 +6799,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B89" s="8">
         <v>46169.55908684028</v>
@@ -6776,16 +6811,16 @@
         <v>46211.700054201385</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H89" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="I89" s="8">
         <v>46335</v>
@@ -6803,13 +6838,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="9" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O89" s="9" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="P89" s="9" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q89" s="9"/>
       <c r="R89" s="9"/>
@@ -6819,7 +6854,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B90" s="5">
         <v>46169.55918673611</v>
@@ -6828,18 +6863,20 @@
         <v>46211.830949814816</v>
       </c>
       <c r="D90" s="5">
-        <v>46211.83096391204</v>
+        <v>46223.57153153935</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H90" s="6"/>
+        <v>73</v>
+      </c>
+      <c r="H90" s="6" t="s">
+        <v>73</v>
+      </c>
       <c r="I90" s="5">
         <v>46336</v>
       </c>
@@ -6856,13 +6893,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q90" s="5">
         <v>46336</v>
@@ -6882,7 +6919,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B91" s="8">
         <v>46169.55919113426</v>
@@ -6891,18 +6928,20 @@
         <v>46211.83093260416</v>
       </c>
       <c r="D91" s="8">
-        <v>46211.83093474537</v>
+        <v>46223.57147459491</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H91" s="9"/>
+        <v>73</v>
+      </c>
+      <c r="H91" s="9" t="s">
+        <v>73</v>
+      </c>
       <c r="I91" s="8">
         <v>46336</v>
       </c>
@@ -6919,13 +6958,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="9" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="O91" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="P91" s="9" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q91" s="9"/>
       <c r="R91" s="9"/>
@@ -6935,7 +6974,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B92" s="5">
         <v>46169.559239560185</v>
@@ -6947,16 +6986,16 @@
         <v>46197.859819363424</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I92" s="5">
         <v>46337</v>
@@ -6974,13 +7013,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q92" s="5">
         <v>46337</v>
@@ -6995,12 +7034,12 @@
         <v>1</v>
       </c>
       <c r="U92" s="12" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B93" s="8">
         <v>46169.559243842596</v>
@@ -7012,16 +7051,16 @@
         <v>46211.830942650464</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H93" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I93" s="8">
         <v>46337</v>
@@ -7039,13 +7078,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="9" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="O93" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="P93" s="9" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q93" s="9"/>
       <c r="R93" s="9"/>
@@ -7055,7 +7094,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B94" s="5">
         <v>46169.55929686343</v>
@@ -7067,16 +7106,16 @@
         <v>46211.86402001158</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I94" s="5">
         <v>46338</v>
@@ -7094,13 +7133,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q94" s="5">
         <v>46338</v>
@@ -7120,7 +7159,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B95" s="8">
         <v>46169.55930180555</v>
@@ -7132,16 +7171,16 @@
         <v>46211.863992280094</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H95" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I95" s="8">
         <v>46338</v>
@@ -7159,13 +7198,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="9" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="O95" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="P95" s="9" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q95" s="9"/>
       <c r="R95" s="9"/>
@@ -7175,7 +7214,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B96" s="5">
         <v>46169.55938721065</v>
@@ -7185,7 +7224,7 @@
         <v>46169.60672822916</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>25</v>
@@ -7209,7 +7248,7 @@
         <v>26</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="P96" s="6" t="s">
         <v>26</v>
@@ -7222,7 +7261,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B97" s="8">
         <v>46169.55939094907</v>
@@ -7232,16 +7271,16 @@
         <v>46211.86403020834</v>
       </c>
       <c r="E97" s="9" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G97" s="9" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H97" s="9" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="I97" s="8">
         <v>46339</v>
@@ -7259,13 +7298,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="9" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="O97" s="9" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="P97" s="9" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q97" s="8">
         <v>46339</v>
@@ -7280,12 +7319,12 @@
         <v>0</v>
       </c>
       <c r="U97" s="12" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B98" s="5">
         <v>46169.55939643519</v>
@@ -7295,7 +7334,7 @@
         <v>46211.86403085648</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -7322,13 +7361,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q98" s="5">
         <v>46339</v>
@@ -7343,7 +7382,7 @@
         <v>0</v>
       </c>
       <c r="U98" s="12" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001557 - ATACAMA KOZAN OT4340.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4340.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1183" uniqueCount="309">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1184" uniqueCount="309">
   <si>
     <t xml:space="preserve"> 50001557 - ATACAMA KOZAN</t>
   </si>
@@ -6401,7 +6401,7 @@
         <v>46204.87991554398</v>
       </c>
       <c r="D82" s="5">
-        <v>46204.87991711806</v>
+        <v>46223.835960763885</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>174</v>
@@ -6410,9 +6410,11 @@
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H82" s="6"/>
+        <v>73</v>
+      </c>
+      <c r="H82" s="6" t="s">
+        <v>73</v>
+      </c>
       <c r="I82" s="5">
         <v>46329</v>
       </c>

--- a/data/50001557 - ATACAMA KOZAN OT4340.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4340.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1184" uniqueCount="309">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1184" uniqueCount="308">
   <si>
     <t xml:space="preserve"> 50001557 - ATACAMA KOZAN</t>
   </si>
@@ -823,9 +823,6 @@
   </si>
   <si>
     <t>OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR,Bodega:</t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
   <si>
     <t>1215166329573431</t>
@@ -5663,7 +5660,7 @@
         <v>46200.81968587963</v>
       </c>
       <c r="D70" s="5">
-        <v>46216.206479560184</v>
+        <v>46224.186405659726</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>235</v>
@@ -5707,8 +5704,8 @@
       <c r="R70" s="5">
         <v>46223</v>
       </c>
-      <c r="S70" s="12" t="s">
-        <v>237</v>
+      <c r="S70" s="11" t="s">
+        <v>106</v>
       </c>
       <c r="T70" s="6">
         <v>1</v>
@@ -5719,7 +5716,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B71" s="8">
         <v>46169.5588177662</v>
@@ -5731,7 +5728,7 @@
         <v>46200.819831597226</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>26</v>
@@ -5764,7 +5761,7 @@
         <v>101</v>
       </c>
       <c r="P71" s="9" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q71" s="8">
         <v>46325</v>
@@ -5784,7 +5781,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B72" s="5">
         <v>46169.55882295139</v>
@@ -5796,7 +5793,7 @@
         <v>46200.81928909722</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
@@ -5849,7 +5846,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B73" s="8">
         <v>46169.55882788195</v>
@@ -5861,7 +5858,7 @@
         <v>46211.7093043287</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>26</v>
@@ -5894,7 +5891,7 @@
         <v>152</v>
       </c>
       <c r="P73" s="9" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="Q73" s="8">
         <v>46282</v>
@@ -5914,7 +5911,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B74" s="5">
         <v>46169.55884254629</v>
@@ -5926,7 +5923,7 @@
         <v>46211.86406403936</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>25</v>
@@ -5950,7 +5947,7 @@
         <v>26</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="P74" s="6" t="s">
         <v>26</v>
@@ -5967,7 +5964,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B75" s="8">
         <v>46169.55884548611</v>
@@ -5979,7 +5976,7 @@
         <v>46223.571425636575</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
@@ -6006,13 +6003,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="Q75" s="8">
         <v>46276</v>
@@ -6032,7 +6029,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B76" s="5">
         <v>46169.55884993056</v>
@@ -6071,13 +6068,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -6087,7 +6084,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B77" s="8">
         <v>46169.55893170139</v>
@@ -6099,7 +6096,7 @@
         <v>46223.57142202546</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>26</v>
@@ -6126,13 +6123,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="9" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="O77" s="9" t="s">
         <v>174</v>
       </c>
       <c r="P77" s="9" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="Q77" s="8">
         <v>46296</v>
@@ -6152,7 +6149,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B78" s="5">
         <v>46169.55893543981</v>
@@ -6191,13 +6188,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="O78" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="P78" s="6" t="s">
         <v>257</v>
-      </c>
-      <c r="P78" s="6" t="s">
-        <v>258</v>
       </c>
       <c r="Q78" s="6"/>
       <c r="R78" s="6"/>
@@ -6207,7 +6204,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B79" s="8">
         <v>46169.558869560184</v>
@@ -6219,7 +6216,7 @@
         <v>46223.57141798611</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>26</v>
@@ -6246,13 +6243,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="9" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="P79" s="9" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="Q79" s="8">
         <v>46328</v>
@@ -6272,7 +6269,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B80" s="5">
         <v>46169.55887296297</v>
@@ -6284,7 +6281,7 @@
         <v>46223.57080435185</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
@@ -6311,13 +6308,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="O80" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="P80" s="6" t="s">
         <v>263</v>
-      </c>
-      <c r="P80" s="6" t="s">
-        <v>264</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -6327,7 +6324,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B81" s="8">
         <v>46169.5589025463</v>
@@ -6339,7 +6336,7 @@
         <v>46223.57141431713</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
@@ -6366,13 +6363,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="O81" s="9" t="s">
         <v>174</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="Q81" s="8">
         <v>46329</v>
@@ -6392,7 +6389,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B82" s="5">
         <v>46169.55890609954</v>
@@ -6431,13 +6428,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="O82" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="P82" s="6" t="s">
         <v>268</v>
-      </c>
-      <c r="P82" s="6" t="s">
-        <v>269</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6447,7 +6444,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B83" s="8">
         <v>46169.55900443287</v>
@@ -6459,7 +6456,7 @@
         <v>46223.57141039352</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>26</v>
@@ -6486,13 +6483,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="9" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="O83" s="9" t="s">
         <v>174</v>
       </c>
       <c r="P83" s="9" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="Q83" s="8">
         <v>46330</v>
@@ -6512,7 +6509,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B84" s="5">
         <v>46169.55901002315</v>
@@ -6551,13 +6548,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="O84" s="6" t="s">
         <v>174</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="Q84" s="6"/>
       <c r="R84" s="6"/>
@@ -6567,7 +6564,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B85" s="8">
         <v>46169.55904462963</v>
@@ -6579,7 +6576,7 @@
         <v>46223.5714043287</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>26</v>
@@ -6606,13 +6603,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="9" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="O85" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="P85" s="9" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="Q85" s="8">
         <v>46332</v>
@@ -6632,7 +6629,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B86" s="5">
         <v>46169.559050138894</v>
@@ -6644,7 +6641,7 @@
         <v>46223.57102379629</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6671,13 +6668,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="O86" s="6" t="s">
         <v>174</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6687,7 +6684,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B87" s="8">
         <v>46169.55907484954</v>
@@ -6697,7 +6694,7 @@
         <v>46211.8640300463</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>25</v>
@@ -6721,7 +6718,7 @@
         <v>26</v>
       </c>
       <c r="O87" s="9" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="P87" s="9" t="s">
         <v>26</v>
@@ -6736,7 +6733,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B88" s="5">
         <v>46169.55907863426</v>
@@ -6748,16 +6745,16 @@
         <v>46211.70008446759</v>
       </c>
       <c r="E88" s="6" t="s">
+        <v>282</v>
+      </c>
+      <c r="F88" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G88" s="6" t="s">
         <v>283</v>
       </c>
-      <c r="F88" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G88" s="6" t="s">
+      <c r="H88" s="6" t="s">
         <v>284</v>
-      </c>
-      <c r="H88" s="6" t="s">
-        <v>285</v>
       </c>
       <c r="I88" s="5">
         <v>46335</v>
@@ -6775,13 +6772,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="Q88" s="5">
         <v>46335</v>
@@ -6801,7 +6798,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B89" s="8">
         <v>46169.55908684028</v>
@@ -6819,10 +6816,10 @@
         <v>26</v>
       </c>
       <c r="G89" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="H89" s="9" t="s">
         <v>284</v>
-      </c>
-      <c r="H89" s="9" t="s">
-        <v>285</v>
       </c>
       <c r="I89" s="8">
         <v>46335</v>
@@ -6840,13 +6837,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="9" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="O89" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="P89" s="9" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="Q89" s="9"/>
       <c r="R89" s="9"/>
@@ -6856,7 +6853,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B90" s="5">
         <v>46169.55918673611</v>
@@ -6868,7 +6865,7 @@
         <v>46223.57153153935</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
@@ -6895,13 +6892,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="O90" s="6" t="s">
         <v>174</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="Q90" s="5">
         <v>46336</v>
@@ -6921,7 +6918,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B91" s="8">
         <v>46169.55919113426</v>
@@ -6960,13 +6957,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="9" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="O91" s="9" t="s">
         <v>174</v>
       </c>
       <c r="P91" s="9" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="Q91" s="9"/>
       <c r="R91" s="9"/>
@@ -6976,7 +6973,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B92" s="5">
         <v>46169.559239560185</v>
@@ -6988,7 +6985,7 @@
         <v>46197.859819363424</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
@@ -7015,13 +7012,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="O92" s="6" t="s">
         <v>174</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="Q92" s="5">
         <v>46337</v>
@@ -7041,7 +7038,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B93" s="8">
         <v>46169.559243842596</v>
@@ -7080,13 +7077,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="9" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="O93" s="9" t="s">
         <v>174</v>
       </c>
       <c r="P93" s="9" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="Q93" s="9"/>
       <c r="R93" s="9"/>
@@ -7096,7 +7093,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B94" s="5">
         <v>46169.55929686343</v>
@@ -7108,7 +7105,7 @@
         <v>46211.86402001158</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
@@ -7135,13 +7132,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="O94" s="6" t="s">
         <v>174</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="Q94" s="5">
         <v>46338</v>
@@ -7161,7 +7158,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B95" s="8">
         <v>46169.55930180555</v>
@@ -7200,13 +7197,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="9" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="O95" s="9" t="s">
         <v>174</v>
       </c>
       <c r="P95" s="9" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="Q95" s="9"/>
       <c r="R95" s="9"/>
@@ -7216,7 +7213,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B96" s="5">
         <v>46169.55938721065</v>
@@ -7226,7 +7223,7 @@
         <v>46169.60672822916</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>25</v>
@@ -7250,7 +7247,7 @@
         <v>26</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="P96" s="6" t="s">
         <v>26</v>
@@ -7263,7 +7260,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B97" s="8">
         <v>46169.55939094907</v>
@@ -7273,16 +7270,16 @@
         <v>46211.86403020834</v>
       </c>
       <c r="E97" s="9" t="s">
+        <v>303</v>
+      </c>
+      <c r="F97" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G97" s="9" t="s">
         <v>304</v>
       </c>
-      <c r="F97" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G97" s="9" t="s">
+      <c r="H97" s="9" t="s">
         <v>305</v>
-      </c>
-      <c r="H97" s="9" t="s">
-        <v>306</v>
       </c>
       <c r="I97" s="8">
         <v>46339</v>
@@ -7300,13 +7297,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="9" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="O97" s="9" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="P97" s="9" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="Q97" s="8">
         <v>46339</v>
@@ -7326,7 +7323,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B98" s="5">
         <v>46169.55939643519</v>
@@ -7336,7 +7333,7 @@
         <v>46211.86403085648</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -7363,13 +7360,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="Q98" s="5">
         <v>46339</v>

--- a/data/50001557 - ATACAMA KOZAN OT4340.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4340.xlsx
@@ -771,7 +771,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t xml:space="preserve">OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR,OT2 4307 ZVN 1-9-86/2 </t>
+    <t>OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A</t>
   </si>
   <si>
     <t>1215166433625244</t>
@@ -5251,7 +5251,7 @@
         <v>46190.645243935185</v>
       </c>
       <c r="D63" s="8">
-        <v>46197.85915361111</v>
+        <v>46224.878386516204</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>216</v>

--- a/data/50001557 - ATACAMA KOZAN OT4340.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4340.xlsx
@@ -771,7 +771,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t>OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A</t>
+    <t>OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA</t>
   </si>
   <si>
     <t>1215166433625244</t>
@@ -5251,7 +5251,7 @@
         <v>46190.645243935185</v>
       </c>
       <c r="D63" s="8">
-        <v>46224.878386516204</v>
+        <v>46225.00959311343</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>216</v>

--- a/data/50001557 - ATACAMA KOZAN OT4340.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4340.xlsx
@@ -771,7 +771,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t>OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA</t>
+    <t xml:space="preserve">OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A </t>
   </si>
   <si>
     <t>1215166433625244</t>
@@ -5251,7 +5251,7 @@
         <v>46190.645243935185</v>
       </c>
       <c r="D63" s="8">
-        <v>46225.00959311343</v>
+        <v>46225.58945508102</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>216</v>

--- a/data/50001557 - ATACAMA KOZAN OT4340.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4340.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1184" uniqueCount="308">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1184" uniqueCount="309">
   <si>
     <t xml:space="preserve"> 50001557 - ATACAMA KOZAN</t>
   </si>
@@ -333,6 +333,9 @@
     <t>propuesta nucleo rodete OT 4340</t>
   </si>
   <si>
+    <t>NATALYA ESPINOZA</t>
+  </si>
+  <si>
     <t>nespinoza@zitron.com</t>
   </si>
   <si>
@@ -771,7 +774,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t xml:space="preserve">OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A </t>
+    <t>OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
   </si>
   <si>
     <t>1215166433625244</t>
@@ -2475,7 +2478,7 @@
         <v>73</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I17" s="8">
         <v>46167</v>
@@ -2499,7 +2502,7 @@
         <v>56</v>
       </c>
       <c r="P17" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q17" s="8">
         <v>46167</v>
@@ -2519,7 +2522,7 @@
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B18" s="5">
         <v>46169.55823646991</v>
@@ -2531,7 +2534,7 @@
         <v>46223.570560636574</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>26</v>
@@ -2540,7 +2543,7 @@
         <v>73</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I18" s="5">
         <v>46239</v>
@@ -2561,10 +2564,10 @@
         <v>63</v>
       </c>
       <c r="O18" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q18" s="5">
         <v>46239</v>
@@ -2584,7 +2587,7 @@
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B19" s="8">
         <v>46169.55824171296</v>
@@ -2596,7 +2599,7 @@
         <v>46223.57055704861</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F19" s="9" t="s">
         <v>26</v>
@@ -2605,7 +2608,7 @@
         <v>73</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I19" s="8">
         <v>46239</v>
@@ -2626,10 +2629,10 @@
         <v>63</v>
       </c>
       <c r="O19" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="P19" s="9" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q19" s="8">
         <v>46239</v>
@@ -2649,7 +2652,7 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B20" s="5">
         <v>46169.55824574074</v>
@@ -2661,7 +2664,7 @@
         <v>46223.57055334491</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
@@ -2670,7 +2673,7 @@
         <v>73</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I20" s="5">
         <v>46239</v>
@@ -2691,10 +2694,10 @@
         <v>63</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q20" s="5">
         <v>46239</v>
@@ -2714,7 +2717,7 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B21" s="8">
         <v>46169.55825006944</v>
@@ -2726,7 +2729,7 @@
         <v>46223.570547662035</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F21" s="9" t="s">
         <v>26</v>
@@ -2735,7 +2738,7 @@
         <v>73</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I21" s="8">
         <v>46239</v>
@@ -2756,10 +2759,10 @@
         <v>63</v>
       </c>
       <c r="O21" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="P21" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Q21" s="8">
         <v>46239</v>
@@ -2779,7 +2782,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B22" s="5">
         <v>46169.55801826389</v>
@@ -2791,7 +2794,7 @@
         <v>46200.818425798614</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>25</v>
@@ -2815,7 +2818,7 @@
         <v>26</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="P22" s="6" t="s">
         <v>26</v>
@@ -2828,7 +2831,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B23" s="8">
         <v>46169.558301956014</v>
@@ -2840,16 +2843,16 @@
         <v>46200.81833380787</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I23" s="8">
         <v>46169</v>
@@ -2867,13 +2870,13 @@
         <v>26</v>
       </c>
       <c r="N23" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O23" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="P23" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="Q23" s="8">
         <v>46169</v>
@@ -2893,7 +2896,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B24" s="5">
         <v>46169.558306516206</v>
@@ -2905,16 +2908,16 @@
         <v>46195.69079224537</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I24" s="5">
         <v>46169</v>
@@ -2932,13 +2935,13 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="O24" s="6" t="s">
         <v>69</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q24" s="6"/>
       <c r="R24" s="6"/>
@@ -2949,12 +2952,12 @@
         <v>0</v>
       </c>
       <c r="U24" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B25" s="8">
         <v>46169.55831137732</v>
@@ -2966,16 +2969,16 @@
         <v>46195.690800474535</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I25" s="8">
         <v>46171</v>
@@ -2993,13 +2996,13 @@
         <v>26</v>
       </c>
       <c r="N25" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="O25" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="P25" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="Q25" s="9"/>
       <c r="R25" s="9"/>
@@ -3010,12 +3013,12 @@
         <v>0</v>
       </c>
       <c r="U25" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B26" s="5">
         <v>46169.55831605324</v>
@@ -3027,16 +3030,16 @@
         <v>46220.171629351855</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I26" s="5">
         <v>46169</v>
@@ -3054,13 +3057,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="Q26" s="5">
         <v>46169</v>
@@ -3069,7 +3072,7 @@
         <v>46219</v>
       </c>
       <c r="S26" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="T26" s="6">
         <v>1</v>
@@ -3080,7 +3083,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B27" s="8">
         <v>46169.55832063657</v>
@@ -3092,16 +3095,16 @@
         <v>46184.7364097338</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I27" s="8">
         <v>46169</v>
@@ -3119,13 +3122,13 @@
         <v>26</v>
       </c>
       <c r="N27" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="O27" s="9" t="s">
         <v>72</v>
       </c>
       <c r="P27" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Q27" s="9"/>
       <c r="R27" s="9"/>
@@ -3136,12 +3139,12 @@
         <v>0</v>
       </c>
       <c r="U27" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B28" s="5">
         <v>46169.55832539352</v>
@@ -3153,16 +3156,16 @@
         <v>46184.736449375</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I28" s="5">
         <v>46171</v>
@@ -3180,13 +3183,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
@@ -3197,12 +3200,12 @@
         <v>0</v>
       </c>
       <c r="U28" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B29" s="8">
         <v>46169.55833006944</v>
@@ -3214,16 +3217,16 @@
         <v>46200.81836952546</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I29" s="8">
         <v>46161</v>
@@ -3241,13 +3244,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O29" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="P29" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="Q29" s="8">
         <v>46161</v>
@@ -3267,7 +3270,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B30" s="5">
         <v>46169.55833486111</v>
@@ -3279,16 +3282,16 @@
         <v>46195.69066259259</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I30" s="5">
         <v>46161</v>
@@ -3306,13 +3309,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O30" s="6" t="s">
         <v>66</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -3323,12 +3326,12 @@
         <v>0</v>
       </c>
       <c r="U30" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B31" s="8">
         <v>46169.5583402662</v>
@@ -3340,16 +3343,16 @@
         <v>46195.69066760417</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I31" s="8">
         <v>46178</v>
@@ -3367,13 +3370,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O31" s="9" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="P31" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="Q31" s="9"/>
       <c r="R31" s="9"/>
@@ -3384,12 +3387,12 @@
         <v>0</v>
       </c>
       <c r="U31" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B32" s="5">
         <v>46169.55834503472</v>
@@ -3401,16 +3404,16 @@
         <v>46195.6906680324</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I32" s="5">
         <v>46178</v>
@@ -3428,13 +3431,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
@@ -3445,12 +3448,12 @@
         <v>0</v>
       </c>
       <c r="U32" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B33" s="8">
         <v>46169.55836335648</v>
@@ -3462,16 +3465,16 @@
         <v>46184.532641875005</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I33" s="8">
         <v>46241</v>
@@ -3489,13 +3492,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="Q33" s="8">
         <v>46241</v>
@@ -3515,7 +3518,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B34" s="5">
         <v>46169.558367986116</v>
@@ -3527,16 +3530,16 @@
         <v>46184.53245875</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I34" s="5">
         <v>46241</v>
@@ -3554,13 +3557,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3571,12 +3574,12 @@
         <v>0</v>
       </c>
       <c r="U34" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B35" s="8">
         <v>46169.55837292824</v>
@@ -3588,16 +3591,16 @@
         <v>46184.532615856486</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I35" s="8">
         <v>46245</v>
@@ -3615,13 +3618,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="P35" s="9" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="Q35" s="9"/>
       <c r="R35" s="9"/>
@@ -3632,12 +3635,12 @@
         <v>0</v>
       </c>
       <c r="U35" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B36" s="5">
         <v>46169.55837825232</v>
@@ -3649,16 +3652,16 @@
         <v>46184.53258194444</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I36" s="5">
         <v>46241</v>
@@ -3676,10 +3679,10 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="P36" s="6" t="s">
         <v>26</v>
@@ -3702,7 +3705,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B37" s="8">
         <v>46169.558381979165</v>
@@ -3714,16 +3717,16 @@
         <v>46184.5322071875</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I37" s="8">
         <v>46241</v>
@@ -3741,13 +3744,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="Q37" s="9"/>
       <c r="R37" s="9"/>
@@ -3757,7 +3760,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B38" s="5">
         <v>46169.55838657408</v>
@@ -3769,16 +3772,16 @@
         <v>46184.53255631945</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I38" s="5">
         <v>46245</v>
@@ -3796,13 +3799,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -3812,7 +3815,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B39" s="8">
         <v>46169.55839107639</v>
@@ -3824,16 +3827,16 @@
         <v>46205.600326053245</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I39" s="8">
         <v>46241</v>
@@ -3851,10 +3854,10 @@
         <v>26</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P39" s="9" t="s">
         <v>26</v>
@@ -3877,7 +3880,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B40" s="5">
         <v>46169.55839478009</v>
@@ -3889,16 +3892,16 @@
         <v>46195.70360162037</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I40" s="5">
         <v>46241</v>
@@ -3916,13 +3919,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -3932,7 +3935,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B41" s="8">
         <v>46169.55839910879</v>
@@ -3944,16 +3947,16 @@
         <v>46195.70375376157</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I41" s="8">
         <v>46252</v>
@@ -3971,13 +3974,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Q41" s="9"/>
       <c r="R41" s="9"/>
@@ -3987,7 +3990,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B42" s="5">
         <v>46169.55840355324</v>
@@ -3999,16 +4002,16 @@
         <v>46205.59994755787</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I42" s="5">
         <v>46281</v>
@@ -4026,10 +4029,10 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>26</v>
@@ -4042,7 +4045,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B43" s="8">
         <v>46169.55840677083</v>
@@ -4054,16 +4057,16 @@
         <v>46191.53701371528</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I43" s="8">
         <v>46241</v>
@@ -4081,10 +4084,10 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="P43" s="9" t="s">
         <v>26</v>
@@ -4107,7 +4110,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B44" s="5">
         <v>46169.55841037037</v>
@@ -4119,16 +4122,16 @@
         <v>46191.53679194444</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I44" s="5">
         <v>46241</v>
@@ -4146,13 +4149,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4162,7 +4165,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B45" s="8">
         <v>46169.558458217594</v>
@@ -4174,16 +4177,16 @@
         <v>46191.53698841435</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I45" s="8">
         <v>46245</v>
@@ -4201,13 +4204,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="P45" s="9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q45" s="9"/>
       <c r="R45" s="9"/>
@@ -4217,7 +4220,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B46" s="5">
         <v>46169.5584643287</v>
@@ -4227,7 +4230,7 @@
         <v>46182.75962331019</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>25</v>
@@ -4251,7 +4254,7 @@
         <v>26</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4261,12 +4264,12 @@
       <c r="S46" s="6"/>
       <c r="T46" s="6"/>
       <c r="U46" s="12" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B47" s="8">
         <v>46169.55846813657</v>
@@ -4278,16 +4281,16 @@
         <v>46197.715420312496</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I47" s="8">
         <v>46167</v>
@@ -4305,13 +4308,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q47" s="8">
         <v>46167</v>
@@ -4320,7 +4323,7 @@
         <v>46184</v>
       </c>
       <c r="S47" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="T47" s="9">
         <v>1</v>
@@ -4331,7 +4334,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B48" s="5">
         <v>46169.558472766206</v>
@@ -4343,16 +4346,16 @@
         <v>46181.72663056713</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I48" s="5">
         <v>46167</v>
@@ -4370,13 +4373,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="O48" s="6" t="s">
         <v>60</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q48" s="6"/>
       <c r="R48" s="6"/>
@@ -4386,7 +4389,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B49" s="8">
         <v>46169.55849938658</v>
@@ -4398,16 +4401,16 @@
         <v>46197.71545016204</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I49" s="8">
         <v>46218</v>
@@ -4425,13 +4428,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q49" s="8">
         <v>46218</v>
@@ -4451,7 +4454,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B50" s="5">
         <v>46169.55850371528</v>
@@ -4463,16 +4466,16 @@
         <v>46195.690583055555</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I50" s="5">
         <v>46218</v>
@@ -4490,13 +4493,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q50" s="6"/>
       <c r="R50" s="6"/>
@@ -4506,7 +4509,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B51" s="8">
         <v>46169.55853228009</v>
@@ -4518,16 +4521,16 @@
         <v>46182.759871076385</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I51" s="8">
         <v>46238</v>
@@ -4545,13 +4548,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q51" s="8">
         <v>46238</v>
@@ -4571,7 +4574,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B52" s="5">
         <v>46169.55854641204</v>
@@ -4583,16 +4586,16 @@
         <v>46182.75984881945</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I52" s="5">
         <v>46238</v>
@@ -4610,13 +4613,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4626,7 +4629,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B53" s="8">
         <v>46169.558565775464</v>
@@ -4638,16 +4641,16 @@
         <v>46211.86422231482</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I53" s="8">
         <v>46331</v>
@@ -4665,10 +4668,10 @@
         <v>26</v>
       </c>
       <c r="N53" s="9" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P53" s="9" t="s">
         <v>26</v>
@@ -4691,7 +4694,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B54" s="5">
         <v>46169.55856972223</v>
@@ -4703,16 +4706,16 @@
         <v>46211.86419394676</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I54" s="5">
         <v>46331</v>
@@ -4730,13 +4733,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q54" s="6"/>
       <c r="R54" s="6"/>
@@ -4746,7 +4749,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B55" s="8">
         <v>46169.558586307874</v>
@@ -4758,7 +4761,7 @@
         <v>46198.597746307874</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>25</v>
@@ -4782,7 +4785,7 @@
         <v>26</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="P55" s="9" t="s">
         <v>26</v>
@@ -4799,7 +4802,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B56" s="5">
         <v>46169.55858945602</v>
@@ -4811,16 +4814,16 @@
         <v>46197.83559606482</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I56" s="5">
         <v>46254</v>
@@ -4838,13 +4841,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q56" s="5">
         <v>46254</v>
@@ -4864,7 +4867,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B57" s="8">
         <v>46169.55859488426</v>
@@ -4876,16 +4879,16 @@
         <v>46197.85937331019</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I57" s="8">
         <v>46258</v>
@@ -4903,13 +4906,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q57" s="8">
         <v>46258</v>
@@ -4929,7 +4932,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B58" s="5">
         <v>46169.55860118056</v>
@@ -4941,16 +4944,16 @@
         <v>46198.59771457176</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I58" s="5">
         <v>46254</v>
@@ -4968,13 +4971,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q58" s="5">
         <v>46254</v>
@@ -4994,7 +4997,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B59" s="8">
         <v>46169.55860636574</v>
@@ -5006,16 +5009,16 @@
         <v>46198.597709444446</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I59" s="8">
         <v>46258</v>
@@ -5033,13 +5036,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q59" s="8">
         <v>46258</v>
@@ -5054,12 +5057,12 @@
         <v>1</v>
       </c>
       <c r="U59" s="12" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B60" s="5">
         <v>46169.558650127314</v>
@@ -5071,16 +5074,16 @@
         <v>46198.59773310185</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I60" s="5">
         <v>46254</v>
@@ -5098,13 +5101,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q60" s="5">
         <v>46254</v>
@@ -5124,7 +5127,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B61" s="8">
         <v>46169.55865608796</v>
@@ -5136,16 +5139,16 @@
         <v>46198.59773317129</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I61" s="8">
         <v>46258</v>
@@ -5163,13 +5166,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q61" s="8">
         <v>46258</v>
@@ -5184,12 +5187,12 @@
         <v>1</v>
       </c>
       <c r="U61" s="12" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B62" s="5">
         <v>46169.55866105324</v>
@@ -5201,7 +5204,7 @@
         <v>46198.68229049769</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>25</v>
@@ -5225,7 +5228,7 @@
         <v>26</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="P62" s="6" t="s">
         <v>26</v>
@@ -5242,7 +5245,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B63" s="8">
         <v>46169.55866469907</v>
@@ -5251,19 +5254,19 @@
         <v>46190.645243935185</v>
       </c>
       <c r="D63" s="8">
-        <v>46225.58945508102</v>
+        <v>46225.86187357639</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H63" s="9" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I63" s="8">
         <v>46260</v>
@@ -5281,13 +5284,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P63" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q63" s="8">
         <v>46260</v>
@@ -5307,7 +5310,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B64" s="5">
         <v>46169.55867099537</v>
@@ -5319,16 +5322,16 @@
         <v>46197.85936673611</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I64" s="5">
         <v>46260</v>
@@ -5346,13 +5349,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5362,7 +5365,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B65" s="8">
         <v>46169.558703518516</v>
@@ -5374,16 +5377,16 @@
         <v>46197.85387390046</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H65" s="9" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I65" s="8">
         <v>46269</v>
@@ -5401,13 +5404,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q65" s="8">
         <v>46269</v>
@@ -5422,12 +5425,12 @@
         <v>1</v>
       </c>
       <c r="U65" s="12" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B66" s="5">
         <v>46169.55870879629</v>
@@ -5439,16 +5442,16 @@
         <v>46197.85915420139</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I66" s="5">
         <v>46269</v>
@@ -5466,13 +5469,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5482,7 +5485,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B67" s="8">
         <v>46169.558740625</v>
@@ -5494,16 +5497,16 @@
         <v>46205.65959174768</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H67" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I67" s="8">
         <v>46274</v>
@@ -5521,13 +5524,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P67" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q67" s="8">
         <v>46274</v>
@@ -5542,12 +5545,12 @@
         <v>1</v>
       </c>
       <c r="U67" s="12" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B68" s="5">
         <v>46169.558745243055</v>
@@ -5559,16 +5562,16 @@
         <v>46205.659588587965</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I68" s="5">
         <v>46274</v>
@@ -5586,13 +5589,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q68" s="6"/>
       <c r="R68" s="6"/>
@@ -5602,7 +5605,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B69" s="8">
         <v>46169.55876947917</v>
@@ -5614,7 +5617,7 @@
         <v>46211.70953918982</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>25</v>
@@ -5638,7 +5641,7 @@
         <v>26</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="P69" s="9" t="s">
         <v>26</v>
@@ -5651,7 +5654,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B70" s="5">
         <v>46169.55880633101</v>
@@ -5663,16 +5666,16 @@
         <v>46224.186405659726</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I70" s="5">
         <v>46220</v>
@@ -5690,13 +5693,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q70" s="5">
         <v>46220</v>
@@ -5705,7 +5708,7 @@
         <v>46223</v>
       </c>
       <c r="S70" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="T70" s="6">
         <v>1</v>
@@ -5716,7 +5719,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B71" s="8">
         <v>46169.5588177662</v>
@@ -5728,16 +5731,16 @@
         <v>46200.819831597226</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H71" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I71" s="8">
         <v>46325</v>
@@ -5755,13 +5758,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="P71" s="9" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q71" s="8">
         <v>46325</v>
@@ -5770,7 +5773,7 @@
         <v>46325</v>
       </c>
       <c r="S71" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="T71" s="9">
         <v>1</v>
@@ -5781,7 +5784,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B72" s="5">
         <v>46169.55882295139</v>
@@ -5793,16 +5796,16 @@
         <v>46200.81928909722</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I72" s="5">
         <v>46293</v>
@@ -5820,13 +5823,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q72" s="5">
         <v>46293</v>
@@ -5846,7 +5849,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B73" s="8">
         <v>46169.55882788195</v>
@@ -5858,16 +5861,16 @@
         <v>46211.7093043287</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H73" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I73" s="8">
         <v>46282</v>
@@ -5885,13 +5888,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="P73" s="9" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q73" s="8">
         <v>46282</v>
@@ -5911,7 +5914,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B74" s="5">
         <v>46169.55884254629</v>
@@ -5923,7 +5926,7 @@
         <v>46211.86406403936</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>25</v>
@@ -5947,7 +5950,7 @@
         <v>26</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P74" s="6" t="s">
         <v>26</v>
@@ -5964,7 +5967,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B75" s="8">
         <v>46169.55884548611</v>
@@ -5976,7 +5979,7 @@
         <v>46223.571425636575</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
@@ -5985,7 +5988,7 @@
         <v>73</v>
       </c>
       <c r="H75" s="9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I75" s="8">
         <v>46276</v>
@@ -6003,13 +6006,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q75" s="8">
         <v>46276</v>
@@ -6024,12 +6027,12 @@
         <v>1</v>
       </c>
       <c r="U75" s="12" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B76" s="5">
         <v>46169.55884993056</v>
@@ -6041,7 +6044,7 @@
         <v>46223.57064498843</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
@@ -6050,7 +6053,7 @@
         <v>73</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I76" s="5">
         <v>46276</v>
@@ -6068,13 +6071,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -6084,7 +6087,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B77" s="8">
         <v>46169.55893170139</v>
@@ -6096,7 +6099,7 @@
         <v>46223.57142202546</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>26</v>
@@ -6105,7 +6108,7 @@
         <v>73</v>
       </c>
       <c r="H77" s="9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I77" s="8">
         <v>46296</v>
@@ -6123,13 +6126,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P77" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q77" s="8">
         <v>46296</v>
@@ -6149,7 +6152,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B78" s="5">
         <v>46169.55893543981</v>
@@ -6161,7 +6164,7 @@
         <v>46223.57074214121</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
@@ -6170,7 +6173,7 @@
         <v>73</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I78" s="5">
         <v>46296</v>
@@ -6188,13 +6191,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q78" s="6"/>
       <c r="R78" s="6"/>
@@ -6204,7 +6207,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B79" s="8">
         <v>46169.558869560184</v>
@@ -6216,7 +6219,7 @@
         <v>46223.57141798611</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>26</v>
@@ -6225,7 +6228,7 @@
         <v>73</v>
       </c>
       <c r="H79" s="9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I79" s="8">
         <v>46328</v>
@@ -6243,13 +6246,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="P79" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q79" s="8">
         <v>46328</v>
@@ -6269,7 +6272,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B80" s="5">
         <v>46169.55887296297</v>
@@ -6281,7 +6284,7 @@
         <v>46223.57080435185</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
@@ -6290,7 +6293,7 @@
         <v>73</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I80" s="5">
         <v>46328</v>
@@ -6308,13 +6311,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -6324,7 +6327,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B81" s="8">
         <v>46169.5589025463</v>
@@ -6336,7 +6339,7 @@
         <v>46223.57141431713</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
@@ -6345,7 +6348,7 @@
         <v>73</v>
       </c>
       <c r="H81" s="9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I81" s="8">
         <v>46329</v>
@@ -6363,13 +6366,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q81" s="8">
         <v>46329</v>
@@ -6389,7 +6392,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B82" s="5">
         <v>46169.55890609954</v>
@@ -6401,7 +6404,7 @@
         <v>46223.835960763885</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
@@ -6410,7 +6413,7 @@
         <v>73</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I82" s="5">
         <v>46329</v>
@@ -6428,13 +6431,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6444,7 +6447,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B83" s="8">
         <v>46169.55900443287</v>
@@ -6456,7 +6459,7 @@
         <v>46223.57141039352</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>26</v>
@@ -6465,7 +6468,7 @@
         <v>73</v>
       </c>
       <c r="H83" s="9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I83" s="8">
         <v>46330</v>
@@ -6483,13 +6486,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O83" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P83" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q83" s="8">
         <v>46330</v>
@@ -6509,7 +6512,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B84" s="5">
         <v>46169.55901002315</v>
@@ -6521,7 +6524,7 @@
         <v>46223.57092783565</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
@@ -6530,7 +6533,7 @@
         <v>73</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I84" s="5">
         <v>46330</v>
@@ -6548,13 +6551,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q84" s="6"/>
       <c r="R84" s="6"/>
@@ -6564,7 +6567,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B85" s="8">
         <v>46169.55904462963</v>
@@ -6576,7 +6579,7 @@
         <v>46223.5714043287</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>26</v>
@@ -6585,7 +6588,7 @@
         <v>73</v>
       </c>
       <c r="H85" s="9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I85" s="8">
         <v>46332</v>
@@ -6603,13 +6606,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O85" s="9" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="P85" s="9" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q85" s="8">
         <v>46332</v>
@@ -6629,7 +6632,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B86" s="5">
         <v>46169.559050138894</v>
@@ -6641,7 +6644,7 @@
         <v>46223.57102379629</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6650,7 +6653,7 @@
         <v>73</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I86" s="5">
         <v>46332</v>
@@ -6668,13 +6671,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6684,7 +6687,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B87" s="8">
         <v>46169.55907484954</v>
@@ -6694,7 +6697,7 @@
         <v>46211.8640300463</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>25</v>
@@ -6718,7 +6721,7 @@
         <v>26</v>
       </c>
       <c r="O87" s="9" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="P87" s="9" t="s">
         <v>26</v>
@@ -6728,12 +6731,12 @@
       <c r="S87" s="9"/>
       <c r="T87" s="9"/>
       <c r="U87" s="12" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B88" s="5">
         <v>46169.55907863426</v>
@@ -6745,16 +6748,16 @@
         <v>46211.70008446759</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="I88" s="5">
         <v>46335</v>
@@ -6772,13 +6775,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q88" s="5">
         <v>46335</v>
@@ -6798,7 +6801,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B89" s="8">
         <v>46169.55908684028</v>
@@ -6810,16 +6813,16 @@
         <v>46211.700054201385</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H89" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="I89" s="8">
         <v>46335</v>
@@ -6837,13 +6840,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="9" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O89" s="9" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="P89" s="9" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q89" s="9"/>
       <c r="R89" s="9"/>
@@ -6853,7 +6856,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B90" s="5">
         <v>46169.55918673611</v>
@@ -6865,7 +6868,7 @@
         <v>46223.57153153935</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
@@ -6874,7 +6877,7 @@
         <v>73</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I90" s="5">
         <v>46336</v>
@@ -6892,13 +6895,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q90" s="5">
         <v>46336</v>
@@ -6918,7 +6921,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B91" s="8">
         <v>46169.55919113426</v>
@@ -6930,7 +6933,7 @@
         <v>46223.57147459491</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>26</v>
@@ -6939,7 +6942,7 @@
         <v>73</v>
       </c>
       <c r="H91" s="9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I91" s="8">
         <v>46336</v>
@@ -6957,13 +6960,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="9" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="O91" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P91" s="9" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q91" s="9"/>
       <c r="R91" s="9"/>
@@ -6973,7 +6976,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B92" s="5">
         <v>46169.559239560185</v>
@@ -6985,16 +6988,16 @@
         <v>46197.859819363424</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I92" s="5">
         <v>46337</v>
@@ -7012,13 +7015,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q92" s="5">
         <v>46337</v>
@@ -7033,12 +7036,12 @@
         <v>1</v>
       </c>
       <c r="U92" s="12" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B93" s="8">
         <v>46169.559243842596</v>
@@ -7050,16 +7053,16 @@
         <v>46211.830942650464</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H93" s="9" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I93" s="8">
         <v>46337</v>
@@ -7077,13 +7080,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="9" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="O93" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P93" s="9" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q93" s="9"/>
       <c r="R93" s="9"/>
@@ -7093,7 +7096,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B94" s="5">
         <v>46169.55929686343</v>
@@ -7105,16 +7108,16 @@
         <v>46211.86402001158</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I94" s="5">
         <v>46338</v>
@@ -7132,13 +7135,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q94" s="5">
         <v>46338</v>
@@ -7158,7 +7161,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B95" s="8">
         <v>46169.55930180555</v>
@@ -7170,16 +7173,16 @@
         <v>46211.863992280094</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H95" s="9" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I95" s="8">
         <v>46338</v>
@@ -7197,13 +7200,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="9" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="O95" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P95" s="9" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q95" s="9"/>
       <c r="R95" s="9"/>
@@ -7213,7 +7216,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B96" s="5">
         <v>46169.55938721065</v>
@@ -7223,7 +7226,7 @@
         <v>46169.60672822916</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>25</v>
@@ -7247,7 +7250,7 @@
         <v>26</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="P96" s="6" t="s">
         <v>26</v>
@@ -7260,7 +7263,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B97" s="8">
         <v>46169.55939094907</v>
@@ -7270,16 +7273,16 @@
         <v>46211.86403020834</v>
       </c>
       <c r="E97" s="9" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G97" s="9" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H97" s="9" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="I97" s="8">
         <v>46339</v>
@@ -7297,13 +7300,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="9" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="O97" s="9" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="P97" s="9" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q97" s="8">
         <v>46339</v>
@@ -7318,12 +7321,12 @@
         <v>0</v>
       </c>
       <c r="U97" s="12" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B98" s="5">
         <v>46169.55939643519</v>
@@ -7333,7 +7336,7 @@
         <v>46211.86403085648</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -7360,13 +7363,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q98" s="5">
         <v>46339</v>
@@ -7381,7 +7384,7 @@
         <v>0</v>
       </c>
       <c r="U98" s="12" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001557 - ATACAMA KOZAN OT4340.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4340.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1184" uniqueCount="309">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1184" uniqueCount="310">
   <si>
     <t xml:space="preserve"> 50001557 - ATACAMA KOZAN</t>
   </si>
@@ -658,6 +658,9 @@
   </si>
   <si>
     <t>Planos definitivos</t>
+  </si>
+  <si>
+    <t>Media</t>
   </si>
   <si>
     <t>1215166041791446</t>
@@ -4398,7 +4401,7 @@
         <v>46182.759602164355</v>
       </c>
       <c r="D49" s="8">
-        <v>46197.71545016204</v>
+        <v>46230.196269340275</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>181</v>
@@ -4442,8 +4445,8 @@
       <c r="R49" s="8">
         <v>46237</v>
       </c>
-      <c r="S49" s="10" t="s">
-        <v>32</v>
+      <c r="S49" s="12" t="s">
+        <v>182</v>
       </c>
       <c r="T49" s="9">
         <v>1</v>
@@ -4454,7 +4457,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B50" s="5">
         <v>46169.55850371528</v>
@@ -4496,10 +4499,10 @@
         <v>181</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q50" s="6"/>
       <c r="R50" s="6"/>
@@ -4509,7 +4512,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B51" s="8">
         <v>46169.55853228009</v>
@@ -4554,7 +4557,7 @@
         <v>175</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q51" s="8">
         <v>46238</v>
@@ -4574,7 +4577,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B52" s="5">
         <v>46169.55854641204</v>
@@ -4629,7 +4632,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B53" s="8">
         <v>46169.558565775464</v>
@@ -4641,16 +4644,16 @@
         <v>46211.86422231482</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I53" s="8">
         <v>46331</v>
@@ -4694,7 +4697,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B54" s="5">
         <v>46169.55856972223</v>
@@ -4712,10 +4715,10 @@
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I54" s="5">
         <v>46331</v>
@@ -4733,13 +4736,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="O54" s="6" t="s">
         <v>175</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q54" s="6"/>
       <c r="R54" s="6"/>
@@ -4749,7 +4752,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B55" s="8">
         <v>46169.558586307874</v>
@@ -4761,7 +4764,7 @@
         <v>46198.597746307874</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>25</v>
@@ -4785,7 +4788,7 @@
         <v>26</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="P55" s="9" t="s">
         <v>26</v>
@@ -4802,7 +4805,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B56" s="5">
         <v>46169.55858945602</v>
@@ -4814,16 +4817,16 @@
         <v>46197.83559606482</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="I56" s="5">
         <v>46254</v>
@@ -4841,13 +4844,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="O56" s="6" t="s">
         <v>135</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q56" s="5">
         <v>46254</v>
@@ -4867,7 +4870,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B57" s="8">
         <v>46169.55859488426</v>
@@ -4879,7 +4882,7 @@
         <v>46197.85937331019</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
@@ -4906,13 +4909,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q57" s="8">
         <v>46258</v>
@@ -4932,7 +4935,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B58" s="5">
         <v>46169.55860118056</v>
@@ -4944,16 +4947,16 @@
         <v>46198.59771457176</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="I58" s="5">
         <v>46254</v>
@@ -4971,13 +4974,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="O58" s="6" t="s">
         <v>143</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q58" s="5">
         <v>46254</v>
@@ -4997,7 +5000,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B59" s="8">
         <v>46169.55860636574</v>
@@ -5009,7 +5012,7 @@
         <v>46198.597709444446</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
@@ -5036,10 +5039,10 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P59" s="9" t="s">
         <v>175</v>
@@ -5062,7 +5065,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B60" s="5">
         <v>46169.558650127314</v>
@@ -5074,16 +5077,16 @@
         <v>46198.59773310185</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="I60" s="5">
         <v>46254</v>
@@ -5101,13 +5104,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="O60" s="6" t="s">
         <v>165</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q60" s="5">
         <v>46254</v>
@@ -5127,7 +5130,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B61" s="8">
         <v>46169.55865608796</v>
@@ -5139,7 +5142,7 @@
         <v>46198.59773317129</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
@@ -5166,10 +5169,10 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P61" s="9" t="s">
         <v>175</v>
@@ -5192,7 +5195,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B62" s="5">
         <v>46169.55866105324</v>
@@ -5204,7 +5207,7 @@
         <v>46198.68229049769</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>25</v>
@@ -5228,7 +5231,7 @@
         <v>26</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="P62" s="6" t="s">
         <v>26</v>
@@ -5245,7 +5248,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B63" s="8">
         <v>46169.55866469907</v>
@@ -5257,16 +5260,16 @@
         <v>46225.86187357639</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="9" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H63" s="9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I63" s="8">
         <v>46260</v>
@@ -5284,13 +5287,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P63" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q63" s="8">
         <v>46260</v>
@@ -5310,7 +5313,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B64" s="5">
         <v>46169.55867099537</v>
@@ -5328,10 +5331,10 @@
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I64" s="5">
         <v>46260</v>
@@ -5349,13 +5352,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5365,7 +5368,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B65" s="8">
         <v>46169.558703518516</v>
@@ -5377,16 +5380,16 @@
         <v>46197.85387390046</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H65" s="9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I65" s="8">
         <v>46269</v>
@@ -5404,13 +5407,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O65" s="9" t="s">
         <v>175</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q65" s="8">
         <v>46269</v>
@@ -5430,7 +5433,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B66" s="5">
         <v>46169.55870879629</v>
@@ -5448,10 +5451,10 @@
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I66" s="5">
         <v>46269</v>
@@ -5469,13 +5472,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5485,7 +5488,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B67" s="8">
         <v>46169.558740625</v>
@@ -5497,7 +5500,7 @@
         <v>46205.65959174768</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
@@ -5524,13 +5527,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O67" s="9" t="s">
         <v>175</v>
       </c>
       <c r="P67" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q67" s="8">
         <v>46274</v>
@@ -5550,7 +5553,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B68" s="5">
         <v>46169.558745243055</v>
@@ -5589,13 +5592,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q68" s="6"/>
       <c r="R68" s="6"/>
@@ -5605,7 +5608,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B69" s="8">
         <v>46169.55876947917</v>
@@ -5617,7 +5620,7 @@
         <v>46211.70953918982</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>25</v>
@@ -5641,7 +5644,7 @@
         <v>26</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="P69" s="9" t="s">
         <v>26</v>
@@ -5654,7 +5657,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B70" s="5">
         <v>46169.55880633101</v>
@@ -5666,16 +5669,16 @@
         <v>46224.186405659726</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="I70" s="5">
         <v>46220</v>
@@ -5693,13 +5696,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="O70" s="6" t="s">
         <v>112</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q70" s="5">
         <v>46220</v>
@@ -5719,7 +5722,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B71" s="8">
         <v>46169.5588177662</v>
@@ -5731,16 +5734,16 @@
         <v>46200.819831597226</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H71" s="9" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="I71" s="8">
         <v>46325</v>
@@ -5758,13 +5761,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="O71" s="9" t="s">
         <v>102</v>
       </c>
       <c r="P71" s="9" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q71" s="8">
         <v>46325</v>
@@ -5784,7 +5787,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B72" s="5">
         <v>46169.55882295139</v>
@@ -5796,16 +5799,16 @@
         <v>46200.81928909722</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="I72" s="5">
         <v>46293</v>
@@ -5823,13 +5826,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="O72" s="6" t="s">
         <v>121</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q72" s="5">
         <v>46293</v>
@@ -5849,7 +5852,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B73" s="8">
         <v>46169.55882788195</v>
@@ -5861,16 +5864,16 @@
         <v>46211.7093043287</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H73" s="9" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="I73" s="8">
         <v>46282</v>
@@ -5888,13 +5891,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="O73" s="9" t="s">
         <v>153</v>
       </c>
       <c r="P73" s="9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q73" s="8">
         <v>46282</v>
@@ -5914,7 +5917,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B74" s="5">
         <v>46169.55884254629</v>
@@ -5926,7 +5929,7 @@
         <v>46211.86406403936</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>25</v>
@@ -5950,7 +5953,7 @@
         <v>26</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="P74" s="6" t="s">
         <v>26</v>
@@ -5967,7 +5970,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B75" s="8">
         <v>46169.55884548611</v>
@@ -5979,7 +5982,7 @@
         <v>46223.571425636575</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
@@ -6006,13 +6009,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q75" s="8">
         <v>46276</v>
@@ -6032,7 +6035,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B76" s="5">
         <v>46169.55884993056</v>
@@ -6071,13 +6074,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -6087,7 +6090,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B77" s="8">
         <v>46169.55893170139</v>
@@ -6099,7 +6102,7 @@
         <v>46223.57142202546</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>26</v>
@@ -6126,13 +6129,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O77" s="9" t="s">
         <v>175</v>
       </c>
       <c r="P77" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q77" s="8">
         <v>46296</v>
@@ -6152,7 +6155,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B78" s="5">
         <v>46169.55893543981</v>
@@ -6191,13 +6194,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q78" s="6"/>
       <c r="R78" s="6"/>
@@ -6207,7 +6210,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B79" s="8">
         <v>46169.558869560184</v>
@@ -6219,7 +6222,7 @@
         <v>46223.57141798611</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>26</v>
@@ -6246,13 +6249,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="P79" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q79" s="8">
         <v>46328</v>
@@ -6272,7 +6275,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B80" s="5">
         <v>46169.55887296297</v>
@@ -6284,7 +6287,7 @@
         <v>46223.57080435185</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
@@ -6311,13 +6314,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -6327,7 +6330,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B81" s="8">
         <v>46169.5589025463</v>
@@ -6339,7 +6342,7 @@
         <v>46223.57141431713</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
@@ -6366,13 +6369,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O81" s="9" t="s">
         <v>175</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q81" s="8">
         <v>46329</v>
@@ -6392,7 +6395,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B82" s="5">
         <v>46169.55890609954</v>
@@ -6431,13 +6434,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6447,7 +6450,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B83" s="8">
         <v>46169.55900443287</v>
@@ -6459,7 +6462,7 @@
         <v>46223.57141039352</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>26</v>
@@ -6486,13 +6489,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O83" s="9" t="s">
         <v>175</v>
       </c>
       <c r="P83" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q83" s="8">
         <v>46330</v>
@@ -6512,7 +6515,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B84" s="5">
         <v>46169.55901002315</v>
@@ -6551,13 +6554,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O84" s="6" t="s">
         <v>175</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q84" s="6"/>
       <c r="R84" s="6"/>
@@ -6567,7 +6570,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B85" s="8">
         <v>46169.55904462963</v>
@@ -6579,7 +6582,7 @@
         <v>46223.5714043287</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>26</v>
@@ -6606,13 +6609,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O85" s="9" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="P85" s="9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q85" s="8">
         <v>46332</v>
@@ -6632,7 +6635,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B86" s="5">
         <v>46169.559050138894</v>
@@ -6644,7 +6647,7 @@
         <v>46223.57102379629</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6671,13 +6674,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O86" s="6" t="s">
         <v>175</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6687,7 +6690,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B87" s="8">
         <v>46169.55907484954</v>
@@ -6697,7 +6700,7 @@
         <v>46211.8640300463</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>25</v>
@@ -6721,7 +6724,7 @@
         <v>26</v>
       </c>
       <c r="O87" s="9" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="P87" s="9" t="s">
         <v>26</v>
@@ -6736,7 +6739,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B88" s="5">
         <v>46169.55907863426</v>
@@ -6748,16 +6751,16 @@
         <v>46211.70008446759</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="I88" s="5">
         <v>46335</v>
@@ -6775,13 +6778,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q88" s="5">
         <v>46335</v>
@@ -6801,7 +6804,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B89" s="8">
         <v>46169.55908684028</v>
@@ -6819,10 +6822,10 @@
         <v>26</v>
       </c>
       <c r="G89" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H89" s="9" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="I89" s="8">
         <v>46335</v>
@@ -6840,13 +6843,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O89" s="9" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="P89" s="9" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q89" s="9"/>
       <c r="R89" s="9"/>
@@ -6856,7 +6859,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B90" s="5">
         <v>46169.55918673611</v>
@@ -6868,7 +6871,7 @@
         <v>46223.57153153935</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
@@ -6895,13 +6898,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O90" s="6" t="s">
         <v>175</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q90" s="5">
         <v>46336</v>
@@ -6921,7 +6924,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B91" s="8">
         <v>46169.55919113426</v>
@@ -6960,13 +6963,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="9" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="O91" s="9" t="s">
         <v>175</v>
       </c>
       <c r="P91" s="9" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q91" s="9"/>
       <c r="R91" s="9"/>
@@ -6976,7 +6979,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B92" s="5">
         <v>46169.559239560185</v>
@@ -6988,16 +6991,16 @@
         <v>46197.859819363424</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I92" s="5">
         <v>46337</v>
@@ -7015,13 +7018,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O92" s="6" t="s">
         <v>175</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q92" s="5">
         <v>46337</v>
@@ -7041,7 +7044,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B93" s="8">
         <v>46169.559243842596</v>
@@ -7059,10 +7062,10 @@
         <v>26</v>
       </c>
       <c r="G93" s="9" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H93" s="9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I93" s="8">
         <v>46337</v>
@@ -7080,13 +7083,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="9" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="O93" s="9" t="s">
         <v>175</v>
       </c>
       <c r="P93" s="9" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q93" s="9"/>
       <c r="R93" s="9"/>
@@ -7096,7 +7099,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B94" s="5">
         <v>46169.55929686343</v>
@@ -7108,16 +7111,16 @@
         <v>46211.86402001158</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I94" s="5">
         <v>46338</v>
@@ -7135,13 +7138,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O94" s="6" t="s">
         <v>175</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q94" s="5">
         <v>46338</v>
@@ -7161,7 +7164,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B95" s="8">
         <v>46169.55930180555</v>
@@ -7179,10 +7182,10 @@
         <v>26</v>
       </c>
       <c r="G95" s="9" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H95" s="9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I95" s="8">
         <v>46338</v>
@@ -7200,13 +7203,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="9" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="O95" s="9" t="s">
         <v>175</v>
       </c>
       <c r="P95" s="9" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q95" s="9"/>
       <c r="R95" s="9"/>
@@ -7216,7 +7219,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B96" s="5">
         <v>46169.55938721065</v>
@@ -7226,7 +7229,7 @@
         <v>46169.60672822916</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>25</v>
@@ -7250,7 +7253,7 @@
         <v>26</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="P96" s="6" t="s">
         <v>26</v>
@@ -7263,7 +7266,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B97" s="8">
         <v>46169.55939094907</v>
@@ -7273,16 +7276,16 @@
         <v>46211.86403020834</v>
       </c>
       <c r="E97" s="9" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G97" s="9" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H97" s="9" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="I97" s="8">
         <v>46339</v>
@@ -7300,13 +7303,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="9" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="O97" s="9" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="P97" s="9" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q97" s="8">
         <v>46339</v>
@@ -7326,7 +7329,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B98" s="5">
         <v>46169.55939643519</v>
@@ -7336,7 +7339,7 @@
         <v>46211.86403085648</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -7363,13 +7366,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q98" s="5">
         <v>46339</v>

--- a/data/50001557 - ATACAMA KOZAN OT4340.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4340.xlsx
@@ -777,7 +777,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t>OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
+    <t xml:space="preserve">OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A </t>
   </si>
   <si>
     <t>1215166433625244</t>
@@ -4521,7 +4521,7 @@
         <v>46182.75986146991</v>
       </c>
       <c r="D51" s="8">
-        <v>46182.759871076385</v>
+        <v>46231.1673975</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>78</v>
@@ -4565,8 +4565,8 @@
       <c r="R51" s="8">
         <v>46238</v>
       </c>
-      <c r="S51" s="10" t="s">
-        <v>32</v>
+      <c r="S51" s="12" t="s">
+        <v>182</v>
       </c>
       <c r="T51" s="9">
         <v>1</v>
@@ -5257,7 +5257,7 @@
         <v>46190.645243935185</v>
       </c>
       <c r="D63" s="8">
-        <v>46225.86187357639</v>
+        <v>46231.56038097222</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>218</v>

--- a/data/50001557 - ATACAMA KOZAN OT4340.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4340.xlsx
@@ -5257,7 +5257,7 @@
         <v>46190.645243935185</v>
       </c>
       <c r="D63" s="8">
-        <v>46231.56038097222</v>
+        <v>46231.65309684028</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>218</v>

--- a/data/50001557 - ATACAMA KOZAN OT4340.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4340.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1184" uniqueCount="310">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1185" uniqueCount="310">
   <si>
     <t xml:space="preserve"> 50001557 - ATACAMA KOZAN</t>
   </si>
@@ -777,7 +777,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t xml:space="preserve">OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A </t>
+    <t xml:space="preserve">OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A </t>
   </si>
   <si>
     <t>1215166433625244</t>
@@ -5257,7 +5257,7 @@
         <v>46190.645243935185</v>
       </c>
       <c r="D63" s="8">
-        <v>46231.65309684028</v>
+        <v>46232.83598179398</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>218</v>
@@ -6695,9 +6695,11 @@
       <c r="B87" s="8">
         <v>46169.55907484954</v>
       </c>
-      <c r="C87" s="9"/>
+      <c r="C87" s="8">
+        <v>46232.66291002315</v>
+      </c>
       <c r="D87" s="8">
-        <v>46211.8640300463</v>
+        <v>46232.66292771991</v>
       </c>
       <c r="E87" s="9" t="s">
         <v>281</v>
@@ -6732,9 +6734,11 @@
       <c r="Q87" s="9"/>
       <c r="R87" s="9"/>
       <c r="S87" s="9"/>
-      <c r="T87" s="9"/>
-      <c r="U87" s="12" t="s">
-        <v>170</v>
+      <c r="T87" s="9">
+        <v>1</v>
+      </c>
+      <c r="U87" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
@@ -7224,9 +7228,11 @@
       <c r="B96" s="5">
         <v>46169.55938721065</v>
       </c>
-      <c r="C96" s="6"/>
+      <c r="C96" s="5">
+        <v>46232.662946296296</v>
+      </c>
       <c r="D96" s="5">
-        <v>46169.60672822916</v>
+        <v>46232.662960601854</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>302</v>
@@ -7261,8 +7267,12 @@
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
       <c r="S96" s="6"/>
-      <c r="T96" s="6"/>
-      <c r="U96" s="6"/>
+      <c r="T96" s="6">
+        <v>1</v>
+      </c>
+      <c r="U96" s="10" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
@@ -7271,9 +7281,11 @@
       <c r="B97" s="8">
         <v>46169.55939094907</v>
       </c>
-      <c r="C97" s="9"/>
+      <c r="C97" s="8">
+        <v>46232.66292962963</v>
+      </c>
       <c r="D97" s="8">
-        <v>46211.86403020834</v>
+        <v>46232.66294618056</v>
       </c>
       <c r="E97" s="9" t="s">
         <v>305</v>
@@ -7321,10 +7333,10 @@
         <v>32</v>
       </c>
       <c r="T97" s="9">
-        <v>0</v>
-      </c>
-      <c r="U97" s="12" t="s">
-        <v>170</v>
+        <v>1</v>
+      </c>
+      <c r="U97" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
@@ -7334,9 +7346,11 @@
       <c r="B98" s="5">
         <v>46169.55939643519</v>
       </c>
-      <c r="C98" s="6"/>
+      <c r="C98" s="5">
+        <v>46232.662935636574</v>
+      </c>
       <c r="D98" s="5">
-        <v>46211.86403085648</v>
+        <v>46232.662950694445</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>309</v>
@@ -7384,10 +7398,10 @@
         <v>32</v>
       </c>
       <c r="T98" s="6">
-        <v>0</v>
-      </c>
-      <c r="U98" s="12" t="s">
-        <v>170</v>
+        <v>1</v>
+      </c>
+      <c r="U98" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001557 - ATACAMA KOZAN OT4340.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4340.xlsx
@@ -354,6 +354,9 @@
     <t>Propuesta compras:,Generación OC materiales corte Laser OT 4340</t>
   </si>
   <si>
+    <t>Media</t>
+  </si>
+  <si>
     <t>1215165982719434</t>
   </si>
   <si>
@@ -660,9 +663,6 @@
     <t>Planos definitivos</t>
   </si>
   <si>
-    <t>Media</t>
-  </si>
-  <si>
     <t>1215166041791446</t>
   </si>
   <si>
@@ -777,7 +777,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t xml:space="preserve">OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A </t>
+    <t>OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4</t>
   </si>
   <si>
     <t>1215166433625244</t>
@@ -1110,12 +1110,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFe8384f"/>
+        <fgColor rgb="FFeec300"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFeec300"/>
+        <fgColor rgb="FFe8384f"/>
       </patternFill>
     </fill>
   </fills>
@@ -2534,7 +2534,7 @@
         <v>46183.90663498842</v>
       </c>
       <c r="D18" s="5">
-        <v>46223.570560636574</v>
+        <v>46233.174886064815</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>77</v>
@@ -2578,8 +2578,8 @@
       <c r="R18" s="5">
         <v>46240</v>
       </c>
-      <c r="S18" s="10" t="s">
-        <v>32</v>
+      <c r="S18" s="11" t="s">
+        <v>80</v>
       </c>
       <c r="T18" s="6">
         <v>1</v>
@@ -2590,7 +2590,7 @@
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B19" s="8">
         <v>46169.55824171296</v>
@@ -2599,10 +2599,10 @@
         <v>46183.906646539355</v>
       </c>
       <c r="D19" s="8">
-        <v>46223.57055704861</v>
+        <v>46233.174886203706</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F19" s="9" t="s">
         <v>26</v>
@@ -2635,7 +2635,7 @@
         <v>78</v>
       </c>
       <c r="P19" s="9" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q19" s="8">
         <v>46239</v>
@@ -2643,8 +2643,8 @@
       <c r="R19" s="8">
         <v>46240</v>
       </c>
-      <c r="S19" s="10" t="s">
-        <v>32</v>
+      <c r="S19" s="11" t="s">
+        <v>80</v>
       </c>
       <c r="T19" s="9">
         <v>1</v>
@@ -2655,7 +2655,7 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B20" s="5">
         <v>46169.55824574074</v>
@@ -2664,10 +2664,10 @@
         <v>46190.644140034725</v>
       </c>
       <c r="D20" s="5">
-        <v>46223.57055334491</v>
+        <v>46233.174886168985</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
@@ -2700,7 +2700,7 @@
         <v>78</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="Q20" s="5">
         <v>46239</v>
@@ -2708,8 +2708,8 @@
       <c r="R20" s="5">
         <v>46240</v>
       </c>
-      <c r="S20" s="10" t="s">
-        <v>32</v>
+      <c r="S20" s="11" t="s">
+        <v>80</v>
       </c>
       <c r="T20" s="6">
         <v>1</v>
@@ -2720,7 +2720,7 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B21" s="8">
         <v>46169.55825006944</v>
@@ -2729,10 +2729,10 @@
         <v>46183.90733957176</v>
       </c>
       <c r="D21" s="8">
-        <v>46223.570547662035</v>
+        <v>46233.174886504625</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F21" s="9" t="s">
         <v>26</v>
@@ -2765,7 +2765,7 @@
         <v>78</v>
       </c>
       <c r="P21" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="Q21" s="8">
         <v>46239</v>
@@ -2773,8 +2773,8 @@
       <c r="R21" s="8">
         <v>46240</v>
       </c>
-      <c r="S21" s="10" t="s">
-        <v>32</v>
+      <c r="S21" s="11" t="s">
+        <v>80</v>
       </c>
       <c r="T21" s="9">
         <v>1</v>
@@ -2785,7 +2785,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B22" s="5">
         <v>46169.55801826389</v>
@@ -2797,7 +2797,7 @@
         <v>46200.818425798614</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>25</v>
@@ -2821,7 +2821,7 @@
         <v>26</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="P22" s="6" t="s">
         <v>26</v>
@@ -2834,7 +2834,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B23" s="8">
         <v>46169.558301956014</v>
@@ -2846,16 +2846,16 @@
         <v>46200.81833380787</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I23" s="8">
         <v>46169</v>
@@ -2873,13 +2873,13 @@
         <v>26</v>
       </c>
       <c r="N23" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O23" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="P23" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="Q23" s="8">
         <v>46169</v>
@@ -2899,7 +2899,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B24" s="5">
         <v>46169.558306516206</v>
@@ -2911,16 +2911,16 @@
         <v>46195.69079224537</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I24" s="5">
         <v>46169</v>
@@ -2938,13 +2938,13 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="O24" s="6" t="s">
         <v>69</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="Q24" s="6"/>
       <c r="R24" s="6"/>
@@ -2954,13 +2954,13 @@
       <c r="T24" s="6">
         <v>0</v>
       </c>
-      <c r="U24" s="11" t="s">
-        <v>100</v>
+      <c r="U24" s="12" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B25" s="8">
         <v>46169.55831137732</v>
@@ -2972,16 +2972,16 @@
         <v>46195.690800474535</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I25" s="8">
         <v>46171</v>
@@ -2999,13 +2999,13 @@
         <v>26</v>
       </c>
       <c r="N25" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="O25" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="P25" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Q25" s="9"/>
       <c r="R25" s="9"/>
@@ -3015,13 +3015,13 @@
       <c r="T25" s="9">
         <v>0</v>
       </c>
-      <c r="U25" s="11" t="s">
-        <v>100</v>
+      <c r="U25" s="12" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B26" s="5">
         <v>46169.55831605324</v>
@@ -3033,16 +3033,16 @@
         <v>46220.171629351855</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I26" s="5">
         <v>46169</v>
@@ -3060,13 +3060,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="Q26" s="5">
         <v>46169</v>
@@ -3074,8 +3074,8 @@
       <c r="R26" s="5">
         <v>46219</v>
       </c>
-      <c r="S26" s="11" t="s">
-        <v>107</v>
+      <c r="S26" s="12" t="s">
+        <v>108</v>
       </c>
       <c r="T26" s="6">
         <v>1</v>
@@ -3086,7 +3086,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B27" s="8">
         <v>46169.55832063657</v>
@@ -3098,16 +3098,16 @@
         <v>46184.7364097338</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I27" s="8">
         <v>46169</v>
@@ -3125,13 +3125,13 @@
         <v>26</v>
       </c>
       <c r="N27" s="9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O27" s="9" t="s">
         <v>72</v>
       </c>
       <c r="P27" s="9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Q27" s="9"/>
       <c r="R27" s="9"/>
@@ -3141,13 +3141,13 @@
       <c r="T27" s="9">
         <v>0</v>
       </c>
-      <c r="U27" s="11" t="s">
-        <v>100</v>
+      <c r="U27" s="12" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B28" s="5">
         <v>46169.55832539352</v>
@@ -3159,16 +3159,16 @@
         <v>46184.736449375</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I28" s="5">
         <v>46171</v>
@@ -3186,13 +3186,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
@@ -3202,13 +3202,13 @@
       <c r="T28" s="6">
         <v>0</v>
       </c>
-      <c r="U28" s="11" t="s">
-        <v>100</v>
+      <c r="U28" s="12" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B29" s="8">
         <v>46169.55833006944</v>
@@ -3220,16 +3220,16 @@
         <v>46200.81836952546</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I29" s="8">
         <v>46161</v>
@@ -3247,13 +3247,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O29" s="9" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="P29" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="Q29" s="8">
         <v>46161</v>
@@ -3273,7 +3273,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B30" s="5">
         <v>46169.55833486111</v>
@@ -3285,16 +3285,16 @@
         <v>46195.69066259259</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I30" s="5">
         <v>46161</v>
@@ -3312,13 +3312,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="O30" s="6" t="s">
         <v>66</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -3328,13 +3328,13 @@
       <c r="T30" s="6">
         <v>0</v>
       </c>
-      <c r="U30" s="11" t="s">
-        <v>100</v>
+      <c r="U30" s="12" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B31" s="8">
         <v>46169.5583402662</v>
@@ -3346,16 +3346,16 @@
         <v>46195.69066760417</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I31" s="8">
         <v>46178</v>
@@ -3373,13 +3373,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="O31" s="9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="P31" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="Q31" s="9"/>
       <c r="R31" s="9"/>
@@ -3389,13 +3389,13 @@
       <c r="T31" s="9">
         <v>0</v>
       </c>
-      <c r="U31" s="11" t="s">
-        <v>100</v>
+      <c r="U31" s="12" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B32" s="5">
         <v>46169.55834503472</v>
@@ -3407,16 +3407,16 @@
         <v>46195.6906680324</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I32" s="5">
         <v>46178</v>
@@ -3434,13 +3434,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
@@ -3450,13 +3450,13 @@
       <c r="T32" s="6">
         <v>0</v>
       </c>
-      <c r="U32" s="11" t="s">
-        <v>100</v>
+      <c r="U32" s="12" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B33" s="8">
         <v>46169.55836335648</v>
@@ -3468,16 +3468,16 @@
         <v>46184.532641875005</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I33" s="8">
         <v>46241</v>
@@ -3495,13 +3495,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="Q33" s="8">
         <v>46241</v>
@@ -3521,7 +3521,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B34" s="5">
         <v>46169.558367986116</v>
@@ -3533,16 +3533,16 @@
         <v>46184.53245875</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I34" s="5">
         <v>46241</v>
@@ -3560,13 +3560,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O34" s="6" t="s">
         <v>77</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3576,13 +3576,13 @@
       <c r="T34" s="6">
         <v>0</v>
       </c>
-      <c r="U34" s="11" t="s">
-        <v>100</v>
+      <c r="U34" s="12" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B35" s="8">
         <v>46169.55837292824</v>
@@ -3594,16 +3594,16 @@
         <v>46184.532615856486</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I35" s="8">
         <v>46245</v>
@@ -3621,13 +3621,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="P35" s="9" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="Q35" s="9"/>
       <c r="R35" s="9"/>
@@ -3637,13 +3637,13 @@
       <c r="T35" s="9">
         <v>0</v>
       </c>
-      <c r="U35" s="11" t="s">
-        <v>100</v>
+      <c r="U35" s="12" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B36" s="5">
         <v>46169.55837825232</v>
@@ -3655,16 +3655,16 @@
         <v>46184.53258194444</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I36" s="5">
         <v>46241</v>
@@ -3682,10 +3682,10 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P36" s="6" t="s">
         <v>26</v>
@@ -3708,7 +3708,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B37" s="8">
         <v>46169.558381979165</v>
@@ -3720,16 +3720,16 @@
         <v>46184.5322071875</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I37" s="8">
         <v>46241</v>
@@ -3747,13 +3747,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="Q37" s="9"/>
       <c r="R37" s="9"/>
@@ -3763,7 +3763,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B38" s="5">
         <v>46169.55838657408</v>
@@ -3775,16 +3775,16 @@
         <v>46184.53255631945</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I38" s="5">
         <v>46245</v>
@@ -3802,13 +3802,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -3818,7 +3818,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B39" s="8">
         <v>46169.55839107639</v>
@@ -3830,16 +3830,16 @@
         <v>46205.600326053245</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I39" s="8">
         <v>46241</v>
@@ -3857,10 +3857,10 @@
         <v>26</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P39" s="9" t="s">
         <v>26</v>
@@ -3883,7 +3883,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B40" s="5">
         <v>46169.55839478009</v>
@@ -3895,16 +3895,16 @@
         <v>46195.70360162037</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I40" s="5">
         <v>46241</v>
@@ -3922,13 +3922,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -3938,7 +3938,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B41" s="8">
         <v>46169.55839910879</v>
@@ -3950,16 +3950,16 @@
         <v>46195.70375376157</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I41" s="8">
         <v>46252</v>
@@ -3977,13 +3977,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q41" s="9"/>
       <c r="R41" s="9"/>
@@ -3993,7 +3993,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B42" s="5">
         <v>46169.55840355324</v>
@@ -4005,16 +4005,16 @@
         <v>46205.59994755787</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I42" s="5">
         <v>46281</v>
@@ -4032,10 +4032,10 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>26</v>
@@ -4048,7 +4048,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B43" s="8">
         <v>46169.55840677083</v>
@@ -4060,16 +4060,16 @@
         <v>46191.53701371528</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I43" s="8">
         <v>46241</v>
@@ -4087,10 +4087,10 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="P43" s="9" t="s">
         <v>26</v>
@@ -4113,7 +4113,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B44" s="5">
         <v>46169.55841037037</v>
@@ -4125,16 +4125,16 @@
         <v>46191.53679194444</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I44" s="5">
         <v>46241</v>
@@ -4152,13 +4152,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4168,7 +4168,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B45" s="8">
         <v>46169.558458217594</v>
@@ -4180,16 +4180,16 @@
         <v>46191.53698841435</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I45" s="8">
         <v>46245</v>
@@ -4207,13 +4207,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="P45" s="9" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q45" s="9"/>
       <c r="R45" s="9"/>
@@ -4223,7 +4223,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B46" s="5">
         <v>46169.5584643287</v>
@@ -4233,7 +4233,7 @@
         <v>46182.75962331019</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>25</v>
@@ -4257,7 +4257,7 @@
         <v>26</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4266,13 +4266,13 @@
       <c r="R46" s="6"/>
       <c r="S46" s="6"/>
       <c r="T46" s="6"/>
-      <c r="U46" s="12" t="s">
-        <v>170</v>
+      <c r="U46" s="11" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B47" s="8">
         <v>46169.55846813657</v>
@@ -4284,16 +4284,16 @@
         <v>46197.715420312496</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I47" s="8">
         <v>46167</v>
@@ -4311,13 +4311,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q47" s="8">
         <v>46167</v>
@@ -4325,8 +4325,8 @@
       <c r="R47" s="8">
         <v>46184</v>
       </c>
-      <c r="S47" s="11" t="s">
-        <v>107</v>
+      <c r="S47" s="12" t="s">
+        <v>108</v>
       </c>
       <c r="T47" s="9">
         <v>1</v>
@@ -4337,7 +4337,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B48" s="5">
         <v>46169.558472766206</v>
@@ -4349,16 +4349,16 @@
         <v>46181.72663056713</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I48" s="5">
         <v>46167</v>
@@ -4376,13 +4376,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="O48" s="6" t="s">
         <v>60</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q48" s="6"/>
       <c r="R48" s="6"/>
@@ -4392,7 +4392,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B49" s="8">
         <v>46169.55849938658</v>
@@ -4404,16 +4404,16 @@
         <v>46230.196269340275</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I49" s="8">
         <v>46218</v>
@@ -4431,13 +4431,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q49" s="8">
         <v>46218</v>
@@ -4445,8 +4445,8 @@
       <c r="R49" s="8">
         <v>46237</v>
       </c>
-      <c r="S49" s="12" t="s">
-        <v>182</v>
+      <c r="S49" s="11" t="s">
+        <v>80</v>
       </c>
       <c r="T49" s="9">
         <v>1</v>
@@ -4469,16 +4469,16 @@
         <v>46195.690583055555</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I50" s="5">
         <v>46218</v>
@@ -4496,7 +4496,7 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="O50" s="6" t="s">
         <v>184</v>
@@ -4530,10 +4530,10 @@
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I51" s="8">
         <v>46238</v>
@@ -4551,10 +4551,10 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P51" s="9" t="s">
         <v>187</v>
@@ -4565,8 +4565,8 @@
       <c r="R51" s="8">
         <v>46238</v>
       </c>
-      <c r="S51" s="12" t="s">
-        <v>182</v>
+      <c r="S51" s="11" t="s">
+        <v>80</v>
       </c>
       <c r="T51" s="9">
         <v>1</v>
@@ -4589,16 +4589,16 @@
         <v>46182.75984881945</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I52" s="5">
         <v>46238</v>
@@ -4619,7 +4619,7 @@
         <v>78</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P52" s="6" t="s">
         <v>78</v>
@@ -4671,10 +4671,10 @@
         <v>26</v>
       </c>
       <c r="N53" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P53" s="9" t="s">
         <v>26</v>
@@ -4709,7 +4709,7 @@
         <v>46211.86419394676</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
@@ -4739,7 +4739,7 @@
         <v>190</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P54" s="6" t="s">
         <v>194</v>
@@ -4847,7 +4847,7 @@
         <v>196</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P56" s="6" t="s">
         <v>202</v>
@@ -4888,10 +4888,10 @@
         <v>26</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I57" s="8">
         <v>46258</v>
@@ -4977,7 +4977,7 @@
         <v>196</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="P58" s="6" t="s">
         <v>208</v>
@@ -5018,10 +5018,10 @@
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I59" s="8">
         <v>46258</v>
@@ -5045,7 +5045,7 @@
         <v>207</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q59" s="8">
         <v>46258</v>
@@ -5059,8 +5059,8 @@
       <c r="T59" s="9">
         <v>1</v>
       </c>
-      <c r="U59" s="12" t="s">
-        <v>170</v>
+      <c r="U59" s="11" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
@@ -5107,7 +5107,7 @@
         <v>196</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="P60" s="6" t="s">
         <v>212</v>
@@ -5148,10 +5148,10 @@
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I61" s="8">
         <v>46258</v>
@@ -5175,7 +5175,7 @@
         <v>211</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q61" s="8">
         <v>46258</v>
@@ -5189,8 +5189,8 @@
       <c r="T61" s="9">
         <v>1</v>
       </c>
-      <c r="U61" s="12" t="s">
-        <v>170</v>
+      <c r="U61" s="11" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
@@ -5325,7 +5325,7 @@
         <v>46197.85936673611</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
@@ -5410,7 +5410,7 @@
         <v>215</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P65" s="9" t="s">
         <v>215</v>
@@ -5427,8 +5427,8 @@
       <c r="T65" s="9">
         <v>1</v>
       </c>
-      <c r="U65" s="12" t="s">
-        <v>170</v>
+      <c r="U65" s="11" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
@@ -5445,7 +5445,7 @@
         <v>46197.85915420139</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
@@ -5506,10 +5506,10 @@
         <v>26</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H67" s="9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I67" s="8">
         <v>46274</v>
@@ -5530,7 +5530,7 @@
         <v>215</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P67" s="9" t="s">
         <v>215</v>
@@ -5547,8 +5547,8 @@
       <c r="T67" s="9">
         <v>1</v>
       </c>
-      <c r="U67" s="12" t="s">
-        <v>170</v>
+      <c r="U67" s="11" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
@@ -5565,16 +5565,16 @@
         <v>46205.659588587965</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I68" s="5">
         <v>46274</v>
@@ -5699,7 +5699,7 @@
         <v>196</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>238</v>
@@ -5710,8 +5710,8 @@
       <c r="R70" s="5">
         <v>46223</v>
       </c>
-      <c r="S70" s="11" t="s">
-        <v>107</v>
+      <c r="S70" s="12" t="s">
+        <v>108</v>
       </c>
       <c r="T70" s="6">
         <v>1</v>
@@ -5764,7 +5764,7 @@
         <v>196</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="P71" s="9" t="s">
         <v>241</v>
@@ -5775,8 +5775,8 @@
       <c r="R71" s="8">
         <v>46325</v>
       </c>
-      <c r="S71" s="11" t="s">
-        <v>107</v>
+      <c r="S71" s="12" t="s">
+        <v>108</v>
       </c>
       <c r="T71" s="9">
         <v>1</v>
@@ -5829,7 +5829,7 @@
         <v>196</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="P72" s="6" t="s">
         <v>205</v>
@@ -5894,7 +5894,7 @@
         <v>196</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="P73" s="9" t="s">
         <v>246</v>
@@ -6029,8 +6029,8 @@
       <c r="T75" s="9">
         <v>1</v>
       </c>
-      <c r="U75" s="12" t="s">
-        <v>170</v>
+      <c r="U75" s="11" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
@@ -6047,7 +6047,7 @@
         <v>46223.57064498843</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
@@ -6132,7 +6132,7 @@
         <v>248</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P77" s="9" t="s">
         <v>248</v>
@@ -6167,7 +6167,7 @@
         <v>46223.57074214121</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
@@ -6372,7 +6372,7 @@
         <v>248</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P81" s="9" t="s">
         <v>248</v>
@@ -6407,7 +6407,7 @@
         <v>46223.835960763885</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
@@ -6492,7 +6492,7 @@
         <v>248</v>
       </c>
       <c r="O83" s="9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P83" s="9" t="s">
         <v>248</v>
@@ -6527,7 +6527,7 @@
         <v>46223.57092783565</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
@@ -6557,7 +6557,7 @@
         <v>272</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P84" s="6" t="s">
         <v>274</v>
@@ -6677,7 +6677,7 @@
         <v>276</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P86" s="6" t="s">
         <v>279</v>
@@ -6820,7 +6820,7 @@
         <v>46211.700054201385</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>26</v>
@@ -6905,7 +6905,7 @@
         <v>281</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P90" s="6" t="s">
         <v>281</v>
@@ -6940,7 +6940,7 @@
         <v>46223.57147459491</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>26</v>
@@ -6970,7 +6970,7 @@
         <v>290</v>
       </c>
       <c r="O91" s="9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P91" s="9" t="s">
         <v>292</v>
@@ -7025,7 +7025,7 @@
         <v>281</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P92" s="6" t="s">
         <v>281</v>
@@ -7042,8 +7042,8 @@
       <c r="T92" s="6">
         <v>1</v>
       </c>
-      <c r="U92" s="12" t="s">
-        <v>170</v>
+      <c r="U92" s="11" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
@@ -7060,7 +7060,7 @@
         <v>46211.830942650464</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>26</v>
@@ -7090,7 +7090,7 @@
         <v>294</v>
       </c>
       <c r="O93" s="9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P93" s="9" t="s">
         <v>296</v>
@@ -7145,7 +7145,7 @@
         <v>281</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P94" s="6" t="s">
         <v>299</v>
@@ -7180,7 +7180,7 @@
         <v>46211.863992280094</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>26</v>
@@ -7210,7 +7210,7 @@
         <v>298</v>
       </c>
       <c r="O95" s="9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P95" s="9" t="s">
         <v>298</v>

--- a/data/50001557 - ATACAMA KOZAN OT4340.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4340.xlsx
@@ -5257,7 +5257,7 @@
         <v>46190.645243935185</v>
       </c>
       <c r="D63" s="8">
-        <v>46232.83598179398</v>
+        <v>46233.64825958334</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>218</v>

--- a/data/50001557 - ATACAMA KOZAN OT4340.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4340.xlsx
@@ -777,7 +777,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t>OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4</t>
+    <t>OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ</t>
   </si>
   <si>
     <t>1215166433625244</t>
@@ -5257,7 +5257,7 @@
         <v>46190.645243935185</v>
       </c>
       <c r="D63" s="8">
-        <v>46233.64825958334</v>
+        <v>46237.570505972224</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>218</v>

--- a/data/50001557 - ATACAMA KOZAN OT4340.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4340.xlsx
@@ -5257,7 +5257,7 @@
         <v>46190.645243935185</v>
       </c>
       <c r="D63" s="8">
-        <v>46237.570505972224</v>
+        <v>46237.81015826389</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>218</v>

--- a/data/50001557 - ATACAMA KOZAN OT4340.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4340.xlsx
@@ -4401,7 +4401,7 @@
         <v>46182.759602164355</v>
       </c>
       <c r="D49" s="8">
-        <v>46230.196269340275</v>
+        <v>46238.18899571759</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>182</v>
@@ -4445,8 +4445,8 @@
       <c r="R49" s="8">
         <v>46237</v>
       </c>
-      <c r="S49" s="11" t="s">
-        <v>80</v>
+      <c r="S49" s="12" t="s">
+        <v>108</v>
       </c>
       <c r="T49" s="9">
         <v>1</v>

--- a/data/50001557 - ATACAMA KOZAN OT4340.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4340.xlsx
@@ -777,7 +777,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t>OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ</t>
+    <t>OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4394 -ZVN 1-9-86/2 + TOB + REJ</t>
   </si>
   <si>
     <t>1215166433625244</t>
@@ -4521,7 +4521,7 @@
         <v>46182.75986146991</v>
       </c>
       <c r="D51" s="8">
-        <v>46231.1673975</v>
+        <v>46239.20354527778</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>78</v>
@@ -4565,8 +4565,8 @@
       <c r="R51" s="8">
         <v>46238</v>
       </c>
-      <c r="S51" s="11" t="s">
-        <v>80</v>
+      <c r="S51" s="12" t="s">
+        <v>108</v>
       </c>
       <c r="T51" s="9">
         <v>1</v>
@@ -5257,7 +5257,7 @@
         <v>46190.645243935185</v>
       </c>
       <c r="D63" s="8">
-        <v>46237.81015826389</v>
+        <v>46239.57423652778</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>218</v>

--- a/data/50001557 - ATACAMA KOZAN OT4340.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4340.xlsx
@@ -777,7 +777,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t>OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4394 -ZVN 1-9-86/2 + TOB + REJ</t>
+    <t>OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200</t>
   </si>
   <si>
     <t>1215166433625244</t>

--- a/data/50001557 - ATACAMA KOZAN OT4340.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4340.xlsx
@@ -5257,7 +5257,7 @@
         <v>46190.645243935185</v>
       </c>
       <c r="D63" s="8">
-        <v>46239.57423652778</v>
+        <v>46240.5827003125</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>218</v>

--- a/data/50001557 - ATACAMA KOZAN OT4340.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4340.xlsx
@@ -627,121 +627,121 @@
     <t>Planos definitivos,Planos preliminar</t>
   </si>
   <si>
+    <t>1215166243396290</t>
+  </si>
+  <si>
+    <t>Planos preliminar</t>
+  </si>
+  <si>
+    <t>Gonzalo Javier Dávila Bade</t>
+  </si>
+  <si>
+    <t>gonzalo.davila@zitron.com</t>
+  </si>
+  <si>
+    <t>OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR</t>
+  </si>
+  <si>
+    <t>1215166433496869</t>
+  </si>
+  <si>
+    <t>Hernan Roberto Gutierrez Barrientos</t>
+  </si>
+  <si>
+    <t>hgutierrez@zitron.com</t>
+  </si>
+  <si>
+    <t>OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR,Planos preliminar</t>
+  </si>
+  <si>
+    <t>1215166041791429</t>
+  </si>
+  <si>
+    <t>Planos definitivos</t>
+  </si>
+  <si>
+    <t>1215166041791446</t>
+  </si>
+  <si>
+    <t>OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR,Planos motor proveedor OT 4340</t>
+  </si>
+  <si>
+    <t>Planos definitivos,OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR</t>
+  </si>
+  <si>
+    <t>1215165982964919</t>
+  </si>
+  <si>
+    <t>Propuesta Mecanizado OT 4340,Propuesta Fabricación externa  OT 4340,propuesta Corte Laser OT 4340,Propuesta Corte plasma  OT 4340,OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR,OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR,OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR</t>
+  </si>
+  <si>
+    <t>1215166243476961</t>
+  </si>
+  <si>
+    <t>1215165982983044</t>
+  </si>
+  <si>
+    <t>check pruebas FAT</t>
+  </si>
+  <si>
+    <t>Francisca González Cornejo</t>
+  </si>
+  <si>
+    <t>francisca.gonzalez@zitron.com</t>
+  </si>
+  <si>
+    <t>1215165982983056</t>
+  </si>
+  <si>
+    <t>check pruebas FAT,OT 4335 - ZVN 1-7-37/2 + TOB + REJ</t>
+  </si>
+  <si>
+    <t>1215165983005052</t>
+  </si>
+  <si>
+    <t>Bodega:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recepcion materiales corte laser,Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>1215165983005064</t>
+  </si>
+  <si>
+    <t>Recepcion materiales corte laser</t>
+  </si>
+  <si>
+    <t>Victor Muñoz</t>
+  </si>
+  <si>
+    <t>victor.munoz@zitron.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bodega:,Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>1215166329404944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>Bodega:,OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR</t>
+  </si>
+  <si>
+    <t>1215166041891869</t>
+  </si>
+  <si>
+    <t>Recepcion Materiales corte plasma</t>
+  </si>
+  <si>
+    <t>Control de calidad Corte plasma</t>
+  </si>
+  <si>
+    <t>1215166041891891</t>
+  </si>
+  <si>
     <t>Tarea en curso</t>
-  </si>
-  <si>
-    <t>1215166243396290</t>
-  </si>
-  <si>
-    <t>Planos preliminar</t>
-  </si>
-  <si>
-    <t>Gonzalo Javier Dávila Bade</t>
-  </si>
-  <si>
-    <t>gonzalo.davila@zitron.com</t>
-  </si>
-  <si>
-    <t>OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR</t>
-  </si>
-  <si>
-    <t>1215166433496869</t>
-  </si>
-  <si>
-    <t>Hernan Roberto Gutierrez Barrientos</t>
-  </si>
-  <si>
-    <t>hgutierrez@zitron.com</t>
-  </si>
-  <si>
-    <t>OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR,Planos preliminar</t>
-  </si>
-  <si>
-    <t>1215166041791429</t>
-  </si>
-  <si>
-    <t>Planos definitivos</t>
-  </si>
-  <si>
-    <t>1215166041791446</t>
-  </si>
-  <si>
-    <t>OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR,Planos motor proveedor OT 4340</t>
-  </si>
-  <si>
-    <t>Planos definitivos,OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR</t>
-  </si>
-  <si>
-    <t>1215165982964919</t>
-  </si>
-  <si>
-    <t>Propuesta Mecanizado OT 4340,Propuesta Fabricación externa  OT 4340,propuesta Corte Laser OT 4340,Propuesta Corte plasma  OT 4340,OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR,OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR,OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR</t>
-  </si>
-  <si>
-    <t>1215166243476961</t>
-  </si>
-  <si>
-    <t>1215165982983044</t>
-  </si>
-  <si>
-    <t>check pruebas FAT</t>
-  </si>
-  <si>
-    <t>Francisca González Cornejo</t>
-  </si>
-  <si>
-    <t>francisca.gonzalez@zitron.com</t>
-  </si>
-  <si>
-    <t>1215165982983056</t>
-  </si>
-  <si>
-    <t>check pruebas FAT,OT 4335 - ZVN 1-7-37/2 + TOB + REJ</t>
-  </si>
-  <si>
-    <t>1215165983005052</t>
-  </si>
-  <si>
-    <t>Bodega:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recepcion materiales corte laser,Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>1215165983005064</t>
-  </si>
-  <si>
-    <t>Recepcion materiales corte laser</t>
-  </si>
-  <si>
-    <t>Victor Muñoz</t>
-  </si>
-  <si>
-    <t>victor.munoz@zitron.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bodega:,Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>1215166329404944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>Bodega:,OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR</t>
-  </si>
-  <si>
-    <t>1215166041891869</t>
-  </si>
-  <si>
-    <t>Recepcion Materiales corte plasma</t>
-  </si>
-  <si>
-    <t>Control de calidad Corte plasma</t>
-  </si>
-  <si>
-    <t>1215166041891891</t>
   </si>
   <si>
     <t>1215165982799201</t>
@@ -4228,9 +4228,11 @@
       <c r="B46" s="5">
         <v>46169.5584643287</v>
       </c>
-      <c r="C46" s="6"/>
+      <c r="C46" s="5">
+        <v>46240.71635880787</v>
+      </c>
       <c r="D46" s="5">
-        <v>46182.75962331019</v>
+        <v>46240.716379722224</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>169</v>
@@ -4265,14 +4267,16 @@
       <c r="Q46" s="6"/>
       <c r="R46" s="6"/>
       <c r="S46" s="6"/>
-      <c r="T46" s="6"/>
-      <c r="U46" s="11" t="s">
-        <v>171</v>
+      <c r="T46" s="6">
+        <v>1</v>
+      </c>
+      <c r="U46" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B47" s="8">
         <v>46169.55846813657</v>
@@ -4284,16 +4288,16 @@
         <v>46197.715420312496</v>
       </c>
       <c r="E47" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="F47" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G47" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="F47" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G47" s="9" t="s">
+      <c r="H47" s="9" t="s">
         <v>174</v>
-      </c>
-      <c r="H47" s="9" t="s">
-        <v>175</v>
       </c>
       <c r="I47" s="8">
         <v>46167</v>
@@ -4314,7 +4318,7 @@
         <v>169</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="P47" s="9" t="s">
         <v>169</v>
@@ -4337,7 +4341,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B48" s="5">
         <v>46169.558472766206</v>
@@ -4349,16 +4353,16 @@
         <v>46181.72663056713</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="H48" s="6" t="s">
         <v>178</v>
-      </c>
-      <c r="H48" s="6" t="s">
-        <v>179</v>
       </c>
       <c r="I48" s="5">
         <v>46167</v>
@@ -4376,13 +4380,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="O48" s="6" t="s">
         <v>60</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q48" s="6"/>
       <c r="R48" s="6"/>
@@ -4392,7 +4396,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B49" s="8">
         <v>46169.55849938658</v>
@@ -4404,16 +4408,16 @@
         <v>46238.18899571759</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="H49" s="9" t="s">
         <v>174</v>
-      </c>
-      <c r="H49" s="9" t="s">
-        <v>175</v>
       </c>
       <c r="I49" s="8">
         <v>46218</v>
@@ -4434,7 +4438,7 @@
         <v>169</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="P49" s="9" t="s">
         <v>169</v>
@@ -4457,7 +4461,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B50" s="5">
         <v>46169.55850371528</v>
@@ -4469,16 +4473,16 @@
         <v>46195.690583055555</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="H50" s="6" t="s">
         <v>178</v>
-      </c>
-      <c r="H50" s="6" t="s">
-        <v>179</v>
       </c>
       <c r="I50" s="5">
         <v>46218</v>
@@ -4496,13 +4500,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="O50" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="P50" s="6" t="s">
         <v>184</v>
-      </c>
-      <c r="P50" s="6" t="s">
-        <v>185</v>
       </c>
       <c r="Q50" s="6"/>
       <c r="R50" s="6"/>
@@ -4512,7 +4516,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B51" s="8">
         <v>46169.55853228009</v>
@@ -4530,10 +4534,10 @@
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="H51" s="9" t="s">
         <v>178</v>
-      </c>
-      <c r="H51" s="9" t="s">
-        <v>179</v>
       </c>
       <c r="I51" s="8">
         <v>46238</v>
@@ -4554,10 +4558,10 @@
         <v>169</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="Q51" s="8">
         <v>46238</v>
@@ -4577,7 +4581,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B52" s="5">
         <v>46169.55854641204</v>
@@ -4589,16 +4593,16 @@
         <v>46182.75984881945</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="H52" s="6" t="s">
         <v>178</v>
-      </c>
-      <c r="H52" s="6" t="s">
-        <v>179</v>
       </c>
       <c r="I52" s="5">
         <v>46238</v>
@@ -4619,7 +4623,7 @@
         <v>78</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="P52" s="6" t="s">
         <v>78</v>
@@ -4632,7 +4636,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B53" s="8">
         <v>46169.558565775464</v>
@@ -4644,16 +4648,16 @@
         <v>46211.86422231482</v>
       </c>
       <c r="E53" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="F53" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G53" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="F53" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G53" s="9" t="s">
+      <c r="H53" s="9" t="s">
         <v>191</v>
-      </c>
-      <c r="H53" s="9" t="s">
-        <v>192</v>
       </c>
       <c r="I53" s="8">
         <v>46331</v>
@@ -4674,7 +4678,7 @@
         <v>169</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="P53" s="9" t="s">
         <v>26</v>
@@ -4697,7 +4701,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B54" s="5">
         <v>46169.55856972223</v>
@@ -4709,16 +4713,16 @@
         <v>46211.86419394676</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="H54" s="6" t="s">
         <v>191</v>
-      </c>
-      <c r="H54" s="6" t="s">
-        <v>192</v>
       </c>
       <c r="I54" s="5">
         <v>46331</v>
@@ -4736,13 +4740,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="Q54" s="6"/>
       <c r="R54" s="6"/>
@@ -4752,7 +4756,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B55" s="8">
         <v>46169.558586307874</v>
@@ -4764,7 +4768,7 @@
         <v>46198.597746307874</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>25</v>
@@ -4788,7 +4792,7 @@
         <v>26</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P55" s="9" t="s">
         <v>26</v>
@@ -4805,7 +4809,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B56" s="5">
         <v>46169.55858945602</v>
@@ -4817,16 +4821,16 @@
         <v>46197.83559606482</v>
       </c>
       <c r="E56" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="F56" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G56" s="6" t="s">
         <v>199</v>
       </c>
-      <c r="F56" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G56" s="6" t="s">
+      <c r="H56" s="6" t="s">
         <v>200</v>
-      </c>
-      <c r="H56" s="6" t="s">
-        <v>201</v>
       </c>
       <c r="I56" s="5">
         <v>46254</v>
@@ -4844,13 +4848,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="O56" s="6" t="s">
         <v>136</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="Q56" s="5">
         <v>46254</v>
@@ -4870,7 +4874,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B57" s="8">
         <v>46169.55859488426</v>
@@ -4882,7 +4886,7 @@
         <v>46197.85937331019</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
@@ -4909,13 +4913,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="Q57" s="8">
         <v>46258</v>
@@ -4935,7 +4939,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B58" s="5">
         <v>46169.55860118056</v>
@@ -4947,16 +4951,16 @@
         <v>46198.59771457176</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="H58" s="6" t="s">
         <v>200</v>
-      </c>
-      <c r="H58" s="6" t="s">
-        <v>201</v>
       </c>
       <c r="I58" s="5">
         <v>46254</v>
@@ -4974,13 +4978,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="O58" s="6" t="s">
         <v>144</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="Q58" s="5">
         <v>46254</v>
@@ -5000,7 +5004,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B59" s="8">
         <v>46169.55860636574</v>
@@ -5012,7 +5016,7 @@
         <v>46198.597709444446</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
@@ -5039,13 +5043,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q59" s="8">
         <v>46258</v>
@@ -5060,7 +5064,7 @@
         <v>1</v>
       </c>
       <c r="U59" s="11" t="s">
-        <v>171</v>
+        <v>209</v>
       </c>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
@@ -5083,10 +5087,10 @@
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="H60" s="6" t="s">
         <v>200</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>201</v>
       </c>
       <c r="I60" s="5">
         <v>46254</v>
@@ -5104,7 +5108,7 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="O60" s="6" t="s">
         <v>166</v>
@@ -5169,13 +5173,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="O61" s="9" t="s">
         <v>211</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q61" s="8">
         <v>46258</v>
@@ -5190,7 +5194,7 @@
         <v>1</v>
       </c>
       <c r="U61" s="11" t="s">
-        <v>171</v>
+        <v>209</v>
       </c>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
@@ -5325,7 +5329,7 @@
         <v>46197.85936673611</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
@@ -5410,7 +5414,7 @@
         <v>215</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="P65" s="9" t="s">
         <v>215</v>
@@ -5428,7 +5432,7 @@
         <v>1</v>
       </c>
       <c r="U65" s="11" t="s">
-        <v>171</v>
+        <v>209</v>
       </c>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
@@ -5445,7 +5449,7 @@
         <v>46197.85915420139</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
@@ -5530,7 +5534,7 @@
         <v>215</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="P67" s="9" t="s">
         <v>215</v>
@@ -5548,7 +5552,7 @@
         <v>1</v>
       </c>
       <c r="U67" s="11" t="s">
-        <v>171</v>
+        <v>209</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
@@ -5565,7 +5569,7 @@
         <v>46205.659588587965</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
@@ -5620,7 +5624,7 @@
         <v>46211.70953918982</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>25</v>
@@ -5675,10 +5679,10 @@
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="H70" s="6" t="s">
         <v>200</v>
-      </c>
-      <c r="H70" s="6" t="s">
-        <v>201</v>
       </c>
       <c r="I70" s="5">
         <v>46220</v>
@@ -5696,7 +5700,7 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="O70" s="6" t="s">
         <v>113</v>
@@ -5740,10 +5744,10 @@
         <v>26</v>
       </c>
       <c r="G71" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="H71" s="9" t="s">
         <v>200</v>
-      </c>
-      <c r="H71" s="9" t="s">
-        <v>201</v>
       </c>
       <c r="I71" s="8">
         <v>46325</v>
@@ -5761,7 +5765,7 @@
         <v>26</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="O71" s="9" t="s">
         <v>103</v>
@@ -5805,10 +5809,10 @@
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="H72" s="6" t="s">
         <v>200</v>
-      </c>
-      <c r="H72" s="6" t="s">
-        <v>201</v>
       </c>
       <c r="I72" s="5">
         <v>46293</v>
@@ -5826,13 +5830,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="O72" s="6" t="s">
         <v>122</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="Q72" s="5">
         <v>46293</v>
@@ -5870,10 +5874,10 @@
         <v>26</v>
       </c>
       <c r="G73" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="H73" s="9" t="s">
         <v>200</v>
-      </c>
-      <c r="H73" s="9" t="s">
-        <v>201</v>
       </c>
       <c r="I73" s="8">
         <v>46282</v>
@@ -5891,7 +5895,7 @@
         <v>26</v>
       </c>
       <c r="N73" s="9" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="O73" s="9" t="s">
         <v>154</v>
@@ -6030,7 +6034,7 @@
         <v>1</v>
       </c>
       <c r="U75" s="11" t="s">
-        <v>171</v>
+        <v>209</v>
       </c>
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
@@ -6047,7 +6051,7 @@
         <v>46223.57064498843</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
@@ -6132,7 +6136,7 @@
         <v>248</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="P77" s="9" t="s">
         <v>248</v>
@@ -6167,7 +6171,7 @@
         <v>46223.57074214121</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
@@ -6372,7 +6376,7 @@
         <v>248</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="P81" s="9" t="s">
         <v>248</v>
@@ -6407,7 +6411,7 @@
         <v>46223.835960763885</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
@@ -6492,7 +6496,7 @@
         <v>248</v>
       </c>
       <c r="O83" s="9" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="P83" s="9" t="s">
         <v>248</v>
@@ -6527,7 +6531,7 @@
         <v>46223.57092783565</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
@@ -6557,7 +6561,7 @@
         <v>272</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="P84" s="6" t="s">
         <v>274</v>
@@ -6677,7 +6681,7 @@
         <v>276</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="P86" s="6" t="s">
         <v>279</v>
@@ -6820,7 +6824,7 @@
         <v>46211.700054201385</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>26</v>
@@ -6905,7 +6909,7 @@
         <v>281</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="P90" s="6" t="s">
         <v>281</v>
@@ -6940,7 +6944,7 @@
         <v>46223.57147459491</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>26</v>
@@ -6970,7 +6974,7 @@
         <v>290</v>
       </c>
       <c r="O91" s="9" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="P91" s="9" t="s">
         <v>292</v>
@@ -7025,7 +7029,7 @@
         <v>281</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="P92" s="6" t="s">
         <v>281</v>
@@ -7043,7 +7047,7 @@
         <v>1</v>
       </c>
       <c r="U92" s="11" t="s">
-        <v>171</v>
+        <v>209</v>
       </c>
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
@@ -7060,7 +7064,7 @@
         <v>46211.830942650464</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>26</v>
@@ -7090,7 +7094,7 @@
         <v>294</v>
       </c>
       <c r="O93" s="9" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="P93" s="9" t="s">
         <v>296</v>
@@ -7145,7 +7149,7 @@
         <v>281</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="P94" s="6" t="s">
         <v>299</v>
@@ -7180,7 +7184,7 @@
         <v>46211.863992280094</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>26</v>
@@ -7210,7 +7214,7 @@
         <v>298</v>
       </c>
       <c r="O95" s="9" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="P95" s="9" t="s">
         <v>298</v>

--- a/data/50001557 - ATACAMA KOZAN OT4340.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4340.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1185" uniqueCount="310">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1185" uniqueCount="309">
   <si>
     <t xml:space="preserve"> 50001557 - ATACAMA KOZAN</t>
   </si>
@@ -354,7 +354,7 @@
     <t>Propuesta compras:,Generación OC materiales corte Laser OT 4340</t>
   </si>
   <si>
-    <t>Media</t>
+    <t>Alta</t>
   </si>
   <si>
     <t>1215165982719434</t>
@@ -436,9 +436,6 @@
   </si>
   <si>
     <t>Generación OC Rodete OT 4340 ,Fabricación Rodete OT 4340</t>
-  </si>
-  <si>
-    <t>Alta</t>
   </si>
   <si>
     <t>1215166329218738</t>
@@ -1110,12 +1107,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFeec300"/>
+        <fgColor rgb="FFe8384f"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFe8384f"/>
+        <fgColor rgb="FFeec300"/>
       </patternFill>
     </fill>
   </fills>
@@ -2534,7 +2531,7 @@
         <v>46183.90663498842</v>
       </c>
       <c r="D18" s="5">
-        <v>46233.174886064815</v>
+        <v>46241.2076584375</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>77</v>
@@ -2599,7 +2596,7 @@
         <v>46183.906646539355</v>
       </c>
       <c r="D19" s="8">
-        <v>46233.174886203706</v>
+        <v>46241.20766320602</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>82</v>
@@ -2664,7 +2661,7 @@
         <v>46190.644140034725</v>
       </c>
       <c r="D20" s="5">
-        <v>46233.174886168985</v>
+        <v>46241.20765859954</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>85</v>
@@ -2729,7 +2726,7 @@
         <v>46183.90733957176</v>
       </c>
       <c r="D21" s="8">
-        <v>46233.174886504625</v>
+        <v>46241.20765909722</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>88</v>
@@ -2954,7 +2951,7 @@
       <c r="T24" s="6">
         <v>0</v>
       </c>
-      <c r="U24" s="12" t="s">
+      <c r="U24" s="11" t="s">
         <v>101</v>
       </c>
     </row>
@@ -3015,7 +3012,7 @@
       <c r="T25" s="9">
         <v>0</v>
       </c>
-      <c r="U25" s="12" t="s">
+      <c r="U25" s="11" t="s">
         <v>101</v>
       </c>
     </row>
@@ -3074,8 +3071,8 @@
       <c r="R26" s="5">
         <v>46219</v>
       </c>
-      <c r="S26" s="12" t="s">
-        <v>108</v>
+      <c r="S26" s="11" t="s">
+        <v>80</v>
       </c>
       <c r="T26" s="6">
         <v>1</v>
@@ -3086,7 +3083,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B27" s="8">
         <v>46169.55832063657</v>
@@ -3098,7 +3095,7 @@
         <v>46184.7364097338</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>26</v>
@@ -3131,7 +3128,7 @@
         <v>72</v>
       </c>
       <c r="P27" s="9" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="Q27" s="9"/>
       <c r="R27" s="9"/>
@@ -3141,13 +3138,13 @@
       <c r="T27" s="9">
         <v>0</v>
       </c>
-      <c r="U27" s="12" t="s">
+      <c r="U27" s="11" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B28" s="5">
         <v>46169.55832539352</v>
@@ -3159,7 +3156,7 @@
         <v>46184.736449375</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
@@ -3189,10 +3186,10 @@
         <v>106</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
@@ -3202,13 +3199,13 @@
       <c r="T28" s="6">
         <v>0</v>
       </c>
-      <c r="U28" s="12" t="s">
+      <c r="U28" s="11" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B29" s="8">
         <v>46169.55833006944</v>
@@ -3220,7 +3217,7 @@
         <v>46200.81836952546</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
@@ -3250,7 +3247,7 @@
         <v>91</v>
       </c>
       <c r="O29" s="9" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="P29" s="9" t="s">
         <v>91</v>
@@ -3273,7 +3270,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B30" s="5">
         <v>46169.55833486111</v>
@@ -3285,7 +3282,7 @@
         <v>46195.69066259259</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
@@ -3312,13 +3309,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="O30" s="6" t="s">
         <v>66</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -3328,13 +3325,13 @@
       <c r="T30" s="6">
         <v>0</v>
       </c>
-      <c r="U30" s="12" t="s">
+      <c r="U30" s="11" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B31" s="8">
         <v>46169.5583402662</v>
@@ -3346,7 +3343,7 @@
         <v>46195.69066760417</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>26</v>
@@ -3373,13 +3370,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="9" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="O31" s="9" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="P31" s="9" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Q31" s="9"/>
       <c r="R31" s="9"/>
@@ -3389,13 +3386,13 @@
       <c r="T31" s="9">
         <v>0</v>
       </c>
-      <c r="U31" s="12" t="s">
+      <c r="U31" s="11" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B32" s="5">
         <v>46169.55834503472</v>
@@ -3407,7 +3404,7 @@
         <v>46195.6906680324</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
@@ -3434,13 +3431,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
@@ -3450,13 +3447,13 @@
       <c r="T32" s="6">
         <v>0</v>
       </c>
-      <c r="U32" s="12" t="s">
+      <c r="U32" s="11" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B33" s="8">
         <v>46169.55836335648</v>
@@ -3468,16 +3465,16 @@
         <v>46184.532641875005</v>
       </c>
       <c r="E33" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="F33" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G33" s="9" t="s">
         <v>128</v>
       </c>
-      <c r="F33" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G33" s="9" t="s">
+      <c r="H33" s="9" t="s">
         <v>129</v>
-      </c>
-      <c r="H33" s="9" t="s">
-        <v>130</v>
       </c>
       <c r="I33" s="8">
         <v>46241</v>
@@ -3498,7 +3495,7 @@
         <v>91</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="P33" s="9" t="s">
         <v>91</v>
@@ -3521,7 +3518,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B34" s="5">
         <v>46169.558367986116</v>
@@ -3533,16 +3530,16 @@
         <v>46184.53245875</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="H34" s="6" t="s">
         <v>129</v>
-      </c>
-      <c r="H34" s="6" t="s">
-        <v>130</v>
       </c>
       <c r="I34" s="5">
         <v>46241</v>
@@ -3560,13 +3557,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="O34" s="6" t="s">
         <v>77</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3576,13 +3573,13 @@
       <c r="T34" s="6">
         <v>0</v>
       </c>
-      <c r="U34" s="12" t="s">
+      <c r="U34" s="11" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B35" s="8">
         <v>46169.55837292824</v>
@@ -3594,16 +3591,16 @@
         <v>46184.532615856486</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="H35" s="9" t="s">
         <v>129</v>
-      </c>
-      <c r="H35" s="9" t="s">
-        <v>130</v>
       </c>
       <c r="I35" s="8">
         <v>46245</v>
@@ -3621,13 +3618,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="P35" s="9" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="Q35" s="9"/>
       <c r="R35" s="9"/>
@@ -3637,13 +3634,13 @@
       <c r="T35" s="9">
         <v>0</v>
       </c>
-      <c r="U35" s="12" t="s">
+      <c r="U35" s="11" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B36" s="5">
         <v>46169.55837825232</v>
@@ -3655,16 +3652,16 @@
         <v>46184.53258194444</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="H36" s="6" t="s">
         <v>129</v>
-      </c>
-      <c r="H36" s="6" t="s">
-        <v>130</v>
       </c>
       <c r="I36" s="5">
         <v>46241</v>
@@ -3685,7 +3682,7 @@
         <v>91</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P36" s="6" t="s">
         <v>26</v>
@@ -3708,7 +3705,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B37" s="8">
         <v>46169.558381979165</v>
@@ -3726,10 +3723,10 @@
         <v>26</v>
       </c>
       <c r="G37" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="H37" s="9" t="s">
         <v>129</v>
-      </c>
-      <c r="H37" s="9" t="s">
-        <v>130</v>
       </c>
       <c r="I37" s="8">
         <v>46241</v>
@@ -3747,13 +3744,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="O37" s="9" t="s">
         <v>82</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="Q37" s="9"/>
       <c r="R37" s="9"/>
@@ -3763,7 +3760,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B38" s="5">
         <v>46169.55838657408</v>
@@ -3775,16 +3772,16 @@
         <v>46184.53255631945</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="H38" s="6" t="s">
         <v>129</v>
-      </c>
-      <c r="H38" s="6" t="s">
-        <v>130</v>
       </c>
       <c r="I38" s="5">
         <v>46245</v>
@@ -3802,13 +3799,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="O38" s="6" t="s">
         <v>83</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -3818,7 +3815,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B39" s="8">
         <v>46169.55839107639</v>
@@ -3830,16 +3827,16 @@
         <v>46205.600326053245</v>
       </c>
       <c r="E39" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="F39" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G39" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="F39" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G39" s="9" t="s">
+      <c r="H39" s="9" t="s">
         <v>148</v>
-      </c>
-      <c r="H39" s="9" t="s">
-        <v>149</v>
       </c>
       <c r="I39" s="8">
         <v>46241</v>
@@ -3860,7 +3857,7 @@
         <v>91</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P39" s="9" t="s">
         <v>26</v>
@@ -3883,7 +3880,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B40" s="5">
         <v>46169.55839478009</v>
@@ -3901,10 +3898,10 @@
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="H40" s="6" t="s">
         <v>148</v>
-      </c>
-      <c r="H40" s="6" t="s">
-        <v>149</v>
       </c>
       <c r="I40" s="5">
         <v>46241</v>
@@ -3922,13 +3919,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="O40" s="6" t="s">
         <v>88</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -3938,7 +3935,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B41" s="8">
         <v>46169.55839910879</v>
@@ -3950,16 +3947,16 @@
         <v>46195.70375376157</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="H41" s="9" t="s">
         <v>148</v>
-      </c>
-      <c r="H41" s="9" t="s">
-        <v>149</v>
       </c>
       <c r="I41" s="8">
         <v>46252</v>
@@ -3977,13 +3974,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="O41" s="9" t="s">
         <v>89</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="Q41" s="9"/>
       <c r="R41" s="9"/>
@@ -3993,7 +3990,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B42" s="5">
         <v>46169.55840355324</v>
@@ -4005,16 +4002,16 @@
         <v>46205.59994755787</v>
       </c>
       <c r="E42" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="F42" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G42" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="F42" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G42" s="6" t="s">
+      <c r="H42" s="6" t="s">
         <v>158</v>
-      </c>
-      <c r="H42" s="6" t="s">
-        <v>159</v>
       </c>
       <c r="I42" s="5">
         <v>46281</v>
@@ -4032,10 +4029,10 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>26</v>
@@ -4048,7 +4045,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B43" s="8">
         <v>46169.55840677083</v>
@@ -4060,16 +4057,16 @@
         <v>46191.53701371528</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="H43" s="9" t="s">
         <v>129</v>
-      </c>
-      <c r="H43" s="9" t="s">
-        <v>130</v>
       </c>
       <c r="I43" s="8">
         <v>46241</v>
@@ -4090,7 +4087,7 @@
         <v>91</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="P43" s="9" t="s">
         <v>26</v>
@@ -4113,7 +4110,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B44" s="5">
         <v>46169.55841037037</v>
@@ -4131,10 +4128,10 @@
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="H44" s="6" t="s">
         <v>129</v>
-      </c>
-      <c r="H44" s="6" t="s">
-        <v>130</v>
       </c>
       <c r="I44" s="5">
         <v>46241</v>
@@ -4152,13 +4149,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="O44" s="6" t="s">
         <v>85</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4168,7 +4165,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B45" s="8">
         <v>46169.558458217594</v>
@@ -4180,16 +4177,16 @@
         <v>46191.53698841435</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="H45" s="9" t="s">
         <v>129</v>
-      </c>
-      <c r="H45" s="9" t="s">
-        <v>130</v>
       </c>
       <c r="I45" s="8">
         <v>46245</v>
@@ -4207,13 +4204,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="O45" s="9" t="s">
         <v>86</v>
       </c>
       <c r="P45" s="9" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="Q45" s="9"/>
       <c r="R45" s="9"/>
@@ -4223,7 +4220,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B46" s="5">
         <v>46169.5584643287</v>
@@ -4235,7 +4232,7 @@
         <v>46240.716379722224</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>25</v>
@@ -4259,7 +4256,7 @@
         <v>26</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4276,7 +4273,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B47" s="8">
         <v>46169.55846813657</v>
@@ -4288,16 +4285,16 @@
         <v>46197.715420312496</v>
       </c>
       <c r="E47" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="F47" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G47" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="F47" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G47" s="9" t="s">
+      <c r="H47" s="9" t="s">
         <v>173</v>
-      </c>
-      <c r="H47" s="9" t="s">
-        <v>174</v>
       </c>
       <c r="I47" s="8">
         <v>46167</v>
@@ -4315,13 +4312,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="Q47" s="8">
         <v>46167</v>
@@ -4329,8 +4326,8 @@
       <c r="R47" s="8">
         <v>46184</v>
       </c>
-      <c r="S47" s="12" t="s">
-        <v>108</v>
+      <c r="S47" s="11" t="s">
+        <v>80</v>
       </c>
       <c r="T47" s="9">
         <v>1</v>
@@ -4341,7 +4338,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B48" s="5">
         <v>46169.558472766206</v>
@@ -4353,16 +4350,16 @@
         <v>46181.72663056713</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="H48" s="6" t="s">
         <v>177</v>
-      </c>
-      <c r="H48" s="6" t="s">
-        <v>178</v>
       </c>
       <c r="I48" s="5">
         <v>46167</v>
@@ -4380,13 +4377,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="O48" s="6" t="s">
         <v>60</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q48" s="6"/>
       <c r="R48" s="6"/>
@@ -4396,7 +4393,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B49" s="8">
         <v>46169.55849938658</v>
@@ -4408,16 +4405,16 @@
         <v>46238.18899571759</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="H49" s="9" t="s">
         <v>173</v>
-      </c>
-      <c r="H49" s="9" t="s">
-        <v>174</v>
       </c>
       <c r="I49" s="8">
         <v>46218</v>
@@ -4435,13 +4432,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="Q49" s="8">
         <v>46218</v>
@@ -4449,8 +4446,8 @@
       <c r="R49" s="8">
         <v>46237</v>
       </c>
-      <c r="S49" s="12" t="s">
-        <v>108</v>
+      <c r="S49" s="11" t="s">
+        <v>80</v>
       </c>
       <c r="T49" s="9">
         <v>1</v>
@@ -4461,7 +4458,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B50" s="5">
         <v>46169.55850371528</v>
@@ -4473,16 +4470,16 @@
         <v>46195.690583055555</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="H50" s="6" t="s">
         <v>177</v>
-      </c>
-      <c r="H50" s="6" t="s">
-        <v>178</v>
       </c>
       <c r="I50" s="5">
         <v>46218</v>
@@ -4500,13 +4497,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="O50" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="P50" s="6" t="s">
         <v>183</v>
-      </c>
-      <c r="P50" s="6" t="s">
-        <v>184</v>
       </c>
       <c r="Q50" s="6"/>
       <c r="R50" s="6"/>
@@ -4516,7 +4513,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B51" s="8">
         <v>46169.55853228009</v>
@@ -4534,10 +4531,10 @@
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="H51" s="9" t="s">
         <v>177</v>
-      </c>
-      <c r="H51" s="9" t="s">
-        <v>178</v>
       </c>
       <c r="I51" s="8">
         <v>46238</v>
@@ -4555,13 +4552,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q51" s="8">
         <v>46238</v>
@@ -4569,8 +4566,8 @@
       <c r="R51" s="8">
         <v>46238</v>
       </c>
-      <c r="S51" s="12" t="s">
-        <v>108</v>
+      <c r="S51" s="11" t="s">
+        <v>80</v>
       </c>
       <c r="T51" s="9">
         <v>1</v>
@@ -4581,7 +4578,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B52" s="5">
         <v>46169.55854641204</v>
@@ -4593,16 +4590,16 @@
         <v>46182.75984881945</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="H52" s="6" t="s">
         <v>177</v>
-      </c>
-      <c r="H52" s="6" t="s">
-        <v>178</v>
       </c>
       <c r="I52" s="5">
         <v>46238</v>
@@ -4623,7 +4620,7 @@
         <v>78</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="P52" s="6" t="s">
         <v>78</v>
@@ -4636,7 +4633,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B53" s="8">
         <v>46169.558565775464</v>
@@ -4648,16 +4645,16 @@
         <v>46211.86422231482</v>
       </c>
       <c r="E53" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="F53" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G53" s="9" t="s">
         <v>189</v>
       </c>
-      <c r="F53" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G53" s="9" t="s">
+      <c r="H53" s="9" t="s">
         <v>190</v>
-      </c>
-      <c r="H53" s="9" t="s">
-        <v>191</v>
       </c>
       <c r="I53" s="8">
         <v>46331</v>
@@ -4675,10 +4672,10 @@
         <v>26</v>
       </c>
       <c r="N53" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="P53" s="9" t="s">
         <v>26</v>
@@ -4701,7 +4698,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B54" s="5">
         <v>46169.55856972223</v>
@@ -4713,16 +4710,16 @@
         <v>46211.86419394676</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="H54" s="6" t="s">
         <v>190</v>
-      </c>
-      <c r="H54" s="6" t="s">
-        <v>191</v>
       </c>
       <c r="I54" s="5">
         <v>46331</v>
@@ -4740,13 +4737,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="Q54" s="6"/>
       <c r="R54" s="6"/>
@@ -4756,7 +4753,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B55" s="8">
         <v>46169.558586307874</v>
@@ -4768,7 +4765,7 @@
         <v>46198.597746307874</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>25</v>
@@ -4792,7 +4789,7 @@
         <v>26</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="P55" s="9" t="s">
         <v>26</v>
@@ -4809,7 +4806,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B56" s="5">
         <v>46169.55858945602</v>
@@ -4821,16 +4818,16 @@
         <v>46197.83559606482</v>
       </c>
       <c r="E56" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="F56" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G56" s="6" t="s">
         <v>198</v>
       </c>
-      <c r="F56" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G56" s="6" t="s">
+      <c r="H56" s="6" t="s">
         <v>199</v>
-      </c>
-      <c r="H56" s="6" t="s">
-        <v>200</v>
       </c>
       <c r="I56" s="5">
         <v>46254</v>
@@ -4848,13 +4845,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="Q56" s="5">
         <v>46254</v>
@@ -4874,7 +4871,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B57" s="8">
         <v>46169.55859488426</v>
@@ -4886,16 +4883,16 @@
         <v>46197.85937331019</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="H57" s="9" t="s">
         <v>158</v>
-      </c>
-      <c r="H57" s="9" t="s">
-        <v>159</v>
       </c>
       <c r="I57" s="8">
         <v>46258</v>
@@ -4913,13 +4910,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="Q57" s="8">
         <v>46258</v>
@@ -4939,7 +4936,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B58" s="5">
         <v>46169.55860118056</v>
@@ -4951,16 +4948,16 @@
         <v>46198.59771457176</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="H58" s="6" t="s">
         <v>199</v>
-      </c>
-      <c r="H58" s="6" t="s">
-        <v>200</v>
       </c>
       <c r="I58" s="5">
         <v>46254</v>
@@ -4978,13 +4975,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Q58" s="5">
         <v>46254</v>
@@ -5004,7 +5001,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B59" s="8">
         <v>46169.55860636574</v>
@@ -5016,16 +5013,16 @@
         <v>46198.597709444446</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="H59" s="9" t="s">
         <v>158</v>
-      </c>
-      <c r="H59" s="9" t="s">
-        <v>159</v>
       </c>
       <c r="I59" s="8">
         <v>46258</v>
@@ -5043,13 +5040,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q59" s="8">
         <v>46258</v>
@@ -5063,13 +5060,13 @@
       <c r="T59" s="9">
         <v>1</v>
       </c>
-      <c r="U59" s="11" t="s">
-        <v>209</v>
+      <c r="U59" s="12" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B60" s="5">
         <v>46169.558650127314</v>
@@ -5081,16 +5078,16 @@
         <v>46198.59773310185</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="H60" s="6" t="s">
         <v>199</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>200</v>
       </c>
       <c r="I60" s="5">
         <v>46254</v>
@@ -5108,13 +5105,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="Q60" s="5">
         <v>46254</v>
@@ -5134,7 +5131,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B61" s="8">
         <v>46169.55865608796</v>
@@ -5146,16 +5143,16 @@
         <v>46198.59773317129</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="H61" s="9" t="s">
         <v>158</v>
-      </c>
-      <c r="H61" s="9" t="s">
-        <v>159</v>
       </c>
       <c r="I61" s="8">
         <v>46258</v>
@@ -5173,13 +5170,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q61" s="8">
         <v>46258</v>
@@ -5193,13 +5190,13 @@
       <c r="T61" s="9">
         <v>1</v>
       </c>
-      <c r="U61" s="11" t="s">
-        <v>209</v>
+      <c r="U61" s="12" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B62" s="5">
         <v>46169.55866105324</v>
@@ -5211,7 +5208,7 @@
         <v>46198.68229049769</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>25</v>
@@ -5235,7 +5232,7 @@
         <v>26</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P62" s="6" t="s">
         <v>26</v>
@@ -5252,7 +5249,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B63" s="8">
         <v>46169.55866469907</v>
@@ -5264,16 +5261,16 @@
         <v>46240.5827003125</v>
       </c>
       <c r="E63" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="F63" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G63" s="9" t="s">
         <v>218</v>
       </c>
-      <c r="F63" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G63" s="9" t="s">
+      <c r="H63" s="9" t="s">
         <v>219</v>
-      </c>
-      <c r="H63" s="9" t="s">
-        <v>220</v>
       </c>
       <c r="I63" s="8">
         <v>46260</v>
@@ -5291,13 +5288,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="P63" s="9" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="Q63" s="8">
         <v>46260</v>
@@ -5317,7 +5314,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B64" s="5">
         <v>46169.55867099537</v>
@@ -5329,16 +5326,16 @@
         <v>46197.85936673611</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="H64" s="6" t="s">
         <v>219</v>
-      </c>
-      <c r="H64" s="6" t="s">
-        <v>220</v>
       </c>
       <c r="I64" s="5">
         <v>46260</v>
@@ -5356,13 +5353,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="O64" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="P64" s="6" t="s">
         <v>223</v>
-      </c>
-      <c r="P64" s="6" t="s">
-        <v>224</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5372,7 +5369,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B65" s="8">
         <v>46169.558703518516</v>
@@ -5384,16 +5381,16 @@
         <v>46197.85387390046</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="H65" s="9" t="s">
         <v>219</v>
-      </c>
-      <c r="H65" s="9" t="s">
-        <v>220</v>
       </c>
       <c r="I65" s="8">
         <v>46269</v>
@@ -5411,13 +5408,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="Q65" s="8">
         <v>46269</v>
@@ -5431,13 +5428,13 @@
       <c r="T65" s="9">
         <v>1</v>
       </c>
-      <c r="U65" s="11" t="s">
-        <v>209</v>
+      <c r="U65" s="12" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B66" s="5">
         <v>46169.55870879629</v>
@@ -5449,16 +5446,16 @@
         <v>46197.85915420139</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="H66" s="6" t="s">
         <v>219</v>
-      </c>
-      <c r="H66" s="6" t="s">
-        <v>220</v>
       </c>
       <c r="I66" s="5">
         <v>46269</v>
@@ -5476,13 +5473,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="O66" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="P66" s="6" t="s">
         <v>228</v>
-      </c>
-      <c r="P66" s="6" t="s">
-        <v>229</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5492,7 +5489,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B67" s="8">
         <v>46169.558740625</v>
@@ -5504,16 +5501,16 @@
         <v>46205.65959174768</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="H67" s="9" t="s">
         <v>158</v>
-      </c>
-      <c r="H67" s="9" t="s">
-        <v>159</v>
       </c>
       <c r="I67" s="8">
         <v>46274</v>
@@ -5531,13 +5528,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="P67" s="9" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="Q67" s="8">
         <v>46274</v>
@@ -5551,13 +5548,13 @@
       <c r="T67" s="9">
         <v>1</v>
       </c>
-      <c r="U67" s="11" t="s">
-        <v>209</v>
+      <c r="U67" s="12" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B68" s="5">
         <v>46169.558745243055</v>
@@ -5569,16 +5566,16 @@
         <v>46205.659588587965</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="H68" s="6" t="s">
         <v>158</v>
-      </c>
-      <c r="H68" s="6" t="s">
-        <v>159</v>
       </c>
       <c r="I68" s="5">
         <v>46274</v>
@@ -5596,13 +5593,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q68" s="6"/>
       <c r="R68" s="6"/>
@@ -5612,7 +5609,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B69" s="8">
         <v>46169.55876947917</v>
@@ -5624,7 +5621,7 @@
         <v>46211.70953918982</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>25</v>
@@ -5648,7 +5645,7 @@
         <v>26</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="P69" s="9" t="s">
         <v>26</v>
@@ -5661,7 +5658,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B70" s="5">
         <v>46169.55880633101</v>
@@ -5673,16 +5670,16 @@
         <v>46224.186405659726</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="H70" s="6" t="s">
         <v>199</v>
-      </c>
-      <c r="H70" s="6" t="s">
-        <v>200</v>
       </c>
       <c r="I70" s="5">
         <v>46220</v>
@@ -5700,13 +5697,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="Q70" s="5">
         <v>46220</v>
@@ -5714,8 +5711,8 @@
       <c r="R70" s="5">
         <v>46223</v>
       </c>
-      <c r="S70" s="12" t="s">
-        <v>108</v>
+      <c r="S70" s="11" t="s">
+        <v>80</v>
       </c>
       <c r="T70" s="6">
         <v>1</v>
@@ -5726,7 +5723,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B71" s="8">
         <v>46169.5588177662</v>
@@ -5738,16 +5735,16 @@
         <v>46200.819831597226</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="9" t="s">
+        <v>198</v>
+      </c>
+      <c r="H71" s="9" t="s">
         <v>199</v>
-      </c>
-      <c r="H71" s="9" t="s">
-        <v>200</v>
       </c>
       <c r="I71" s="8">
         <v>46325</v>
@@ -5765,13 +5762,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="O71" s="9" t="s">
         <v>103</v>
       </c>
       <c r="P71" s="9" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="Q71" s="8">
         <v>46325</v>
@@ -5779,8 +5776,8 @@
       <c r="R71" s="8">
         <v>46325</v>
       </c>
-      <c r="S71" s="12" t="s">
-        <v>108</v>
+      <c r="S71" s="11" t="s">
+        <v>80</v>
       </c>
       <c r="T71" s="9">
         <v>1</v>
@@ -5791,7 +5788,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B72" s="5">
         <v>46169.55882295139</v>
@@ -5803,16 +5800,16 @@
         <v>46200.81928909722</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="H72" s="6" t="s">
         <v>199</v>
-      </c>
-      <c r="H72" s="6" t="s">
-        <v>200</v>
       </c>
       <c r="I72" s="5">
         <v>46293</v>
@@ -5830,13 +5827,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="Q72" s="5">
         <v>46293</v>
@@ -5856,7 +5853,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B73" s="8">
         <v>46169.55882788195</v>
@@ -5868,16 +5865,16 @@
         <v>46211.7093043287</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="9" t="s">
+        <v>198</v>
+      </c>
+      <c r="H73" s="9" t="s">
         <v>199</v>
-      </c>
-      <c r="H73" s="9" t="s">
-        <v>200</v>
       </c>
       <c r="I73" s="8">
         <v>46282</v>
@@ -5895,13 +5892,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="9" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="P73" s="9" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="Q73" s="8">
         <v>46282</v>
@@ -5921,7 +5918,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B74" s="5">
         <v>46169.55884254629</v>
@@ -5933,7 +5930,7 @@
         <v>46211.86406403936</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>25</v>
@@ -5957,7 +5954,7 @@
         <v>26</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="P74" s="6" t="s">
         <v>26</v>
@@ -5974,7 +5971,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B75" s="8">
         <v>46169.55884548611</v>
@@ -5986,7 +5983,7 @@
         <v>46223.571425636575</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
@@ -6013,13 +6010,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="Q75" s="8">
         <v>46276</v>
@@ -6033,13 +6030,13 @@
       <c r="T75" s="9">
         <v>1</v>
       </c>
-      <c r="U75" s="11" t="s">
-        <v>209</v>
+      <c r="U75" s="12" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B76" s="5">
         <v>46169.55884993056</v>
@@ -6051,7 +6048,7 @@
         <v>46223.57064498843</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
@@ -6078,13 +6075,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -6094,7 +6091,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B77" s="8">
         <v>46169.55893170139</v>
@@ -6106,7 +6103,7 @@
         <v>46223.57142202546</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>26</v>
@@ -6133,13 +6130,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="P77" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="Q77" s="8">
         <v>46296</v>
@@ -6159,7 +6156,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B78" s="5">
         <v>46169.55893543981</v>
@@ -6171,7 +6168,7 @@
         <v>46223.57074214121</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
@@ -6198,13 +6195,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="O78" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="P78" s="6" t="s">
         <v>258</v>
-      </c>
-      <c r="P78" s="6" t="s">
-        <v>259</v>
       </c>
       <c r="Q78" s="6"/>
       <c r="R78" s="6"/>
@@ -6214,7 +6211,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B79" s="8">
         <v>46169.558869560184</v>
@@ -6226,7 +6223,7 @@
         <v>46223.57141798611</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>26</v>
@@ -6253,13 +6250,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="P79" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="Q79" s="8">
         <v>46328</v>
@@ -6279,7 +6276,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B80" s="5">
         <v>46169.55887296297</v>
@@ -6291,7 +6288,7 @@
         <v>46223.57080435185</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
@@ -6318,13 +6315,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="O80" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="P80" s="6" t="s">
         <v>264</v>
-      </c>
-      <c r="P80" s="6" t="s">
-        <v>265</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -6334,7 +6331,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B81" s="8">
         <v>46169.5589025463</v>
@@ -6346,7 +6343,7 @@
         <v>46223.57141431713</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
@@ -6373,13 +6370,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="Q81" s="8">
         <v>46329</v>
@@ -6399,7 +6396,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B82" s="5">
         <v>46169.55890609954</v>
@@ -6411,7 +6408,7 @@
         <v>46223.835960763885</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
@@ -6438,13 +6435,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="O82" s="6" t="s">
+        <v>268</v>
+      </c>
+      <c r="P82" s="6" t="s">
         <v>269</v>
-      </c>
-      <c r="P82" s="6" t="s">
-        <v>270</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6454,7 +6451,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B83" s="8">
         <v>46169.55900443287</v>
@@ -6466,7 +6463,7 @@
         <v>46223.57141039352</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>26</v>
@@ -6493,13 +6490,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="O83" s="9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="P83" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="Q83" s="8">
         <v>46330</v>
@@ -6519,7 +6516,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B84" s="5">
         <v>46169.55901002315</v>
@@ -6531,7 +6528,7 @@
         <v>46223.57092783565</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
@@ -6558,13 +6555,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="Q84" s="6"/>
       <c r="R84" s="6"/>
@@ -6574,7 +6571,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B85" s="8">
         <v>46169.55904462963</v>
@@ -6586,7 +6583,7 @@
         <v>46223.5714043287</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>26</v>
@@ -6613,13 +6610,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="O85" s="9" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="P85" s="9" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="Q85" s="8">
         <v>46332</v>
@@ -6639,7 +6636,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B86" s="5">
         <v>46169.559050138894</v>
@@ -6651,7 +6648,7 @@
         <v>46223.57102379629</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6678,13 +6675,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6694,7 +6691,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B87" s="8">
         <v>46169.55907484954</v>
@@ -6706,7 +6703,7 @@
         <v>46232.66292771991</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>25</v>
@@ -6730,7 +6727,7 @@
         <v>26</v>
       </c>
       <c r="O87" s="9" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="P87" s="9" t="s">
         <v>26</v>
@@ -6747,7 +6744,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B88" s="5">
         <v>46169.55907863426</v>
@@ -6759,16 +6756,16 @@
         <v>46211.70008446759</v>
       </c>
       <c r="E88" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="F88" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G88" s="6" t="s">
         <v>284</v>
       </c>
-      <c r="F88" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G88" s="6" t="s">
+      <c r="H88" s="6" t="s">
         <v>285</v>
-      </c>
-      <c r="H88" s="6" t="s">
-        <v>286</v>
       </c>
       <c r="I88" s="5">
         <v>46335</v>
@@ -6786,13 +6783,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="Q88" s="5">
         <v>46335</v>
@@ -6812,7 +6809,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B89" s="8">
         <v>46169.55908684028</v>
@@ -6824,16 +6821,16 @@
         <v>46211.700054201385</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="9" t="s">
+        <v>284</v>
+      </c>
+      <c r="H89" s="9" t="s">
         <v>285</v>
-      </c>
-      <c r="H89" s="9" t="s">
-        <v>286</v>
       </c>
       <c r="I89" s="8">
         <v>46335</v>
@@ -6851,13 +6848,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="9" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="O89" s="9" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="P89" s="9" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="Q89" s="9"/>
       <c r="R89" s="9"/>
@@ -6867,7 +6864,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B90" s="5">
         <v>46169.55918673611</v>
@@ -6879,7 +6876,7 @@
         <v>46223.57153153935</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
@@ -6906,13 +6903,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="Q90" s="5">
         <v>46336</v>
@@ -6932,7 +6929,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B91" s="8">
         <v>46169.55919113426</v>
@@ -6944,7 +6941,7 @@
         <v>46223.57147459491</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>26</v>
@@ -6971,13 +6968,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="9" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="O91" s="9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="P91" s="9" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="Q91" s="9"/>
       <c r="R91" s="9"/>
@@ -6987,7 +6984,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B92" s="5">
         <v>46169.559239560185</v>
@@ -6999,16 +6996,16 @@
         <v>46197.859819363424</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="H92" s="6" t="s">
         <v>219</v>
-      </c>
-      <c r="H92" s="6" t="s">
-        <v>220</v>
       </c>
       <c r="I92" s="5">
         <v>46337</v>
@@ -7026,13 +7023,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="Q92" s="5">
         <v>46337</v>
@@ -7046,13 +7043,13 @@
       <c r="T92" s="6">
         <v>1</v>
       </c>
-      <c r="U92" s="11" t="s">
-        <v>209</v>
+      <c r="U92" s="12" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B93" s="8">
         <v>46169.559243842596</v>
@@ -7064,16 +7061,16 @@
         <v>46211.830942650464</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="H93" s="9" t="s">
         <v>219</v>
-      </c>
-      <c r="H93" s="9" t="s">
-        <v>220</v>
       </c>
       <c r="I93" s="8">
         <v>46337</v>
@@ -7091,13 +7088,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="9" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="O93" s="9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="P93" s="9" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="Q93" s="9"/>
       <c r="R93" s="9"/>
@@ -7107,7 +7104,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B94" s="5">
         <v>46169.55929686343</v>
@@ -7119,16 +7116,16 @@
         <v>46211.86402001158</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="H94" s="6" t="s">
         <v>219</v>
-      </c>
-      <c r="H94" s="6" t="s">
-        <v>220</v>
       </c>
       <c r="I94" s="5">
         <v>46338</v>
@@ -7146,13 +7143,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="Q94" s="5">
         <v>46338</v>
@@ -7172,7 +7169,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B95" s="8">
         <v>46169.55930180555</v>
@@ -7184,16 +7181,16 @@
         <v>46211.863992280094</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="H95" s="9" t="s">
         <v>219</v>
-      </c>
-      <c r="H95" s="9" t="s">
-        <v>220</v>
       </c>
       <c r="I95" s="8">
         <v>46338</v>
@@ -7211,13 +7208,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="9" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="O95" s="9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="P95" s="9" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="Q95" s="9"/>
       <c r="R95" s="9"/>
@@ -7227,7 +7224,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B96" s="5">
         <v>46169.55938721065</v>
@@ -7239,7 +7236,7 @@
         <v>46232.662960601854</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>25</v>
@@ -7263,7 +7260,7 @@
         <v>26</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P96" s="6" t="s">
         <v>26</v>
@@ -7280,7 +7277,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B97" s="8">
         <v>46169.55939094907</v>
@@ -7292,16 +7289,16 @@
         <v>46232.66294618056</v>
       </c>
       <c r="E97" s="9" t="s">
+        <v>304</v>
+      </c>
+      <c r="F97" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G97" s="9" t="s">
         <v>305</v>
       </c>
-      <c r="F97" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G97" s="9" t="s">
+      <c r="H97" s="9" t="s">
         <v>306</v>
-      </c>
-      <c r="H97" s="9" t="s">
-        <v>307</v>
       </c>
       <c r="I97" s="8">
         <v>46339</v>
@@ -7319,13 +7316,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="9" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="O97" s="9" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="P97" s="9" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="Q97" s="8">
         <v>46339</v>
@@ -7345,7 +7342,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B98" s="5">
         <v>46169.55939643519</v>
@@ -7357,7 +7354,7 @@
         <v>46232.662950694445</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -7384,13 +7381,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="Q98" s="5">
         <v>46339</v>

--- a/data/50001557 - ATACAMA KOZAN OT4340.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4340.xlsx
@@ -774,7 +774,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t>OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200</t>
+    <t>OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200</t>
   </si>
   <si>
     <t>1215166433625244</t>
@@ -5258,7 +5258,7 @@
         <v>46190.645243935185</v>
       </c>
       <c r="D63" s="8">
-        <v>46240.5827003125</v>
+        <v>46244.58203513889</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>217</v>

--- a/data/50001557 - ATACAMA KOZAN OT4340.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4340.xlsx
@@ -774,7 +774,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t>OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200</t>
+    <t xml:space="preserve">OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200,ot  4390 -ZVN 1-12-110/4 + TOB + REJ ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A </t>
   </si>
   <si>
     <t>1215166433625244</t>
@@ -5258,7 +5258,7 @@
         <v>46190.645243935185</v>
       </c>
       <c r="D63" s="8">
-        <v>46244.58203513889</v>
+        <v>46244.81646715278</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>217</v>

--- a/data/50001557 - ATACAMA KOZAN OT4340.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4340.xlsx
@@ -774,7 +774,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t xml:space="preserve">OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200,ot  4390 -ZVN 1-12-110/4 + TOB + REJ ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A </t>
+    <t xml:space="preserve">OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200,ot  4390 -ZVN 1-12-110/4 + TOB + REJ </t>
   </si>
   <si>
     <t>1215166433625244</t>
@@ -5258,7 +5258,7 @@
         <v>46190.645243935185</v>
       </c>
       <c r="D63" s="8">
-        <v>46244.81646715278</v>
+        <v>46244.91622329861</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>217</v>

--- a/data/50001557 - ATACAMA KOZAN OT4340.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4340.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1185" uniqueCount="309">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1185" uniqueCount="310">
   <si>
     <t xml:space="preserve"> 50001557 - ATACAMA KOZAN</t>
   </si>
@@ -505,6 +505,9 @@
   </si>
   <si>
     <t>Fabricacion Corte Laser  OT 4340,Generación OC materiales corte Laser OT 4340</t>
+  </si>
+  <si>
+    <t>Media</t>
   </si>
   <si>
     <t>1215166433428453</t>
@@ -3462,7 +3465,7 @@
         <v>46184.532628437504</v>
       </c>
       <c r="D33" s="8">
-        <v>46184.532641875005</v>
+        <v>46246.19158646991</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>127</v>
@@ -3506,8 +3509,8 @@
       <c r="R33" s="8">
         <v>46253</v>
       </c>
-      <c r="S33" s="10" t="s">
-        <v>32</v>
+      <c r="S33" s="12" t="s">
+        <v>131</v>
       </c>
       <c r="T33" s="9">
         <v>1</v>
@@ -3518,7 +3521,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B34" s="5">
         <v>46169.558367986116</v>
@@ -3530,7 +3533,7 @@
         <v>46184.53245875</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
@@ -3563,7 +3566,7 @@
         <v>77</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3579,7 +3582,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B35" s="8">
         <v>46169.55837292824</v>
@@ -3591,7 +3594,7 @@
         <v>46184.532615856486</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
@@ -3621,10 +3624,10 @@
         <v>127</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="P35" s="9" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="Q35" s="9"/>
       <c r="R35" s="9"/>
@@ -3640,7 +3643,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B36" s="5">
         <v>46169.55837825232</v>
@@ -3649,10 +3652,10 @@
         <v>46184.53257122685</v>
       </c>
       <c r="D36" s="5">
-        <v>46184.53258194444</v>
+        <v>46246.19158778935</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
@@ -3682,7 +3685,7 @@
         <v>91</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P36" s="6" t="s">
         <v>26</v>
@@ -3693,8 +3696,8 @@
       <c r="R36" s="5">
         <v>46253</v>
       </c>
-      <c r="S36" s="10" t="s">
-        <v>32</v>
+      <c r="S36" s="12" t="s">
+        <v>131</v>
       </c>
       <c r="T36" s="6">
         <v>1</v>
@@ -3705,7 +3708,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B37" s="8">
         <v>46169.558381979165</v>
@@ -3744,13 +3747,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O37" s="9" t="s">
         <v>82</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="Q37" s="9"/>
       <c r="R37" s="9"/>
@@ -3760,7 +3763,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B38" s="5">
         <v>46169.55838657408</v>
@@ -3772,7 +3775,7 @@
         <v>46184.53255631945</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
@@ -3799,13 +3802,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O38" s="6" t="s">
         <v>83</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -3815,7 +3818,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B39" s="8">
         <v>46169.55839107639</v>
@@ -3827,16 +3830,16 @@
         <v>46205.600326053245</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I39" s="8">
         <v>46241</v>
@@ -3857,7 +3860,7 @@
         <v>91</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P39" s="9" t="s">
         <v>26</v>
@@ -3880,7 +3883,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B40" s="5">
         <v>46169.55839478009</v>
@@ -3898,10 +3901,10 @@
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I40" s="5">
         <v>46241</v>
@@ -3919,13 +3922,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="O40" s="6" t="s">
         <v>88</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -3935,7 +3938,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B41" s="8">
         <v>46169.55839910879</v>
@@ -3947,16 +3950,16 @@
         <v>46195.70375376157</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I41" s="8">
         <v>46252</v>
@@ -3974,13 +3977,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="O41" s="9" t="s">
         <v>89</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q41" s="9"/>
       <c r="R41" s="9"/>
@@ -3990,7 +3993,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B42" s="5">
         <v>46169.55840355324</v>
@@ -4002,16 +4005,16 @@
         <v>46205.59994755787</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I42" s="5">
         <v>46281</v>
@@ -4029,10 +4032,10 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>26</v>
@@ -4045,7 +4048,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B43" s="8">
         <v>46169.55840677083</v>
@@ -4054,10 +4057,10 @@
         <v>46191.53700108796</v>
       </c>
       <c r="D43" s="8">
-        <v>46191.53701371528</v>
+        <v>46246.19158665509</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
@@ -4087,7 +4090,7 @@
         <v>91</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="P43" s="9" t="s">
         <v>26</v>
@@ -4098,8 +4101,8 @@
       <c r="R43" s="8">
         <v>46253</v>
       </c>
-      <c r="S43" s="10" t="s">
-        <v>32</v>
+      <c r="S43" s="12" t="s">
+        <v>131</v>
       </c>
       <c r="T43" s="9">
         <v>1</v>
@@ -4110,7 +4113,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B44" s="5">
         <v>46169.55841037037</v>
@@ -4149,13 +4152,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O44" s="6" t="s">
         <v>85</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4165,7 +4168,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B45" s="8">
         <v>46169.558458217594</v>
@@ -4177,7 +4180,7 @@
         <v>46191.53698841435</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>26</v>
@@ -4204,13 +4207,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O45" s="9" t="s">
         <v>86</v>
       </c>
       <c r="P45" s="9" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q45" s="9"/>
       <c r="R45" s="9"/>
@@ -4220,7 +4223,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B46" s="5">
         <v>46169.5584643287</v>
@@ -4232,7 +4235,7 @@
         <v>46240.716379722224</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>25</v>
@@ -4256,7 +4259,7 @@
         <v>26</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4273,7 +4276,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B47" s="8">
         <v>46169.55846813657</v>
@@ -4285,16 +4288,16 @@
         <v>46197.715420312496</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I47" s="8">
         <v>46167</v>
@@ -4312,13 +4315,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q47" s="8">
         <v>46167</v>
@@ -4338,7 +4341,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B48" s="5">
         <v>46169.558472766206</v>
@@ -4350,16 +4353,16 @@
         <v>46181.72663056713</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I48" s="5">
         <v>46167</v>
@@ -4377,13 +4380,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="O48" s="6" t="s">
         <v>60</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q48" s="6"/>
       <c r="R48" s="6"/>
@@ -4393,7 +4396,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B49" s="8">
         <v>46169.55849938658</v>
@@ -4405,16 +4408,16 @@
         <v>46238.18899571759</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I49" s="8">
         <v>46218</v>
@@ -4432,13 +4435,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q49" s="8">
         <v>46218</v>
@@ -4458,7 +4461,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B50" s="5">
         <v>46169.55850371528</v>
@@ -4470,16 +4473,16 @@
         <v>46195.690583055555</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I50" s="5">
         <v>46218</v>
@@ -4497,13 +4500,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q50" s="6"/>
       <c r="R50" s="6"/>
@@ -4513,7 +4516,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B51" s="8">
         <v>46169.55853228009</v>
@@ -4531,10 +4534,10 @@
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I51" s="8">
         <v>46238</v>
@@ -4552,13 +4555,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q51" s="8">
         <v>46238</v>
@@ -4578,7 +4581,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B52" s="5">
         <v>46169.55854641204</v>
@@ -4590,16 +4593,16 @@
         <v>46182.75984881945</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I52" s="5">
         <v>46238</v>
@@ -4620,7 +4623,7 @@
         <v>78</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P52" s="6" t="s">
         <v>78</v>
@@ -4633,7 +4636,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B53" s="8">
         <v>46169.558565775464</v>
@@ -4645,16 +4648,16 @@
         <v>46211.86422231482</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I53" s="8">
         <v>46331</v>
@@ -4672,10 +4675,10 @@
         <v>26</v>
       </c>
       <c r="N53" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P53" s="9" t="s">
         <v>26</v>
@@ -4698,7 +4701,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B54" s="5">
         <v>46169.55856972223</v>
@@ -4710,16 +4713,16 @@
         <v>46211.86419394676</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I54" s="5">
         <v>46331</v>
@@ -4737,13 +4740,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q54" s="6"/>
       <c r="R54" s="6"/>
@@ -4753,7 +4756,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B55" s="8">
         <v>46169.558586307874</v>
@@ -4765,7 +4768,7 @@
         <v>46198.597746307874</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>25</v>
@@ -4789,7 +4792,7 @@
         <v>26</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="P55" s="9" t="s">
         <v>26</v>
@@ -4806,7 +4809,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B56" s="5">
         <v>46169.55858945602</v>
@@ -4818,16 +4821,16 @@
         <v>46197.83559606482</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I56" s="5">
         <v>46254</v>
@@ -4845,13 +4848,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q56" s="5">
         <v>46254</v>
@@ -4871,7 +4874,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B57" s="8">
         <v>46169.55859488426</v>
@@ -4883,16 +4886,16 @@
         <v>46197.85937331019</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I57" s="8">
         <v>46258</v>
@@ -4910,13 +4913,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q57" s="8">
         <v>46258</v>
@@ -4936,7 +4939,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B58" s="5">
         <v>46169.55860118056</v>
@@ -4948,16 +4951,16 @@
         <v>46198.59771457176</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I58" s="5">
         <v>46254</v>
@@ -4975,13 +4978,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q58" s="5">
         <v>46254</v>
@@ -5001,7 +5004,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B59" s="8">
         <v>46169.55860636574</v>
@@ -5013,16 +5016,16 @@
         <v>46198.597709444446</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I59" s="8">
         <v>46258</v>
@@ -5040,13 +5043,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q59" s="8">
         <v>46258</v>
@@ -5061,12 +5064,12 @@
         <v>1</v>
       </c>
       <c r="U59" s="12" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B60" s="5">
         <v>46169.558650127314</v>
@@ -5078,16 +5081,16 @@
         <v>46198.59773310185</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I60" s="5">
         <v>46254</v>
@@ -5105,13 +5108,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q60" s="5">
         <v>46254</v>
@@ -5131,7 +5134,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B61" s="8">
         <v>46169.55865608796</v>
@@ -5143,16 +5146,16 @@
         <v>46198.59773317129</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I61" s="8">
         <v>46258</v>
@@ -5170,13 +5173,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q61" s="8">
         <v>46258</v>
@@ -5191,12 +5194,12 @@
         <v>1</v>
       </c>
       <c r="U61" s="12" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B62" s="5">
         <v>46169.55866105324</v>
@@ -5208,7 +5211,7 @@
         <v>46198.68229049769</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>25</v>
@@ -5232,7 +5235,7 @@
         <v>26</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="P62" s="6" t="s">
         <v>26</v>
@@ -5249,7 +5252,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B63" s="8">
         <v>46169.55866469907</v>
@@ -5261,16 +5264,16 @@
         <v>46244.91622329861</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="9" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H63" s="9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I63" s="8">
         <v>46260</v>
@@ -5288,13 +5291,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P63" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q63" s="8">
         <v>46260</v>
@@ -5314,7 +5317,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B64" s="5">
         <v>46169.55867099537</v>
@@ -5326,16 +5329,16 @@
         <v>46197.85936673611</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I64" s="5">
         <v>46260</v>
@@ -5353,13 +5356,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5369,7 +5372,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B65" s="8">
         <v>46169.558703518516</v>
@@ -5381,16 +5384,16 @@
         <v>46197.85387390046</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H65" s="9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I65" s="8">
         <v>46269</v>
@@ -5408,13 +5411,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q65" s="8">
         <v>46269</v>
@@ -5429,12 +5432,12 @@
         <v>1</v>
       </c>
       <c r="U65" s="12" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B66" s="5">
         <v>46169.55870879629</v>
@@ -5446,16 +5449,16 @@
         <v>46197.85915420139</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I66" s="5">
         <v>46269</v>
@@ -5473,13 +5476,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5489,7 +5492,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B67" s="8">
         <v>46169.558740625</v>
@@ -5501,16 +5504,16 @@
         <v>46205.65959174768</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H67" s="9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I67" s="8">
         <v>46274</v>
@@ -5528,13 +5531,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P67" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q67" s="8">
         <v>46274</v>
@@ -5549,12 +5552,12 @@
         <v>1</v>
       </c>
       <c r="U67" s="12" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B68" s="5">
         <v>46169.558745243055</v>
@@ -5566,16 +5569,16 @@
         <v>46205.659588587965</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I68" s="5">
         <v>46274</v>
@@ -5593,13 +5596,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q68" s="6"/>
       <c r="R68" s="6"/>
@@ -5609,7 +5612,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B69" s="8">
         <v>46169.55876947917</v>
@@ -5621,7 +5624,7 @@
         <v>46211.70953918982</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>25</v>
@@ -5645,7 +5648,7 @@
         <v>26</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="P69" s="9" t="s">
         <v>26</v>
@@ -5658,7 +5661,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B70" s="5">
         <v>46169.55880633101</v>
@@ -5670,16 +5673,16 @@
         <v>46224.186405659726</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I70" s="5">
         <v>46220</v>
@@ -5697,13 +5700,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O70" s="6" t="s">
         <v>112</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q70" s="5">
         <v>46220</v>
@@ -5723,7 +5726,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B71" s="8">
         <v>46169.5588177662</v>
@@ -5735,16 +5738,16 @@
         <v>46200.819831597226</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H71" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I71" s="8">
         <v>46325</v>
@@ -5762,13 +5765,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O71" s="9" t="s">
         <v>103</v>
       </c>
       <c r="P71" s="9" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q71" s="8">
         <v>46325</v>
@@ -5788,7 +5791,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B72" s="5">
         <v>46169.55882295139</v>
@@ -5800,16 +5803,16 @@
         <v>46200.81928909722</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I72" s="5">
         <v>46293</v>
@@ -5827,13 +5830,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O72" s="6" t="s">
         <v>121</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q72" s="5">
         <v>46293</v>
@@ -5853,7 +5856,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B73" s="8">
         <v>46169.55882788195</v>
@@ -5865,16 +5868,16 @@
         <v>46211.7093043287</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H73" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I73" s="8">
         <v>46282</v>
@@ -5892,13 +5895,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="P73" s="9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q73" s="8">
         <v>46282</v>
@@ -5918,7 +5921,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B74" s="5">
         <v>46169.55884254629</v>
@@ -5930,7 +5933,7 @@
         <v>46211.86406403936</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>25</v>
@@ -5954,7 +5957,7 @@
         <v>26</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="P74" s="6" t="s">
         <v>26</v>
@@ -5971,7 +5974,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B75" s="8">
         <v>46169.55884548611</v>
@@ -5983,7 +5986,7 @@
         <v>46223.571425636575</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
@@ -6010,13 +6013,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q75" s="8">
         <v>46276</v>
@@ -6031,12 +6034,12 @@
         <v>1</v>
       </c>
       <c r="U75" s="12" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B76" s="5">
         <v>46169.55884993056</v>
@@ -6048,7 +6051,7 @@
         <v>46223.57064498843</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
@@ -6075,13 +6078,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -6091,7 +6094,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B77" s="8">
         <v>46169.55893170139</v>
@@ -6103,7 +6106,7 @@
         <v>46223.57142202546</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>26</v>
@@ -6130,13 +6133,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P77" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q77" s="8">
         <v>46296</v>
@@ -6156,7 +6159,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B78" s="5">
         <v>46169.55893543981</v>
@@ -6168,7 +6171,7 @@
         <v>46223.57074214121</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
@@ -6195,13 +6198,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q78" s="6"/>
       <c r="R78" s="6"/>
@@ -6211,7 +6214,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B79" s="8">
         <v>46169.558869560184</v>
@@ -6223,7 +6226,7 @@
         <v>46223.57141798611</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>26</v>
@@ -6250,13 +6253,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="P79" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q79" s="8">
         <v>46328</v>
@@ -6276,7 +6279,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B80" s="5">
         <v>46169.55887296297</v>
@@ -6288,7 +6291,7 @@
         <v>46223.57080435185</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
@@ -6315,13 +6318,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -6331,7 +6334,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B81" s="8">
         <v>46169.5589025463</v>
@@ -6343,7 +6346,7 @@
         <v>46223.57141431713</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
@@ -6370,13 +6373,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q81" s="8">
         <v>46329</v>
@@ -6396,7 +6399,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B82" s="5">
         <v>46169.55890609954</v>
@@ -6408,7 +6411,7 @@
         <v>46223.835960763885</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
@@ -6435,13 +6438,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6451,7 +6454,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B83" s="8">
         <v>46169.55900443287</v>
@@ -6463,7 +6466,7 @@
         <v>46223.57141039352</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>26</v>
@@ -6490,13 +6493,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O83" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P83" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q83" s="8">
         <v>46330</v>
@@ -6516,7 +6519,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B84" s="5">
         <v>46169.55901002315</v>
@@ -6528,7 +6531,7 @@
         <v>46223.57092783565</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
@@ -6555,13 +6558,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q84" s="6"/>
       <c r="R84" s="6"/>
@@ -6571,7 +6574,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B85" s="8">
         <v>46169.55904462963</v>
@@ -6583,7 +6586,7 @@
         <v>46223.5714043287</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>26</v>
@@ -6610,13 +6613,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O85" s="9" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="P85" s="9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q85" s="8">
         <v>46332</v>
@@ -6636,7 +6639,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B86" s="5">
         <v>46169.559050138894</v>
@@ -6648,7 +6651,7 @@
         <v>46223.57102379629</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6675,13 +6678,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6691,7 +6694,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B87" s="8">
         <v>46169.55907484954</v>
@@ -6703,7 +6706,7 @@
         <v>46232.66292771991</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>25</v>
@@ -6727,7 +6730,7 @@
         <v>26</v>
       </c>
       <c r="O87" s="9" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="P87" s="9" t="s">
         <v>26</v>
@@ -6744,7 +6747,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B88" s="5">
         <v>46169.55907863426</v>
@@ -6756,16 +6759,16 @@
         <v>46211.70008446759</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="I88" s="5">
         <v>46335</v>
@@ -6783,13 +6786,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q88" s="5">
         <v>46335</v>
@@ -6809,7 +6812,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B89" s="8">
         <v>46169.55908684028</v>
@@ -6821,16 +6824,16 @@
         <v>46211.700054201385</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H89" s="9" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="I89" s="8">
         <v>46335</v>
@@ -6848,13 +6851,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O89" s="9" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="P89" s="9" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q89" s="9"/>
       <c r="R89" s="9"/>
@@ -6864,7 +6867,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B90" s="5">
         <v>46169.55918673611</v>
@@ -6876,7 +6879,7 @@
         <v>46223.57153153935</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
@@ -6903,13 +6906,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q90" s="5">
         <v>46336</v>
@@ -6929,7 +6932,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B91" s="8">
         <v>46169.55919113426</v>
@@ -6941,7 +6944,7 @@
         <v>46223.57147459491</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>26</v>
@@ -6968,13 +6971,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="9" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="O91" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P91" s="9" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q91" s="9"/>
       <c r="R91" s="9"/>
@@ -6984,7 +6987,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B92" s="5">
         <v>46169.559239560185</v>
@@ -6996,16 +6999,16 @@
         <v>46197.859819363424</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I92" s="5">
         <v>46337</v>
@@ -7023,13 +7026,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q92" s="5">
         <v>46337</v>
@@ -7044,12 +7047,12 @@
         <v>1</v>
       </c>
       <c r="U92" s="12" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B93" s="8">
         <v>46169.559243842596</v>
@@ -7061,16 +7064,16 @@
         <v>46211.830942650464</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="9" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H93" s="9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I93" s="8">
         <v>46337</v>
@@ -7088,13 +7091,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="9" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="O93" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P93" s="9" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q93" s="9"/>
       <c r="R93" s="9"/>
@@ -7104,7 +7107,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B94" s="5">
         <v>46169.55929686343</v>
@@ -7116,16 +7119,16 @@
         <v>46211.86402001158</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I94" s="5">
         <v>46338</v>
@@ -7143,13 +7146,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q94" s="5">
         <v>46338</v>
@@ -7169,7 +7172,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B95" s="8">
         <v>46169.55930180555</v>
@@ -7181,16 +7184,16 @@
         <v>46211.863992280094</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="9" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H95" s="9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I95" s="8">
         <v>46338</v>
@@ -7208,13 +7211,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="9" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="O95" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P95" s="9" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q95" s="9"/>
       <c r="R95" s="9"/>
@@ -7224,7 +7227,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B96" s="5">
         <v>46169.55938721065</v>
@@ -7236,7 +7239,7 @@
         <v>46232.662960601854</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>25</v>
@@ -7260,7 +7263,7 @@
         <v>26</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="P96" s="6" t="s">
         <v>26</v>
@@ -7277,7 +7280,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B97" s="8">
         <v>46169.55939094907</v>
@@ -7289,16 +7292,16 @@
         <v>46232.66294618056</v>
       </c>
       <c r="E97" s="9" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G97" s="9" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H97" s="9" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="I97" s="8">
         <v>46339</v>
@@ -7316,13 +7319,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="9" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="O97" s="9" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="P97" s="9" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q97" s="8">
         <v>46339</v>
@@ -7342,7 +7345,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B98" s="5">
         <v>46169.55939643519</v>
@@ -7354,7 +7357,7 @@
         <v>46232.662950694445</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -7381,13 +7384,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q98" s="5">
         <v>46339</v>

--- a/data/50001557 - ATACAMA KOZAN OT4340.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4340.xlsx
@@ -4818,7 +4818,7 @@
         <v>46190.64495354166</v>
       </c>
       <c r="D56" s="5">
-        <v>46197.83559606482</v>
+        <v>46248.18827115741</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>198</v>
@@ -4862,8 +4862,8 @@
       <c r="R56" s="5">
         <v>46255</v>
       </c>
-      <c r="S56" s="10" t="s">
-        <v>32</v>
+      <c r="S56" s="12" t="s">
+        <v>131</v>
       </c>
       <c r="T56" s="6">
         <v>1</v>
@@ -4948,7 +4948,7 @@
         <v>46198.597692881944</v>
       </c>
       <c r="D58" s="5">
-        <v>46198.59771457176</v>
+        <v>46248.18827105324</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>206</v>
@@ -4992,8 +4992,8 @@
       <c r="R58" s="5">
         <v>46255</v>
       </c>
-      <c r="S58" s="10" t="s">
-        <v>32</v>
+      <c r="S58" s="12" t="s">
+        <v>131</v>
       </c>
       <c r="T58" s="6">
         <v>1</v>
@@ -5078,7 +5078,7 @@
         <v>46198.59771644676</v>
       </c>
       <c r="D60" s="5">
-        <v>46198.59773310185</v>
+        <v>46248.18827099537</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>211</v>
@@ -5122,8 +5122,8 @@
       <c r="R60" s="5">
         <v>46255</v>
       </c>
-      <c r="S60" s="10" t="s">
-        <v>32</v>
+      <c r="S60" s="12" t="s">
+        <v>131</v>
       </c>
       <c r="T60" s="6">
         <v>1</v>

--- a/data/50001557 - ATACAMA KOZAN OT4340.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4340.xlsx
@@ -1786,7 +1786,7 @@
         <v>46181.62347399305</v>
       </c>
       <c r="D6" s="5">
-        <v>46213.7119689699</v>
+        <v>46248.9293791088</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>

--- a/data/50001557 - ATACAMA KOZAN OT4340.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4340.xlsx
@@ -2286,7 +2286,7 @@
         <v>46190.64415828703</v>
       </c>
       <c r="D14" s="5">
-        <v>46190.64417138889</v>
+        <v>46250.10666709491</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>63</v>
@@ -2794,7 +2794,7 @@
         <v>46200.818312083335</v>
       </c>
       <c r="D22" s="5">
-        <v>46200.818425798614</v>
+        <v>46250.11191280093</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>91</v>
@@ -4285,7 +4285,7 @@
         <v>46181.72664483797</v>
       </c>
       <c r="D47" s="8">
-        <v>46197.715420312496</v>
+        <v>46250.128330694446</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>172</v>
@@ -4405,7 +4405,7 @@
         <v>46182.759602164355</v>
       </c>
       <c r="D49" s="8">
-        <v>46238.18899571759</v>
+        <v>46250.12945143519</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>181</v>
@@ -4525,7 +4525,7 @@
         <v>46182.75986146991</v>
       </c>
       <c r="D51" s="8">
-        <v>46239.20354527778</v>
+        <v>46250.12957107639</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>78</v>
@@ -4645,7 +4645,7 @@
         <v>46211.86420568287</v>
       </c>
       <c r="D53" s="8">
-        <v>46211.86422231482</v>
+        <v>46250.12991684028</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>189</v>
@@ -5261,7 +5261,7 @@
         <v>46190.645243935185</v>
       </c>
       <c r="D63" s="8">
-        <v>46244.91622329861</v>
+        <v>46250.130695416665</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>218</v>
@@ -5381,7 +5381,7 @@
         <v>46190.64532476851</v>
       </c>
       <c r="D65" s="8">
-        <v>46197.85387390046</v>
+        <v>46250.13078278935</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>226</v>
@@ -5501,7 +5501,7 @@
         <v>46198.68226086805</v>
       </c>
       <c r="D67" s="8">
-        <v>46205.65959174768</v>
+        <v>46250.130836076394</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>231</v>
@@ -5621,7 +5621,7 @@
         <v>46205.60074232639</v>
       </c>
       <c r="D69" s="8">
-        <v>46211.70953918982</v>
+        <v>46250.12706636574</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>195</v>
@@ -5983,7 +5983,7 @@
         <v>46197.49536869213</v>
       </c>
       <c r="D75" s="8">
-        <v>46223.571425636575</v>
+        <v>46250.13094851852</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>251</v>
@@ -6103,7 +6103,7 @@
         <v>46197.49516923611</v>
       </c>
       <c r="D77" s="8">
-        <v>46223.57142202546</v>
+        <v>46250.13113033565</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>256</v>
@@ -6223,7 +6223,7 @@
         <v>46204.87979715278</v>
       </c>
       <c r="D79" s="8">
-        <v>46223.57141798611</v>
+        <v>46250.1314003588</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>261</v>
@@ -6343,7 +6343,7 @@
         <v>46204.87992821759</v>
       </c>
       <c r="D81" s="8">
-        <v>46223.57141431713</v>
+        <v>46250.131459537035</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>267</v>
@@ -6463,7 +6463,7 @@
         <v>46206.4867090162</v>
       </c>
       <c r="D83" s="8">
-        <v>46223.57141039352</v>
+        <v>46250.13158090277</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>272</v>
@@ -6583,7 +6583,7 @@
         <v>46206.48680728009</v>
       </c>
       <c r="D85" s="8">
-        <v>46223.5714043287</v>
+        <v>46250.131641886575</v>
       </c>
       <c r="E85" s="9" t="s">
         <v>276</v>
@@ -6756,7 +6756,7 @@
         <v>46211.700068715276</v>
       </c>
       <c r="D88" s="5">
-        <v>46211.70008446759</v>
+        <v>46250.13191203703</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>284</v>
@@ -6876,7 +6876,7 @@
         <v>46211.830949814816</v>
       </c>
       <c r="D90" s="5">
-        <v>46223.57153153935</v>
+        <v>46250.132057986106</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>290</v>
@@ -6996,7 +6996,7 @@
         <v>46197.859617372684</v>
       </c>
       <c r="D92" s="5">
-        <v>46197.859819363424</v>
+        <v>46250.13227645833</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>294</v>
@@ -7116,7 +7116,7 @@
         <v>46211.86400608796</v>
       </c>
       <c r="D94" s="5">
-        <v>46211.86402001158</v>
+        <v>46250.132594421295</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>298</v>

--- a/data/50001557 - ATACAMA KOZAN OT4340.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4340.xlsx
@@ -777,7 +777,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t xml:space="preserve">OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200,ot  4390 -ZVN 1-12-110/4 + TOB + REJ </t>
+    <t>OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200,ot  4390 -ZVN 1-12-110/4 + TOB + REJ ,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
   </si>
   <si>
     <t>1215166433625244</t>
@@ -4883,7 +4883,7 @@
         <v>46197.85935881945</v>
       </c>
       <c r="D57" s="8">
-        <v>46197.85937331019</v>
+        <v>46252.20508138889</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>203</v>
@@ -4927,8 +4927,8 @@
       <c r="R57" s="8">
         <v>46259</v>
       </c>
-      <c r="S57" s="10" t="s">
-        <v>32</v>
+      <c r="S57" s="12" t="s">
+        <v>131</v>
       </c>
       <c r="T57" s="9">
         <v>1</v>
@@ -5013,7 +5013,7 @@
         <v>46197.85931310186</v>
       </c>
       <c r="D59" s="8">
-        <v>46198.597709444446</v>
+        <v>46252.205081527776</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>207</v>
@@ -5057,8 +5057,8 @@
       <c r="R59" s="8">
         <v>46259</v>
       </c>
-      <c r="S59" s="10" t="s">
-        <v>32</v>
+      <c r="S59" s="12" t="s">
+        <v>131</v>
       </c>
       <c r="T59" s="9">
         <v>1</v>
@@ -5143,7 +5143,7 @@
         <v>46197.85923987269</v>
       </c>
       <c r="D61" s="8">
-        <v>46198.59773317129</v>
+        <v>46252.20508148149</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>212</v>
@@ -5187,8 +5187,8 @@
       <c r="R61" s="8">
         <v>46259</v>
       </c>
-      <c r="S61" s="10" t="s">
-        <v>32</v>
+      <c r="S61" s="12" t="s">
+        <v>131</v>
       </c>
       <c r="T61" s="9">
         <v>1</v>
@@ -5261,7 +5261,7 @@
         <v>46190.645243935185</v>
       </c>
       <c r="D63" s="8">
-        <v>46250.130695416665</v>
+        <v>46252.55708208334</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>218</v>

--- a/data/50001557 - ATACAMA KOZAN OT4340.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4340.xlsx
@@ -777,7 +777,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t>OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200,ot  4390 -ZVN 1-12-110/4 + TOB + REJ ,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
+    <t>OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200,ot  4390 -ZVN 1-12-110/4 + TOB + REJ ,OT 4391 -ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
   </si>
   <si>
     <t>1215166433625244</t>
@@ -5261,7 +5261,7 @@
         <v>46190.645243935185</v>
       </c>
       <c r="D63" s="8">
-        <v>46252.55708208334</v>
+        <v>46252.698028935185</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>218</v>

--- a/data/50001557 - ATACAMA KOZAN OT4340.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4340.xlsx
@@ -507,217 +507,217 @@
     <t>Fabricacion Corte Laser  OT 4340,Generación OC materiales corte Laser OT 4340</t>
   </si>
   <si>
+    <t>1215166433428453</t>
+  </si>
+  <si>
+    <t>Generación OC materiales corte Laser OT 4340</t>
+  </si>
+  <si>
+    <t>Fabricacion Corte Laser  OT 4340,Materiales corte Laser OT 4340</t>
+  </si>
+  <si>
+    <t>1215166041659706</t>
+  </si>
+  <si>
+    <t>Fabricacion Corte Laser  OT 4340</t>
+  </si>
+  <si>
+    <t>Recepcion materiales corte laser,Materiales corte Laser OT 4340</t>
+  </si>
+  <si>
+    <t>1215166041659726</t>
+  </si>
+  <si>
+    <t>Materiales Corte Plasma  OT 4340</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generación OC Corte Plasma  OT 4340,Fabricación Corte Plasma OT 4340 </t>
+  </si>
+  <si>
+    <t>1215166243334496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Materiales Corte Plasma  OT 4340,Fabricación Corte Plasma OT 4340 </t>
+  </si>
+  <si>
+    <t>1215166243334513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabricación Corte Plasma OT 4340 </t>
+  </si>
+  <si>
+    <t>Recepcion Materiales corte plasma,Materiales Corte Plasma  OT 4340</t>
+  </si>
+  <si>
+    <t>1215166243334594</t>
+  </si>
+  <si>
+    <t>Fabricación Externa  OT 4340</t>
+  </si>
+  <si>
+    <t>Rosemary Singh</t>
+  </si>
+  <si>
+    <t>rosemary.singh@zitron.com</t>
+  </si>
+  <si>
+    <t>Fabricación estructura proveedor externo OT 4340,Generacion OC Fabricación Externa OT 4340</t>
+  </si>
+  <si>
+    <t>1215166243334606</t>
+  </si>
+  <si>
+    <t>Fabricación estructura proveedor externo OT 4340,Fabricación Externa  OT 4340</t>
+  </si>
+  <si>
+    <t>1215165982859560</t>
+  </si>
+  <si>
+    <t>Fabricación estructura proveedor externo OT 4340</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabricación Externa  OT 4340,Control de calidad fabricación externa  OT 4340,Recepcion fabricación externa </t>
+  </si>
+  <si>
+    <t>1215165982859577</t>
+  </si>
+  <si>
+    <t>Control de calidad fabricación externa  OT 4340</t>
+  </si>
+  <si>
+    <t>Nicolás López</t>
+  </si>
+  <si>
+    <t>nicolas.lopez@zitron.com</t>
+  </si>
+  <si>
+    <t>1215165982859589</t>
+  </si>
+  <si>
+    <t>Mecanizado OT 4340</t>
+  </si>
+  <si>
+    <t>Fabricación Mecanizado OT 4340,Generación OC Mecanizado OT 4340</t>
+  </si>
+  <si>
+    <t>1215166433442059</t>
+  </si>
+  <si>
+    <t>Fabricación Mecanizado OT 4340,Mecanizado OT 4340</t>
+  </si>
+  <si>
+    <t>1215166243346004</t>
+  </si>
+  <si>
+    <t>Fabricación Mecanizado OT 4340</t>
+  </si>
+  <si>
+    <t>Recepcion mecanizado,Mecanizado OT 4340</t>
+  </si>
+  <si>
+    <t>1215166243396278</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseñoo:</t>
+  </si>
+  <si>
+    <t>Planos definitivos,Planos preliminar</t>
+  </si>
+  <si>
+    <t>1215166243396290</t>
+  </si>
+  <si>
+    <t>Planos preliminar</t>
+  </si>
+  <si>
+    <t>Gonzalo Javier Dávila Bade</t>
+  </si>
+  <si>
+    <t>gonzalo.davila@zitron.com</t>
+  </si>
+  <si>
+    <t>OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR</t>
+  </si>
+  <si>
+    <t>1215166433496869</t>
+  </si>
+  <si>
+    <t>Hernan Roberto Gutierrez Barrientos</t>
+  </si>
+  <si>
+    <t>hgutierrez@zitron.com</t>
+  </si>
+  <si>
+    <t>OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR,Planos preliminar</t>
+  </si>
+  <si>
+    <t>1215166041791429</t>
+  </si>
+  <si>
+    <t>Planos definitivos</t>
+  </si>
+  <si>
+    <t>1215166041791446</t>
+  </si>
+  <si>
+    <t>OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR,Planos motor proveedor OT 4340</t>
+  </si>
+  <si>
+    <t>Planos definitivos,OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR</t>
+  </si>
+  <si>
+    <t>1215165982964919</t>
+  </si>
+  <si>
+    <t>Propuesta Mecanizado OT 4340,Propuesta Fabricación externa  OT 4340,propuesta Corte Laser OT 4340,Propuesta Corte plasma  OT 4340,OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR,OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR,OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR</t>
+  </si>
+  <si>
+    <t>1215166243476961</t>
+  </si>
+  <si>
+    <t>1215165982983044</t>
+  </si>
+  <si>
+    <t>check pruebas FAT</t>
+  </si>
+  <si>
+    <t>Francisca González Cornejo</t>
+  </si>
+  <si>
+    <t>francisca.gonzalez@zitron.com</t>
+  </si>
+  <si>
+    <t>1215165982983056</t>
+  </si>
+  <si>
+    <t>check pruebas FAT,OT 4335 - ZVN 1-7-37/2 + TOB + REJ</t>
+  </si>
+  <si>
+    <t>1215165983005052</t>
+  </si>
+  <si>
+    <t>Bodega:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recepcion materiales corte laser,Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>1215165983005064</t>
+  </si>
+  <si>
+    <t>Recepcion materiales corte laser</t>
+  </si>
+  <si>
+    <t>Victor Muñoz</t>
+  </si>
+  <si>
+    <t>victor.munoz@zitron.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bodega:,Control de calidad corte laser </t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1215166433428453</t>
-  </si>
-  <si>
-    <t>Generación OC materiales corte Laser OT 4340</t>
-  </si>
-  <si>
-    <t>Fabricacion Corte Laser  OT 4340,Materiales corte Laser OT 4340</t>
-  </si>
-  <si>
-    <t>1215166041659706</t>
-  </si>
-  <si>
-    <t>Fabricacion Corte Laser  OT 4340</t>
-  </si>
-  <si>
-    <t>Recepcion materiales corte laser,Materiales corte Laser OT 4340</t>
-  </si>
-  <si>
-    <t>1215166041659726</t>
-  </si>
-  <si>
-    <t>Materiales Corte Plasma  OT 4340</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generación OC Corte Plasma  OT 4340,Fabricación Corte Plasma OT 4340 </t>
-  </si>
-  <si>
-    <t>1215166243334496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Materiales Corte Plasma  OT 4340,Fabricación Corte Plasma OT 4340 </t>
-  </si>
-  <si>
-    <t>1215166243334513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabricación Corte Plasma OT 4340 </t>
-  </si>
-  <si>
-    <t>Recepcion Materiales corte plasma,Materiales Corte Plasma  OT 4340</t>
-  </si>
-  <si>
-    <t>1215166243334594</t>
-  </si>
-  <si>
-    <t>Fabricación Externa  OT 4340</t>
-  </si>
-  <si>
-    <t>Rosemary Singh</t>
-  </si>
-  <si>
-    <t>rosemary.singh@zitron.com</t>
-  </si>
-  <si>
-    <t>Fabricación estructura proveedor externo OT 4340,Generacion OC Fabricación Externa OT 4340</t>
-  </si>
-  <si>
-    <t>1215166243334606</t>
-  </si>
-  <si>
-    <t>Fabricación estructura proveedor externo OT 4340,Fabricación Externa  OT 4340</t>
-  </si>
-  <si>
-    <t>1215165982859560</t>
-  </si>
-  <si>
-    <t>Fabricación estructura proveedor externo OT 4340</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabricación Externa  OT 4340,Control de calidad fabricación externa  OT 4340,Recepcion fabricación externa </t>
-  </si>
-  <si>
-    <t>1215165982859577</t>
-  </si>
-  <si>
-    <t>Control de calidad fabricación externa  OT 4340</t>
-  </si>
-  <si>
-    <t>Nicolás López</t>
-  </si>
-  <si>
-    <t>nicolas.lopez@zitron.com</t>
-  </si>
-  <si>
-    <t>1215165982859589</t>
-  </si>
-  <si>
-    <t>Mecanizado OT 4340</t>
-  </si>
-  <si>
-    <t>Fabricación Mecanizado OT 4340,Generación OC Mecanizado OT 4340</t>
-  </si>
-  <si>
-    <t>1215166433442059</t>
-  </si>
-  <si>
-    <t>Fabricación Mecanizado OT 4340,Mecanizado OT 4340</t>
-  </si>
-  <si>
-    <t>1215166243346004</t>
-  </si>
-  <si>
-    <t>Fabricación Mecanizado OT 4340</t>
-  </si>
-  <si>
-    <t>Recepcion mecanizado,Mecanizado OT 4340</t>
-  </si>
-  <si>
-    <t>1215166243396278</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseñoo:</t>
-  </si>
-  <si>
-    <t>Planos definitivos,Planos preliminar</t>
-  </si>
-  <si>
-    <t>1215166243396290</t>
-  </si>
-  <si>
-    <t>Planos preliminar</t>
-  </si>
-  <si>
-    <t>Gonzalo Javier Dávila Bade</t>
-  </si>
-  <si>
-    <t>gonzalo.davila@zitron.com</t>
-  </si>
-  <si>
-    <t>OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR</t>
-  </si>
-  <si>
-    <t>1215166433496869</t>
-  </si>
-  <si>
-    <t>Hernan Roberto Gutierrez Barrientos</t>
-  </si>
-  <si>
-    <t>hgutierrez@zitron.com</t>
-  </si>
-  <si>
-    <t>OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR,Planos preliminar</t>
-  </si>
-  <si>
-    <t>1215166041791429</t>
-  </si>
-  <si>
-    <t>Planos definitivos</t>
-  </si>
-  <si>
-    <t>1215166041791446</t>
-  </si>
-  <si>
-    <t>OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR,Planos motor proveedor OT 4340</t>
-  </si>
-  <si>
-    <t>Planos definitivos,OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR</t>
-  </si>
-  <si>
-    <t>1215165982964919</t>
-  </si>
-  <si>
-    <t>Propuesta Mecanizado OT 4340,Propuesta Fabricación externa  OT 4340,propuesta Corte Laser OT 4340,Propuesta Corte plasma  OT 4340,OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR,OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR,OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR</t>
-  </si>
-  <si>
-    <t>1215166243476961</t>
-  </si>
-  <si>
-    <t>1215165982983044</t>
-  </si>
-  <si>
-    <t>check pruebas FAT</t>
-  </si>
-  <si>
-    <t>Francisca González Cornejo</t>
-  </si>
-  <si>
-    <t>francisca.gonzalez@zitron.com</t>
-  </si>
-  <si>
-    <t>1215165982983056</t>
-  </si>
-  <si>
-    <t>check pruebas FAT,OT 4335 - ZVN 1-7-37/2 + TOB + REJ</t>
-  </si>
-  <si>
-    <t>1215165983005052</t>
-  </si>
-  <si>
-    <t>Bodega:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recepcion materiales corte laser,Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>1215165983005064</t>
-  </si>
-  <si>
-    <t>Recepcion materiales corte laser</t>
-  </si>
-  <si>
-    <t>Victor Muñoz</t>
-  </si>
-  <si>
-    <t>victor.munoz@zitron.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bodega:,Control de calidad corte laser </t>
   </si>
   <si>
     <t>1215166329404944</t>
@@ -3465,7 +3465,7 @@
         <v>46184.532628437504</v>
       </c>
       <c r="D33" s="8">
-        <v>46246.19158646991</v>
+        <v>46254.16898400463</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>127</v>
@@ -3509,8 +3509,8 @@
       <c r="R33" s="8">
         <v>46253</v>
       </c>
-      <c r="S33" s="12" t="s">
-        <v>131</v>
+      <c r="S33" s="11" t="s">
+        <v>80</v>
       </c>
       <c r="T33" s="9">
         <v>1</v>
@@ -3521,7 +3521,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B34" s="5">
         <v>46169.558367986116</v>
@@ -3533,7 +3533,7 @@
         <v>46184.53245875</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
@@ -3566,7 +3566,7 @@
         <v>77</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3582,7 +3582,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B35" s="8">
         <v>46169.55837292824</v>
@@ -3594,7 +3594,7 @@
         <v>46184.532615856486</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
@@ -3624,10 +3624,10 @@
         <v>127</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="P35" s="9" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="Q35" s="9"/>
       <c r="R35" s="9"/>
@@ -3643,7 +3643,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B36" s="5">
         <v>46169.55837825232</v>
@@ -3652,10 +3652,10 @@
         <v>46184.53257122685</v>
       </c>
       <c r="D36" s="5">
-        <v>46246.19158778935</v>
+        <v>46254.16898402778</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
@@ -3685,7 +3685,7 @@
         <v>91</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P36" s="6" t="s">
         <v>26</v>
@@ -3696,8 +3696,8 @@
       <c r="R36" s="5">
         <v>46253</v>
       </c>
-      <c r="S36" s="12" t="s">
-        <v>131</v>
+      <c r="S36" s="11" t="s">
+        <v>80</v>
       </c>
       <c r="T36" s="6">
         <v>1</v>
@@ -3708,7 +3708,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B37" s="8">
         <v>46169.558381979165</v>
@@ -3747,13 +3747,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="O37" s="9" t="s">
         <v>82</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="Q37" s="9"/>
       <c r="R37" s="9"/>
@@ -3763,7 +3763,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B38" s="5">
         <v>46169.55838657408</v>
@@ -3775,7 +3775,7 @@
         <v>46184.53255631945</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
@@ -3802,13 +3802,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="O38" s="6" t="s">
         <v>83</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -3818,7 +3818,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B39" s="8">
         <v>46169.55839107639</v>
@@ -3830,16 +3830,16 @@
         <v>46205.600326053245</v>
       </c>
       <c r="E39" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="F39" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G39" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="F39" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G39" s="9" t="s">
+      <c r="H39" s="9" t="s">
         <v>148</v>
-      </c>
-      <c r="H39" s="9" t="s">
-        <v>149</v>
       </c>
       <c r="I39" s="8">
         <v>46241</v>
@@ -3860,7 +3860,7 @@
         <v>91</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P39" s="9" t="s">
         <v>26</v>
@@ -3883,7 +3883,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B40" s="5">
         <v>46169.55839478009</v>
@@ -3901,10 +3901,10 @@
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="H40" s="6" t="s">
         <v>148</v>
-      </c>
-      <c r="H40" s="6" t="s">
-        <v>149</v>
       </c>
       <c r="I40" s="5">
         <v>46241</v>
@@ -3922,13 +3922,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="O40" s="6" t="s">
         <v>88</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -3938,7 +3938,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B41" s="8">
         <v>46169.55839910879</v>
@@ -3950,16 +3950,16 @@
         <v>46195.70375376157</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="H41" s="9" t="s">
         <v>148</v>
-      </c>
-      <c r="H41" s="9" t="s">
-        <v>149</v>
       </c>
       <c r="I41" s="8">
         <v>46252</v>
@@ -3977,13 +3977,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="O41" s="9" t="s">
         <v>89</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="Q41" s="9"/>
       <c r="R41" s="9"/>
@@ -3993,7 +3993,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B42" s="5">
         <v>46169.55840355324</v>
@@ -4005,16 +4005,16 @@
         <v>46205.59994755787</v>
       </c>
       <c r="E42" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="F42" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G42" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="F42" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G42" s="6" t="s">
+      <c r="H42" s="6" t="s">
         <v>158</v>
-      </c>
-      <c r="H42" s="6" t="s">
-        <v>159</v>
       </c>
       <c r="I42" s="5">
         <v>46281</v>
@@ -4032,10 +4032,10 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>26</v>
@@ -4048,7 +4048,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B43" s="8">
         <v>46169.55840677083</v>
@@ -4057,10 +4057,10 @@
         <v>46191.53700108796</v>
       </c>
       <c r="D43" s="8">
-        <v>46246.19158665509</v>
+        <v>46254.168984062504</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
@@ -4090,7 +4090,7 @@
         <v>91</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="P43" s="9" t="s">
         <v>26</v>
@@ -4101,8 +4101,8 @@
       <c r="R43" s="8">
         <v>46253</v>
       </c>
-      <c r="S43" s="12" t="s">
-        <v>131</v>
+      <c r="S43" s="11" t="s">
+        <v>80</v>
       </c>
       <c r="T43" s="9">
         <v>1</v>
@@ -4113,7 +4113,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B44" s="5">
         <v>46169.55841037037</v>
@@ -4152,13 +4152,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="O44" s="6" t="s">
         <v>85</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4168,7 +4168,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B45" s="8">
         <v>46169.558458217594</v>
@@ -4180,7 +4180,7 @@
         <v>46191.53698841435</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>26</v>
@@ -4207,13 +4207,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="O45" s="9" t="s">
         <v>86</v>
       </c>
       <c r="P45" s="9" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="Q45" s="9"/>
       <c r="R45" s="9"/>
@@ -4223,7 +4223,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B46" s="5">
         <v>46169.5584643287</v>
@@ -4235,7 +4235,7 @@
         <v>46240.716379722224</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>25</v>
@@ -4259,7 +4259,7 @@
         <v>26</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4276,7 +4276,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B47" s="8">
         <v>46169.55846813657</v>
@@ -4288,16 +4288,16 @@
         <v>46250.128330694446</v>
       </c>
       <c r="E47" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="F47" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G47" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="F47" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G47" s="9" t="s">
+      <c r="H47" s="9" t="s">
         <v>173</v>
-      </c>
-      <c r="H47" s="9" t="s">
-        <v>174</v>
       </c>
       <c r="I47" s="8">
         <v>46167</v>
@@ -4315,13 +4315,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="Q47" s="8">
         <v>46167</v>
@@ -4341,7 +4341,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B48" s="5">
         <v>46169.558472766206</v>
@@ -4353,16 +4353,16 @@
         <v>46181.72663056713</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="H48" s="6" t="s">
         <v>177</v>
-      </c>
-      <c r="H48" s="6" t="s">
-        <v>178</v>
       </c>
       <c r="I48" s="5">
         <v>46167</v>
@@ -4380,13 +4380,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="O48" s="6" t="s">
         <v>60</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q48" s="6"/>
       <c r="R48" s="6"/>
@@ -4396,7 +4396,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B49" s="8">
         <v>46169.55849938658</v>
@@ -4408,16 +4408,16 @@
         <v>46250.12945143519</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="H49" s="9" t="s">
         <v>173</v>
-      </c>
-      <c r="H49" s="9" t="s">
-        <v>174</v>
       </c>
       <c r="I49" s="8">
         <v>46218</v>
@@ -4435,13 +4435,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="Q49" s="8">
         <v>46218</v>
@@ -4461,7 +4461,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B50" s="5">
         <v>46169.55850371528</v>
@@ -4473,16 +4473,16 @@
         <v>46195.690583055555</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="H50" s="6" t="s">
         <v>177</v>
-      </c>
-      <c r="H50" s="6" t="s">
-        <v>178</v>
       </c>
       <c r="I50" s="5">
         <v>46218</v>
@@ -4500,13 +4500,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="O50" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="P50" s="6" t="s">
         <v>183</v>
-      </c>
-      <c r="P50" s="6" t="s">
-        <v>184</v>
       </c>
       <c r="Q50" s="6"/>
       <c r="R50" s="6"/>
@@ -4516,7 +4516,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B51" s="8">
         <v>46169.55853228009</v>
@@ -4534,10 +4534,10 @@
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="H51" s="9" t="s">
         <v>177</v>
-      </c>
-      <c r="H51" s="9" t="s">
-        <v>178</v>
       </c>
       <c r="I51" s="8">
         <v>46238</v>
@@ -4555,13 +4555,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q51" s="8">
         <v>46238</v>
@@ -4581,7 +4581,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B52" s="5">
         <v>46169.55854641204</v>
@@ -4593,16 +4593,16 @@
         <v>46182.75984881945</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="H52" s="6" t="s">
         <v>177</v>
-      </c>
-      <c r="H52" s="6" t="s">
-        <v>178</v>
       </c>
       <c r="I52" s="5">
         <v>46238</v>
@@ -4623,7 +4623,7 @@
         <v>78</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="P52" s="6" t="s">
         <v>78</v>
@@ -4636,7 +4636,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B53" s="8">
         <v>46169.558565775464</v>
@@ -4648,16 +4648,16 @@
         <v>46250.12991684028</v>
       </c>
       <c r="E53" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="F53" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G53" s="9" t="s">
         <v>189</v>
       </c>
-      <c r="F53" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G53" s="9" t="s">
+      <c r="H53" s="9" t="s">
         <v>190</v>
-      </c>
-      <c r="H53" s="9" t="s">
-        <v>191</v>
       </c>
       <c r="I53" s="8">
         <v>46331</v>
@@ -4675,10 +4675,10 @@
         <v>26</v>
       </c>
       <c r="N53" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="P53" s="9" t="s">
         <v>26</v>
@@ -4701,7 +4701,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B54" s="5">
         <v>46169.55856972223</v>
@@ -4713,16 +4713,16 @@
         <v>46211.86419394676</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="H54" s="6" t="s">
         <v>190</v>
-      </c>
-      <c r="H54" s="6" t="s">
-        <v>191</v>
       </c>
       <c r="I54" s="5">
         <v>46331</v>
@@ -4740,13 +4740,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="Q54" s="6"/>
       <c r="R54" s="6"/>
@@ -4756,7 +4756,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B55" s="8">
         <v>46169.558586307874</v>
@@ -4768,7 +4768,7 @@
         <v>46198.597746307874</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>25</v>
@@ -4792,7 +4792,7 @@
         <v>26</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="P55" s="9" t="s">
         <v>26</v>
@@ -4809,7 +4809,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B56" s="5">
         <v>46169.55858945602</v>
@@ -4821,16 +4821,16 @@
         <v>46248.18827115741</v>
       </c>
       <c r="E56" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="F56" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G56" s="6" t="s">
         <v>198</v>
       </c>
-      <c r="F56" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G56" s="6" t="s">
+      <c r="H56" s="6" t="s">
         <v>199</v>
-      </c>
-      <c r="H56" s="6" t="s">
-        <v>200</v>
       </c>
       <c r="I56" s="5">
         <v>46254</v>
@@ -4848,13 +4848,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="Q56" s="5">
         <v>46254</v>
@@ -4863,7 +4863,7 @@
         <v>46255</v>
       </c>
       <c r="S56" s="12" t="s">
-        <v>131</v>
+        <v>201</v>
       </c>
       <c r="T56" s="6">
         <v>1</v>
@@ -4892,10 +4892,10 @@
         <v>26</v>
       </c>
       <c r="G57" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="H57" s="9" t="s">
         <v>158</v>
-      </c>
-      <c r="H57" s="9" t="s">
-        <v>159</v>
       </c>
       <c r="I57" s="8">
         <v>46258</v>
@@ -4913,10 +4913,10 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="P57" s="9" t="s">
         <v>204</v>
@@ -4928,7 +4928,7 @@
         <v>46259</v>
       </c>
       <c r="S57" s="12" t="s">
-        <v>131</v>
+        <v>201</v>
       </c>
       <c r="T57" s="9">
         <v>1</v>
@@ -4957,10 +4957,10 @@
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="H58" s="6" t="s">
         <v>199</v>
-      </c>
-      <c r="H58" s="6" t="s">
-        <v>200</v>
       </c>
       <c r="I58" s="5">
         <v>46254</v>
@@ -4978,10 +4978,10 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="P58" s="6" t="s">
         <v>207</v>
@@ -4993,7 +4993,7 @@
         <v>46255</v>
       </c>
       <c r="S58" s="12" t="s">
-        <v>131</v>
+        <v>201</v>
       </c>
       <c r="T58" s="6">
         <v>1</v>
@@ -5022,10 +5022,10 @@
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="H59" s="9" t="s">
         <v>158</v>
-      </c>
-      <c r="H59" s="9" t="s">
-        <v>159</v>
       </c>
       <c r="I59" s="8">
         <v>46258</v>
@@ -5043,13 +5043,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="O59" s="9" t="s">
         <v>206</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q59" s="8">
         <v>46258</v>
@@ -5058,7 +5058,7 @@
         <v>46259</v>
       </c>
       <c r="S59" s="12" t="s">
-        <v>131</v>
+        <v>201</v>
       </c>
       <c r="T59" s="9">
         <v>1</v>
@@ -5087,10 +5087,10 @@
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="H60" s="6" t="s">
         <v>199</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>200</v>
       </c>
       <c r="I60" s="5">
         <v>46254</v>
@@ -5108,10 +5108,10 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P60" s="6" t="s">
         <v>212</v>
@@ -5123,7 +5123,7 @@
         <v>46255</v>
       </c>
       <c r="S60" s="12" t="s">
-        <v>131</v>
+        <v>201</v>
       </c>
       <c r="T60" s="6">
         <v>1</v>
@@ -5152,10 +5152,10 @@
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="H61" s="9" t="s">
         <v>158</v>
-      </c>
-      <c r="H61" s="9" t="s">
-        <v>159</v>
       </c>
       <c r="I61" s="8">
         <v>46258</v>
@@ -5173,13 +5173,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="O61" s="9" t="s">
         <v>211</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q61" s="8">
         <v>46258</v>
@@ -5188,7 +5188,7 @@
         <v>46259</v>
       </c>
       <c r="S61" s="12" t="s">
-        <v>131</v>
+        <v>201</v>
       </c>
       <c r="T61" s="9">
         <v>1</v>
@@ -5329,7 +5329,7 @@
         <v>46197.85936673611</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
@@ -5414,7 +5414,7 @@
         <v>215</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="P65" s="9" t="s">
         <v>215</v>
@@ -5449,7 +5449,7 @@
         <v>46197.85915420139</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
@@ -5510,10 +5510,10 @@
         <v>26</v>
       </c>
       <c r="G67" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="H67" s="9" t="s">
         <v>158</v>
-      </c>
-      <c r="H67" s="9" t="s">
-        <v>159</v>
       </c>
       <c r="I67" s="8">
         <v>46274</v>
@@ -5534,7 +5534,7 @@
         <v>215</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="P67" s="9" t="s">
         <v>215</v>
@@ -5569,16 +5569,16 @@
         <v>46205.659588587965</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="H68" s="6" t="s">
         <v>158</v>
-      </c>
-      <c r="H68" s="6" t="s">
-        <v>159</v>
       </c>
       <c r="I68" s="5">
         <v>46274</v>
@@ -5624,7 +5624,7 @@
         <v>46250.12706636574</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>25</v>
@@ -5679,10 +5679,10 @@
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="H70" s="6" t="s">
         <v>199</v>
-      </c>
-      <c r="H70" s="6" t="s">
-        <v>200</v>
       </c>
       <c r="I70" s="5">
         <v>46220</v>
@@ -5700,7 +5700,7 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="O70" s="6" t="s">
         <v>112</v>
@@ -5744,10 +5744,10 @@
         <v>26</v>
       </c>
       <c r="G71" s="9" t="s">
+        <v>198</v>
+      </c>
+      <c r="H71" s="9" t="s">
         <v>199</v>
-      </c>
-      <c r="H71" s="9" t="s">
-        <v>200</v>
       </c>
       <c r="I71" s="8">
         <v>46325</v>
@@ -5765,7 +5765,7 @@
         <v>26</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="O71" s="9" t="s">
         <v>103</v>
@@ -5809,10 +5809,10 @@
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="H72" s="6" t="s">
         <v>199</v>
-      </c>
-      <c r="H72" s="6" t="s">
-        <v>200</v>
       </c>
       <c r="I72" s="5">
         <v>46293</v>
@@ -5830,7 +5830,7 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="O72" s="6" t="s">
         <v>121</v>
@@ -5874,10 +5874,10 @@
         <v>26</v>
       </c>
       <c r="G73" s="9" t="s">
+        <v>198</v>
+      </c>
+      <c r="H73" s="9" t="s">
         <v>199</v>
-      </c>
-      <c r="H73" s="9" t="s">
-        <v>200</v>
       </c>
       <c r="I73" s="8">
         <v>46282</v>
@@ -5895,10 +5895,10 @@
         <v>26</v>
       </c>
       <c r="N73" s="9" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="P73" s="9" t="s">
         <v>246</v>
@@ -6051,7 +6051,7 @@
         <v>46223.57064498843</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
@@ -6136,7 +6136,7 @@
         <v>248</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="P77" s="9" t="s">
         <v>248</v>
@@ -6171,7 +6171,7 @@
         <v>46223.57074214121</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
@@ -6376,7 +6376,7 @@
         <v>248</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="P81" s="9" t="s">
         <v>248</v>
@@ -6411,7 +6411,7 @@
         <v>46223.835960763885</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
@@ -6496,7 +6496,7 @@
         <v>248</v>
       </c>
       <c r="O83" s="9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="P83" s="9" t="s">
         <v>248</v>
@@ -6531,7 +6531,7 @@
         <v>46223.57092783565</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
@@ -6561,7 +6561,7 @@
         <v>272</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="P84" s="6" t="s">
         <v>274</v>
@@ -6681,7 +6681,7 @@
         <v>276</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="P86" s="6" t="s">
         <v>279</v>
@@ -6824,7 +6824,7 @@
         <v>46211.700054201385</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>26</v>
@@ -6909,7 +6909,7 @@
         <v>281</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="P90" s="6" t="s">
         <v>281</v>
@@ -6944,7 +6944,7 @@
         <v>46223.57147459491</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>26</v>
@@ -6974,7 +6974,7 @@
         <v>290</v>
       </c>
       <c r="O91" s="9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="P91" s="9" t="s">
         <v>292</v>
@@ -7029,7 +7029,7 @@
         <v>281</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="P92" s="6" t="s">
         <v>281</v>
@@ -7064,7 +7064,7 @@
         <v>46211.830942650464</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>26</v>
@@ -7094,7 +7094,7 @@
         <v>294</v>
       </c>
       <c r="O93" s="9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="P93" s="9" t="s">
         <v>296</v>
@@ -7149,7 +7149,7 @@
         <v>281</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="P94" s="6" t="s">
         <v>299</v>
@@ -7184,7 +7184,7 @@
         <v>46211.863992280094</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>26</v>
@@ -7214,7 +7214,7 @@
         <v>298</v>
       </c>
       <c r="O95" s="9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="P95" s="9" t="s">
         <v>298</v>

--- a/data/50001557 - ATACAMA KOZAN OT4340.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4340.xlsx
@@ -717,16 +717,16 @@
     <t xml:space="preserve">Bodega:,Control de calidad corte laser </t>
   </si>
   <si>
+    <t>1215166329404944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>Bodega:,OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1215166329404944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>Bodega:,OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR</t>
   </si>
   <si>
     <t>1215166041891869</t>
@@ -4818,7 +4818,7 @@
         <v>46190.64495354166</v>
       </c>
       <c r="D56" s="5">
-        <v>46248.18827115741</v>
+        <v>46256.202002488426</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>197</v>
@@ -4862,8 +4862,8 @@
       <c r="R56" s="5">
         <v>46255</v>
       </c>
-      <c r="S56" s="12" t="s">
-        <v>201</v>
+      <c r="S56" s="11" t="s">
+        <v>80</v>
       </c>
       <c r="T56" s="6">
         <v>1</v>
@@ -4874,7 +4874,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B57" s="8">
         <v>46169.55859488426</v>
@@ -4886,7 +4886,7 @@
         <v>46252.20508138889</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
@@ -4919,7 +4919,7 @@
         <v>197</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="Q57" s="8">
         <v>46258</v>
@@ -4928,7 +4928,7 @@
         <v>46259</v>
       </c>
       <c r="S57" s="12" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="T57" s="9">
         <v>1</v>
@@ -4948,7 +4948,7 @@
         <v>46198.597692881944</v>
       </c>
       <c r="D58" s="5">
-        <v>46248.18827105324</v>
+        <v>46256.2020027199</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>206</v>
@@ -4992,8 +4992,8 @@
       <c r="R58" s="5">
         <v>46255</v>
       </c>
-      <c r="S58" s="12" t="s">
-        <v>201</v>
+      <c r="S58" s="11" t="s">
+        <v>80</v>
       </c>
       <c r="T58" s="6">
         <v>1</v>
@@ -5058,7 +5058,7 @@
         <v>46259</v>
       </c>
       <c r="S59" s="12" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="T59" s="9">
         <v>1</v>
@@ -5078,7 +5078,7 @@
         <v>46198.59771644676</v>
       </c>
       <c r="D60" s="5">
-        <v>46248.18827099537</v>
+        <v>46256.20200275463</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>211</v>
@@ -5122,8 +5122,8 @@
       <c r="R60" s="5">
         <v>46255</v>
       </c>
-      <c r="S60" s="12" t="s">
-        <v>201</v>
+      <c r="S60" s="11" t="s">
+        <v>80</v>
       </c>
       <c r="T60" s="6">
         <v>1</v>
@@ -5188,7 +5188,7 @@
         <v>46259</v>
       </c>
       <c r="S61" s="12" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="T61" s="9">
         <v>1</v>
@@ -5836,7 +5836,7 @@
         <v>121</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="Q72" s="5">
         <v>46293</v>

--- a/data/50001557 - ATACAMA KOZAN OT4340.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4340.xlsx
@@ -2794,7 +2794,7 @@
         <v>46200.818312083335</v>
       </c>
       <c r="D22" s="5">
-        <v>46250.11191280093</v>
+        <v>46256.801152037035</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>91</v>

--- a/data/50001557 - ATACAMA KOZAN OT4340.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4340.xlsx
@@ -777,7 +777,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t>OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200,ot  4390 -ZVN 1-12-110/4 + TOB + REJ ,OT 4391 -ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
+    <t>OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200,ot  4390 -ZVN 1-12-110/4 + TOB + REJ ,OT 4391 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4080 -VENTILADOR ZVNv 1-18-90/6</t>
   </si>
   <si>
     <t>1215166433625244</t>
@@ -5261,7 +5261,7 @@
         <v>46190.645243935185</v>
       </c>
       <c r="D63" s="8">
-        <v>46252.698028935185</v>
+        <v>46258.64932049769</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>218</v>

--- a/data/50001557 - ATACAMA KOZAN OT4340.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4340.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1185" uniqueCount="310">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1185" uniqueCount="309">
   <si>
     <t xml:space="preserve"> 50001557 - ATACAMA KOZAN</t>
   </si>
@@ -724,9 +724,6 @@
   </si>
   <si>
     <t>Bodega:,OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR</t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
   <si>
     <t>1215166041891869</t>
@@ -4883,7 +4880,7 @@
         <v>46197.85935881945</v>
       </c>
       <c r="D57" s="8">
-        <v>46252.20508138889</v>
+        <v>46260.206319432866</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>202</v>
@@ -4927,8 +4924,8 @@
       <c r="R57" s="8">
         <v>46259</v>
       </c>
-      <c r="S57" s="12" t="s">
-        <v>204</v>
+      <c r="S57" s="11" t="s">
+        <v>80</v>
       </c>
       <c r="T57" s="9">
         <v>1</v>
@@ -4939,7 +4936,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B58" s="5">
         <v>46169.55860118056</v>
@@ -4951,7 +4948,7 @@
         <v>46256.2020027199</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
@@ -4984,7 +4981,7 @@
         <v>143</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Q58" s="5">
         <v>46254</v>
@@ -5004,7 +5001,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B59" s="8">
         <v>46169.55860636574</v>
@@ -5013,10 +5010,10 @@
         <v>46197.85931310186</v>
       </c>
       <c r="D59" s="8">
-        <v>46252.205081527776</v>
+        <v>46260.2063193287</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
@@ -5046,7 +5043,7 @@
         <v>194</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="P59" s="9" t="s">
         <v>174</v>
@@ -5057,19 +5054,19 @@
       <c r="R59" s="8">
         <v>46259</v>
       </c>
-      <c r="S59" s="12" t="s">
-        <v>204</v>
+      <c r="S59" s="11" t="s">
+        <v>80</v>
       </c>
       <c r="T59" s="9">
         <v>1</v>
       </c>
       <c r="U59" s="12" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B60" s="5">
         <v>46169.558650127314</v>
@@ -5081,7 +5078,7 @@
         <v>46256.20200275463</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
@@ -5114,7 +5111,7 @@
         <v>165</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="Q60" s="5">
         <v>46254</v>
@@ -5134,7 +5131,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B61" s="8">
         <v>46169.55865608796</v>
@@ -5143,10 +5140,10 @@
         <v>46197.85923987269</v>
       </c>
       <c r="D61" s="8">
-        <v>46252.20508148149</v>
+        <v>46260.20631930555</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
@@ -5176,7 +5173,7 @@
         <v>194</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P61" s="9" t="s">
         <v>174</v>
@@ -5187,19 +5184,19 @@
       <c r="R61" s="8">
         <v>46259</v>
       </c>
-      <c r="S61" s="12" t="s">
-        <v>204</v>
+      <c r="S61" s="11" t="s">
+        <v>80</v>
       </c>
       <c r="T61" s="9">
         <v>1</v>
       </c>
       <c r="U61" s="12" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B62" s="5">
         <v>46169.55866105324</v>
@@ -5211,7 +5208,7 @@
         <v>46198.68229049769</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>25</v>
@@ -5235,7 +5232,7 @@
         <v>26</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P62" s="6" t="s">
         <v>26</v>
@@ -5252,7 +5249,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B63" s="8">
         <v>46169.55866469907</v>
@@ -5264,16 +5261,16 @@
         <v>46258.64932049769</v>
       </c>
       <c r="E63" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="F63" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G63" s="9" t="s">
         <v>218</v>
       </c>
-      <c r="F63" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G63" s="9" t="s">
+      <c r="H63" s="9" t="s">
         <v>219</v>
-      </c>
-      <c r="H63" s="9" t="s">
-        <v>220</v>
       </c>
       <c r="I63" s="8">
         <v>46260</v>
@@ -5291,13 +5288,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="P63" s="9" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="Q63" s="8">
         <v>46260</v>
@@ -5317,7 +5314,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B64" s="5">
         <v>46169.55867099537</v>
@@ -5335,10 +5332,10 @@
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="H64" s="6" t="s">
         <v>219</v>
-      </c>
-      <c r="H64" s="6" t="s">
-        <v>220</v>
       </c>
       <c r="I64" s="5">
         <v>46260</v>
@@ -5356,13 +5353,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="O64" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="P64" s="6" t="s">
         <v>223</v>
-      </c>
-      <c r="P64" s="6" t="s">
-        <v>224</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5372,7 +5369,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B65" s="8">
         <v>46169.558703518516</v>
@@ -5384,16 +5381,16 @@
         <v>46250.13078278935</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="H65" s="9" t="s">
         <v>219</v>
-      </c>
-      <c r="H65" s="9" t="s">
-        <v>220</v>
       </c>
       <c r="I65" s="8">
         <v>46269</v>
@@ -5411,13 +5408,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="O65" s="9" t="s">
         <v>174</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="Q65" s="8">
         <v>46269</v>
@@ -5432,12 +5429,12 @@
         <v>1</v>
       </c>
       <c r="U65" s="12" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B66" s="5">
         <v>46169.55870879629</v>
@@ -5455,10 +5452,10 @@
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="H66" s="6" t="s">
         <v>219</v>
-      </c>
-      <c r="H66" s="6" t="s">
-        <v>220</v>
       </c>
       <c r="I66" s="5">
         <v>46269</v>
@@ -5476,13 +5473,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="O66" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="P66" s="6" t="s">
         <v>228</v>
-      </c>
-      <c r="P66" s="6" t="s">
-        <v>229</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5492,7 +5489,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B67" s="8">
         <v>46169.558740625</v>
@@ -5504,7 +5501,7 @@
         <v>46250.130836076394</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
@@ -5531,13 +5528,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="O67" s="9" t="s">
         <v>174</v>
       </c>
       <c r="P67" s="9" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="Q67" s="8">
         <v>46274</v>
@@ -5552,12 +5549,12 @@
         <v>1</v>
       </c>
       <c r="U67" s="12" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B68" s="5">
         <v>46169.558745243055</v>
@@ -5596,13 +5593,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q68" s="6"/>
       <c r="R68" s="6"/>
@@ -5612,7 +5609,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B69" s="8">
         <v>46169.55876947917</v>
@@ -5648,7 +5645,7 @@
         <v>26</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="P69" s="9" t="s">
         <v>26</v>
@@ -5661,7 +5658,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B70" s="5">
         <v>46169.55880633101</v>
@@ -5673,7 +5670,7 @@
         <v>46224.186405659726</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
@@ -5706,7 +5703,7 @@
         <v>112</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="Q70" s="5">
         <v>46220</v>
@@ -5726,7 +5723,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B71" s="8">
         <v>46169.5588177662</v>
@@ -5738,7 +5735,7 @@
         <v>46200.819831597226</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>26</v>
@@ -5771,7 +5768,7 @@
         <v>103</v>
       </c>
       <c r="P71" s="9" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="Q71" s="8">
         <v>46325</v>
@@ -5791,7 +5788,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B72" s="5">
         <v>46169.55882295139</v>
@@ -5803,7 +5800,7 @@
         <v>46200.81928909722</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
@@ -5856,7 +5853,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B73" s="8">
         <v>46169.55882788195</v>
@@ -5868,7 +5865,7 @@
         <v>46211.7093043287</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>26</v>
@@ -5901,7 +5898,7 @@
         <v>153</v>
       </c>
       <c r="P73" s="9" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="Q73" s="8">
         <v>46282</v>
@@ -5921,7 +5918,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B74" s="5">
         <v>46169.55884254629</v>
@@ -5933,7 +5930,7 @@
         <v>46211.86406403936</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>25</v>
@@ -5957,7 +5954,7 @@
         <v>26</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="P74" s="6" t="s">
         <v>26</v>
@@ -5974,7 +5971,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B75" s="8">
         <v>46169.55884548611</v>
@@ -5986,7 +5983,7 @@
         <v>46250.13094851852</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
@@ -6013,13 +6010,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="Q75" s="8">
         <v>46276</v>
@@ -6034,12 +6031,12 @@
         <v>1</v>
       </c>
       <c r="U75" s="12" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B76" s="5">
         <v>46169.55884993056</v>
@@ -6078,13 +6075,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -6094,7 +6091,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B77" s="8">
         <v>46169.55893170139</v>
@@ -6106,7 +6103,7 @@
         <v>46250.13113033565</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>26</v>
@@ -6133,13 +6130,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="O77" s="9" t="s">
         <v>174</v>
       </c>
       <c r="P77" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="Q77" s="8">
         <v>46296</v>
@@ -6159,7 +6156,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B78" s="5">
         <v>46169.55893543981</v>
@@ -6198,13 +6195,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="O78" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="P78" s="6" t="s">
         <v>258</v>
-      </c>
-      <c r="P78" s="6" t="s">
-        <v>259</v>
       </c>
       <c r="Q78" s="6"/>
       <c r="R78" s="6"/>
@@ -6214,7 +6211,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B79" s="8">
         <v>46169.558869560184</v>
@@ -6226,7 +6223,7 @@
         <v>46250.1314003588</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>26</v>
@@ -6253,13 +6250,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="P79" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="Q79" s="8">
         <v>46328</v>
@@ -6279,7 +6276,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B80" s="5">
         <v>46169.55887296297</v>
@@ -6291,7 +6288,7 @@
         <v>46223.57080435185</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
@@ -6318,13 +6315,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="O80" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="P80" s="6" t="s">
         <v>264</v>
-      </c>
-      <c r="P80" s="6" t="s">
-        <v>265</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -6334,7 +6331,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B81" s="8">
         <v>46169.5589025463</v>
@@ -6346,7 +6343,7 @@
         <v>46250.131459537035</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
@@ -6373,13 +6370,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="O81" s="9" t="s">
         <v>174</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="Q81" s="8">
         <v>46329</v>
@@ -6399,7 +6396,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B82" s="5">
         <v>46169.55890609954</v>
@@ -6438,13 +6435,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="O82" s="6" t="s">
+        <v>268</v>
+      </c>
+      <c r="P82" s="6" t="s">
         <v>269</v>
-      </c>
-      <c r="P82" s="6" t="s">
-        <v>270</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6454,7 +6451,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B83" s="8">
         <v>46169.55900443287</v>
@@ -6466,7 +6463,7 @@
         <v>46250.13158090277</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>26</v>
@@ -6493,13 +6490,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="O83" s="9" t="s">
         <v>174</v>
       </c>
       <c r="P83" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="Q83" s="8">
         <v>46330</v>
@@ -6519,7 +6516,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B84" s="5">
         <v>46169.55901002315</v>
@@ -6558,13 +6555,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="O84" s="6" t="s">
         <v>174</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="Q84" s="6"/>
       <c r="R84" s="6"/>
@@ -6574,7 +6571,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B85" s="8">
         <v>46169.55904462963</v>
@@ -6586,7 +6583,7 @@
         <v>46250.131641886575</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>26</v>
@@ -6613,13 +6610,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="O85" s="9" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="P85" s="9" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="Q85" s="8">
         <v>46332</v>
@@ -6639,7 +6636,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B86" s="5">
         <v>46169.559050138894</v>
@@ -6651,7 +6648,7 @@
         <v>46223.57102379629</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6678,13 +6675,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="O86" s="6" t="s">
         <v>174</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6694,7 +6691,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B87" s="8">
         <v>46169.55907484954</v>
@@ -6706,7 +6703,7 @@
         <v>46232.66292771991</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>25</v>
@@ -6730,7 +6727,7 @@
         <v>26</v>
       </c>
       <c r="O87" s="9" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="P87" s="9" t="s">
         <v>26</v>
@@ -6747,7 +6744,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B88" s="5">
         <v>46169.55907863426</v>
@@ -6759,16 +6756,16 @@
         <v>46250.13191203703</v>
       </c>
       <c r="E88" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="F88" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G88" s="6" t="s">
         <v>284</v>
       </c>
-      <c r="F88" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G88" s="6" t="s">
+      <c r="H88" s="6" t="s">
         <v>285</v>
-      </c>
-      <c r="H88" s="6" t="s">
-        <v>286</v>
       </c>
       <c r="I88" s="5">
         <v>46335</v>
@@ -6786,13 +6783,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="Q88" s="5">
         <v>46335</v>
@@ -6812,7 +6809,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B89" s="8">
         <v>46169.55908684028</v>
@@ -6830,10 +6827,10 @@
         <v>26</v>
       </c>
       <c r="G89" s="9" t="s">
+        <v>284</v>
+      </c>
+      <c r="H89" s="9" t="s">
         <v>285</v>
-      </c>
-      <c r="H89" s="9" t="s">
-        <v>286</v>
       </c>
       <c r="I89" s="8">
         <v>46335</v>
@@ -6851,13 +6848,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="9" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="O89" s="9" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="P89" s="9" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="Q89" s="9"/>
       <c r="R89" s="9"/>
@@ -6867,7 +6864,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B90" s="5">
         <v>46169.55918673611</v>
@@ -6879,7 +6876,7 @@
         <v>46250.132057986106</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
@@ -6906,13 +6903,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="O90" s="6" t="s">
         <v>174</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="Q90" s="5">
         <v>46336</v>
@@ -6932,7 +6929,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B91" s="8">
         <v>46169.55919113426</v>
@@ -6971,13 +6968,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="9" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="O91" s="9" t="s">
         <v>174</v>
       </c>
       <c r="P91" s="9" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="Q91" s="9"/>
       <c r="R91" s="9"/>
@@ -6987,7 +6984,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B92" s="5">
         <v>46169.559239560185</v>
@@ -6999,16 +6996,16 @@
         <v>46250.13227645833</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="H92" s="6" t="s">
         <v>219</v>
-      </c>
-      <c r="H92" s="6" t="s">
-        <v>220</v>
       </c>
       <c r="I92" s="5">
         <v>46337</v>
@@ -7026,13 +7023,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="O92" s="6" t="s">
         <v>174</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="Q92" s="5">
         <v>46337</v>
@@ -7047,12 +7044,12 @@
         <v>1</v>
       </c>
       <c r="U92" s="12" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B93" s="8">
         <v>46169.559243842596</v>
@@ -7070,10 +7067,10 @@
         <v>26</v>
       </c>
       <c r="G93" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="H93" s="9" t="s">
         <v>219</v>
-      </c>
-      <c r="H93" s="9" t="s">
-        <v>220</v>
       </c>
       <c r="I93" s="8">
         <v>46337</v>
@@ -7091,13 +7088,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="9" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="O93" s="9" t="s">
         <v>174</v>
       </c>
       <c r="P93" s="9" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="Q93" s="9"/>
       <c r="R93" s="9"/>
@@ -7107,7 +7104,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B94" s="5">
         <v>46169.55929686343</v>
@@ -7119,16 +7116,16 @@
         <v>46250.132594421295</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="H94" s="6" t="s">
         <v>219</v>
-      </c>
-      <c r="H94" s="6" t="s">
-        <v>220</v>
       </c>
       <c r="I94" s="5">
         <v>46338</v>
@@ -7146,13 +7143,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="O94" s="6" t="s">
         <v>174</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="Q94" s="5">
         <v>46338</v>
@@ -7172,7 +7169,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B95" s="8">
         <v>46169.55930180555</v>
@@ -7190,10 +7187,10 @@
         <v>26</v>
       </c>
       <c r="G95" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="H95" s="9" t="s">
         <v>219</v>
-      </c>
-      <c r="H95" s="9" t="s">
-        <v>220</v>
       </c>
       <c r="I95" s="8">
         <v>46338</v>
@@ -7211,13 +7208,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="9" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="O95" s="9" t="s">
         <v>174</v>
       </c>
       <c r="P95" s="9" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="Q95" s="9"/>
       <c r="R95" s="9"/>
@@ -7227,7 +7224,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B96" s="5">
         <v>46169.55938721065</v>
@@ -7239,7 +7236,7 @@
         <v>46232.662960601854</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>25</v>
@@ -7263,7 +7260,7 @@
         <v>26</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P96" s="6" t="s">
         <v>26</v>
@@ -7280,7 +7277,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B97" s="8">
         <v>46169.55939094907</v>
@@ -7292,16 +7289,16 @@
         <v>46232.66294618056</v>
       </c>
       <c r="E97" s="9" t="s">
+        <v>304</v>
+      </c>
+      <c r="F97" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G97" s="9" t="s">
         <v>305</v>
       </c>
-      <c r="F97" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G97" s="9" t="s">
+      <c r="H97" s="9" t="s">
         <v>306</v>
-      </c>
-      <c r="H97" s="9" t="s">
-        <v>307</v>
       </c>
       <c r="I97" s="8">
         <v>46339</v>
@@ -7319,13 +7316,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="9" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="O97" s="9" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="P97" s="9" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="Q97" s="8">
         <v>46339</v>
@@ -7345,7 +7342,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B98" s="5">
         <v>46169.55939643519</v>
@@ -7357,7 +7354,7 @@
         <v>46232.662950694445</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -7384,13 +7381,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="Q98" s="5">
         <v>46339</v>

--- a/data/50001557 - ATACAMA KOZAN OT4340.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4340.xlsx
@@ -774,7 +774,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t>OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200,ot  4390 -ZVN 1-12-110/4 + TOB + REJ ,OT 4391 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4080 -VENTILADOR ZVNv 1-18-90/6</t>
+    <t>OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200,ot  4390 -ZVN 1-12-110/4 + TOB + REJ ,OT 4391 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4080 -VENTILADOR ZVNv 1-18-90/6</t>
   </si>
   <si>
     <t>1215166433625244</t>
@@ -5258,7 +5258,7 @@
         <v>46190.645243935185</v>
       </c>
       <c r="D63" s="8">
-        <v>46258.64932049769</v>
+        <v>46260.67955321759</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>217</v>

--- a/data/50001557 - ATACAMA KOZAN OT4340.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4340.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1185" uniqueCount="309">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1185" uniqueCount="310">
   <si>
     <t xml:space="preserve"> 50001557 - ATACAMA KOZAN</t>
   </si>
@@ -774,7 +774,10 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t>OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200,ot  4390 -ZVN 1-12-110/4 + TOB + REJ ,OT 4391 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4080 -VENTILADOR ZVNv 1-18-90/6</t>
+    <t xml:space="preserve">OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200,ot  4390 -ZVN 1-12-110/4 + TOB + REJ ,OT 4391 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4080 -VENTILADOR ZVNv 1-18-90/6,OT 4075  -ZVRv 1-16-37/6 ,OT 4413  -ZVRv 1-22-185/6  </t>
+  </si>
+  <si>
+    <t>Media</t>
   </si>
   <si>
     <t>1215166433625244</t>
@@ -5258,7 +5261,7 @@
         <v>46190.645243935185</v>
       </c>
       <c r="D63" s="8">
-        <v>46260.67955321759</v>
+        <v>46261.60082583333</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>217</v>
@@ -5302,8 +5305,8 @@
       <c r="R63" s="8">
         <v>46268</v>
       </c>
-      <c r="S63" s="10" t="s">
-        <v>32</v>
+      <c r="S63" s="12" t="s">
+        <v>221</v>
       </c>
       <c r="T63" s="9">
         <v>1</v>
@@ -5314,7 +5317,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B64" s="5">
         <v>46169.55867099537</v>
@@ -5356,10 +5359,10 @@
         <v>217</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5369,7 +5372,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B65" s="8">
         <v>46169.558703518516</v>
@@ -5381,7 +5384,7 @@
         <v>46250.13078278935</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
@@ -5434,7 +5437,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B66" s="5">
         <v>46169.55870879629</v>
@@ -5473,13 +5476,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5489,7 +5492,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B67" s="8">
         <v>46169.558740625</v>
@@ -5501,7 +5504,7 @@
         <v>46250.130836076394</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
@@ -5554,7 +5557,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B68" s="5">
         <v>46169.558745243055</v>
@@ -5593,13 +5596,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q68" s="6"/>
       <c r="R68" s="6"/>
@@ -5609,7 +5612,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B69" s="8">
         <v>46169.55876947917</v>
@@ -5645,7 +5648,7 @@
         <v>26</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="P69" s="9" t="s">
         <v>26</v>
@@ -5658,7 +5661,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B70" s="5">
         <v>46169.55880633101</v>
@@ -5670,7 +5673,7 @@
         <v>46224.186405659726</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
@@ -5703,7 +5706,7 @@
         <v>112</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q70" s="5">
         <v>46220</v>
@@ -5723,7 +5726,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B71" s="8">
         <v>46169.5588177662</v>
@@ -5735,7 +5738,7 @@
         <v>46200.819831597226</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>26</v>
@@ -5768,7 +5771,7 @@
         <v>103</v>
       </c>
       <c r="P71" s="9" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q71" s="8">
         <v>46325</v>
@@ -5788,7 +5791,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B72" s="5">
         <v>46169.55882295139</v>
@@ -5800,7 +5803,7 @@
         <v>46200.81928909722</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
@@ -5853,7 +5856,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B73" s="8">
         <v>46169.55882788195</v>
@@ -5865,7 +5868,7 @@
         <v>46211.7093043287</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>26</v>
@@ -5898,7 +5901,7 @@
         <v>153</v>
       </c>
       <c r="P73" s="9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q73" s="8">
         <v>46282</v>
@@ -5918,7 +5921,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B74" s="5">
         <v>46169.55884254629</v>
@@ -5930,7 +5933,7 @@
         <v>46211.86406403936</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>25</v>
@@ -5954,7 +5957,7 @@
         <v>26</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="P74" s="6" t="s">
         <v>26</v>
@@ -5971,7 +5974,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B75" s="8">
         <v>46169.55884548611</v>
@@ -5983,7 +5986,7 @@
         <v>46250.13094851852</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
@@ -6010,13 +6013,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q75" s="8">
         <v>46276</v>
@@ -6036,7 +6039,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B76" s="5">
         <v>46169.55884993056</v>
@@ -6075,13 +6078,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -6091,7 +6094,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B77" s="8">
         <v>46169.55893170139</v>
@@ -6103,7 +6106,7 @@
         <v>46250.13113033565</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>26</v>
@@ -6130,13 +6133,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O77" s="9" t="s">
         <v>174</v>
       </c>
       <c r="P77" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q77" s="8">
         <v>46296</v>
@@ -6156,7 +6159,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B78" s="5">
         <v>46169.55893543981</v>
@@ -6195,13 +6198,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q78" s="6"/>
       <c r="R78" s="6"/>
@@ -6211,7 +6214,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B79" s="8">
         <v>46169.558869560184</v>
@@ -6223,7 +6226,7 @@
         <v>46250.1314003588</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>26</v>
@@ -6250,13 +6253,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="P79" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q79" s="8">
         <v>46328</v>
@@ -6276,7 +6279,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B80" s="5">
         <v>46169.55887296297</v>
@@ -6288,7 +6291,7 @@
         <v>46223.57080435185</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
@@ -6315,13 +6318,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -6331,7 +6334,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B81" s="8">
         <v>46169.5589025463</v>
@@ -6343,7 +6346,7 @@
         <v>46250.131459537035</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
@@ -6370,13 +6373,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O81" s="9" t="s">
         <v>174</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q81" s="8">
         <v>46329</v>
@@ -6396,7 +6399,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B82" s="5">
         <v>46169.55890609954</v>
@@ -6435,13 +6438,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6451,7 +6454,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B83" s="8">
         <v>46169.55900443287</v>
@@ -6463,7 +6466,7 @@
         <v>46250.13158090277</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>26</v>
@@ -6490,13 +6493,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O83" s="9" t="s">
         <v>174</v>
       </c>
       <c r="P83" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q83" s="8">
         <v>46330</v>
@@ -6516,7 +6519,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B84" s="5">
         <v>46169.55901002315</v>
@@ -6555,13 +6558,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O84" s="6" t="s">
         <v>174</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q84" s="6"/>
       <c r="R84" s="6"/>
@@ -6571,7 +6574,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B85" s="8">
         <v>46169.55904462963</v>
@@ -6583,7 +6586,7 @@
         <v>46250.131641886575</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>26</v>
@@ -6610,13 +6613,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O85" s="9" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="P85" s="9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q85" s="8">
         <v>46332</v>
@@ -6636,7 +6639,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B86" s="5">
         <v>46169.559050138894</v>
@@ -6648,7 +6651,7 @@
         <v>46223.57102379629</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6675,13 +6678,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O86" s="6" t="s">
         <v>174</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6691,7 +6694,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B87" s="8">
         <v>46169.55907484954</v>
@@ -6703,7 +6706,7 @@
         <v>46232.66292771991</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>25</v>
@@ -6727,7 +6730,7 @@
         <v>26</v>
       </c>
       <c r="O87" s="9" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="P87" s="9" t="s">
         <v>26</v>
@@ -6744,7 +6747,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B88" s="5">
         <v>46169.55907863426</v>
@@ -6756,16 +6759,16 @@
         <v>46250.13191203703</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="I88" s="5">
         <v>46335</v>
@@ -6783,13 +6786,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q88" s="5">
         <v>46335</v>
@@ -6809,7 +6812,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B89" s="8">
         <v>46169.55908684028</v>
@@ -6827,10 +6830,10 @@
         <v>26</v>
       </c>
       <c r="G89" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H89" s="9" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="I89" s="8">
         <v>46335</v>
@@ -6848,13 +6851,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O89" s="9" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="P89" s="9" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q89" s="9"/>
       <c r="R89" s="9"/>
@@ -6864,7 +6867,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B90" s="5">
         <v>46169.55918673611</v>
@@ -6876,7 +6879,7 @@
         <v>46250.132057986106</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
@@ -6903,13 +6906,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O90" s="6" t="s">
         <v>174</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q90" s="5">
         <v>46336</v>
@@ -6929,7 +6932,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B91" s="8">
         <v>46169.55919113426</v>
@@ -6968,13 +6971,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="9" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="O91" s="9" t="s">
         <v>174</v>
       </c>
       <c r="P91" s="9" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q91" s="9"/>
       <c r="R91" s="9"/>
@@ -6984,7 +6987,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B92" s="5">
         <v>46169.559239560185</v>
@@ -6996,7 +6999,7 @@
         <v>46250.13227645833</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
@@ -7023,13 +7026,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O92" s="6" t="s">
         <v>174</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q92" s="5">
         <v>46337</v>
@@ -7049,7 +7052,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B93" s="8">
         <v>46169.559243842596</v>
@@ -7088,13 +7091,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="9" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="O93" s="9" t="s">
         <v>174</v>
       </c>
       <c r="P93" s="9" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q93" s="9"/>
       <c r="R93" s="9"/>
@@ -7104,7 +7107,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B94" s="5">
         <v>46169.55929686343</v>
@@ -7116,7 +7119,7 @@
         <v>46250.132594421295</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
@@ -7143,13 +7146,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O94" s="6" t="s">
         <v>174</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q94" s="5">
         <v>46338</v>
@@ -7169,7 +7172,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B95" s="8">
         <v>46169.55930180555</v>
@@ -7208,13 +7211,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="9" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="O95" s="9" t="s">
         <v>174</v>
       </c>
       <c r="P95" s="9" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q95" s="9"/>
       <c r="R95" s="9"/>
@@ -7224,7 +7227,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B96" s="5">
         <v>46169.55938721065</v>
@@ -7236,7 +7239,7 @@
         <v>46232.662960601854</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>25</v>
@@ -7260,7 +7263,7 @@
         <v>26</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="P96" s="6" t="s">
         <v>26</v>
@@ -7277,7 +7280,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B97" s="8">
         <v>46169.55939094907</v>
@@ -7289,16 +7292,16 @@
         <v>46232.66294618056</v>
       </c>
       <c r="E97" s="9" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G97" s="9" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H97" s="9" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="I97" s="8">
         <v>46339</v>
@@ -7316,13 +7319,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="9" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="O97" s="9" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="P97" s="9" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q97" s="8">
         <v>46339</v>
@@ -7342,7 +7345,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B98" s="5">
         <v>46169.55939643519</v>
@@ -7354,7 +7357,7 @@
         <v>46232.662950694445</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -7381,13 +7384,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q98" s="5">
         <v>46339</v>

--- a/data/50001557 - ATACAMA KOZAN OT4340.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4340.xlsx
@@ -2038,7 +2038,7 @@
         <v>46197.83890001157</v>
       </c>
       <c r="D10" s="5">
-        <v>46197.83892112269</v>
+        <v>46264.096079027775</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>48</v>

--- a/data/50001557 - ATACAMA KOZAN OT4340.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4340.xlsx
@@ -5381,7 +5381,7 @@
         <v>46190.64532476851</v>
       </c>
       <c r="D65" s="8">
-        <v>46250.13078278935</v>
+        <v>46266.190070833334</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>226</v>
@@ -5425,8 +5425,8 @@
       <c r="R65" s="8">
         <v>46273</v>
       </c>
-      <c r="S65" s="10" t="s">
-        <v>32</v>
+      <c r="S65" s="12" t="s">
+        <v>221</v>
       </c>
       <c r="T65" s="9">
         <v>1</v>

--- a/data/50001557 - ATACAMA KOZAN OT4340.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4340.xlsx
@@ -5501,7 +5501,7 @@
         <v>46198.68226086805</v>
       </c>
       <c r="D67" s="8">
-        <v>46250.130836076394</v>
+        <v>46268.20563142361</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>231</v>
@@ -5545,8 +5545,8 @@
       <c r="R67" s="8">
         <v>46275</v>
       </c>
-      <c r="S67" s="10" t="s">
-        <v>32</v>
+      <c r="S67" s="12" t="s">
+        <v>221</v>
       </c>
       <c r="T67" s="9">
         <v>1</v>

--- a/data/50001557 - ATACAMA KOZAN OT4340.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4340.xlsx
@@ -777,22 +777,22 @@
     <t xml:space="preserve">OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200,ot  4390 -ZVN 1-12-110/4 + TOB + REJ ,OT 4391 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4080 -VENTILADOR ZVNv 1-18-90/6,OT 4075  -ZVRv 1-16-37/6 ,OT 4413  -ZVRv 1-22-185/6  </t>
   </si>
   <si>
+    <t>1215166433625244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad Mecanizado,Control de calidad Corte plasma,Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>Preparación Materiales,OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR</t>
+  </si>
+  <si>
+    <t>1215166243563189</t>
+  </si>
+  <si>
+    <t>Armado</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1215166433625244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad Mecanizado,Control de calidad Corte plasma,Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>Preparación Materiales,OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR</t>
-  </si>
-  <si>
-    <t>1215166243563189</t>
-  </si>
-  <si>
-    <t>Armado</t>
   </si>
   <si>
     <t>1215166329517772</t>
@@ -5261,7 +5261,7 @@
         <v>46190.645243935185</v>
       </c>
       <c r="D63" s="8">
-        <v>46261.60082583333</v>
+        <v>46269.174344178246</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>217</v>
@@ -5305,8 +5305,8 @@
       <c r="R63" s="8">
         <v>46268</v>
       </c>
-      <c r="S63" s="12" t="s">
-        <v>221</v>
+      <c r="S63" s="11" t="s">
+        <v>80</v>
       </c>
       <c r="T63" s="9">
         <v>1</v>
@@ -5317,7 +5317,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B64" s="5">
         <v>46169.55867099537</v>
@@ -5359,10 +5359,10 @@
         <v>217</v>
       </c>
       <c r="O64" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="P64" s="6" t="s">
         <v>223</v>
-      </c>
-      <c r="P64" s="6" t="s">
-        <v>224</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5372,7 +5372,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B65" s="8">
         <v>46169.558703518516</v>
@@ -5384,7 +5384,7 @@
         <v>46266.190070833334</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
@@ -5426,7 +5426,7 @@
         <v>46273</v>
       </c>
       <c r="S65" s="12" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="T65" s="9">
         <v>1</v>
@@ -5476,7 +5476,7 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="O66" s="6" t="s">
         <v>228</v>
@@ -5546,7 +5546,7 @@
         <v>46275</v>
       </c>
       <c r="S67" s="12" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="T67" s="9">
         <v>1</v>

--- a/data/50001557 - ATACAMA KOZAN OT4340.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4340.xlsx
@@ -564,6 +564,9 @@
     <t>Fabricación estructura proveedor externo OT 4340,Generacion OC Fabricación Externa OT 4340</t>
   </si>
   <si>
+    <t>Media</t>
+  </si>
+  <si>
     <t>1215166243334606</t>
   </si>
   <si>
@@ -790,9 +793,6 @@
   </si>
   <si>
     <t>Armado</t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
   <si>
     <t>1215166329517772</t>
@@ -3827,7 +3827,7 @@
         <v>46190.64487847222</v>
       </c>
       <c r="D39" s="8">
-        <v>46205.600326053245</v>
+        <v>46274.147179050924</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>146</v>
@@ -3871,8 +3871,8 @@
       <c r="R39" s="8">
         <v>46281</v>
       </c>
-      <c r="S39" s="10" t="s">
-        <v>32</v>
+      <c r="S39" s="12" t="s">
+        <v>150</v>
       </c>
       <c r="T39" s="9">
         <v>1</v>
@@ -3883,7 +3883,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B40" s="5">
         <v>46169.55839478009</v>
@@ -3928,7 +3928,7 @@
         <v>88</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -3938,7 +3938,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B41" s="8">
         <v>46169.55839910879</v>
@@ -3950,7 +3950,7 @@
         <v>46195.70375376157</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
@@ -3983,7 +3983,7 @@
         <v>89</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q41" s="9"/>
       <c r="R41" s="9"/>
@@ -3993,7 +3993,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B42" s="5">
         <v>46169.55840355324</v>
@@ -4005,16 +4005,16 @@
         <v>46205.59994755787</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I42" s="5">
         <v>46281</v>
@@ -4035,7 +4035,7 @@
         <v>146</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>26</v>
@@ -4048,7 +4048,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B43" s="8">
         <v>46169.55840677083</v>
@@ -4060,7 +4060,7 @@
         <v>46254.168984062504</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
@@ -4090,7 +4090,7 @@
         <v>91</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="P43" s="9" t="s">
         <v>26</v>
@@ -4113,7 +4113,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B44" s="5">
         <v>46169.55841037037</v>
@@ -4152,13 +4152,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O44" s="6" t="s">
         <v>85</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4168,7 +4168,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B45" s="8">
         <v>46169.558458217594</v>
@@ -4180,7 +4180,7 @@
         <v>46191.53698841435</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>26</v>
@@ -4207,13 +4207,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O45" s="9" t="s">
         <v>86</v>
       </c>
       <c r="P45" s="9" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q45" s="9"/>
       <c r="R45" s="9"/>
@@ -4223,7 +4223,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B46" s="5">
         <v>46169.5584643287</v>
@@ -4235,7 +4235,7 @@
         <v>46240.716379722224</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>25</v>
@@ -4259,7 +4259,7 @@
         <v>26</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4276,7 +4276,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B47" s="8">
         <v>46169.55846813657</v>
@@ -4288,16 +4288,16 @@
         <v>46250.128330694446</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I47" s="8">
         <v>46167</v>
@@ -4315,13 +4315,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q47" s="8">
         <v>46167</v>
@@ -4341,7 +4341,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B48" s="5">
         <v>46169.558472766206</v>
@@ -4353,16 +4353,16 @@
         <v>46181.72663056713</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I48" s="5">
         <v>46167</v>
@@ -4380,13 +4380,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="O48" s="6" t="s">
         <v>60</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q48" s="6"/>
       <c r="R48" s="6"/>
@@ -4396,7 +4396,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B49" s="8">
         <v>46169.55849938658</v>
@@ -4408,16 +4408,16 @@
         <v>46250.12945143519</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I49" s="8">
         <v>46218</v>
@@ -4435,13 +4435,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q49" s="8">
         <v>46218</v>
@@ -4461,7 +4461,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B50" s="5">
         <v>46169.55850371528</v>
@@ -4473,16 +4473,16 @@
         <v>46195.690583055555</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I50" s="5">
         <v>46218</v>
@@ -4500,13 +4500,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q50" s="6"/>
       <c r="R50" s="6"/>
@@ -4516,7 +4516,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B51" s="8">
         <v>46169.55853228009</v>
@@ -4534,10 +4534,10 @@
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I51" s="8">
         <v>46238</v>
@@ -4555,13 +4555,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q51" s="8">
         <v>46238</v>
@@ -4581,7 +4581,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B52" s="5">
         <v>46169.55854641204</v>
@@ -4593,16 +4593,16 @@
         <v>46182.75984881945</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I52" s="5">
         <v>46238</v>
@@ -4623,7 +4623,7 @@
         <v>78</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P52" s="6" t="s">
         <v>78</v>
@@ -4636,7 +4636,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B53" s="8">
         <v>46169.558565775464</v>
@@ -4648,16 +4648,16 @@
         <v>46250.12991684028</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I53" s="8">
         <v>46331</v>
@@ -4675,10 +4675,10 @@
         <v>26</v>
       </c>
       <c r="N53" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P53" s="9" t="s">
         <v>26</v>
@@ -4701,7 +4701,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B54" s="5">
         <v>46169.55856972223</v>
@@ -4713,16 +4713,16 @@
         <v>46211.86419394676</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I54" s="5">
         <v>46331</v>
@@ -4740,13 +4740,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q54" s="6"/>
       <c r="R54" s="6"/>
@@ -4756,7 +4756,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B55" s="8">
         <v>46169.558586307874</v>
@@ -4768,7 +4768,7 @@
         <v>46198.597746307874</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>25</v>
@@ -4792,7 +4792,7 @@
         <v>26</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="P55" s="9" t="s">
         <v>26</v>
@@ -4809,7 +4809,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B56" s="5">
         <v>46169.55858945602</v>
@@ -4821,16 +4821,16 @@
         <v>46256.202002488426</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I56" s="5">
         <v>46254</v>
@@ -4848,13 +4848,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O56" s="6" t="s">
         <v>135</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q56" s="5">
         <v>46254</v>
@@ -4874,7 +4874,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B57" s="8">
         <v>46169.55859488426</v>
@@ -4886,16 +4886,16 @@
         <v>46260.206319432866</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I57" s="8">
         <v>46258</v>
@@ -4913,13 +4913,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q57" s="8">
         <v>46258</v>
@@ -4939,7 +4939,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B58" s="5">
         <v>46169.55860118056</v>
@@ -4951,16 +4951,16 @@
         <v>46256.2020027199</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I58" s="5">
         <v>46254</v>
@@ -4978,13 +4978,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O58" s="6" t="s">
         <v>143</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q58" s="5">
         <v>46254</v>
@@ -5004,7 +5004,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B59" s="8">
         <v>46169.55860636574</v>
@@ -5016,16 +5016,16 @@
         <v>46260.2063193287</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I59" s="8">
         <v>46258</v>
@@ -5043,13 +5043,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q59" s="8">
         <v>46258</v>
@@ -5064,12 +5064,12 @@
         <v>1</v>
       </c>
       <c r="U59" s="12" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B60" s="5">
         <v>46169.558650127314</v>
@@ -5081,16 +5081,16 @@
         <v>46256.20200275463</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I60" s="5">
         <v>46254</v>
@@ -5108,13 +5108,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q60" s="5">
         <v>46254</v>
@@ -5134,7 +5134,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B61" s="8">
         <v>46169.55865608796</v>
@@ -5146,16 +5146,16 @@
         <v>46260.20631930555</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I61" s="8">
         <v>46258</v>
@@ -5173,13 +5173,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q61" s="8">
         <v>46258</v>
@@ -5194,12 +5194,12 @@
         <v>1</v>
       </c>
       <c r="U61" s="12" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B62" s="5">
         <v>46169.55866105324</v>
@@ -5211,7 +5211,7 @@
         <v>46198.68229049769</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>25</v>
@@ -5235,7 +5235,7 @@
         <v>26</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="P62" s="6" t="s">
         <v>26</v>
@@ -5252,7 +5252,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B63" s="8">
         <v>46169.55866469907</v>
@@ -5264,16 +5264,16 @@
         <v>46269.174344178246</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="9" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H63" s="9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I63" s="8">
         <v>46260</v>
@@ -5291,13 +5291,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P63" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q63" s="8">
         <v>46260</v>
@@ -5317,7 +5317,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B64" s="5">
         <v>46169.55867099537</v>
@@ -5329,16 +5329,16 @@
         <v>46197.85936673611</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I64" s="5">
         <v>46260</v>
@@ -5356,13 +5356,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5372,7 +5372,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B65" s="8">
         <v>46169.558703518516</v>
@@ -5381,19 +5381,19 @@
         <v>46190.64532476851</v>
       </c>
       <c r="D65" s="8">
-        <v>46266.190070833334</v>
+        <v>46274.16343969907</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H65" s="9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I65" s="8">
         <v>46269</v>
@@ -5411,13 +5411,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q65" s="8">
         <v>46269</v>
@@ -5425,14 +5425,14 @@
       <c r="R65" s="8">
         <v>46273</v>
       </c>
-      <c r="S65" s="12" t="s">
-        <v>226</v>
+      <c r="S65" s="11" t="s">
+        <v>80</v>
       </c>
       <c r="T65" s="9">
         <v>1</v>
       </c>
       <c r="U65" s="12" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
@@ -5449,16 +5449,16 @@
         <v>46197.85915420139</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I66" s="5">
         <v>46269</v>
@@ -5476,7 +5476,7 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="O66" s="6" t="s">
         <v>228</v>
@@ -5510,10 +5510,10 @@
         <v>26</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H67" s="9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I67" s="8">
         <v>46274</v>
@@ -5531,13 +5531,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P67" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q67" s="8">
         <v>46274</v>
@@ -5546,13 +5546,13 @@
         <v>46275</v>
       </c>
       <c r="S67" s="12" t="s">
-        <v>226</v>
+        <v>150</v>
       </c>
       <c r="T67" s="9">
         <v>1</v>
       </c>
       <c r="U67" s="12" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
@@ -5569,16 +5569,16 @@
         <v>46205.659588587965</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I68" s="5">
         <v>46274</v>
@@ -5624,7 +5624,7 @@
         <v>46250.12706636574</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>25</v>
@@ -5679,10 +5679,10 @@
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I70" s="5">
         <v>46220</v>
@@ -5700,7 +5700,7 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O70" s="6" t="s">
         <v>112</v>
@@ -5744,10 +5744,10 @@
         <v>26</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H71" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I71" s="8">
         <v>46325</v>
@@ -5765,7 +5765,7 @@
         <v>26</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O71" s="9" t="s">
         <v>103</v>
@@ -5809,10 +5809,10 @@
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I72" s="5">
         <v>46293</v>
@@ -5830,13 +5830,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O72" s="6" t="s">
         <v>121</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q72" s="5">
         <v>46293</v>
@@ -5874,10 +5874,10 @@
         <v>26</v>
       </c>
       <c r="G73" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H73" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I73" s="8">
         <v>46282</v>
@@ -5895,10 +5895,10 @@
         <v>26</v>
       </c>
       <c r="N73" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="P73" s="9" t="s">
         <v>246</v>
@@ -6034,7 +6034,7 @@
         <v>1</v>
       </c>
       <c r="U75" s="12" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
@@ -6051,7 +6051,7 @@
         <v>46223.57064498843</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
@@ -6136,7 +6136,7 @@
         <v>248</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P77" s="9" t="s">
         <v>248</v>
@@ -6171,7 +6171,7 @@
         <v>46223.57074214121</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
@@ -6376,7 +6376,7 @@
         <v>248</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P81" s="9" t="s">
         <v>248</v>
@@ -6411,7 +6411,7 @@
         <v>46223.835960763885</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
@@ -6496,7 +6496,7 @@
         <v>248</v>
       </c>
       <c r="O83" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P83" s="9" t="s">
         <v>248</v>
@@ -6531,7 +6531,7 @@
         <v>46223.57092783565</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
@@ -6561,7 +6561,7 @@
         <v>272</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P84" s="6" t="s">
         <v>274</v>
@@ -6681,7 +6681,7 @@
         <v>276</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P86" s="6" t="s">
         <v>279</v>
@@ -6824,7 +6824,7 @@
         <v>46211.700054201385</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>26</v>
@@ -6909,7 +6909,7 @@
         <v>281</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P90" s="6" t="s">
         <v>281</v>
@@ -6944,7 +6944,7 @@
         <v>46223.57147459491</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>26</v>
@@ -6974,7 +6974,7 @@
         <v>290</v>
       </c>
       <c r="O91" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P91" s="9" t="s">
         <v>292</v>
@@ -7005,10 +7005,10 @@
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I92" s="5">
         <v>46337</v>
@@ -7029,7 +7029,7 @@
         <v>281</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P92" s="6" t="s">
         <v>281</v>
@@ -7047,7 +7047,7 @@
         <v>1</v>
       </c>
       <c r="U92" s="12" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
@@ -7064,16 +7064,16 @@
         <v>46211.830942650464</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="9" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H93" s="9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I93" s="8">
         <v>46337</v>
@@ -7094,7 +7094,7 @@
         <v>294</v>
       </c>
       <c r="O93" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P93" s="9" t="s">
         <v>296</v>
@@ -7125,10 +7125,10 @@
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I94" s="5">
         <v>46338</v>
@@ -7149,7 +7149,7 @@
         <v>281</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P94" s="6" t="s">
         <v>299</v>
@@ -7184,16 +7184,16 @@
         <v>46211.863992280094</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="9" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H95" s="9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I95" s="8">
         <v>46338</v>
@@ -7214,7 +7214,7 @@
         <v>298</v>
       </c>
       <c r="O95" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P95" s="9" t="s">
         <v>298</v>

--- a/data/50001557 - ATACAMA KOZAN OT4340.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4340.xlsx
@@ -5865,7 +5865,7 @@
         <v>46211.70928436343</v>
       </c>
       <c r="D73" s="8">
-        <v>46211.7093043287</v>
+        <v>46275.13273378472</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>245</v>
@@ -5909,8 +5909,8 @@
       <c r="R73" s="8">
         <v>46282</v>
       </c>
-      <c r="S73" s="10" t="s">
-        <v>32</v>
+      <c r="S73" s="12" t="s">
+        <v>150</v>
       </c>
       <c r="T73" s="9">
         <v>1</v>

--- a/data/50001557 - ATACAMA KOZAN OT4340.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4340.xlsx
@@ -5501,7 +5501,7 @@
         <v>46198.68226086805</v>
       </c>
       <c r="D67" s="8">
-        <v>46268.20563142361</v>
+        <v>46276.14507925926</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>231</v>
@@ -5545,8 +5545,8 @@
       <c r="R67" s="8">
         <v>46275</v>
       </c>
-      <c r="S67" s="12" t="s">
-        <v>150</v>
+      <c r="S67" s="11" t="s">
+        <v>80</v>
       </c>
       <c r="T67" s="9">
         <v>1</v>
